--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tab1_KPI" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Update yellow cells with your notebook results, then upload to GitHub.</t>
+          <t>Auto-generated from Jupyter notebook on 2026-04-15</t>
         </is>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1,78 +1,296 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373CE9BC-CED8-4448-8DC2-0B4BD37EF3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tab1_KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
+    <sheet name="Tab2_Regional" sheetId="2" r:id="rId2"/>
+    <sheet name="Tab3_Campaign" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
+  <si>
+    <t>Tab 1 — KPI Cards (MTD)</t>
+  </si>
+  <si>
+    <t>Update yellow cells daily with your notebook results.</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Invoca Leads</t>
+  </si>
+  <si>
+    <t>build_source != Web</t>
+  </si>
+  <si>
+    <t>Form Leads</t>
+  </si>
+  <si>
+    <t>build_source == Web</t>
+  </si>
+  <si>
+    <t>CRM Leads (Total)</t>
+  </si>
+  <si>
+    <t>Invoca + Form</t>
+  </si>
+  <si>
+    <t>Appointments</t>
+  </si>
+  <si>
+    <t>Milestone 214</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Matched to webinvoices</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Tab 2 — Regional Office Performance (MTD)</t>
+  </si>
+  <si>
+    <t>One row per regional office. Update daily.</t>
+  </si>
+  <si>
+    <t>Regional Office</t>
+  </si>
+  <si>
+    <t>Unique Leads</t>
+  </si>
+  <si>
+    <t>New Leads</t>
+  </si>
+  <si>
+    <t>Apt</t>
+  </si>
+  <si>
+    <t>Quote</t>
+  </si>
+  <si>
+    <t>Sales Amount</t>
+  </si>
+  <si>
+    <t>NL Customers</t>
+  </si>
+  <si>
+    <t>NL Sales</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Bay Area</t>
+  </si>
+  <si>
+    <t>CDR</t>
+  </si>
+  <si>
+    <t>Central Coast</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Fresno</t>
+  </si>
+  <si>
+    <t>Inland Empire</t>
+  </si>
+  <si>
+    <t>Las Vegas</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>Pasadena</t>
+  </si>
+  <si>
+    <t>Sacramento</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Ventura/SB County</t>
+  </si>
+  <si>
+    <t>Tab 3 — Campaign Performance</t>
+  </si>
+  <si>
+    <t>One row per campaign per month. Add historical months for trend charts.</t>
+  </si>
+  <si>
+    <t>Campaign</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Clicks</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Conversions</t>
+  </si>
+  <si>
+    <t>Leads</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>ROI %</t>
+  </si>
+  <si>
+    <t>(TWC) LifeSource Brand</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>AZ - Tucson Single Form</t>
+  </si>
+  <si>
+    <t>Bay Area Single Form</t>
+  </si>
+  <si>
+    <t>PMAX 1 - LA</t>
+  </si>
+  <si>
+    <t>Las Vegas Single Form</t>
+  </si>
+  <si>
+    <t>Orange County Single Form</t>
+  </si>
+  <si>
+    <t>PMAX 2 - NoCal</t>
+  </si>
+  <si>
+    <t>Pasadena Single Form</t>
+  </si>
+  <si>
+    <t>RLSA - All</t>
+  </si>
+  <si>
+    <t>Ventura County Single Form</t>
+  </si>
+  <si>
+    <t>National Sales Team</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF111827"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="14"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00111827"/>
-        <bgColor rgb="00111827"/>
+        <fgColor rgb="FF111827"/>
+        <bgColor rgb="FF111827"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEFCE8"/>
-        <bgColor rgb="00FEFCE8"/>
+        <fgColor rgb="FFFEFCE8"/>
+        <bgColor rgb="FFFEFCE8"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,96 +306,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -465,135 +629,1621 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tab 1 — Daily KPI Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Auto-generated from Jupyter notebook on 2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Invoca Leads</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
+    <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>95</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5">
+        <v>454</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5">
+        <v>549</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5">
+        <v>209</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>47</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46132</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="9" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="5">
+        <v>53</v>
+      </c>
+      <c r="C5" s="5">
+        <v>51</v>
+      </c>
+      <c r="D5" s="5">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5">
+        <v>7</v>
+      </c>
+      <c r="G5" s="8">
+        <v>51999.8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>7</v>
+      </c>
+      <c r="I5" s="8">
+        <v>51999.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="5">
+        <v>78</v>
+      </c>
+      <c r="C7" s="5">
+        <v>73</v>
+      </c>
+      <c r="D7" s="5">
+        <v>31</v>
+      </c>
+      <c r="E7" s="5">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7</v>
+      </c>
+      <c r="G7" s="8">
+        <v>40905.56</v>
+      </c>
+      <c r="H7" s="5">
+        <v>6</v>
+      </c>
+      <c r="I7" s="8">
+        <v>40755.56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8">
+        <v>729</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="5">
+        <v>54</v>
+      </c>
+      <c r="C12" s="5">
+        <v>49</v>
+      </c>
+      <c r="D12" s="5">
+        <v>25</v>
+      </c>
+      <c r="E12" s="5">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8">
+        <v>40077.94</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="8">
+        <v>32156.94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5">
+        <v>23</v>
+      </c>
+      <c r="D13" s="5">
+        <v>10</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8">
+        <v>12943.84</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="8">
+        <v>12943.84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="5">
+        <v>64</v>
+      </c>
+      <c r="C14" s="5">
         <v>62</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>build_source != Web</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Form Leads</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>build_source == Web</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CRM Leads (Total)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Invoca + Form</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Appointments</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Milestone 214, created minus cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Matched to webinvoices</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>20</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
+        <v>7499</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8">
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>47</v>
+      </c>
+      <c r="C15" s="5">
+        <v>40</v>
+      </c>
+      <c r="D15" s="5">
+        <v>29</v>
+      </c>
+      <c r="E15" s="5">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5">
+        <v>9</v>
+      </c>
+      <c r="G15" s="8">
+        <v>71454.61</v>
+      </c>
+      <c r="H15" s="5">
+        <v>7</v>
+      </c>
+      <c r="I15" s="8">
+        <v>55280.61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5">
+        <v>83</v>
+      </c>
+      <c r="C16" s="5">
+        <v>72</v>
+      </c>
+      <c r="D16" s="5">
+        <v>33</v>
+      </c>
+      <c r="E16" s="5">
+        <v>20</v>
+      </c>
+      <c r="F16" s="5">
+        <v>8</v>
+      </c>
+      <c r="G16" s="8">
+        <v>61182</v>
+      </c>
+      <c r="H16" s="5">
+        <v>8</v>
+      </c>
+      <c r="I16" s="8">
+        <v>61182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5">
+        <v>32</v>
+      </c>
+      <c r="C17" s="5">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>8166</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>8166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5">
+        <v>10</v>
+      </c>
+      <c r="E18" s="5">
+        <v>4</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <v>8641</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5">
+        <v>8641</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5">
+        <v>16</v>
+      </c>
+      <c r="E19" s="5">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2</v>
+      </c>
+      <c r="G19" s="5">
+        <v>13015.8</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5">
+        <v>13015.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
+        <v>18</v>
+      </c>
+      <c r="D20" s="5">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5">
+        <v>3</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5">
+        <v>16532</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5">
+        <v>16532</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="11" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1431</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2209</v>
+      </c>
+      <c r="F5" s="5">
+        <v>110</v>
+      </c>
+      <c r="G5" s="5">
+        <v>58</v>
+      </c>
+      <c r="H5" s="5">
+        <v>25</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5">
+        <v>47427</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1380</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2150</v>
+      </c>
+      <c r="F6" s="5">
+        <v>105</v>
+      </c>
+      <c r="G6" s="5">
+        <v>55</v>
+      </c>
+      <c r="H6" s="5">
+        <v>23</v>
+      </c>
+      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5">
+        <v>44000</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1310</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2050</v>
+      </c>
+      <c r="F7" s="5">
+        <v>98</v>
+      </c>
+      <c r="G7" s="5">
+        <v>52</v>
+      </c>
+      <c r="H7" s="5">
+        <v>21</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="5">
+        <v>41000</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1250</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1980</v>
+      </c>
+      <c r="F8" s="5">
+        <v>92</v>
+      </c>
+      <c r="G8" s="5">
+        <v>48</v>
+      </c>
+      <c r="H8" s="5">
+        <v>19</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4</v>
+      </c>
+      <c r="J8" s="5">
+        <v>38000</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1250</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1950</v>
+      </c>
+      <c r="F9" s="5">
+        <v>95</v>
+      </c>
+      <c r="G9" s="5">
+        <v>50</v>
+      </c>
+      <c r="H9" s="5">
+        <v>22</v>
+      </c>
+      <c r="I9" s="5">
+        <v>5</v>
+      </c>
+      <c r="J9" s="5">
+        <v>42000</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5">
+        <v>224</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3164</v>
+      </c>
+      <c r="F10" s="5">
+        <v>15</v>
+      </c>
+      <c r="G10" s="5">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5">
+        <v>210</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2980</v>
+      </c>
+      <c r="F11" s="5">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5">
+        <v>7</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="5">
+        <v>198</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2800</v>
+      </c>
+      <c r="F12" s="5">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5">
+        <v>7</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="5">
+        <v>794</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9648</v>
+      </c>
+      <c r="F13" s="5">
+        <v>33</v>
+      </c>
+      <c r="G13" s="5">
+        <v>25</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>7072</v>
+      </c>
+      <c r="K13" s="5">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="5">
+        <v>750</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9100</v>
+      </c>
+      <c r="F14" s="5">
+        <v>30</v>
+      </c>
+      <c r="G14" s="5">
+        <v>23</v>
+      </c>
+      <c r="H14" s="5">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>6800</v>
+      </c>
+      <c r="K14" s="5">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="5">
+        <v>700</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8500</v>
+      </c>
+      <c r="F15" s="5">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5">
+        <v>22</v>
+      </c>
+      <c r="H15" s="5">
+        <v>4</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>6500</v>
+      </c>
+      <c r="K15" s="5">
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1673</v>
+      </c>
+      <c r="E16" s="5">
+        <v>12122</v>
+      </c>
+      <c r="F16" s="5">
+        <v>34</v>
+      </c>
+      <c r="G16" s="5">
+        <v>23</v>
+      </c>
+      <c r="H16" s="5">
+        <v>9</v>
+      </c>
+      <c r="I16" s="5">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5">
+        <v>22277</v>
+      </c>
+      <c r="K16" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1580</v>
+      </c>
+      <c r="E17" s="5">
+        <v>11500</v>
+      </c>
+      <c r="F17" s="5">
+        <v>32</v>
+      </c>
+      <c r="G17" s="5">
+        <v>21</v>
+      </c>
+      <c r="H17" s="5">
+        <v>8</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3</v>
+      </c>
+      <c r="J17" s="5">
+        <v>21000</v>
+      </c>
+      <c r="K17" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1470</v>
+      </c>
+      <c r="E18" s="5">
+        <v>10600</v>
+      </c>
+      <c r="F18" s="5">
+        <v>30</v>
+      </c>
+      <c r="G18" s="5">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5">
+        <v>8</v>
+      </c>
+      <c r="I18" s="5">
+        <v>2</v>
+      </c>
+      <c r="J18" s="5">
+        <v>19500</v>
+      </c>
+      <c r="K18" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="5">
+        <v>414</v>
+      </c>
+      <c r="E19" s="5">
+        <v>5437</v>
+      </c>
+      <c r="F19" s="5">
+        <v>25</v>
+      </c>
+      <c r="G19" s="5">
+        <v>11</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5">
+        <v>6453</v>
+      </c>
+      <c r="K19" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="5">
+        <v>390</v>
+      </c>
+      <c r="E20" s="5">
+        <v>5100</v>
+      </c>
+      <c r="F20" s="5">
+        <v>23</v>
+      </c>
+      <c r="G20" s="5">
+        <v>10</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5">
+        <v>6200</v>
+      </c>
+      <c r="K20" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="5">
+        <v>365</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4800</v>
+      </c>
+      <c r="F21" s="5">
+        <v>21</v>
+      </c>
+      <c r="G21" s="5">
+        <v>9</v>
+      </c>
+      <c r="H21" s="5">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5">
+        <v>5900</v>
+      </c>
+      <c r="K21" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="5">
+        <v>910</v>
+      </c>
+      <c r="E22" s="5">
+        <v>11060</v>
+      </c>
+      <c r="F22" s="5">
+        <v>37</v>
+      </c>
+      <c r="G22" s="5">
+        <v>11</v>
+      </c>
+      <c r="H22" s="5">
+        <v>9</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="5">
+        <v>850</v>
+      </c>
+      <c r="E23" s="5">
+        <v>10300</v>
+      </c>
+      <c r="F23" s="5">
+        <v>34</v>
+      </c>
+      <c r="G23" s="5">
+        <v>10</v>
+      </c>
+      <c r="H23" s="5">
+        <v>8</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3049</v>
+      </c>
+      <c r="E24" s="5">
+        <v>13006</v>
+      </c>
+      <c r="F24" s="5">
+        <v>65</v>
+      </c>
+      <c r="G24" s="5">
+        <v>36</v>
+      </c>
+      <c r="H24" s="5">
+        <v>10</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1</v>
+      </c>
+      <c r="J24" s="5">
+        <v>6572</v>
+      </c>
+      <c r="K24" s="5">
+        <v>-49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2800</v>
+      </c>
+      <c r="E25" s="5">
+        <v>12000</v>
+      </c>
+      <c r="F25" s="5">
+        <v>60</v>
+      </c>
+      <c r="G25" s="5">
+        <v>33</v>
+      </c>
+      <c r="H25" s="5">
+        <v>9</v>
+      </c>
+      <c r="I25" s="5">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5">
+        <v>6200</v>
+      </c>
+      <c r="K25" s="5">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1152</v>
+      </c>
+      <c r="E26" s="5">
+        <v>13657</v>
+      </c>
+      <c r="F26" s="5">
+        <v>65</v>
+      </c>
+      <c r="G26" s="5">
+        <v>25</v>
+      </c>
+      <c r="H26" s="5">
+        <v>5</v>
+      </c>
+      <c r="I26" s="5">
+        <v>2</v>
+      </c>
+      <c r="J26" s="5">
+        <v>8133</v>
+      </c>
+      <c r="K26" s="5">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1080</v>
+      </c>
+      <c r="E27" s="5">
+        <v>12800</v>
+      </c>
+      <c r="F27" s="5">
+        <v>60</v>
+      </c>
+      <c r="G27" s="5">
+        <v>23</v>
+      </c>
+      <c r="H27" s="5">
+        <v>5</v>
+      </c>
+      <c r="I27" s="5">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5">
+        <v>7800</v>
+      </c>
+      <c r="K27" s="5">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="5">
+        <v>273</v>
+      </c>
+      <c r="E28" s="5">
+        <v>3055</v>
+      </c>
+      <c r="F28" s="5">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5">
+        <v>6</v>
+      </c>
+      <c r="H28" s="5">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5">
+        <v>7794</v>
+      </c>
+      <c r="K28" s="5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="5">
+        <v>255</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2850</v>
+      </c>
+      <c r="F29" s="5">
+        <v>13</v>
+      </c>
+      <c r="G29" s="5">
+        <v>5</v>
+      </c>
+      <c r="H29" s="5">
+        <v>2</v>
+      </c>
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5">
+        <v>7200</v>
+      </c>
+      <c r="K29" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="5">
+        <v>264</v>
+      </c>
+      <c r="E30" s="5">
+        <v>4112</v>
+      </c>
+      <c r="F30" s="5">
+        <v>19</v>
+      </c>
+      <c r="G30" s="5">
+        <v>7</v>
+      </c>
+      <c r="H30" s="5">
+        <v>3</v>
+      </c>
+      <c r="I30" s="5">
+        <v>2</v>
+      </c>
+      <c r="J30" s="5">
+        <v>16532</v>
+      </c>
+      <c r="K30" s="5">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="5">
+        <v>245</v>
+      </c>
+      <c r="E31" s="5">
+        <v>3850</v>
+      </c>
+      <c r="F31" s="5">
+        <v>17</v>
+      </c>
+      <c r="G31" s="5">
+        <v>6</v>
+      </c>
+      <c r="H31" s="5">
+        <v>3</v>
+      </c>
+      <c r="I31" s="5">
+        <v>2</v>
+      </c>
+      <c r="J31" s="5">
+        <v>15800</v>
+      </c>
+      <c r="K31" s="5">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -11,6 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab2_Regional" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab3_Campaign" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_MTD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Brand" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Search" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Display" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1_Local" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3366,4 +3370,1252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Brand awareness — (TWC) LifeSource Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow=TY | Blue=LY MTD | Green=LY Full Month | Purple=Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TY (this year MTD)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LY MTD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LY Full Month</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cost ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>980</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>850</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Invoca Leads</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>build_source != Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Form Leads</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>build_source == Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CRM Leads (Total)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Invoca + Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Milestone 214</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Webinvoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Apt</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>736</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>665</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Search — HVAC campaigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow=TY | Blue=LY MTD | Green=LY Full Month | Purple=Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TY (this year MTD)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LY MTD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LY Full Month</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cost ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2210</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Invoca Leads</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>build_source != Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Form Leads</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>build_source == Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CRM Leads (Total)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Invoca + Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Milestone 214</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Webinvoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Apt</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Display retargeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow=TY | Blue=LY MTD | Green=LY Full Month | Purple=Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TY (this year MTD)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LY MTD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LY Full Month</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cost ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>890</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Invoca Leads</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>build_source != Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Form Leads</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>build_source == Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CRM Leads (Total)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Invoca + Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Milestone 214</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Webinvoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Apt</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>695</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Local services ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow=TY | Blue=LY MTD | Green=LY Full Month | Purple=Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TY (this year MTD)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LY MTD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LY Full Month</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Cost ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>590</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Invoca Leads</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>build_source != Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Form Leads</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>build_source == Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CRM Leads (Total)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Invoca + Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Milestone 214</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Webinvoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Lead</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cost per Apt</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>576</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>544</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Your calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,12 @@
         <bgColor rgb="00FDF4FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7ED"/>
+        <bgColor rgb="00FFF7ED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -102,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +128,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,42 +504,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tab 1 — KPI Data (all campaigns in one sheet)</t>
+          <t>Tab 1 — KPI Data</t>
         </is>
       </c>
     </row>
@@ -544,7 +557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Yellow=TY MTD  |  Blue=LY MTD  |  Green=LY Full Month  |  Purple=Budget</t>
+          <t>Yellow=TY MTD | Blue=LY MTD | Green=LY Full Month | Purple=Budget | Orange=Last Month Full</t>
         </is>
       </c>
     </row>
@@ -561,19 +574,19 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>TY Conv Invoca</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>TY Conv Form</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>TY Cost</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>TY Invoca</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>TY Form</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>TY Leads</t>
@@ -581,105 +594,125 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>TY CRM Invoca</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>TY CRM Form</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>TY Apt</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>TY Cust</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>TY CPL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>TY CPA</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>TY ROI%</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>LY MTD Conv</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>LY MTD Cost</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>LY MTD Leads</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>LY MTD Apt</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>LY MTD Cust</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>LY MTD CPL</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>LY MTD CPA</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>LY MTD ROI%</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>LY Full Conv</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>LY Full Cost</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>LY Full Leads</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>LY Full Apt</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>LY Full Cust</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Budget Conv</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Budget Cost</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>LM Full Leads</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>LM Full Apt</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -695,78 +728,90 @@
         <v>110</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>4820</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>454</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>549</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>454</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="L6" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>688</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="O6" s="6" t="n">
         <v>4200</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>185</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="S6" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="T6" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="U6" s="6" t="n">
         <v>638</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="V6" s="7" t="n">
         <v>280</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="W6" s="7" t="n">
         <v>12800</v>
       </c>
-      <c r="V6" s="7" t="n">
+      <c r="X6" s="7" t="n">
         <v>1240</v>
       </c>
-      <c r="W6" s="7" t="n">
+      <c r="Y6" s="7" t="n">
         <v>498</v>
       </c>
-      <c r="X6" s="7" t="n">
+      <c r="Z6" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="Y6" s="8" t="n">
+      <c r="AA6" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="Z6" s="8" t="n">
+      <c r="AB6" s="8" t="n">
         <v>15000</v>
       </c>
-      <c r="AA6" s="9" t="inlineStr">
+      <c r="AC6" s="9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AD6" s="9" t="n">
+        <v>520</v>
+      </c>
+      <c r="AE6" s="10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -782,78 +827,90 @@
         <v>42</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>980</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>46</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>736</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="O7" s="6" t="n">
         <v>850</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="R7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="S7" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="T7" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="U7" s="6" t="n">
         <v>665</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="V7" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="W7" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="V7" s="7" t="n">
+      <c r="X7" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="W7" s="7" t="n">
+      <c r="Y7" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="X7" s="7" t="n">
+      <c r="Z7" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="Y7" s="8" t="n">
+      <c r="AA7" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="Z7" s="8" t="n">
+      <c r="AB7" s="8" t="n">
         <v>2500</v>
       </c>
-      <c r="AA7" s="9" t="inlineStr">
+      <c r="AC7" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AD7" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE7" s="10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -869,78 +926,90 @@
         <v>76</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>2210</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>32</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>83</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="K8" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="L8" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>669</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="O8" s="6" t="n">
         <v>1980</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="S8" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="T8" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="U8" s="6" t="n">
         <v>632</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>210</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>6500</v>
       </c>
       <c r="V8" s="7" t="n">
         <v>210</v>
       </c>
       <c r="W8" s="7" t="n">
+        <v>6500</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="Y8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="X8" s="7" t="n">
+      <c r="Z8" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Y8" s="8" t="n">
+      <c r="AA8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="Z8" s="8" t="n">
+      <c r="AB8" s="8" t="n">
         <v>5500</v>
       </c>
-      <c r="AA8" s="9" t="inlineStr">
+      <c r="AC8" s="9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AD8" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE8" s="10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -956,78 +1025,90 @@
         <v>38</v>
       </c>
       <c r="C9" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>890</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>16</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>41</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="K9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="L9" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>777</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>780</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="R9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="S9" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="T9" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="U9" s="6" t="n">
         <v>695</v>
-      </c>
-      <c r="T9" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>2500</v>
       </c>
       <c r="V9" s="7" t="n">
         <v>120</v>
       </c>
       <c r="W9" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="X9" s="7" t="n">
+      <c r="Z9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Y9" s="8" t="n">
+      <c r="AA9" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="Z9" s="8" t="n">
+      <c r="AB9" s="8" t="n">
         <v>2200</v>
       </c>
-      <c r="AA9" s="9" t="inlineStr">
+      <c r="AC9" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="AE9" s="10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1043,80 +1124,99 @@
         <v>28</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>740</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>10</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>31</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>576</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>590</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="T10" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>544</v>
-      </c>
-      <c r="T10" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="U10" s="7" t="n">
-        <v>1800</v>
       </c>
       <c r="V10" s="7" t="n">
         <v>90</v>
       </c>
       <c r="W10" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Y10" s="8" t="n">
+      <c r="AA10" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="Z10" s="8" t="n">
+      <c r="AB10" s="8" t="n">
         <v>1900</v>
       </c>
-      <c r="AA10" s="9" t="inlineStr">
+      <c r="AC10" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AD10" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE10" s="10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Yellow=TY | Blue=LY MTD | Green=LY Full | Purple=Budget | Orange=LM Full</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1307,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
@@ -1238,7 +1338,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
@@ -1269,7 +1369,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Bay Area</t>
         </is>
@@ -1300,7 +1400,7 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>CDR</t>
         </is>
@@ -1331,7 +1431,7 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Central Coast</t>
         </is>
@@ -1362,7 +1462,7 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
@@ -1393,7 +1493,7 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
@@ -1424,7 +1524,7 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Inland Empire</t>
         </is>
@@ -1455,7 +1555,7 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
@@ -1486,7 +1586,7 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>National Sales</t>
         </is>
@@ -1517,7 +1617,7 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Orange County</t>
         </is>
@@ -1548,7 +1648,7 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Pasadena</t>
         </is>
@@ -1579,7 +1679,7 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
@@ -1610,7 +1710,7 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
@@ -1641,7 +1741,7 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
@@ -1672,7 +1772,7 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Ventura/SB County</t>
         </is>
@@ -1713,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1739,7 +1839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per campaign per month. Add historical data for trend charts.</t>
+          <t>One row per campaign per month.</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1901,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>(TWC) LifeSource Brand</t>
         </is>
@@ -1840,7 +1940,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>(TWC) LifeSource Brand</t>
         </is>
@@ -1879,48 +1979,48 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>(TWC) LifeSource Brand</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1310</v>
+        <v>1250</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2050</v>
+        <v>1950</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>5</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1900</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>(TWC) LifeSource Brand</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>AZ - Tucson Single Form</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -1928,38 +2028,38 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1250</v>
+        <v>224</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1980</v>
+        <v>3164</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1820</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>(TWC) LifeSource Brand</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>AZ - Tucson Single Form</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -1971,34 +2071,34 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1250</v>
+        <v>198</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1950</v>
+        <v>2800</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1850</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>AZ - Tucson Single Form</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Bay Area Single Form</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -2010,34 +2110,34 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>224</v>
+        <v>794</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3164</v>
+        <v>9648</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-100</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>AZ - Tucson Single Form</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Bay Area Single Form</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -2049,34 +2149,34 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>198</v>
+        <v>700</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2800</v>
+        <v>8500</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-100</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Bay Area Single Form</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>PMAX 1 - LA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -2088,34 +2188,34 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>794</v>
+        <v>1673</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>9648</v>
+        <v>12122</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>7072</v>
+        <v>22277</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Bay Area Single Form</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>PMAX 1 - LA</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -2127,34 +2227,34 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>700</v>
+        <v>1470</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>8500</v>
+        <v>10600</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>6500</v>
+        <v>19500</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>PMAX 1 - LA</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Las Vegas Single Form</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -2166,34 +2266,34 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1673</v>
+        <v>414</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>12122</v>
+        <v>5437</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>22277</v>
+        <v>6453</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>PMAX 1 - LA</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Las Vegas Single Form</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -2205,34 +2305,34 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1470</v>
+        <v>365</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>10600</v>
+        <v>4800</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>19500</v>
+        <v>5900</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Las Vegas Single Form</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Orange County Single Form</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -2244,34 +2344,34 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>414</v>
+        <v>910</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5437</v>
+        <v>11060</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6453</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>19</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Las Vegas Single Form</t>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Orange County Single Form</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -2283,34 +2383,34 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>365</v>
+        <v>850</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>4800</v>
+        <v>10300</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Orange County Single Form</t>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Ventura County Single Form</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -2322,34 +2422,34 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>910</v>
+        <v>264</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>11060</v>
+        <v>4112</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>16532</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-100</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Orange County Single Form</t>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Ventura County Single Form</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -2361,105 +2461,27 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>850</v>
+        <v>245</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10300</v>
+        <v>3850</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Ventura County Single Form</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>264</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>4112</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>16532</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Ventura County Single Form</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>245</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>3850</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>15800</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>290</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346084E8-3E88-4DEB-9758-06FB7B6BB6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0272B7-C553-4A4C-A9AA-80C995D28831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="120">
   <si>
     <t>Tab 1 — KPI Data</t>
   </si>
@@ -381,111 +381,6 @@
   </si>
   <si>
     <t>inf</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-31</t>
-  </si>
-  <si>
-    <t>2026-04-32</t>
-  </si>
-  <si>
-    <t>2026-04-33</t>
-  </si>
-  <si>
-    <t>2026-04-34</t>
-  </si>
-  <si>
-    <t>2026-04-35</t>
-  </si>
-  <si>
-    <t>2026-04-36</t>
-  </si>
-  <si>
-    <t>2026-04-37</t>
-  </si>
-  <si>
-    <t>2026-04-38</t>
-  </si>
-  <si>
-    <t>2026-04-39</t>
-  </si>
-  <si>
-    <t>2026-04-40</t>
-  </si>
-  <si>
-    <t>2026-04-41</t>
-  </si>
-  <si>
-    <t>2026-04-42</t>
-  </si>
-  <si>
-    <t>2026-04-43</t>
-  </si>
-  <si>
-    <t>2026-04-44</t>
-  </si>
-  <si>
-    <t>2026-04-45</t>
-  </si>
-  <si>
-    <t>2026-04-46</t>
-  </si>
-  <si>
-    <t>2026-04-47</t>
-  </si>
-  <si>
-    <t>2026-04-48</t>
-  </si>
-  <si>
-    <t>2026-04-49</t>
-  </si>
-  <si>
-    <t>2026-04-50</t>
-  </si>
-  <si>
-    <t>2026-04-51</t>
-  </si>
-  <si>
-    <t>2026-04-52</t>
-  </si>
-  <si>
-    <t>2026-04-53</t>
-  </si>
-  <si>
-    <t>2026-04-54</t>
-  </si>
-  <si>
-    <t>2026-04-55</t>
-  </si>
-  <si>
-    <t>2026-04-56</t>
   </si>
   <si>
     <t>National Sales Team</t>
@@ -602,15 +497,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1055,2670 +947,2670 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:31" s="11" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>1230.73</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>657.3</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>573.42999999999995</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>255190.71</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>544</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>94</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>450</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>205</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>46</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
         <v>469</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <v>1244</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
         <v>27</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>788.74999999999977</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>150950.10000000006</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>683</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>207</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="5">
         <v>54</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>221</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="5">
         <v>729</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="5">
         <v>136</v>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="6">
         <v>1308.3900000000001</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="6">
         <v>228581.82000000004</v>
       </c>
-      <c r="X6" s="7">
+      <c r="X6" s="6">
         <v>1052</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="6">
         <v>333</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Z6" s="6">
         <v>54</v>
       </c>
-      <c r="AA6" s="8">
+      <c r="AA6" s="7">
         <v>350</v>
       </c>
-      <c r="AB6" s="8">
+      <c r="AB6" s="7">
         <v>15000</v>
       </c>
-      <c r="AC6" s="9">
+      <c r="AC6" s="8">
         <v>1350</v>
       </c>
-      <c r="AD6" s="9">
+      <c r="AD6" s="8">
         <v>520</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AE6" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:31" s="11" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>185.34</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>101.59</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>83.75</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>3186.05</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>100</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>24</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>76</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>47</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>17</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>31.86</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <v>67.790000000000006</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
         <v>4034</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>137.85</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>7408.4</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>223</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="5">
         <v>45</v>
       </c>
-      <c r="R7" s="6">
+      <c r="R7" s="5">
         <v>18</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="5">
         <v>33.22</v>
       </c>
-      <c r="T7" s="6">
+      <c r="T7" s="5">
         <v>164.63</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="5">
         <v>1436</v>
       </c>
-      <c r="V7" s="7">
+      <c r="V7" s="6">
         <v>180.34</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="6">
         <v>11126.61</v>
       </c>
-      <c r="X7" s="7">
+      <c r="X7" s="6">
         <v>362</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="6">
         <v>82</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7" s="6">
         <v>18</v>
       </c>
-      <c r="AA7" s="8">
+      <c r="AA7" s="7">
         <v>110</v>
       </c>
-      <c r="AB7" s="8">
+      <c r="AB7" s="7">
         <v>2500</v>
       </c>
-      <c r="AC7" s="9">
+      <c r="AC7" s="8">
         <v>110</v>
       </c>
-      <c r="AD7" s="9">
+      <c r="AD7" s="8">
         <v>32</v>
       </c>
-      <c r="AE7" s="10" t="s">
+      <c r="AE7" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:31" s="11" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="5">
         <v>105.47</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <v>20472.32</v>
       </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="7">
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="6">
         <v>174.59</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="6">
         <v>29000.33</v>
       </c>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="8">
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="7">
         <v>100</v>
       </c>
-      <c r="AB8" s="8">
+      <c r="AB8" s="7">
         <v>5500</v>
       </c>
-      <c r="AC8" s="9">
+      <c r="AC8" s="8">
         <v>220</v>
       </c>
-      <c r="AD8" s="9">
+      <c r="AD8" s="8">
         <v>55</v>
       </c>
-      <c r="AE8" s="10" t="s">
+      <c r="AE8" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:31" s="11" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>21.96</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>9.99</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>11.97</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>5416.04</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>12</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>12</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>6</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>1</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
         <v>451.34</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="4">
         <v>902.67</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="4">
         <v>50</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>11.5</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>1727.67</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <v>7</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="5">
         <v>3</v>
       </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>246.81</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="5">
         <v>575.89</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="5">
         <v>-100</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9" s="6">
         <v>13</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="6">
         <v>2836.17</v>
       </c>
-      <c r="X9" s="7">
+      <c r="X9" s="6">
         <v>11</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="6">
         <v>7</v>
       </c>
-      <c r="Z9" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="8">
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
         <v>55</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AB9" s="7">
         <v>2200</v>
       </c>
-      <c r="AC9" s="9">
+      <c r="AC9" s="8">
         <v>130</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AD9" s="8">
         <v>35</v>
       </c>
-      <c r="AE9" s="10" t="s">
+      <c r="AE9" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:31" s="11" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>114.37</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>66.989999999999995</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>47.38</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>27315.15</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>39</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>8</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>31</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>12</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>1</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>700.39</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>2276.2600000000002</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>-74</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>20.65</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>4677.78</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <v>57</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>24</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="5">
         <v>6</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="5">
         <v>82.07</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="5">
         <v>194.91</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="5">
         <v>750</v>
       </c>
-      <c r="V10" s="7">
+      <c r="V10" s="6">
         <v>26.65</v>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="6">
         <v>6253.57</v>
       </c>
-      <c r="X10" s="7">
+      <c r="X10" s="6">
         <v>83</v>
       </c>
-      <c r="Y10" s="7">
+      <c r="Y10" s="6">
         <v>31</v>
       </c>
-      <c r="Z10" s="7">
+      <c r="Z10" s="6">
         <v>6</v>
       </c>
-      <c r="AA10" s="8">
+      <c r="AA10" s="7">
         <v>40</v>
       </c>
-      <c r="AB10" s="8">
+      <c r="AB10" s="7">
         <v>1900</v>
       </c>
-      <c r="AC10" s="9">
+      <c r="AC10" s="8">
         <v>95</v>
       </c>
-      <c r="AD10" s="9">
+      <c r="AD10" s="8">
         <v>22</v>
       </c>
-      <c r="AE10" s="10" t="s">
+      <c r="AE10" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="11">
         <v>20.07</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="11">
         <v>13327.42</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="11">
         <v>29.05</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="11">
         <v>18828.98</v>
       </c>
-      <c r="AA11" s="8">
+      <c r="AA11" s="7">
         <v>40</v>
       </c>
-      <c r="AB11" s="8">
+      <c r="AB11" s="7">
         <v>1900</v>
       </c>
-      <c r="AC11" s="9">
+      <c r="AC11" s="8">
         <v>95</v>
       </c>
-      <c r="AD11" s="9">
+      <c r="AD11" s="8">
         <v>22</v>
       </c>
-      <c r="AE11" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="AE11" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="11">
         <v>26.3</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="11">
         <v>3269.69</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="11">
         <v>13</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="11">
         <v>3</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="11">
         <v>1</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="11">
         <v>251.51</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="11">
         <v>1089.9000000000001</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="11">
         <v>70</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="11">
         <v>73.209999999999994</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="11">
         <v>6655.75</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="11">
         <v>18</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="11">
         <v>5</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="11">
         <v>1</v>
       </c>
-      <c r="AA12" s="8">
+      <c r="AA12" s="7">
         <v>40</v>
       </c>
-      <c r="AB12" s="8">
+      <c r="AB12" s="7">
         <v>1900</v>
       </c>
-      <c r="AC12" s="9">
+      <c r="AC12" s="8">
         <v>95</v>
       </c>
-      <c r="AD12" s="9">
+      <c r="AD12" s="8">
         <v>22</v>
       </c>
-      <c r="AE12" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="AE12" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="11">
         <v>3.98</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="11">
         <v>541.13</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="11">
         <v>16</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="11">
         <v>3</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="11">
         <v>1</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="11">
         <v>33.82</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="11">
         <v>180.38</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="11">
         <v>1149</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="11">
         <v>5.98</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="11">
         <v>833.66</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="11">
         <v>20</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="11">
         <v>6</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="11">
         <v>1</v>
       </c>
-      <c r="AA13" s="8">
+      <c r="AA13" s="7">
         <v>40</v>
       </c>
-      <c r="AB13" s="8">
+      <c r="AB13" s="7">
         <v>1900</v>
       </c>
-      <c r="AC13" s="9">
+      <c r="AC13" s="8">
         <v>95</v>
       </c>
-      <c r="AD13" s="9">
+      <c r="AD13" s="8">
         <v>22</v>
       </c>
-      <c r="AE13" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="AE13" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="11">
         <v>7.0299999999999896</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="11">
         <v>3853.98</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="11">
         <v>10.02</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="11">
         <v>5445.86</v>
       </c>
-      <c r="AA14" s="8">
+      <c r="AA14" s="7">
         <v>40</v>
       </c>
-      <c r="AB14" s="8">
+      <c r="AB14" s="7">
         <v>1900</v>
       </c>
-      <c r="AC14" s="9">
+      <c r="AC14" s="8">
         <v>95</v>
       </c>
-      <c r="AD14" s="9">
+      <c r="AD14" s="8">
         <v>22</v>
       </c>
-      <c r="AE14" s="10" t="s">
+      <c r="AE14" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="11">
+        <v>14</v>
+      </c>
+      <c r="O15" s="11">
+        <v>648.91</v>
+      </c>
+      <c r="V15" s="11">
+        <v>16</v>
+      </c>
+      <c r="W15" s="11">
+        <v>1036.27</v>
+      </c>
+      <c r="AA15" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE15" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="11">
+        <v>3</v>
+      </c>
+      <c r="C16" s="11">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1061.96</v>
+      </c>
+      <c r="N16" s="11">
+        <v>2</v>
+      </c>
+      <c r="O16" s="11">
+        <v>304.22000000000003</v>
+      </c>
+      <c r="P16" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>1</v>
+      </c>
+      <c r="R16" s="11">
+        <v>0</v>
+      </c>
+      <c r="S16" s="11">
+        <v>101.41</v>
+      </c>
+      <c r="T16" s="11">
+        <v>304.22000000000003</v>
+      </c>
+      <c r="U16" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V16" s="11">
+        <v>3</v>
+      </c>
+      <c r="W16" s="11">
+        <v>422.36</v>
+      </c>
+      <c r="X16" s="11">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC16" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD16" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="11">
+        <v>47.03</v>
+      </c>
+      <c r="C17" s="11">
+        <v>15</v>
+      </c>
+      <c r="D17" s="11">
+        <v>32.03</v>
+      </c>
+      <c r="E17" s="11">
+        <v>13237.97</v>
+      </c>
+      <c r="F17" s="11">
+        <v>32</v>
+      </c>
+      <c r="G17" s="11">
+        <v>6</v>
+      </c>
+      <c r="H17" s="11">
+        <v>26</v>
+      </c>
+      <c r="I17" s="11">
+        <v>10</v>
+      </c>
+      <c r="J17" s="11">
+        <v>4</v>
+      </c>
+      <c r="K17" s="11">
+        <v>413.69</v>
+      </c>
+      <c r="L17" s="11">
+        <v>1323.8</v>
+      </c>
+      <c r="M17" s="11">
+        <v>104</v>
+      </c>
+      <c r="N17" s="11">
+        <v>46.99</v>
+      </c>
+      <c r="O17" s="11">
+        <v>10879.93</v>
+      </c>
+      <c r="P17" s="11">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>18</v>
+      </c>
+      <c r="R17" s="11">
+        <v>0</v>
+      </c>
+      <c r="S17" s="11">
+        <v>190.88</v>
+      </c>
+      <c r="T17" s="11">
+        <v>604.44000000000005</v>
+      </c>
+      <c r="U17" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V17" s="11">
+        <v>61.03</v>
+      </c>
+      <c r="W17" s="11">
+        <v>15298.11</v>
+      </c>
+      <c r="X17" s="11">
+        <v>79</v>
+      </c>
+      <c r="Y17" s="11">
+        <v>29</v>
+      </c>
+      <c r="Z17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC17" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD17" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="N18" s="11">
+        <v>25</v>
+      </c>
+      <c r="O18" s="11">
+        <v>2044.61</v>
+      </c>
+      <c r="P18" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>6</v>
+      </c>
+      <c r="R18" s="11">
+        <v>1</v>
+      </c>
+      <c r="S18" s="11">
+        <v>120.27</v>
+      </c>
+      <c r="T18" s="11">
+        <v>340.77</v>
+      </c>
+      <c r="U18" s="11">
+        <v>264</v>
+      </c>
+      <c r="V18" s="11">
+        <v>54</v>
+      </c>
+      <c r="W18" s="11">
+        <v>5213.1000000000004</v>
+      </c>
+      <c r="X18" s="11">
+        <v>26</v>
+      </c>
+      <c r="Y18" s="11">
+        <v>11</v>
+      </c>
+      <c r="Z18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC18" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD18" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" s="11">
+        <v>10</v>
+      </c>
+      <c r="O19" s="11">
+        <v>1100.05</v>
+      </c>
+      <c r="P19" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>4</v>
+      </c>
+      <c r="R19" s="11">
+        <v>1</v>
+      </c>
+      <c r="S19" s="11">
+        <v>110</v>
+      </c>
+      <c r="T19" s="11">
+        <v>275.01</v>
+      </c>
+      <c r="U19" s="11">
+        <v>679</v>
+      </c>
+      <c r="V19" s="11">
+        <v>10</v>
+      </c>
+      <c r="W19" s="11">
+        <v>1552.36</v>
+      </c>
+      <c r="X19" s="11">
+        <v>11</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC19" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD19" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE19" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N20" s="11">
+        <v>3</v>
+      </c>
+      <c r="O20" s="11">
+        <v>475.21</v>
+      </c>
+      <c r="V20" s="11">
+        <v>3</v>
+      </c>
+      <c r="W20" s="11">
+        <v>912.36</v>
+      </c>
+      <c r="AA20" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC20" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD20" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE20" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="N21" s="11">
+        <v>9</v>
+      </c>
+      <c r="O21" s="11">
+        <v>2521.44</v>
+      </c>
+      <c r="V21" s="11">
+        <v>15</v>
+      </c>
+      <c r="W21" s="11">
+        <v>3696.93</v>
+      </c>
+      <c r="AA21" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC21" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD21" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="11">
+        <v>61.43</v>
+      </c>
+      <c r="C22" s="11">
+        <v>21.32</v>
+      </c>
+      <c r="D22" s="11">
+        <v>40.11</v>
+      </c>
+      <c r="E22" s="11">
+        <v>15607.52</v>
+      </c>
+      <c r="F22" s="11">
+        <v>43</v>
+      </c>
+      <c r="G22" s="11">
+        <v>5</v>
+      </c>
+      <c r="H22" s="11">
+        <v>38</v>
+      </c>
+      <c r="I22" s="11">
+        <v>20</v>
+      </c>
+      <c r="J22" s="11">
+        <v>4</v>
+      </c>
+      <c r="K22" s="11">
+        <v>362.97</v>
+      </c>
+      <c r="L22" s="11">
+        <v>780.38</v>
+      </c>
+      <c r="M22" s="11">
+        <v>59</v>
+      </c>
+      <c r="AA22" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB22" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC22" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD22" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE22" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="11">
+        <v>3</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2</v>
+      </c>
+      <c r="E23" s="11">
+        <v>2100.29</v>
+      </c>
+      <c r="AA23" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE23" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="11">
+        <v>108.72</v>
+      </c>
+      <c r="C24" s="11">
+        <v>100.72</v>
+      </c>
+      <c r="D24" s="11">
+        <v>8</v>
+      </c>
+      <c r="E24" s="11">
+        <v>25478.66</v>
+      </c>
+      <c r="F24" s="11">
+        <v>11</v>
+      </c>
+      <c r="G24" s="11">
+        <v>5</v>
+      </c>
+      <c r="H24" s="11">
+        <v>6</v>
+      </c>
+      <c r="I24" s="11">
+        <v>3</v>
+      </c>
+      <c r="J24" s="11">
+        <v>2</v>
+      </c>
+      <c r="K24" s="11">
+        <v>2316.2399999999998</v>
+      </c>
+      <c r="L24" s="11">
+        <v>8492.89</v>
+      </c>
+      <c r="M24" s="11">
+        <v>-70</v>
+      </c>
+      <c r="AA24" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB24" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC24" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD24" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE24" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="11">
+        <v>9</v>
+      </c>
+      <c r="C25" s="11">
+        <v>2</v>
+      </c>
+      <c r="D25" s="11">
+        <v>7</v>
+      </c>
+      <c r="E25" s="11">
+        <v>4087.49</v>
+      </c>
+      <c r="F25" s="11">
+        <v>9</v>
+      </c>
+      <c r="G25" s="11">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11">
+        <v>8</v>
+      </c>
+      <c r="I25" s="11">
+        <v>2</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11">
+        <v>454.17</v>
+      </c>
+      <c r="L25" s="11">
+        <v>2043.74</v>
+      </c>
+      <c r="M25" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N25" s="11">
+        <v>9</v>
+      </c>
+      <c r="O25" s="11">
+        <v>1700.93</v>
+      </c>
+      <c r="V25" s="11">
+        <v>16</v>
+      </c>
+      <c r="W25" s="11">
+        <v>2548.09</v>
+      </c>
+      <c r="AA25" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC25" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD25" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE25" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="C26" s="11">
+        <v>4</v>
+      </c>
+      <c r="D26" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="E26" s="11">
+        <v>2607.0500000000002</v>
+      </c>
+      <c r="F26" s="11">
+        <v>3</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>3</v>
+      </c>
+      <c r="I26" s="11">
+        <v>2</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
+      <c r="K26" s="11">
+        <v>869.02</v>
+      </c>
+      <c r="L26" s="11">
+        <v>1303.53</v>
+      </c>
+      <c r="M26" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="11">
+        <v>1</v>
+      </c>
+      <c r="O26" s="11">
+        <v>625.91</v>
+      </c>
+      <c r="P26" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>0</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0</v>
+      </c>
+      <c r="S26" s="11">
+        <v>312.95999999999998</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="U26" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V26" s="11">
+        <v>2</v>
+      </c>
+      <c r="W26" s="11">
+        <v>883.31</v>
+      </c>
+      <c r="X26" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB26" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC26" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD26" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE26" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="11">
+        <v>30.49</v>
+      </c>
+      <c r="C27" s="11">
+        <v>13.01</v>
+      </c>
+      <c r="D27" s="11">
+        <v>17.48</v>
+      </c>
+      <c r="E27" s="11">
+        <v>8243.42</v>
+      </c>
+      <c r="F27" s="11">
+        <v>19</v>
+      </c>
+      <c r="G27" s="11">
+        <v>2</v>
+      </c>
+      <c r="H27" s="11">
+        <v>17</v>
+      </c>
+      <c r="I27" s="11">
+        <v>4</v>
+      </c>
+      <c r="J27" s="11">
+        <v>1</v>
+      </c>
+      <c r="K27" s="11">
+        <v>433.86</v>
+      </c>
+      <c r="L27" s="11">
+        <v>2060.86</v>
+      </c>
+      <c r="M27" s="11">
+        <v>-7</v>
+      </c>
+      <c r="N27" s="11">
+        <v>34.69</v>
+      </c>
+      <c r="O27" s="11">
+        <v>6993.67</v>
+      </c>
+      <c r="P27" s="11">
+        <v>29</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>8</v>
+      </c>
+      <c r="R27" s="11">
+        <v>2</v>
+      </c>
+      <c r="S27" s="11">
+        <v>241.16</v>
+      </c>
+      <c r="T27" s="11">
+        <v>874.21</v>
+      </c>
+      <c r="U27" s="11">
         <v>118</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15">
+      <c r="V27" s="11">
+        <v>51.71</v>
+      </c>
+      <c r="W27" s="11">
+        <v>10989.82</v>
+      </c>
+      <c r="X27" s="11">
+        <v>45</v>
+      </c>
+      <c r="Y27" s="11">
+        <v>15</v>
+      </c>
+      <c r="Z27" s="11">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB27" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE27" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N28" s="11">
+        <v>9</v>
+      </c>
+      <c r="O28" s="11">
+        <v>1299.76</v>
+      </c>
+      <c r="P28" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>3</v>
+      </c>
+      <c r="R28" s="11">
+        <v>0</v>
+      </c>
+      <c r="S28" s="11">
+        <v>216.63</v>
+      </c>
+      <c r="T28" s="11">
+        <v>433.25</v>
+      </c>
+      <c r="U28" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V28" s="11">
+        <v>16.939999999999898</v>
+      </c>
+      <c r="W28" s="11">
+        <v>2070.7399999999998</v>
+      </c>
+      <c r="X28" s="11">
+        <v>10</v>
+      </c>
+      <c r="Y28" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB28" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE28" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="11">
+        <v>46</v>
+      </c>
+      <c r="C29" s="11">
+        <v>15</v>
+      </c>
+      <c r="D29" s="11">
+        <v>31</v>
+      </c>
+      <c r="E29" s="11">
+        <v>8724.92</v>
+      </c>
+      <c r="F29" s="11">
+        <v>21</v>
+      </c>
+      <c r="G29" s="11">
+        <v>1</v>
+      </c>
+      <c r="H29" s="11">
+        <v>20</v>
+      </c>
+      <c r="I29" s="11">
+        <v>6</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0</v>
+      </c>
+      <c r="K29" s="11">
+        <v>415.47</v>
+      </c>
+      <c r="L29" s="11">
+        <v>1454.15</v>
+      </c>
+      <c r="M29" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N29" s="11">
+        <v>9.0599999999999898</v>
+      </c>
+      <c r="O29" s="11">
+        <v>1964.96</v>
+      </c>
+      <c r="P29" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>5</v>
+      </c>
+      <c r="R29" s="11">
+        <v>1</v>
+      </c>
+      <c r="S29" s="11">
+        <v>131</v>
+      </c>
+      <c r="T29" s="11">
+        <v>392.99</v>
+      </c>
+      <c r="U29" s="11">
+        <v>-92</v>
+      </c>
+      <c r="V29" s="11">
+        <v>17.03</v>
+      </c>
+      <c r="W29" s="11">
+        <v>3580.98</v>
+      </c>
+      <c r="X29" s="11">
+        <v>28</v>
+      </c>
+      <c r="Y29" s="11">
+        <v>11</v>
+      </c>
+      <c r="Z29" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB29" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC29" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD29" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE29" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N30" s="11">
+        <v>12</v>
+      </c>
+      <c r="O30" s="11">
+        <v>7478.62</v>
+      </c>
+      <c r="V30" s="11">
+        <v>18</v>
+      </c>
+      <c r="W30" s="11">
+        <v>9228.76</v>
+      </c>
+      <c r="AA30" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB30" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC30" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD30" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE30" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="N31" s="11">
+        <v>15.03</v>
+      </c>
+      <c r="O31" s="11">
+        <v>1936.99</v>
+      </c>
+      <c r="P31" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>5</v>
+      </c>
+      <c r="R31" s="11">
+        <v>0</v>
+      </c>
+      <c r="S31" s="11">
+        <v>276.70999999999998</v>
+      </c>
+      <c r="T31" s="11">
+        <v>387.4</v>
+      </c>
+      <c r="U31" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V31" s="11">
+        <v>60.559999999999903</v>
+      </c>
+      <c r="W31" s="11">
+        <v>4824.59</v>
+      </c>
+      <c r="X31" s="11">
+        <v>22</v>
+      </c>
+      <c r="Y31" s="11">
+        <v>7</v>
+      </c>
+      <c r="Z31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB31" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC31" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD31" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE31" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="N32" s="11">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="O32" s="11">
+        <v>2028.11</v>
+      </c>
+      <c r="P32" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>4</v>
+      </c>
+      <c r="R32" s="11">
+        <v>1</v>
+      </c>
+      <c r="S32" s="11">
+        <v>225.35</v>
+      </c>
+      <c r="T32" s="11">
+        <v>507.03</v>
+      </c>
+      <c r="U32" s="11">
+        <v>269</v>
+      </c>
+      <c r="V32" s="11">
+        <v>66.84</v>
+      </c>
+      <c r="W32" s="11">
+        <v>4891.78</v>
+      </c>
+      <c r="X32" s="11">
+        <v>22</v>
+      </c>
+      <c r="Y32" s="11">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB32" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC32" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD32" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE32" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="11">
+        <v>64.17</v>
+      </c>
+      <c r="C33" s="11">
+        <v>36.5</v>
+      </c>
+      <c r="D33" s="11">
+        <v>27.67</v>
+      </c>
+      <c r="E33" s="11">
+        <v>19410.23</v>
+      </c>
+      <c r="F33" s="11">
+        <v>23</v>
+      </c>
+      <c r="G33" s="11">
+        <v>7</v>
+      </c>
+      <c r="H33" s="11">
+        <v>16</v>
+      </c>
+      <c r="I33" s="11">
         <v>14</v>
       </c>
-      <c r="O15">
-        <v>648.91</v>
-      </c>
-      <c r="V15">
+      <c r="J33" s="11">
+        <v>3</v>
+      </c>
+      <c r="K33" s="11">
+        <v>843.92</v>
+      </c>
+      <c r="L33" s="11">
+        <v>1386.44</v>
+      </c>
+      <c r="M33" s="11">
+        <v>-15</v>
+      </c>
+      <c r="N33" s="11">
+        <v>33.090000000000003</v>
+      </c>
+      <c r="O33" s="11">
+        <v>8950.5499999999993</v>
+      </c>
+      <c r="P33" s="11">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>20</v>
+      </c>
+      <c r="R33" s="11">
+        <v>5</v>
+      </c>
+      <c r="S33" s="11">
+        <v>255.73</v>
+      </c>
+      <c r="T33" s="11">
+        <v>447.53</v>
+      </c>
+      <c r="U33" s="11">
+        <v>338</v>
+      </c>
+      <c r="V33" s="11">
+        <v>46.14</v>
+      </c>
+      <c r="W33" s="11">
+        <v>13471.99</v>
+      </c>
+      <c r="X33" s="11">
+        <v>56</v>
+      </c>
+      <c r="Y33" s="11">
+        <v>29</v>
+      </c>
+      <c r="Z33" s="11">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB33" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE33" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="11">
+        <v>61.67</v>
+      </c>
+      <c r="C34" s="11">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="D34" s="11">
+        <v>41.34</v>
+      </c>
+      <c r="E34" s="11">
+        <v>20737.11</v>
+      </c>
+      <c r="F34" s="11">
+        <v>41</v>
+      </c>
+      <c r="G34" s="11">
+        <v>10</v>
+      </c>
+      <c r="H34" s="11">
+        <v>31</v>
+      </c>
+      <c r="I34" s="11">
+        <v>18</v>
+      </c>
+      <c r="J34" s="11">
+        <v>5</v>
+      </c>
+      <c r="K34" s="11">
+        <v>505.78</v>
+      </c>
+      <c r="L34" s="11">
+        <v>1152.06</v>
+      </c>
+      <c r="M34" s="11">
+        <v>65</v>
+      </c>
+      <c r="AA34" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB34" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE34" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="11">
+        <v>115.2</v>
+      </c>
+      <c r="C35" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="D35" s="11">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="E35" s="11">
+        <v>21136.46</v>
+      </c>
+      <c r="F35" s="11">
+        <v>64</v>
+      </c>
+      <c r="G35" s="11">
+        <v>9</v>
+      </c>
+      <c r="H35" s="11">
+        <v>55</v>
+      </c>
+      <c r="I35" s="11">
+        <v>18</v>
+      </c>
+      <c r="J35" s="11">
+        <v>2</v>
+      </c>
+      <c r="K35" s="11">
+        <v>330.26</v>
+      </c>
+      <c r="L35" s="11">
+        <v>1174.25</v>
+      </c>
+      <c r="M35" s="11">
+        <v>-30</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB35" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC35" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD35" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE35" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="11">
+        <v>114.8</v>
+      </c>
+      <c r="C36" s="11">
+        <v>68.3</v>
+      </c>
+      <c r="D36" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="E36" s="11">
+        <v>23335.14</v>
+      </c>
+      <c r="F36" s="11">
+        <v>39</v>
+      </c>
+      <c r="G36" s="11">
+        <v>5</v>
+      </c>
+      <c r="H36" s="11">
+        <v>34</v>
+      </c>
+      <c r="I36" s="11">
+        <v>9</v>
+      </c>
+      <c r="J36" s="11">
+        <v>3</v>
+      </c>
+      <c r="K36" s="11">
+        <v>598.34</v>
+      </c>
+      <c r="L36" s="11">
+        <v>2592.79</v>
+      </c>
+      <c r="M36" s="11">
+        <v>-12</v>
+      </c>
+      <c r="N36" s="11">
+        <v>94.26</v>
+      </c>
+      <c r="O36" s="11">
+        <v>23768.15</v>
+      </c>
+      <c r="P36" s="11">
+        <v>85</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>31</v>
+      </c>
+      <c r="R36" s="11">
+        <v>13</v>
+      </c>
+      <c r="S36" s="11">
+        <v>279.63</v>
+      </c>
+      <c r="T36" s="11">
+        <v>766.71</v>
+      </c>
+      <c r="U36" s="11">
+        <v>280</v>
+      </c>
+      <c r="V36" s="11">
+        <v>121.28</v>
+      </c>
+      <c r="W36" s="11">
+        <v>32532.17</v>
+      </c>
+      <c r="X36" s="11">
+        <v>112</v>
+      </c>
+      <c r="Y36" s="11">
+        <v>43</v>
+      </c>
+      <c r="Z36" s="11">
+        <v>13</v>
+      </c>
+      <c r="AA36" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB36" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE36" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="N37" s="11">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="O37" s="11">
+        <v>1906.67</v>
+      </c>
+      <c r="P37" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>1</v>
+      </c>
+      <c r="R37" s="11">
+        <v>0</v>
+      </c>
+      <c r="S37" s="11">
+        <v>317.77999999999997</v>
+      </c>
+      <c r="T37" s="11">
+        <v>1906.67</v>
+      </c>
+      <c r="U37" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V37" s="11">
+        <v>46.9</v>
+      </c>
+      <c r="W37" s="11">
+        <v>3023.13</v>
+      </c>
+      <c r="X37" s="11">
+        <v>9</v>
+      </c>
+      <c r="Y37" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC37" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD37" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE37" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="11">
+        <v>27.6</v>
+      </c>
+      <c r="C38" s="11">
+        <v>17.59</v>
+      </c>
+      <c r="D38" s="11">
+        <v>10.01</v>
+      </c>
+      <c r="E38" s="11">
+        <v>5220.04</v>
+      </c>
+      <c r="F38" s="11">
+        <v>10</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1</v>
+      </c>
+      <c r="H38" s="11">
+        <v>9</v>
+      </c>
+      <c r="I38" s="11">
+        <v>4</v>
+      </c>
+      <c r="J38" s="11">
+        <v>1</v>
+      </c>
+      <c r="K38" s="11">
+        <v>522</v>
+      </c>
+      <c r="L38" s="11">
+        <v>1305.01</v>
+      </c>
+      <c r="M38" s="11">
+        <v>49</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB38" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC38" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD38" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE38" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="11">
+        <v>64.899999999999906</v>
+      </c>
+      <c r="C39" s="11">
+        <v>31.49</v>
+      </c>
+      <c r="D39" s="11">
+        <v>33.409999999999997</v>
+      </c>
+      <c r="E39" s="11">
+        <v>13549.23</v>
+      </c>
+      <c r="F39" s="11">
+        <v>21</v>
+      </c>
+      <c r="G39" s="11">
+        <v>4</v>
+      </c>
+      <c r="H39" s="11">
+        <v>17</v>
+      </c>
+      <c r="I39" s="11">
+        <v>10</v>
+      </c>
+      <c r="J39" s="11">
+        <v>0</v>
+      </c>
+      <c r="K39" s="11">
+        <v>645.20000000000005</v>
+      </c>
+      <c r="L39" s="11">
+        <v>1354.92</v>
+      </c>
+      <c r="M39" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N39" s="11">
+        <v>19</v>
+      </c>
+      <c r="O39" s="11">
+        <v>5541.69</v>
+      </c>
+      <c r="P39" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>11</v>
+      </c>
+      <c r="R39" s="11">
+        <v>4</v>
+      </c>
+      <c r="S39" s="11">
+        <v>173.18</v>
+      </c>
+      <c r="T39" s="11">
+        <v>503.79</v>
+      </c>
+      <c r="U39" s="11">
+        <v>323</v>
+      </c>
+      <c r="V39" s="11">
+        <v>34</v>
+      </c>
+      <c r="W39" s="11">
+        <v>9463.0300000000007</v>
+      </c>
+      <c r="X39" s="11">
+        <v>49</v>
+      </c>
+      <c r="Y39" s="11">
+        <v>17</v>
+      </c>
+      <c r="Z39" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA39" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE39" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N40" s="11">
+        <v>19</v>
+      </c>
+      <c r="O40" s="11">
+        <v>1654.39</v>
+      </c>
+      <c r="P40" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>1</v>
+      </c>
+      <c r="R40" s="11">
+        <v>0</v>
+      </c>
+      <c r="S40" s="11">
+        <v>275.73</v>
+      </c>
+      <c r="T40" s="11">
+        <v>1654.39</v>
+      </c>
+      <c r="U40" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V40" s="11">
+        <v>29</v>
+      </c>
+      <c r="W40" s="11">
+        <v>3368</v>
+      </c>
+      <c r="X40" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y40" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z40" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC40" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD40" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE40" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="11">
+        <v>62.96</v>
+      </c>
+      <c r="C41" s="11">
+        <v>32.99</v>
+      </c>
+      <c r="D41" s="11">
+        <v>29.97</v>
+      </c>
+      <c r="E41" s="11">
+        <v>11488.72</v>
+      </c>
+      <c r="F41" s="11">
+        <v>25</v>
+      </c>
+      <c r="G41" s="11">
+        <v>2</v>
+      </c>
+      <c r="H41" s="11">
+        <v>23</v>
+      </c>
+      <c r="I41" s="11">
+        <v>8</v>
+      </c>
+      <c r="J41" s="11">
+        <v>0</v>
+      </c>
+      <c r="K41" s="11">
+        <v>459.55</v>
+      </c>
+      <c r="L41" s="11">
+        <v>1436.09</v>
+      </c>
+      <c r="M41" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N41" s="11">
+        <v>3</v>
+      </c>
+      <c r="O41" s="11">
+        <v>397.28</v>
+      </c>
+      <c r="P41" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>0</v>
+      </c>
+      <c r="R41" s="11">
+        <v>0</v>
+      </c>
+      <c r="S41" s="11">
+        <v>397.28</v>
+      </c>
+      <c r="T41" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="U41" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V41" s="11">
+        <v>4</v>
+      </c>
+      <c r="W41" s="11">
+        <v>677.6</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB41" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC41" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD41" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE41" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="11">
+        <v>53.91</v>
+      </c>
+      <c r="C42" s="11">
+        <v>31.51</v>
+      </c>
+      <c r="D42" s="11">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="11">
+        <v>16212.1</v>
+      </c>
+      <c r="F42" s="11">
+        <v>21</v>
+      </c>
+      <c r="G42" s="11">
+        <v>3</v>
+      </c>
+      <c r="H42" s="11">
+        <v>18</v>
+      </c>
+      <c r="I42" s="11">
+        <v>8</v>
+      </c>
+      <c r="J42" s="11">
+        <v>0</v>
+      </c>
+      <c r="K42" s="11">
+        <v>772</v>
+      </c>
+      <c r="L42" s="11">
+        <v>2026.51</v>
+      </c>
+      <c r="M42" s="11">
+        <v>-100</v>
+      </c>
+      <c r="N42" s="11">
+        <v>25.54</v>
+      </c>
+      <c r="O42" s="11">
+        <v>5596.85</v>
+      </c>
+      <c r="P42" s="11">
+        <v>22</v>
+      </c>
+      <c r="Q42" s="11">
+        <v>6</v>
+      </c>
+      <c r="R42" s="11">
+        <v>0</v>
+      </c>
+      <c r="S42" s="11">
+        <v>254.4</v>
+      </c>
+      <c r="T42" s="11">
+        <v>932.81</v>
+      </c>
+      <c r="U42" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V42" s="11">
+        <v>36.5</v>
+      </c>
+      <c r="W42" s="11">
+        <v>8945.9699999999993</v>
+      </c>
+      <c r="X42" s="11">
+        <v>34</v>
+      </c>
+      <c r="Y42" s="11">
+        <v>7</v>
+      </c>
+      <c r="Z42" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE42" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="N43" s="11">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="O43" s="11">
+        <v>1572.89</v>
+      </c>
+      <c r="P43" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>4</v>
+      </c>
+      <c r="R43" s="11">
+        <v>0</v>
+      </c>
+      <c r="S43" s="11">
+        <v>224.7</v>
+      </c>
+      <c r="T43" s="11">
+        <v>393.22</v>
+      </c>
+      <c r="U43" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V43" s="11">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="W43" s="11">
+        <v>3006.79</v>
+      </c>
+      <c r="X43" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y43" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z43" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="7">
+        <v>40</v>
+      </c>
+      <c r="AB43" s="7">
+        <v>1900</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>95</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>22</v>
+      </c>
+      <c r="AE43" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="11">
+        <v>28.68</v>
+      </c>
+      <c r="C44" s="11">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="D44" s="11">
+        <v>12.51</v>
+      </c>
+      <c r="E44" s="11">
+        <v>7035.16</v>
+      </c>
+      <c r="F44" s="11">
+        <v>11</v>
+      </c>
+      <c r="G44" s="11">
+        <v>1</v>
+      </c>
+      <c r="H44" s="11">
+        <v>10</v>
+      </c>
+      <c r="I44" s="11">
+        <v>4</v>
+      </c>
+      <c r="J44" s="11">
+        <v>2</v>
+      </c>
+      <c r="K44" s="11">
+        <v>639.55999999999995</v>
+      </c>
+      <c r="L44" s="11">
+        <v>1758.79</v>
+      </c>
+      <c r="M44" s="11">
+        <v>135</v>
+      </c>
+      <c r="N44" s="11">
+        <v>10.99</v>
+      </c>
+      <c r="O44" s="11">
+        <v>3609.31</v>
+      </c>
+      <c r="P44" s="11">
         <v>16</v>
       </c>
-      <c r="W15">
-        <v>1036.27</v>
-      </c>
-      <c r="AA15" s="8">
+      <c r="Q44" s="11">
+        <v>1</v>
+      </c>
+      <c r="R44" s="11">
+        <v>0</v>
+      </c>
+      <c r="S44" s="11">
+        <v>225.58</v>
+      </c>
+      <c r="T44" s="11">
+        <v>3609.31</v>
+      </c>
+      <c r="U44" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V44" s="11">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="W44" s="11">
+        <v>4902.3</v>
+      </c>
+      <c r="X44" s="11">
+        <v>23</v>
+      </c>
+      <c r="Y44" s="11">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="7">
         <v>40</v>
       </c>
-      <c r="AB15" s="8">
+      <c r="AB44" s="7">
         <v>1900</v>
       </c>
-      <c r="AC15" s="9">
+      <c r="AC44" s="8">
         <v>95</v>
       </c>
-      <c r="AD15" s="9">
+      <c r="AD44" s="8">
         <v>22</v>
       </c>
-      <c r="AE15" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16">
+      <c r="AE44" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N45" s="11">
         <v>3</v>
       </c>
-      <c r="C16">
+      <c r="O45" s="11">
+        <v>670.61</v>
+      </c>
+      <c r="P45" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>0</v>
+      </c>
+      <c r="R45" s="11">
+        <v>0</v>
+      </c>
+      <c r="S45" s="11">
+        <v>335.3</v>
+      </c>
+      <c r="T45" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="U45" s="11">
+        <v>-100</v>
+      </c>
+      <c r="V45" s="11">
+        <v>8</v>
+      </c>
+      <c r="W45" s="11">
+        <v>1060.3499999999999</v>
+      </c>
+      <c r="X45" s="11">
         <v>3</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>1061.96</v>
-      </c>
-      <c r="N16">
-        <v>2</v>
-      </c>
-      <c r="O16">
-        <v>304.22000000000003</v>
-      </c>
-      <c r="P16">
-        <v>3</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>101.41</v>
-      </c>
-      <c r="T16">
-        <v>304.22000000000003</v>
-      </c>
-      <c r="U16">
-        <v>-100</v>
-      </c>
-      <c r="V16">
-        <v>3</v>
-      </c>
-      <c r="W16">
-        <v>422.36</v>
-      </c>
-      <c r="X16">
-        <v>4</v>
-      </c>
-      <c r="Y16">
-        <v>2</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="8">
+      <c r="Y45" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="7">
         <v>40</v>
       </c>
-      <c r="AB16" s="8">
+      <c r="AB45" s="7">
         <v>1900</v>
       </c>
-      <c r="AC16" s="9">
+      <c r="AC45" s="8">
         <v>95</v>
       </c>
-      <c r="AD16" s="9">
+      <c r="AD45" s="8">
         <v>22</v>
       </c>
-      <c r="AE16" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17">
-        <v>47.03</v>
-      </c>
-      <c r="C17">
-        <v>15</v>
-      </c>
-      <c r="D17">
-        <v>32.03</v>
-      </c>
-      <c r="E17">
-        <v>13237.97</v>
-      </c>
-      <c r="F17">
-        <v>32</v>
-      </c>
-      <c r="G17">
-        <v>6</v>
-      </c>
-      <c r="H17">
-        <v>26</v>
-      </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <v>4</v>
-      </c>
-      <c r="K17">
-        <v>413.69</v>
-      </c>
-      <c r="L17">
-        <v>1323.8</v>
-      </c>
-      <c r="M17">
-        <v>104</v>
-      </c>
-      <c r="N17">
-        <v>46.99</v>
-      </c>
-      <c r="O17">
-        <v>10879.93</v>
-      </c>
-      <c r="P17">
-        <v>57</v>
-      </c>
-      <c r="Q17">
-        <v>18</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>190.88</v>
-      </c>
-      <c r="T17">
-        <v>604.44000000000005</v>
-      </c>
-      <c r="U17">
-        <v>-100</v>
-      </c>
-      <c r="V17">
-        <v>61.03</v>
-      </c>
-      <c r="W17">
-        <v>15298.11</v>
-      </c>
-      <c r="X17">
-        <v>79</v>
-      </c>
-      <c r="Y17">
-        <v>29</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB17" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="N18">
-        <v>25</v>
-      </c>
-      <c r="O18">
-        <v>2044.61</v>
-      </c>
-      <c r="P18">
-        <v>17</v>
-      </c>
-      <c r="Q18">
-        <v>6</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <v>120.27</v>
-      </c>
-      <c r="T18">
-        <v>340.77</v>
-      </c>
-      <c r="U18">
-        <v>264</v>
-      </c>
-      <c r="V18">
-        <v>54</v>
-      </c>
-      <c r="W18">
-        <v>5213.1000000000004</v>
-      </c>
-      <c r="X18">
-        <v>26</v>
-      </c>
-      <c r="Y18">
-        <v>11</v>
-      </c>
-      <c r="Z18">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB18" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC18" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE18" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="N19">
-        <v>10</v>
-      </c>
-      <c r="O19">
-        <v>1100.05</v>
-      </c>
-      <c r="P19">
-        <v>10</v>
-      </c>
-      <c r="Q19">
-        <v>4</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <v>110</v>
-      </c>
-      <c r="T19">
-        <v>275.01</v>
-      </c>
-      <c r="U19">
-        <v>679</v>
-      </c>
-      <c r="V19">
-        <v>10</v>
-      </c>
-      <c r="W19">
-        <v>1552.36</v>
-      </c>
-      <c r="X19">
-        <v>11</v>
-      </c>
-      <c r="Y19">
-        <v>7</v>
-      </c>
-      <c r="Z19">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB19" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC19" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD19" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE19" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="N20">
-        <v>3</v>
-      </c>
-      <c r="O20">
-        <v>475.21</v>
-      </c>
-      <c r="V20">
-        <v>3</v>
-      </c>
-      <c r="W20">
-        <v>912.36</v>
-      </c>
-      <c r="AA20" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB20" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC20" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD20" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE20" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="N21">
-        <v>9</v>
-      </c>
-      <c r="O21">
-        <v>2521.44</v>
-      </c>
-      <c r="V21">
-        <v>15</v>
-      </c>
-      <c r="W21">
-        <v>3696.93</v>
-      </c>
-      <c r="AA21" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB21" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE21" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22">
-        <v>61.43</v>
-      </c>
-      <c r="C22">
-        <v>21.32</v>
-      </c>
-      <c r="D22">
-        <v>40.11</v>
-      </c>
-      <c r="E22">
-        <v>15607.52</v>
-      </c>
-      <c r="F22">
-        <v>43</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-      <c r="H22">
-        <v>38</v>
-      </c>
-      <c r="I22">
-        <v>20</v>
-      </c>
-      <c r="J22">
-        <v>4</v>
-      </c>
-      <c r="K22">
-        <v>362.97</v>
-      </c>
-      <c r="L22">
-        <v>780.38</v>
-      </c>
-      <c r="M22">
-        <v>59</v>
-      </c>
-      <c r="AA22" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB22" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC22" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE22" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>2100.29</v>
-      </c>
-      <c r="AA23" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB23" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC23" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD23" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE23" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24">
-        <v>108.72</v>
-      </c>
-      <c r="C24">
-        <v>100.72</v>
-      </c>
-      <c r="D24">
-        <v>8</v>
-      </c>
-      <c r="E24">
-        <v>25478.66</v>
-      </c>
-      <c r="F24">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-      <c r="H24">
-        <v>6</v>
-      </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
-      <c r="J24">
-        <v>2</v>
-      </c>
-      <c r="K24">
-        <v>2316.2399999999998</v>
-      </c>
-      <c r="L24">
-        <v>8492.89</v>
-      </c>
-      <c r="M24">
-        <v>-70</v>
-      </c>
-      <c r="AA24" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB24" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC24" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD24" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE24" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25">
-        <v>9</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="E25">
-        <v>4087.49</v>
-      </c>
-      <c r="F25">
-        <v>9</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>8</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>454.17</v>
-      </c>
-      <c r="L25">
-        <v>2043.74</v>
-      </c>
-      <c r="M25">
-        <v>-100</v>
-      </c>
-      <c r="N25">
-        <v>9</v>
-      </c>
-      <c r="O25">
-        <v>1700.93</v>
-      </c>
-      <c r="V25">
-        <v>16</v>
-      </c>
-      <c r="W25">
-        <v>2548.09</v>
-      </c>
-      <c r="AA25" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB25" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC25" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD25" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE25" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26">
-        <v>6.5</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>2.5</v>
-      </c>
-      <c r="E26">
-        <v>2607.0500000000002</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>869.02</v>
-      </c>
-      <c r="L26">
-        <v>1303.53</v>
-      </c>
-      <c r="M26">
-        <v>-100</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>625.91</v>
-      </c>
-      <c r="P26">
-        <v>2</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>312.95999999999998</v>
-      </c>
-      <c r="T26" t="s">
-        <v>114</v>
-      </c>
-      <c r="U26">
-        <v>-100</v>
-      </c>
-      <c r="V26">
-        <v>2</v>
-      </c>
-      <c r="W26">
-        <v>883.31</v>
-      </c>
-      <c r="X26">
-        <v>5</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB26" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC26" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD26" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE26" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27">
-        <v>30.49</v>
-      </c>
-      <c r="C27">
-        <v>13.01</v>
-      </c>
-      <c r="D27">
-        <v>17.48</v>
-      </c>
-      <c r="E27">
-        <v>8243.42</v>
-      </c>
-      <c r="F27">
-        <v>19</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27">
-        <v>17</v>
-      </c>
-      <c r="I27">
-        <v>4</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>433.86</v>
-      </c>
-      <c r="L27">
-        <v>2060.86</v>
-      </c>
-      <c r="M27">
-        <v>-7</v>
-      </c>
-      <c r="N27">
-        <v>34.69</v>
-      </c>
-      <c r="O27">
-        <v>6993.67</v>
-      </c>
-      <c r="P27">
-        <v>29</v>
-      </c>
-      <c r="Q27">
-        <v>8</v>
-      </c>
-      <c r="R27">
-        <v>2</v>
-      </c>
-      <c r="S27">
-        <v>241.16</v>
-      </c>
-      <c r="T27">
-        <v>874.21</v>
-      </c>
-      <c r="U27">
-        <v>118</v>
-      </c>
-      <c r="V27">
-        <v>51.71</v>
-      </c>
-      <c r="W27">
-        <v>10989.82</v>
-      </c>
-      <c r="X27">
-        <v>45</v>
-      </c>
-      <c r="Y27">
-        <v>15</v>
-      </c>
-      <c r="Z27">
-        <v>2</v>
-      </c>
-      <c r="AA27" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB27" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC27" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD27" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE27" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="N28">
-        <v>9</v>
-      </c>
-      <c r="O28">
-        <v>1299.76</v>
-      </c>
-      <c r="P28">
-        <v>6</v>
-      </c>
-      <c r="Q28">
-        <v>3</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>216.63</v>
-      </c>
-      <c r="T28">
-        <v>433.25</v>
-      </c>
-      <c r="U28">
-        <v>-100</v>
-      </c>
-      <c r="V28">
-        <v>16.939999999999898</v>
-      </c>
-      <c r="W28">
-        <v>2070.7399999999998</v>
-      </c>
-      <c r="X28">
-        <v>10</v>
-      </c>
-      <c r="Y28">
-        <v>4</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB28" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC28" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD28" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE28" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29">
-        <v>46</v>
-      </c>
-      <c r="C29">
-        <v>15</v>
-      </c>
-      <c r="D29">
-        <v>31</v>
-      </c>
-      <c r="E29">
-        <v>8724.92</v>
-      </c>
-      <c r="F29">
-        <v>21</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>20</v>
-      </c>
-      <c r="I29">
-        <v>6</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>415.47</v>
-      </c>
-      <c r="L29">
-        <v>1454.15</v>
-      </c>
-      <c r="M29">
-        <v>-100</v>
-      </c>
-      <c r="N29">
-        <v>9.0599999999999898</v>
-      </c>
-      <c r="O29">
-        <v>1964.96</v>
-      </c>
-      <c r="P29">
-        <v>15</v>
-      </c>
-      <c r="Q29">
-        <v>5</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>131</v>
-      </c>
-      <c r="T29">
-        <v>392.99</v>
-      </c>
-      <c r="U29">
-        <v>-92</v>
-      </c>
-      <c r="V29">
-        <v>17.03</v>
-      </c>
-      <c r="W29">
-        <v>3580.98</v>
-      </c>
-      <c r="X29">
-        <v>28</v>
-      </c>
-      <c r="Y29">
-        <v>11</v>
-      </c>
-      <c r="Z29">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB29" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC29" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD29" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE29" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="N30">
-        <v>12</v>
-      </c>
-      <c r="O30">
-        <v>7478.62</v>
-      </c>
-      <c r="V30">
-        <v>18</v>
-      </c>
-      <c r="W30">
-        <v>9228.76</v>
-      </c>
-      <c r="AA30" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB30" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC30" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD30" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE30" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="N31">
-        <v>15.03</v>
-      </c>
-      <c r="O31">
-        <v>1936.99</v>
-      </c>
-      <c r="P31">
-        <v>7</v>
-      </c>
-      <c r="Q31">
-        <v>5</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>276.70999999999998</v>
-      </c>
-      <c r="T31">
-        <v>387.4</v>
-      </c>
-      <c r="U31">
-        <v>-100</v>
-      </c>
-      <c r="V31">
-        <v>60.559999999999903</v>
-      </c>
-      <c r="W31">
-        <v>4824.59</v>
-      </c>
-      <c r="X31">
-        <v>22</v>
-      </c>
-      <c r="Y31">
-        <v>7</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB31" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD31" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE31" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="N32">
-        <v>20.309999999999999</v>
-      </c>
-      <c r="O32">
-        <v>2028.11</v>
-      </c>
-      <c r="P32">
-        <v>9</v>
-      </c>
-      <c r="Q32">
-        <v>4</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32">
-        <v>225.35</v>
-      </c>
-      <c r="T32">
-        <v>507.03</v>
-      </c>
-      <c r="U32">
-        <v>269</v>
-      </c>
-      <c r="V32">
-        <v>66.84</v>
-      </c>
-      <c r="W32">
-        <v>4891.78</v>
-      </c>
-      <c r="X32">
-        <v>22</v>
-      </c>
-      <c r="Y32">
-        <v>5</v>
-      </c>
-      <c r="Z32">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB32" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC32" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD32" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE32" s="10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33">
-        <v>64.17</v>
-      </c>
-      <c r="C33">
-        <v>36.5</v>
-      </c>
-      <c r="D33">
-        <v>27.67</v>
-      </c>
-      <c r="E33">
-        <v>19410.23</v>
-      </c>
-      <c r="F33">
-        <v>23</v>
-      </c>
-      <c r="G33">
-        <v>7</v>
-      </c>
-      <c r="H33">
-        <v>16</v>
-      </c>
-      <c r="I33">
-        <v>14</v>
-      </c>
-      <c r="J33">
-        <v>3</v>
-      </c>
-      <c r="K33">
-        <v>843.92</v>
-      </c>
-      <c r="L33">
-        <v>1386.44</v>
-      </c>
-      <c r="M33">
-        <v>-15</v>
-      </c>
-      <c r="N33">
-        <v>33.090000000000003</v>
-      </c>
-      <c r="O33">
-        <v>8950.5499999999993</v>
-      </c>
-      <c r="P33">
+      <c r="AE45" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="Q33">
-        <v>20</v>
-      </c>
-      <c r="R33">
-        <v>5</v>
-      </c>
-      <c r="S33">
-        <v>255.73</v>
-      </c>
-      <c r="T33">
-        <v>447.53</v>
-      </c>
-      <c r="U33">
-        <v>338</v>
-      </c>
-      <c r="V33">
-        <v>46.14</v>
-      </c>
-      <c r="W33">
-        <v>13471.99</v>
-      </c>
-      <c r="X33">
-        <v>56</v>
-      </c>
-      <c r="Y33">
-        <v>29</v>
-      </c>
-      <c r="Z33">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB33" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC33" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD33" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE33" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34">
-        <v>61.67</v>
-      </c>
-      <c r="C34">
-        <v>20.329999999999998</v>
-      </c>
-      <c r="D34">
-        <v>41.34</v>
-      </c>
-      <c r="E34">
-        <v>20737.11</v>
-      </c>
-      <c r="F34">
-        <v>41</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34">
-        <v>31</v>
-      </c>
-      <c r="I34">
-        <v>18</v>
-      </c>
-      <c r="J34">
-        <v>5</v>
-      </c>
-      <c r="K34">
-        <v>505.78</v>
-      </c>
-      <c r="L34">
-        <v>1152.06</v>
-      </c>
-      <c r="M34">
-        <v>65</v>
-      </c>
-      <c r="AA34" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB34" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC34" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD34" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE34" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35">
-        <v>115.2</v>
-      </c>
-      <c r="C35">
-        <v>48.8</v>
-      </c>
-      <c r="D35">
-        <v>66.400000000000006</v>
-      </c>
-      <c r="E35">
-        <v>21136.46</v>
-      </c>
-      <c r="F35">
-        <v>64</v>
-      </c>
-      <c r="G35">
-        <v>9</v>
-      </c>
-      <c r="H35">
-        <v>55</v>
-      </c>
-      <c r="I35">
-        <v>18</v>
-      </c>
-      <c r="J35">
-        <v>2</v>
-      </c>
-      <c r="K35">
-        <v>330.26</v>
-      </c>
-      <c r="L35">
-        <v>1174.25</v>
-      </c>
-      <c r="M35">
-        <v>-30</v>
-      </c>
-      <c r="AA35" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB35" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC35" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD35" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE35" s="10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36">
-        <v>114.8</v>
-      </c>
-      <c r="C36">
-        <v>68.3</v>
-      </c>
-      <c r="D36">
-        <v>46.5</v>
-      </c>
-      <c r="E36">
-        <v>23335.14</v>
-      </c>
-      <c r="F36">
-        <v>39</v>
-      </c>
-      <c r="G36">
-        <v>5</v>
-      </c>
-      <c r="H36">
-        <v>34</v>
-      </c>
-      <c r="I36">
-        <v>9</v>
-      </c>
-      <c r="J36">
-        <v>3</v>
-      </c>
-      <c r="K36">
-        <v>598.34</v>
-      </c>
-      <c r="L36">
-        <v>2592.79</v>
-      </c>
-      <c r="M36">
-        <v>-12</v>
-      </c>
-      <c r="N36">
-        <v>94.26</v>
-      </c>
-      <c r="O36">
-        <v>23768.15</v>
-      </c>
-      <c r="P36">
-        <v>85</v>
-      </c>
-      <c r="Q36">
-        <v>31</v>
-      </c>
-      <c r="R36">
-        <v>13</v>
-      </c>
-      <c r="S36">
-        <v>279.63</v>
-      </c>
-      <c r="T36">
-        <v>766.71</v>
-      </c>
-      <c r="U36">
-        <v>280</v>
-      </c>
-      <c r="V36">
-        <v>121.28</v>
-      </c>
-      <c r="W36">
-        <v>32532.17</v>
-      </c>
-      <c r="X36">
-        <v>112</v>
-      </c>
-      <c r="Y36">
-        <v>43</v>
-      </c>
-      <c r="Z36">
-        <v>13</v>
-      </c>
-      <c r="AA36" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB36" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC36" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD36" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE36" s="10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="N37">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="O37">
-        <v>1906.67</v>
-      </c>
-      <c r="P37">
-        <v>6</v>
-      </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>317.77999999999997</v>
-      </c>
-      <c r="T37">
-        <v>1906.67</v>
-      </c>
-      <c r="U37">
-        <v>-100</v>
-      </c>
-      <c r="V37">
-        <v>46.9</v>
-      </c>
-      <c r="W37">
-        <v>3023.13</v>
-      </c>
-      <c r="X37">
-        <v>9</v>
-      </c>
-      <c r="Y37">
-        <v>2</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB37" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC37" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD37" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE37" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38">
-        <v>27.6</v>
-      </c>
-      <c r="C38">
-        <v>17.59</v>
-      </c>
-      <c r="D38">
-        <v>10.01</v>
-      </c>
-      <c r="E38">
-        <v>5220.04</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <v>9</v>
-      </c>
-      <c r="I38">
-        <v>4</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38">
-        <v>522</v>
-      </c>
-      <c r="L38">
-        <v>1305.01</v>
-      </c>
-      <c r="M38">
-        <v>49</v>
-      </c>
-      <c r="AA38" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB38" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD38" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE38" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39">
-        <v>64.899999999999906</v>
-      </c>
-      <c r="C39">
-        <v>31.49</v>
-      </c>
-      <c r="D39">
-        <v>33.409999999999997</v>
-      </c>
-      <c r="E39">
-        <v>13549.23</v>
-      </c>
-      <c r="F39">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
-      </c>
-      <c r="H39">
-        <v>17</v>
-      </c>
-      <c r="I39">
-        <v>10</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>645.20000000000005</v>
-      </c>
-      <c r="L39">
-        <v>1354.92</v>
-      </c>
-      <c r="M39">
-        <v>-100</v>
-      </c>
-      <c r="N39">
-        <v>19</v>
-      </c>
-      <c r="O39">
-        <v>5541.69</v>
-      </c>
-      <c r="P39">
-        <v>32</v>
-      </c>
-      <c r="Q39">
-        <v>11</v>
-      </c>
-      <c r="R39">
-        <v>4</v>
-      </c>
-      <c r="S39">
-        <v>173.18</v>
-      </c>
-      <c r="T39">
-        <v>503.79</v>
-      </c>
-      <c r="U39">
-        <v>323</v>
-      </c>
-      <c r="V39">
-        <v>34</v>
-      </c>
-      <c r="W39">
-        <v>9463.0300000000007</v>
-      </c>
-      <c r="X39">
-        <v>49</v>
-      </c>
-      <c r="Y39">
-        <v>17</v>
-      </c>
-      <c r="Z39">
-        <v>4</v>
-      </c>
-      <c r="AA39" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB39" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC39" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD39" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE39" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N40">
-        <v>19</v>
-      </c>
-      <c r="O40">
-        <v>1654.39</v>
-      </c>
-      <c r="P40">
-        <v>6</v>
-      </c>
-      <c r="Q40">
-        <v>1</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>275.73</v>
-      </c>
-      <c r="T40">
-        <v>1654.39</v>
-      </c>
-      <c r="U40">
-        <v>-100</v>
-      </c>
-      <c r="V40">
-        <v>29</v>
-      </c>
-      <c r="W40">
-        <v>3368</v>
-      </c>
-      <c r="X40">
-        <v>12</v>
-      </c>
-      <c r="Y40">
-        <v>4</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB40" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD40" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE40" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41">
-        <v>62.96</v>
-      </c>
-      <c r="C41">
-        <v>32.99</v>
-      </c>
-      <c r="D41">
-        <v>29.97</v>
-      </c>
-      <c r="E41">
-        <v>11488.72</v>
-      </c>
-      <c r="F41">
-        <v>25</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-      <c r="H41">
-        <v>23</v>
-      </c>
-      <c r="I41">
-        <v>8</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>459.55</v>
-      </c>
-      <c r="L41">
-        <v>1436.09</v>
-      </c>
-      <c r="M41">
-        <v>-100</v>
-      </c>
-      <c r="N41">
-        <v>3</v>
-      </c>
-      <c r="O41">
-        <v>397.28</v>
-      </c>
-      <c r="P41">
-        <v>1</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>397.28</v>
-      </c>
-      <c r="T41" t="s">
-        <v>114</v>
-      </c>
-      <c r="U41">
-        <v>-100</v>
-      </c>
-      <c r="V41">
-        <v>4</v>
-      </c>
-      <c r="W41">
-        <v>677.6</v>
-      </c>
-      <c r="AA41" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB41" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC41" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD41" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE41" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B42">
-        <v>53.91</v>
-      </c>
-      <c r="C42">
-        <v>31.51</v>
-      </c>
-      <c r="D42">
-        <v>22.4</v>
-      </c>
-      <c r="E42">
-        <v>16212.1</v>
-      </c>
-      <c r="F42">
-        <v>21</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
-      </c>
-      <c r="H42">
-        <v>18</v>
-      </c>
-      <c r="I42">
-        <v>8</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>772</v>
-      </c>
-      <c r="L42">
-        <v>2026.51</v>
-      </c>
-      <c r="M42">
-        <v>-100</v>
-      </c>
-      <c r="N42">
-        <v>25.54</v>
-      </c>
-      <c r="O42">
-        <v>5596.85</v>
-      </c>
-      <c r="P42">
-        <v>22</v>
-      </c>
-      <c r="Q42">
-        <v>6</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>254.4</v>
-      </c>
-      <c r="T42">
-        <v>932.81</v>
-      </c>
-      <c r="U42">
-        <v>-100</v>
-      </c>
-      <c r="V42">
-        <v>36.5</v>
-      </c>
-      <c r="W42">
-        <v>8945.9699999999993</v>
-      </c>
-      <c r="X42">
-        <v>34</v>
-      </c>
-      <c r="Y42">
-        <v>7</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB42" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC42" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD42" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE42" s="10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="N43">
-        <v>18.059999999999999</v>
-      </c>
-      <c r="O43">
-        <v>1572.89</v>
-      </c>
-      <c r="P43">
-        <v>7</v>
-      </c>
-      <c r="Q43">
-        <v>4</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>224.7</v>
-      </c>
-      <c r="T43">
-        <v>393.22</v>
-      </c>
-      <c r="U43">
-        <v>-100</v>
-      </c>
-      <c r="V43">
-        <v>39.630000000000003</v>
-      </c>
-      <c r="W43">
-        <v>3006.79</v>
-      </c>
-      <c r="X43">
-        <v>8</v>
-      </c>
-      <c r="Y43">
-        <v>4</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB43" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC43" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD43" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE43" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A44" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44">
-        <v>28.68</v>
-      </c>
-      <c r="C44">
-        <v>16.170000000000002</v>
-      </c>
-      <c r="D44">
-        <v>12.51</v>
-      </c>
-      <c r="E44">
-        <v>7035.16</v>
-      </c>
-      <c r="F44">
-        <v>11</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>10</v>
-      </c>
-      <c r="I44">
-        <v>4</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44">
-        <v>639.55999999999995</v>
-      </c>
-      <c r="L44">
-        <v>1758.79</v>
-      </c>
-      <c r="M44">
-        <v>135</v>
-      </c>
-      <c r="N44">
-        <v>10.99</v>
-      </c>
-      <c r="O44">
-        <v>3609.31</v>
-      </c>
-      <c r="P44">
-        <v>16</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>225.58</v>
-      </c>
-      <c r="T44">
-        <v>3609.31</v>
-      </c>
-      <c r="U44">
-        <v>-100</v>
-      </c>
-      <c r="V44">
-        <v>18.989999999999998</v>
-      </c>
-      <c r="W44">
-        <v>4902.3</v>
-      </c>
-      <c r="X44">
-        <v>23</v>
-      </c>
-      <c r="Y44">
-        <v>5</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB44" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC44" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD44" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE44" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="N45">
-        <v>3</v>
-      </c>
-      <c r="O45">
-        <v>670.61</v>
-      </c>
-      <c r="P45">
-        <v>2</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>335.3</v>
-      </c>
-      <c r="T45" t="s">
-        <v>114</v>
-      </c>
-      <c r="U45">
-        <v>-100</v>
-      </c>
-      <c r="V45">
-        <v>8</v>
-      </c>
-      <c r="W45">
-        <v>1060.3499999999999</v>
-      </c>
-      <c r="X45">
-        <v>3</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="8">
-        <v>40</v>
-      </c>
-      <c r="AB45" s="8">
-        <v>1900</v>
-      </c>
-      <c r="AC45" s="9">
-        <v>95</v>
-      </c>
-      <c r="AD45" s="9">
-        <v>22</v>
-      </c>
-      <c r="AE45" s="10" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3776,466 +3668,466 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>55</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>53</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>22</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>15</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>9</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>68362.8</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>9</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>68362.8</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>79</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>74</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>32</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>12</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>7</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>40905.56</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>6</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>40755.56</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>11</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>9</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>1</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>729</v>
       </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>6</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>4</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>2</v>
       </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>13</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>12</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>2</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>58</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>52</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>25</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>19</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>6</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>40077.9399999999</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>32156.9399999999</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>30</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>23</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>11</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>6</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>3</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>18177.84</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>2</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
         <v>12943.84</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="5">
+      <c r="A14" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="4">
         <v>69</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>67</v>
       </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
         <v>21</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>7499</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>1</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>7499</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>54</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>47</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>31</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>10</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>10</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>79612.61</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>8</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>63438.61</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>89</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>76</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>34</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>23</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>9</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>68476</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>9</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>68476</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>33</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>30</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>18</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>12</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>8166</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>1</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>8166</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>22</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>22</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>10</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>4</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>1</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>8641</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>1</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>8641</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>35</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>34</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>16</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>14</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>3</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>25054</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>3</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>25054</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>20</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>18</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>9</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>3</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>2</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>16532</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>2</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>16532</v>
       </c>
     </row>
@@ -4251,7 +4143,7 @@
   <cols>
     <col min="1" max="1" width="54.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="11" customWidth="1"/>
     <col min="4" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4301,519 +4193,519 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5">
+      <c r="A5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4">
         <v>7</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>7092</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="4">
         <v>4567</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>12666.13</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>366.52</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>246</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>94</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>36</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>242533.65</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
         <v>18.149999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="4">
         <v>4420</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>11192.06</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>346.14</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>221</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>85</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>41</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>309366.3</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>26.64</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>4524</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>9916.58</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>419</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>251</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>99</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>49</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>336857.91</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="4">
         <v>32.97</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>2260</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>3186.05</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>185.34</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>98</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>48</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>17</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>131715.45000000001</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
         <v>40.340000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="B10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="4">
         <v>573</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>8252.69</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>29.95</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>19</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>14</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>3</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>24440.59</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>1.96</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="B11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="4">
         <v>574</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>7873.75</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>33.97</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>18</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>12</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
         <v>6</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>42574.400000000001</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="4">
         <v>4.41</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>617</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>7873.74</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>30.04</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>11</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>6</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>2</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>8675</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>393</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>5416.04</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>21.96</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>12</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>7</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
         <v>1</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>8149.6800000000012</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
         <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="B14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="4">
         <v>2996</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>28724.1</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>100.03</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>63</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>32</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>12</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="4">
         <v>96393</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
         <v>2.36</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="B15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="4">
         <v>2864</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>27112.02</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>104.95</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>64</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>26</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>5</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>38091</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
         <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>3423</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>34341.65</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>141.16999999999999</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>61</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>36</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>14</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="4">
         <v>98722.240000000005</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="4">
         <v>1.87</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>2378</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>27315.15</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>114.37</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>38</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>11</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>1</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="4">
         <v>7138.12</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="4">
         <v>-0.74</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="B18" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="4">
         <v>172</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>2066.37</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>12</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>7</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>2</v>
       </c>
-      <c r="I18" s="5">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5">
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
         <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="B19" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="4">
         <v>175</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>2178.34</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>3</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>1</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>1</v>
       </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
         <v>-1</v>
       </c>
     </row>
@@ -4821,10 +4713,10 @@
       <c r="A20" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D20">
@@ -4841,10 +4733,10 @@
       <c r="A21" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D21">
@@ -4861,11 +4753,11 @@
       <c r="A22" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>153</v>
+      <c r="B22" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D22">
         <v>2119</v>
@@ -4896,11 +4788,11 @@
       <c r="A23" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>154</v>
+      <c r="B23" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D23">
         <v>1914</v>
@@ -4931,10 +4823,10 @@
       <c r="A24" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D24">
@@ -4966,10 +4858,10 @@
       <c r="A25" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D25">
@@ -5001,11 +4893,11 @@
       <c r="A26" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>153</v>
+      <c r="B26" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D26">
         <v>489</v>
@@ -5036,11 +4928,11 @@
       <c r="A27" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>154</v>
+      <c r="B27" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D27">
         <v>371</v>
@@ -5071,10 +4963,10 @@
       <c r="A28" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D28">
@@ -5106,11 +4998,11 @@
       <c r="A29" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>153</v>
+      <c r="B29" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D29">
         <v>172</v>
@@ -5141,11 +5033,11 @@
       <c r="A30" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>154</v>
+      <c r="B30" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D30">
         <v>134</v>
@@ -5176,11 +5068,11 @@
       <c r="A31" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>153</v>
+      <c r="B31" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D31">
         <v>2248</v>
@@ -5208,11 +5100,11 @@
       <c r="A32" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>154</v>
+      <c r="B32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D32">
         <v>1955</v>
@@ -5240,10 +5132,10 @@
       <c r="A33" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C33" s="12" t="s">
+      <c r="B33" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D33">
@@ -5272,10 +5164,10 @@
       <c r="A34" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C34" s="12" t="s">
+      <c r="B34" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D34">
@@ -5304,10 +5196,10 @@
       <c r="A35" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="B35" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D35">
@@ -5324,10 +5216,10 @@
       <c r="A36" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="B36" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D36">
@@ -5344,10 +5236,10 @@
       <c r="A37" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="B37" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D37">
@@ -5379,11 +5271,11 @@
       <c r="A38" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>153</v>
+      <c r="B38" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D38">
         <v>428</v>
@@ -5414,11 +5306,11 @@
       <c r="A39" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>154</v>
+      <c r="B39" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D39">
         <v>358</v>
@@ -5449,10 +5341,10 @@
       <c r="A40" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="B40" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D40">
@@ -5484,10 +5376,10 @@
       <c r="A41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C41" s="12" t="s">
+      <c r="B41" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D41">
@@ -5519,11 +5411,11 @@
       <c r="A42" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>153</v>
+      <c r="B42" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D42">
         <v>249</v>
@@ -5554,11 +5446,11 @@
       <c r="A43" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>154</v>
+      <c r="B43" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D43">
         <v>266</v>
@@ -5589,10 +5481,10 @@
       <c r="A44" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="B44" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D44">
@@ -5624,10 +5516,10 @@
       <c r="A45" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C45" s="12" t="s">
+      <c r="B45" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C45" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D45">
@@ -5659,11 +5551,11 @@
       <c r="A46" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>153</v>
+      <c r="B46" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D46">
         <v>643</v>
@@ -5694,11 +5586,11 @@
       <c r="A47" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>154</v>
+      <c r="B47" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D47">
         <v>1049</v>
@@ -5729,10 +5621,10 @@
       <c r="A48" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C48" s="12" t="s">
+      <c r="B48" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C48" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D48">
@@ -5764,10 +5656,10 @@
       <c r="A49" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C49" s="12" t="s">
+      <c r="B49" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C49" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D49">
@@ -5799,11 +5691,11 @@
       <c r="A50" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>153</v>
+      <c r="B50" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D50">
         <v>1338</v>
@@ -5834,11 +5726,11 @@
       <c r="A51" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>154</v>
+      <c r="B51" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D51">
         <v>1332</v>
@@ -5869,10 +5761,10 @@
       <c r="A52" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C52" s="12" t="s">
+      <c r="B52" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D52">
@@ -5904,10 +5796,10 @@
       <c r="A53" t="s">
         <v>79</v>
       </c>
-      <c r="B53" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="B53" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C53" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D53">
@@ -5939,11 +5831,11 @@
       <c r="A54" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>153</v>
+      <c r="B54" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D54">
         <v>2434</v>
@@ -5974,11 +5866,11 @@
       <c r="A55" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>154</v>
+      <c r="B55" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D55">
         <v>2158</v>
@@ -6009,10 +5901,10 @@
       <c r="A56" t="s">
         <v>80</v>
       </c>
-      <c r="B56" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="B56" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C56" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D56">
@@ -6044,10 +5936,10 @@
       <c r="A57" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="B57" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C57" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D57">
@@ -6079,11 +5971,11 @@
       <c r="A58" t="s">
         <v>78</v>
       </c>
-      <c r="B58" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>153</v>
+      <c r="B58" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D58">
         <v>6193</v>
@@ -6114,11 +6006,11 @@
       <c r="A59" t="s">
         <v>78</v>
       </c>
-      <c r="B59" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>154</v>
+      <c r="B59" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D59">
         <v>6040</v>
@@ -6149,10 +6041,10 @@
       <c r="A60" t="s">
         <v>78</v>
       </c>
-      <c r="B60" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C60" s="12" t="s">
+      <c r="B60" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D60">
@@ -6184,10 +6076,10 @@
       <c r="A61" t="s">
         <v>78</v>
       </c>
-      <c r="B61" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C61" s="12" t="s">
+      <c r="B61" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C61" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D61">
@@ -6219,11 +6111,11 @@
       <c r="A62" t="s">
         <v>104</v>
       </c>
-      <c r="B62" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>153</v>
+      <c r="B62" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D62">
         <v>6542</v>
@@ -6254,11 +6146,11 @@
       <c r="A63" t="s">
         <v>104</v>
       </c>
-      <c r="B63" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>154</v>
+      <c r="B63" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D63">
         <v>6331</v>
@@ -6289,10 +6181,10 @@
       <c r="A64" t="s">
         <v>104</v>
       </c>
-      <c r="B64" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C64" s="12" t="s">
+      <c r="B64" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D64">
@@ -6324,10 +6216,10 @@
       <c r="A65" t="s">
         <v>104</v>
       </c>
-      <c r="B65" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="B65" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D65">
@@ -6359,11 +6251,11 @@
       <c r="A66" t="s">
         <v>105</v>
       </c>
-      <c r="B66" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>153</v>
+      <c r="B66" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D66">
         <v>3204</v>
@@ -6394,11 +6286,11 @@
       <c r="A67" t="s">
         <v>105</v>
       </c>
-      <c r="B67" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>154</v>
+      <c r="B67" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D67">
         <v>2906</v>
@@ -6429,10 +6321,10 @@
       <c r="A68" t="s">
         <v>105</v>
       </c>
-      <c r="B68" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C68" s="12" t="s">
+      <c r="B68" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C68" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D68">
@@ -6464,10 +6356,10 @@
       <c r="A69" t="s">
         <v>105</v>
       </c>
-      <c r="B69" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C69" s="12" t="s">
+      <c r="B69" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C69" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D69">
@@ -6499,11 +6391,11 @@
       <c r="A70" t="s">
         <v>107</v>
       </c>
-      <c r="B70" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>153</v>
+      <c r="B70" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D70">
         <v>546</v>
@@ -6534,11 +6426,11 @@
       <c r="A71" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>154</v>
+      <c r="B71" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D71">
         <v>568</v>
@@ -6569,10 +6461,10 @@
       <c r="A72" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C72" s="12" t="s">
+      <c r="B72" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C72" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D72">
@@ -6604,10 +6496,10 @@
       <c r="A73" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C73" s="12" t="s">
+      <c r="B73" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C73" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D73">
@@ -6639,11 +6531,11 @@
       <c r="A74" t="s">
         <v>108</v>
       </c>
-      <c r="B74" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>153</v>
+      <c r="B74" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D74">
         <v>1861</v>
@@ -6674,11 +6566,11 @@
       <c r="A75" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>154</v>
+      <c r="B75" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D75">
         <v>1516</v>
@@ -6709,10 +6601,10 @@
       <c r="A76" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C76" s="12" t="s">
+      <c r="B76" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D76">
@@ -6744,10 +6636,10 @@
       <c r="A77" t="s">
         <v>108</v>
       </c>
-      <c r="B77" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C77" s="12" t="s">
+      <c r="B77" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C77" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D77">
@@ -6779,11 +6671,11 @@
       <c r="A78" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>153</v>
+      <c r="B78" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D78">
         <v>545</v>
@@ -6811,11 +6703,11 @@
       <c r="A79" t="s">
         <v>110</v>
       </c>
-      <c r="B79" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>154</v>
+      <c r="B79" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D79">
         <v>575</v>
@@ -6843,10 +6735,10 @@
       <c r="A80" t="s">
         <v>110</v>
       </c>
-      <c r="B80" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C80" s="12" t="s">
+      <c r="B80" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C80" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D80">
@@ -6875,10 +6767,10 @@
       <c r="A81" t="s">
         <v>110</v>
       </c>
-      <c r="B81" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C81" s="12" t="s">
+      <c r="B81" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C81" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D81">
@@ -6907,11 +6799,11 @@
       <c r="A82" t="s">
         <v>111</v>
       </c>
-      <c r="B82" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>153</v>
+      <c r="B82" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D82">
         <v>1456</v>
@@ -6942,11 +6834,11 @@
       <c r="A83" t="s">
         <v>111</v>
       </c>
-      <c r="B83" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>154</v>
+      <c r="B83" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D83">
         <v>1682</v>
@@ -6977,10 +6869,10 @@
       <c r="A84" t="s">
         <v>111</v>
       </c>
-      <c r="B84" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C84" s="12" t="s">
+      <c r="B84" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C84" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D84">
@@ -7012,10 +6904,10 @@
       <c r="A85" t="s">
         <v>111</v>
       </c>
-      <c r="B85" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C85" s="12" t="s">
+      <c r="B85" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D85">
@@ -7045,13 +6937,13 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>152</v>
-      </c>
-      <c r="B86" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>153</v>
+        <v>117</v>
+      </c>
+      <c r="B86" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D86">
         <v>75</v>
@@ -7065,13 +6957,13 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>154</v>
+        <v>117</v>
+      </c>
+      <c r="B87" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D87">
         <v>130</v>
@@ -7087,11 +6979,11 @@
       <c r="A88" t="s">
         <v>81</v>
       </c>
-      <c r="B88" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>153</v>
+      <c r="B88" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="D88">
         <v>512</v>
@@ -7122,11 +7014,11 @@
       <c r="A89" t="s">
         <v>81</v>
       </c>
-      <c r="B89" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>154</v>
+      <c r="B89" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="D89">
         <v>450</v>
@@ -7157,10 +7049,10 @@
       <c r="A90" t="s">
         <v>81</v>
       </c>
-      <c r="B90" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C90" s="12" t="s">
+      <c r="B90" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C90" s="11" t="s">
         <v>75</v>
       </c>
       <c r="D90">
@@ -7192,10 +7084,10 @@
       <c r="A91" t="s">
         <v>81</v>
       </c>
-      <c r="B91" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C91" s="12" t="s">
+      <c r="B91" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C91" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D91">
@@ -7225,13 +7117,13 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>154</v>
+        <v>116</v>
+      </c>
+      <c r="B92" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="G92">
         <v>6</v>
@@ -7248,12 +7140,12 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>151</v>
-      </c>
-      <c r="B93" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C93" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C93" s="11" t="s">
         <v>75</v>
       </c>
       <c r="G93">
@@ -7271,12 +7163,12 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>151</v>
-      </c>
-      <c r="B94" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C94" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C94" s="11" t="s">
         <v>74</v>
       </c>
       <c r="G94">

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C755A3-84A2-446F-9FCB-F0FC5A11583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D7FBF6-5F03-4439-ABDB-847C475C1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="171">
   <si>
     <t>Tab 1 — KPI Data</t>
   </si>
@@ -541,7 +541,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +572,12 @@
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1157,9 +1163,15 @@
         <v>54</v>
       </c>
       <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
+      <c r="AB6" s="8">
+        <v>253000</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>867</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>364</v>
+      </c>
       <c r="AE6" s="9" t="s">
         <v>35</v>
       </c>
@@ -1244,14 +1256,12 @@
         <v>18</v>
       </c>
       <c r="AA7" s="8"/>
-      <c r="AB7" s="8">
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="9">
         <v>257</v>
       </c>
-      <c r="AC7" s="9">
-        <v>0</v>
-      </c>
       <c r="AD7" s="9">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AE7" s="9" t="s">
         <v>35</v>
@@ -1340,13 +1350,13 @@
         <v>8000</v>
       </c>
       <c r="AB8" s="8">
+        <v>8000</v>
+      </c>
+      <c r="AC8" s="9">
         <v>11</v>
       </c>
-      <c r="AC8" s="9">
-        <v>0</v>
-      </c>
       <c r="AD8" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE8" s="9" t="s">
         <v>35</v>
@@ -1435,13 +1445,13 @@
         <v>40000</v>
       </c>
       <c r="AB9" s="8">
+        <v>40000</v>
+      </c>
+      <c r="AC9" s="9">
         <v>62</v>
       </c>
-      <c r="AC9" s="9">
-        <v>0</v>
-      </c>
       <c r="AD9" s="9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE9" s="9" t="s">
         <v>35</v>
@@ -1774,7 +1784,9 @@
       <c r="AA15" s="8">
         <v>4000</v>
       </c>
-      <c r="AB15" s="8"/>
+      <c r="AB15" s="8">
+        <v>4000</v>
+      </c>
       <c r="AC15" s="9"/>
       <c r="AD15" s="9"/>
       <c r="AE15" s="9" t="s">
@@ -1864,13 +1876,13 @@
         <v>24000</v>
       </c>
       <c r="AB16" s="8">
+        <v>24000</v>
+      </c>
+      <c r="AC16" s="9">
         <v>44</v>
       </c>
-      <c r="AC16" s="9">
-        <v>0</v>
-      </c>
       <c r="AD16" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE16" s="9" t="s">
         <v>35</v>
@@ -2022,13 +2034,13 @@
         <v>7000</v>
       </c>
       <c r="AB18" s="8">
+        <v>7000</v>
+      </c>
+      <c r="AC18" s="9">
         <v>7</v>
       </c>
-      <c r="AC18" s="9">
-        <v>0</v>
-      </c>
       <c r="AD18" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE18" s="9" t="s">
         <v>35</v>
@@ -2125,14 +2137,12 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="8"/>
-      <c r="AB20" s="8">
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="9">
         <v>3</v>
       </c>
-      <c r="AC20" s="9">
-        <v>0</v>
-      </c>
       <c r="AD20" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE20" s="9" t="s">
         <v>35</v>
@@ -2370,13 +2380,13 @@
         <v>6000</v>
       </c>
       <c r="AB24" s="8">
+        <v>6000</v>
+      </c>
+      <c r="AC24" s="9">
         <v>8</v>
       </c>
-      <c r="AC24" s="9">
-        <v>0</v>
-      </c>
       <c r="AD24" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE24" s="9" t="s">
         <v>35</v>
@@ -2462,7 +2472,9 @@
       <c r="AA25" s="8">
         <v>7000</v>
       </c>
-      <c r="AB25" s="8"/>
+      <c r="AB25" s="8">
+        <v>7000</v>
+      </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
       <c r="AE25" s="9" t="s">
@@ -2552,13 +2564,13 @@
         <v>12000</v>
       </c>
       <c r="AB26" s="8">
+        <v>12000</v>
+      </c>
+      <c r="AC26" s="9">
         <v>26</v>
       </c>
-      <c r="AC26" s="9">
-        <v>0</v>
-      </c>
       <c r="AD26" s="9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE26" s="9" t="s">
         <v>35</v>
@@ -2710,13 +2722,13 @@
         <v>13000</v>
       </c>
       <c r="AB28" s="8">
+        <v>13000</v>
+      </c>
+      <c r="AC28" s="9">
         <v>29</v>
       </c>
-      <c r="AC28" s="9">
-        <v>0</v>
-      </c>
       <c r="AD28" s="9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE28" s="9" t="s">
         <v>35</v>
@@ -2976,13 +2988,13 @@
         <v>28000</v>
       </c>
       <c r="AB32" s="8">
+        <v>28000</v>
+      </c>
+      <c r="AC32" s="9">
         <v>43</v>
       </c>
-      <c r="AC32" s="9">
-        <v>0</v>
-      </c>
       <c r="AD32" s="9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE32" s="9" t="s">
         <v>35</v>
@@ -3042,14 +3054,12 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="8"/>
-      <c r="AB33" s="8">
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="9">
         <v>85</v>
       </c>
-      <c r="AC33" s="9">
-        <v>0</v>
-      </c>
       <c r="AD33" s="9">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AE33" s="9" t="s">
         <v>35</v>
@@ -3109,14 +3119,12 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
       <c r="AA34" s="8"/>
-      <c r="AB34" s="8">
+      <c r="AB34" s="8"/>
+      <c r="AC34" s="9">
         <v>55</v>
       </c>
-      <c r="AC34" s="9">
-        <v>0</v>
-      </c>
       <c r="AD34" s="9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE34" s="9" t="s">
         <v>35</v>
@@ -3205,13 +3213,13 @@
         <v>35000</v>
       </c>
       <c r="AB35" s="8">
+        <v>35000</v>
+      </c>
+      <c r="AC35" s="9">
         <v>52</v>
       </c>
-      <c r="AC35" s="9">
-        <v>0</v>
-      </c>
       <c r="AD35" s="9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE35" s="9" t="s">
         <v>35</v>
@@ -3334,14 +3342,12 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="8"/>
-      <c r="AB37" s="8">
+      <c r="AB37" s="8"/>
+      <c r="AC37" s="9">
         <v>28</v>
       </c>
-      <c r="AC37" s="9">
-        <v>0</v>
-      </c>
       <c r="AD37" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE37" s="9" t="s">
         <v>35</v>
@@ -3430,13 +3436,13 @@
         <v>17000</v>
       </c>
       <c r="AB38" s="8">
+        <v>17000</v>
+      </c>
+      <c r="AC38" s="9">
         <v>25</v>
       </c>
-      <c r="AC38" s="9">
-        <v>0</v>
-      </c>
       <c r="AD38" s="9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE38" s="9" t="s">
         <v>35</v>
@@ -3579,7 +3585,9 @@
       <c r="AA40" s="8">
         <v>17000</v>
       </c>
-      <c r="AB40" s="8"/>
+      <c r="AB40" s="8">
+        <v>17000</v>
+      </c>
       <c r="AC40" s="9"/>
       <c r="AD40" s="9"/>
       <c r="AE40" s="9" t="s">
@@ -3669,13 +3677,16 @@
         <v>24000</v>
       </c>
       <c r="AB41">
+        <v>24000</v>
+      </c>
+      <c r="AC41">
         <v>32</v>
       </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
       <c r="AD41">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="AE41" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
@@ -3721,6 +3732,9 @@
       <c r="Z42">
         <v>0</v>
       </c>
+      <c r="AE42" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -3805,13 +3819,16 @@
         <v>11000</v>
       </c>
       <c r="AB43">
+        <v>11000</v>
+      </c>
+      <c r="AC43">
         <v>11</v>
       </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
       <c r="AD43">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="AE43" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
@@ -3854,8 +3871,12 @@
       <c r="Z44">
         <v>0</v>
       </c>
+      <c r="AE44" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D7FBF6-5F03-4439-ABDB-847C475C1B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A04112-4BDC-4103-903B-03EBD95E8866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Tab2_Regional" sheetId="2" r:id="rId2"/>
     <sheet name="Tab3_Campaign" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tab1_KPI!$A$5:$AE$44</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -541,7 +544,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +581,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -636,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -662,6 +672,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -966,11 +979,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="31" width="14" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
@@ -1084,7 +1123,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="5">
@@ -1164,7 +1203,7 @@
       </c>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8">
-        <v>253000</v>
+        <v>395500</v>
       </c>
       <c r="AC6" s="9">
         <v>867</v>
@@ -1256,7 +1295,9 @@
         <v>18</v>
       </c>
       <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
+      <c r="AB7" s="8">
+        <v>15000</v>
+      </c>
       <c r="AC7" s="9">
         <v>257</v>
       </c>
@@ -1457,7 +1498,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>39</v>
       </c>
@@ -1502,7 +1543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
@@ -1565,7 +1606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
@@ -1628,7 +1669,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>42</v>
       </c>
@@ -1673,7 +1714,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1888,7 +1929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>46</v>
       </c>
@@ -2046,7 +2087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
@@ -2091,7 +2132,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>49</v>
       </c>
@@ -2137,7 +2178,9 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
+      <c r="AB20" s="8">
+        <v>0</v>
+      </c>
       <c r="AC20" s="9">
         <v>3</v>
       </c>
@@ -2202,7 +2245,9 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
       <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
+      <c r="AB21" s="8">
+        <v>22000</v>
+      </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
       <c r="AE21" s="9" t="s">
@@ -2247,7 +2292,9 @@
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
       <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
+      <c r="AB22" s="8">
+        <v>3000</v>
+      </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
       <c r="AE22" s="9" t="s">
@@ -2308,7 +2355,9 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
       <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
+      <c r="AB23" s="8">
+        <v>40000</v>
+      </c>
       <c r="AC23" s="9"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="9" t="s">
@@ -2576,7 +2625,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
@@ -2734,7 +2783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
@@ -2779,7 +2828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>59</v>
       </c>
@@ -2842,7 +2891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>166</v>
       </c>
@@ -3054,7 +3103,9 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
+      <c r="AB33" s="8">
+        <v>30000</v>
+      </c>
       <c r="AC33" s="9">
         <v>85</v>
       </c>
@@ -3119,7 +3170,9 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
       <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
+      <c r="AB34" s="8">
+        <v>25000</v>
+      </c>
       <c r="AC34" s="9">
         <v>55</v>
       </c>
@@ -3225,7 +3278,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>167</v>
       </c>
@@ -3342,7 +3395,9 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="8"/>
-      <c r="AB37" s="8"/>
+      <c r="AB37" s="8">
+        <v>7500</v>
+      </c>
       <c r="AC37" s="9">
         <v>28</v>
       </c>
@@ -3448,7 +3503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>168</v>
       </c>
@@ -3689,7 +3744,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>169</v>
       </c>
@@ -3831,7 +3886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -3876,6 +3931,31 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:AE44" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="27">
+      <filters>
+        <filter val="11000"/>
+        <filter val="12000"/>
+        <filter val="13000"/>
+        <filter val="15000"/>
+        <filter val="17000"/>
+        <filter val="22000"/>
+        <filter val="24000"/>
+        <filter val="25000"/>
+        <filter val="28000"/>
+        <filter val="3000"/>
+        <filter val="30000"/>
+        <filter val="35000"/>
+        <filter val="395500"/>
+        <filter val="4000"/>
+        <filter val="40000"/>
+        <filter val="6000"/>
+        <filter val="7000"/>
+        <filter val="7500"/>
+        <filter val="8000"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A04112-4BDC-4103-903B-03EBD95E8866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08061D92-7746-4B3E-8BBF-87475ED9B49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -387,9 +387,6 @@
     <t>6.67%</t>
   </si>
   <si>
-    <t>National Sales</t>
-  </si>
-  <si>
     <t>12.96%</t>
   </si>
   <si>
@@ -538,6 +535,9 @@
   </si>
   <si>
     <t>Ventura-Performance Max</t>
+  </si>
+  <si>
+    <t>National Sales Team</t>
   </si>
 </sst>
 </file>
@@ -557,24 +557,28 @@
       <sz val="13"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2893,7 +2897,7 @@
     </row>
     <row r="31" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -3280,7 +3284,7 @@
     </row>
     <row r="36" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3505,7 +3509,7 @@
     </row>
     <row r="39" spans="1:31" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3746,7 +3750,7 @@
     </row>
     <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N42">
         <v>18.059999999999999</v>
@@ -3888,7 +3892,7 @@
     </row>
     <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -4040,28 +4044,28 @@
         <v>85</v>
       </c>
       <c r="B5" s="5">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5">
-        <v>23304</v>
+        <v>68362.8</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>23304</v>
+        <v>68362.8</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>86</v>
@@ -4084,13 +4088,13 @@
         <v>91</v>
       </c>
       <c r="B6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -4128,28 +4132,28 @@
         <v>94</v>
       </c>
       <c r="B7" s="5">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D7" s="5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E7" s="5">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5">
+        <v>40905.56</v>
+      </c>
+      <c r="H7" s="5">
         <v>6</v>
       </c>
-      <c r="F7" s="5">
-        <v>3</v>
-      </c>
-      <c r="G7" s="5">
-        <v>13794</v>
-      </c>
-      <c r="H7" s="5">
-        <v>2</v>
-      </c>
       <c r="I7" s="5">
-        <v>13644</v>
+        <v>40755.56</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>95</v>
@@ -4172,22 +4176,22 @@
         <v>100</v>
       </c>
       <c r="B8" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>6</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
       <c r="G8" s="5">
-        <v>0</v>
+        <v>729</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -4216,16 +4220,16 @@
         <v>102</v>
       </c>
       <c r="B9" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
         <v>3</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -4260,16 +4264,16 @@
         <v>105</v>
       </c>
       <c r="B10" s="5">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
         <v>1</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -4304,16 +4308,16 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -4348,28 +4352,28 @@
         <v>108</v>
       </c>
       <c r="B12" s="5">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C12" s="5">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D12" s="5">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F12" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>12797</v>
+        <v>40077.9399999999</v>
       </c>
       <c r="H12" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" s="5">
-        <v>12797</v>
+        <v>32156.9399999999</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>109</v>
@@ -4392,28 +4396,28 @@
         <v>114</v>
       </c>
       <c r="B13" s="5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C13" s="5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5">
+        <v>6</v>
+      </c>
+      <c r="F13" s="5">
         <v>3</v>
       </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
       <c r="G13" s="5">
-        <v>7954</v>
+        <v>18177.84</v>
       </c>
       <c r="H13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="5">
-        <v>7954</v>
+        <v>12943.84</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>115</v>
@@ -4433,37 +4437,37 @@
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="5">
+        <v>69</v>
+      </c>
+      <c r="C14" s="5">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>7499</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>7499</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="5">
-        <v>37</v>
-      </c>
-      <c r="C14" s="5">
-        <v>36</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>13</v>
-      </c>
-      <c r="F14" s="5">
-        <v>2</v>
-      </c>
-      <c r="G14" s="5">
-        <v>7684</v>
-      </c>
-      <c r="H14" s="5">
-        <v>2</v>
-      </c>
-      <c r="I14" s="5">
-        <v>7684</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>93</v>
@@ -4472,133 +4476,133 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="5">
+        <v>54</v>
+      </c>
+      <c r="C15" s="5">
+        <v>47</v>
+      </c>
+      <c r="D15" s="5">
+        <v>31</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5">
+        <v>79612.61</v>
+      </c>
+      <c r="H15" s="5">
+        <v>8</v>
+      </c>
+      <c r="I15" s="5">
+        <v>63438.61</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B15" s="5">
-        <v>26</v>
-      </c>
-      <c r="C15" s="5">
-        <v>21</v>
-      </c>
-      <c r="D15" s="5">
-        <v>17</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5">
-        <v>16352</v>
-      </c>
-      <c r="H15" s="5">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5">
-        <v>7794</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="L15" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="M15" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="N15" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="5">
+        <v>89</v>
+      </c>
+      <c r="C16" s="5">
+        <v>76</v>
+      </c>
+      <c r="D16" s="5">
+        <v>34</v>
+      </c>
+      <c r="E16" s="5">
+        <v>23</v>
+      </c>
+      <c r="F16" s="5">
+        <v>9</v>
+      </c>
+      <c r="G16" s="5">
+        <v>68476</v>
+      </c>
+      <c r="H16" s="5">
+        <v>9</v>
+      </c>
+      <c r="I16" s="5">
+        <v>68476</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="5">
-        <v>44</v>
-      </c>
-      <c r="C16" s="5">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5">
-        <v>14</v>
-      </c>
-      <c r="E16" s="5">
-        <v>10</v>
-      </c>
-      <c r="F16" s="5">
-        <v>3</v>
-      </c>
-      <c r="G16" s="5">
-        <v>23993</v>
-      </c>
-      <c r="H16" s="5">
-        <v>3</v>
-      </c>
-      <c r="I16" s="5">
-        <v>23993</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="M16" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="5">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>18</v>
+      </c>
+      <c r="E17" s="5">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>8166</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>8166</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="5">
-        <v>19</v>
-      </c>
-      <c r="C17" s="5">
-        <v>18</v>
-      </c>
-      <c r="D17" s="5">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="K17" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="L17" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>93</v>
@@ -4609,19 +4613,19 @@
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C18" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -4636,57 +4640,57 @@
         <v>8641</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="L18" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="M18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="N18" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="5">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5">
+        <v>16</v>
+      </c>
+      <c r="E19" s="5">
+        <v>14</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3</v>
+      </c>
+      <c r="G19" s="5">
+        <v>25054</v>
+      </c>
+      <c r="H19" s="5">
+        <v>3</v>
+      </c>
+      <c r="I19" s="5">
+        <v>25054</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="5">
-        <v>22</v>
-      </c>
-      <c r="C19" s="5">
-        <v>21</v>
-      </c>
-      <c r="D19" s="5">
-        <v>6</v>
-      </c>
-      <c r="E19" s="5">
-        <v>4</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="L19" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>93</v>
@@ -4697,19 +4701,19 @@
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="5">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
+        <v>18</v>
+      </c>
+      <c r="D20" s="5">
         <v>9</v>
       </c>
-      <c r="C20" s="5">
-        <v>8</v>
-      </c>
-      <c r="D20" s="5">
-        <v>5</v>
-      </c>
       <c r="E20" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="5">
         <v>2</v>
@@ -4724,13 +4728,13 @@
         <v>16532</v>
       </c>
       <c r="J20" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="L20" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>88</v>
@@ -4755,12 +4759,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4768,34 +4772,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4806,7 +4810,7 @@
         <v>2026</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D5" s="5">
         <v>1431</v>
@@ -4841,7 +4845,7 @@
         <v>2026</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D6" s="5">
         <v>1380</v>
@@ -4876,7 +4880,7 @@
         <v>2025</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D7" s="5">
         <v>1250</v>
@@ -4911,7 +4915,7 @@
         <v>2026</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="5">
         <v>224</v>
@@ -4946,7 +4950,7 @@
         <v>2025</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" s="5">
         <v>198</v>
@@ -4981,7 +4985,7 @@
         <v>2026</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="5">
         <v>794</v>
@@ -5016,7 +5020,7 @@
         <v>2025</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" s="5">
         <v>700</v>
@@ -5051,7 +5055,7 @@
         <v>2026</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="5">
         <v>1673</v>
@@ -5086,7 +5090,7 @@
         <v>2025</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" s="5">
         <v>1470</v>
@@ -5121,7 +5125,7 @@
         <v>2026</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14" s="5">
         <v>414</v>
@@ -5156,7 +5160,7 @@
         <v>2025</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="5">
         <v>365</v>
@@ -5191,7 +5195,7 @@
         <v>2026</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D16" s="5">
         <v>910</v>
@@ -5226,7 +5230,7 @@
         <v>2025</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17" s="5">
         <v>850</v>
@@ -5261,7 +5265,7 @@
         <v>2026</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D18" s="5">
         <v>264</v>
@@ -5296,7 +5300,7 @@
         <v>2025</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D19" s="5">
         <v>245</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A047C455-77EA-495C-86CB-C25EF29BA0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FF8EEE-BFC2-451C-A7D4-C7F7F960515E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -573,18 +573,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,7 +920,7 @@
     <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="14" style="15" customWidth="1"/>
+    <col min="31" max="31" width="14" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
@@ -1029,7 +1029,7 @@
       <c r="AD5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AE5" s="16" t="s">
+      <c r="AE5" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       <c r="AD6" s="9">
         <v>364</v>
       </c>
-      <c r="AE6" s="17">
+      <c r="AE6" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       <c r="AD7" s="9">
         <v>5</v>
       </c>
-      <c r="AE7" s="17">
+      <c r="AE7" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="AD8" s="9">
         <v>30</v>
       </c>
-      <c r="AE8" s="17">
+      <c r="AE8" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="9"/>
       <c r="AD9" s="9"/>
-      <c r="AE9" s="17">
+      <c r="AE9" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       <c r="AB10" s="8"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
-      <c r="AE10" s="17">
+      <c r="AE10" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       <c r="AB11" s="8"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="9"/>
-      <c r="AE11" s="17">
+      <c r="AE11" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="AB12" s="8"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
-      <c r="AE12" s="17">
+      <c r="AE12" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       <c r="AB13" s="8"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="9"/>
-      <c r="AE13" s="17">
+      <c r="AE13" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
-      <c r="AE14" s="17">
+      <c r="AE14" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       <c r="AD15" s="9">
         <v>20</v>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       <c r="AB16" s="8"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
-      <c r="AE16" s="17">
+      <c r="AE16" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       <c r="AD17" s="9">
         <v>3</v>
       </c>
-      <c r="AE17" s="17">
+      <c r="AE17" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       <c r="AB18" s="8"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
-      <c r="AE18" s="17">
+      <c r="AE18" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       <c r="AD19" s="9">
         <v>3</v>
       </c>
-      <c r="AE19" s="17">
+      <c r="AE19" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
-      <c r="AE20" s="17">
+      <c r="AE20" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
-      <c r="AE21" s="17">
+      <c r="AE21" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
-      <c r="AE22" s="17">
+      <c r="AE22" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       <c r="AD23" s="9">
         <v>2</v>
       </c>
-      <c r="AE23" s="17">
+      <c r="AE23" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
-      <c r="AE24" s="17">
+      <c r="AE24" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       <c r="AD25" s="9">
         <v>11</v>
       </c>
-      <c r="AE25" s="17">
+      <c r="AE25" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
-      <c r="AE26" s="17">
+      <c r="AE26" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       <c r="AD27" s="9">
         <v>12</v>
       </c>
-      <c r="AE27" s="17">
+      <c r="AE27" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       <c r="AB28" s="8"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9"/>
-      <c r="AE28" s="17">
+      <c r="AE28" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       <c r="AB29" s="8"/>
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
-      <c r="AE29" s="17">
+      <c r="AE29" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="9"/>
-      <c r="AE30" s="17">
+      <c r="AE30" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       <c r="AD31" s="9">
         <v>19</v>
       </c>
-      <c r="AE31" s="17">
+      <c r="AE31" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       <c r="AD32" s="9">
         <v>41</v>
       </c>
-      <c r="AE32" s="17">
+      <c r="AE32" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       <c r="AD33" s="9">
         <v>23</v>
       </c>
-      <c r="AE33" s="17">
+      <c r="AE33" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       <c r="AD34" s="9">
         <v>14</v>
       </c>
-      <c r="AE34" s="17">
+      <c r="AE34" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       <c r="AB35" s="8"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
-      <c r="AE35" s="17">
+      <c r="AE35" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       <c r="AD36" s="9">
         <v>15</v>
       </c>
-      <c r="AE36" s="17">
+      <c r="AE36" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       <c r="AD37" s="9">
         <v>14</v>
       </c>
-      <c r="AE37" s="17">
+      <c r="AE37" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       <c r="AB38" s="8"/>
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
-      <c r="AE38" s="17">
+      <c r="AE38" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
-      <c r="AE39" s="17">
+      <c r="AE39" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       <c r="AD40" s="9">
         <v>14</v>
       </c>
-      <c r="AE40" s="17">
+      <c r="AE40" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       <c r="AA41">
         <v>24000</v>
       </c>
-      <c r="AE41" s="17">
+      <c r="AE41" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       <c r="Z42">
         <v>0</v>
       </c>
-      <c r="AE42" s="17">
+      <c r="AE42" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       <c r="AD43">
         <v>5</v>
       </c>
-      <c r="AE43" s="17">
+      <c r="AE43" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       <c r="Z44">
         <v>0</v>
       </c>
-      <c r="AE44" s="17">
+      <c r="AE44" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3783,11 +3783,11 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="13" style="12" customWidth="1"/>
-    <col min="11" max="11" width="16" style="12" customWidth="1"/>
-    <col min="12" max="12" width="11" style="12" customWidth="1"/>
-    <col min="13" max="13" width="12" style="12" customWidth="1"/>
-    <col min="14" max="14" width="13" style="12" customWidth="1"/>
+    <col min="10" max="10" width="13" style="15" customWidth="1"/>
+    <col min="11" max="11" width="16" style="15" customWidth="1"/>
+    <col min="12" max="12" width="11" style="15" customWidth="1"/>
+    <col min="13" max="13" width="12" style="15" customWidth="1"/>
+    <col min="14" max="14" width="13" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -3828,19 +3828,19 @@
       <c r="I4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="16" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3872,20 +3872,20 @@
       <c r="I5" s="5">
         <v>68362.8</v>
       </c>
-      <c r="J5" s="14">
-        <v>4.8092868988391303E-2</v>
-      </c>
-      <c r="K5" s="14">
-        <v>9.2333362732210003E-2</v>
-      </c>
-      <c r="L5" s="14">
-        <v>0.37931034482758602</v>
-      </c>
-      <c r="M5" s="14">
-        <v>0.40909090909090901</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0.15517241379310301</v>
+      <c r="J5" s="17">
+        <v>4</v>
+      </c>
+      <c r="K5" s="17">
+        <v>9</v>
+      </c>
+      <c r="L5" s="17">
+        <v>37</v>
+      </c>
+      <c r="M5" s="17">
+        <v>40</v>
+      </c>
+      <c r="N5" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3916,19 +3916,19 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="14">
-        <v>8.2918739635157504E-4</v>
-      </c>
-      <c r="K6" s="14">
-        <v>0</v>
-      </c>
-      <c r="L6" s="14">
-        <v>1</v>
-      </c>
-      <c r="M6" s="14">
-        <v>0</v>
-      </c>
-      <c r="N6" s="14">
+      <c r="J6" s="17">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <v>0</v>
+      </c>
+      <c r="L6" s="17">
+        <v>100</v>
+      </c>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3960,20 +3960,20 @@
       <c r="I7" s="5">
         <v>40755.56</v>
       </c>
-      <c r="J7" s="14">
-        <v>6.7164179104477598E-2</v>
-      </c>
-      <c r="K7" s="14">
-        <v>5.5248584160452398E-2</v>
-      </c>
-      <c r="L7" s="14">
-        <v>0.407407407407407</v>
-      </c>
-      <c r="M7" s="14">
-        <v>0.21212121212121199</v>
-      </c>
-      <c r="N7" s="14">
-        <v>8.6419753086419707E-2</v>
+      <c r="J7" s="17">
+        <v>6</v>
+      </c>
+      <c r="K7" s="17">
+        <v>5</v>
+      </c>
+      <c r="L7" s="17">
+        <v>40</v>
+      </c>
+      <c r="M7" s="17">
+        <v>21</v>
+      </c>
+      <c r="N7" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4004,20 +4004,20 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="14">
-        <v>9.9502487562189001E-3</v>
-      </c>
-      <c r="K8" s="14">
-        <v>9.8461475293260491E-4</v>
-      </c>
-      <c r="L8" s="14">
-        <v>0.16666666666666599</v>
-      </c>
-      <c r="M8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="N8" s="14">
-        <v>8.3333333333333301E-2</v>
+      <c r="J8" s="17">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17">
+        <v>0</v>
+      </c>
+      <c r="L8" s="17">
+        <v>16</v>
+      </c>
+      <c r="M8" s="17">
+        <v>50</v>
+      </c>
+      <c r="N8" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4048,19 +4048,19 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="14">
-        <v>5.80431177446102E-3</v>
-      </c>
-      <c r="K9" s="14">
-        <v>0</v>
-      </c>
-      <c r="L9" s="14">
-        <v>0.57142857142857095</v>
-      </c>
-      <c r="M9" s="14">
-        <v>0</v>
-      </c>
-      <c r="N9" s="14">
+      <c r="J9" s="17">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17">
+        <v>0</v>
+      </c>
+      <c r="L9" s="17">
+        <v>57</v>
+      </c>
+      <c r="M9" s="17">
+        <v>0</v>
+      </c>
+      <c r="N9" s="17">
         <v>0</v>
       </c>
     </row>
@@ -4092,17 +4092,19 @@
       <c r="I10" s="5">
         <v>0</v>
       </c>
-      <c r="J10" s="14">
-        <v>1.6583747927031501E-3</v>
-      </c>
-      <c r="K10" s="14">
-        <v>0</v>
-      </c>
-      <c r="L10" s="14">
-        <v>0</v>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14">
+      <c r="J10" s="17">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
+      <c r="M10" s="17">
+        <v>0</v>
+      </c>
+      <c r="N10" s="17">
         <v>0</v>
       </c>
     </row>
@@ -4134,19 +4136,19 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="14">
-        <v>1.0779436152570401E-2</v>
-      </c>
-      <c r="K11" s="14">
-        <v>0</v>
-      </c>
-      <c r="L11" s="14">
-        <v>0.23076923076923</v>
-      </c>
-      <c r="M11" s="14">
-        <v>0</v>
-      </c>
-      <c r="N11" s="14">
+      <c r="J11" s="17">
+        <v>1</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17">
+        <v>23</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17">
         <v>0</v>
       </c>
     </row>
@@ -4178,20 +4180,20 @@
       <c r="I12" s="5">
         <v>32156.9399999999</v>
       </c>
-      <c r="J12" s="14">
-        <v>4.9751243781094502E-2</v>
-      </c>
-      <c r="K12" s="14">
-        <v>5.4130769535182102E-2</v>
-      </c>
-      <c r="L12" s="14">
-        <v>0.43333333333333302</v>
-      </c>
-      <c r="M12" s="14">
-        <v>0.23076923076923</v>
-      </c>
-      <c r="N12" s="14">
-        <v>0.1</v>
+      <c r="J12" s="17">
+        <v>4</v>
+      </c>
+      <c r="K12" s="17">
+        <v>5</v>
+      </c>
+      <c r="L12" s="17">
+        <v>43</v>
+      </c>
+      <c r="M12" s="17">
+        <v>23</v>
+      </c>
+      <c r="N12" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4222,20 +4224,20 @@
       <c r="I13" s="5">
         <v>12943.84</v>
       </c>
-      <c r="J13" s="14">
-        <v>2.5704809286898798E-2</v>
-      </c>
-      <c r="K13" s="14">
-        <v>2.4551672757816698E-2</v>
-      </c>
-      <c r="L13" s="14">
-        <v>0.38709677419354799</v>
-      </c>
-      <c r="M13" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="N13" s="14">
-        <v>9.6774193548387094E-2</v>
+      <c r="J13" s="17">
+        <v>2</v>
+      </c>
+      <c r="K13" s="17">
+        <v>2</v>
+      </c>
+      <c r="L13" s="17">
+        <v>38</v>
+      </c>
+      <c r="M13" s="17">
+        <v>25</v>
+      </c>
+      <c r="N13" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4266,18 +4268,20 @@
       <c r="I14" s="5">
         <v>7499</v>
       </c>
-      <c r="J14" s="14">
-        <v>6.1359867330016499E-2</v>
-      </c>
-      <c r="K14" s="14">
-        <v>1.0128430771250399E-2</v>
-      </c>
-      <c r="L14" s="14">
-        <v>0</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14">
-        <v>1.35135135135135E-2</v>
+      <c r="J14" s="17">
+        <v>6</v>
+      </c>
+      <c r="K14" s="17">
+        <v>1</v>
+      </c>
+      <c r="L14" s="17">
+        <v>0</v>
+      </c>
+      <c r="M14" s="17">
+        <v>0</v>
+      </c>
+      <c r="N14" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4308,20 +4312,20 @@
       <c r="I15" s="5">
         <v>63438.61</v>
       </c>
-      <c r="J15" s="14">
-        <v>4.4776119402985003E-2</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0.10752777822423799</v>
-      </c>
-      <c r="L15" s="14">
-        <v>0.57407407407407396</v>
-      </c>
-      <c r="M15" s="14">
-        <v>0.32258064516128998</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0.18518518518518501</v>
+      <c r="J15" s="17">
+        <v>4</v>
+      </c>
+      <c r="K15" s="17">
+        <v>10</v>
+      </c>
+      <c r="L15" s="17">
+        <v>57</v>
+      </c>
+      <c r="M15" s="17">
+        <v>32</v>
+      </c>
+      <c r="N15" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4352,20 +4356,20 @@
       <c r="I16" s="5">
         <v>68476</v>
       </c>
-      <c r="J16" s="14">
-        <v>7.8772802653399601E-2</v>
-      </c>
-      <c r="K16" s="14">
-        <v>9.2486254899606393E-2</v>
-      </c>
-      <c r="L16" s="14">
-        <v>0.42105263157894701</v>
-      </c>
-      <c r="M16" s="14">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="N16" s="14">
-        <v>9.4736842105263105E-2</v>
+      <c r="J16" s="17">
+        <v>7</v>
+      </c>
+      <c r="K16" s="17">
+        <v>9</v>
+      </c>
+      <c r="L16" s="17">
+        <v>42</v>
+      </c>
+      <c r="M16" s="17">
+        <v>22</v>
+      </c>
+      <c r="N16" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4396,20 +4400,20 @@
       <c r="I17" s="5">
         <v>8166</v>
       </c>
-      <c r="J17" s="14">
-        <v>2.73631840796019E-2</v>
-      </c>
-      <c r="K17" s="14">
-        <v>1.1029305997870499E-2</v>
-      </c>
-      <c r="L17" s="14">
-        <v>0.54545454545454497</v>
-      </c>
-      <c r="M17" s="14">
-        <v>5.5555555555555497E-2</v>
-      </c>
-      <c r="N17" s="14">
-        <v>3.03030303030303E-2</v>
+      <c r="J17" s="17">
+        <v>2</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1</v>
+      </c>
+      <c r="L17" s="17">
+        <v>54</v>
+      </c>
+      <c r="M17" s="17">
+        <v>5</v>
+      </c>
+      <c r="N17" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4440,20 +4444,20 @@
       <c r="I18" s="5">
         <v>8641</v>
       </c>
-      <c r="J18" s="14">
-        <v>1.8242122719734601E-2</v>
-      </c>
-      <c r="K18" s="14">
-        <v>1.16708588204261E-2</v>
-      </c>
-      <c r="L18" s="14">
-        <v>0.45454545454545398</v>
-      </c>
-      <c r="M18" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="N18" s="14">
-        <v>4.54545454545454E-2</v>
+      <c r="J18" s="17">
+        <v>1</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" s="17">
+        <v>45</v>
+      </c>
+      <c r="M18" s="17">
+        <v>10</v>
+      </c>
+      <c r="N18" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4484,20 +4488,20 @@
       <c r="I19" s="5">
         <v>13015.8</v>
       </c>
-      <c r="J19" s="14">
-        <v>2.9850746268656699E-2</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1.7579627848038602E-2</v>
-      </c>
-      <c r="L19" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="14">
-        <v>0.11111111111111099</v>
-      </c>
-      <c r="N19" s="14">
-        <v>5.5555555555555497E-2</v>
+      <c r="J19" s="17">
+        <v>2</v>
+      </c>
+      <c r="K19" s="17">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17">
+        <v>50</v>
+      </c>
+      <c r="M19" s="17">
+        <v>11</v>
+      </c>
+      <c r="N19" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4528,20 +4532,20 @@
       <c r="I20" s="5">
         <v>16532</v>
       </c>
-      <c r="J20" s="14">
-        <v>1.99004975124378E-2</v>
-      </c>
-      <c r="K20" s="14">
-        <v>2.2328739499974999E-2</v>
-      </c>
-      <c r="L20" s="14">
-        <v>0.41666666666666602</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="N20" s="14">
-        <v>8.3333333333333301E-2</v>
+      <c r="J20" s="17">
+        <v>1</v>
+      </c>
+      <c r="K20" s="17">
+        <v>2</v>
+      </c>
+      <c r="L20" s="17">
+        <v>41</v>
+      </c>
+      <c r="M20" s="17">
+        <v>20</v>
+      </c>
+      <c r="N20" s="17">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,35 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FF8EEE-BFC2-451C-A7D4-C7F7F960515E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23270A9-7F85-4538-9FC2-C1A05407CCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
     <sheet name="Tab2_Regional" sheetId="2" r:id="rId2"/>
     <sheet name="Tab3_Campaign" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tab1_KPI!$A$5:$AE$44</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="181">
   <si>
     <t>Tab 1 — KPI Data</t>
   </si>
@@ -293,48 +279,201 @@
     <t>Arizona</t>
   </si>
   <si>
+    <t>17.89%</t>
+  </si>
+  <si>
+    <t>40.00%</t>
+  </si>
+  <si>
+    <t>25.00%</t>
+  </si>
+  <si>
+    <t>10.00%</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
+    <t>0.19%</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
     <t>Bay Area</t>
   </si>
   <si>
+    <t>14.31%</t>
+  </si>
+  <si>
+    <t>10.70%</t>
+  </si>
+  <si>
+    <t>39.13%</t>
+  </si>
+  <si>
+    <t>16.67%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
     <t>CDR</t>
   </si>
   <si>
+    <t>0.39%</t>
+  </si>
+  <si>
     <t>Central Coast</t>
   </si>
   <si>
+    <t>1.16%</t>
+  </si>
+  <si>
+    <t>60.00%</t>
+  </si>
+  <si>
     <t>Corporate</t>
   </si>
   <si>
     <t>Fresno</t>
   </si>
   <si>
+    <t>2.32%</t>
+  </si>
+  <si>
     <t>Inland Empire</t>
   </si>
   <si>
+    <t>10.06%</t>
+  </si>
+  <si>
+    <t>10.49%</t>
+  </si>
+  <si>
+    <t>46.88%</t>
+  </si>
+  <si>
+    <t>13.33%</t>
+  </si>
+  <si>
+    <t>6.25%</t>
+  </si>
+  <si>
     <t>Las Vegas</t>
   </si>
   <si>
+    <t>4.45%</t>
+  </si>
+  <si>
+    <t>4.76%</t>
+  </si>
+  <si>
+    <t>20.00%</t>
+  </si>
+  <si>
+    <t>33.33%</t>
+  </si>
+  <si>
+    <t>6.67%</t>
+  </si>
+  <si>
+    <t>12.96%</t>
+  </si>
+  <si>
+    <t>1.96%</t>
+  </si>
+  <si>
+    <t>5.56%</t>
+  </si>
+  <si>
     <t>Orange County</t>
   </si>
   <si>
+    <t>9.09%</t>
+  </si>
+  <si>
+    <t>20.83%</t>
+  </si>
+  <si>
+    <t>80.95%</t>
+  </si>
+  <si>
+    <t>11.76%</t>
+  </si>
+  <si>
+    <t>9.52%</t>
+  </si>
+  <si>
     <t>Pasadena</t>
   </si>
   <si>
+    <t>14.70%</t>
+  </si>
+  <si>
+    <t>17.91%</t>
+  </si>
+  <si>
+    <t>38.89%</t>
+  </si>
+  <si>
+    <t>21.43%</t>
+  </si>
+  <si>
+    <t>8.33%</t>
+  </si>
+  <si>
     <t>Sacramento</t>
   </si>
   <si>
+    <t>5.80%</t>
+  </si>
+  <si>
+    <t>2.14%</t>
+  </si>
+  <si>
+    <t>44.44%</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
+    <t>4.26%</t>
+  </si>
+  <si>
+    <t>2.26%</t>
+  </si>
+  <si>
+    <t>58.33%</t>
+  </si>
+  <si>
+    <t>14.29%</t>
+  </si>
+  <si>
     <t>San Diego</t>
   </si>
   <si>
+    <t>6.58%</t>
+  </si>
+  <si>
+    <t>6.55%</t>
+  </si>
+  <si>
+    <t>28.57%</t>
+  </si>
+  <si>
     <t>Ventura/SB County</t>
   </si>
   <si>
+    <t>3.48%</t>
+  </si>
+  <si>
+    <t>4.33%</t>
+  </si>
+  <si>
+    <t>62.50%</t>
+  </si>
+  <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
   <si>
@@ -398,6 +537,9 @@
     <t>Feb</t>
   </si>
   <si>
+    <t>May</t>
+  </si>
+  <si>
     <t>Jun</t>
   </si>
   <si>
@@ -417,9 +559,6 @@
   </si>
   <si>
     <t>Dec</t>
-  </si>
-  <si>
-    <t>May</t>
   </si>
   <si>
     <t>PMAX 3 - Emerging Markets</t>
@@ -432,10 +571,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,41 +584,24 @@
       <sz val="13"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -538,11 +657,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -567,30 +685,18 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -893,34 +999,8 @@
   <dimension ref="A1:AE44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="14" style="12" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="31" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
@@ -1029,7 +1109,7 @@
       <c r="AD5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AE5" s="13" t="s">
+      <c r="AE5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1122,7 +1202,7 @@
       <c r="AD6" s="9">
         <v>364</v>
       </c>
-      <c r="AE6" s="14">
+      <c r="AE6" s="10">
         <v>46135</v>
       </c>
     </row>
@@ -1215,7 +1295,7 @@
       <c r="AD7" s="9">
         <v>5</v>
       </c>
-      <c r="AE7" s="14">
+      <c r="AE7" s="10">
         <v>46135</v>
       </c>
     </row>
@@ -1310,7 +1390,7 @@
       <c r="AD8" s="9">
         <v>30</v>
       </c>
-      <c r="AE8" s="14">
+      <c r="AE8" s="10">
         <v>46135</v>
       </c>
     </row>
@@ -1357,7 +1437,7 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="9"/>
       <c r="AD9" s="9"/>
-      <c r="AE9" s="14">
+      <c r="AE9" s="10">
         <v>46135</v>
       </c>
     </row>
@@ -1420,7 +1500,7 @@
       <c r="AB10" s="8"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
-      <c r="AE10" s="14">
+      <c r="AE10" s="10">
         <v>46135</v>
       </c>
     </row>
@@ -1483,7 +1563,7 @@
       <c r="AB11" s="8"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="9"/>
-      <c r="AE11" s="14">
+      <c r="AE11">
         <v>46135</v>
       </c>
     </row>
@@ -1528,7 +1608,7 @@
       <c r="AB12" s="8"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
-      <c r="AE12" s="14">
+      <c r="AE12">
         <v>46135</v>
       </c>
     </row>
@@ -1573,7 +1653,7 @@
       <c r="AB13" s="8"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="9"/>
-      <c r="AE13" s="14">
+      <c r="AE13">
         <v>46135</v>
       </c>
     </row>
@@ -1646,7 +1726,7 @@
       </c>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
-      <c r="AE14" s="14">
+      <c r="AE14">
         <v>46135</v>
       </c>
     </row>
@@ -1741,7 +1821,7 @@
       <c r="AD15" s="9">
         <v>20</v>
       </c>
-      <c r="AE15" s="14">
+      <c r="AE15">
         <v>46135</v>
       </c>
     </row>
@@ -1806,7 +1886,7 @@
       <c r="AB16" s="8"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
-      <c r="AE16" s="14">
+      <c r="AE16">
         <v>46135</v>
       </c>
     </row>
@@ -1875,7 +1955,7 @@
       <c r="AD17" s="9">
         <v>3</v>
       </c>
-      <c r="AE17" s="14">
+      <c r="AE17">
         <v>46135</v>
       </c>
     </row>
@@ -1922,7 +2002,7 @@
       <c r="AB18" s="8"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
-      <c r="AE18" s="14">
+      <c r="AE18">
         <v>46135</v>
       </c>
     </row>
@@ -1973,7 +2053,7 @@
       <c r="AD19" s="9">
         <v>3</v>
       </c>
-      <c r="AE19" s="14">
+      <c r="AE19">
         <v>46135</v>
       </c>
     </row>
@@ -2036,7 +2116,7 @@
       </c>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
-      <c r="AE20" s="14">
+      <c r="AE20">
         <v>46135</v>
       </c>
     </row>
@@ -2083,7 +2163,7 @@
       </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
-      <c r="AE21" s="14">
+      <c r="AE21">
         <v>46135</v>
       </c>
     </row>
@@ -2146,7 +2226,7 @@
       </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
-      <c r="AE22" s="14">
+      <c r="AE22">
         <v>46135</v>
       </c>
     </row>
@@ -2221,7 +2301,7 @@
       <c r="AD23" s="9">
         <v>2</v>
       </c>
-      <c r="AE23" s="14">
+      <c r="AE23">
         <v>46135</v>
       </c>
     </row>
@@ -2310,7 +2390,7 @@
       </c>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
-      <c r="AE24" s="14">
+      <c r="AE24">
         <v>46135</v>
       </c>
     </row>
@@ -2405,7 +2485,7 @@
       <c r="AD25" s="9">
         <v>11</v>
       </c>
-      <c r="AE25" s="14">
+      <c r="AE25">
         <v>46135</v>
       </c>
     </row>
@@ -2470,7 +2550,7 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
-      <c r="AE26" s="14">
+      <c r="AE26">
         <v>46135</v>
       </c>
     </row>
@@ -2563,7 +2643,7 @@
       <c r="AD27" s="9">
         <v>12</v>
       </c>
-      <c r="AE27" s="14">
+      <c r="AE27">
         <v>46135</v>
       </c>
     </row>
@@ -2610,7 +2690,7 @@
       <c r="AB28" s="8"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9"/>
-      <c r="AE28" s="14">
+      <c r="AE28">
         <v>46135</v>
       </c>
     </row>
@@ -2673,13 +2753,13 @@
       <c r="AB29" s="8"/>
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
-      <c r="AE29" s="14">
+      <c r="AE29">
         <v>46135</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2736,7 +2816,7 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="9"/>
-      <c r="AE30" s="14">
+      <c r="AE30">
         <v>46135</v>
       </c>
     </row>
@@ -2829,7 +2909,7 @@
       <c r="AD31" s="9">
         <v>19</v>
       </c>
-      <c r="AE31" s="14">
+      <c r="AE31">
         <v>46135</v>
       </c>
     </row>
@@ -2898,7 +2978,7 @@
       <c r="AD32" s="9">
         <v>41</v>
       </c>
-      <c r="AE32" s="14">
+      <c r="AE32">
         <v>46135</v>
       </c>
     </row>
@@ -2965,7 +3045,7 @@
       <c r="AD33" s="9">
         <v>23</v>
       </c>
-      <c r="AE33" s="14">
+      <c r="AE33">
         <v>46135</v>
       </c>
     </row>
@@ -3058,13 +3138,13 @@
       <c r="AD34" s="9">
         <v>14</v>
       </c>
-      <c r="AE34" s="14">
+      <c r="AE34">
         <v>46135</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -3123,7 +3203,7 @@
       <c r="AB35" s="8"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
-      <c r="AE35" s="14">
+      <c r="AE35">
         <v>46135</v>
       </c>
     </row>
@@ -3190,7 +3270,7 @@
       <c r="AD36" s="9">
         <v>15</v>
       </c>
-      <c r="AE36" s="14">
+      <c r="AE36">
         <v>46135</v>
       </c>
     </row>
@@ -3283,13 +3363,13 @@
       <c r="AD37" s="9">
         <v>14</v>
       </c>
-      <c r="AE37" s="14">
+      <c r="AE37">
         <v>46135</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3348,7 +3428,7 @@
       <c r="AB38" s="8"/>
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
-      <c r="AE38" s="14">
+      <c r="AE38">
         <v>46135</v>
       </c>
     </row>
@@ -3429,7 +3509,7 @@
       </c>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
-      <c r="AE39" s="14">
+      <c r="AE39">
         <v>46135</v>
       </c>
     </row>
@@ -3524,13 +3604,13 @@
       <c r="AD40" s="9">
         <v>14</v>
       </c>
-      <c r="AE40" s="14">
+      <c r="AE40">
         <v>46135</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="N41">
         <v>19.059999999999999</v>
@@ -3574,13 +3654,13 @@
       <c r="AA41">
         <v>24000</v>
       </c>
-      <c r="AE41" s="14">
+      <c r="AE41">
         <v>46135</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="N42">
         <v>19.059999999999999</v>
@@ -3621,7 +3701,7 @@
       <c r="Z42">
         <v>0</v>
       </c>
-      <c r="AE42" s="14">
+      <c r="AE42">
         <v>46135</v>
       </c>
     </row>
@@ -3716,13 +3796,13 @@
       <c r="AD43">
         <v>5</v>
       </c>
-      <c r="AE43" s="14">
+      <c r="AE43">
         <v>46135</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -3760,12 +3840,11 @@
       <c r="Z44">
         <v>0</v>
       </c>
-      <c r="AE44" s="14">
+      <c r="AE44">
         <v>46135</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3783,11 +3862,11 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="13" style="15" customWidth="1"/>
-    <col min="11" max="11" width="16" style="15" customWidth="1"/>
-    <col min="12" max="12" width="11" style="15" customWidth="1"/>
-    <col min="13" max="13" width="12" style="15" customWidth="1"/>
-    <col min="14" max="14" width="13" style="15" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -3828,24 +3907,24 @@
       <c r="I4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="L4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>84</v>
       </c>
       <c r="B5" s="5">
@@ -3872,25 +3951,25 @@
       <c r="I5" s="5">
         <v>68362.8</v>
       </c>
-      <c r="J5" s="17">
-        <v>4</v>
-      </c>
-      <c r="K5" s="17">
-        <v>9</v>
-      </c>
-      <c r="L5" s="17">
-        <v>37</v>
-      </c>
-      <c r="M5" s="17">
-        <v>40</v>
-      </c>
-      <c r="N5" s="17">
-        <v>15</v>
+      <c r="J5" s="12">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>85</v>
+      <c r="A6" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -3916,25 +3995,25 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="17">
-        <v>0</v>
-      </c>
-      <c r="K6" s="17">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17">
-        <v>100</v>
-      </c>
-      <c r="M6" s="17">
-        <v>0</v>
-      </c>
-      <c r="N6" s="17">
-        <v>0</v>
+      <c r="J6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="5" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>86</v>
+      <c r="A7" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="B7" s="5">
         <v>81</v>
@@ -3960,25 +4039,25 @@
       <c r="I7" s="5">
         <v>40755.56</v>
       </c>
-      <c r="J7" s="17">
-        <v>6</v>
-      </c>
-      <c r="K7" s="17">
-        <v>5</v>
-      </c>
-      <c r="L7" s="17">
-        <v>40</v>
-      </c>
-      <c r="M7" s="17">
-        <v>21</v>
-      </c>
-      <c r="N7" s="17">
-        <v>8</v>
+      <c r="J7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>87</v>
+      <c r="A8" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="B8" s="5">
         <v>12</v>
@@ -4004,25 +4083,25 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="17">
-        <v>0</v>
-      </c>
-      <c r="K8" s="17">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17">
-        <v>16</v>
-      </c>
-      <c r="M8" s="17">
-        <v>50</v>
-      </c>
-      <c r="N8" s="17">
-        <v>8</v>
+      <c r="J8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="5" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>88</v>
+      <c r="A9" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="B9" s="5">
         <v>7</v>
@@ -4048,25 +4127,25 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="17">
-        <v>0</v>
-      </c>
-      <c r="K9" s="17">
-        <v>0</v>
-      </c>
-      <c r="L9" s="17">
-        <v>57</v>
-      </c>
-      <c r="M9" s="17">
-        <v>0</v>
-      </c>
-      <c r="N9" s="17">
-        <v>0</v>
+      <c r="J9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>89</v>
+      <c r="A10" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="B10" s="5">
         <v>2</v>
@@ -4092,25 +4171,25 @@
       <c r="I10" s="5">
         <v>0</v>
       </c>
-      <c r="J10" s="17">
-        <v>0</v>
-      </c>
-      <c r="K10" s="17">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17">
-        <v>0</v>
-      </c>
-      <c r="M10" s="17">
-        <v>0</v>
-      </c>
-      <c r="N10" s="17">
-        <v>0</v>
+      <c r="J10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="M10" s="5" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>90</v>
+      <c r="A11" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="B11" s="5">
         <v>13</v>
@@ -4136,25 +4215,25 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="17">
-        <v>1</v>
-      </c>
-      <c r="K11" s="17">
-        <v>0</v>
-      </c>
-      <c r="L11" s="17">
-        <v>23</v>
-      </c>
-      <c r="M11" s="17">
-        <v>0</v>
-      </c>
-      <c r="N11" s="17">
-        <v>0</v>
+      <c r="J11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>91</v>
+      <c r="A12" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="B12" s="5">
         <v>60</v>
@@ -4180,25 +4259,25 @@
       <c r="I12" s="5">
         <v>32156.9399999999</v>
       </c>
-      <c r="J12" s="17">
-        <v>4</v>
-      </c>
-      <c r="K12" s="17">
-        <v>5</v>
-      </c>
-      <c r="L12" s="17">
-        <v>43</v>
-      </c>
-      <c r="M12" s="17">
-        <v>23</v>
-      </c>
-      <c r="N12" s="17">
-        <v>10</v>
+      <c r="J12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>92</v>
+      <c r="A13" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="B13" s="5">
         <v>31</v>
@@ -4224,25 +4303,25 @@
       <c r="I13" s="5">
         <v>12943.84</v>
       </c>
-      <c r="J13" s="17">
-        <v>2</v>
-      </c>
-      <c r="K13" s="17">
-        <v>2</v>
-      </c>
-      <c r="L13" s="17">
-        <v>38</v>
-      </c>
-      <c r="M13" s="17">
-        <v>25</v>
-      </c>
-      <c r="N13" s="17">
-        <v>9</v>
+      <c r="J13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>117</v>
+      <c r="A14" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="B14" s="5">
         <v>74</v>
@@ -4268,25 +4347,25 @@
       <c r="I14" s="5">
         <v>7499</v>
       </c>
-      <c r="J14" s="17">
-        <v>6</v>
-      </c>
-      <c r="K14" s="17">
-        <v>1</v>
-      </c>
-      <c r="L14" s="17">
-        <v>0</v>
-      </c>
-      <c r="M14" s="17">
-        <v>0</v>
-      </c>
-      <c r="N14" s="17">
-        <v>1</v>
+      <c r="J14" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="5" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>93</v>
+      <c r="A15" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="B15" s="5">
         <v>54</v>
@@ -4312,25 +4391,25 @@
       <c r="I15" s="5">
         <v>63438.61</v>
       </c>
-      <c r="J15" s="17">
-        <v>4</v>
-      </c>
-      <c r="K15" s="17">
-        <v>10</v>
-      </c>
-      <c r="L15" s="17">
-        <v>57</v>
-      </c>
-      <c r="M15" s="17">
-        <v>32</v>
-      </c>
-      <c r="N15" s="17">
-        <v>18</v>
+      <c r="J15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>94</v>
+      <c r="A16" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="B16" s="5">
         <v>95</v>
@@ -4356,25 +4435,25 @@
       <c r="I16" s="5">
         <v>68476</v>
       </c>
-      <c r="J16" s="17">
-        <v>7</v>
-      </c>
-      <c r="K16" s="17">
-        <v>9</v>
-      </c>
-      <c r="L16" s="17">
-        <v>42</v>
-      </c>
-      <c r="M16" s="17">
-        <v>22</v>
-      </c>
-      <c r="N16" s="17">
-        <v>9</v>
+      <c r="J16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>95</v>
+      <c r="A17" s="11" t="s">
+        <v>133</v>
       </c>
       <c r="B17" s="5">
         <v>33</v>
@@ -4400,25 +4479,25 @@
       <c r="I17" s="5">
         <v>8166</v>
       </c>
-      <c r="J17" s="17">
-        <v>2</v>
-      </c>
-      <c r="K17" s="17">
-        <v>1</v>
-      </c>
-      <c r="L17" s="17">
-        <v>54</v>
-      </c>
-      <c r="M17" s="17">
-        <v>5</v>
-      </c>
-      <c r="N17" s="17">
-        <v>3</v>
+      <c r="J17" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>96</v>
+      <c r="A18" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="B18" s="5">
         <v>22</v>
@@ -4444,25 +4523,25 @@
       <c r="I18" s="5">
         <v>8641</v>
       </c>
-      <c r="J18" s="17">
-        <v>1</v>
-      </c>
-      <c r="K18" s="17">
-        <v>1</v>
-      </c>
-      <c r="L18" s="17">
-        <v>45</v>
-      </c>
-      <c r="M18" s="17">
-        <v>10</v>
-      </c>
-      <c r="N18" s="17">
-        <v>4</v>
+      <c r="J18" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>97</v>
+      <c r="A19" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="B19" s="5">
         <v>36</v>
@@ -4488,25 +4567,25 @@
       <c r="I19" s="5">
         <v>13015.8</v>
       </c>
-      <c r="J19" s="17">
-        <v>2</v>
-      </c>
-      <c r="K19" s="17">
-        <v>1</v>
-      </c>
-      <c r="L19" s="17">
-        <v>50</v>
-      </c>
-      <c r="M19" s="17">
-        <v>11</v>
-      </c>
-      <c r="N19" s="17">
-        <v>5</v>
+      <c r="J19" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>98</v>
+      <c r="A20" s="11" t="s">
+        <v>146</v>
       </c>
       <c r="B20" s="5">
         <v>24</v>
@@ -4532,20 +4611,20 @@
       <c r="I20" s="5">
         <v>16532</v>
       </c>
-      <c r="J20" s="17">
-        <v>1</v>
-      </c>
-      <c r="K20" s="17">
-        <v>2</v>
-      </c>
-      <c r="L20" s="17">
-        <v>41</v>
-      </c>
-      <c r="M20" s="17">
-        <v>20</v>
-      </c>
-      <c r="N20" s="17">
-        <v>8</v>
+      <c r="J20" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4555,7 +4634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O320"/>
+  <dimension ref="A1:K320"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4564,12 +4643,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4577,45 +4656,45 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5">
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D5" s="5">
         <v>4599</v>
@@ -4643,14 +4722,14 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="5">
         <v>2025</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D6" s="5">
         <v>4898</v>
@@ -4678,14 +4757,14 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="5">
         <v>2025</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D7" s="5">
         <v>5001</v>
@@ -4713,14 +4792,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="5">
         <v>2025</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D8" s="5">
         <v>5381</v>
@@ -4748,14 +4827,14 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5">
         <v>2025</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D9" s="5">
         <v>4516</v>
@@ -4783,14 +4862,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="5">
         <v>2025</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D10" s="5">
         <v>4270</v>
@@ -4818,14 +4897,14 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="5">
         <v>2025</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D11" s="5">
         <v>4709</v>
@@ -4853,14 +4932,14 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="5">
         <v>2025</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D12" s="5">
         <v>4436</v>
@@ -4888,14 +4967,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="5">
         <v>2025</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D13" s="5">
         <v>4357</v>
@@ -4923,14 +5002,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="5">
         <v>2025</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D14" s="5">
         <v>4550</v>
@@ -4958,14 +5037,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5">
         <v>2025</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D15" s="5">
         <v>4554</v>
@@ -4993,14 +5072,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="5">
         <v>2025</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D16" s="5">
         <v>5380</v>
@@ -5028,14 +5107,14 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="5">
         <v>2026</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D17" s="5">
         <v>4567</v>
@@ -5063,14 +5142,14 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="5">
         <v>2026</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D18" s="5">
         <v>4420</v>
@@ -5098,14 +5177,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="5">
         <v>2026</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D19" s="5">
         <v>4524</v>
@@ -5140,7 +5219,7 @@
         <v>2026</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D20">
         <v>2260</v>
@@ -5175,7 +5254,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D21">
         <v>298</v>
@@ -5210,7 +5289,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D22">
         <v>461</v>
@@ -5245,7 +5324,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D23">
         <v>300</v>
@@ -5280,7 +5359,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D24">
         <v>339</v>
@@ -5315,7 +5394,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D25">
         <v>405</v>
@@ -5350,7 +5429,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D26">
         <v>432</v>
@@ -5385,7 +5464,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D27">
         <v>446</v>
@@ -5420,7 +5499,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D28">
         <v>449</v>
@@ -5455,7 +5534,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D29">
         <v>501</v>
@@ -5490,7 +5569,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D30">
         <v>532</v>
@@ -5525,7 +5604,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D31">
         <v>473</v>
@@ -5560,7 +5639,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D32">
         <v>595</v>
@@ -5595,7 +5674,7 @@
         <v>2026</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D33">
         <v>573</v>
@@ -5630,7 +5709,7 @@
         <v>2026</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D34">
         <v>574</v>
@@ -5665,7 +5744,7 @@
         <v>2026</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D35">
         <v>617</v>
@@ -5700,7 +5779,7 @@
         <v>2026</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D36">
         <v>393</v>
@@ -5735,7 +5814,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D37">
         <v>2098</v>
@@ -5770,7 +5849,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D38">
         <v>2428</v>
@@ -5805,7 +5884,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D39">
         <v>1807</v>
@@ -5840,7 +5919,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D40">
         <v>2202</v>
@@ -5875,7 +5954,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D41">
         <v>1377</v>
@@ -5910,7 +5989,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D42">
         <v>2116</v>
@@ -5945,7 +6024,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D43">
         <v>730</v>
@@ -5980,7 +6059,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D44">
         <v>1854</v>
@@ -6015,7 +6094,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D45">
         <v>1627</v>
@@ -6050,7 +6129,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D46">
         <v>1675</v>
@@ -6085,7 +6164,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D47">
         <v>1383</v>
@@ -6120,7 +6199,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D48">
         <v>1061</v>
@@ -6155,7 +6234,7 @@
         <v>2026</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D49">
         <v>2996</v>
@@ -6190,7 +6269,7 @@
         <v>2026</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D50">
         <v>2864</v>
@@ -6225,7 +6304,7 @@
         <v>2026</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D51">
         <v>3423</v>
@@ -6260,7 +6339,7 @@
         <v>2026</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D52">
         <v>2378</v>
@@ -6295,7 +6374,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D53">
         <v>510</v>
@@ -6330,7 +6409,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D54">
         <v>750</v>
@@ -6365,7 +6444,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D55">
         <v>378</v>
@@ -6400,7 +6479,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D56">
         <v>518</v>
@@ -6435,7 +6514,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D57">
         <v>518</v>
@@ -6470,7 +6549,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D58">
         <v>676</v>
@@ -6505,7 +6584,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D59">
         <v>695</v>
@@ -6540,7 +6619,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D60">
         <v>653</v>
@@ -6575,7 +6654,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D61">
         <v>476</v>
@@ -6610,7 +6689,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D62">
         <v>454</v>
@@ -6645,7 +6724,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D63">
         <v>595</v>
@@ -6680,7 +6759,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D64">
         <v>26</v>
@@ -6715,7 +6794,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D65">
         <v>202</v>
@@ -6750,7 +6829,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D66">
         <v>87</v>
@@ -6770,7 +6849,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D67">
         <v>22</v>
@@ -6790,7 +6869,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D68">
         <v>98</v>
@@ -6825,7 +6904,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D69">
         <v>239</v>
@@ -6845,7 +6924,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D70">
         <v>421</v>
@@ -6865,7 +6944,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D71">
         <v>524</v>
@@ -6900,7 +6979,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D72">
         <v>509</v>
@@ -6935,7 +7014,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D73">
         <v>447</v>
@@ -6970,7 +7049,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D74">
         <v>181</v>
@@ -6990,7 +7069,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D75">
         <v>69</v>
@@ -7025,7 +7104,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D76">
         <v>54</v>
@@ -7045,7 +7124,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D77">
         <v>56</v>
@@ -7080,7 +7159,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D78">
         <v>112</v>
@@ -7115,7 +7194,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D79">
         <v>114</v>
@@ -7150,7 +7229,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D80">
         <v>141</v>
@@ -7185,7 +7264,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D81">
         <v>231</v>
@@ -7220,7 +7299,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D82">
         <v>113</v>
@@ -7255,7 +7334,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D83">
         <v>175</v>
@@ -7290,7 +7369,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D84">
         <v>234</v>
@@ -7325,7 +7404,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D85">
         <v>145</v>
@@ -7360,7 +7439,7 @@
         <v>2026</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D86">
         <v>172</v>
@@ -7395,7 +7474,7 @@
         <v>2026</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D87">
         <v>175</v>
@@ -7430,7 +7509,7 @@
         <v>2026</v>
       </c>
       <c r="C88" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D88">
         <v>20</v>
@@ -7450,7 +7529,7 @@
         <v>2026</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D89">
         <v>87</v>
@@ -7470,7 +7549,7 @@
         <v>2025</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D90">
         <v>2449</v>
@@ -7505,7 +7584,7 @@
         <v>2025</v>
       </c>
       <c r="C91" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D91">
         <v>2981</v>
@@ -7540,7 +7619,7 @@
         <v>2025</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D92">
         <v>2292</v>
@@ -7575,7 +7654,7 @@
         <v>2025</v>
       </c>
       <c r="C93" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D93">
         <v>1930</v>
@@ -7610,7 +7689,7 @@
         <v>2025</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D94">
         <v>2334</v>
@@ -7645,7 +7724,7 @@
         <v>2025</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D95">
         <v>2616</v>
@@ -7680,7 +7759,7 @@
         <v>2025</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D96">
         <v>1012</v>
@@ -7715,7 +7794,7 @@
         <v>2025</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D97">
         <v>737</v>
@@ -7750,7 +7829,7 @@
         <v>2025</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D98">
         <v>1336</v>
@@ -7785,7 +7864,7 @@
         <v>2025</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D99">
         <v>1621</v>
@@ -7820,7 +7899,7 @@
         <v>2025</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D100">
         <v>1725</v>
@@ -7855,7 +7934,7 @@
         <v>2025</v>
       </c>
       <c r="C101" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D101">
         <v>1973</v>
@@ -7890,7 +7969,7 @@
         <v>2026</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D102">
         <v>2119</v>
@@ -7925,7 +8004,7 @@
         <v>2026</v>
       </c>
       <c r="C103" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D103">
         <v>1914</v>
@@ -7960,7 +8039,7 @@
         <v>2026</v>
       </c>
       <c r="C104" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D104">
         <v>1958</v>
@@ -7995,7 +8074,7 @@
         <v>2026</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D105">
         <v>1071</v>
@@ -8030,7 +8109,7 @@
         <v>2025</v>
       </c>
       <c r="C106" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D106">
         <v>262</v>
@@ -8065,7 +8144,7 @@
         <v>2025</v>
       </c>
       <c r="C107" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D107">
         <v>340</v>
@@ -8100,7 +8179,7 @@
         <v>2025</v>
       </c>
       <c r="C108" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D108">
         <v>214</v>
@@ -8135,7 +8214,7 @@
         <v>2025</v>
       </c>
       <c r="C109" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D109">
         <v>178</v>
@@ -8170,7 +8249,7 @@
         <v>2025</v>
       </c>
       <c r="C110" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D110">
         <v>226</v>
@@ -8205,7 +8284,7 @@
         <v>2025</v>
       </c>
       <c r="C111" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D111">
         <v>215</v>
@@ -8240,7 +8319,7 @@
         <v>2025</v>
       </c>
       <c r="C112" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D112">
         <v>212</v>
@@ -8275,7 +8354,7 @@
         <v>2025</v>
       </c>
       <c r="C113" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D113">
         <v>211</v>
@@ -8310,7 +8389,7 @@
         <v>2025</v>
       </c>
       <c r="C114" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D114">
         <v>237</v>
@@ -8345,7 +8424,7 @@
         <v>2025</v>
       </c>
       <c r="C115" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D115">
         <v>443</v>
@@ -8380,7 +8459,7 @@
         <v>2025</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D116">
         <v>486</v>
@@ -8415,7 +8494,7 @@
         <v>2025</v>
       </c>
       <c r="C117" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D117">
         <v>453</v>
@@ -8450,7 +8529,7 @@
         <v>2026</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D118">
         <v>489</v>
@@ -8485,7 +8564,7 @@
         <v>2026</v>
       </c>
       <c r="C119" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D119">
         <v>371</v>
@@ -8520,7 +8599,7 @@
         <v>2026</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D120">
         <v>477</v>
@@ -8555,7 +8634,7 @@
         <v>2026</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G121">
         <v>2</v>
@@ -8578,7 +8657,7 @@
         <v>2025</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D122">
         <v>601</v>
@@ -8598,7 +8677,7 @@
         <v>2025</v>
       </c>
       <c r="C123" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D123">
         <v>678</v>
@@ -8633,7 +8712,7 @@
         <v>2025</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D124">
         <v>894</v>
@@ -8668,7 +8747,7 @@
         <v>2025</v>
       </c>
       <c r="C125" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D125">
         <v>637</v>
@@ -8703,7 +8782,7 @@
         <v>2025</v>
       </c>
       <c r="C126" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D126">
         <v>219</v>
@@ -8738,7 +8817,7 @@
         <v>2025</v>
       </c>
       <c r="C127" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D127">
         <v>225</v>
@@ -8773,7 +8852,7 @@
         <v>2025</v>
       </c>
       <c r="C128" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D128">
         <v>479</v>
@@ -8808,7 +8887,7 @@
         <v>2025</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D129">
         <v>674</v>
@@ -8843,7 +8922,7 @@
         <v>2025</v>
       </c>
       <c r="C130" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D130">
         <v>473</v>
@@ -8878,7 +8957,7 @@
         <v>2026</v>
       </c>
       <c r="C131" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D131">
         <v>172</v>
@@ -8913,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="C132" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D132">
         <v>134</v>
@@ -8948,7 +9027,7 @@
         <v>2026</v>
       </c>
       <c r="C133" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="G133">
         <v>2</v>
@@ -8971,7 +9050,7 @@
         <v>2025</v>
       </c>
       <c r="C134" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D134">
         <v>1022</v>
@@ -9003,7 +9082,7 @@
         <v>2025</v>
       </c>
       <c r="C135" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D135">
         <v>1633</v>
@@ -9035,7 +9114,7 @@
         <v>2025</v>
       </c>
       <c r="C136" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D136">
         <v>2023</v>
@@ -9067,7 +9146,7 @@
         <v>2025</v>
       </c>
       <c r="C137" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D137">
         <v>2136</v>
@@ -9099,7 +9178,7 @@
         <v>2025</v>
       </c>
       <c r="C138" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D138">
         <v>1956</v>
@@ -9131,7 +9210,7 @@
         <v>2025</v>
       </c>
       <c r="C139" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D139">
         <v>2154</v>
@@ -9163,7 +9242,7 @@
         <v>2026</v>
       </c>
       <c r="C140" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D140">
         <v>2248</v>
@@ -9195,7 +9274,7 @@
         <v>2026</v>
       </c>
       <c r="C141" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D141">
         <v>1955</v>
@@ -9227,7 +9306,7 @@
         <v>2026</v>
       </c>
       <c r="C142" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D142">
         <v>2188</v>
@@ -9259,7 +9338,7 @@
         <v>2026</v>
       </c>
       <c r="C143" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D143">
         <v>1653</v>
@@ -9291,7 +9370,7 @@
         <v>2026</v>
       </c>
       <c r="C144" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D144">
         <v>70</v>
@@ -9311,7 +9390,7 @@
         <v>2026</v>
       </c>
       <c r="C145" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D145">
         <v>142</v>
@@ -9331,7 +9410,7 @@
         <v>2026</v>
       </c>
       <c r="C146" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D146">
         <v>37441</v>
@@ -9366,7 +9445,7 @@
         <v>2025</v>
       </c>
       <c r="C147" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D147">
         <v>347</v>
@@ -9401,7 +9480,7 @@
         <v>2025</v>
       </c>
       <c r="C148" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D148">
         <v>504</v>
@@ -9436,7 +9515,7 @@
         <v>2025</v>
       </c>
       <c r="C149" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D149">
         <v>521</v>
@@ -9471,7 +9550,7 @@
         <v>2025</v>
       </c>
       <c r="C150" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D150">
         <v>330</v>
@@ -9491,7 +9570,7 @@
         <v>2025</v>
       </c>
       <c r="C151" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D151">
         <v>517</v>
@@ -9526,7 +9605,7 @@
         <v>2025</v>
       </c>
       <c r="C152" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D152">
         <v>464</v>
@@ -9561,7 +9640,7 @@
         <v>2025</v>
       </c>
       <c r="C153" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D153">
         <v>467</v>
@@ -9596,7 +9675,7 @@
         <v>2025</v>
       </c>
       <c r="C154" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D154">
         <v>446</v>
@@ -9631,7 +9710,7 @@
         <v>2025</v>
       </c>
       <c r="C155" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D155">
         <v>429</v>
@@ -9666,7 +9745,7 @@
         <v>2025</v>
       </c>
       <c r="C156" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D156">
         <v>437</v>
@@ -9701,7 +9780,7 @@
         <v>2025</v>
       </c>
       <c r="C157" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D157">
         <v>452</v>
@@ -9736,7 +9815,7 @@
         <v>2025</v>
       </c>
       <c r="C158" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D158">
         <v>492</v>
@@ -9771,7 +9850,7 @@
         <v>2026</v>
       </c>
       <c r="C159" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D159">
         <v>428</v>
@@ -9806,7 +9885,7 @@
         <v>2026</v>
       </c>
       <c r="C160" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D160">
         <v>358</v>
@@ -9841,7 +9920,7 @@
         <v>2026</v>
       </c>
       <c r="C161" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D161">
         <v>437</v>
@@ -9876,7 +9955,7 @@
         <v>2026</v>
       </c>
       <c r="C162" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D162">
         <v>336</v>
@@ -9911,7 +9990,7 @@
         <v>2025</v>
       </c>
       <c r="C163" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D163">
         <v>168</v>
@@ -9946,7 +10025,7 @@
         <v>2025</v>
       </c>
       <c r="C164" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D164">
         <v>192</v>
@@ -9981,7 +10060,7 @@
         <v>2025</v>
       </c>
       <c r="C165" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D165">
         <v>152</v>
@@ -10016,7 +10095,7 @@
         <v>2025</v>
       </c>
       <c r="C166" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D166">
         <v>82</v>
@@ -10051,7 +10130,7 @@
         <v>2025</v>
       </c>
       <c r="C167" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D167">
         <v>106</v>
@@ -10086,7 +10165,7 @@
         <v>2025</v>
       </c>
       <c r="C168" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D168">
         <v>98</v>
@@ -10121,7 +10200,7 @@
         <v>2025</v>
       </c>
       <c r="C169" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -10156,7 +10235,7 @@
         <v>2025</v>
       </c>
       <c r="C170" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D170">
         <v>47</v>
@@ -10191,7 +10270,7 @@
         <v>2025</v>
       </c>
       <c r="C171" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D171">
         <v>88</v>
@@ -10226,7 +10305,7 @@
         <v>2025</v>
       </c>
       <c r="C172" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D172">
         <v>117</v>
@@ -10261,7 +10340,7 @@
         <v>2025</v>
       </c>
       <c r="C173" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D173">
         <v>81</v>
@@ -10296,7 +10375,7 @@
         <v>2025</v>
       </c>
       <c r="C174" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D174">
         <v>161</v>
@@ -10331,7 +10410,7 @@
         <v>2026</v>
       </c>
       <c r="C175" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D175">
         <v>249</v>
@@ -10366,7 +10445,7 @@
         <v>2026</v>
       </c>
       <c r="C176" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D176">
         <v>266</v>
@@ -10393,7 +10472,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>53</v>
       </c>
@@ -10401,7 +10480,7 @@
         <v>2026</v>
       </c>
       <c r="C177" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D177">
         <v>268</v>
@@ -10428,7 +10507,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>53</v>
       </c>
@@ -10436,7 +10515,7 @@
         <v>2026</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D178">
         <v>155</v>
@@ -10463,7 +10542,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>54</v>
       </c>
@@ -10471,7 +10550,7 @@
         <v>2025</v>
       </c>
       <c r="C179" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D179">
         <v>1154</v>
@@ -10497,9 +10576,8 @@
       <c r="K179">
         <v>0.49</v>
       </c>
-      <c r="O179" s="11"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>54</v>
       </c>
@@ -10507,7 +10585,7 @@
         <v>2025</v>
       </c>
       <c r="C180" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D180">
         <v>1318</v>
@@ -10534,7 +10612,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>54</v>
       </c>
@@ -10542,7 +10620,7 @@
         <v>2025</v>
       </c>
       <c r="C181" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D181">
         <v>1115</v>
@@ -10569,7 +10647,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>54</v>
       </c>
@@ -10577,7 +10655,7 @@
         <v>2025</v>
       </c>
       <c r="C182" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D182">
         <v>1177</v>
@@ -10604,7 +10682,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>54</v>
       </c>
@@ -10612,7 +10690,7 @@
         <v>2025</v>
       </c>
       <c r="C183" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D183">
         <v>1634</v>
@@ -10639,7 +10717,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>54</v>
       </c>
@@ -10647,7 +10725,7 @@
         <v>2025</v>
       </c>
       <c r="C184" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D184">
         <v>1345</v>
@@ -10674,7 +10752,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>54</v>
       </c>
@@ -10682,7 +10760,7 @@
         <v>2025</v>
       </c>
       <c r="C185" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D185">
         <v>1465</v>
@@ -10709,7 +10787,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>54</v>
       </c>
@@ -10717,7 +10795,7 @@
         <v>2025</v>
       </c>
       <c r="C186" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D186">
         <v>1366</v>
@@ -10744,7 +10822,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>54</v>
       </c>
@@ -10752,7 +10830,7 @@
         <v>2025</v>
       </c>
       <c r="C187" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D187">
         <v>1346</v>
@@ -10779,7 +10857,7 @@
         <v>-0.53</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>54</v>
       </c>
@@ -10787,7 +10865,7 @@
         <v>2025</v>
       </c>
       <c r="C188" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D188">
         <v>1341</v>
@@ -10814,7 +10892,7 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>54</v>
       </c>
@@ -10822,7 +10900,7 @@
         <v>2025</v>
       </c>
       <c r="C189" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D189">
         <v>728</v>
@@ -10849,7 +10927,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>54</v>
       </c>
@@ -10857,7 +10935,7 @@
         <v>2025</v>
       </c>
       <c r="C190" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D190">
         <v>736</v>
@@ -10884,7 +10962,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>54</v>
       </c>
@@ -10892,7 +10970,7 @@
         <v>2026</v>
       </c>
       <c r="C191" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D191">
         <v>643</v>
@@ -10919,7 +10997,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>54</v>
       </c>
@@ -10927,7 +11005,7 @@
         <v>2026</v>
       </c>
       <c r="C192" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D192">
         <v>1049</v>
@@ -10962,7 +11040,7 @@
         <v>2026</v>
       </c>
       <c r="C193" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D193">
         <v>1167</v>
@@ -10997,7 +11075,7 @@
         <v>2026</v>
       </c>
       <c r="C194" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D194">
         <v>733</v>
@@ -11032,7 +11110,7 @@
         <v>2025</v>
       </c>
       <c r="C195" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D195">
         <v>1121</v>
@@ -11067,7 +11145,7 @@
         <v>2025</v>
       </c>
       <c r="C196" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D196">
         <v>1446</v>
@@ -11102,7 +11180,7 @@
         <v>2025</v>
       </c>
       <c r="C197" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D197">
         <v>1051</v>
@@ -11137,7 +11215,7 @@
         <v>2025</v>
       </c>
       <c r="C198" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D198">
         <v>991</v>
@@ -11172,7 +11250,7 @@
         <v>2025</v>
       </c>
       <c r="C199" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D199">
         <v>1050</v>
@@ -11207,7 +11285,7 @@
         <v>2025</v>
       </c>
       <c r="C200" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D200">
         <v>1299</v>
@@ -11242,7 +11320,7 @@
         <v>2025</v>
       </c>
       <c r="C201" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D201">
         <v>1288</v>
@@ -11277,7 +11355,7 @@
         <v>2025</v>
       </c>
       <c r="C202" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D202">
         <v>1381</v>
@@ -11312,7 +11390,7 @@
         <v>2025</v>
       </c>
       <c r="C203" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D203">
         <v>1412</v>
@@ -11347,7 +11425,7 @@
         <v>2025</v>
       </c>
       <c r="C204" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D204">
         <v>1092</v>
@@ -11382,7 +11460,7 @@
         <v>2025</v>
       </c>
       <c r="C205" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D205">
         <v>1226</v>
@@ -11417,7 +11495,7 @@
         <v>2025</v>
       </c>
       <c r="C206" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D206">
         <v>715</v>
@@ -11452,7 +11530,7 @@
         <v>2026</v>
       </c>
       <c r="C207" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D207">
         <v>1338</v>
@@ -11487,7 +11565,7 @@
         <v>2026</v>
       </c>
       <c r="C208" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D208">
         <v>1332</v>
@@ -11522,7 +11600,7 @@
         <v>2026</v>
       </c>
       <c r="C209" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D209">
         <v>1440</v>
@@ -11557,7 +11635,7 @@
         <v>2026</v>
       </c>
       <c r="C210" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D210">
         <v>692</v>
@@ -11592,7 +11670,7 @@
         <v>2025</v>
       </c>
       <c r="C211" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D211">
         <v>2628</v>
@@ -11627,7 +11705,7 @@
         <v>2025</v>
       </c>
       <c r="C212" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D212">
         <v>2305</v>
@@ -11662,7 +11740,7 @@
         <v>2025</v>
       </c>
       <c r="C213" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D213">
         <v>1999</v>
@@ -11697,7 +11775,7 @@
         <v>2025</v>
       </c>
       <c r="C214" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D214">
         <v>1499</v>
@@ -11732,7 +11810,7 @@
         <v>2025</v>
       </c>
       <c r="C215" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D215">
         <v>792</v>
@@ -11767,7 +11845,7 @@
         <v>2025</v>
       </c>
       <c r="C216" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D216">
         <v>471</v>
@@ -11802,7 +11880,7 @@
         <v>2025</v>
       </c>
       <c r="C217" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D217">
         <v>2036</v>
@@ -11837,7 +11915,7 @@
         <v>2025</v>
       </c>
       <c r="C218" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D218">
         <v>1853</v>
@@ -11872,7 +11950,7 @@
         <v>2025</v>
       </c>
       <c r="C219" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D219">
         <v>1592</v>
@@ -11907,7 +11985,7 @@
         <v>2025</v>
       </c>
       <c r="C220" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D220">
         <v>1752</v>
@@ -11942,7 +12020,7 @@
         <v>2025</v>
       </c>
       <c r="C221" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D221">
         <v>1795</v>
@@ -11977,7 +12055,7 @@
         <v>2025</v>
       </c>
       <c r="C222" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D222">
         <v>1735</v>
@@ -12012,7 +12090,7 @@
         <v>2026</v>
       </c>
       <c r="C223" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D223">
         <v>2434</v>
@@ -12047,7 +12125,7 @@
         <v>2026</v>
       </c>
       <c r="C224" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D224">
         <v>2158</v>
@@ -12082,7 +12160,7 @@
         <v>2026</v>
       </c>
       <c r="C225" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D225">
         <v>2242</v>
@@ -12117,7 +12195,7 @@
         <v>2026</v>
       </c>
       <c r="C226" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D226">
         <v>1621</v>
@@ -12152,7 +12230,7 @@
         <v>2025</v>
       </c>
       <c r="C227" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D227">
         <v>7951</v>
@@ -12172,7 +12250,7 @@
         <v>2025</v>
       </c>
       <c r="C228" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D228">
         <v>6531</v>
@@ -12207,7 +12285,7 @@
         <v>2025</v>
       </c>
       <c r="C229" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D229">
         <v>5116</v>
@@ -12242,7 +12320,7 @@
         <v>2026</v>
       </c>
       <c r="C230" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D230">
         <v>6193</v>
@@ -12277,7 +12355,7 @@
         <v>2026</v>
       </c>
       <c r="C231" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D231">
         <v>6040</v>
@@ -12312,7 +12390,7 @@
         <v>2026</v>
       </c>
       <c r="C232" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D232">
         <v>4717</v>
@@ -12347,7 +12425,7 @@
         <v>2026</v>
       </c>
       <c r="C233" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D233">
         <v>2918</v>
@@ -12382,7 +12460,7 @@
         <v>2025</v>
       </c>
       <c r="C234" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D234">
         <v>10540</v>
@@ -12417,7 +12495,7 @@
         <v>2025</v>
       </c>
       <c r="C235" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D235">
         <v>7316</v>
@@ -12452,7 +12530,7 @@
         <v>2025</v>
       </c>
       <c r="C236" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D236">
         <v>5323</v>
@@ -12487,7 +12565,7 @@
         <v>2026</v>
       </c>
       <c r="C237" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D237">
         <v>6542</v>
@@ -12522,7 +12600,7 @@
         <v>2026</v>
       </c>
       <c r="C238" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D238">
         <v>6331</v>
@@ -12557,7 +12635,7 @@
         <v>2026</v>
       </c>
       <c r="C239" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D239">
         <v>6674</v>
@@ -12592,7 +12670,7 @@
         <v>2026</v>
       </c>
       <c r="C240" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D240">
         <v>5251</v>
@@ -12621,13 +12699,13 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B241">
         <v>2025</v>
       </c>
       <c r="C241" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D241">
         <v>6306</v>
@@ -12647,7 +12725,7 @@
         <v>2025</v>
       </c>
       <c r="C242" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D242">
         <v>3097</v>
@@ -12682,7 +12760,7 @@
         <v>2025</v>
       </c>
       <c r="C243" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D243">
         <v>3595</v>
@@ -12717,7 +12795,7 @@
         <v>2025</v>
       </c>
       <c r="C244" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D244">
         <v>3503</v>
@@ -12752,7 +12830,7 @@
         <v>2025</v>
       </c>
       <c r="C245" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D245">
         <v>3152</v>
@@ -12787,7 +12865,7 @@
         <v>2025</v>
       </c>
       <c r="C246" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D246">
         <v>3158</v>
@@ -12822,7 +12900,7 @@
         <v>2025</v>
       </c>
       <c r="C247" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D247">
         <v>3243</v>
@@ -12857,7 +12935,7 @@
         <v>2025</v>
       </c>
       <c r="C248" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D248">
         <v>2111</v>
@@ -12892,7 +12970,7 @@
         <v>2025</v>
       </c>
       <c r="C249" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D249">
         <v>2109</v>
@@ -12927,7 +13005,7 @@
         <v>2025</v>
       </c>
       <c r="C250" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D250">
         <v>1494</v>
@@ -12962,7 +13040,7 @@
         <v>2025</v>
       </c>
       <c r="C251" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D251">
         <v>1703</v>
@@ -12997,7 +13075,7 @@
         <v>2025</v>
       </c>
       <c r="C252" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D252">
         <v>1519</v>
@@ -13032,7 +13110,7 @@
         <v>2025</v>
       </c>
       <c r="C253" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D253">
         <v>1902</v>
@@ -13067,7 +13145,7 @@
         <v>2026</v>
       </c>
       <c r="C254" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D254">
         <v>3204</v>
@@ -13102,7 +13180,7 @@
         <v>2026</v>
       </c>
       <c r="C255" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D255">
         <v>2906</v>
@@ -13137,7 +13215,7 @@
         <v>2026</v>
       </c>
       <c r="C256" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D256">
         <v>2773</v>
@@ -13172,7 +13250,7 @@
         <v>2026</v>
       </c>
       <c r="C257" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D257">
         <v>1958</v>
@@ -13207,7 +13285,7 @@
         <v>2025</v>
       </c>
       <c r="C258" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D258">
         <v>285</v>
@@ -13227,7 +13305,7 @@
         <v>2025</v>
       </c>
       <c r="C259" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D259">
         <v>539</v>
@@ -13262,7 +13340,7 @@
         <v>2026</v>
       </c>
       <c r="C260" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D260">
         <v>546</v>
@@ -13297,7 +13375,7 @@
         <v>2026</v>
       </c>
       <c r="C261" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D261">
         <v>568</v>
@@ -13332,7 +13410,7 @@
         <v>2026</v>
       </c>
       <c r="C262" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D262">
         <v>711</v>
@@ -13367,7 +13445,7 @@
         <v>2026</v>
       </c>
       <c r="C263" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D263">
         <v>460</v>
@@ -13402,7 +13480,7 @@
         <v>2025</v>
       </c>
       <c r="C264" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D264">
         <v>1279</v>
@@ -13437,7 +13515,7 @@
         <v>2025</v>
       </c>
       <c r="C265" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D265">
         <v>1343</v>
@@ -13472,7 +13550,7 @@
         <v>2025</v>
       </c>
       <c r="C266" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D266">
         <v>986</v>
@@ -13507,7 +13585,7 @@
         <v>2025</v>
       </c>
       <c r="C267" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D267">
         <v>1032</v>
@@ -13542,7 +13620,7 @@
         <v>2025</v>
       </c>
       <c r="C268" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D268">
         <v>1399</v>
@@ -13577,7 +13655,7 @@
         <v>2025</v>
       </c>
       <c r="C269" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D269">
         <v>1186</v>
@@ -13612,7 +13690,7 @@
         <v>2025</v>
       </c>
       <c r="C270" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D270">
         <v>1647</v>
@@ -13647,7 +13725,7 @@
         <v>2025</v>
       </c>
       <c r="C271" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D271">
         <v>1846</v>
@@ -13682,7 +13760,7 @@
         <v>2025</v>
       </c>
       <c r="C272" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D272">
         <v>1506</v>
@@ -13717,7 +13795,7 @@
         <v>2025</v>
       </c>
       <c r="C273" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D273">
         <v>1305</v>
@@ -13752,7 +13830,7 @@
         <v>2025</v>
       </c>
       <c r="C274" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D274">
         <v>1379</v>
@@ -13787,7 +13865,7 @@
         <v>2025</v>
       </c>
       <c r="C275" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D275">
         <v>1592</v>
@@ -13822,7 +13900,7 @@
         <v>2026</v>
       </c>
       <c r="C276" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D276">
         <v>1861</v>
@@ -13857,7 +13935,7 @@
         <v>2026</v>
       </c>
       <c r="C277" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D277">
         <v>1516</v>
@@ -13892,7 +13970,7 @@
         <v>2026</v>
       </c>
       <c r="C278" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D278">
         <v>1685</v>
@@ -13927,7 +14005,7 @@
         <v>2026</v>
       </c>
       <c r="C279" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D279">
         <v>1027</v>
@@ -13962,7 +14040,7 @@
         <v>2025</v>
       </c>
       <c r="C280" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D280">
         <v>430</v>
@@ -13994,7 +14072,7 @@
         <v>2025</v>
       </c>
       <c r="C281" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D281">
         <v>640</v>
@@ -14026,7 +14104,7 @@
         <v>2025</v>
       </c>
       <c r="C282" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D282">
         <v>1058</v>
@@ -14058,7 +14136,7 @@
         <v>2026</v>
       </c>
       <c r="C283" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D283">
         <v>545</v>
@@ -14090,7 +14168,7 @@
         <v>2026</v>
       </c>
       <c r="C284" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D284">
         <v>575</v>
@@ -14122,7 +14200,7 @@
         <v>2026</v>
       </c>
       <c r="C285" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D285">
         <v>1193</v>
@@ -14154,7 +14232,7 @@
         <v>2026</v>
       </c>
       <c r="C286" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D286">
         <v>887</v>
@@ -14186,7 +14264,7 @@
         <v>2025</v>
       </c>
       <c r="C287" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D287">
         <v>1120</v>
@@ -14221,7 +14299,7 @@
         <v>2025</v>
       </c>
       <c r="C288" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D288">
         <v>1428</v>
@@ -14256,7 +14334,7 @@
         <v>2025</v>
       </c>
       <c r="C289" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D289">
         <v>1375</v>
@@ -14291,7 +14369,7 @@
         <v>2025</v>
       </c>
       <c r="C290" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D290">
         <v>1013</v>
@@ -14326,7 +14404,7 @@
         <v>2025</v>
       </c>
       <c r="C291" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D291">
         <v>1203</v>
@@ -14361,7 +14439,7 @@
         <v>2025</v>
       </c>
       <c r="C292" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D292">
         <v>1039</v>
@@ -14396,7 +14474,7 @@
         <v>2025</v>
       </c>
       <c r="C293" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D293">
         <v>1570</v>
@@ -14431,7 +14509,7 @@
         <v>2025</v>
       </c>
       <c r="C294" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D294">
         <v>1875</v>
@@ -14466,7 +14544,7 @@
         <v>2025</v>
       </c>
       <c r="C295" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D295">
         <v>1869</v>
@@ -14501,7 +14579,7 @@
         <v>2025</v>
       </c>
       <c r="C296" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D296">
         <v>1542</v>
@@ -14536,7 +14614,7 @@
         <v>2025</v>
       </c>
       <c r="C297" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D297">
         <v>1232</v>
@@ -14571,7 +14649,7 @@
         <v>2025</v>
       </c>
       <c r="C298" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D298">
         <v>1254</v>
@@ -14606,7 +14684,7 @@
         <v>2026</v>
       </c>
       <c r="C299" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D299">
         <v>1456</v>
@@ -14641,7 +14719,7 @@
         <v>2026</v>
       </c>
       <c r="C300" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D300">
         <v>1682</v>
@@ -14676,7 +14754,7 @@
         <v>2026</v>
       </c>
       <c r="C301" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D301">
         <v>1622</v>
@@ -14711,7 +14789,7 @@
         <v>2026</v>
       </c>
       <c r="C302" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D302">
         <v>1198</v>
@@ -14740,13 +14818,13 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="B303">
         <v>2026</v>
       </c>
       <c r="C303" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D303">
         <v>75</v>
@@ -14760,13 +14838,13 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="B304">
         <v>2026</v>
       </c>
       <c r="C304" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D304">
         <v>130</v>
@@ -14786,7 +14864,7 @@
         <v>2025</v>
       </c>
       <c r="C305" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D305">
         <v>782</v>
@@ -14821,7 +14899,7 @@
         <v>2025</v>
       </c>
       <c r="C306" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D306">
         <v>799</v>
@@ -14856,7 +14934,7 @@
         <v>2025</v>
       </c>
       <c r="C307" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D307">
         <v>715</v>
@@ -14891,7 +14969,7 @@
         <v>2025</v>
       </c>
       <c r="C308" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D308">
         <v>437</v>
@@ -14926,7 +15004,7 @@
         <v>2025</v>
       </c>
       <c r="C309" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="D309">
         <v>482</v>
@@ -14961,7 +15039,7 @@
         <v>2025</v>
       </c>
       <c r="C310" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D310">
         <v>596</v>
@@ -14996,7 +15074,7 @@
         <v>2025</v>
       </c>
       <c r="C311" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D311">
         <v>608</v>
@@ -15031,7 +15109,7 @@
         <v>2025</v>
       </c>
       <c r="C312" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="D312">
         <v>631</v>
@@ -15066,7 +15144,7 @@
         <v>2025</v>
       </c>
       <c r="C313" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="D313">
         <v>709</v>
@@ -15101,7 +15179,7 @@
         <v>2025</v>
       </c>
       <c r="C314" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D314">
         <v>558</v>
@@ -15136,7 +15214,7 @@
         <v>2025</v>
       </c>
       <c r="C315" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D315">
         <v>487</v>
@@ -15171,7 +15249,7 @@
         <v>2025</v>
       </c>
       <c r="C316" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="D316">
         <v>615</v>
@@ -15206,7 +15284,7 @@
         <v>2026</v>
       </c>
       <c r="C317" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D317">
         <v>512</v>
@@ -15241,7 +15319,7 @@
         <v>2026</v>
       </c>
       <c r="C318" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="D318">
         <v>450</v>
@@ -15276,7 +15354,7 @@
         <v>2026</v>
       </c>
       <c r="C319" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D319">
         <v>675</v>
@@ -15311,7 +15389,7 @@
         <v>2026</v>
       </c>
       <c r="C320" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D320">
         <v>429</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,21 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23270A9-7F85-4538-9FC2-C1A05407CCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FF8EEE-BFC2-451C-A7D4-C7F7F960515E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
     <sheet name="Tab2_Regional" sheetId="2" r:id="rId2"/>
     <sheet name="Tab3_Campaign" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tab1_KPI!$A$5:$AE$44</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="130">
   <si>
     <t>Tab 1 — KPI Data</t>
   </si>
@@ -279,58 +293,16 @@
     <t>Arizona</t>
   </si>
   <si>
-    <t>17.89%</t>
-  </si>
-  <si>
-    <t>40.00%</t>
-  </si>
-  <si>
-    <t>25.00%</t>
-  </si>
-  <si>
-    <t>10.00%</t>
-  </si>
-  <si>
     <t>Austin</t>
-  </si>
-  <si>
-    <t>0.19%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
   </si>
   <si>
     <t>Bay Area</t>
   </si>
   <si>
-    <t>14.31%</t>
-  </si>
-  <si>
-    <t>10.70%</t>
-  </si>
-  <si>
-    <t>39.13%</t>
-  </si>
-  <si>
-    <t>16.67%</t>
-  </si>
-  <si>
-    <t>6.52%</t>
-  </si>
-  <si>
     <t>CDR</t>
   </si>
   <si>
-    <t>0.39%</t>
-  </si>
-  <si>
     <t>Central Coast</t>
-  </si>
-  <si>
-    <t>1.16%</t>
-  </si>
-  <si>
-    <t>60.00%</t>
   </si>
   <si>
     <t>Corporate</t>
@@ -339,139 +311,28 @@
     <t>Fresno</t>
   </si>
   <si>
-    <t>2.32%</t>
-  </si>
-  <si>
     <t>Inland Empire</t>
-  </si>
-  <si>
-    <t>10.06%</t>
-  </si>
-  <si>
-    <t>10.49%</t>
-  </si>
-  <si>
-    <t>46.88%</t>
-  </si>
-  <si>
-    <t>13.33%</t>
-  </si>
-  <si>
-    <t>6.25%</t>
   </si>
   <si>
     <t>Las Vegas</t>
   </si>
   <si>
-    <t>4.45%</t>
-  </si>
-  <si>
-    <t>4.76%</t>
-  </si>
-  <si>
-    <t>20.00%</t>
-  </si>
-  <si>
-    <t>33.33%</t>
-  </si>
-  <si>
-    <t>6.67%</t>
-  </si>
-  <si>
-    <t>12.96%</t>
-  </si>
-  <si>
-    <t>1.96%</t>
-  </si>
-  <si>
-    <t>5.56%</t>
-  </si>
-  <si>
     <t>Orange County</t>
-  </si>
-  <si>
-    <t>9.09%</t>
-  </si>
-  <si>
-    <t>20.83%</t>
-  </si>
-  <si>
-    <t>80.95%</t>
-  </si>
-  <si>
-    <t>11.76%</t>
-  </si>
-  <si>
-    <t>9.52%</t>
   </si>
   <si>
     <t>Pasadena</t>
   </si>
   <si>
-    <t>14.70%</t>
-  </si>
-  <si>
-    <t>17.91%</t>
-  </si>
-  <si>
-    <t>38.89%</t>
-  </si>
-  <si>
-    <t>21.43%</t>
-  </si>
-  <si>
-    <t>8.33%</t>
-  </si>
-  <si>
     <t>Sacramento</t>
-  </si>
-  <si>
-    <t>5.80%</t>
-  </si>
-  <si>
-    <t>2.14%</t>
-  </si>
-  <si>
-    <t>44.44%</t>
   </si>
   <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>4.26%</t>
-  </si>
-  <si>
-    <t>2.26%</t>
-  </si>
-  <si>
-    <t>58.33%</t>
-  </si>
-  <si>
-    <t>14.29%</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
-    <t>6.58%</t>
-  </si>
-  <si>
-    <t>6.55%</t>
-  </si>
-  <si>
-    <t>28.57%</t>
-  </si>
-  <si>
     <t>Ventura/SB County</t>
-  </si>
-  <si>
-    <t>3.48%</t>
-  </si>
-  <si>
-    <t>4.33%</t>
-  </si>
-  <si>
-    <t>62.50%</t>
   </si>
   <si>
     <t>Tab 3 — Campaign Performance</t>
@@ -537,9 +398,6 @@
     <t>Feb</t>
   </si>
   <si>
-    <t>May</t>
-  </si>
-  <si>
     <t>Jun</t>
   </si>
   <si>
@@ -561,6 +419,9 @@
     <t>Dec</t>
   </si>
   <si>
+    <t>May</t>
+  </si>
+  <si>
     <t>PMAX 3 - Emerging Markets</t>
   </si>
   <si>
@@ -571,7 +432,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,24 +448,41 @@
       <sz val="13"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -657,10 +538,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -685,18 +567,30 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -999,8 +893,34 @@
   <dimension ref="A1:AE44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="31" width="14" customWidth="1"/>
+    <col min="1" max="1" width="40.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="14" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
@@ -1109,7 +1029,7 @@
       <c r="AD5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1202,7 +1122,7 @@
       <c r="AD6" s="9">
         <v>364</v>
       </c>
-      <c r="AE6" s="10">
+      <c r="AE6" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1295,7 +1215,7 @@
       <c r="AD7" s="9">
         <v>5</v>
       </c>
-      <c r="AE7" s="10">
+      <c r="AE7" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1390,7 +1310,7 @@
       <c r="AD8" s="9">
         <v>30</v>
       </c>
-      <c r="AE8" s="10">
+      <c r="AE8" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1437,7 +1357,7 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="9"/>
       <c r="AD9" s="9"/>
-      <c r="AE9" s="10">
+      <c r="AE9" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1500,7 +1420,7 @@
       <c r="AB10" s="8"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
-      <c r="AE10" s="10">
+      <c r="AE10" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1563,7 +1483,7 @@
       <c r="AB11" s="8"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="9"/>
-      <c r="AE11">
+      <c r="AE11" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1608,7 +1528,7 @@
       <c r="AB12" s="8"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
-      <c r="AE12">
+      <c r="AE12" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1653,7 +1573,7 @@
       <c r="AB13" s="8"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="9"/>
-      <c r="AE13">
+      <c r="AE13" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1726,7 +1646,7 @@
       </c>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
-      <c r="AE14">
+      <c r="AE14" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1821,7 +1741,7 @@
       <c r="AD15" s="9">
         <v>20</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1886,7 +1806,7 @@
       <c r="AB16" s="8"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
-      <c r="AE16">
+      <c r="AE16" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -1955,7 +1875,7 @@
       <c r="AD17" s="9">
         <v>3</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2002,7 +1922,7 @@
       <c r="AB18" s="8"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
-      <c r="AE18">
+      <c r="AE18" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2053,7 +1973,7 @@
       <c r="AD19" s="9">
         <v>3</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2116,7 +2036,7 @@
       </c>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
-      <c r="AE20">
+      <c r="AE20" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2163,7 +2083,7 @@
       </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
-      <c r="AE21">
+      <c r="AE21" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2226,7 +2146,7 @@
       </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
-      <c r="AE22">
+      <c r="AE22" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2301,7 +2221,7 @@
       <c r="AD23" s="9">
         <v>2</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2390,7 +2310,7 @@
       </c>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
-      <c r="AE24">
+      <c r="AE24" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2485,7 +2405,7 @@
       <c r="AD25" s="9">
         <v>11</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2550,7 +2470,7 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
-      <c r="AE26">
+      <c r="AE26" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2643,7 +2563,7 @@
       <c r="AD27" s="9">
         <v>12</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2690,7 +2610,7 @@
       <c r="AB28" s="8"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9"/>
-      <c r="AE28">
+      <c r="AE28" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2753,13 +2673,13 @@
       <c r="AB29" s="8"/>
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
-      <c r="AE29">
+      <c r="AE29" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2816,7 +2736,7 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="9"/>
-      <c r="AE30">
+      <c r="AE30" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2909,7 +2829,7 @@
       <c r="AD31" s="9">
         <v>19</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -2978,7 +2898,7 @@
       <c r="AD32" s="9">
         <v>41</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3045,7 +2965,7 @@
       <c r="AD33" s="9">
         <v>23</v>
       </c>
-      <c r="AE33">
+      <c r="AE33" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3138,13 +3058,13 @@
       <c r="AD34" s="9">
         <v>14</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -3203,7 +3123,7 @@
       <c r="AB35" s="8"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
-      <c r="AE35">
+      <c r="AE35" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3270,7 +3190,7 @@
       <c r="AD36" s="9">
         <v>15</v>
       </c>
-      <c r="AE36">
+      <c r="AE36" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3363,13 +3283,13 @@
       <c r="AD37" s="9">
         <v>14</v>
       </c>
-      <c r="AE37">
+      <c r="AE37" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3428,7 +3348,7 @@
       <c r="AB38" s="8"/>
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
-      <c r="AE38">
+      <c r="AE38" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3509,7 +3429,7 @@
       </c>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
-      <c r="AE39">
+      <c r="AE39" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3604,13 +3524,13 @@
       <c r="AD40" s="9">
         <v>14</v>
       </c>
-      <c r="AE40">
+      <c r="AE40" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="N41">
         <v>19.059999999999999</v>
@@ -3654,13 +3574,13 @@
       <c r="AA41">
         <v>24000</v>
       </c>
-      <c r="AE41">
+      <c r="AE41" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="N42">
         <v>19.059999999999999</v>
@@ -3701,7 +3621,7 @@
       <c r="Z42">
         <v>0</v>
       </c>
-      <c r="AE42">
+      <c r="AE42" s="14">
         <v>46135</v>
       </c>
     </row>
@@ -3796,13 +3716,13 @@
       <c r="AD43">
         <v>5</v>
       </c>
-      <c r="AE43">
+      <c r="AE43" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -3840,11 +3760,12 @@
       <c r="Z44">
         <v>0</v>
       </c>
-      <c r="AE44">
+      <c r="AE44" s="14">
         <v>46135</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3862,11 +3783,11 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13" style="15" customWidth="1"/>
+    <col min="11" max="11" width="16" style="15" customWidth="1"/>
+    <col min="12" max="12" width="11" style="15" customWidth="1"/>
+    <col min="13" max="13" width="12" style="15" customWidth="1"/>
+    <col min="14" max="14" width="13" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -3907,24 +3828,24 @@
       <c r="I4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>84</v>
       </c>
       <c r="B5" s="5">
@@ -3951,25 +3872,25 @@
       <c r="I5" s="5">
         <v>68362.8</v>
       </c>
-      <c r="J5" s="12">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="J5" s="17">
+        <v>4</v>
+      </c>
+      <c r="K5" s="17">
+        <v>9</v>
+      </c>
+      <c r="L5" s="17">
+        <v>37</v>
+      </c>
+      <c r="M5" s="17">
+        <v>40</v>
+      </c>
+      <c r="N5" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>89</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -3995,25 +3916,25 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M6" s="5" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>91</v>
+      <c r="J6" s="17">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <v>0</v>
+      </c>
+      <c r="L6" s="17">
+        <v>100</v>
+      </c>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>92</v>
+      <c r="A7" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="B7" s="5">
         <v>81</v>
@@ -4039,25 +3960,25 @@
       <c r="I7" s="5">
         <v>40755.56</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>97</v>
+      <c r="J7" s="17">
+        <v>6</v>
+      </c>
+      <c r="K7" s="17">
+        <v>5</v>
+      </c>
+      <c r="L7" s="17">
+        <v>40</v>
+      </c>
+      <c r="M7" s="17">
+        <v>21</v>
+      </c>
+      <c r="N7" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>98</v>
+      <c r="A8" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="B8" s="5">
         <v>12</v>
@@ -4083,25 +4004,25 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="5" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>91</v>
+      <c r="J8" s="17">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17">
+        <v>0</v>
+      </c>
+      <c r="L8" s="17">
+        <v>16</v>
+      </c>
+      <c r="M8" s="17">
+        <v>50</v>
+      </c>
+      <c r="N8" s="17">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>100</v>
+      <c r="A9" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="B9" s="5">
         <v>7</v>
@@ -4127,25 +4048,25 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>91</v>
+      <c r="J9" s="17">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17">
+        <v>0</v>
+      </c>
+      <c r="L9" s="17">
+        <v>57</v>
+      </c>
+      <c r="M9" s="17">
+        <v>0</v>
+      </c>
+      <c r="N9" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>103</v>
+      <c r="A10" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="B10" s="5">
         <v>2</v>
@@ -4171,25 +4092,25 @@
       <c r="I10" s="5">
         <v>0</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" s="5" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>91</v>
+      <c r="J10" s="17">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
+      <c r="M10" s="17">
+        <v>0</v>
+      </c>
+      <c r="N10" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>104</v>
+      <c r="A11" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="B11" s="5">
         <v>13</v>
@@ -4215,25 +4136,25 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" s="5" t="s">
+      <c r="J11" s="17">
+        <v>1</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17">
+        <v>23</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="B12" s="5">
         <v>60</v>
@@ -4259,25 +4180,25 @@
       <c r="I12" s="5">
         <v>32156.9399999999</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>111</v>
+      <c r="J12" s="17">
+        <v>4</v>
+      </c>
+      <c r="K12" s="17">
+        <v>5</v>
+      </c>
+      <c r="L12" s="17">
+        <v>43</v>
+      </c>
+      <c r="M12" s="17">
+        <v>23</v>
+      </c>
+      <c r="N12" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>112</v>
+      <c r="A13" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="B13" s="5">
         <v>31</v>
@@ -4303,25 +4224,25 @@
       <c r="I13" s="5">
         <v>12943.84</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="N13" s="5" t="s">
+      <c r="J13" s="17">
+        <v>2</v>
+      </c>
+      <c r="K13" s="17">
+        <v>2</v>
+      </c>
+      <c r="L13" s="17">
+        <v>38</v>
+      </c>
+      <c r="M13" s="17">
+        <v>25</v>
+      </c>
+      <c r="N13" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="B14" s="5">
         <v>74</v>
@@ -4347,25 +4268,25 @@
       <c r="I14" s="5">
         <v>7499</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M14" s="5" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>120</v>
+      <c r="J14" s="17">
+        <v>6</v>
+      </c>
+      <c r="K14" s="17">
+        <v>1</v>
+      </c>
+      <c r="L14" s="17">
+        <v>0</v>
+      </c>
+      <c r="M14" s="17">
+        <v>0</v>
+      </c>
+      <c r="N14" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>121</v>
+      <c r="A15" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="B15" s="5">
         <v>54</v>
@@ -4391,25 +4312,25 @@
       <c r="I15" s="5">
         <v>63438.61</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>126</v>
+      <c r="J15" s="17">
+        <v>4</v>
+      </c>
+      <c r="K15" s="17">
+        <v>10</v>
+      </c>
+      <c r="L15" s="17">
+        <v>57</v>
+      </c>
+      <c r="M15" s="17">
+        <v>32</v>
+      </c>
+      <c r="N15" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>127</v>
+      <c r="A16" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="B16" s="5">
         <v>95</v>
@@ -4435,25 +4356,25 @@
       <c r="I16" s="5">
         <v>68476</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>132</v>
+      <c r="J16" s="17">
+        <v>7</v>
+      </c>
+      <c r="K16" s="17">
+        <v>9</v>
+      </c>
+      <c r="L16" s="17">
+        <v>42</v>
+      </c>
+      <c r="M16" s="17">
+        <v>22</v>
+      </c>
+      <c r="N16" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>133</v>
+      <c r="A17" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="B17" s="5">
         <v>33</v>
@@ -4479,25 +4400,25 @@
       <c r="I17" s="5">
         <v>8166</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>91</v>
+      <c r="J17" s="17">
+        <v>2</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1</v>
+      </c>
+      <c r="L17" s="17">
+        <v>54</v>
+      </c>
+      <c r="M17" s="17">
+        <v>5</v>
+      </c>
+      <c r="N17" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>137</v>
+      <c r="A18" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="B18" s="5">
         <v>22</v>
@@ -4523,25 +4444,25 @@
       <c r="I18" s="5">
         <v>8641</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>132</v>
+      <c r="J18" s="17">
+        <v>1</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" s="17">
+        <v>45</v>
+      </c>
+      <c r="M18" s="17">
+        <v>10</v>
+      </c>
+      <c r="N18" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>142</v>
+      <c r="A19" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="B19" s="5">
         <v>36</v>
@@ -4567,25 +4488,25 @@
       <c r="I19" s="5">
         <v>13015.8</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>91</v>
+      <c r="J19" s="17">
+        <v>2</v>
+      </c>
+      <c r="K19" s="17">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17">
+        <v>50</v>
+      </c>
+      <c r="M19" s="17">
+        <v>11</v>
+      </c>
+      <c r="N19" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>146</v>
+      <c r="A20" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="B20" s="5">
         <v>24</v>
@@ -4611,20 +4532,20 @@
       <c r="I20" s="5">
         <v>16532</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>87</v>
+      <c r="J20" s="17">
+        <v>1</v>
+      </c>
+      <c r="K20" s="17">
+        <v>2</v>
+      </c>
+      <c r="L20" s="17">
+        <v>41</v>
+      </c>
+      <c r="M20" s="17">
+        <v>20</v>
+      </c>
+      <c r="N20" s="17">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4634,7 +4555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K320"/>
+  <dimension ref="A1:O320"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4643,12 +4564,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4656,45 +4577,45 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5">
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D5" s="5">
         <v>4599</v>
@@ -4722,14 +4643,14 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="5">
         <v>2025</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D6" s="5">
         <v>4898</v>
@@ -4757,14 +4678,14 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="5">
         <v>2025</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D7" s="5">
         <v>5001</v>
@@ -4792,14 +4713,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="5">
         <v>2025</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D8" s="5">
         <v>5381</v>
@@ -4827,14 +4748,14 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5">
         <v>2025</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D9" s="5">
         <v>4516</v>
@@ -4862,14 +4783,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="5">
         <v>2025</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D10" s="5">
         <v>4270</v>
@@ -4897,14 +4818,14 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="5">
         <v>2025</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D11" s="5">
         <v>4709</v>
@@ -4932,14 +4853,14 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="5">
         <v>2025</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D12" s="5">
         <v>4436</v>
@@ -4967,14 +4888,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="5">
         <v>2025</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D13" s="5">
         <v>4357</v>
@@ -5002,14 +4923,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="5">
         <v>2025</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D14" s="5">
         <v>4550</v>
@@ -5037,14 +4958,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5">
         <v>2025</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D15" s="5">
         <v>4554</v>
@@ -5072,14 +4993,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="5">
         <v>2025</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D16" s="5">
         <v>5380</v>
@@ -5107,14 +5028,14 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="5">
         <v>2026</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D17" s="5">
         <v>4567</v>
@@ -5142,14 +5063,14 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="5">
         <v>2026</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D18" s="5">
         <v>4420</v>
@@ -5177,14 +5098,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="5">
         <v>2026</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D19" s="5">
         <v>4524</v>
@@ -5219,7 +5140,7 @@
         <v>2026</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D20">
         <v>2260</v>
@@ -5254,7 +5175,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>298</v>
@@ -5289,7 +5210,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D22">
         <v>461</v>
@@ -5324,7 +5245,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D23">
         <v>300</v>
@@ -5359,7 +5280,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D24">
         <v>339</v>
@@ -5394,7 +5315,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D25">
         <v>405</v>
@@ -5429,7 +5350,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D26">
         <v>432</v>
@@ -5464,7 +5385,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D27">
         <v>446</v>
@@ -5499,7 +5420,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D28">
         <v>449</v>
@@ -5534,7 +5455,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D29">
         <v>501</v>
@@ -5569,7 +5490,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D30">
         <v>532</v>
@@ -5604,7 +5525,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D31">
         <v>473</v>
@@ -5639,7 +5560,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D32">
         <v>595</v>
@@ -5674,7 +5595,7 @@
         <v>2026</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D33">
         <v>573</v>
@@ -5709,7 +5630,7 @@
         <v>2026</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D34">
         <v>574</v>
@@ -5744,7 +5665,7 @@
         <v>2026</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D35">
         <v>617</v>
@@ -5779,7 +5700,7 @@
         <v>2026</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D36">
         <v>393</v>
@@ -5814,7 +5735,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D37">
         <v>2098</v>
@@ -5849,7 +5770,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D38">
         <v>2428</v>
@@ -5884,7 +5805,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D39">
         <v>1807</v>
@@ -5919,7 +5840,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D40">
         <v>2202</v>
@@ -5954,7 +5875,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D41">
         <v>1377</v>
@@ -5989,7 +5910,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D42">
         <v>2116</v>
@@ -6024,7 +5945,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D43">
         <v>730</v>
@@ -6059,7 +5980,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D44">
         <v>1854</v>
@@ -6094,7 +6015,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D45">
         <v>1627</v>
@@ -6129,7 +6050,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D46">
         <v>1675</v>
@@ -6164,7 +6085,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D47">
         <v>1383</v>
@@ -6199,7 +6120,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D48">
         <v>1061</v>
@@ -6234,7 +6155,7 @@
         <v>2026</v>
       </c>
       <c r="C49" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D49">
         <v>2996</v>
@@ -6269,7 +6190,7 @@
         <v>2026</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D50">
         <v>2864</v>
@@ -6304,7 +6225,7 @@
         <v>2026</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D51">
         <v>3423</v>
@@ -6339,7 +6260,7 @@
         <v>2026</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D52">
         <v>2378</v>
@@ -6374,7 +6295,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D53">
         <v>510</v>
@@ -6409,7 +6330,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D54">
         <v>750</v>
@@ -6444,7 +6365,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D55">
         <v>378</v>
@@ -6479,7 +6400,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D56">
         <v>518</v>
@@ -6514,7 +6435,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D57">
         <v>518</v>
@@ -6549,7 +6470,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D58">
         <v>676</v>
@@ -6584,7 +6505,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D59">
         <v>695</v>
@@ -6619,7 +6540,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D60">
         <v>653</v>
@@ -6654,7 +6575,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D61">
         <v>476</v>
@@ -6689,7 +6610,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D62">
         <v>454</v>
@@ -6724,7 +6645,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D63">
         <v>595</v>
@@ -6759,7 +6680,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D64">
         <v>26</v>
@@ -6794,7 +6715,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D65">
         <v>202</v>
@@ -6829,7 +6750,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D66">
         <v>87</v>
@@ -6849,7 +6770,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D67">
         <v>22</v>
@@ -6869,7 +6790,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D68">
         <v>98</v>
@@ -6904,7 +6825,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D69">
         <v>239</v>
@@ -6924,7 +6845,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D70">
         <v>421</v>
@@ -6944,7 +6865,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D71">
         <v>524</v>
@@ -6979,7 +6900,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D72">
         <v>509</v>
@@ -7014,7 +6935,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D73">
         <v>447</v>
@@ -7049,7 +6970,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D74">
         <v>181</v>
@@ -7069,7 +6990,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D75">
         <v>69</v>
@@ -7104,7 +7025,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D76">
         <v>54</v>
@@ -7124,7 +7045,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D77">
         <v>56</v>
@@ -7159,7 +7080,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D78">
         <v>112</v>
@@ -7194,7 +7115,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D79">
         <v>114</v>
@@ -7229,7 +7150,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D80">
         <v>141</v>
@@ -7264,7 +7185,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D81">
         <v>231</v>
@@ -7299,7 +7220,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D82">
         <v>113</v>
@@ -7334,7 +7255,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D83">
         <v>175</v>
@@ -7369,7 +7290,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D84">
         <v>234</v>
@@ -7404,7 +7325,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D85">
         <v>145</v>
@@ -7439,7 +7360,7 @@
         <v>2026</v>
       </c>
       <c r="C86" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D86">
         <v>172</v>
@@ -7474,7 +7395,7 @@
         <v>2026</v>
       </c>
       <c r="C87" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D87">
         <v>175</v>
@@ -7509,7 +7430,7 @@
         <v>2026</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D88">
         <v>20</v>
@@ -7529,7 +7450,7 @@
         <v>2026</v>
       </c>
       <c r="C89" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D89">
         <v>87</v>
@@ -7549,7 +7470,7 @@
         <v>2025</v>
       </c>
       <c r="C90" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D90">
         <v>2449</v>
@@ -7584,7 +7505,7 @@
         <v>2025</v>
       </c>
       <c r="C91" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D91">
         <v>2981</v>
@@ -7619,7 +7540,7 @@
         <v>2025</v>
       </c>
       <c r="C92" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D92">
         <v>2292</v>
@@ -7654,7 +7575,7 @@
         <v>2025</v>
       </c>
       <c r="C93" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D93">
         <v>1930</v>
@@ -7689,7 +7610,7 @@
         <v>2025</v>
       </c>
       <c r="C94" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D94">
         <v>2334</v>
@@ -7724,7 +7645,7 @@
         <v>2025</v>
       </c>
       <c r="C95" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D95">
         <v>2616</v>
@@ -7759,7 +7680,7 @@
         <v>2025</v>
       </c>
       <c r="C96" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D96">
         <v>1012</v>
@@ -7794,7 +7715,7 @@
         <v>2025</v>
       </c>
       <c r="C97" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D97">
         <v>737</v>
@@ -7829,7 +7750,7 @@
         <v>2025</v>
       </c>
       <c r="C98" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D98">
         <v>1336</v>
@@ -7864,7 +7785,7 @@
         <v>2025</v>
       </c>
       <c r="C99" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D99">
         <v>1621</v>
@@ -7899,7 +7820,7 @@
         <v>2025</v>
       </c>
       <c r="C100" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D100">
         <v>1725</v>
@@ -7934,7 +7855,7 @@
         <v>2025</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D101">
         <v>1973</v>
@@ -7969,7 +7890,7 @@
         <v>2026</v>
       </c>
       <c r="C102" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D102">
         <v>2119</v>
@@ -8004,7 +7925,7 @@
         <v>2026</v>
       </c>
       <c r="C103" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D103">
         <v>1914</v>
@@ -8039,7 +7960,7 @@
         <v>2026</v>
       </c>
       <c r="C104" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D104">
         <v>1958</v>
@@ -8074,7 +7995,7 @@
         <v>2026</v>
       </c>
       <c r="C105" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D105">
         <v>1071</v>
@@ -8109,7 +8030,7 @@
         <v>2025</v>
       </c>
       <c r="C106" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D106">
         <v>262</v>
@@ -8144,7 +8065,7 @@
         <v>2025</v>
       </c>
       <c r="C107" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D107">
         <v>340</v>
@@ -8179,7 +8100,7 @@
         <v>2025</v>
       </c>
       <c r="C108" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D108">
         <v>214</v>
@@ -8214,7 +8135,7 @@
         <v>2025</v>
       </c>
       <c r="C109" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D109">
         <v>178</v>
@@ -8249,7 +8170,7 @@
         <v>2025</v>
       </c>
       <c r="C110" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D110">
         <v>226</v>
@@ -8284,7 +8205,7 @@
         <v>2025</v>
       </c>
       <c r="C111" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D111">
         <v>215</v>
@@ -8319,7 +8240,7 @@
         <v>2025</v>
       </c>
       <c r="C112" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D112">
         <v>212</v>
@@ -8354,7 +8275,7 @@
         <v>2025</v>
       </c>
       <c r="C113" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D113">
         <v>211</v>
@@ -8389,7 +8310,7 @@
         <v>2025</v>
       </c>
       <c r="C114" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D114">
         <v>237</v>
@@ -8424,7 +8345,7 @@
         <v>2025</v>
       </c>
       <c r="C115" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D115">
         <v>443</v>
@@ -8459,7 +8380,7 @@
         <v>2025</v>
       </c>
       <c r="C116" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D116">
         <v>486</v>
@@ -8494,7 +8415,7 @@
         <v>2025</v>
       </c>
       <c r="C117" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D117">
         <v>453</v>
@@ -8529,7 +8450,7 @@
         <v>2026</v>
       </c>
       <c r="C118" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D118">
         <v>489</v>
@@ -8564,7 +8485,7 @@
         <v>2026</v>
       </c>
       <c r="C119" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D119">
         <v>371</v>
@@ -8599,7 +8520,7 @@
         <v>2026</v>
       </c>
       <c r="C120" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D120">
         <v>477</v>
@@ -8634,7 +8555,7 @@
         <v>2026</v>
       </c>
       <c r="C121" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="G121">
         <v>2</v>
@@ -8657,7 +8578,7 @@
         <v>2025</v>
       </c>
       <c r="C122" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D122">
         <v>601</v>
@@ -8677,7 +8598,7 @@
         <v>2025</v>
       </c>
       <c r="C123" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D123">
         <v>678</v>
@@ -8712,7 +8633,7 @@
         <v>2025</v>
       </c>
       <c r="C124" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D124">
         <v>894</v>
@@ -8747,7 +8668,7 @@
         <v>2025</v>
       </c>
       <c r="C125" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D125">
         <v>637</v>
@@ -8782,7 +8703,7 @@
         <v>2025</v>
       </c>
       <c r="C126" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D126">
         <v>219</v>
@@ -8817,7 +8738,7 @@
         <v>2025</v>
       </c>
       <c r="C127" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D127">
         <v>225</v>
@@ -8852,7 +8773,7 @@
         <v>2025</v>
       </c>
       <c r="C128" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D128">
         <v>479</v>
@@ -8887,7 +8808,7 @@
         <v>2025</v>
       </c>
       <c r="C129" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D129">
         <v>674</v>
@@ -8922,7 +8843,7 @@
         <v>2025</v>
       </c>
       <c r="C130" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D130">
         <v>473</v>
@@ -8957,7 +8878,7 @@
         <v>2026</v>
       </c>
       <c r="C131" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D131">
         <v>172</v>
@@ -8992,7 +8913,7 @@
         <v>2026</v>
       </c>
       <c r="C132" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D132">
         <v>134</v>
@@ -9027,7 +8948,7 @@
         <v>2026</v>
       </c>
       <c r="C133" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="G133">
         <v>2</v>
@@ -9050,7 +8971,7 @@
         <v>2025</v>
       </c>
       <c r="C134" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D134">
         <v>1022</v>
@@ -9082,7 +9003,7 @@
         <v>2025</v>
       </c>
       <c r="C135" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D135">
         <v>1633</v>
@@ -9114,7 +9035,7 @@
         <v>2025</v>
       </c>
       <c r="C136" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D136">
         <v>2023</v>
@@ -9146,7 +9067,7 @@
         <v>2025</v>
       </c>
       <c r="C137" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D137">
         <v>2136</v>
@@ -9178,7 +9099,7 @@
         <v>2025</v>
       </c>
       <c r="C138" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D138">
         <v>1956</v>
@@ -9210,7 +9131,7 @@
         <v>2025</v>
       </c>
       <c r="C139" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D139">
         <v>2154</v>
@@ -9242,7 +9163,7 @@
         <v>2026</v>
       </c>
       <c r="C140" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D140">
         <v>2248</v>
@@ -9274,7 +9195,7 @@
         <v>2026</v>
       </c>
       <c r="C141" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D141">
         <v>1955</v>
@@ -9306,7 +9227,7 @@
         <v>2026</v>
       </c>
       <c r="C142" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D142">
         <v>2188</v>
@@ -9338,7 +9259,7 @@
         <v>2026</v>
       </c>
       <c r="C143" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D143">
         <v>1653</v>
@@ -9370,7 +9291,7 @@
         <v>2026</v>
       </c>
       <c r="C144" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D144">
         <v>70</v>
@@ -9390,7 +9311,7 @@
         <v>2026</v>
       </c>
       <c r="C145" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D145">
         <v>142</v>
@@ -9410,7 +9331,7 @@
         <v>2026</v>
       </c>
       <c r="C146" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D146">
         <v>37441</v>
@@ -9445,7 +9366,7 @@
         <v>2025</v>
       </c>
       <c r="C147" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D147">
         <v>347</v>
@@ -9480,7 +9401,7 @@
         <v>2025</v>
       </c>
       <c r="C148" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D148">
         <v>504</v>
@@ -9515,7 +9436,7 @@
         <v>2025</v>
       </c>
       <c r="C149" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D149">
         <v>521</v>
@@ -9550,7 +9471,7 @@
         <v>2025</v>
       </c>
       <c r="C150" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D150">
         <v>330</v>
@@ -9570,7 +9491,7 @@
         <v>2025</v>
       </c>
       <c r="C151" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D151">
         <v>517</v>
@@ -9605,7 +9526,7 @@
         <v>2025</v>
       </c>
       <c r="C152" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D152">
         <v>464</v>
@@ -9640,7 +9561,7 @@
         <v>2025</v>
       </c>
       <c r="C153" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D153">
         <v>467</v>
@@ -9675,7 +9596,7 @@
         <v>2025</v>
       </c>
       <c r="C154" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D154">
         <v>446</v>
@@ -9710,7 +9631,7 @@
         <v>2025</v>
       </c>
       <c r="C155" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D155">
         <v>429</v>
@@ -9745,7 +9666,7 @@
         <v>2025</v>
       </c>
       <c r="C156" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D156">
         <v>437</v>
@@ -9780,7 +9701,7 @@
         <v>2025</v>
       </c>
       <c r="C157" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D157">
         <v>452</v>
@@ -9815,7 +9736,7 @@
         <v>2025</v>
       </c>
       <c r="C158" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D158">
         <v>492</v>
@@ -9850,7 +9771,7 @@
         <v>2026</v>
       </c>
       <c r="C159" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D159">
         <v>428</v>
@@ -9885,7 +9806,7 @@
         <v>2026</v>
       </c>
       <c r="C160" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D160">
         <v>358</v>
@@ -9920,7 +9841,7 @@
         <v>2026</v>
       </c>
       <c r="C161" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D161">
         <v>437</v>
@@ -9955,7 +9876,7 @@
         <v>2026</v>
       </c>
       <c r="C162" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D162">
         <v>336</v>
@@ -9990,7 +9911,7 @@
         <v>2025</v>
       </c>
       <c r="C163" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D163">
         <v>168</v>
@@ -10025,7 +9946,7 @@
         <v>2025</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D164">
         <v>192</v>
@@ -10060,7 +9981,7 @@
         <v>2025</v>
       </c>
       <c r="C165" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D165">
         <v>152</v>
@@ -10095,7 +10016,7 @@
         <v>2025</v>
       </c>
       <c r="C166" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D166">
         <v>82</v>
@@ -10130,7 +10051,7 @@
         <v>2025</v>
       </c>
       <c r="C167" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D167">
         <v>106</v>
@@ -10165,7 +10086,7 @@
         <v>2025</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D168">
         <v>98</v>
@@ -10200,7 +10121,7 @@
         <v>2025</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -10235,7 +10156,7 @@
         <v>2025</v>
       </c>
       <c r="C170" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D170">
         <v>47</v>
@@ -10270,7 +10191,7 @@
         <v>2025</v>
       </c>
       <c r="C171" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D171">
         <v>88</v>
@@ -10305,7 +10226,7 @@
         <v>2025</v>
       </c>
       <c r="C172" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D172">
         <v>117</v>
@@ -10340,7 +10261,7 @@
         <v>2025</v>
       </c>
       <c r="C173" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D173">
         <v>81</v>
@@ -10375,7 +10296,7 @@
         <v>2025</v>
       </c>
       <c r="C174" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D174">
         <v>161</v>
@@ -10410,7 +10331,7 @@
         <v>2026</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D175">
         <v>249</v>
@@ -10445,7 +10366,7 @@
         <v>2026</v>
       </c>
       <c r="C176" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D176">
         <v>266</v>
@@ -10472,7 +10393,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>53</v>
       </c>
@@ -10480,7 +10401,7 @@
         <v>2026</v>
       </c>
       <c r="C177" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D177">
         <v>268</v>
@@ -10507,7 +10428,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>53</v>
       </c>
@@ -10515,7 +10436,7 @@
         <v>2026</v>
       </c>
       <c r="C178" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D178">
         <v>155</v>
@@ -10542,7 +10463,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>54</v>
       </c>
@@ -10550,7 +10471,7 @@
         <v>2025</v>
       </c>
       <c r="C179" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D179">
         <v>1154</v>
@@ -10576,8 +10497,9 @@
       <c r="K179">
         <v>0.49</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O179" s="11"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>54</v>
       </c>
@@ -10585,7 +10507,7 @@
         <v>2025</v>
       </c>
       <c r="C180" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D180">
         <v>1318</v>
@@ -10612,7 +10534,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>54</v>
       </c>
@@ -10620,7 +10542,7 @@
         <v>2025</v>
       </c>
       <c r="C181" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D181">
         <v>1115</v>
@@ -10647,7 +10569,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>54</v>
       </c>
@@ -10655,7 +10577,7 @@
         <v>2025</v>
       </c>
       <c r="C182" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D182">
         <v>1177</v>
@@ -10682,7 +10604,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>54</v>
       </c>
@@ -10690,7 +10612,7 @@
         <v>2025</v>
       </c>
       <c r="C183" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D183">
         <v>1634</v>
@@ -10717,7 +10639,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>54</v>
       </c>
@@ -10725,7 +10647,7 @@
         <v>2025</v>
       </c>
       <c r="C184" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D184">
         <v>1345</v>
@@ -10752,7 +10674,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>54</v>
       </c>
@@ -10760,7 +10682,7 @@
         <v>2025</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D185">
         <v>1465</v>
@@ -10787,7 +10709,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>54</v>
       </c>
@@ -10795,7 +10717,7 @@
         <v>2025</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D186">
         <v>1366</v>
@@ -10822,7 +10744,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>54</v>
       </c>
@@ -10830,7 +10752,7 @@
         <v>2025</v>
       </c>
       <c r="C187" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D187">
         <v>1346</v>
@@ -10857,7 +10779,7 @@
         <v>-0.53</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>54</v>
       </c>
@@ -10865,7 +10787,7 @@
         <v>2025</v>
       </c>
       <c r="C188" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D188">
         <v>1341</v>
@@ -10892,7 +10814,7 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>54</v>
       </c>
@@ -10900,7 +10822,7 @@
         <v>2025</v>
       </c>
       <c r="C189" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D189">
         <v>728</v>
@@ -10927,7 +10849,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>54</v>
       </c>
@@ -10935,7 +10857,7 @@
         <v>2025</v>
       </c>
       <c r="C190" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D190">
         <v>736</v>
@@ -10962,7 +10884,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>54</v>
       </c>
@@ -10970,7 +10892,7 @@
         <v>2026</v>
       </c>
       <c r="C191" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D191">
         <v>643</v>
@@ -10997,7 +10919,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>54</v>
       </c>
@@ -11005,7 +10927,7 @@
         <v>2026</v>
       </c>
       <c r="C192" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D192">
         <v>1049</v>
@@ -11040,7 +10962,7 @@
         <v>2026</v>
       </c>
       <c r="C193" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D193">
         <v>1167</v>
@@ -11075,7 +10997,7 @@
         <v>2026</v>
       </c>
       <c r="C194" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D194">
         <v>733</v>
@@ -11110,7 +11032,7 @@
         <v>2025</v>
       </c>
       <c r="C195" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D195">
         <v>1121</v>
@@ -11145,7 +11067,7 @@
         <v>2025</v>
       </c>
       <c r="C196" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D196">
         <v>1446</v>
@@ -11180,7 +11102,7 @@
         <v>2025</v>
       </c>
       <c r="C197" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D197">
         <v>1051</v>
@@ -11215,7 +11137,7 @@
         <v>2025</v>
       </c>
       <c r="C198" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D198">
         <v>991</v>
@@ -11250,7 +11172,7 @@
         <v>2025</v>
       </c>
       <c r="C199" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D199">
         <v>1050</v>
@@ -11285,7 +11207,7 @@
         <v>2025</v>
       </c>
       <c r="C200" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D200">
         <v>1299</v>
@@ -11320,7 +11242,7 @@
         <v>2025</v>
       </c>
       <c r="C201" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D201">
         <v>1288</v>
@@ -11355,7 +11277,7 @@
         <v>2025</v>
       </c>
       <c r="C202" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D202">
         <v>1381</v>
@@ -11390,7 +11312,7 @@
         <v>2025</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D203">
         <v>1412</v>
@@ -11425,7 +11347,7 @@
         <v>2025</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D204">
         <v>1092</v>
@@ -11460,7 +11382,7 @@
         <v>2025</v>
       </c>
       <c r="C205" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D205">
         <v>1226</v>
@@ -11495,7 +11417,7 @@
         <v>2025</v>
       </c>
       <c r="C206" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D206">
         <v>715</v>
@@ -11530,7 +11452,7 @@
         <v>2026</v>
       </c>
       <c r="C207" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D207">
         <v>1338</v>
@@ -11565,7 +11487,7 @@
         <v>2026</v>
       </c>
       <c r="C208" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D208">
         <v>1332</v>
@@ -11600,7 +11522,7 @@
         <v>2026</v>
       </c>
       <c r="C209" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D209">
         <v>1440</v>
@@ -11635,7 +11557,7 @@
         <v>2026</v>
       </c>
       <c r="C210" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D210">
         <v>692</v>
@@ -11670,7 +11592,7 @@
         <v>2025</v>
       </c>
       <c r="C211" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D211">
         <v>2628</v>
@@ -11705,7 +11627,7 @@
         <v>2025</v>
       </c>
       <c r="C212" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D212">
         <v>2305</v>
@@ -11740,7 +11662,7 @@
         <v>2025</v>
       </c>
       <c r="C213" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D213">
         <v>1999</v>
@@ -11775,7 +11697,7 @@
         <v>2025</v>
       </c>
       <c r="C214" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D214">
         <v>1499</v>
@@ -11810,7 +11732,7 @@
         <v>2025</v>
       </c>
       <c r="C215" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D215">
         <v>792</v>
@@ -11845,7 +11767,7 @@
         <v>2025</v>
       </c>
       <c r="C216" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D216">
         <v>471</v>
@@ -11880,7 +11802,7 @@
         <v>2025</v>
       </c>
       <c r="C217" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D217">
         <v>2036</v>
@@ -11915,7 +11837,7 @@
         <v>2025</v>
       </c>
       <c r="C218" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D218">
         <v>1853</v>
@@ -11950,7 +11872,7 @@
         <v>2025</v>
       </c>
       <c r="C219" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D219">
         <v>1592</v>
@@ -11985,7 +11907,7 @@
         <v>2025</v>
       </c>
       <c r="C220" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D220">
         <v>1752</v>
@@ -12020,7 +11942,7 @@
         <v>2025</v>
       </c>
       <c r="C221" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D221">
         <v>1795</v>
@@ -12055,7 +11977,7 @@
         <v>2025</v>
       </c>
       <c r="C222" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D222">
         <v>1735</v>
@@ -12090,7 +12012,7 @@
         <v>2026</v>
       </c>
       <c r="C223" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D223">
         <v>2434</v>
@@ -12125,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="C224" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D224">
         <v>2158</v>
@@ -12160,7 +12082,7 @@
         <v>2026</v>
       </c>
       <c r="C225" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D225">
         <v>2242</v>
@@ -12195,7 +12117,7 @@
         <v>2026</v>
       </c>
       <c r="C226" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D226">
         <v>1621</v>
@@ -12230,7 +12152,7 @@
         <v>2025</v>
       </c>
       <c r="C227" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D227">
         <v>7951</v>
@@ -12250,7 +12172,7 @@
         <v>2025</v>
       </c>
       <c r="C228" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D228">
         <v>6531</v>
@@ -12285,7 +12207,7 @@
         <v>2025</v>
       </c>
       <c r="C229" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D229">
         <v>5116</v>
@@ -12320,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="C230" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D230">
         <v>6193</v>
@@ -12355,7 +12277,7 @@
         <v>2026</v>
       </c>
       <c r="C231" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D231">
         <v>6040</v>
@@ -12390,7 +12312,7 @@
         <v>2026</v>
       </c>
       <c r="C232" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D232">
         <v>4717</v>
@@ -12425,7 +12347,7 @@
         <v>2026</v>
       </c>
       <c r="C233" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D233">
         <v>2918</v>
@@ -12460,7 +12382,7 @@
         <v>2025</v>
       </c>
       <c r="C234" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D234">
         <v>10540</v>
@@ -12495,7 +12417,7 @@
         <v>2025</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D235">
         <v>7316</v>
@@ -12530,7 +12452,7 @@
         <v>2025</v>
       </c>
       <c r="C236" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D236">
         <v>5323</v>
@@ -12565,7 +12487,7 @@
         <v>2026</v>
       </c>
       <c r="C237" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D237">
         <v>6542</v>
@@ -12600,7 +12522,7 @@
         <v>2026</v>
       </c>
       <c r="C238" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D238">
         <v>6331</v>
@@ -12635,7 +12557,7 @@
         <v>2026</v>
       </c>
       <c r="C239" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D239">
         <v>6674</v>
@@ -12670,7 +12592,7 @@
         <v>2026</v>
       </c>
       <c r="C240" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D240">
         <v>5251</v>
@@ -12699,13 +12621,13 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B241">
         <v>2025</v>
       </c>
       <c r="C241" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D241">
         <v>6306</v>
@@ -12725,7 +12647,7 @@
         <v>2025</v>
       </c>
       <c r="C242" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D242">
         <v>3097</v>
@@ -12760,7 +12682,7 @@
         <v>2025</v>
       </c>
       <c r="C243" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D243">
         <v>3595</v>
@@ -12795,7 +12717,7 @@
         <v>2025</v>
       </c>
       <c r="C244" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D244">
         <v>3503</v>
@@ -12830,7 +12752,7 @@
         <v>2025</v>
       </c>
       <c r="C245" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D245">
         <v>3152</v>
@@ -12865,7 +12787,7 @@
         <v>2025</v>
       </c>
       <c r="C246" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D246">
         <v>3158</v>
@@ -12900,7 +12822,7 @@
         <v>2025</v>
       </c>
       <c r="C247" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D247">
         <v>3243</v>
@@ -12935,7 +12857,7 @@
         <v>2025</v>
       </c>
       <c r="C248" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D248">
         <v>2111</v>
@@ -12970,7 +12892,7 @@
         <v>2025</v>
       </c>
       <c r="C249" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D249">
         <v>2109</v>
@@ -13005,7 +12927,7 @@
         <v>2025</v>
       </c>
       <c r="C250" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D250">
         <v>1494</v>
@@ -13040,7 +12962,7 @@
         <v>2025</v>
       </c>
       <c r="C251" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D251">
         <v>1703</v>
@@ -13075,7 +12997,7 @@
         <v>2025</v>
       </c>
       <c r="C252" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D252">
         <v>1519</v>
@@ -13110,7 +13032,7 @@
         <v>2025</v>
       </c>
       <c r="C253" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D253">
         <v>1902</v>
@@ -13145,7 +13067,7 @@
         <v>2026</v>
       </c>
       <c r="C254" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D254">
         <v>3204</v>
@@ -13180,7 +13102,7 @@
         <v>2026</v>
       </c>
       <c r="C255" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D255">
         <v>2906</v>
@@ -13215,7 +13137,7 @@
         <v>2026</v>
       </c>
       <c r="C256" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D256">
         <v>2773</v>
@@ -13250,7 +13172,7 @@
         <v>2026</v>
       </c>
       <c r="C257" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D257">
         <v>1958</v>
@@ -13285,7 +13207,7 @@
         <v>2025</v>
       </c>
       <c r="C258" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D258">
         <v>285</v>
@@ -13305,7 +13227,7 @@
         <v>2025</v>
       </c>
       <c r="C259" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D259">
         <v>539</v>
@@ -13340,7 +13262,7 @@
         <v>2026</v>
       </c>
       <c r="C260" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D260">
         <v>546</v>
@@ -13375,7 +13297,7 @@
         <v>2026</v>
       </c>
       <c r="C261" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D261">
         <v>568</v>
@@ -13410,7 +13332,7 @@
         <v>2026</v>
       </c>
       <c r="C262" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D262">
         <v>711</v>
@@ -13445,7 +13367,7 @@
         <v>2026</v>
       </c>
       <c r="C263" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D263">
         <v>460</v>
@@ -13480,7 +13402,7 @@
         <v>2025</v>
       </c>
       <c r="C264" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D264">
         <v>1279</v>
@@ -13515,7 +13437,7 @@
         <v>2025</v>
       </c>
       <c r="C265" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D265">
         <v>1343</v>
@@ -13550,7 +13472,7 @@
         <v>2025</v>
       </c>
       <c r="C266" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D266">
         <v>986</v>
@@ -13585,7 +13507,7 @@
         <v>2025</v>
       </c>
       <c r="C267" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D267">
         <v>1032</v>
@@ -13620,7 +13542,7 @@
         <v>2025</v>
       </c>
       <c r="C268" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D268">
         <v>1399</v>
@@ -13655,7 +13577,7 @@
         <v>2025</v>
       </c>
       <c r="C269" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D269">
         <v>1186</v>
@@ -13690,7 +13612,7 @@
         <v>2025</v>
       </c>
       <c r="C270" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D270">
         <v>1647</v>
@@ -13725,7 +13647,7 @@
         <v>2025</v>
       </c>
       <c r="C271" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D271">
         <v>1846</v>
@@ -13760,7 +13682,7 @@
         <v>2025</v>
       </c>
       <c r="C272" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D272">
         <v>1506</v>
@@ -13795,7 +13717,7 @@
         <v>2025</v>
       </c>
       <c r="C273" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D273">
         <v>1305</v>
@@ -13830,7 +13752,7 @@
         <v>2025</v>
       </c>
       <c r="C274" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D274">
         <v>1379</v>
@@ -13865,7 +13787,7 @@
         <v>2025</v>
       </c>
       <c r="C275" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D275">
         <v>1592</v>
@@ -13900,7 +13822,7 @@
         <v>2026</v>
       </c>
       <c r="C276" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D276">
         <v>1861</v>
@@ -13935,7 +13857,7 @@
         <v>2026</v>
       </c>
       <c r="C277" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D277">
         <v>1516</v>
@@ -13970,7 +13892,7 @@
         <v>2026</v>
       </c>
       <c r="C278" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D278">
         <v>1685</v>
@@ -14005,7 +13927,7 @@
         <v>2026</v>
       </c>
       <c r="C279" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D279">
         <v>1027</v>
@@ -14040,7 +13962,7 @@
         <v>2025</v>
       </c>
       <c r="C280" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D280">
         <v>430</v>
@@ -14072,7 +13994,7 @@
         <v>2025</v>
       </c>
       <c r="C281" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D281">
         <v>640</v>
@@ -14104,7 +14026,7 @@
         <v>2025</v>
       </c>
       <c r="C282" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D282">
         <v>1058</v>
@@ -14136,7 +14058,7 @@
         <v>2026</v>
       </c>
       <c r="C283" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D283">
         <v>545</v>
@@ -14168,7 +14090,7 @@
         <v>2026</v>
       </c>
       <c r="C284" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D284">
         <v>575</v>
@@ -14200,7 +14122,7 @@
         <v>2026</v>
       </c>
       <c r="C285" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D285">
         <v>1193</v>
@@ -14232,7 +14154,7 @@
         <v>2026</v>
       </c>
       <c r="C286" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D286">
         <v>887</v>
@@ -14264,7 +14186,7 @@
         <v>2025</v>
       </c>
       <c r="C287" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D287">
         <v>1120</v>
@@ -14299,7 +14221,7 @@
         <v>2025</v>
       </c>
       <c r="C288" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D288">
         <v>1428</v>
@@ -14334,7 +14256,7 @@
         <v>2025</v>
       </c>
       <c r="C289" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D289">
         <v>1375</v>
@@ -14369,7 +14291,7 @@
         <v>2025</v>
       </c>
       <c r="C290" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D290">
         <v>1013</v>
@@ -14404,7 +14326,7 @@
         <v>2025</v>
       </c>
       <c r="C291" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D291">
         <v>1203</v>
@@ -14439,7 +14361,7 @@
         <v>2025</v>
       </c>
       <c r="C292" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D292">
         <v>1039</v>
@@ -14474,7 +14396,7 @@
         <v>2025</v>
       </c>
       <c r="C293" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D293">
         <v>1570</v>
@@ -14509,7 +14431,7 @@
         <v>2025</v>
       </c>
       <c r="C294" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D294">
         <v>1875</v>
@@ -14544,7 +14466,7 @@
         <v>2025</v>
       </c>
       <c r="C295" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D295">
         <v>1869</v>
@@ -14579,7 +14501,7 @@
         <v>2025</v>
       </c>
       <c r="C296" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D296">
         <v>1542</v>
@@ -14614,7 +14536,7 @@
         <v>2025</v>
       </c>
       <c r="C297" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D297">
         <v>1232</v>
@@ -14649,7 +14571,7 @@
         <v>2025</v>
       </c>
       <c r="C298" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D298">
         <v>1254</v>
@@ -14684,7 +14606,7 @@
         <v>2026</v>
       </c>
       <c r="C299" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D299">
         <v>1456</v>
@@ -14719,7 +14641,7 @@
         <v>2026</v>
       </c>
       <c r="C300" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D300">
         <v>1682</v>
@@ -14754,7 +14676,7 @@
         <v>2026</v>
       </c>
       <c r="C301" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D301">
         <v>1622</v>
@@ -14789,7 +14711,7 @@
         <v>2026</v>
       </c>
       <c r="C302" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D302">
         <v>1198</v>
@@ -14818,13 +14740,13 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="B303">
         <v>2026</v>
       </c>
       <c r="C303" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D303">
         <v>75</v>
@@ -14838,13 +14760,13 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="B304">
         <v>2026</v>
       </c>
       <c r="C304" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D304">
         <v>130</v>
@@ -14864,7 +14786,7 @@
         <v>2025</v>
       </c>
       <c r="C305" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D305">
         <v>782</v>
@@ -14899,7 +14821,7 @@
         <v>2025</v>
       </c>
       <c r="C306" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D306">
         <v>799</v>
@@ -14934,7 +14856,7 @@
         <v>2025</v>
       </c>
       <c r="C307" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D307">
         <v>715</v>
@@ -14969,7 +14891,7 @@
         <v>2025</v>
       </c>
       <c r="C308" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D308">
         <v>437</v>
@@ -15004,7 +14926,7 @@
         <v>2025</v>
       </c>
       <c r="C309" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="D309">
         <v>482</v>
@@ -15039,7 +14961,7 @@
         <v>2025</v>
       </c>
       <c r="C310" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D310">
         <v>596</v>
@@ -15074,7 +14996,7 @@
         <v>2025</v>
       </c>
       <c r="C311" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D311">
         <v>608</v>
@@ -15109,7 +15031,7 @@
         <v>2025</v>
       </c>
       <c r="C312" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="D312">
         <v>631</v>
@@ -15144,7 +15066,7 @@
         <v>2025</v>
       </c>
       <c r="C313" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="D313">
         <v>709</v>
@@ -15179,7 +15101,7 @@
         <v>2025</v>
       </c>
       <c r="C314" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D314">
         <v>558</v>
@@ -15214,7 +15136,7 @@
         <v>2025</v>
       </c>
       <c r="C315" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="D315">
         <v>487</v>
@@ -15249,7 +15171,7 @@
         <v>2025</v>
       </c>
       <c r="C316" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D316">
         <v>615</v>
@@ -15284,7 +15206,7 @@
         <v>2026</v>
       </c>
       <c r="C317" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="D317">
         <v>512</v>
@@ -15319,7 +15241,7 @@
         <v>2026</v>
       </c>
       <c r="C318" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D318">
         <v>450</v>
@@ -15354,7 +15276,7 @@
         <v>2026</v>
       </c>
       <c r="C319" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D319">
         <v>675</v>
@@ -15389,7 +15311,7 @@
         <v>2026</v>
       </c>
       <c r="C320" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="D320">
         <v>429</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FF8EEE-BFC2-451C-A7D4-C7F7F960515E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB81697-4EFF-446C-BFDC-6757926E5940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -1128,92 +1128,92 @@
     </row>
     <row r="7" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="5">
-        <v>22.96</v>
+        <v>207.35</v>
       </c>
       <c r="C7" s="5">
-        <v>9.99</v>
+        <v>109.6</v>
       </c>
       <c r="D7" s="5">
-        <v>12.97</v>
+        <v>97.75</v>
       </c>
       <c r="E7" s="5">
-        <v>6000.94</v>
+        <v>3818.18</v>
       </c>
       <c r="F7" s="5">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="G7" s="5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H7" s="5">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="I7" s="5">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="J7" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K7" s="5">
-        <v>461.61076923076899</v>
+        <v>33.201565217391298</v>
       </c>
       <c r="L7" s="5">
-        <v>1000.15666666666</v>
+        <v>76.363599999999906</v>
       </c>
       <c r="M7" s="5">
-        <v>162.720173839431</v>
+        <v>3858.60462314505</v>
       </c>
       <c r="N7" s="6">
-        <v>12</v>
+        <v>145.84</v>
       </c>
       <c r="O7" s="6">
-        <v>1912.57</v>
+        <v>8075.64</v>
       </c>
       <c r="P7" s="6">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="Q7" s="6">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="R7" s="6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S7" s="6">
-        <v>212.50777777777699</v>
+        <v>32.694898785425103</v>
       </c>
       <c r="T7" s="6">
-        <v>637.52333333333297</v>
+        <v>164.80897959183599</v>
       </c>
       <c r="U7" s="6">
-        <v>-100</v>
+        <v>1477.67780634104</v>
       </c>
       <c r="V7" s="7">
-        <v>13</v>
+        <v>180.34</v>
       </c>
       <c r="W7" s="7">
-        <v>2836.17</v>
+        <v>11126.61</v>
       </c>
       <c r="X7" s="7">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="Y7" s="7">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="Z7" s="7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="AC7" s="9">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="AD7" s="9">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="AE7" s="14">
         <v>46135</v>
@@ -1221,94 +1221,94 @@
     </row>
     <row r="8" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="5">
-        <v>127.87</v>
+        <v>22.96</v>
       </c>
       <c r="C8" s="5">
-        <v>75.489999999999995</v>
+        <v>9.99</v>
       </c>
       <c r="D8" s="5">
-        <v>52.38</v>
+        <v>12.97</v>
       </c>
       <c r="E8" s="5">
-        <v>30008.78</v>
+        <v>6000.94</v>
       </c>
       <c r="F8" s="5">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G8" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I8" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J8" s="5">
         <v>2</v>
       </c>
       <c r="K8" s="5">
-        <v>666.86177777777698</v>
+        <v>461.61076923076899</v>
       </c>
       <c r="L8" s="5">
-        <v>2500.7316666666602</v>
+        <v>1000.15666666666</v>
       </c>
       <c r="M8" s="5">
-        <v>-47.065092282991799</v>
+        <v>162.720173839431</v>
       </c>
       <c r="N8" s="6">
-        <v>21.65</v>
+        <v>12</v>
       </c>
       <c r="O8" s="6">
-        <v>4893.6099999999997</v>
+        <v>1912.57</v>
       </c>
       <c r="P8" s="6">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="Q8" s="6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="R8" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>80.223114754098305</v>
+        <v>212.50777777777699</v>
       </c>
       <c r="T8" s="6">
-        <v>203.90041666666599</v>
+        <v>637.52333333333297</v>
       </c>
       <c r="U8" s="6">
-        <v>1212.6936964735601</v>
+        <v>-100</v>
       </c>
       <c r="V8" s="7">
-        <v>26.65</v>
+        <v>13</v>
       </c>
       <c r="W8" s="7">
-        <v>6253.57</v>
+        <v>2836.17</v>
       </c>
       <c r="X8" s="7">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="7">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="8">
         <v>8000</v>
       </c>
       <c r="AB8" s="8">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="AC8" s="9">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="AD8" s="9">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AE8" s="14">
         <v>46135</v>
@@ -1316,54 +1316,102 @@
     </row>
     <row r="9" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="B9" s="5">
+        <v>127.87</v>
+      </c>
+      <c r="C9" s="5">
+        <v>75.489999999999995</v>
+      </c>
+      <c r="D9" s="5">
+        <v>52.38</v>
+      </c>
+      <c r="E9" s="5">
+        <v>30008.78</v>
+      </c>
+      <c r="F9" s="5">
+        <v>45</v>
+      </c>
+      <c r="G9" s="5">
+        <v>9</v>
+      </c>
+      <c r="H9" s="5">
+        <v>36</v>
+      </c>
+      <c r="I9" s="5">
+        <v>12</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>666.86177777777698</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2500.7316666666602</v>
+      </c>
+      <c r="M9" s="5">
+        <v>-47.065092282991799</v>
+      </c>
       <c r="N9" s="6">
-        <v>21.07</v>
+        <v>21.65</v>
       </c>
       <c r="O9" s="6">
-        <v>13974.49</v>
-      </c>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
+        <v>4893.6099999999997</v>
+      </c>
+      <c r="P9" s="6">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>24</v>
+      </c>
+      <c r="R9" s="6">
+        <v>9</v>
+      </c>
+      <c r="S9" s="6">
+        <v>80.223114754098305</v>
+      </c>
+      <c r="T9" s="6">
+        <v>203.90041666666599</v>
+      </c>
+      <c r="U9" s="6">
+        <v>1212.6936964735601</v>
+      </c>
       <c r="V9" s="7">
-        <v>29.05</v>
+        <v>26.65</v>
       </c>
       <c r="W9" s="7">
-        <v>18828.98</v>
-      </c>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
+        <v>6253.57</v>
+      </c>
+      <c r="X9" s="7">
+        <v>83</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>31</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>9</v>
+      </c>
       <c r="AA9" s="8">
         <v>40000</v>
       </c>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
+      <c r="AB9" s="8">
+        <v>40000</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>62</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>30</v>
+      </c>
       <c r="AE9" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1378,44 +1426,26 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="6">
-        <v>31.67</v>
+        <v>21.07</v>
       </c>
       <c r="O10" s="6">
-        <v>3708.91</v>
-      </c>
-      <c r="P10" s="6">
-        <v>13</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>3</v>
-      </c>
-      <c r="R10" s="6">
-        <v>1</v>
-      </c>
-      <c r="S10" s="6">
-        <v>285.30076923076899</v>
-      </c>
-      <c r="T10" s="6">
-        <v>1236.3033333333301</v>
-      </c>
-      <c r="U10" s="6">
-        <v>49.477878945566196</v>
-      </c>
+        <v>13974.49</v>
+      </c>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
       <c r="V10" s="7">
-        <v>73.209999999999994</v>
+        <v>29.05</v>
       </c>
       <c r="W10" s="7">
-        <v>6655.75</v>
-      </c>
-      <c r="X10" s="7">
-        <v>18</v>
-      </c>
-      <c r="Y10" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="7">
-        <v>1</v>
-      </c>
+        <v>18828.98</v>
+      </c>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
       <c r="AC10" s="9"/>
@@ -1426,7 +1456,7 @@
     </row>
     <row r="11" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1441,13 +1471,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>3.98</v>
+        <v>31.67</v>
       </c>
       <c r="O11" s="6">
-        <v>581.29999999999995</v>
+        <v>3708.91</v>
       </c>
       <c r="P11" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="6">
         <v>3</v>
@@ -1456,25 +1486,25 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>36.331249999999997</v>
+        <v>285.30076923076899</v>
       </c>
       <c r="T11" s="6">
-        <v>193.766666666666</v>
+        <v>1236.3033333333301</v>
       </c>
       <c r="U11" s="6">
-        <v>1062.4118355410201</v>
+        <v>49.477878945566196</v>
       </c>
       <c r="V11" s="7">
-        <v>5.98</v>
+        <v>73.209999999999994</v>
       </c>
       <c r="W11" s="7">
-        <v>833.66</v>
+        <v>6655.75</v>
       </c>
       <c r="X11" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y11" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11" s="7">
         <v>1</v>
@@ -1489,7 +1519,7 @@
     </row>
     <row r="12" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1504,26 +1534,44 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="6">
-        <v>7.0299999999999896</v>
+        <v>3.98</v>
       </c>
       <c r="O12" s="6">
-        <v>3947.21</v>
-      </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
+        <v>581.29999999999995</v>
+      </c>
+      <c r="P12" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>3</v>
+      </c>
+      <c r="R12" s="6">
+        <v>1</v>
+      </c>
+      <c r="S12" s="6">
+        <v>36.331249999999997</v>
+      </c>
+      <c r="T12" s="6">
+        <v>193.766666666666</v>
+      </c>
+      <c r="U12" s="6">
+        <v>1062.4118355410201</v>
+      </c>
       <c r="V12" s="7">
-        <v>10.02</v>
+        <v>5.98</v>
       </c>
       <c r="W12" s="7">
-        <v>5445.86</v>
-      </c>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
+        <v>833.66</v>
+      </c>
+      <c r="X12" s="7">
+        <v>20</v>
+      </c>
+      <c r="Y12" s="7">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="7">
+        <v>1</v>
+      </c>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
       <c r="AC12" s="9"/>
@@ -1534,7 +1582,7 @@
     </row>
     <row r="13" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1549,10 +1597,10 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="6">
-        <v>14</v>
+        <v>7.0299999999999896</v>
       </c>
       <c r="O13" s="6">
-        <v>683.33</v>
+        <v>3947.21</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -1561,10 +1609,10 @@
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="7">
-        <v>16</v>
+        <v>10.02</v>
       </c>
       <c r="W13" s="7">
-        <v>1036.27</v>
+        <v>5445.86</v>
       </c>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
@@ -1579,20 +1627,12 @@
     </row>
     <row r="14" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1226.8599999999999</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1602,48 +1642,28 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O14" s="6">
-        <v>337.3</v>
-      </c>
-      <c r="P14" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>1</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <v>112.433333333333</v>
-      </c>
-      <c r="T14" s="6">
-        <v>337.3</v>
-      </c>
-      <c r="U14" s="6">
-        <v>-100</v>
-      </c>
+        <v>683.33</v>
+      </c>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
       <c r="V14" s="7">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="W14" s="7">
-        <v>422.36</v>
-      </c>
-      <c r="X14" s="7">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="7">
-        <v>2</v>
-      </c>
-      <c r="Z14" s="7">
-        <v>0</v>
-      </c>
+        <v>1036.27</v>
+      </c>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
       <c r="AA14" s="8"/>
-      <c r="AB14" s="8">
-        <v>4000</v>
-      </c>
+      <c r="AB14" s="8"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
       <c r="AE14" s="14">
@@ -1652,79 +1672,63 @@
     </row>
     <row r="15" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5">
-        <v>49.03</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5">
-        <v>32.03</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5">
-        <v>13330.8</v>
-      </c>
-      <c r="F15" s="5">
-        <v>32</v>
-      </c>
-      <c r="G15" s="5">
-        <v>6</v>
-      </c>
-      <c r="H15" s="5">
-        <v>26</v>
-      </c>
-      <c r="I15" s="5">
-        <v>10</v>
-      </c>
-      <c r="J15" s="5">
-        <v>4</v>
-      </c>
-      <c r="K15" s="5">
-        <v>416.58749999999998</v>
-      </c>
-      <c r="L15" s="5">
-        <v>1333.08</v>
-      </c>
-      <c r="M15" s="5">
-        <v>102.966063552074</v>
-      </c>
+        <v>1226.8599999999999</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
       <c r="N15" s="6">
-        <v>48.99</v>
+        <v>2</v>
       </c>
       <c r="O15" s="6">
-        <v>11556.93</v>
+        <v>337.3</v>
       </c>
       <c r="P15" s="6">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R15" s="6">
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>195.88016949152501</v>
+        <v>112.433333333333</v>
       </c>
       <c r="T15" s="6">
-        <v>550.33000000000004</v>
+        <v>337.3</v>
       </c>
       <c r="U15" s="6">
         <v>-100</v>
       </c>
       <c r="V15" s="7">
-        <v>61.03</v>
+        <v>3</v>
       </c>
       <c r="W15" s="7">
-        <v>15298.11</v>
+        <v>422.36</v>
       </c>
       <c r="X15" s="7">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="7">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="7">
         <v>0</v>
@@ -1733,86 +1737,112 @@
         <v>4000</v>
       </c>
       <c r="AB15" s="8">
-        <v>24000</v>
-      </c>
-      <c r="AC15" s="9">
-        <v>44</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>20</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
       <c r="AE15" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="B16" s="5">
+        <v>49.03</v>
+      </c>
+      <c r="C16" s="5">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5">
+        <v>32.03</v>
+      </c>
+      <c r="E16" s="5">
+        <v>13330.8</v>
+      </c>
+      <c r="F16" s="5">
+        <v>32</v>
+      </c>
+      <c r="G16" s="5">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5">
+        <v>26</v>
+      </c>
+      <c r="I16" s="5">
+        <v>10</v>
+      </c>
+      <c r="J16" s="5">
+        <v>4</v>
+      </c>
+      <c r="K16" s="5">
+        <v>416.58749999999998</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1333.08</v>
+      </c>
+      <c r="M16" s="5">
+        <v>102.966063552074</v>
+      </c>
       <c r="N16" s="6">
-        <v>25</v>
+        <v>48.99</v>
       </c>
       <c r="O16" s="6">
-        <v>2222.02</v>
+        <v>11556.93</v>
       </c>
       <c r="P16" s="6">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="6">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R16" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>130.707058823529</v>
+        <v>195.88016949152501</v>
       </c>
       <c r="T16" s="6">
-        <v>370.33666666666602</v>
+        <v>550.33000000000004</v>
       </c>
       <c r="U16" s="6">
-        <v>536.31290447430695</v>
+        <v>-100</v>
       </c>
       <c r="V16" s="7">
-        <v>54</v>
+        <v>61.03</v>
       </c>
       <c r="W16" s="7">
-        <v>5213.1000000000004</v>
+        <v>15298.11</v>
       </c>
       <c r="X16" s="7">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="Y16" s="7">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Z16" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="8">
         <v>24000</v>
       </c>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
+      <c r="AB16" s="8">
+        <v>24000</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>44</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>20</v>
+      </c>
       <c r="AE16" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1827,61 +1857,55 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O17" s="6">
-        <v>1139.6300000000001</v>
+        <v>2222.02</v>
       </c>
       <c r="P17" s="6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" s="6">
-        <v>113.96299999999999</v>
+        <v>130.707058823529</v>
       </c>
       <c r="T17" s="6">
-        <v>227.92599999999999</v>
+        <v>370.33666666666602</v>
       </c>
       <c r="U17" s="6">
-        <v>651.73521230574795</v>
+        <v>536.31290447430695</v>
       </c>
       <c r="V17" s="7">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="W17" s="7">
-        <v>1552.36</v>
+        <v>5213.1000000000004</v>
       </c>
       <c r="X17" s="7">
+        <v>26</v>
+      </c>
+      <c r="Y17" s="7">
         <v>11</v>
       </c>
-      <c r="Y17" s="7">
-        <v>7</v>
-      </c>
       <c r="Z17" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="8"/>
-      <c r="AB17" s="8">
-        <v>7000</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>7</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>3</v>
-      </c>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
       <c r="AE17" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1896,39 +1920,63 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O18" s="6">
-        <v>515.46</v>
-      </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
+        <v>1139.6300000000001</v>
+      </c>
+      <c r="P18" s="6">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>5</v>
+      </c>
+      <c r="R18" s="6">
+        <v>1</v>
+      </c>
+      <c r="S18" s="6">
+        <v>113.96299999999999</v>
+      </c>
+      <c r="T18" s="6">
+        <v>227.92599999999999</v>
+      </c>
+      <c r="U18" s="6">
+        <v>651.73521230574795</v>
+      </c>
       <c r="V18" s="7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W18" s="7">
-        <v>912.36</v>
-      </c>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
+        <v>1552.36</v>
+      </c>
+      <c r="X18" s="7">
+        <v>11</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>1</v>
+      </c>
       <c r="AA18" s="8">
         <v>7000</v>
       </c>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
+      <c r="AB18" s="8">
+        <v>7000</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>7</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>3</v>
+      </c>
       <c r="AE18" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1943,10 +1991,10 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O19" s="6">
-        <v>2718.41</v>
+        <v>515.46</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -1955,115 +2003,113 @@
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W19" s="7">
-        <v>3696.93</v>
+        <v>912.36</v>
       </c>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
       <c r="AA19" s="8"/>
-      <c r="AB19" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="9">
-        <v>3</v>
-      </c>
-      <c r="AD19" s="9">
-        <v>3</v>
-      </c>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
       <c r="AE19" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="5">
-        <v>76.430000000000007</v>
-      </c>
-      <c r="C20" s="5">
-        <v>30.32</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46.11</v>
-      </c>
-      <c r="E20" s="5">
-        <v>17125.759999999998</v>
-      </c>
-      <c r="F20" s="5">
-        <v>46</v>
-      </c>
-      <c r="G20" s="5">
-        <v>5</v>
-      </c>
-      <c r="H20" s="5">
-        <v>41</v>
-      </c>
-      <c r="I20" s="5">
-        <v>22</v>
-      </c>
-      <c r="J20" s="5">
-        <v>5</v>
-      </c>
-      <c r="K20" s="5">
-        <v>372.299130434782</v>
-      </c>
-      <c r="L20" s="5">
-        <v>778.44363636363596</v>
-      </c>
-      <c r="M20" s="5">
-        <v>86.657760005979299</v>
-      </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6">
+        <v>9</v>
+      </c>
+      <c r="O20" s="6">
+        <v>2718.41</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
+      <c r="V20" s="7">
+        <v>15</v>
+      </c>
+      <c r="W20" s="7">
+        <v>3696.93</v>
+      </c>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8">
-        <v>22000</v>
-      </c>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="9">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="9">
+        <v>3</v>
+      </c>
       <c r="AE20" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5">
-        <v>3</v>
+        <v>76.430000000000007</v>
       </c>
       <c r="C21" s="5">
-        <v>1</v>
+        <v>30.32</v>
       </c>
       <c r="D21" s="5">
-        <v>2</v>
+        <v>46.11</v>
       </c>
       <c r="E21" s="5">
-        <v>2336.48</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+        <v>17125.759999999998</v>
+      </c>
+      <c r="F21" s="5">
+        <v>46</v>
+      </c>
+      <c r="G21" s="5">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5">
+        <v>41</v>
+      </c>
+      <c r="I21" s="5">
+        <v>22</v>
+      </c>
+      <c r="J21" s="5">
+        <v>5</v>
+      </c>
+      <c r="K21" s="5">
+        <v>372.299130434782</v>
+      </c>
+      <c r="L21" s="5">
+        <v>778.44363636363596</v>
+      </c>
+      <c r="M21" s="5">
+        <v>86.657760005979299</v>
+      </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
@@ -2079,7 +2125,7 @@
       <c r="Z21" s="7"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
@@ -2089,44 +2135,28 @@
     </row>
     <row r="22" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5">
-        <v>128.36000000000001</v>
+        <v>3</v>
       </c>
       <c r="C22" s="5">
-        <v>120.36</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5">
-        <v>27929.69</v>
-      </c>
-      <c r="F22" s="5">
-        <v>13</v>
-      </c>
-      <c r="G22" s="5">
-        <v>8</v>
-      </c>
-      <c r="H22" s="5">
-        <v>5</v>
-      </c>
-      <c r="I22" s="5">
-        <v>3</v>
-      </c>
-      <c r="J22" s="5">
-        <v>2</v>
-      </c>
-      <c r="K22" s="5">
-        <v>2148.4376923076902</v>
-      </c>
-      <c r="L22" s="5">
-        <v>9309.8966666666602</v>
-      </c>
-      <c r="M22" s="5">
-        <v>-72.613373080760994</v>
-      </c>
+        <v>2336.48</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -2142,7 +2172,7 @@
       <c r="Z22" s="7"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
@@ -2152,103 +2182,91 @@
     </row>
     <row r="23" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5">
-        <v>11</v>
+        <v>128.36000000000001</v>
       </c>
       <c r="C23" s="5">
-        <v>4</v>
+        <v>120.36</v>
       </c>
       <c r="D23" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="5">
-        <v>4491.79</v>
+        <v>27929.69</v>
       </c>
       <c r="F23" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23" s="5">
+        <v>8</v>
+      </c>
+      <c r="H23" s="5">
+        <v>5</v>
+      </c>
+      <c r="I23" s="5">
+        <v>3</v>
+      </c>
+      <c r="J23" s="5">
         <v>2</v>
       </c>
-      <c r="H23" s="5">
-        <v>8</v>
-      </c>
-      <c r="I23" s="5">
-        <v>2</v>
-      </c>
-      <c r="J23" s="5">
-        <v>0</v>
-      </c>
       <c r="K23" s="5">
-        <v>449.17899999999997</v>
+        <v>2148.4376923076902</v>
       </c>
       <c r="L23" s="5">
-        <v>2245.895</v>
+        <v>9309.8966666666602</v>
       </c>
       <c r="M23" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N23" s="6">
-        <v>9</v>
-      </c>
-      <c r="O23" s="6">
-        <v>1780.79</v>
-      </c>
+        <v>-72.613373080760994</v>
+      </c>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
-      <c r="V23" s="7">
-        <v>16</v>
-      </c>
-      <c r="W23" s="7">
-        <v>2548.09</v>
-      </c>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8">
-        <v>6000</v>
-      </c>
-      <c r="AC23" s="9">
-        <v>8</v>
-      </c>
-      <c r="AD23" s="9">
-        <v>2</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
       <c r="AE23" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="C24" s="5">
         <v>4</v>
       </c>
       <c r="D24" s="5">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="E24" s="5">
-        <v>2949.88</v>
+        <v>4491.79</v>
       </c>
       <c r="F24" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G24" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I24" s="5">
         <v>2</v>
@@ -2257,366 +2275,396 @@
         <v>0</v>
       </c>
       <c r="K24" s="5">
-        <v>983.29333333333295</v>
+        <v>449.17899999999997</v>
       </c>
       <c r="L24" s="5">
-        <v>1474.94</v>
+        <v>2245.895</v>
       </c>
       <c r="M24" s="5">
         <v>-100</v>
       </c>
       <c r="N24" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O24" s="6">
-        <v>646.71</v>
-      </c>
-      <c r="P24" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <v>215.57</v>
-      </c>
+        <v>1780.79</v>
+      </c>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
       <c r="T24" s="6"/>
-      <c r="U24" s="6">
-        <v>-100</v>
-      </c>
+      <c r="U24" s="6"/>
       <c r="V24" s="7">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="W24" s="7">
-        <v>883.31</v>
-      </c>
-      <c r="X24" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>0</v>
-      </c>
+        <v>2548.09</v>
+      </c>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
       <c r="AA24" s="8">
         <v>6000</v>
       </c>
       <c r="AB24" s="8">
-        <v>7000</v>
-      </c>
-      <c r="AC24" s="9"/>
-      <c r="AD24" s="9"/>
+        <v>6000</v>
+      </c>
+      <c r="AC24" s="9">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="9">
+        <v>2</v>
+      </c>
       <c r="AE24" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="5">
-        <v>32.49</v>
+        <v>6.5</v>
       </c>
       <c r="C25" s="5">
-        <v>15.01</v>
+        <v>4</v>
       </c>
       <c r="D25" s="5">
-        <v>17.48</v>
+        <v>2.5</v>
       </c>
       <c r="E25" s="5">
-        <v>9009.02</v>
+        <v>2949.88</v>
       </c>
       <c r="F25" s="5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>3</v>
+      </c>
+      <c r="I25" s="5">
         <v>2</v>
       </c>
-      <c r="H25" s="5">
-        <v>17</v>
-      </c>
-      <c r="I25" s="5">
-        <v>4</v>
-      </c>
       <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5">
+        <v>983.29333333333295</v>
+      </c>
+      <c r="L25" s="5">
+        <v>1474.94</v>
+      </c>
+      <c r="M25" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N25" s="6">
         <v>1</v>
       </c>
-      <c r="K25" s="5">
-        <v>474.15894736842102</v>
-      </c>
-      <c r="L25" s="5">
-        <v>2252.2550000000001</v>
-      </c>
-      <c r="M25" s="5">
-        <v>-15.054245633820299</v>
-      </c>
-      <c r="N25" s="6">
-        <v>34.69</v>
-      </c>
       <c r="O25" s="6">
-        <v>7463.88</v>
+        <v>646.71</v>
       </c>
       <c r="P25" s="6">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
+        <v>215.57</v>
+      </c>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V25" s="7">
         <v>2</v>
       </c>
-      <c r="S25" s="6">
-        <v>257.375172413793</v>
-      </c>
-      <c r="T25" s="6">
-        <v>746.38800000000003</v>
-      </c>
-      <c r="U25" s="6">
-        <v>103.83326098490301</v>
-      </c>
-      <c r="V25" s="7">
-        <v>51.71</v>
-      </c>
       <c r="W25" s="7">
-        <v>10989.82</v>
+        <v>883.31</v>
       </c>
       <c r="X25" s="7">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="8">
         <v>7000</v>
       </c>
       <c r="AB25" s="8">
-        <v>12000</v>
-      </c>
-      <c r="AC25" s="9">
-        <v>26</v>
-      </c>
-      <c r="AD25" s="9">
-        <v>11</v>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
       <c r="AE25" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="B26" s="5">
+        <v>32.49</v>
+      </c>
+      <c r="C26" s="5">
+        <v>15.01</v>
+      </c>
+      <c r="D26" s="5">
+        <v>17.48</v>
+      </c>
+      <c r="E26" s="5">
+        <v>9009.02</v>
+      </c>
+      <c r="F26" s="5">
+        <v>19</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5">
+        <v>17</v>
+      </c>
+      <c r="I26" s="5">
+        <v>4</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>474.15894736842102</v>
+      </c>
+      <c r="L26" s="5">
+        <v>2252.2550000000001</v>
+      </c>
+      <c r="M26" s="5">
+        <v>-15.054245633820299</v>
+      </c>
       <c r="N26" s="6">
-        <v>9</v>
+        <v>34.69</v>
       </c>
       <c r="O26" s="6">
-        <v>1367.82</v>
+        <v>7463.88</v>
       </c>
       <c r="P26" s="6">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q26" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R26" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="6">
-        <v>227.97</v>
+        <v>257.375172413793</v>
       </c>
       <c r="T26" s="6">
-        <v>341.95499999999998</v>
+        <v>746.38800000000003</v>
       </c>
       <c r="U26" s="6">
-        <v>-100</v>
+        <v>103.83326098490301</v>
       </c>
       <c r="V26" s="7">
-        <v>16.939999999999898</v>
+        <v>51.71</v>
       </c>
       <c r="W26" s="7">
-        <v>2070.7399999999998</v>
+        <v>10989.82</v>
       </c>
       <c r="X26" s="7">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="Y26" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Z26" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" s="8">
         <v>12000</v>
       </c>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
+      <c r="AB26" s="8">
+        <v>12000</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>26</v>
+      </c>
+      <c r="AD26" s="9">
+        <v>11</v>
+      </c>
       <c r="AE26" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="5">
-        <v>49</v>
-      </c>
-      <c r="C27" s="5">
-        <v>17</v>
-      </c>
-      <c r="D27" s="5">
-        <v>32</v>
-      </c>
-      <c r="E27" s="5">
-        <v>9496.34</v>
-      </c>
-      <c r="F27" s="5">
-        <v>23</v>
-      </c>
-      <c r="G27" s="5">
-        <v>3</v>
-      </c>
-      <c r="H27" s="5">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <v>8</v>
-      </c>
-      <c r="J27" s="5">
-        <v>1</v>
-      </c>
-      <c r="K27" s="5">
-        <v>412.88434782608698</v>
-      </c>
-      <c r="L27" s="5">
-        <v>1187.0425</v>
-      </c>
-      <c r="M27" s="5">
-        <v>-44.884029004858697</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
       <c r="N27" s="6">
-        <v>9.0599999999999898</v>
+        <v>9</v>
       </c>
       <c r="O27" s="6">
-        <v>2137.33</v>
+        <v>1367.82</v>
       </c>
       <c r="P27" s="6">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" s="6">
-        <v>142.48866666666601</v>
+        <v>227.97</v>
       </c>
       <c r="T27" s="6">
-        <v>427.46600000000001</v>
+        <v>341.95499999999998</v>
       </c>
       <c r="U27" s="6">
-        <v>-92.981897975511501</v>
+        <v>-100</v>
       </c>
       <c r="V27" s="7">
-        <v>17.03</v>
+        <v>16.939999999999898</v>
       </c>
       <c r="W27" s="7">
-        <v>3580.98</v>
+        <v>2070.7399999999998</v>
       </c>
       <c r="X27" s="7">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Z27" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="8"/>
-      <c r="AB27" s="8">
-        <v>13000</v>
-      </c>
-      <c r="AC27" s="9">
-        <v>29</v>
-      </c>
-      <c r="AD27" s="9">
-        <v>12</v>
-      </c>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
       <c r="AE27" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="B28" s="5">
+        <v>49</v>
+      </c>
+      <c r="C28" s="5">
+        <v>17</v>
+      </c>
+      <c r="D28" s="5">
+        <v>32</v>
+      </c>
+      <c r="E28" s="5">
+        <v>9496.34</v>
+      </c>
+      <c r="F28" s="5">
+        <v>23</v>
+      </c>
+      <c r="G28" s="5">
+        <v>3</v>
+      </c>
+      <c r="H28" s="5">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <v>8</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5">
+        <v>412.88434782608698</v>
+      </c>
+      <c r="L28" s="5">
+        <v>1187.0425</v>
+      </c>
+      <c r="M28" s="5">
+        <v>-44.884029004858697</v>
+      </c>
       <c r="N28" s="6">
-        <v>12</v>
+        <v>9.0599999999999898</v>
       </c>
       <c r="O28" s="6">
-        <v>8318.86</v>
-      </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
+        <v>2137.33</v>
+      </c>
+      <c r="P28" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>5</v>
+      </c>
+      <c r="R28" s="6">
+        <v>1</v>
+      </c>
+      <c r="S28" s="6">
+        <v>142.48866666666601</v>
+      </c>
+      <c r="T28" s="6">
+        <v>427.46600000000001</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-92.981897975511501</v>
+      </c>
       <c r="V28" s="7">
-        <v>18</v>
+        <v>17.03</v>
       </c>
       <c r="W28" s="7">
-        <v>9228.76</v>
-      </c>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
+        <v>3580.98</v>
+      </c>
+      <c r="X28" s="7">
+        <v>28</v>
+      </c>
+      <c r="Y28" s="7">
+        <v>11</v>
+      </c>
+      <c r="Z28" s="7">
+        <v>1</v>
+      </c>
       <c r="AA28" s="8">
         <v>13000</v>
       </c>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="9"/>
+      <c r="AB28" s="8">
+        <v>13000</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>29</v>
+      </c>
+      <c r="AD28" s="9">
+        <v>12</v>
+      </c>
       <c r="AE28" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2631,44 +2679,26 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="6">
-        <v>20.03</v>
+        <v>12</v>
       </c>
       <c r="O29" s="6">
-        <v>2091.2800000000002</v>
-      </c>
-      <c r="P29" s="6">
-        <v>9</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>5</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="6">
-        <v>232.36444444444399</v>
-      </c>
-      <c r="T29" s="6">
-        <v>418.25599999999997</v>
-      </c>
-      <c r="U29" s="6">
-        <v>-100</v>
-      </c>
+        <v>8318.86</v>
+      </c>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="6"/>
       <c r="V29" s="7">
-        <v>60.559999999999903</v>
+        <v>18</v>
       </c>
       <c r="W29" s="7">
-        <v>4824.59</v>
-      </c>
-      <c r="X29" s="7">
-        <v>22</v>
-      </c>
-      <c r="Y29" s="7">
-        <v>7</v>
-      </c>
-      <c r="Z29" s="7">
-        <v>0</v>
-      </c>
+        <v>9228.76</v>
+      </c>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="7"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
       <c r="AC29" s="9"/>
@@ -2679,7 +2709,7 @@
     </row>
     <row r="30" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2694,43 +2724,43 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>24.98</v>
+        <v>20.03</v>
       </c>
       <c r="O30" s="6">
-        <v>2530.15</v>
+        <v>2091.2800000000002</v>
       </c>
       <c r="P30" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q30" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R30" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>230.01363636363601</v>
+        <v>232.36444444444399</v>
       </c>
       <c r="T30" s="6">
-        <v>632.53750000000002</v>
+        <v>418.25599999999997</v>
       </c>
       <c r="U30" s="6">
-        <v>195.95992332470399</v>
+        <v>-100</v>
       </c>
       <c r="V30" s="7">
-        <v>66.84</v>
+        <v>60.559999999999903</v>
       </c>
       <c r="W30" s="7">
-        <v>4891.78</v>
+        <v>4824.59</v>
       </c>
       <c r="X30" s="7">
         <v>22</v>
       </c>
       <c r="Y30" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
@@ -2742,161 +2772,157 @@
     </row>
     <row r="31" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="5">
-        <v>73.67</v>
-      </c>
-      <c r="C31" s="5">
-        <v>39</v>
-      </c>
-      <c r="D31" s="5">
-        <v>34.67</v>
-      </c>
-      <c r="E31" s="5">
-        <v>21342.63</v>
-      </c>
-      <c r="F31" s="5">
-        <v>30</v>
-      </c>
-      <c r="G31" s="5">
-        <v>8</v>
-      </c>
-      <c r="H31" s="5">
+        <v>112</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6">
+        <v>24.98</v>
+      </c>
+      <c r="O31" s="6">
+        <v>2530.15</v>
+      </c>
+      <c r="P31" s="6">
+        <v>11</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>4</v>
+      </c>
+      <c r="R31" s="6">
+        <v>1</v>
+      </c>
+      <c r="S31" s="6">
+        <v>230.01363636363601</v>
+      </c>
+      <c r="T31" s="6">
+        <v>632.53750000000002</v>
+      </c>
+      <c r="U31" s="6">
+        <v>195.95992332470399</v>
+      </c>
+      <c r="V31" s="7">
+        <v>66.84</v>
+      </c>
+      <c r="W31" s="7">
+        <v>4891.78</v>
+      </c>
+      <c r="X31" s="7">
         <v>22</v>
       </c>
-      <c r="I31" s="5">
-        <v>16</v>
-      </c>
-      <c r="J31" s="5">
-        <v>6</v>
-      </c>
-      <c r="K31" s="5">
-        <v>711.42100000000005</v>
-      </c>
-      <c r="L31" s="5">
-        <v>1333.9143750000001</v>
-      </c>
-      <c r="M31" s="5">
-        <v>85.239588560547503</v>
-      </c>
-      <c r="N31" s="6">
-        <v>36.090000000000003</v>
-      </c>
-      <c r="O31" s="6">
-        <v>9653.36</v>
-      </c>
-      <c r="P31" s="6">
-        <v>38</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>21</v>
-      </c>
-      <c r="R31" s="6">
+      <c r="Y31" s="7">
         <v>5</v>
       </c>
-      <c r="S31" s="6">
-        <v>254.03578947368399</v>
-      </c>
-      <c r="T31" s="6">
-        <v>459.68380952380897</v>
-      </c>
-      <c r="U31" s="6">
-        <v>306.34027944674102</v>
-      </c>
-      <c r="V31" s="7">
-        <v>46.14</v>
-      </c>
-      <c r="W31" s="7">
-        <v>13471.99</v>
-      </c>
-      <c r="X31" s="7">
-        <v>56</v>
-      </c>
-      <c r="Y31" s="7">
-        <v>29</v>
-      </c>
       <c r="Z31" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="8"/>
-      <c r="AB31" s="8">
-        <v>28000</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>43</v>
-      </c>
-      <c r="AD31" s="9">
-        <v>19</v>
-      </c>
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
       <c r="AE31" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" s="5">
-        <v>67.67</v>
+        <v>73.67</v>
       </c>
       <c r="C32" s="5">
-        <v>23.33</v>
+        <v>39</v>
       </c>
       <c r="D32" s="5">
-        <v>44.34</v>
+        <v>34.67</v>
       </c>
       <c r="E32" s="5">
-        <v>22542.94</v>
+        <v>21342.63</v>
       </c>
       <c r="F32" s="5">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G32" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H32" s="5">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I32" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J32" s="5">
         <v>6</v>
       </c>
       <c r="K32" s="5">
-        <v>479.63702127659502</v>
+        <v>711.42100000000005</v>
       </c>
       <c r="L32" s="5">
-        <v>1024.6790909090901</v>
+        <v>1333.9143750000001</v>
       </c>
       <c r="M32" s="5">
-        <v>83.897752467069495</v>
-      </c>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
+        <v>85.239588560547503</v>
+      </c>
+      <c r="N32" s="6">
+        <v>36.090000000000003</v>
+      </c>
+      <c r="O32" s="6">
+        <v>9653.36</v>
+      </c>
+      <c r="P32" s="6">
+        <v>38</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>21</v>
+      </c>
+      <c r="R32" s="6">
+        <v>5</v>
+      </c>
+      <c r="S32" s="6">
+        <v>254.03578947368399</v>
+      </c>
+      <c r="T32" s="6">
+        <v>459.68380952380897</v>
+      </c>
+      <c r="U32" s="6">
+        <v>306.34027944674102</v>
+      </c>
+      <c r="V32" s="7">
+        <v>46.14</v>
+      </c>
+      <c r="W32" s="7">
+        <v>13471.99</v>
+      </c>
+      <c r="X32" s="7">
+        <v>56</v>
+      </c>
+      <c r="Y32" s="7">
+        <v>29</v>
+      </c>
+      <c r="Z32" s="7">
+        <v>5</v>
+      </c>
       <c r="AA32" s="8">
         <v>28000</v>
       </c>
       <c r="AB32" s="8">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="AC32" s="9">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="AD32" s="9">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="AE32" s="14">
         <v>46135</v>
@@ -2904,43 +2930,43 @@
     </row>
     <row r="33" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="5">
-        <v>122.2</v>
+        <v>67.67</v>
       </c>
       <c r="C33" s="5">
-        <v>52.8</v>
+        <v>23.33</v>
       </c>
       <c r="D33" s="5">
-        <v>69.400000000000006</v>
+        <v>44.34</v>
       </c>
       <c r="E33" s="5">
-        <v>23251.8</v>
+        <v>22542.94</v>
       </c>
       <c r="F33" s="5">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="G33" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33" s="5">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I33" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J33" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K33" s="5">
-        <v>347.04179104477601</v>
+        <v>479.63702127659502</v>
       </c>
       <c r="L33" s="5">
-        <v>1223.7789473684199</v>
+        <v>1024.6790909090901</v>
       </c>
       <c r="M33" s="5">
-        <v>-36.615659862892301</v>
+        <v>83.897752467069495</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -2957,13 +2983,13 @@
       <c r="Z33" s="7"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AC33" s="9">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AD33" s="9">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="AE33" s="14">
         <v>46135</v>
@@ -2971,92 +2997,66 @@
     </row>
     <row r="34" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" s="5">
-        <v>122.79</v>
+        <v>122.2</v>
       </c>
       <c r="C34" s="5">
-        <v>74.290000000000006</v>
+        <v>52.8</v>
       </c>
       <c r="D34" s="5">
-        <v>48.5</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="E34" s="5">
-        <v>25668.16</v>
+        <v>23251.8</v>
       </c>
       <c r="F34" s="5">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G34" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H34" s="5">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I34" s="5">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J34" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" s="5">
-        <v>611.14666666666596</v>
+        <v>347.04179104477601</v>
       </c>
       <c r="L34" s="5">
-        <v>2333.46909090909</v>
+        <v>1223.7789473684199</v>
       </c>
       <c r="M34" s="5">
-        <v>-20.305935446872699</v>
-      </c>
-      <c r="N34" s="6">
-        <v>96.28</v>
-      </c>
-      <c r="O34" s="6">
-        <v>25348.75</v>
-      </c>
-      <c r="P34" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>31</v>
-      </c>
-      <c r="R34" s="6">
-        <v>14</v>
-      </c>
-      <c r="S34" s="6">
-        <v>284.81741573033702</v>
-      </c>
-      <c r="T34" s="6">
-        <v>817.70161290322505</v>
-      </c>
-      <c r="U34" s="6">
-        <v>285.073820208097</v>
-      </c>
-      <c r="V34" s="7">
-        <v>121.28</v>
-      </c>
-      <c r="W34" s="7">
-        <v>32532.17</v>
-      </c>
-      <c r="X34" s="7">
-        <v>112</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>43</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>14</v>
-      </c>
+        <v>-36.615659862892301</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="AC34" s="9">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AD34" s="9">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE34" s="14">
         <v>46135</v>
@@ -3064,224 +3064,224 @@
     </row>
     <row r="35" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="B35" s="5">
+        <v>122.79</v>
+      </c>
+      <c r="C35" s="5">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="D35" s="5">
+        <v>48.5</v>
+      </c>
+      <c r="E35" s="5">
+        <v>25668.16</v>
+      </c>
+      <c r="F35" s="5">
+        <v>42</v>
+      </c>
+      <c r="G35" s="5">
+        <v>6</v>
+      </c>
+      <c r="H35" s="5">
+        <v>36</v>
+      </c>
+      <c r="I35" s="5">
+        <v>11</v>
+      </c>
+      <c r="J35" s="5">
+        <v>3</v>
+      </c>
+      <c r="K35" s="5">
+        <v>611.14666666666596</v>
+      </c>
+      <c r="L35" s="5">
+        <v>2333.46909090909</v>
+      </c>
+      <c r="M35" s="5">
+        <v>-20.305935446872699</v>
+      </c>
       <c r="N35" s="6">
-        <v>13.88</v>
+        <v>96.28</v>
       </c>
       <c r="O35" s="6">
-        <v>2035.83</v>
+        <v>25348.75</v>
       </c>
       <c r="P35" s="6">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="Q35" s="6">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="R35" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S35" s="6">
-        <v>339.30500000000001</v>
+        <v>284.81741573033702</v>
       </c>
       <c r="T35" s="6">
-        <v>2035.83</v>
+        <v>817.70161290322505</v>
       </c>
       <c r="U35" s="6">
-        <v>-100</v>
+        <v>285.073820208097</v>
       </c>
       <c r="V35" s="7">
-        <v>46.9</v>
+        <v>121.28</v>
       </c>
       <c r="W35" s="7">
-        <v>3023.13</v>
+        <v>32532.17</v>
       </c>
       <c r="X35" s="7">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="Y35" s="7">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="Z35" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA35" s="8">
         <v>35000</v>
       </c>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="9"/>
-      <c r="AD35" s="9"/>
+      <c r="AB35" s="8">
+        <v>35000</v>
+      </c>
+      <c r="AC35" s="9">
+        <v>52</v>
+      </c>
+      <c r="AD35" s="9">
+        <v>14</v>
+      </c>
       <c r="AE35" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="5">
-        <v>29.93</v>
-      </c>
-      <c r="C36" s="5">
-        <v>19.920000000000002</v>
-      </c>
-      <c r="D36" s="5">
-        <v>10.01</v>
-      </c>
-      <c r="E36" s="5">
-        <v>5780.66</v>
-      </c>
-      <c r="F36" s="5">
-        <v>10</v>
-      </c>
-      <c r="G36" s="5">
+        <v>113</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6">
+        <v>13.88</v>
+      </c>
+      <c r="O36" s="6">
+        <v>2035.83</v>
+      </c>
+      <c r="P36" s="6">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="6">
         <v>1</v>
       </c>
-      <c r="H36" s="5">
+      <c r="R36" s="6">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>339.30500000000001</v>
+      </c>
+      <c r="T36" s="6">
+        <v>2035.83</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V36" s="7">
+        <v>46.9</v>
+      </c>
+      <c r="W36" s="7">
+        <v>3023.13</v>
+      </c>
+      <c r="X36" s="7">
         <v>9</v>
       </c>
-      <c r="I36" s="5">
-        <v>4</v>
-      </c>
-      <c r="J36" s="5">
-        <v>1</v>
-      </c>
-      <c r="K36" s="5">
-        <v>578.06600000000003</v>
-      </c>
-      <c r="L36" s="5">
-        <v>1445.165</v>
-      </c>
-      <c r="M36" s="5">
-        <v>34.8288949704705</v>
-      </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
+      <c r="Y36" s="7">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="7">
+        <v>0</v>
+      </c>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="8">
-        <v>7500</v>
-      </c>
-      <c r="AC36" s="9">
-        <v>28</v>
-      </c>
-      <c r="AD36" s="9">
-        <v>15</v>
-      </c>
+      <c r="AB36" s="8"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
       <c r="AE36" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="5">
-        <v>71.400000000000006</v>
+        <v>29.93</v>
       </c>
       <c r="C37" s="5">
-        <v>35.49</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="D37" s="5">
-        <v>35.909999999999997</v>
+        <v>10.01</v>
       </c>
       <c r="E37" s="5">
-        <v>15274.42</v>
+        <v>5780.66</v>
       </c>
       <c r="F37" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G37" s="5">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5">
+        <v>9</v>
+      </c>
+      <c r="I37" s="5">
         <v>4</v>
       </c>
-      <c r="H37" s="5">
-        <v>18</v>
-      </c>
-      <c r="I37" s="5">
-        <v>11</v>
-      </c>
       <c r="J37" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="5">
-        <v>694.29181818181803</v>
+        <v>578.06600000000003</v>
       </c>
       <c r="L37" s="5">
-        <v>1388.5836363636299</v>
+        <v>1445.165</v>
       </c>
       <c r="M37" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N37" s="6">
-        <v>23</v>
-      </c>
-      <c r="O37" s="6">
-        <v>6058.44</v>
-      </c>
-      <c r="P37" s="6">
-        <v>33</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>13</v>
-      </c>
-      <c r="R37" s="6">
-        <v>4</v>
-      </c>
-      <c r="S37" s="6">
-        <v>183.58909090909</v>
-      </c>
-      <c r="T37" s="6">
-        <v>466.03384615384601</v>
-      </c>
-      <c r="U37" s="6">
-        <v>286.857672932306</v>
-      </c>
-      <c r="V37" s="7">
-        <v>34</v>
-      </c>
-      <c r="W37" s="7">
-        <v>9463.0300000000007</v>
-      </c>
-      <c r="X37" s="7">
-        <v>49</v>
-      </c>
-      <c r="Y37" s="7">
-        <v>17</v>
-      </c>
-      <c r="Z37" s="7">
-        <v>4</v>
-      </c>
+        <v>34.8288949704705</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8">
-        <v>17000</v>
+        <v>7500</v>
       </c>
       <c r="AC37" s="9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AD37" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE37" s="14">
         <v>46135</v>
@@ -3289,144 +3289,156 @@
     </row>
     <row r="38" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="B38" s="5">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="C38" s="5">
+        <v>35.49</v>
+      </c>
+      <c r="D38" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="E38" s="5">
+        <v>15274.42</v>
+      </c>
+      <c r="F38" s="5">
+        <v>22</v>
+      </c>
+      <c r="G38" s="5">
+        <v>4</v>
+      </c>
+      <c r="H38" s="5">
+        <v>18</v>
+      </c>
+      <c r="I38" s="5">
+        <v>11</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>694.29181818181803</v>
+      </c>
+      <c r="L38" s="5">
+        <v>1388.5836363636299</v>
+      </c>
+      <c r="M38" s="5">
+        <v>-100</v>
+      </c>
       <c r="N38" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O38" s="6">
-        <v>1956.99</v>
+        <v>6058.44</v>
       </c>
       <c r="P38" s="6">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="Q38" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R38" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S38" s="6">
-        <v>326.16500000000002</v>
+        <v>183.58909090909</v>
       </c>
       <c r="T38" s="6">
-        <v>1956.99</v>
+        <v>466.03384615384601</v>
       </c>
       <c r="U38" s="6">
-        <v>-100</v>
+        <v>286.857672932306</v>
       </c>
       <c r="V38" s="7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="W38" s="7">
-        <v>3368</v>
+        <v>9463.0300000000007</v>
       </c>
       <c r="X38" s="7">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="Y38" s="7">
+        <v>17</v>
+      </c>
+      <c r="Z38" s="7">
         <v>4</v>
-      </c>
-      <c r="Z38" s="7">
-        <v>0</v>
       </c>
       <c r="AA38" s="8">
         <v>17000</v>
       </c>
-      <c r="AB38" s="8"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="9"/>
+      <c r="AB38" s="8">
+        <v>17000</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>25</v>
+      </c>
+      <c r="AD38" s="9">
+        <v>14</v>
+      </c>
       <c r="AE38" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="5">
-        <v>65.97</v>
-      </c>
-      <c r="C39" s="5">
-        <v>35</v>
-      </c>
-      <c r="D39" s="5">
-        <v>30.97</v>
-      </c>
-      <c r="E39" s="5">
-        <v>12646.31</v>
-      </c>
-      <c r="F39" s="5">
-        <v>27</v>
-      </c>
-      <c r="G39" s="5">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5">
-        <v>25</v>
-      </c>
-      <c r="I39" s="5">
-        <v>8</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>468.38185185185102</v>
-      </c>
-      <c r="L39" s="5">
-        <v>1580.7887499999999</v>
-      </c>
-      <c r="M39" s="5">
-        <v>-100</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
       <c r="N39" s="6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O39" s="6">
-        <v>449.86</v>
+        <v>1956.99</v>
       </c>
       <c r="P39" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="6">
         <v>0</v>
       </c>
       <c r="S39" s="6">
-        <v>224.93</v>
-      </c>
-      <c r="T39" s="6"/>
+        <v>326.16500000000002</v>
+      </c>
+      <c r="T39" s="6">
+        <v>1956.99</v>
+      </c>
       <c r="U39" s="6">
         <v>-100</v>
       </c>
       <c r="V39" s="7">
+        <v>29</v>
+      </c>
+      <c r="W39" s="7">
+        <v>3368</v>
+      </c>
+      <c r="X39" s="7">
+        <v>12</v>
+      </c>
+      <c r="Y39" s="7">
         <v>4</v>
       </c>
-      <c r="W39" s="7">
-        <v>677.6</v>
-      </c>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
+      <c r="Z39" s="7">
+        <v>0</v>
+      </c>
       <c r="AA39" s="8"/>
-      <c r="AB39" s="8">
-        <v>17000</v>
-      </c>
+      <c r="AB39" s="8"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
       <c r="AE39" s="14">
@@ -3435,144 +3447,177 @@
     </row>
     <row r="40" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" s="5">
-        <v>59.91</v>
+        <v>65.97</v>
       </c>
       <c r="C40" s="5">
-        <v>34.51</v>
+        <v>35</v>
       </c>
       <c r="D40" s="5">
-        <v>25.4</v>
+        <v>30.97</v>
       </c>
       <c r="E40" s="5">
-        <v>17959.560000000001</v>
+        <v>12646.31</v>
       </c>
       <c r="F40" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G40" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I40" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J40" s="5">
         <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>748.31500000000005</v>
+        <v>468.38185185185102</v>
       </c>
       <c r="L40" s="5">
-        <v>1995.5066666666601</v>
+        <v>1580.7887499999999</v>
       </c>
       <c r="M40" s="5">
         <v>-100</v>
       </c>
       <c r="N40" s="6">
-        <v>26.54</v>
+        <v>4</v>
       </c>
       <c r="O40" s="6">
-        <v>6066.2</v>
+        <v>449.86</v>
       </c>
       <c r="P40" s="6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="6">
-        <v>263.74782608695602</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1011.03333333333</v>
-      </c>
+        <v>224.93</v>
+      </c>
+      <c r="T40" s="6"/>
       <c r="U40" s="6">
         <v>-100</v>
       </c>
       <c r="V40" s="7">
-        <v>36.5</v>
+        <v>4</v>
       </c>
       <c r="W40" s="7">
-        <v>8945.9699999999993</v>
-      </c>
-      <c r="X40" s="7">
-        <v>34</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>7</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>0</v>
-      </c>
+        <v>677.6</v>
+      </c>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
       <c r="AA40" s="8">
         <v>17000</v>
       </c>
       <c r="AB40" s="8">
-        <v>24000</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>32</v>
-      </c>
-      <c r="AD40" s="9">
-        <v>14</v>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
       <c r="AE40" s="14">
         <v>46135</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>66</v>
+      </c>
+      <c r="B41">
+        <v>59.91</v>
+      </c>
+      <c r="C41">
+        <v>34.51</v>
+      </c>
+      <c r="D41">
+        <v>25.4</v>
+      </c>
+      <c r="E41">
+        <v>17959.560000000001</v>
+      </c>
+      <c r="F41">
+        <v>24</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>21</v>
+      </c>
+      <c r="I41">
+        <v>9</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>748.31500000000005</v>
+      </c>
+      <c r="L41">
+        <v>1995.5066666666601</v>
+      </c>
+      <c r="M41">
+        <v>-100</v>
       </c>
       <c r="N41">
-        <v>19.059999999999999</v>
+        <v>26.54</v>
       </c>
       <c r="O41">
-        <v>1803.46</v>
+        <v>6066.2</v>
       </c>
       <c r="P41">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R41">
         <v>0</v>
       </c>
       <c r="S41">
-        <v>257.63714285714201</v>
+        <v>263.74782608695602</v>
       </c>
       <c r="T41">
-        <v>450.86500000000001</v>
+        <v>1011.03333333333</v>
       </c>
       <c r="U41">
         <v>-100</v>
       </c>
       <c r="V41">
-        <v>39.630000000000003</v>
+        <v>36.5</v>
       </c>
       <c r="W41">
-        <v>3006.79</v>
+        <v>8945.9699999999993</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="Y41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z41">
         <v>0</v>
       </c>
       <c r="AA41">
         <v>24000</v>
+      </c>
+      <c r="AB41">
+        <v>24000</v>
+      </c>
+      <c r="AC41">
+        <v>32</v>
+      </c>
+      <c r="AD41">
+        <v>14</v>
       </c>
       <c r="AE41" s="14">
         <v>46135</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB81697-4EFF-446C-BFDC-6757926E5940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58445988-B911-481E-9185-D937C963E464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -1123,7 +1123,7 @@
         <v>364</v>
       </c>
       <c r="AE6" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1216,7 +1216,7 @@
         <v>94</v>
       </c>
       <c r="AE7" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1311,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="AE8" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1406,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AE9" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1451,7 +1451,7 @@
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
       <c r="AE10" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1514,7 +1514,7 @@
       <c r="AC11" s="9"/>
       <c r="AD11" s="9"/>
       <c r="AE11" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1577,7 +1577,7 @@
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
       <c r="AE12" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
       <c r="AC13" s="9"/>
       <c r="AD13" s="9"/>
       <c r="AE13" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1667,7 +1667,7 @@
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
       <c r="AE14" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1742,7 +1742,7 @@
       <c r="AC15" s="9"/>
       <c r="AD15" s="9"/>
       <c r="AE15" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1837,7 +1837,7 @@
         <v>20</v>
       </c>
       <c r="AE16" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1900,7 +1900,7 @@
       <c r="AC17" s="9"/>
       <c r="AD17" s="9"/>
       <c r="AE17" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1971,7 +1971,7 @@
         <v>3</v>
       </c>
       <c r="AE18" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2016,7 +2016,7 @@
       <c r="AC19" s="9"/>
       <c r="AD19" s="9"/>
       <c r="AE19" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2067,7 +2067,7 @@
         <v>3</v>
       </c>
       <c r="AE20" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2130,7 +2130,7 @@
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
       <c r="AE21" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2177,7 +2177,7 @@
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
       <c r="AE22" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2240,7 +2240,7 @@
       <c r="AC23" s="9"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>2</v>
       </c>
       <c r="AE24" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2406,7 +2406,7 @@
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
       <c r="AE25" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2501,7 +2501,7 @@
         <v>11</v>
       </c>
       <c r="AE26" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2564,7 +2564,7 @@
       <c r="AC27" s="9"/>
       <c r="AD27" s="9"/>
       <c r="AE27" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2659,7 +2659,7 @@
         <v>12</v>
       </c>
       <c r="AE28" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2704,7 +2704,7 @@
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
       <c r="AE29" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2767,7 +2767,7 @@
       <c r="AC30" s="9"/>
       <c r="AD30" s="9"/>
       <c r="AE30" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2830,7 +2830,7 @@
       <c r="AC31" s="9"/>
       <c r="AD31" s="9"/>
       <c r="AE31" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2925,7 +2925,7 @@
         <v>19</v>
       </c>
       <c r="AE32" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2992,7 +2992,7 @@
         <v>41</v>
       </c>
       <c r="AE33" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3059,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="AE34" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3154,7 +3154,7 @@
         <v>14</v>
       </c>
       <c r="AE35" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3217,7 +3217,7 @@
       <c r="AC36" s="9"/>
       <c r="AD36" s="9"/>
       <c r="AE36" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3284,7 +3284,7 @@
         <v>15</v>
       </c>
       <c r="AE37" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3379,7 +3379,7 @@
         <v>14</v>
       </c>
       <c r="AE38" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
       <c r="AE39" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3525,7 +3525,7 @@
       <c r="AC40" s="9"/>
       <c r="AD40" s="9"/>
       <c r="AE40" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
@@ -3620,7 +3620,7 @@
         <v>14</v>
       </c>
       <c r="AE41" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="AE42" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>5</v>
       </c>
       <c r="AE43" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="AE44" s="14">
-        <v>46135</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58445988-B911-481E-9185-D937C963E464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4791C-C3C2-4FBB-8F77-9543EC371D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -3918,19 +3918,19 @@
         <v>68362.8</v>
       </c>
       <c r="J5" s="17">
-        <v>4</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="K5" s="17">
-        <v>9</v>
+        <v>18.88</v>
       </c>
       <c r="L5" s="17">
-        <v>37</v>
+        <v>0.38</v>
       </c>
       <c r="M5" s="17">
-        <v>40</v>
+        <v>0.41</v>
       </c>
       <c r="N5" s="17">
-        <v>15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3962,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="17">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K6" s="17">
         <v>0</v>
       </c>
       <c r="L6" s="17">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M6" s="17">
         <v>0</v>
@@ -3982,10 +3982,10 @@
         <v>86</v>
       </c>
       <c r="B7" s="5">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="5">
         <v>33</v>
@@ -4006,19 +4006,19 @@
         <v>40755.56</v>
       </c>
       <c r="J7" s="17">
-        <v>6</v>
+        <v>13.27</v>
       </c>
       <c r="K7" s="17">
-        <v>5</v>
+        <v>11.3</v>
       </c>
       <c r="L7" s="17">
-        <v>40</v>
+        <v>0.41</v>
       </c>
       <c r="M7" s="17">
-        <v>21</v>
+        <v>0.21</v>
       </c>
       <c r="N7" s="17">
-        <v>8</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4050,19 +4050,19 @@
         <v>0</v>
       </c>
       <c r="J8" s="17">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="K8" s="17">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="17">
-        <v>16</v>
+        <v>0.17</v>
       </c>
       <c r="M8" s="17">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="17">
-        <v>8</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4094,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="17">
-        <v>0</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="K9" s="17">
         <v>0</v>
       </c>
       <c r="L9" s="17">
-        <v>57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M9" s="17">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="17">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="K10" s="17">
         <v>0</v>
@@ -4146,9 +4146,7 @@
       <c r="L10" s="17">
         <v>0</v>
       </c>
-      <c r="M10" s="17">
-        <v>0</v>
-      </c>
+      <c r="M10" s="17"/>
       <c r="N10" s="17">
         <v>0</v>
       </c>
@@ -4182,13 +4180,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="17">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="K11" s="17">
         <v>0</v>
       </c>
       <c r="L11" s="17">
-        <v>23</v>
+        <v>0.23</v>
       </c>
       <c r="M11" s="17">
         <v>0</v>
@@ -4217,28 +4215,28 @@
         <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>40077.9399999999</v>
+        <v>40077.94</v>
       </c>
       <c r="H12" s="5">
         <v>5</v>
       </c>
       <c r="I12" s="5">
-        <v>32156.9399999999</v>
+        <v>32156.94</v>
       </c>
       <c r="J12" s="17">
-        <v>4</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="K12" s="17">
-        <v>5</v>
+        <v>11.07</v>
       </c>
       <c r="L12" s="17">
-        <v>43</v>
+        <v>0.43</v>
       </c>
       <c r="M12" s="17">
-        <v>23</v>
+        <v>0.23</v>
       </c>
       <c r="N12" s="17">
-        <v>10</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4270,19 +4268,19 @@
         <v>12943.84</v>
       </c>
       <c r="J13" s="17">
-        <v>2</v>
+        <v>5.14</v>
       </c>
       <c r="K13" s="17">
-        <v>2</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="L13" s="17">
-        <v>38</v>
+        <v>0.39</v>
       </c>
       <c r="M13" s="17">
-        <v>25</v>
+        <v>0.25</v>
       </c>
       <c r="N13" s="17">
-        <v>9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4314,19 +4312,17 @@
         <v>7499</v>
       </c>
       <c r="J14" s="17">
-        <v>6</v>
+        <v>12.27</v>
       </c>
       <c r="K14" s="17">
-        <v>1</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L14" s="17">
         <v>0</v>
       </c>
-      <c r="M14" s="17">
-        <v>0</v>
-      </c>
+      <c r="M14" s="17"/>
       <c r="N14" s="17">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4334,43 +4330,43 @@
         <v>93</v>
       </c>
       <c r="B15" s="5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="5">
-        <v>79612.61</v>
+        <v>71454.61</v>
       </c>
       <c r="H15" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="5">
-        <v>63438.61</v>
+        <v>55280.61</v>
       </c>
       <c r="J15" s="17">
-        <v>4</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="K15" s="17">
-        <v>10</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="L15" s="17">
-        <v>57</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M15" s="17">
-        <v>32</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="N15" s="17">
-        <v>18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4402,19 +4398,19 @@
         <v>68476</v>
       </c>
       <c r="J16" s="17">
-        <v>7</v>
+        <v>15.75</v>
       </c>
       <c r="K16" s="17">
-        <v>9</v>
+        <v>18.91</v>
       </c>
       <c r="L16" s="17">
-        <v>42</v>
+        <v>0.42</v>
       </c>
       <c r="M16" s="17">
-        <v>22</v>
+        <v>0.22</v>
       </c>
       <c r="N16" s="17">
-        <v>9</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4446,19 +4442,19 @@
         <v>8166</v>
       </c>
       <c r="J17" s="17">
-        <v>2</v>
+        <v>5.47</v>
       </c>
       <c r="K17" s="17">
-        <v>1</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="L17" s="17">
-        <v>54</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M17" s="17">
-        <v>5</v>
+        <v>0.06</v>
       </c>
       <c r="N17" s="17">
-        <v>3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4490,19 +4486,19 @@
         <v>8641</v>
       </c>
       <c r="J18" s="17">
-        <v>1</v>
+        <v>3.65</v>
       </c>
       <c r="K18" s="17">
-        <v>1</v>
+        <v>2.39</v>
       </c>
       <c r="L18" s="17">
-        <v>45</v>
+        <v>0.45</v>
       </c>
       <c r="M18" s="17">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="N18" s="17">
-        <v>4</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4534,19 +4530,19 @@
         <v>13015.8</v>
       </c>
       <c r="J19" s="17">
-        <v>2</v>
+        <v>5.97</v>
       </c>
       <c r="K19" s="17">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="L19" s="17">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="17">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="N19" s="17">
-        <v>5</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4578,19 +4574,19 @@
         <v>16532</v>
       </c>
       <c r="J20" s="17">
-        <v>1</v>
+        <v>3.98</v>
       </c>
       <c r="K20" s="17">
-        <v>2</v>
+        <v>4.57</v>
       </c>
       <c r="L20" s="17">
-        <v>41</v>
+        <v>0.42</v>
       </c>
       <c r="M20" s="17">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="N20" s="17">
-        <v>8</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4791C-C3C2-4FBB-8F77-9543EC371D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8316A1D2-35A7-4D49-A792-697F285709C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,7 +584,7 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3918,10 +3918,10 @@
         <v>68362.8</v>
       </c>
       <c r="J5" s="17">
-        <v>9.6199999999999992</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="17">
-        <v>18.88</v>
+        <v>0.19</v>
       </c>
       <c r="L5" s="17">
         <v>0.38</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="17">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="17">
         <v>0</v>
@@ -4006,10 +4006,10 @@
         <v>40755.56</v>
       </c>
       <c r="J7" s="17">
-        <v>13.27</v>
+        <v>0.13</v>
       </c>
       <c r="K7" s="17">
-        <v>11.3</v>
+        <v>0.11</v>
       </c>
       <c r="L7" s="17">
         <v>0.41</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="17">
-        <v>1.99</v>
+        <v>0.02</v>
       </c>
       <c r="K8" s="17">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="17">
         <v>0.17</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="17">
-        <v>1.1599999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="K9" s="17">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="17">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="K10" s="17">
         <v>0</v>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="17">
-        <v>2.16</v>
+        <v>0.02</v>
       </c>
       <c r="K11" s="17">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>32156.94</v>
       </c>
       <c r="J12" s="17">
-        <v>9.9499999999999993</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="17">
-        <v>11.07</v>
+        <v>0.11</v>
       </c>
       <c r="L12" s="17">
         <v>0.43</v>
@@ -4268,10 +4268,10 @@
         <v>12943.84</v>
       </c>
       <c r="J13" s="17">
-        <v>5.14</v>
+        <v>0.05</v>
       </c>
       <c r="K13" s="17">
-        <v>5.0199999999999996</v>
+        <v>0.05</v>
       </c>
       <c r="L13" s="17">
         <v>0.39</v>
@@ -4312,10 +4312,10 @@
         <v>7499</v>
       </c>
       <c r="J14" s="17">
-        <v>12.27</v>
+        <v>0.12</v>
       </c>
       <c r="K14" s="17">
-        <v>2.0699999999999998</v>
+        <v>0.02</v>
       </c>
       <c r="L14" s="17">
         <v>0</v>
@@ -4354,10 +4354,10 @@
         <v>55280.61</v>
       </c>
       <c r="J15" s="17">
-        <v>9.1199999999999992</v>
+        <v>0.09</v>
       </c>
       <c r="K15" s="17">
-        <v>19.739999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="L15" s="17">
         <v>0.57999999999999996</v>
@@ -4398,10 +4398,10 @@
         <v>68476</v>
       </c>
       <c r="J16" s="17">
-        <v>15.75</v>
+        <v>0.16</v>
       </c>
       <c r="K16" s="17">
-        <v>18.91</v>
+        <v>0.19</v>
       </c>
       <c r="L16" s="17">
         <v>0.42</v>
@@ -4442,10 +4442,10 @@
         <v>8166</v>
       </c>
       <c r="J17" s="17">
-        <v>5.47</v>
+        <v>0.05</v>
       </c>
       <c r="K17" s="17">
-        <v>2.2599999999999998</v>
+        <v>0.02</v>
       </c>
       <c r="L17" s="17">
         <v>0.55000000000000004</v>
@@ -4486,10 +4486,10 @@
         <v>8641</v>
       </c>
       <c r="J18" s="17">
-        <v>3.65</v>
+        <v>0.04</v>
       </c>
       <c r="K18" s="17">
-        <v>2.39</v>
+        <v>0.02</v>
       </c>
       <c r="L18" s="17">
         <v>0.45</v>
@@ -4530,10 +4530,10 @@
         <v>13015.8</v>
       </c>
       <c r="J19" s="17">
-        <v>5.97</v>
+        <v>0.06</v>
       </c>
       <c r="K19" s="17">
-        <v>3.6</v>
+        <v>0.04</v>
       </c>
       <c r="L19" s="17">
         <v>0.5</v>
@@ -4574,10 +4574,10 @@
         <v>16532</v>
       </c>
       <c r="J20" s="17">
-        <v>3.98</v>
+        <v>0.04</v>
       </c>
       <c r="K20" s="17">
-        <v>4.57</v>
+        <v>0.05</v>
       </c>
       <c r="L20" s="17">
         <v>0.42</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8316A1D2-35A7-4D49-A792-697F285709C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB07CD-114D-4519-82D4-18AA419E66CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,7 +584,7 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3900,7 +3900,7 @@
         <v>56</v>
       </c>
       <c r="D5" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5">
         <v>16</v>
@@ -3918,19 +3918,19 @@
         <v>68362.8</v>
       </c>
       <c r="J5" s="17">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="K5" s="17">
-        <v>0.19</v>
+        <v>16.95</v>
       </c>
       <c r="L5" s="17">
-        <v>0.38</v>
+        <v>41.38</v>
       </c>
       <c r="M5" s="17">
-        <v>0.41</v>
+        <v>37.5</v>
       </c>
       <c r="N5" s="17">
-        <v>0.16</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3962,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="17">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K6" s="17">
         <v>0</v>
       </c>
       <c r="L6" s="17">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M6" s="17">
         <v>0</v>
@@ -3988,10 +3988,10 @@
         <v>75</v>
       </c>
       <c r="D7" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" s="5">
         <v>7</v>
@@ -4006,19 +4006,19 @@
         <v>40755.56</v>
       </c>
       <c r="J7" s="17">
-        <v>0.13</v>
+        <v>13.25</v>
       </c>
       <c r="K7" s="17">
-        <v>0.11</v>
+        <v>10.14</v>
       </c>
       <c r="L7" s="17">
-        <v>0.41</v>
+        <v>43.75</v>
       </c>
       <c r="M7" s="17">
-        <v>0.21</v>
+        <v>20</v>
       </c>
       <c r="N7" s="17">
-        <v>0.09</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4050,19 +4050,19 @@
         <v>0</v>
       </c>
       <c r="J8" s="17">
-        <v>0.02</v>
+        <v>1.99</v>
       </c>
       <c r="K8" s="17">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L8" s="17">
-        <v>0.17</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="M8" s="17">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="N8" s="17">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4094,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="17">
-        <v>0.01</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="K9" s="17">
         <v>0</v>
       </c>
       <c r="L9" s="17">
-        <v>0.56999999999999995</v>
+        <v>57.14</v>
       </c>
       <c r="M9" s="17">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="17">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="K10" s="17">
         <v>0</v>
@@ -4180,13 +4180,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="17">
-        <v>0.02</v>
+        <v>2.15</v>
       </c>
       <c r="K11" s="17">
         <v>0</v>
       </c>
       <c r="L11" s="17">
-        <v>0.23</v>
+        <v>23.08</v>
       </c>
       <c r="M11" s="17">
         <v>0</v>
@@ -4200,16 +4200,16 @@
         <v>91</v>
       </c>
       <c r="B12" s="5">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="5">
         <v>6</v>
@@ -4224,19 +4224,19 @@
         <v>32156.94</v>
       </c>
       <c r="J12" s="17">
-        <v>0.1</v>
+        <v>10.1</v>
       </c>
       <c r="K12" s="17">
-        <v>0.11</v>
+        <v>9.94</v>
       </c>
       <c r="L12" s="17">
-        <v>0.43</v>
+        <v>44.26</v>
       </c>
       <c r="M12" s="17">
-        <v>0.23</v>
+        <v>22.22</v>
       </c>
       <c r="N12" s="17">
-        <v>0.1</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4253,34 +4253,34 @@
         <v>12</v>
       </c>
       <c r="E13" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>25271.84</v>
+      </c>
+      <c r="H13" s="5">
         <v>3</v>
       </c>
-      <c r="G13" s="5">
-        <v>18177.84</v>
-      </c>
-      <c r="H13" s="5">
-        <v>2</v>
-      </c>
       <c r="I13" s="5">
-        <v>12943.84</v>
+        <v>20037.84</v>
       </c>
       <c r="J13" s="17">
-        <v>0.05</v>
+        <v>5.13</v>
       </c>
       <c r="K13" s="17">
-        <v>0.05</v>
+        <v>6.27</v>
       </c>
       <c r="L13" s="17">
-        <v>0.39</v>
+        <v>38.71</v>
       </c>
       <c r="M13" s="17">
-        <v>0.25</v>
+        <v>33.33</v>
       </c>
       <c r="N13" s="17">
-        <v>0.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4288,16 +4288,16 @@
         <v>117</v>
       </c>
       <c r="B14" s="5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="5">
         <v>0</v>
       </c>
       <c r="E14" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="5">
         <v>1</v>
@@ -4312,17 +4312,17 @@
         <v>7499</v>
       </c>
       <c r="J14" s="17">
-        <v>0.12</v>
+        <v>12.42</v>
       </c>
       <c r="K14" s="17">
-        <v>0.02</v>
+        <v>1.86</v>
       </c>
       <c r="L14" s="17">
         <v>0</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17">
-        <v>0.01</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4330,43 +4330,43 @@
         <v>93</v>
       </c>
       <c r="B15" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="5">
         <v>32</v>
       </c>
       <c r="E15" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="5">
+        <v>11</v>
+      </c>
+      <c r="G15" s="5">
+        <v>86242.61</v>
+      </c>
+      <c r="H15" s="5">
         <v>9</v>
       </c>
-      <c r="G15" s="5">
-        <v>71454.61</v>
-      </c>
-      <c r="H15" s="5">
-        <v>7</v>
-      </c>
       <c r="I15" s="5">
-        <v>55280.61</v>
+        <v>70068.61</v>
       </c>
       <c r="J15" s="17">
-        <v>0.09</v>
+        <v>8.94</v>
       </c>
       <c r="K15" s="17">
-        <v>0.2</v>
+        <v>21.38</v>
       </c>
       <c r="L15" s="17">
-        <v>0.57999999999999996</v>
+        <v>59.26</v>
       </c>
       <c r="M15" s="17">
-        <v>0.28000000000000003</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="N15" s="17">
-        <v>0.16</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4383,34 +4383,34 @@
         <v>40</v>
       </c>
       <c r="E16" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="5">
-        <v>68476</v>
+        <v>75869</v>
       </c>
       <c r="H16" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="5">
-        <v>68476</v>
+        <v>75869</v>
       </c>
       <c r="J16" s="17">
-        <v>0.16</v>
+        <v>15.73</v>
       </c>
       <c r="K16" s="17">
-        <v>0.19</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="L16" s="17">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
       <c r="M16" s="17">
-        <v>0.22</v>
+        <v>25</v>
       </c>
       <c r="N16" s="17">
-        <v>0.09</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4427,7 +4427,7 @@
         <v>18</v>
       </c>
       <c r="E17" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -4442,19 +4442,19 @@
         <v>8166</v>
       </c>
       <c r="J17" s="17">
-        <v>0.05</v>
+        <v>5.46</v>
       </c>
       <c r="K17" s="17">
-        <v>0.02</v>
+        <v>2.02</v>
       </c>
       <c r="L17" s="17">
-        <v>0.55000000000000004</v>
+        <v>54.55</v>
       </c>
       <c r="M17" s="17">
-        <v>0.06</v>
+        <v>5.56</v>
       </c>
       <c r="N17" s="17">
-        <v>0.03</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4471,7 +4471,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -4486,19 +4486,19 @@
         <v>8641</v>
       </c>
       <c r="J18" s="17">
-        <v>0.04</v>
+        <v>3.64</v>
       </c>
       <c r="K18" s="17">
-        <v>0.02</v>
+        <v>2.14</v>
       </c>
       <c r="L18" s="17">
-        <v>0.45</v>
+        <v>45.45</v>
       </c>
       <c r="M18" s="17">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="N18" s="17">
-        <v>0.05</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4518,31 +4518,31 @@
         <v>15</v>
       </c>
       <c r="F19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="5">
-        <v>13015.8</v>
+        <v>25054</v>
       </c>
       <c r="H19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5">
-        <v>13015.8</v>
+        <v>25054</v>
       </c>
       <c r="J19" s="17">
-        <v>0.06</v>
+        <v>5.96</v>
       </c>
       <c r="K19" s="17">
-        <v>0.04</v>
+        <v>6.21</v>
       </c>
       <c r="L19" s="17">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="M19" s="17">
-        <v>0.11</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="N19" s="17">
-        <v>0.06</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4556,10 +4556,10 @@
         <v>22</v>
       </c>
       <c r="D20" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="5">
         <v>2</v>
@@ -4574,19 +4574,19 @@
         <v>16532</v>
       </c>
       <c r="J20" s="17">
-        <v>0.04</v>
+        <v>3.97</v>
       </c>
       <c r="K20" s="17">
-        <v>0.05</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L20" s="17">
-        <v>0.42</v>
+        <v>45.83</v>
       </c>
       <c r="M20" s="17">
-        <v>0.2</v>
+        <v>18.18</v>
       </c>
       <c r="N20" s="17">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B92D9B3-E03E-4167-BAB8-D65EDAEF4C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E69D77-2C2F-4986-88C5-6492C29BA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="135">
   <si>
     <t>Tab 1 — KPI Data</t>
   </si>
@@ -427,9 +427,6 @@
   </si>
   <si>
     <t>Utah -  Single Form</t>
-  </si>
-  <si>
-    <t>BAC San Antonio</t>
   </si>
   <si>
     <t>LifeSource_VRC_Bay Area 2</t>
@@ -4733,7 +4730,7 @@
         <v>667.25</v>
       </c>
       <c r="G5" s="5">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H5" s="5">
         <v>70</v>
@@ -4873,19 +4870,19 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H9" s="5">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I9" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="5">
-        <v>342710.37</v>
+        <v>341967.37</v>
       </c>
       <c r="K9" s="5">
-        <v>23.92</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5013,7 +5010,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5118,7 +5115,7 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
@@ -5226,16 +5223,16 @@
         <v>250</v>
       </c>
       <c r="H19" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I19" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J19" s="5">
-        <v>356094.91</v>
+        <v>348300.91</v>
       </c>
       <c r="K19" s="5">
-        <v>34.909999999999997</v>
+        <v>34.119999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5573,7 +5570,7 @@
         <v>14.33</v>
       </c>
       <c r="G29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29">
         <v>7</v>
@@ -6063,10 +6060,10 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G43">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43">
         <v>7</v>
@@ -7275,7 +7272,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B79">
         <v>2025</v>
@@ -7310,7 +7307,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B80">
         <v>2025</v>
@@ -7330,7 +7327,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B81">
         <v>2025</v>
@@ -7350,7 +7347,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B82">
         <v>2025</v>
@@ -7385,7 +7382,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B83">
         <v>2025</v>
@@ -7405,7 +7402,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B84">
         <v>2025</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B85">
         <v>2025</v>
@@ -7460,7 +7457,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B86">
         <v>2025</v>
@@ -7495,7 +7492,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B87">
         <v>2025</v>
@@ -7530,7 +7527,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B88">
         <v>2025</v>
@@ -7565,7 +7562,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B89">
         <v>2025</v>
@@ -7600,7 +7597,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B90">
         <v>2025</v>
@@ -7635,7 +7632,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B91">
         <v>2026</v>
@@ -7670,7 +7667,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B92">
         <v>2026</v>
@@ -7705,7 +7702,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B93">
         <v>2026</v>
@@ -7740,7 +7737,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B94">
         <v>2026</v>
@@ -8468,7 +8465,7 @@
         <v>87.75</v>
       </c>
       <c r="G116">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H116">
         <v>28</v>
@@ -8573,7 +8570,7 @@
         <v>50.47</v>
       </c>
       <c r="G119">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H119">
         <v>19</v>
@@ -9133,7 +9130,7 @@
         <v>8.01</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H135">
         <v>2</v>
@@ -10344,7 +10341,7 @@
         <v>65.849999999999994</v>
       </c>
       <c r="G172">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H172">
         <v>15</v>
@@ -13327,7 +13324,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B259">
         <v>2025</v>
@@ -13347,7 +13344,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B260">
         <v>2025</v>
@@ -13367,7 +13364,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B261">
         <v>2025</v>
@@ -13387,7 +13384,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B262">
         <v>2025</v>
@@ -13407,7 +13404,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B263">
         <v>2025</v>
@@ -13427,7 +13424,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B264">
         <v>2025</v>
@@ -13447,7 +13444,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B265">
         <v>2025</v>
@@ -13467,7 +13464,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B266">
         <v>2025</v>
@@ -13487,7 +13484,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B267">
         <v>2025</v>
@@ -13910,7 +13907,7 @@
         <v>22.8</v>
       </c>
       <c r="G279">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H279">
         <v>12</v>
@@ -14050,10 +14047,10 @@
         <v>70.47</v>
       </c>
       <c r="G283">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H283">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I283">
         <v>8</v>
@@ -14295,10 +14292,10 @@
         <v>93.92</v>
       </c>
       <c r="G290">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H290">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I290">
         <v>5</v>
@@ -14385,7 +14382,7 @@
         <v>196.53</v>
       </c>
       <c r="G293">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293">
         <v>35</v>
@@ -14860,7 +14857,7 @@
         <v>237.06</v>
       </c>
       <c r="G307">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H307">
         <v>32</v>
@@ -15350,7 +15347,7 @@
         <v>153.71</v>
       </c>
       <c r="G321">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H321">
         <v>10</v>
@@ -15860,7 +15857,7 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G336">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H336">
         <v>23</v>
@@ -16070,10 +16067,10 @@
         <v>51.08</v>
       </c>
       <c r="G342">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H342">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I342">
         <v>6</v>
@@ -16315,19 +16312,19 @@
         <v>81.229999999999905</v>
       </c>
       <c r="G349">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H349">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I349">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J349">
-        <v>44060.479999999901</v>
+        <v>51854.48</v>
       </c>
       <c r="K349">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
@@ -17382,7 +17379,7 @@
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B380">
         <v>2025</v>
@@ -17402,7 +17399,7 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B381">
         <v>2025</v>
@@ -17422,7 +17419,7 @@
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B382">
         <v>2025</v>
@@ -17442,7 +17439,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B383">
         <v>2025</v>
@@ -17477,7 +17474,7 @@
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B384">
         <v>2025</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E69D77-2C2F-4986-88C5-6492C29BA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE1A9BD-2FC2-4D77-9CF0-CCA186A3E94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -4736,13 +4736,13 @@
         <v>70</v>
       </c>
       <c r="I5" s="5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" s="5">
-        <v>366703.45</v>
+        <v>367284.45</v>
       </c>
       <c r="K5" s="5">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4765,7 +4765,7 @@
         <v>425.17</v>
       </c>
       <c r="G6" s="5">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H6" s="5">
         <v>110</v>
@@ -4835,19 +4835,19 @@
         <v>354.93</v>
       </c>
       <c r="G8" s="5">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H8" s="5">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I8" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" s="5">
-        <v>401414.38</v>
+        <v>394170.38</v>
       </c>
       <c r="K8" s="5">
-        <v>9</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4870,7 +4870,7 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H9" s="5">
         <v>105</v>
@@ -4905,7 +4905,7 @@
         <v>322.38</v>
       </c>
       <c r="G10" s="5">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H10" s="5">
         <v>109</v>
@@ -5010,7 +5010,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5080,7 +5080,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -5115,19 +5115,19 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
       </c>
       <c r="I16" s="5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" s="5">
-        <v>504461.62</v>
+        <v>509480.62</v>
       </c>
       <c r="K16" s="5">
-        <v>32.369999999999997</v>
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5220,19 +5220,19 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H19" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I19" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J19" s="5">
-        <v>348300.91</v>
+        <v>356094.91</v>
       </c>
       <c r="K19" s="5">
-        <v>34.119999999999997</v>
+        <v>34.909999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5255,19 +5255,19 @@
         <v>254.45</v>
       </c>
       <c r="G20">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="H20">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I20">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J20">
-        <v>157989.65</v>
+        <v>196212.66999999899</v>
       </c>
       <c r="K20">
-        <v>31.52</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5815,19 +5815,19 @@
         <v>24.96</v>
       </c>
       <c r="G36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H36">
         <v>9</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>15765.68</v>
+        <v>23381.68</v>
       </c>
       <c r="K36">
-        <v>1.2</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -6375,19 +6375,19 @@
         <v>149.57</v>
       </c>
       <c r="G52">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H52">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>15885.119999999901</v>
+        <v>38106.129999999997</v>
       </c>
       <c r="K52">
-        <v>-0.56000000000000005</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
@@ -7755,10 +7755,10 @@
         <v>74.97</v>
       </c>
       <c r="G94">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H94">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8269,6 +8269,21 @@
       <c r="F110">
         <v>4</v>
       </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>-1</v>
+      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -8570,7 +8585,7 @@
         <v>50.47</v>
       </c>
       <c r="G119">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H119">
         <v>19</v>
@@ -8640,10 +8655,10 @@
         <v>104.45</v>
       </c>
       <c r="G121">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H121">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I121">
         <v>13</v>
@@ -8815,7 +8830,7 @@
         <v>50.36</v>
       </c>
       <c r="G126">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H126">
         <v>11</v>
@@ -9130,7 +9145,7 @@
         <v>8.01</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135">
         <v>2</v>
@@ -10586,10 +10601,10 @@
         <v>88.43</v>
       </c>
       <c r="G179">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H179">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I179">
         <v>5</v>
@@ -10662,19 +10677,19 @@
         <v>174.41</v>
       </c>
       <c r="G182">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182">
-        <v>7499</v>
+        <v>8398</v>
       </c>
       <c r="K182">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
@@ -11207,10 +11222,10 @@
         <v>13.91</v>
       </c>
       <c r="G198">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H198">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -11767,7 +11782,7 @@
         <v>8.5</v>
       </c>
       <c r="G214">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H214">
         <v>2</v>
@@ -12327,19 +12342,19 @@
         <v>42.38</v>
       </c>
       <c r="G230">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H230">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J230">
-        <v>7652.78</v>
+        <v>15351.779999999901</v>
       </c>
       <c r="K230">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
@@ -13097,19 +13112,19 @@
         <v>60</v>
       </c>
       <c r="G252">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H252">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252">
-        <v>0</v>
+        <v>4004</v>
       </c>
       <c r="K252">
-        <v>-1</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
@@ -14047,10 +14062,10 @@
         <v>70.47</v>
       </c>
       <c r="G283">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H283">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I283">
         <v>8</v>
@@ -14292,10 +14307,10 @@
         <v>93.92</v>
       </c>
       <c r="G290">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H290">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I290">
         <v>5</v>
@@ -14382,7 +14397,7 @@
         <v>196.53</v>
       </c>
       <c r="G293">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293">
         <v>35</v>
@@ -14522,19 +14537,19 @@
         <v>90.52</v>
       </c>
       <c r="G297">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H297">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I297">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J297">
-        <v>41455.96</v>
+        <v>54609.96</v>
       </c>
       <c r="K297">
-        <v>0.51</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
@@ -14767,19 +14782,19 @@
         <v>148.13999999999999</v>
       </c>
       <c r="G304">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H304">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I304">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J304">
-        <v>14738</v>
+        <v>30257</v>
       </c>
       <c r="K304">
-        <v>-0.47</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
@@ -14997,19 +15012,19 @@
         <v>95.25</v>
       </c>
       <c r="G311">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H311">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I311">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J311">
-        <v>108090.19</v>
+        <v>101762.3</v>
       </c>
       <c r="K311">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
@@ -15347,10 +15362,10 @@
         <v>153.71</v>
       </c>
       <c r="G321">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H321">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I321">
         <v>3</v>
@@ -15787,10 +15802,10 @@
         <v>40.9</v>
       </c>
       <c r="G334">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H334">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I334">
         <v>1</v>
@@ -15857,7 +15872,7 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G336">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H336">
         <v>23</v>
@@ -16347,19 +16362,19 @@
         <v>78.37</v>
       </c>
       <c r="G350">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H350">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J350">
-        <v>0</v>
+        <v>8353</v>
       </c>
       <c r="K350">
-        <v>-1</v>
+        <v>-0.55000000000000004</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
@@ -17012,19 +17027,19 @@
         <v>60.65</v>
       </c>
       <c r="G369">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H369">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I369">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J369">
-        <v>26825.68</v>
+        <v>27841.64</v>
       </c>
       <c r="K369">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
@@ -17152,19 +17167,19 @@
         <v>71.02</v>
       </c>
       <c r="G373">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H373">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I373">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J373">
-        <v>0</v>
+        <v>7311</v>
       </c>
       <c r="K373">
-        <v>-1</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
@@ -18077,10 +18092,10 @@
         <v>34.68</v>
       </c>
       <c r="G402">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H402">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I402">
         <v>2</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE1A9BD-2FC2-4D77-9CF0-CCA186A3E94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E69D77-2C2F-4986-88C5-6492C29BA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -4736,13 +4736,13 @@
         <v>70</v>
       </c>
       <c r="I5" s="5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J5" s="5">
-        <v>367284.45</v>
+        <v>366703.45</v>
       </c>
       <c r="K5" s="5">
-        <v>11.62</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4765,7 +4765,7 @@
         <v>425.17</v>
       </c>
       <c r="G6" s="5">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H6" s="5">
         <v>110</v>
@@ -4835,19 +4835,19 @@
         <v>354.93</v>
       </c>
       <c r="G8" s="5">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H8" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J8" s="5">
-        <v>394170.38</v>
+        <v>401414.38</v>
       </c>
       <c r="K8" s="5">
-        <v>8.82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4870,7 +4870,7 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H9" s="5">
         <v>105</v>
@@ -4905,7 +4905,7 @@
         <v>322.38</v>
       </c>
       <c r="G10" s="5">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H10" s="5">
         <v>109</v>
@@ -5010,7 +5010,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5080,7 +5080,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -5115,19 +5115,19 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
       </c>
       <c r="I16" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J16" s="5">
-        <v>509480.62</v>
+        <v>504461.62</v>
       </c>
       <c r="K16" s="5">
-        <v>32.700000000000003</v>
+        <v>32.369999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5220,19 +5220,19 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H19" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I19" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J19" s="5">
-        <v>356094.91</v>
+        <v>348300.91</v>
       </c>
       <c r="K19" s="5">
-        <v>34.909999999999997</v>
+        <v>34.119999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5255,19 +5255,19 @@
         <v>254.45</v>
       </c>
       <c r="G20">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="H20">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="I20">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J20">
-        <v>196212.66999999899</v>
+        <v>157989.65</v>
       </c>
       <c r="K20">
-        <v>39.39</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5815,19 +5815,19 @@
         <v>24.96</v>
       </c>
       <c r="G36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H36">
         <v>9</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>23381.68</v>
+        <v>15765.68</v>
       </c>
       <c r="K36">
-        <v>2.27</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -6375,19 +6375,19 @@
         <v>149.57</v>
       </c>
       <c r="G52">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H52">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>38106.129999999997</v>
+        <v>15885.119999999901</v>
       </c>
       <c r="K52">
-        <v>0.04</v>
+        <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
@@ -7755,10 +7755,10 @@
         <v>74.97</v>
       </c>
       <c r="G94">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H94">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8269,21 +8269,6 @@
       <c r="F110">
         <v>4</v>
       </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>-1</v>
-      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -8585,7 +8570,7 @@
         <v>50.47</v>
       </c>
       <c r="G119">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H119">
         <v>19</v>
@@ -8655,10 +8640,10 @@
         <v>104.45</v>
       </c>
       <c r="G121">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H121">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I121">
         <v>13</v>
@@ -8830,7 +8815,7 @@
         <v>50.36</v>
       </c>
       <c r="G126">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H126">
         <v>11</v>
@@ -9145,7 +9130,7 @@
         <v>8.01</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H135">
         <v>2</v>
@@ -10601,10 +10586,10 @@
         <v>88.43</v>
       </c>
       <c r="G179">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H179">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I179">
         <v>5</v>
@@ -10677,19 +10662,19 @@
         <v>174.41</v>
       </c>
       <c r="G182">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H182">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J182">
-        <v>8398</v>
+        <v>7499</v>
       </c>
       <c r="K182">
-        <v>-0.75</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
@@ -11222,10 +11207,10 @@
         <v>13.91</v>
       </c>
       <c r="G198">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H198">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -11782,7 +11767,7 @@
         <v>8.5</v>
       </c>
       <c r="G214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H214">
         <v>2</v>
@@ -12342,19 +12327,19 @@
         <v>42.38</v>
       </c>
       <c r="G230">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H230">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J230">
-        <v>15351.779999999901</v>
+        <v>7652.78</v>
       </c>
       <c r="K230">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
@@ -13112,19 +13097,19 @@
         <v>60</v>
       </c>
       <c r="G252">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H252">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252">
-        <v>4004</v>
+        <v>0</v>
       </c>
       <c r="K252">
-        <v>-0.65</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
@@ -14062,10 +14047,10 @@
         <v>70.47</v>
       </c>
       <c r="G283">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H283">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I283">
         <v>8</v>
@@ -14307,10 +14292,10 @@
         <v>93.92</v>
       </c>
       <c r="G290">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H290">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I290">
         <v>5</v>
@@ -14397,7 +14382,7 @@
         <v>196.53</v>
       </c>
       <c r="G293">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293">
         <v>35</v>
@@ -14537,19 +14522,19 @@
         <v>90.52</v>
       </c>
       <c r="G297">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H297">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I297">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J297">
-        <v>54609.96</v>
+        <v>41455.96</v>
       </c>
       <c r="K297">
-        <v>0.99</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
@@ -14782,19 +14767,19 @@
         <v>148.13999999999999</v>
       </c>
       <c r="G304">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H304">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I304">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J304">
-        <v>30257</v>
+        <v>14738</v>
       </c>
       <c r="K304">
-        <v>0.1</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
@@ -15012,19 +14997,19 @@
         <v>95.25</v>
       </c>
       <c r="G311">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H311">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I311">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J311">
-        <v>101762.3</v>
+        <v>108090.19</v>
       </c>
       <c r="K311">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
@@ -15362,10 +15347,10 @@
         <v>153.71</v>
       </c>
       <c r="G321">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H321">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I321">
         <v>3</v>
@@ -15802,10 +15787,10 @@
         <v>40.9</v>
       </c>
       <c r="G334">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H334">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I334">
         <v>1</v>
@@ -15872,7 +15857,7 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G336">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H336">
         <v>23</v>
@@ -16362,19 +16347,19 @@
         <v>78.37</v>
       </c>
       <c r="G350">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H350">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I350">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350">
-        <v>8353</v>
+        <v>0</v>
       </c>
       <c r="K350">
-        <v>-0.55000000000000004</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
@@ -17027,19 +17012,19 @@
         <v>60.65</v>
       </c>
       <c r="G369">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H369">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J369">
-        <v>27841.64</v>
+        <v>26825.68</v>
       </c>
       <c r="K369">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
@@ -17167,19 +17152,19 @@
         <v>71.02</v>
       </c>
       <c r="G373">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H373">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J373">
-        <v>7311</v>
+        <v>0</v>
       </c>
       <c r="K373">
-        <v>-0.66</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
@@ -18092,10 +18077,10 @@
         <v>34.68</v>
       </c>
       <c r="G402">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H402">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I402">
         <v>2</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6F0716-F4BF-4E15-99F5-C761829F0DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC10BE9F-B800-4719-A04F-19BA7E8A09D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -5354,13 +5354,13 @@
         <v>1</v>
       </c>
       <c r="I33" s="10">
-        <v>7953.68</v>
+        <v>7853.68</v>
       </c>
       <c r="J33" s="10">
         <v>1</v>
       </c>
       <c r="K33" s="10">
-        <v>7953.68</v>
+        <v>7853.68</v>
       </c>
       <c r="L33" s="10">
         <v>6.19</v>
@@ -26157,13 +26157,13 @@
         <v>1</v>
       </c>
       <c r="J162">
-        <v>7953.68</v>
+        <v>7853.68</v>
       </c>
       <c r="K162">
         <v>1</v>
       </c>
       <c r="L162">
-        <v>7953.68</v>
+        <v>7853.68</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC10BE9F-B800-4719-A04F-19BA7E8A09D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A546942D-EA15-4F2A-BD45-26C53609AAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A546942D-EA15-4F2A-BD45-26C53609AAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000009A7-9118-4A21-9F81-BB0F719E5868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -1100,28 +1100,28 @@
         <v>50651.360000000001</v>
       </c>
       <c r="F6" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G6" s="5">
         <v>4</v>
       </c>
       <c r="H6" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
       </c>
       <c r="K6" s="5">
-        <v>527.618333333333</v>
+        <v>522.17896907216402</v>
       </c>
       <c r="L6" s="5">
-        <v>1688.3786666666599</v>
+        <v>1633.91483870967</v>
       </c>
       <c r="M6" s="5">
-        <v>-84.297203470943302</v>
+        <v>-84.494631536053504</v>
       </c>
       <c r="N6" s="6">
         <v>247.61</v>
@@ -1166,7 +1166,7 @@
         <v>392500</v>
       </c>
       <c r="AB6" s="9">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AC6" s="9">
         <v>314</v>
@@ -1258,7 +1258,7 @@
         <v>15000</v>
       </c>
       <c r="AB7" s="9">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC7" s="9">
         <v>71</v>
@@ -2451,8 +2451,12 @@
       <c r="AA25" s="8">
         <v>7000</v>
       </c>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
+      <c r="AB25" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC25" s="9">
+        <v>2</v>
+      </c>
       <c r="AD25" s="13">
         <v>46146</v>
       </c>
@@ -2524,10 +2528,10 @@
         <v>12000</v>
       </c>
       <c r="AB26" s="9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AC26" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD26" s="13">
         <v>46146</v>
@@ -3495,7 +3499,7 @@
         <v>672.01666666666597</v>
       </c>
       <c r="M40" s="5">
-        <v>294.51799310532903</v>
+        <v>289.55779866570703</v>
       </c>
       <c r="N40" s="6">
         <v>8.02</v>
@@ -3731,85 +3735,28 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44">
+        <v>139</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
         <v>2</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44">
-        <v>972.12</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>2</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>486.06</v>
-      </c>
-      <c r="M44">
-        <v>-100</v>
-      </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
-      <c r="O44">
-        <v>381.49</v>
-      </c>
-      <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>381.49</v>
-      </c>
-      <c r="U44">
-        <v>-100</v>
-      </c>
-      <c r="V44">
-        <v>23.02</v>
-      </c>
-      <c r="W44">
-        <v>4636.55</v>
-      </c>
-      <c r="X44">
-        <v>23</v>
-      </c>
-      <c r="Y44">
-        <v>9</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>11000</v>
-      </c>
-      <c r="AB44">
-        <v>14</v>
-      </c>
       <c r="AC44">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD44" s="13">
         <v>46146</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000009A7-9118-4A21-9F81-BB0F719E5868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FBD425-8755-474A-AC31-9986E84D80E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -592,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -641,6 +641,7 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5044,10 +5045,10 @@
         <v>9</v>
       </c>
       <c r="F28" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -5068,11 +5069,9 @@
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="O28" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O28" s="10"/>
       <c r="P28" s="10">
         <v>0</v>
       </c>
@@ -5094,7 +5093,7 @@
         <v>9</v>
       </c>
       <c r="F29" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="10">
         <v>1</v>
@@ -5118,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>45.45</v>
+        <v>36.36</v>
       </c>
       <c r="O29" s="10">
         <v>0</v>
@@ -24555,7 +24554,7 @@
         <v>16532</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>117</v>
       </c>
@@ -24565,31 +24564,31 @@
       <c r="C122" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="10">
-        <v>1</v>
-      </c>
-      <c r="F122" s="10">
-        <v>1</v>
-      </c>
-      <c r="G122" s="10">
-        <v>1</v>
-      </c>
-      <c r="H122" s="10">
-        <v>0</v>
-      </c>
-      <c r="I122" s="10">
-        <v>0</v>
-      </c>
-      <c r="J122" s="10">
-        <v>0</v>
-      </c>
-      <c r="K122" s="10">
-        <v>0</v>
-      </c>
-      <c r="L122" s="10">
+      <c r="E122" s="20">
+        <v>1</v>
+      </c>
+      <c r="F122" s="20">
+        <v>1</v>
+      </c>
+      <c r="G122" s="20">
+        <v>1</v>
+      </c>
+      <c r="H122" s="20">
+        <v>0</v>
+      </c>
+      <c r="I122" s="20">
+        <v>0</v>
+      </c>
+      <c r="J122" s="20">
+        <v>0</v>
+      </c>
+      <c r="K122" s="20">
+        <v>0</v>
+      </c>
+      <c r="L122" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24603,31 +24602,31 @@
       <c r="C123" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="20">
         <v>6</v>
       </c>
-      <c r="F123" s="10">
+      <c r="F123" s="20">
         <v>4</v>
       </c>
-      <c r="G123" s="10">
+      <c r="G123" s="20">
         <v>3</v>
       </c>
-      <c r="H123" s="10">
-        <v>1</v>
-      </c>
-      <c r="I123" s="10">
-        <v>0</v>
-      </c>
-      <c r="J123" s="10">
-        <v>0</v>
-      </c>
-      <c r="K123" s="10">
-        <v>0</v>
-      </c>
-      <c r="L123" s="10">
+      <c r="H123" s="20">
+        <v>1</v>
+      </c>
+      <c r="I123" s="20">
+        <v>0</v>
+      </c>
+      <c r="J123" s="20">
+        <v>0</v>
+      </c>
+      <c r="K123" s="20">
+        <v>0</v>
+      </c>
+      <c r="L123" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24641,31 +24640,31 @@
       <c r="C124" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E124" s="10">
+      <c r="E124" s="20">
         <v>3</v>
       </c>
-      <c r="F124" s="10">
+      <c r="F124" s="20">
         <v>3</v>
       </c>
-      <c r="G124" s="10">
-        <v>1</v>
-      </c>
-      <c r="H124" s="10">
-        <v>0</v>
-      </c>
-      <c r="I124" s="10">
-        <v>0</v>
-      </c>
-      <c r="J124" s="10">
-        <v>0</v>
-      </c>
-      <c r="K124" s="10">
-        <v>0</v>
-      </c>
-      <c r="L124" s="10">
+      <c r="G124" s="20">
+        <v>1</v>
+      </c>
+      <c r="H124" s="20">
+        <v>0</v>
+      </c>
+      <c r="I124" s="20">
+        <v>0</v>
+      </c>
+      <c r="J124" s="20">
+        <v>0</v>
+      </c>
+      <c r="K124" s="20">
+        <v>0</v>
+      </c>
+      <c r="L124" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24679,31 +24678,31 @@
       <c r="C125" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E125" s="10">
+      <c r="E125" s="20">
         <v>2</v>
       </c>
-      <c r="F125" s="10">
+      <c r="F125" s="20">
         <v>2</v>
       </c>
-      <c r="G125" s="10">
-        <v>0</v>
-      </c>
-      <c r="H125" s="10">
-        <v>0</v>
-      </c>
-      <c r="I125" s="10">
-        <v>0</v>
-      </c>
-      <c r="J125" s="10">
-        <v>0</v>
-      </c>
-      <c r="K125" s="10">
-        <v>0</v>
-      </c>
-      <c r="L125" s="10">
+      <c r="G125" s="20">
+        <v>0</v>
+      </c>
+      <c r="H125" s="20">
+        <v>0</v>
+      </c>
+      <c r="I125" s="20">
+        <v>0</v>
+      </c>
+      <c r="J125" s="20">
+        <v>0</v>
+      </c>
+      <c r="K125" s="20">
+        <v>0</v>
+      </c>
+      <c r="L125" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24717,31 +24716,31 @@
       <c r="C126" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E126" s="10">
-        <v>1</v>
-      </c>
-      <c r="F126" s="10">
-        <v>1</v>
-      </c>
-      <c r="G126" s="10">
-        <v>1</v>
-      </c>
-      <c r="H126" s="10">
-        <v>1</v>
-      </c>
-      <c r="I126" s="10">
-        <v>0</v>
-      </c>
-      <c r="J126" s="10">
-        <v>0</v>
-      </c>
-      <c r="K126" s="10">
-        <v>0</v>
-      </c>
-      <c r="L126" s="10">
+      <c r="E126" s="20">
+        <v>1</v>
+      </c>
+      <c r="F126" s="20">
+        <v>1</v>
+      </c>
+      <c r="G126" s="20">
+        <v>1</v>
+      </c>
+      <c r="H126" s="20">
+        <v>1</v>
+      </c>
+      <c r="I126" s="20">
+        <v>0</v>
+      </c>
+      <c r="J126" s="20">
+        <v>0</v>
+      </c>
+      <c r="K126" s="20">
+        <v>0</v>
+      </c>
+      <c r="L126" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24755,31 +24754,31 @@
       <c r="C127" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E127" s="10">
-        <v>1</v>
-      </c>
-      <c r="F127" s="10">
-        <v>1</v>
-      </c>
-      <c r="G127" s="10">
-        <v>1</v>
-      </c>
-      <c r="H127" s="10">
-        <v>0</v>
-      </c>
-      <c r="I127" s="10">
-        <v>0</v>
-      </c>
-      <c r="J127" s="10">
-        <v>0</v>
-      </c>
-      <c r="K127" s="10">
-        <v>0</v>
-      </c>
-      <c r="L127" s="10">
+      <c r="E127" s="20">
+        <v>1</v>
+      </c>
+      <c r="F127" s="20">
+        <v>1</v>
+      </c>
+      <c r="G127" s="20">
+        <v>1</v>
+      </c>
+      <c r="H127" s="20">
+        <v>0</v>
+      </c>
+      <c r="I127" s="20">
+        <v>0</v>
+      </c>
+      <c r="J127" s="20">
+        <v>0</v>
+      </c>
+      <c r="K127" s="20">
+        <v>0</v>
+      </c>
+      <c r="L127" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24793,31 +24792,31 @@
       <c r="C128" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="20">
         <v>6</v>
       </c>
-      <c r="F128" s="10">
+      <c r="F128" s="20">
         <v>5</v>
       </c>
-      <c r="G128" s="10">
+      <c r="G128" s="20">
         <v>2</v>
       </c>
-      <c r="H128" s="10">
-        <v>0</v>
-      </c>
-      <c r="I128" s="10">
-        <v>0</v>
-      </c>
-      <c r="J128" s="10">
-        <v>0</v>
-      </c>
-      <c r="K128" s="10">
-        <v>0</v>
-      </c>
-      <c r="L128" s="10">
+      <c r="H128" s="20">
+        <v>0</v>
+      </c>
+      <c r="I128" s="20">
+        <v>0</v>
+      </c>
+      <c r="J128" s="20">
+        <v>0</v>
+      </c>
+      <c r="K128" s="20">
+        <v>0</v>
+      </c>
+      <c r="L128" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24831,31 +24830,31 @@
       <c r="C129" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="D129" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E129" s="10">
-        <v>1</v>
-      </c>
-      <c r="F129" s="10">
-        <v>1</v>
-      </c>
-      <c r="G129" s="10">
-        <v>0</v>
-      </c>
-      <c r="H129" s="10">
-        <v>1</v>
-      </c>
-      <c r="I129" s="10">
-        <v>0</v>
-      </c>
-      <c r="J129" s="10">
-        <v>0</v>
-      </c>
-      <c r="K129" s="10">
-        <v>0</v>
-      </c>
-      <c r="L129" s="10">
+      <c r="E129" s="20">
+        <v>1</v>
+      </c>
+      <c r="F129" s="20">
+        <v>1</v>
+      </c>
+      <c r="G129" s="20">
+        <v>0</v>
+      </c>
+      <c r="H129" s="20">
+        <v>1</v>
+      </c>
+      <c r="I129" s="20">
+        <v>0</v>
+      </c>
+      <c r="J129" s="20">
+        <v>0</v>
+      </c>
+      <c r="K129" s="20">
+        <v>0</v>
+      </c>
+      <c r="L129" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24869,31 +24868,31 @@
       <c r="C130" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E130" s="10">
-        <v>1</v>
-      </c>
-      <c r="F130" s="10">
-        <v>1</v>
-      </c>
-      <c r="G130" s="10">
-        <v>0</v>
-      </c>
-      <c r="H130" s="10">
-        <v>0</v>
-      </c>
-      <c r="I130" s="10">
-        <v>0</v>
-      </c>
-      <c r="J130" s="10">
-        <v>0</v>
-      </c>
-      <c r="K130" s="10">
-        <v>0</v>
-      </c>
-      <c r="L130" s="10">
+      <c r="E130" s="20">
+        <v>1</v>
+      </c>
+      <c r="F130" s="20">
+        <v>1</v>
+      </c>
+      <c r="G130" s="20">
+        <v>0</v>
+      </c>
+      <c r="H130" s="20">
+        <v>0</v>
+      </c>
+      <c r="I130" s="20">
+        <v>0</v>
+      </c>
+      <c r="J130" s="20">
+        <v>0</v>
+      </c>
+      <c r="K130" s="20">
+        <v>0</v>
+      </c>
+      <c r="L130" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24907,31 +24906,31 @@
       <c r="C131" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="D131" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E131" s="10">
-        <v>1</v>
-      </c>
-      <c r="F131" s="10">
-        <v>1</v>
-      </c>
-      <c r="G131" s="10">
-        <v>1</v>
-      </c>
-      <c r="H131" s="10">
-        <v>0</v>
-      </c>
-      <c r="I131" s="10">
-        <v>0</v>
-      </c>
-      <c r="J131" s="10">
-        <v>0</v>
-      </c>
-      <c r="K131" s="10">
-        <v>0</v>
-      </c>
-      <c r="L131" s="10">
+      <c r="E131" s="20">
+        <v>1</v>
+      </c>
+      <c r="F131" s="20">
+        <v>1</v>
+      </c>
+      <c r="G131" s="20">
+        <v>1</v>
+      </c>
+      <c r="H131" s="20">
+        <v>0</v>
+      </c>
+      <c r="I131" s="20">
+        <v>0</v>
+      </c>
+      <c r="J131" s="20">
+        <v>0</v>
+      </c>
+      <c r="K131" s="20">
+        <v>0</v>
+      </c>
+      <c r="L131" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24945,31 +24944,31 @@
       <c r="C132" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E132" s="10">
-        <v>1</v>
-      </c>
-      <c r="F132" s="10">
-        <v>0</v>
-      </c>
-      <c r="G132" s="10">
-        <v>0</v>
-      </c>
-      <c r="H132" s="10">
-        <v>0</v>
-      </c>
-      <c r="I132" s="10">
-        <v>0</v>
-      </c>
-      <c r="J132" s="10">
-        <v>0</v>
-      </c>
-      <c r="K132" s="10">
-        <v>0</v>
-      </c>
-      <c r="L132" s="10">
+      <c r="E132" s="20">
+        <v>1</v>
+      </c>
+      <c r="F132" s="20">
+        <v>0</v>
+      </c>
+      <c r="G132" s="20">
+        <v>0</v>
+      </c>
+      <c r="H132" s="20">
+        <v>0</v>
+      </c>
+      <c r="I132" s="20">
+        <v>0</v>
+      </c>
+      <c r="J132" s="20">
+        <v>0</v>
+      </c>
+      <c r="K132" s="20">
+        <v>0</v>
+      </c>
+      <c r="L132" s="20">
         <v>0</v>
       </c>
     </row>
@@ -24983,31 +24982,31 @@
       <c r="C133" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="20">
         <v>3</v>
       </c>
-      <c r="F133" s="10">
+      <c r="F133" s="20">
         <v>3</v>
       </c>
-      <c r="G133" s="10">
-        <v>1</v>
-      </c>
-      <c r="H133" s="10">
-        <v>0</v>
-      </c>
-      <c r="I133" s="10">
-        <v>0</v>
-      </c>
-      <c r="J133" s="10">
-        <v>0</v>
-      </c>
-      <c r="K133" s="10">
-        <v>0</v>
-      </c>
-      <c r="L133" s="10">
+      <c r="G133" s="20">
+        <v>1</v>
+      </c>
+      <c r="H133" s="20">
+        <v>0</v>
+      </c>
+      <c r="I133" s="20">
+        <v>0</v>
+      </c>
+      <c r="J133" s="20">
+        <v>0</v>
+      </c>
+      <c r="K133" s="20">
+        <v>0</v>
+      </c>
+      <c r="L133" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25021,31 +25020,31 @@
       <c r="C134" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="D134" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="20">
         <v>2</v>
       </c>
-      <c r="F134" s="10">
+      <c r="F134" s="20">
         <v>2</v>
       </c>
-      <c r="G134" s="10">
-        <v>1</v>
-      </c>
-      <c r="H134" s="10">
-        <v>0</v>
-      </c>
-      <c r="I134" s="10">
-        <v>0</v>
-      </c>
-      <c r="J134" s="10">
-        <v>0</v>
-      </c>
-      <c r="K134" s="10">
-        <v>0</v>
-      </c>
-      <c r="L134" s="10">
+      <c r="G134" s="20">
+        <v>1</v>
+      </c>
+      <c r="H134" s="20">
+        <v>0</v>
+      </c>
+      <c r="I134" s="20">
+        <v>0</v>
+      </c>
+      <c r="J134" s="20">
+        <v>0</v>
+      </c>
+      <c r="K134" s="20">
+        <v>0</v>
+      </c>
+      <c r="L134" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25059,31 +25058,31 @@
       <c r="C135" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="D135" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="20">
         <v>3</v>
       </c>
-      <c r="F135" s="10">
+      <c r="F135" s="20">
         <v>3</v>
       </c>
-      <c r="G135" s="10">
+      <c r="G135" s="20">
         <v>2</v>
       </c>
-      <c r="H135" s="10">
-        <v>0</v>
-      </c>
-      <c r="I135" s="10">
-        <v>0</v>
-      </c>
-      <c r="J135" s="10">
-        <v>0</v>
-      </c>
-      <c r="K135" s="10">
-        <v>0</v>
-      </c>
-      <c r="L135" s="10">
+      <c r="H135" s="20">
+        <v>0</v>
+      </c>
+      <c r="I135" s="20">
+        <v>0</v>
+      </c>
+      <c r="J135" s="20">
+        <v>0</v>
+      </c>
+      <c r="K135" s="20">
+        <v>0</v>
+      </c>
+      <c r="L135" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25097,31 +25096,31 @@
       <c r="C136" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E136" s="10">
+      <c r="E136" s="20">
         <v>3</v>
       </c>
-      <c r="F136" s="10">
+      <c r="F136" s="20">
         <v>3</v>
       </c>
-      <c r="G136" s="10">
-        <v>1</v>
-      </c>
-      <c r="H136" s="10">
-        <v>1</v>
-      </c>
-      <c r="I136" s="10">
-        <v>0</v>
-      </c>
-      <c r="J136" s="10">
-        <v>0</v>
-      </c>
-      <c r="K136" s="10">
-        <v>0</v>
-      </c>
-      <c r="L136" s="10">
+      <c r="G136" s="20">
+        <v>1</v>
+      </c>
+      <c r="H136" s="20">
+        <v>1</v>
+      </c>
+      <c r="I136" s="20">
+        <v>0</v>
+      </c>
+      <c r="J136" s="20">
+        <v>0</v>
+      </c>
+      <c r="K136" s="20">
+        <v>0</v>
+      </c>
+      <c r="L136" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25135,31 +25134,31 @@
       <c r="C137" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D137" s="10" t="s">
+      <c r="D137" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="20">
         <v>2</v>
       </c>
-      <c r="F137" s="10">
+      <c r="F137" s="20">
         <v>2</v>
       </c>
-      <c r="G137" s="10">
-        <v>0</v>
-      </c>
-      <c r="H137" s="10">
-        <v>0</v>
-      </c>
-      <c r="I137" s="10">
-        <v>0</v>
-      </c>
-      <c r="J137" s="10">
-        <v>0</v>
-      </c>
-      <c r="K137" s="10">
-        <v>0</v>
-      </c>
-      <c r="L137" s="10">
+      <c r="G137" s="20">
+        <v>0</v>
+      </c>
+      <c r="H137" s="20">
+        <v>0</v>
+      </c>
+      <c r="I137" s="20">
+        <v>0</v>
+      </c>
+      <c r="J137" s="20">
+        <v>0</v>
+      </c>
+      <c r="K137" s="20">
+        <v>0</v>
+      </c>
+      <c r="L137" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25173,31 +25172,31 @@
       <c r="C138" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="D138" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E138" s="10">
+      <c r="E138" s="20">
         <v>2</v>
       </c>
-      <c r="F138" s="10">
+      <c r="F138" s="20">
         <v>2</v>
       </c>
-      <c r="G138" s="10">
-        <v>1</v>
-      </c>
-      <c r="H138" s="10">
-        <v>1</v>
-      </c>
-      <c r="I138" s="10">
-        <v>0</v>
-      </c>
-      <c r="J138" s="10">
-        <v>0</v>
-      </c>
-      <c r="K138" s="10">
-        <v>0</v>
-      </c>
-      <c r="L138" s="10">
+      <c r="G138" s="20">
+        <v>1</v>
+      </c>
+      <c r="H138" s="20">
+        <v>1</v>
+      </c>
+      <c r="I138" s="20">
+        <v>0</v>
+      </c>
+      <c r="J138" s="20">
+        <v>0</v>
+      </c>
+      <c r="K138" s="20">
+        <v>0</v>
+      </c>
+      <c r="L138" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25211,31 +25210,31 @@
       <c r="C139" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="D139" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E139" s="10">
+      <c r="E139" s="20">
         <v>2</v>
       </c>
-      <c r="F139" s="10">
+      <c r="F139" s="20">
         <v>2</v>
       </c>
-      <c r="G139" s="10">
-        <v>0</v>
-      </c>
-      <c r="H139" s="10">
-        <v>0</v>
-      </c>
-      <c r="I139" s="10">
-        <v>0</v>
-      </c>
-      <c r="J139" s="10">
-        <v>0</v>
-      </c>
-      <c r="K139" s="10">
-        <v>0</v>
-      </c>
-      <c r="L139" s="10">
+      <c r="G139" s="20">
+        <v>0</v>
+      </c>
+      <c r="H139" s="20">
+        <v>0</v>
+      </c>
+      <c r="I139" s="20">
+        <v>0</v>
+      </c>
+      <c r="J139" s="20">
+        <v>0</v>
+      </c>
+      <c r="K139" s="20">
+        <v>0</v>
+      </c>
+      <c r="L139" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25249,31 +25248,31 @@
       <c r="C140" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D140" s="10" t="s">
+      <c r="D140" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E140" s="10">
-        <v>1</v>
-      </c>
-      <c r="F140" s="10">
-        <v>1</v>
-      </c>
-      <c r="G140" s="10">
-        <v>1</v>
-      </c>
-      <c r="H140" s="10">
-        <v>0</v>
-      </c>
-      <c r="I140" s="10">
-        <v>0</v>
-      </c>
-      <c r="J140" s="10">
-        <v>0</v>
-      </c>
-      <c r="K140" s="10">
-        <v>0</v>
-      </c>
-      <c r="L140" s="10">
+      <c r="E140" s="20">
+        <v>1</v>
+      </c>
+      <c r="F140" s="20">
+        <v>1</v>
+      </c>
+      <c r="G140" s="20">
+        <v>1</v>
+      </c>
+      <c r="H140" s="20">
+        <v>0</v>
+      </c>
+      <c r="I140" s="20">
+        <v>0</v>
+      </c>
+      <c r="J140" s="20">
+        <v>0</v>
+      </c>
+      <c r="K140" s="20">
+        <v>0</v>
+      </c>
+      <c r="L140" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25287,31 +25286,31 @@
       <c r="C141" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D141" s="10" t="s">
+      <c r="D141" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="20">
         <v>5</v>
       </c>
-      <c r="F141" s="10">
+      <c r="F141" s="20">
         <v>4</v>
       </c>
-      <c r="G141" s="10">
-        <v>0</v>
-      </c>
-      <c r="H141" s="10">
-        <v>0</v>
-      </c>
-      <c r="I141" s="10">
-        <v>0</v>
-      </c>
-      <c r="J141" s="10">
-        <v>0</v>
-      </c>
-      <c r="K141" s="10">
-        <v>0</v>
-      </c>
-      <c r="L141" s="10">
+      <c r="G141" s="20">
+        <v>0</v>
+      </c>
+      <c r="H141" s="20">
+        <v>0</v>
+      </c>
+      <c r="I141" s="20">
+        <v>0</v>
+      </c>
+      <c r="J141" s="20">
+        <v>0</v>
+      </c>
+      <c r="K141" s="20">
+        <v>0</v>
+      </c>
+      <c r="L141" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25325,31 +25324,31 @@
       <c r="C142" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D142" s="10" t="s">
+      <c r="D142" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E142" s="10">
-        <v>1</v>
-      </c>
-      <c r="F142" s="10">
-        <v>1</v>
-      </c>
-      <c r="G142" s="10">
-        <v>0</v>
-      </c>
-      <c r="H142" s="10">
-        <v>0</v>
-      </c>
-      <c r="I142" s="10">
-        <v>0</v>
-      </c>
-      <c r="J142" s="10">
-        <v>0</v>
-      </c>
-      <c r="K142" s="10">
-        <v>0</v>
-      </c>
-      <c r="L142" s="10">
+      <c r="E142" s="20">
+        <v>1</v>
+      </c>
+      <c r="F142" s="20">
+        <v>1</v>
+      </c>
+      <c r="G142" s="20">
+        <v>0</v>
+      </c>
+      <c r="H142" s="20">
+        <v>0</v>
+      </c>
+      <c r="I142" s="20">
+        <v>0</v>
+      </c>
+      <c r="J142" s="20">
+        <v>0</v>
+      </c>
+      <c r="K142" s="20">
+        <v>0</v>
+      </c>
+      <c r="L142" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25363,31 +25362,31 @@
       <c r="C143" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="D143" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="20">
         <v>6</v>
       </c>
-      <c r="F143" s="10">
+      <c r="F143" s="20">
         <v>5</v>
       </c>
-      <c r="G143" s="10">
-        <v>0</v>
-      </c>
-      <c r="H143" s="10">
-        <v>1</v>
-      </c>
-      <c r="I143" s="10">
-        <v>0</v>
-      </c>
-      <c r="J143" s="10">
-        <v>0</v>
-      </c>
-      <c r="K143" s="10">
-        <v>0</v>
-      </c>
-      <c r="L143" s="10">
+      <c r="G143" s="20">
+        <v>0</v>
+      </c>
+      <c r="H143" s="20">
+        <v>1</v>
+      </c>
+      <c r="I143" s="20">
+        <v>0</v>
+      </c>
+      <c r="J143" s="20">
+        <v>0</v>
+      </c>
+      <c r="K143" s="20">
+        <v>0</v>
+      </c>
+      <c r="L143" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25401,31 +25400,31 @@
       <c r="C144" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E144" s="10">
-        <v>1</v>
-      </c>
-      <c r="F144" s="10">
-        <v>1</v>
-      </c>
-      <c r="G144" s="10">
-        <v>1</v>
-      </c>
-      <c r="H144" s="10">
-        <v>0</v>
-      </c>
-      <c r="I144" s="10">
-        <v>0</v>
-      </c>
-      <c r="J144" s="10">
-        <v>0</v>
-      </c>
-      <c r="K144" s="10">
-        <v>0</v>
-      </c>
-      <c r="L144" s="10">
+      <c r="E144" s="20">
+        <v>1</v>
+      </c>
+      <c r="F144" s="20">
+        <v>1</v>
+      </c>
+      <c r="G144" s="20">
+        <v>0</v>
+      </c>
+      <c r="H144" s="20">
+        <v>0</v>
+      </c>
+      <c r="I144" s="20">
+        <v>0</v>
+      </c>
+      <c r="J144" s="20">
+        <v>0</v>
+      </c>
+      <c r="K144" s="20">
+        <v>0</v>
+      </c>
+      <c r="L144" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25439,31 +25438,31 @@
       <c r="C145" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="D145" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E145" s="10">
-        <v>1</v>
-      </c>
-      <c r="F145" s="10">
-        <v>1</v>
-      </c>
-      <c r="G145" s="10">
-        <v>0</v>
-      </c>
-      <c r="H145" s="10">
-        <v>0</v>
-      </c>
-      <c r="I145" s="10">
-        <v>0</v>
-      </c>
-      <c r="J145" s="10">
-        <v>0</v>
-      </c>
-      <c r="K145" s="10">
-        <v>0</v>
-      </c>
-      <c r="L145" s="10">
+      <c r="E145" s="20">
+        <v>1</v>
+      </c>
+      <c r="F145" s="20">
+        <v>1</v>
+      </c>
+      <c r="G145" s="20">
+        <v>0</v>
+      </c>
+      <c r="H145" s="20">
+        <v>0</v>
+      </c>
+      <c r="I145" s="20">
+        <v>0</v>
+      </c>
+      <c r="J145" s="20">
+        <v>0</v>
+      </c>
+      <c r="K145" s="20">
+        <v>0</v>
+      </c>
+      <c r="L145" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25477,31 +25476,31 @@
       <c r="C146" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="D146" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E146" s="10">
+      <c r="E146" s="20">
         <v>2</v>
       </c>
-      <c r="F146" s="10">
+      <c r="F146" s="20">
         <v>2</v>
       </c>
-      <c r="G146" s="10">
-        <v>1</v>
-      </c>
-      <c r="H146" s="10">
+      <c r="G146" s="20">
+        <v>0</v>
+      </c>
+      <c r="H146" s="20">
         <v>2</v>
       </c>
-      <c r="I146" s="10">
-        <v>0</v>
-      </c>
-      <c r="J146" s="10">
-        <v>0</v>
-      </c>
-      <c r="K146" s="10">
-        <v>0</v>
-      </c>
-      <c r="L146" s="10">
+      <c r="I146" s="20">
+        <v>0</v>
+      </c>
+      <c r="J146" s="20">
+        <v>0</v>
+      </c>
+      <c r="K146" s="20">
+        <v>0</v>
+      </c>
+      <c r="L146" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25515,31 +25514,31 @@
       <c r="C147" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="D147" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E147" s="10">
+      <c r="E147" s="20">
         <v>2</v>
       </c>
-      <c r="F147" s="10">
-        <v>0</v>
-      </c>
-      <c r="G147" s="10">
-        <v>0</v>
-      </c>
-      <c r="H147" s="10">
-        <v>2</v>
-      </c>
-      <c r="I147" s="10">
-        <v>0</v>
-      </c>
-      <c r="J147" s="10">
-        <v>0</v>
-      </c>
-      <c r="K147" s="10">
-        <v>0</v>
-      </c>
-      <c r="L147" s="10">
+      <c r="F147" s="20">
+        <v>0</v>
+      </c>
+      <c r="G147" s="20">
+        <v>0</v>
+      </c>
+      <c r="H147" s="20">
+        <v>1</v>
+      </c>
+      <c r="I147" s="20">
+        <v>0</v>
+      </c>
+      <c r="J147" s="20">
+        <v>0</v>
+      </c>
+      <c r="K147" s="20">
+        <v>0</v>
+      </c>
+      <c r="L147" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25553,31 +25552,31 @@
       <c r="C148" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="D148" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E148" s="10">
-        <v>1</v>
-      </c>
-      <c r="F148" s="10">
-        <v>1</v>
-      </c>
-      <c r="G148" s="10">
-        <v>0</v>
-      </c>
-      <c r="H148" s="10">
-        <v>0</v>
-      </c>
-      <c r="I148" s="10">
-        <v>0</v>
-      </c>
-      <c r="J148" s="10">
-        <v>0</v>
-      </c>
-      <c r="K148" s="10">
-        <v>0</v>
-      </c>
-      <c r="L148" s="10">
+      <c r="E148" s="20">
+        <v>1</v>
+      </c>
+      <c r="F148" s="20">
+        <v>1</v>
+      </c>
+      <c r="G148" s="20">
+        <v>0</v>
+      </c>
+      <c r="H148" s="20">
+        <v>0</v>
+      </c>
+      <c r="I148" s="20">
+        <v>0</v>
+      </c>
+      <c r="J148" s="20">
+        <v>0</v>
+      </c>
+      <c r="K148" s="20">
+        <v>0</v>
+      </c>
+      <c r="L148" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25591,31 +25590,31 @@
       <c r="C149" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="D149" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E149" s="10">
+      <c r="E149" s="20">
         <v>7</v>
       </c>
-      <c r="F149" s="10">
+      <c r="F149" s="20">
         <v>6</v>
       </c>
-      <c r="G149" s="10">
+      <c r="G149" s="20">
         <v>3</v>
       </c>
-      <c r="H149" s="10">
-        <v>0</v>
-      </c>
-      <c r="I149" s="10">
-        <v>0</v>
-      </c>
-      <c r="J149" s="10">
-        <v>0</v>
-      </c>
-      <c r="K149" s="10">
-        <v>0</v>
-      </c>
-      <c r="L149" s="10">
+      <c r="H149" s="20">
+        <v>0</v>
+      </c>
+      <c r="I149" s="20">
+        <v>0</v>
+      </c>
+      <c r="J149" s="20">
+        <v>0</v>
+      </c>
+      <c r="K149" s="20">
+        <v>0</v>
+      </c>
+      <c r="L149" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25629,31 +25628,31 @@
       <c r="C150" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D150" s="10" t="s">
+      <c r="D150" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E150" s="10">
+      <c r="E150" s="20">
         <v>2</v>
       </c>
-      <c r="F150" s="10">
-        <v>1</v>
-      </c>
-      <c r="G150" s="10">
-        <v>1</v>
-      </c>
-      <c r="H150" s="10">
-        <v>1</v>
-      </c>
-      <c r="I150" s="10">
-        <v>0</v>
-      </c>
-      <c r="J150" s="10">
-        <v>0</v>
-      </c>
-      <c r="K150" s="10">
-        <v>0</v>
-      </c>
-      <c r="L150" s="10">
+      <c r="F150" s="20">
+        <v>1</v>
+      </c>
+      <c r="G150" s="20">
+        <v>0</v>
+      </c>
+      <c r="H150" s="20">
+        <v>1</v>
+      </c>
+      <c r="I150" s="20">
+        <v>0</v>
+      </c>
+      <c r="J150" s="20">
+        <v>0</v>
+      </c>
+      <c r="K150" s="20">
+        <v>0</v>
+      </c>
+      <c r="L150" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25667,31 +25666,31 @@
       <c r="C151" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="D151" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="E151" s="10">
-        <v>1</v>
-      </c>
-      <c r="F151" s="10">
-        <v>1</v>
-      </c>
-      <c r="G151" s="10">
-        <v>1</v>
-      </c>
-      <c r="H151" s="10">
-        <v>0</v>
-      </c>
-      <c r="I151" s="10">
-        <v>0</v>
-      </c>
-      <c r="J151" s="10">
-        <v>0</v>
-      </c>
-      <c r="K151" s="10">
-        <v>0</v>
-      </c>
-      <c r="L151" s="10">
+      <c r="E151" s="20">
+        <v>1</v>
+      </c>
+      <c r="F151" s="20">
+        <v>1</v>
+      </c>
+      <c r="G151" s="20">
+        <v>1</v>
+      </c>
+      <c r="H151" s="20">
+        <v>0</v>
+      </c>
+      <c r="I151" s="20">
+        <v>0</v>
+      </c>
+      <c r="J151" s="20">
+        <v>0</v>
+      </c>
+      <c r="K151" s="20">
+        <v>0</v>
+      </c>
+      <c r="L151" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25705,31 +25704,31 @@
       <c r="C152" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D152" s="10" t="s">
+      <c r="D152" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E152" s="10">
+      <c r="E152" s="20">
         <v>3</v>
       </c>
-      <c r="F152" s="10">
+      <c r="F152" s="20">
         <v>2</v>
       </c>
-      <c r="G152" s="10">
-        <v>1</v>
-      </c>
-      <c r="H152" s="10">
-        <v>0</v>
-      </c>
-      <c r="I152" s="10">
-        <v>0</v>
-      </c>
-      <c r="J152" s="10">
-        <v>0</v>
-      </c>
-      <c r="K152" s="10">
-        <v>0</v>
-      </c>
-      <c r="L152" s="10">
+      <c r="G152" s="20">
+        <v>1</v>
+      </c>
+      <c r="H152" s="20">
+        <v>0</v>
+      </c>
+      <c r="I152" s="20">
+        <v>0</v>
+      </c>
+      <c r="J152" s="20">
+        <v>0</v>
+      </c>
+      <c r="K152" s="20">
+        <v>0</v>
+      </c>
+      <c r="L152" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25743,31 +25742,31 @@
       <c r="C153" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D153" s="10" t="s">
+      <c r="D153" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E153" s="10">
+      <c r="E153" s="20">
         <v>2</v>
       </c>
-      <c r="F153" s="10">
+      <c r="F153" s="20">
         <v>2</v>
       </c>
-      <c r="G153" s="10">
-        <v>0</v>
-      </c>
-      <c r="H153" s="10">
-        <v>0</v>
-      </c>
-      <c r="I153" s="10">
-        <v>0</v>
-      </c>
-      <c r="J153" s="10">
-        <v>0</v>
-      </c>
-      <c r="K153" s="10">
-        <v>0</v>
-      </c>
-      <c r="L153" s="10">
+      <c r="G153" s="20">
+        <v>0</v>
+      </c>
+      <c r="H153" s="20">
+        <v>0</v>
+      </c>
+      <c r="I153" s="20">
+        <v>0</v>
+      </c>
+      <c r="J153" s="20">
+        <v>0</v>
+      </c>
+      <c r="K153" s="20">
+        <v>0</v>
+      </c>
+      <c r="L153" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25781,31 +25780,31 @@
       <c r="C154" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D154" s="10" t="s">
+      <c r="D154" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E154" s="10">
+      <c r="E154" s="20">
         <v>2</v>
       </c>
-      <c r="F154" s="10">
-        <v>1</v>
-      </c>
-      <c r="G154" s="10">
-        <v>1</v>
-      </c>
-      <c r="H154" s="10">
-        <v>0</v>
-      </c>
-      <c r="I154" s="10">
-        <v>0</v>
-      </c>
-      <c r="J154" s="10">
-        <v>0</v>
-      </c>
-      <c r="K154" s="10">
-        <v>0</v>
-      </c>
-      <c r="L154" s="10">
+      <c r="F154" s="20">
+        <v>1</v>
+      </c>
+      <c r="G154" s="20">
+        <v>1</v>
+      </c>
+      <c r="H154" s="20">
+        <v>0</v>
+      </c>
+      <c r="I154" s="20">
+        <v>0</v>
+      </c>
+      <c r="J154" s="20">
+        <v>0</v>
+      </c>
+      <c r="K154" s="20">
+        <v>0</v>
+      </c>
+      <c r="L154" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25819,31 +25818,31 @@
       <c r="C155" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D155" s="10" t="s">
+      <c r="D155" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E155" s="10">
-        <v>1</v>
-      </c>
-      <c r="F155" s="10">
-        <v>1</v>
-      </c>
-      <c r="G155" s="10">
-        <v>1</v>
-      </c>
-      <c r="H155" s="10">
-        <v>0</v>
-      </c>
-      <c r="I155" s="10">
-        <v>0</v>
-      </c>
-      <c r="J155" s="10">
-        <v>0</v>
-      </c>
-      <c r="K155" s="10">
-        <v>0</v>
-      </c>
-      <c r="L155" s="10">
+      <c r="E155" s="20">
+        <v>1</v>
+      </c>
+      <c r="F155" s="20">
+        <v>1</v>
+      </c>
+      <c r="G155" s="20">
+        <v>1</v>
+      </c>
+      <c r="H155" s="20">
+        <v>0</v>
+      </c>
+      <c r="I155" s="20">
+        <v>0</v>
+      </c>
+      <c r="J155" s="20">
+        <v>0</v>
+      </c>
+      <c r="K155" s="20">
+        <v>0</v>
+      </c>
+      <c r="L155" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25857,31 +25856,31 @@
       <c r="C156" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E156" s="10">
-        <v>1</v>
-      </c>
-      <c r="F156" s="10">
-        <v>1</v>
-      </c>
-      <c r="G156" s="10">
-        <v>0</v>
-      </c>
-      <c r="H156" s="10">
-        <v>0</v>
-      </c>
-      <c r="I156" s="10">
-        <v>0</v>
-      </c>
-      <c r="J156" s="10">
-        <v>0</v>
-      </c>
-      <c r="K156" s="10">
-        <v>0</v>
-      </c>
-      <c r="L156" s="10">
+      <c r="E156" s="20">
+        <v>1</v>
+      </c>
+      <c r="F156" s="20">
+        <v>1</v>
+      </c>
+      <c r="G156" s="20">
+        <v>0</v>
+      </c>
+      <c r="H156" s="20">
+        <v>0</v>
+      </c>
+      <c r="I156" s="20">
+        <v>0</v>
+      </c>
+      <c r="J156" s="20">
+        <v>0</v>
+      </c>
+      <c r="K156" s="20">
+        <v>0</v>
+      </c>
+      <c r="L156" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25895,31 +25894,31 @@
       <c r="C157" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="D157" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E157" s="10">
+      <c r="E157" s="20">
         <v>2</v>
       </c>
-      <c r="F157" s="10">
+      <c r="F157" s="20">
         <v>2</v>
       </c>
-      <c r="G157" s="10">
-        <v>1</v>
-      </c>
-      <c r="H157" s="10">
-        <v>0</v>
-      </c>
-      <c r="I157" s="10">
-        <v>0</v>
-      </c>
-      <c r="J157" s="10">
-        <v>0</v>
-      </c>
-      <c r="K157" s="10">
-        <v>0</v>
-      </c>
-      <c r="L157" s="10">
+      <c r="G157" s="20">
+        <v>1</v>
+      </c>
+      <c r="H157" s="20">
+        <v>0</v>
+      </c>
+      <c r="I157" s="20">
+        <v>0</v>
+      </c>
+      <c r="J157" s="20">
+        <v>0</v>
+      </c>
+      <c r="K157" s="20">
+        <v>0</v>
+      </c>
+      <c r="L157" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25933,31 +25932,31 @@
       <c r="C158" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="D158" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E158" s="10">
-        <v>1</v>
-      </c>
-      <c r="F158" s="10">
-        <v>1</v>
-      </c>
-      <c r="G158" s="10">
-        <v>1</v>
-      </c>
-      <c r="H158" s="10">
-        <v>0</v>
-      </c>
-      <c r="I158" s="10">
-        <v>0</v>
-      </c>
-      <c r="J158" s="10">
-        <v>0</v>
-      </c>
-      <c r="K158" s="10">
-        <v>0</v>
-      </c>
-      <c r="L158" s="10">
+      <c r="E158" s="20">
+        <v>1</v>
+      </c>
+      <c r="F158" s="20">
+        <v>1</v>
+      </c>
+      <c r="G158" s="20">
+        <v>1</v>
+      </c>
+      <c r="H158" s="20">
+        <v>0</v>
+      </c>
+      <c r="I158" s="20">
+        <v>0</v>
+      </c>
+      <c r="J158" s="20">
+        <v>0</v>
+      </c>
+      <c r="K158" s="20">
+        <v>0</v>
+      </c>
+      <c r="L158" s="20">
         <v>0</v>
       </c>
     </row>
@@ -25971,31 +25970,31 @@
       <c r="C159" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="20">
         <v>3</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="20">
         <v>3</v>
       </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-      <c r="H159">
-        <v>0</v>
-      </c>
-      <c r="I159">
-        <v>0</v>
-      </c>
-      <c r="J159">
-        <v>0</v>
-      </c>
-      <c r="K159">
-        <v>0</v>
-      </c>
-      <c r="L159">
+      <c r="G159" s="20">
+        <v>0</v>
+      </c>
+      <c r="H159" s="20">
+        <v>0</v>
+      </c>
+      <c r="I159" s="20">
+        <v>0</v>
+      </c>
+      <c r="J159" s="20">
+        <v>0</v>
+      </c>
+      <c r="K159" s="20">
+        <v>0</v>
+      </c>
+      <c r="L159" s="20">
         <v>0</v>
       </c>
     </row>
@@ -26009,31 +26008,31 @@
       <c r="C160" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-      <c r="H160">
-        <v>0</v>
-      </c>
-      <c r="I160">
-        <v>0</v>
-      </c>
-      <c r="J160">
-        <v>0</v>
-      </c>
-      <c r="K160">
-        <v>0</v>
-      </c>
-      <c r="L160">
+      <c r="E160" s="20">
+        <v>1</v>
+      </c>
+      <c r="F160" s="20">
+        <v>1</v>
+      </c>
+      <c r="G160" s="20">
+        <v>0</v>
+      </c>
+      <c r="H160" s="20">
+        <v>0</v>
+      </c>
+      <c r="I160" s="20">
+        <v>0</v>
+      </c>
+      <c r="J160" s="20">
+        <v>0</v>
+      </c>
+      <c r="K160" s="20">
+        <v>0</v>
+      </c>
+      <c r="L160" s="20">
         <v>0</v>
       </c>
     </row>
@@ -26047,31 +26046,31 @@
       <c r="C161" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D161" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="20">
         <v>2</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="20">
         <v>2</v>
       </c>
-      <c r="G161">
-        <v>1</v>
-      </c>
-      <c r="H161">
-        <v>0</v>
-      </c>
-      <c r="I161">
-        <v>0</v>
-      </c>
-      <c r="J161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <v>0</v>
-      </c>
-      <c r="L161">
+      <c r="G161" s="20">
+        <v>1</v>
+      </c>
+      <c r="H161" s="20">
+        <v>0</v>
+      </c>
+      <c r="I161" s="20">
+        <v>0</v>
+      </c>
+      <c r="J161" s="20">
+        <v>0</v>
+      </c>
+      <c r="K161" s="20">
+        <v>0</v>
+      </c>
+      <c r="L161" s="20">
         <v>0</v>
       </c>
     </row>
@@ -26085,31 +26084,31 @@
       <c r="C162" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="20">
         <v>4</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="20">
         <v>4</v>
       </c>
-      <c r="G162">
+      <c r="G162" s="20">
         <v>3</v>
       </c>
-      <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162">
-        <v>1</v>
-      </c>
-      <c r="J162">
+      <c r="H162" s="20">
+        <v>0</v>
+      </c>
+      <c r="I162" s="20">
+        <v>1</v>
+      </c>
+      <c r="J162" s="20">
         <v>7853.68</v>
       </c>
-      <c r="K162">
-        <v>1</v>
-      </c>
-      <c r="L162">
+      <c r="K162" s="20">
+        <v>1</v>
+      </c>
+      <c r="L162" s="20">
         <v>7853.68</v>
       </c>
     </row>
@@ -26123,31 +26122,31 @@
       <c r="C163" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D163" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E163">
-        <v>1</v>
-      </c>
-      <c r="F163">
-        <v>1</v>
-      </c>
-      <c r="G163">
-        <v>1</v>
-      </c>
-      <c r="H163">
-        <v>0</v>
-      </c>
-      <c r="I163">
-        <v>0</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
-      </c>
-      <c r="K163">
-        <v>0</v>
-      </c>
-      <c r="L163">
+      <c r="E163" s="20">
+        <v>1</v>
+      </c>
+      <c r="F163" s="20">
+        <v>1</v>
+      </c>
+      <c r="G163" s="20">
+        <v>1</v>
+      </c>
+      <c r="H163" s="20">
+        <v>0</v>
+      </c>
+      <c r="I163" s="20">
+        <v>0</v>
+      </c>
+      <c r="J163" s="20">
+        <v>0</v>
+      </c>
+      <c r="K163" s="20">
+        <v>0</v>
+      </c>
+      <c r="L163" s="20">
         <v>0</v>
       </c>
     </row>
@@ -26161,31 +26160,31 @@
       <c r="C164" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D164" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E164">
-        <v>1</v>
-      </c>
-      <c r="F164">
-        <v>1</v>
-      </c>
-      <c r="G164">
-        <v>0</v>
-      </c>
-      <c r="H164">
-        <v>0</v>
-      </c>
-      <c r="I164">
-        <v>0</v>
-      </c>
-      <c r="J164">
-        <v>0</v>
-      </c>
-      <c r="K164">
-        <v>0</v>
-      </c>
-      <c r="L164">
+      <c r="E164" s="20">
+        <v>1</v>
+      </c>
+      <c r="F164" s="20">
+        <v>1</v>
+      </c>
+      <c r="G164" s="20">
+        <v>0</v>
+      </c>
+      <c r="H164" s="20">
+        <v>0</v>
+      </c>
+      <c r="I164" s="20">
+        <v>0</v>
+      </c>
+      <c r="J164" s="20">
+        <v>0</v>
+      </c>
+      <c r="K164" s="20">
+        <v>0</v>
+      </c>
+      <c r="L164" s="20">
         <v>0</v>
       </c>
     </row>
@@ -26199,31 +26198,31 @@
       <c r="C165" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="20">
         <v>2</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="20">
         <v>2</v>
       </c>
-      <c r="G165">
-        <v>1</v>
-      </c>
-      <c r="H165">
-        <v>0</v>
-      </c>
-      <c r="I165">
-        <v>0</v>
-      </c>
-      <c r="J165">
-        <v>0</v>
-      </c>
-      <c r="K165">
-        <v>0</v>
-      </c>
-      <c r="L165">
+      <c r="G165" s="20">
+        <v>1</v>
+      </c>
+      <c r="H165" s="20">
+        <v>0</v>
+      </c>
+      <c r="I165" s="20">
+        <v>0</v>
+      </c>
+      <c r="J165" s="20">
+        <v>0</v>
+      </c>
+      <c r="K165" s="20">
+        <v>0</v>
+      </c>
+      <c r="L165" s="20">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FBD425-8755-474A-AC31-9986E84D80E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1B0F1-B16C-4513-AFD4-02927874DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="140">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -592,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -641,7 +641,6 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.44140625" customWidth="1"/>
@@ -3128,12 +3127,20 @@
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="B35" s="5">
+        <v>3</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1458.13</v>
+      </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3142,43 +3149,19 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="6">
-        <v>27.81</v>
-      </c>
-      <c r="O35" s="6">
-        <v>880.27</v>
-      </c>
-      <c r="P35" s="6">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="6">
-        <v>0</v>
-      </c>
-      <c r="R35" s="6">
-        <v>0</v>
-      </c>
-      <c r="S35" s="6">
-        <v>220.0675</v>
-      </c>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
       <c r="T35" s="6"/>
-      <c r="U35" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V35" s="7">
-        <v>250.18</v>
-      </c>
-      <c r="W35" s="7">
-        <v>7865.5</v>
-      </c>
-      <c r="X35" s="7">
-        <v>18</v>
-      </c>
-      <c r="Y35" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="7">
-        <v>0</v>
-      </c>
+      <c r="U35" s="6"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -3188,94 +3171,88 @@
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="5">
-        <v>5</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2</v>
-      </c>
-      <c r="D36" s="5">
-        <v>3</v>
-      </c>
-      <c r="E36" s="5">
-        <v>1019.98</v>
-      </c>
-      <c r="F36" s="5">
-        <v>2</v>
-      </c>
-      <c r="G36" s="5">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
-        <v>2</v>
-      </c>
-      <c r="I36" s="5">
-        <v>1</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <v>509.99</v>
-      </c>
-      <c r="L36" s="5">
-        <v>1019.98</v>
-      </c>
-      <c r="M36" s="5">
+        <v>56</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6">
+        <v>27.81</v>
+      </c>
+      <c r="O36" s="6">
+        <v>880.27</v>
+      </c>
+      <c r="P36" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>220.0675</v>
+      </c>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6">
         <v>-100</v>
       </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="8">
-        <v>7500</v>
-      </c>
-      <c r="AB36" s="9">
-        <v>16</v>
-      </c>
-      <c r="AC36" s="9">
-        <v>7</v>
-      </c>
+      <c r="V36" s="7">
+        <v>250.18</v>
+      </c>
+      <c r="W36" s="7">
+        <v>7865.5</v>
+      </c>
+      <c r="X36" s="7">
+        <v>18</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
       <c r="AD36" s="13">
         <v>46146</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>8.99</v>
+        <v>5</v>
       </c>
       <c r="C37" s="5">
-        <v>6.99</v>
+        <v>2</v>
       </c>
       <c r="D37" s="5">
+        <v>3</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1019.98</v>
+      </c>
+      <c r="F37" s="5">
         <v>2</v>
       </c>
-      <c r="E37" s="5">
-        <v>2742.85</v>
-      </c>
-      <c r="F37" s="5">
-        <v>1</v>
-      </c>
       <c r="G37" s="5">
         <v>0</v>
       </c>
       <c r="H37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="5">
         <v>1</v>
@@ -3284,61 +3261,35 @@
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>2742.85</v>
+        <v>509.99</v>
       </c>
       <c r="L37" s="5">
-        <v>2742.85</v>
+        <v>1019.98</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
       </c>
-      <c r="N37" s="6">
-        <v>1</v>
-      </c>
-      <c r="O37" s="6">
-        <v>1242.1099999999999</v>
-      </c>
-      <c r="P37" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>1</v>
-      </c>
-      <c r="R37" s="6">
-        <v>0</v>
-      </c>
-      <c r="S37" s="6">
-        <v>414.03666666666601</v>
-      </c>
-      <c r="T37" s="6">
-        <v>1242.1099999999999</v>
-      </c>
-      <c r="U37" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V37" s="7">
-        <v>42.5</v>
-      </c>
-      <c r="W37" s="7">
-        <v>12015.14</v>
-      </c>
-      <c r="X37" s="7">
-        <v>56</v>
-      </c>
-      <c r="Y37" s="7">
-        <v>24</v>
-      </c>
-      <c r="Z37" s="7">
-        <v>0</v>
-      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
       <c r="AA37" s="8">
-        <v>17000</v>
+        <v>7500</v>
       </c>
       <c r="AB37" s="9">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AC37" s="9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD37" s="13">
         <v>46146</v>
@@ -3346,97 +3297,117 @@
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B38" s="5">
+        <v>8.99</v>
+      </c>
+      <c r="C38" s="5">
+        <v>6.99</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2742.85</v>
+      </c>
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5">
+        <v>1</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>2742.85</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2742.85</v>
+      </c>
+      <c r="M38" s="5">
+        <v>-100</v>
+      </c>
       <c r="N38" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O38" s="6">
-        <v>767.62</v>
-      </c>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
+        <v>1242.1099999999999</v>
+      </c>
+      <c r="P38" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>1</v>
+      </c>
+      <c r="R38" s="6">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6">
+        <v>414.03666666666601</v>
+      </c>
+      <c r="T38" s="6">
+        <v>1242.1099999999999</v>
+      </c>
+      <c r="U38" s="6">
+        <v>-100</v>
+      </c>
       <c r="V38" s="7">
-        <v>97.34</v>
+        <v>42.5</v>
       </c>
       <c r="W38" s="7">
-        <v>5964.35</v>
+        <v>12015.14</v>
       </c>
       <c r="X38" s="7">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="Y38" s="7">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Z38" s="7">
         <v>0</v>
       </c>
-      <c r="AA38" s="8"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
+      <c r="AA38" s="8">
+        <v>17000</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>27</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>16</v>
+      </c>
       <c r="AD38" s="13">
         <v>46146</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="5">
-        <v>3</v>
-      </c>
-      <c r="C39" s="5">
-        <v>2</v>
-      </c>
-      <c r="D39" s="5">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5">
-        <v>2322.61</v>
-      </c>
-      <c r="F39" s="5">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>2322.61</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
       <c r="L39" s="5"/>
-      <c r="M39" s="5">
-        <v>-100</v>
-      </c>
+      <c r="M39" s="5"/>
       <c r="N39" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O39" s="6">
-        <v>89.37</v>
+        <v>767.62</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
@@ -3445,17 +3416,21 @@
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
       <c r="V39" s="7">
-        <v>3.01</v>
+        <v>97.34</v>
       </c>
       <c r="W39" s="7">
-        <v>1758.25</v>
-      </c>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="8">
-        <v>17000</v>
-      </c>
+        <v>5964.35</v>
+      </c>
+      <c r="X39" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y39" s="7">
+        <v>3</v>
+      </c>
+      <c r="Z39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8"/>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
@@ -3464,135 +3439,159 @@
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="C40" s="5">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="D40" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E40" s="5">
-        <v>2016.05</v>
+        <v>2322.61</v>
       </c>
       <c r="F40" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5">
         <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I40" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>288.00714285714201</v>
-      </c>
-      <c r="L40" s="5">
-        <v>672.01666666666597</v>
-      </c>
+        <v>2322.61</v>
+      </c>
+      <c r="L40" s="5"/>
       <c r="M40" s="5">
-        <v>289.55779866570703</v>
+        <v>-100</v>
       </c>
       <c r="N40" s="6">
-        <v>8.02</v>
+        <v>0</v>
       </c>
       <c r="O40" s="6">
-        <v>979.17</v>
-      </c>
-      <c r="P40" s="6">
-        <v>9</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>1</v>
-      </c>
-      <c r="R40" s="6">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6">
-        <v>108.796666666666</v>
-      </c>
-      <c r="T40" s="6">
-        <v>979.17</v>
-      </c>
-      <c r="U40" s="6">
-        <v>-100</v>
-      </c>
+        <v>89.37</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
       <c r="V40" s="7">
-        <v>52.03</v>
+        <v>3.01</v>
       </c>
       <c r="W40" s="7">
-        <v>10931.15</v>
-      </c>
-      <c r="X40" s="7">
-        <v>47</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>13</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>0</v>
-      </c>
+        <v>1758.25</v>
+      </c>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
       <c r="AA40" s="8">
-        <v>24000</v>
-      </c>
-      <c r="AB40" s="9">
-        <v>29</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>12</v>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
       <c r="AD40" s="13">
         <v>46146</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="B41">
+        <v>7.2</v>
+      </c>
+      <c r="C41">
+        <v>3.2</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>2016.05</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>288.00714285714201</v>
+      </c>
+      <c r="L41">
+        <v>672.01666666666597</v>
+      </c>
+      <c r="M41">
+        <v>289.55779866570703</v>
       </c>
       <c r="N41">
-        <v>20</v>
+        <v>8.02</v>
       </c>
       <c r="O41">
-        <v>936.73</v>
+        <v>979.17</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>0</v>
       </c>
       <c r="S41">
-        <v>234.1825</v>
+        <v>108.796666666666</v>
+      </c>
+      <c r="T41">
+        <v>979.17</v>
       </c>
       <c r="U41">
         <v>-100</v>
       </c>
       <c r="V41">
-        <v>127.59</v>
+        <v>52.03</v>
       </c>
       <c r="W41">
-        <v>8783.7999999999993</v>
+        <v>10931.15</v>
       </c>
       <c r="X41">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="Y41">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Z41">
         <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>24000</v>
+      </c>
+      <c r="AB41">
+        <v>29</v>
+      </c>
+      <c r="AC41">
+        <v>12</v>
       </c>
       <c r="AD41" s="13">
         <v>46146</v>
@@ -3600,88 +3599,19 @@
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="B42">
-        <v>3.99</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>1.99</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>1416.29</v>
-      </c>
-      <c r="F42">
-        <v>2</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>2</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>708.14499999999998</v>
-      </c>
-      <c r="L42">
-        <v>1416.29</v>
-      </c>
-      <c r="M42">
-        <v>-100</v>
-      </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-      <c r="O42">
-        <v>473.88</v>
-      </c>
-      <c r="P42">
-        <v>2</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>236.94</v>
-      </c>
-      <c r="U42">
-        <v>-100</v>
-      </c>
-      <c r="V42">
-        <v>23.02</v>
-      </c>
-      <c r="W42">
-        <v>4636.55</v>
-      </c>
-      <c r="X42">
-        <v>23</v>
-      </c>
-      <c r="Y42">
-        <v>9</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>11000</v>
-      </c>
-      <c r="AB42">
-        <v>14</v>
-      </c>
-      <c r="AC42">
-        <v>6</v>
+        <v>1104.46</v>
       </c>
       <c r="AD42" s="13">
         <v>46146</v>
@@ -3689,40 +3619,37 @@
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N43">
-        <v>7.19</v>
+        <v>20</v>
       </c>
       <c r="O43">
-        <v>531.65</v>
+        <v>936.73</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>265.82499999999999</v>
-      </c>
-      <c r="T43">
-        <v>531.65</v>
+        <v>234.1825</v>
       </c>
       <c r="U43">
         <v>-100</v>
       </c>
       <c r="V43">
-        <v>56.01</v>
+        <v>127.59</v>
       </c>
       <c r="W43">
-        <v>4863.79</v>
+        <v>8783.7999999999993</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="Y43">
         <v>4</v>
@@ -3736,16 +3663,28 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>65</v>
+      </c>
+      <c r="B44">
+        <v>3.99</v>
+      </c>
+      <c r="C44">
+        <v>1.99</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>1416.29</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -3753,11 +3692,59 @@
       <c r="J44">
         <v>0</v>
       </c>
+      <c r="K44">
+        <v>708.14499999999998</v>
+      </c>
+      <c r="L44">
+        <v>1416.29</v>
+      </c>
+      <c r="M44">
+        <v>-100</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>473.88</v>
+      </c>
+      <c r="P44">
+        <v>2</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>236.94</v>
+      </c>
+      <c r="U44">
+        <v>-100</v>
+      </c>
+      <c r="V44">
+        <v>23.02</v>
+      </c>
+      <c r="W44">
+        <v>4636.55</v>
+      </c>
+      <c r="X44">
+        <v>23</v>
+      </c>
+      <c r="Y44">
+        <v>9</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>11000</v>
+      </c>
       <c r="AB44">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AC44">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD44" s="13">
         <v>46146</v>
@@ -3768,10 +3755,10 @@
         <v>66</v>
       </c>
       <c r="N45">
-        <v>4.1900000000000004</v>
+        <v>7.19</v>
       </c>
       <c r="O45">
-        <v>350.08</v>
+        <v>531.65</v>
       </c>
       <c r="P45">
         <v>2</v>
@@ -3783,10 +3770,10 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>175.04</v>
+        <v>265.82499999999999</v>
       </c>
       <c r="T45">
-        <v>350.08</v>
+        <v>531.65</v>
       </c>
       <c r="U45">
         <v>-100</v>
@@ -3805,6 +3792,32 @@
       </c>
       <c r="Z45">
         <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>2</v>
+      </c>
+      <c r="AC46">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5454,7 +5467,7 @@
         <v>667.25</v>
       </c>
       <c r="G5" s="5">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H5" s="5">
         <v>70</v>
@@ -5559,19 +5572,19 @@
         <v>354.93</v>
       </c>
       <c r="G8" s="5">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H8" s="5">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I8" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" s="5">
-        <v>401414.38</v>
+        <v>394170.38</v>
       </c>
       <c r="K8" s="5">
-        <v>9</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5594,19 +5607,19 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H9" s="5">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I9" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="5">
-        <v>342710.37</v>
+        <v>341967.37</v>
       </c>
       <c r="K9" s="5">
-        <v>23.92</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5629,7 +5642,7 @@
         <v>322.38</v>
       </c>
       <c r="G10" s="5">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H10" s="5">
         <v>109</v>
@@ -5734,7 +5747,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5842,16 +5855,16 @@
         <v>301</v>
       </c>
       <c r="H16" s="5">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I16" s="5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" s="5">
-        <v>504461.62</v>
+        <v>511623.25</v>
       </c>
       <c r="K16" s="5">
-        <v>32.369999999999997</v>
+        <v>32.840000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5944,7 +5957,7 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H19" s="5">
         <v>101</v>
@@ -5979,7 +5992,7 @@
         <v>293.32</v>
       </c>
       <c r="G20" s="10">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H20" s="10">
         <v>76</v>
@@ -7134,7 +7147,7 @@
         <v>141.16999999999999</v>
       </c>
       <c r="G53" s="10">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53" s="10">
         <v>36</v>
@@ -9459,7 +9472,7 @@
         <v>87.75</v>
       </c>
       <c r="G122" s="10">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H122" s="10">
         <v>28</v>
@@ -9564,7 +9577,7 @@
         <v>50.47</v>
       </c>
       <c r="G125" s="10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H125" s="10">
         <v>19</v>
@@ -10299,7 +10312,7 @@
         <v>7.83</v>
       </c>
       <c r="G146" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H146" s="10">
         <v>4</v>
@@ -13459,10 +13472,10 @@
         <v>31.97</v>
       </c>
       <c r="G239" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H239" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I239" s="10">
         <v>4</v>
@@ -15389,10 +15402,10 @@
         <v>70.47</v>
       </c>
       <c r="G297" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H297" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I297" s="10">
         <v>8</v>
@@ -15424,19 +15437,19 @@
         <v>104.01</v>
       </c>
       <c r="G298" s="10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H298" s="10">
         <v>30</v>
       </c>
       <c r="I298" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J298" s="10">
-        <v>55483.13</v>
+        <v>61881.13</v>
       </c>
       <c r="K298" s="10">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
@@ -15764,7 +15777,7 @@
         <v>196.53</v>
       </c>
       <c r="G308" s="10">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H308" s="10">
         <v>35</v>
@@ -16044,19 +16057,19 @@
         <v>119.16</v>
       </c>
       <c r="G316" s="10">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H316" s="10">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I316" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J316" s="10">
-        <v>64394.84</v>
+        <v>57233.21</v>
       </c>
       <c r="K316" s="10">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
@@ -16184,7 +16197,7 @@
         <v>163.26999999999899</v>
       </c>
       <c r="G320" s="10">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H320" s="10">
         <v>27</v>
@@ -16349,19 +16362,19 @@
         <v>118.06</v>
       </c>
       <c r="G325" s="10">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H325" s="10">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I325" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J325" s="10">
-        <v>132287.63</v>
+        <v>126854.51</v>
       </c>
       <c r="K325" s="10">
-        <v>2.57</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
@@ -16804,7 +16817,7 @@
         <v>171.77</v>
       </c>
       <c r="G338" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H338" s="10">
         <v>14</v>
@@ -17414,19 +17427,19 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G356" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H356" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I356" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J356" s="10">
-        <v>80023.12</v>
+        <v>86918.12</v>
       </c>
       <c r="K356" s="10">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.3">
@@ -17624,10 +17637,10 @@
         <v>51.08</v>
       </c>
       <c r="G362" s="10">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H362" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I362" s="10">
         <v>6</v>
@@ -17869,7 +17882,7 @@
         <v>81.229999999999905</v>
       </c>
       <c r="G369" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H369" s="10">
         <v>15</v>
@@ -18464,7 +18477,7 @@
         <v>51.14</v>
       </c>
       <c r="G386" s="10">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H386" s="10">
         <v>19</v>
@@ -18788,10 +18801,10 @@
         <v>1</v>
       </c>
       <c r="J395" s="10">
-        <v>7953.68</v>
+        <v>7853.68</v>
       </c>
       <c r="K395" s="10">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
@@ -19444,7 +19457,7 @@
         <v>19.079999999999998</v>
       </c>
       <c r="G416" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H416" s="10">
         <v>4</v>
@@ -24564,31 +24577,31 @@
       <c r="C122" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D122" s="20" t="s">
+      <c r="D122" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="20">
-        <v>1</v>
-      </c>
-      <c r="F122" s="20">
-        <v>1</v>
-      </c>
-      <c r="G122" s="20">
-        <v>1</v>
-      </c>
-      <c r="H122" s="20">
-        <v>0</v>
-      </c>
-      <c r="I122" s="20">
-        <v>0</v>
-      </c>
-      <c r="J122" s="20">
-        <v>0</v>
-      </c>
-      <c r="K122" s="20">
-        <v>0</v>
-      </c>
-      <c r="L122" s="20">
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
         <v>0</v>
       </c>
     </row>
@@ -24602,31 +24615,31 @@
       <c r="C123" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="20" t="s">
+      <c r="D123" t="s">
         <v>27</v>
       </c>
-      <c r="E123" s="20">
+      <c r="E123">
         <v>6</v>
       </c>
-      <c r="F123" s="20">
+      <c r="F123">
         <v>4</v>
       </c>
-      <c r="G123" s="20">
+      <c r="G123">
         <v>3</v>
       </c>
-      <c r="H123" s="20">
-        <v>1</v>
-      </c>
-      <c r="I123" s="20">
-        <v>0</v>
-      </c>
-      <c r="J123" s="20">
-        <v>0</v>
-      </c>
-      <c r="K123" s="20">
-        <v>0</v>
-      </c>
-      <c r="L123" s="20">
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
         <v>0</v>
       </c>
     </row>
@@ -24640,31 +24653,31 @@
       <c r="C124" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D124" s="20" t="s">
+      <c r="D124" t="s">
         <v>137</v>
       </c>
-      <c r="E124" s="20">
+      <c r="E124">
         <v>3</v>
       </c>
-      <c r="F124" s="20">
+      <c r="F124">
         <v>3</v>
       </c>
-      <c r="G124" s="20">
-        <v>1</v>
-      </c>
-      <c r="H124" s="20">
-        <v>0</v>
-      </c>
-      <c r="I124" s="20">
-        <v>0</v>
-      </c>
-      <c r="J124" s="20">
-        <v>0</v>
-      </c>
-      <c r="K124" s="20">
-        <v>0</v>
-      </c>
-      <c r="L124" s="20">
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
         <v>0</v>
       </c>
     </row>
@@ -24678,31 +24691,31 @@
       <c r="C125" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="20" t="s">
+      <c r="D125" t="s">
         <v>13</v>
       </c>
-      <c r="E125" s="20">
+      <c r="E125">
         <v>2</v>
       </c>
-      <c r="F125" s="20">
+      <c r="F125">
         <v>2</v>
       </c>
-      <c r="G125" s="20">
-        <v>0</v>
-      </c>
-      <c r="H125" s="20">
-        <v>0</v>
-      </c>
-      <c r="I125" s="20">
-        <v>0</v>
-      </c>
-      <c r="J125" s="20">
-        <v>0</v>
-      </c>
-      <c r="K125" s="20">
-        <v>0</v>
-      </c>
-      <c r="L125" s="20">
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
         <v>0</v>
       </c>
     </row>
@@ -24716,31 +24729,31 @@
       <c r="C126" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D126" s="20" t="s">
+      <c r="D126" t="s">
         <v>33</v>
       </c>
-      <c r="E126" s="20">
-        <v>1</v>
-      </c>
-      <c r="F126" s="20">
-        <v>1</v>
-      </c>
-      <c r="G126" s="20">
-        <v>1</v>
-      </c>
-      <c r="H126" s="20">
-        <v>1</v>
-      </c>
-      <c r="I126" s="20">
-        <v>0</v>
-      </c>
-      <c r="J126" s="20">
-        <v>0</v>
-      </c>
-      <c r="K126" s="20">
-        <v>0</v>
-      </c>
-      <c r="L126" s="20">
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
         <v>0</v>
       </c>
     </row>
@@ -24754,31 +24767,31 @@
       <c r="C127" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D127" s="20" t="s">
+      <c r="D127" t="s">
         <v>40</v>
       </c>
-      <c r="E127" s="20">
-        <v>1</v>
-      </c>
-      <c r="F127" s="20">
-        <v>1</v>
-      </c>
-      <c r="G127" s="20">
-        <v>1</v>
-      </c>
-      <c r="H127" s="20">
-        <v>0</v>
-      </c>
-      <c r="I127" s="20">
-        <v>0</v>
-      </c>
-      <c r="J127" s="20">
-        <v>0</v>
-      </c>
-      <c r="K127" s="20">
-        <v>0</v>
-      </c>
-      <c r="L127" s="20">
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
         <v>0</v>
       </c>
     </row>
@@ -24792,31 +24805,31 @@
       <c r="C128" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D128" s="20" t="s">
+      <c r="D128" t="s">
         <v>53</v>
       </c>
-      <c r="E128" s="20">
+      <c r="E128">
         <v>6</v>
       </c>
-      <c r="F128" s="20">
+      <c r="F128">
         <v>5</v>
       </c>
-      <c r="G128" s="20">
+      <c r="G128">
         <v>2</v>
       </c>
-      <c r="H128" s="20">
-        <v>0</v>
-      </c>
-      <c r="I128" s="20">
-        <v>0</v>
-      </c>
-      <c r="J128" s="20">
-        <v>0</v>
-      </c>
-      <c r="K128" s="20">
-        <v>0</v>
-      </c>
-      <c r="L128" s="20">
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
         <v>0</v>
       </c>
     </row>
@@ -24830,31 +24843,31 @@
       <c r="C129" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D129" s="20" t="s">
+      <c r="D129" t="s">
         <v>13</v>
       </c>
-      <c r="E129" s="20">
-        <v>1</v>
-      </c>
-      <c r="F129" s="20">
-        <v>1</v>
-      </c>
-      <c r="G129" s="20">
-        <v>0</v>
-      </c>
-      <c r="H129" s="20">
-        <v>1</v>
-      </c>
-      <c r="I129" s="20">
-        <v>0</v>
-      </c>
-      <c r="J129" s="20">
-        <v>0</v>
-      </c>
-      <c r="K129" s="20">
-        <v>0</v>
-      </c>
-      <c r="L129" s="20">
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
         <v>0</v>
       </c>
     </row>
@@ -24868,31 +24881,31 @@
       <c r="C130" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D130" s="20" t="s">
+      <c r="D130" t="s">
         <v>13</v>
       </c>
-      <c r="E130" s="20">
-        <v>1</v>
-      </c>
-      <c r="F130" s="20">
-        <v>1</v>
-      </c>
-      <c r="G130" s="20">
-        <v>0</v>
-      </c>
-      <c r="H130" s="20">
-        <v>0</v>
-      </c>
-      <c r="I130" s="20">
-        <v>0</v>
-      </c>
-      <c r="J130" s="20">
-        <v>0</v>
-      </c>
-      <c r="K130" s="20">
-        <v>0</v>
-      </c>
-      <c r="L130" s="20">
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
         <v>0</v>
       </c>
     </row>
@@ -24906,31 +24919,31 @@
       <c r="C131" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D131" s="20" t="s">
+      <c r="D131" t="s">
         <v>137</v>
       </c>
-      <c r="E131" s="20">
-        <v>1</v>
-      </c>
-      <c r="F131" s="20">
-        <v>1</v>
-      </c>
-      <c r="G131" s="20">
-        <v>1</v>
-      </c>
-      <c r="H131" s="20">
-        <v>0</v>
-      </c>
-      <c r="I131" s="20">
-        <v>0</v>
-      </c>
-      <c r="J131" s="20">
-        <v>0</v>
-      </c>
-      <c r="K131" s="20">
-        <v>0</v>
-      </c>
-      <c r="L131" s="20">
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
         <v>0</v>
       </c>
     </row>
@@ -24944,31 +24957,31 @@
       <c r="C132" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D132" s="20" t="s">
+      <c r="D132" t="s">
         <v>13</v>
       </c>
-      <c r="E132" s="20">
-        <v>1</v>
-      </c>
-      <c r="F132" s="20">
-        <v>0</v>
-      </c>
-      <c r="G132" s="20">
-        <v>0</v>
-      </c>
-      <c r="H132" s="20">
-        <v>0</v>
-      </c>
-      <c r="I132" s="20">
-        <v>0</v>
-      </c>
-      <c r="J132" s="20">
-        <v>0</v>
-      </c>
-      <c r="K132" s="20">
-        <v>0</v>
-      </c>
-      <c r="L132" s="20">
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
         <v>0</v>
       </c>
     </row>
@@ -24982,31 +24995,31 @@
       <c r="C133" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D133" s="20" t="s">
+      <c r="D133" t="s">
         <v>137</v>
       </c>
-      <c r="E133" s="20">
+      <c r="E133">
         <v>3</v>
       </c>
-      <c r="F133" s="20">
+      <c r="F133">
         <v>3</v>
       </c>
-      <c r="G133" s="20">
-        <v>1</v>
-      </c>
-      <c r="H133" s="20">
-        <v>0</v>
-      </c>
-      <c r="I133" s="20">
-        <v>0</v>
-      </c>
-      <c r="J133" s="20">
-        <v>0</v>
-      </c>
-      <c r="K133" s="20">
-        <v>0</v>
-      </c>
-      <c r="L133" s="20">
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
         <v>0</v>
       </c>
     </row>
@@ -25020,31 +25033,31 @@
       <c r="C134" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D134" s="20" t="s">
+      <c r="D134" t="s">
         <v>41</v>
       </c>
-      <c r="E134" s="20">
+      <c r="E134">
         <v>2</v>
       </c>
-      <c r="F134" s="20">
+      <c r="F134">
         <v>2</v>
       </c>
-      <c r="G134" s="20">
-        <v>1</v>
-      </c>
-      <c r="H134" s="20">
-        <v>0</v>
-      </c>
-      <c r="I134" s="20">
-        <v>0</v>
-      </c>
-      <c r="J134" s="20">
-        <v>0</v>
-      </c>
-      <c r="K134" s="20">
-        <v>0</v>
-      </c>
-      <c r="L134" s="20">
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
         <v>0</v>
       </c>
     </row>
@@ -25058,31 +25071,31 @@
       <c r="C135" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D135" s="20" t="s">
+      <c r="D135" t="s">
         <v>13</v>
       </c>
-      <c r="E135" s="20">
+      <c r="E135">
         <v>3</v>
       </c>
-      <c r="F135" s="20">
+      <c r="F135">
         <v>3</v>
       </c>
-      <c r="G135" s="20">
+      <c r="G135">
         <v>2</v>
       </c>
-      <c r="H135" s="20">
-        <v>0</v>
-      </c>
-      <c r="I135" s="20">
-        <v>0</v>
-      </c>
-      <c r="J135" s="20">
-        <v>0</v>
-      </c>
-      <c r="K135" s="20">
-        <v>0</v>
-      </c>
-      <c r="L135" s="20">
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
         <v>0</v>
       </c>
     </row>
@@ -25096,31 +25109,31 @@
       <c r="C136" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D136" s="20" t="s">
+      <c r="D136" t="s">
         <v>42</v>
       </c>
-      <c r="E136" s="20">
+      <c r="E136">
         <v>3</v>
       </c>
-      <c r="F136" s="20">
+      <c r="F136">
         <v>3</v>
       </c>
-      <c r="G136" s="20">
-        <v>1</v>
-      </c>
-      <c r="H136" s="20">
-        <v>1</v>
-      </c>
-      <c r="I136" s="20">
-        <v>0</v>
-      </c>
-      <c r="J136" s="20">
-        <v>0</v>
-      </c>
-      <c r="K136" s="20">
-        <v>0</v>
-      </c>
-      <c r="L136" s="20">
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
         <v>0</v>
       </c>
     </row>
@@ -25134,31 +25147,31 @@
       <c r="C137" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D137" s="20" t="s">
+      <c r="D137" t="s">
         <v>52</v>
       </c>
-      <c r="E137" s="20">
+      <c r="E137">
         <v>2</v>
       </c>
-      <c r="F137" s="20">
+      <c r="F137">
         <v>2</v>
       </c>
-      <c r="G137" s="20">
-        <v>0</v>
-      </c>
-      <c r="H137" s="20">
-        <v>0</v>
-      </c>
-      <c r="I137" s="20">
-        <v>0</v>
-      </c>
-      <c r="J137" s="20">
-        <v>0</v>
-      </c>
-      <c r="K137" s="20">
-        <v>0</v>
-      </c>
-      <c r="L137" s="20">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
         <v>0</v>
       </c>
     </row>
@@ -25172,31 +25185,31 @@
       <c r="C138" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D138" s="20" t="s">
+      <c r="D138" t="s">
         <v>55</v>
       </c>
-      <c r="E138" s="20">
+      <c r="E138">
         <v>2</v>
       </c>
-      <c r="F138" s="20">
+      <c r="F138">
         <v>2</v>
       </c>
-      <c r="G138" s="20">
-        <v>1</v>
-      </c>
-      <c r="H138" s="20">
-        <v>1</v>
-      </c>
-      <c r="I138" s="20">
-        <v>0</v>
-      </c>
-      <c r="J138" s="20">
-        <v>0</v>
-      </c>
-      <c r="K138" s="20">
-        <v>0</v>
-      </c>
-      <c r="L138" s="20">
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
         <v>0</v>
       </c>
     </row>
@@ -25210,31 +25223,31 @@
       <c r="C139" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D139" s="20" t="s">
+      <c r="D139" t="s">
         <v>60</v>
       </c>
-      <c r="E139" s="20">
+      <c r="E139">
         <v>2</v>
       </c>
-      <c r="F139" s="20">
+      <c r="F139">
         <v>2</v>
       </c>
-      <c r="G139" s="20">
-        <v>0</v>
-      </c>
-      <c r="H139" s="20">
-        <v>0</v>
-      </c>
-      <c r="I139" s="20">
-        <v>0</v>
-      </c>
-      <c r="J139" s="20">
-        <v>0</v>
-      </c>
-      <c r="K139" s="20">
-        <v>0</v>
-      </c>
-      <c r="L139" s="20">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
         <v>0</v>
       </c>
     </row>
@@ -25248,31 +25261,31 @@
       <c r="C140" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D140" s="20" t="s">
+      <c r="D140" t="s">
         <v>137</v>
       </c>
-      <c r="E140" s="20">
-        <v>1</v>
-      </c>
-      <c r="F140" s="20">
-        <v>1</v>
-      </c>
-      <c r="G140" s="20">
-        <v>1</v>
-      </c>
-      <c r="H140" s="20">
-        <v>0</v>
-      </c>
-      <c r="I140" s="20">
-        <v>0</v>
-      </c>
-      <c r="J140" s="20">
-        <v>0</v>
-      </c>
-      <c r="K140" s="20">
-        <v>0</v>
-      </c>
-      <c r="L140" s="20">
+      <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
         <v>0</v>
       </c>
     </row>
@@ -25286,31 +25299,31 @@
       <c r="C141" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D141" s="20" t="s">
+      <c r="D141" t="s">
         <v>45</v>
       </c>
-      <c r="E141" s="20">
+      <c r="E141">
         <v>5</v>
       </c>
-      <c r="F141" s="20">
+      <c r="F141">
         <v>4</v>
       </c>
-      <c r="G141" s="20">
-        <v>0</v>
-      </c>
-      <c r="H141" s="20">
-        <v>0</v>
-      </c>
-      <c r="I141" s="20">
-        <v>0</v>
-      </c>
-      <c r="J141" s="20">
-        <v>0</v>
-      </c>
-      <c r="K141" s="20">
-        <v>0</v>
-      </c>
-      <c r="L141" s="20">
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
         <v>0</v>
       </c>
     </row>
@@ -25324,31 +25337,31 @@
       <c r="C142" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D142" s="20" t="s">
+      <c r="D142" t="s">
         <v>57</v>
       </c>
-      <c r="E142" s="20">
-        <v>1</v>
-      </c>
-      <c r="F142" s="20">
-        <v>1</v>
-      </c>
-      <c r="G142" s="20">
-        <v>0</v>
-      </c>
-      <c r="H142" s="20">
-        <v>0</v>
-      </c>
-      <c r="I142" s="20">
-        <v>0</v>
-      </c>
-      <c r="J142" s="20">
-        <v>0</v>
-      </c>
-      <c r="K142" s="20">
-        <v>0</v>
-      </c>
-      <c r="L142" s="20">
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
         <v>0</v>
       </c>
     </row>
@@ -25362,31 +25375,31 @@
       <c r="C143" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D143" s="20" t="s">
+      <c r="D143" t="s">
         <v>13</v>
       </c>
-      <c r="E143" s="20">
+      <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="20">
+      <c r="F143">
         <v>5</v>
       </c>
-      <c r="G143" s="20">
-        <v>0</v>
-      </c>
-      <c r="H143" s="20">
-        <v>1</v>
-      </c>
-      <c r="I143" s="20">
-        <v>0</v>
-      </c>
-      <c r="J143" s="20">
-        <v>0</v>
-      </c>
-      <c r="K143" s="20">
-        <v>0</v>
-      </c>
-      <c r="L143" s="20">
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
         <v>0</v>
       </c>
     </row>
@@ -25400,31 +25413,31 @@
       <c r="C144" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D144" s="20" t="s">
+      <c r="D144" t="s">
         <v>27</v>
       </c>
-      <c r="E144" s="20">
-        <v>1</v>
-      </c>
-      <c r="F144" s="20">
-        <v>1</v>
-      </c>
-      <c r="G144" s="20">
-        <v>0</v>
-      </c>
-      <c r="H144" s="20">
-        <v>0</v>
-      </c>
-      <c r="I144" s="20">
-        <v>0</v>
-      </c>
-      <c r="J144" s="20">
-        <v>0</v>
-      </c>
-      <c r="K144" s="20">
-        <v>0</v>
-      </c>
-      <c r="L144" s="20">
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
         <v>0</v>
       </c>
     </row>
@@ -25438,31 +25451,31 @@
       <c r="C145" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D145" s="20" t="s">
+      <c r="D145" t="s">
         <v>137</v>
       </c>
-      <c r="E145" s="20">
-        <v>1</v>
-      </c>
-      <c r="F145" s="20">
-        <v>1</v>
-      </c>
-      <c r="G145" s="20">
-        <v>0</v>
-      </c>
-      <c r="H145" s="20">
-        <v>0</v>
-      </c>
-      <c r="I145" s="20">
-        <v>0</v>
-      </c>
-      <c r="J145" s="20">
-        <v>0</v>
-      </c>
-      <c r="K145" s="20">
-        <v>0</v>
-      </c>
-      <c r="L145" s="20">
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
         <v>0</v>
       </c>
     </row>
@@ -25476,31 +25489,31 @@
       <c r="C146" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D146" s="20" t="s">
+      <c r="D146" t="s">
         <v>41</v>
       </c>
-      <c r="E146" s="20">
+      <c r="E146">
         <v>2</v>
       </c>
-      <c r="F146" s="20">
+      <c r="F146">
         <v>2</v>
       </c>
-      <c r="G146" s="20">
-        <v>0</v>
-      </c>
-      <c r="H146" s="20">
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
         <v>2</v>
       </c>
-      <c r="I146" s="20">
-        <v>0</v>
-      </c>
-      <c r="J146" s="20">
-        <v>0</v>
-      </c>
-      <c r="K146" s="20">
-        <v>0</v>
-      </c>
-      <c r="L146" s="20">
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
         <v>0</v>
       </c>
     </row>
@@ -25514,31 +25527,31 @@
       <c r="C147" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D147" s="20" t="s">
+      <c r="D147" t="s">
         <v>45</v>
       </c>
-      <c r="E147" s="20">
+      <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="20">
-        <v>0</v>
-      </c>
-      <c r="G147" s="20">
-        <v>0</v>
-      </c>
-      <c r="H147" s="20">
-        <v>1</v>
-      </c>
-      <c r="I147" s="20">
-        <v>0</v>
-      </c>
-      <c r="J147" s="20">
-        <v>0</v>
-      </c>
-      <c r="K147" s="20">
-        <v>0</v>
-      </c>
-      <c r="L147" s="20">
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
         <v>0</v>
       </c>
     </row>
@@ -25552,31 +25565,31 @@
       <c r="C148" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D148" s="20" t="s">
+      <c r="D148" t="s">
         <v>13</v>
       </c>
-      <c r="E148" s="20">
-        <v>1</v>
-      </c>
-      <c r="F148" s="20">
-        <v>1</v>
-      </c>
-      <c r="G148" s="20">
-        <v>0</v>
-      </c>
-      <c r="H148" s="20">
-        <v>0</v>
-      </c>
-      <c r="I148" s="20">
-        <v>0</v>
-      </c>
-      <c r="J148" s="20">
-        <v>0</v>
-      </c>
-      <c r="K148" s="20">
-        <v>0</v>
-      </c>
-      <c r="L148" s="20">
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
         <v>0</v>
       </c>
     </row>
@@ -25590,31 +25603,31 @@
       <c r="C149" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D149" s="20" t="s">
+      <c r="D149" t="s">
         <v>51</v>
       </c>
-      <c r="E149" s="20">
+      <c r="E149">
         <v>7</v>
       </c>
-      <c r="F149" s="20">
+      <c r="F149">
         <v>6</v>
       </c>
-      <c r="G149" s="20">
+      <c r="G149">
         <v>3</v>
       </c>
-      <c r="H149" s="20">
-        <v>0</v>
-      </c>
-      <c r="I149" s="20">
-        <v>0</v>
-      </c>
-      <c r="J149" s="20">
-        <v>0</v>
-      </c>
-      <c r="K149" s="20">
-        <v>0</v>
-      </c>
-      <c r="L149" s="20">
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
         <v>0</v>
       </c>
     </row>
@@ -25628,31 +25641,31 @@
       <c r="C150" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D150" s="20" t="s">
+      <c r="D150" t="s">
         <v>52</v>
       </c>
-      <c r="E150" s="20">
+      <c r="E150">
         <v>2</v>
       </c>
-      <c r="F150" s="20">
-        <v>1</v>
-      </c>
-      <c r="G150" s="20">
-        <v>0</v>
-      </c>
-      <c r="H150" s="20">
-        <v>1</v>
-      </c>
-      <c r="I150" s="20">
-        <v>0</v>
-      </c>
-      <c r="J150" s="20">
-        <v>0</v>
-      </c>
-      <c r="K150" s="20">
-        <v>0</v>
-      </c>
-      <c r="L150" s="20">
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
         <v>0</v>
       </c>
     </row>
@@ -25666,31 +25679,31 @@
       <c r="C151" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D151" s="20" t="s">
+      <c r="D151" t="s">
         <v>139</v>
       </c>
-      <c r="E151" s="20">
-        <v>1</v>
-      </c>
-      <c r="F151" s="20">
-        <v>1</v>
-      </c>
-      <c r="G151" s="20">
-        <v>1</v>
-      </c>
-      <c r="H151" s="20">
-        <v>0</v>
-      </c>
-      <c r="I151" s="20">
-        <v>0</v>
-      </c>
-      <c r="J151" s="20">
-        <v>0</v>
-      </c>
-      <c r="K151" s="20">
-        <v>0</v>
-      </c>
-      <c r="L151" s="20">
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
         <v>0</v>
       </c>
     </row>
@@ -25704,31 +25717,31 @@
       <c r="C152" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D152" s="20" t="s">
+      <c r="D152" t="s">
         <v>13</v>
       </c>
-      <c r="E152" s="20">
+      <c r="E152">
         <v>3</v>
       </c>
-      <c r="F152" s="20">
+      <c r="F152">
         <v>2</v>
       </c>
-      <c r="G152" s="20">
-        <v>1</v>
-      </c>
-      <c r="H152" s="20">
-        <v>0</v>
-      </c>
-      <c r="I152" s="20">
-        <v>0</v>
-      </c>
-      <c r="J152" s="20">
-        <v>0</v>
-      </c>
-      <c r="K152" s="20">
-        <v>0</v>
-      </c>
-      <c r="L152" s="20">
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
         <v>0</v>
       </c>
     </row>
@@ -25742,31 +25755,31 @@
       <c r="C153" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D153" s="20" t="s">
+      <c r="D153" t="s">
         <v>52</v>
       </c>
-      <c r="E153" s="20">
+      <c r="E153">
         <v>2</v>
       </c>
-      <c r="F153" s="20">
+      <c r="F153">
         <v>2</v>
       </c>
-      <c r="G153" s="20">
-        <v>0</v>
-      </c>
-      <c r="H153" s="20">
-        <v>0</v>
-      </c>
-      <c r="I153" s="20">
-        <v>0</v>
-      </c>
-      <c r="J153" s="20">
-        <v>0</v>
-      </c>
-      <c r="K153" s="20">
-        <v>0</v>
-      </c>
-      <c r="L153" s="20">
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
         <v>0</v>
       </c>
     </row>
@@ -25780,31 +25793,31 @@
       <c r="C154" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D154" s="20" t="s">
+      <c r="D154" t="s">
         <v>55</v>
       </c>
-      <c r="E154" s="20">
+      <c r="E154">
         <v>2</v>
       </c>
-      <c r="F154" s="20">
-        <v>1</v>
-      </c>
-      <c r="G154" s="20">
-        <v>1</v>
-      </c>
-      <c r="H154" s="20">
-        <v>0</v>
-      </c>
-      <c r="I154" s="20">
-        <v>0</v>
-      </c>
-      <c r="J154" s="20">
-        <v>0</v>
-      </c>
-      <c r="K154" s="20">
-        <v>0</v>
-      </c>
-      <c r="L154" s="20">
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
         <v>0</v>
       </c>
     </row>
@@ -25818,31 +25831,31 @@
       <c r="C155" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D155" s="20" t="s">
+      <c r="D155" t="s">
         <v>57</v>
       </c>
-      <c r="E155" s="20">
-        <v>1</v>
-      </c>
-      <c r="F155" s="20">
-        <v>1</v>
-      </c>
-      <c r="G155" s="20">
-        <v>1</v>
-      </c>
-      <c r="H155" s="20">
-        <v>0</v>
-      </c>
-      <c r="I155" s="20">
-        <v>0</v>
-      </c>
-      <c r="J155" s="20">
-        <v>0</v>
-      </c>
-      <c r="K155" s="20">
-        <v>0</v>
-      </c>
-      <c r="L155" s="20">
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
         <v>0</v>
       </c>
     </row>
@@ -25856,31 +25869,31 @@
       <c r="C156" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D156" s="20" t="s">
+      <c r="D156" t="s">
         <v>60</v>
       </c>
-      <c r="E156" s="20">
-        <v>1</v>
-      </c>
-      <c r="F156" s="20">
-        <v>1</v>
-      </c>
-      <c r="G156" s="20">
-        <v>0</v>
-      </c>
-      <c r="H156" s="20">
-        <v>0</v>
-      </c>
-      <c r="I156" s="20">
-        <v>0</v>
-      </c>
-      <c r="J156" s="20">
-        <v>0</v>
-      </c>
-      <c r="K156" s="20">
-        <v>0</v>
-      </c>
-      <c r="L156" s="20">
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
         <v>0</v>
       </c>
     </row>
@@ -25894,31 +25907,31 @@
       <c r="C157" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D157" s="20" t="s">
+      <c r="D157" t="s">
         <v>53</v>
       </c>
-      <c r="E157" s="20">
+      <c r="E157">
         <v>2</v>
       </c>
-      <c r="F157" s="20">
+      <c r="F157">
         <v>2</v>
       </c>
-      <c r="G157" s="20">
-        <v>1</v>
-      </c>
-      <c r="H157" s="20">
-        <v>0</v>
-      </c>
-      <c r="I157" s="20">
-        <v>0</v>
-      </c>
-      <c r="J157" s="20">
-        <v>0</v>
-      </c>
-      <c r="K157" s="20">
-        <v>0</v>
-      </c>
-      <c r="L157" s="20">
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
         <v>0</v>
       </c>
     </row>
@@ -25932,31 +25945,31 @@
       <c r="C158" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D158" s="20" t="s">
+      <c r="D158" t="s">
         <v>58</v>
       </c>
-      <c r="E158" s="20">
-        <v>1</v>
-      </c>
-      <c r="F158" s="20">
-        <v>1</v>
-      </c>
-      <c r="G158" s="20">
-        <v>1</v>
-      </c>
-      <c r="H158" s="20">
-        <v>0</v>
-      </c>
-      <c r="I158" s="20">
-        <v>0</v>
-      </c>
-      <c r="J158" s="20">
-        <v>0</v>
-      </c>
-      <c r="K158" s="20">
-        <v>0</v>
-      </c>
-      <c r="L158" s="20">
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
         <v>0</v>
       </c>
     </row>
@@ -25970,31 +25983,31 @@
       <c r="C159" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D159" s="20" t="s">
+      <c r="D159" t="s">
         <v>29</v>
       </c>
-      <c r="E159" s="20">
+      <c r="E159">
         <v>3</v>
       </c>
-      <c r="F159" s="20">
+      <c r="F159">
         <v>3</v>
       </c>
-      <c r="G159" s="20">
-        <v>0</v>
-      </c>
-      <c r="H159" s="20">
-        <v>0</v>
-      </c>
-      <c r="I159" s="20">
-        <v>0</v>
-      </c>
-      <c r="J159" s="20">
-        <v>0</v>
-      </c>
-      <c r="K159" s="20">
-        <v>0</v>
-      </c>
-      <c r="L159" s="20">
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
         <v>0</v>
       </c>
     </row>
@@ -26008,31 +26021,31 @@
       <c r="C160" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D160" s="20" t="s">
+      <c r="D160" t="s">
         <v>138</v>
       </c>
-      <c r="E160" s="20">
-        <v>1</v>
-      </c>
-      <c r="F160" s="20">
-        <v>1</v>
-      </c>
-      <c r="G160" s="20">
-        <v>0</v>
-      </c>
-      <c r="H160" s="20">
-        <v>0</v>
-      </c>
-      <c r="I160" s="20">
-        <v>0</v>
-      </c>
-      <c r="J160" s="20">
-        <v>0</v>
-      </c>
-      <c r="K160" s="20">
-        <v>0</v>
-      </c>
-      <c r="L160" s="20">
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
         <v>0</v>
       </c>
     </row>
@@ -26046,31 +26059,31 @@
       <c r="C161" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D161" s="20" t="s">
+      <c r="D161" t="s">
         <v>13</v>
       </c>
-      <c r="E161" s="20">
+      <c r="E161">
         <v>2</v>
       </c>
-      <c r="F161" s="20">
+      <c r="F161">
         <v>2</v>
       </c>
-      <c r="G161" s="20">
-        <v>1</v>
-      </c>
-      <c r="H161" s="20">
-        <v>0</v>
-      </c>
-      <c r="I161" s="20">
-        <v>0</v>
-      </c>
-      <c r="J161" s="20">
-        <v>0</v>
-      </c>
-      <c r="K161" s="20">
-        <v>0</v>
-      </c>
-      <c r="L161" s="20">
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
         <v>0</v>
       </c>
     </row>
@@ -26084,31 +26097,31 @@
       <c r="C162" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D162" s="20" t="s">
+      <c r="D162" t="s">
         <v>60</v>
       </c>
-      <c r="E162" s="20">
+      <c r="E162">
         <v>4</v>
       </c>
-      <c r="F162" s="20">
+      <c r="F162">
         <v>4</v>
       </c>
-      <c r="G162" s="20">
+      <c r="G162">
         <v>3</v>
       </c>
-      <c r="H162" s="20">
-        <v>0</v>
-      </c>
-      <c r="I162" s="20">
-        <v>1</v>
-      </c>
-      <c r="J162" s="20">
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
         <v>7853.68</v>
       </c>
-      <c r="K162" s="20">
-        <v>1</v>
-      </c>
-      <c r="L162" s="20">
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
         <v>7853.68</v>
       </c>
     </row>
@@ -26122,31 +26135,31 @@
       <c r="C163" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D163" s="20" t="s">
+      <c r="D163" t="s">
         <v>52</v>
       </c>
-      <c r="E163" s="20">
-        <v>1</v>
-      </c>
-      <c r="F163" s="20">
-        <v>1</v>
-      </c>
-      <c r="G163" s="20">
-        <v>1</v>
-      </c>
-      <c r="H163" s="20">
-        <v>0</v>
-      </c>
-      <c r="I163" s="20">
-        <v>0</v>
-      </c>
-      <c r="J163" s="20">
-        <v>0</v>
-      </c>
-      <c r="K163" s="20">
-        <v>0</v>
-      </c>
-      <c r="L163" s="20">
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
         <v>0</v>
       </c>
     </row>
@@ -26160,31 +26173,31 @@
       <c r="C164" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D164" s="20" t="s">
+      <c r="D164" t="s">
         <v>55</v>
       </c>
-      <c r="E164" s="20">
-        <v>1</v>
-      </c>
-      <c r="F164" s="20">
-        <v>1</v>
-      </c>
-      <c r="G164" s="20">
-        <v>0</v>
-      </c>
-      <c r="H164" s="20">
-        <v>0</v>
-      </c>
-      <c r="I164" s="20">
-        <v>0</v>
-      </c>
-      <c r="J164" s="20">
-        <v>0</v>
-      </c>
-      <c r="K164" s="20">
-        <v>0</v>
-      </c>
-      <c r="L164" s="20">
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
         <v>0</v>
       </c>
     </row>
@@ -26198,31 +26211,31 @@
       <c r="C165" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D165" s="20" t="s">
+      <c r="D165" t="s">
         <v>65</v>
       </c>
-      <c r="E165" s="20">
+      <c r="E165">
         <v>2</v>
       </c>
-      <c r="F165" s="20">
+      <c r="F165">
         <v>2</v>
       </c>
-      <c r="G165" s="20">
-        <v>1</v>
-      </c>
-      <c r="H165" s="20">
-        <v>0</v>
-      </c>
-      <c r="I165" s="20">
-        <v>0</v>
-      </c>
-      <c r="J165" s="20">
-        <v>0</v>
-      </c>
-      <c r="K165" s="20">
-        <v>0</v>
-      </c>
-      <c r="L165" s="20">
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1B0F1-B16C-4513-AFD4-02927874DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41511329-2019-4BFC-9CDC-4283B86DF55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="141">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>gbp</t>
+  </si>
+  <si>
+    <t>Competitors â€“ USA</t>
   </si>
 </sst>
 </file>
@@ -1088,64 +1091,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>188.9</v>
+        <v>253.89</v>
       </c>
       <c r="C6" s="5">
-        <v>100.81</v>
+        <v>133.80000000000001</v>
       </c>
       <c r="D6" s="5">
-        <v>88.09</v>
+        <v>120.09</v>
       </c>
       <c r="E6" s="5">
-        <v>50651.360000000001</v>
+        <v>63757.31</v>
       </c>
       <c r="F6" s="5">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="G6" s="5">
+        <v>7</v>
+      </c>
+      <c r="H6" s="5">
+        <v>115</v>
+      </c>
+      <c r="I6" s="5">
+        <v>39</v>
+      </c>
+      <c r="J6" s="5">
         <v>4</v>
       </c>
-      <c r="H6" s="5">
-        <v>93</v>
-      </c>
-      <c r="I6" s="5">
-        <v>31</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
       <c r="K6" s="5">
-        <v>522.17896907216402</v>
+        <v>522.60090163934399</v>
       </c>
       <c r="L6" s="5">
-        <v>1633.91483870967</v>
+        <v>1634.8028205128201</v>
       </c>
       <c r="M6" s="5">
-        <v>-84.494631536053504</v>
+        <v>-62.050343717449799</v>
       </c>
       <c r="N6" s="6">
-        <v>247.61</v>
+        <v>324.14</v>
       </c>
       <c r="O6" s="6">
-        <v>27073.87</v>
+        <v>35412.97</v>
       </c>
       <c r="P6" s="6">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="Q6" s="6">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R6" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6" s="6">
-        <v>184.17598639455699</v>
+        <v>183.48689119170899</v>
       </c>
       <c r="T6" s="6">
-        <v>1128.07791666666</v>
+        <v>983.69361111111095</v>
       </c>
       <c r="U6" s="6">
-        <v>-39.886687791586503</v>
+        <v>-19.439120751521202</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1160,7 +1163,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1172,7 +1175,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1180,64 +1183,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>33.01</v>
+        <v>43.51</v>
       </c>
       <c r="C7" s="5">
-        <v>15.75</v>
+        <v>20.75</v>
       </c>
       <c r="D7" s="5">
-        <v>17.260000000000002</v>
+        <v>22.76</v>
       </c>
       <c r="E7" s="5">
-        <v>1307.6300000000001</v>
+        <v>1785.97</v>
       </c>
       <c r="F7" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
       <c r="H7" s="5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I7" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>65.381500000000003</v>
+        <v>74.415416666666601</v>
       </c>
       <c r="L7" s="5">
-        <v>326.90750000000003</v>
+        <v>297.66166666666601</v>
       </c>
       <c r="M7" s="5">
-        <v>-100</v>
+        <v>18.926969657944898</v>
       </c>
       <c r="N7" s="6">
-        <v>43.47</v>
+        <v>57.54</v>
       </c>
       <c r="O7" s="6">
-        <v>2402.2199999999998</v>
+        <v>3345.9</v>
       </c>
       <c r="P7" s="6">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R7" s="6">
         <v>2</v>
       </c>
       <c r="S7" s="6">
-        <v>42.896785714285699</v>
+        <v>46.470833333333303</v>
       </c>
       <c r="T7" s="6">
-        <v>266.91333333333301</v>
+        <v>238.99285714285699</v>
       </c>
       <c r="U7" s="6">
-        <v>503.31693183804902</v>
+        <v>333.156998117098</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1264,7 +1267,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1272,49 +1275,47 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5">
-        <v>1186.94</v>
+        <v>1551.92</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1186.94</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1186.94</v>
-      </c>
+        <v>775.96</v>
+      </c>
+      <c r="L8" s="5"/>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
       <c r="N8" s="6">
-        <v>2.0299999999999998</v>
+        <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>347.28</v>
+        <v>508.95</v>
       </c>
       <c r="P8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="6">
         <v>1</v>
@@ -1323,10 +1324,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>347.28</v>
+        <v>254.47499999999999</v>
       </c>
       <c r="T8" s="6">
-        <v>347.28</v>
+        <v>508.95</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1356,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1364,25 +1365,25 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="5">
-        <v>5346.43</v>
+        <v>6637.43</v>
       </c>
       <c r="F9" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="5">
         <v>3</v>
@@ -1391,35 +1392,37 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>763.775714285714</v>
+        <v>829.67875000000004</v>
       </c>
       <c r="L9" s="5">
-        <v>1782.14333333333</v>
+        <v>2212.4766666666601</v>
       </c>
       <c r="M9" s="5">
         <v>-100</v>
       </c>
       <c r="N9" s="6">
-        <v>4.34</v>
+        <v>6.84</v>
       </c>
       <c r="O9" s="6">
-        <v>951</v>
+        <v>1414.13</v>
       </c>
       <c r="P9" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="6">
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>158.5</v>
-      </c>
-      <c r="T9" s="6"/>
+        <v>141.41300000000001</v>
+      </c>
+      <c r="T9" s="6">
+        <v>1414.13</v>
+      </c>
       <c r="U9" s="6">
-        <v>87.381703470031496</v>
+        <v>26.013874254842101</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1446,7 +1449,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1490,7 +1493,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1510,28 +1513,28 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>18.8</v>
+        <v>28.8</v>
       </c>
       <c r="O11" s="6">
-        <v>1372.54</v>
+        <v>1627.18</v>
       </c>
       <c r="P11" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="6">
         <v>2</v>
       </c>
       <c r="R11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>343.13499999999999</v>
+        <v>325.43599999999998</v>
       </c>
       <c r="T11" s="6">
-        <v>686.27</v>
+        <v>813.59</v>
       </c>
       <c r="U11" s="6">
-        <v>-100</v>
+        <v>363.50127213952902</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1546,13 +1549,13 @@
         <v>5</v>
       </c>
       <c r="Z11" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="8"/>
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1560,47 +1563,49 @@
         <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="C12" s="5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="D12" s="5">
         <v>3</v>
       </c>
       <c r="E12" s="5">
-        <v>1140.1199999999999</v>
+        <v>1298.3800000000001</v>
       </c>
       <c r="F12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5">
         <v>3</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5">
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>380.04</v>
-      </c>
-      <c r="L12" s="5"/>
+        <v>324.59500000000003</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1298.3800000000001</v>
+      </c>
       <c r="M12" s="5">
         <v>-100</v>
       </c>
       <c r="N12" s="6">
-        <v>1</v>
+        <v>2.02</v>
       </c>
       <c r="O12" s="6">
-        <v>128.59</v>
+        <v>251.99</v>
       </c>
       <c r="P12" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -1609,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>64.295000000000002</v>
+        <v>83.996666666666599</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6">
@@ -1640,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1660,10 +1665,10 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O13" s="6">
-        <v>575.92999999999995</v>
+        <v>658.38</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -1684,7 +1689,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1704,10 +1709,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>1.05</v>
+        <v>4.05</v>
       </c>
       <c r="O14" s="6">
-        <v>349.07</v>
+        <v>396.63</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1734,7 +1739,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1757,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>108.75</v>
+        <v>117.44</v>
       </c>
       <c r="P15" s="6">
         <v>1</v>
@@ -1769,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>108.75</v>
+        <v>117.44</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1798,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1815,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="5">
-        <v>55.35</v>
+        <v>109.62</v>
       </c>
       <c r="F16" s="5">
         <v>1</v>
@@ -1833,34 +1838,34 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>55.35</v>
+        <v>109.62</v>
       </c>
       <c r="L16" s="5">
-        <v>55.35</v>
+        <v>109.62</v>
       </c>
       <c r="M16" s="5">
         <v>-100</v>
       </c>
       <c r="N16" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O16" s="6">
-        <v>1742.21</v>
+        <v>2494.98</v>
       </c>
       <c r="P16" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>158.38272727272701</v>
+        <v>166.33199999999999</v>
       </c>
       <c r="T16" s="6">
-        <v>1742.21</v>
+        <v>1247.49</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1890,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,13 +1915,13 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O17" s="6">
-        <v>1444.04</v>
+        <v>1732.13</v>
       </c>
       <c r="P17" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -1925,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>722.02</v>
+        <v>577.37666666666598</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6">
@@ -1950,7 +1955,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1973,7 +1978,7 @@
         <v>0.98</v>
       </c>
       <c r="O18" s="6">
-        <v>210.34</v>
+        <v>286.91000000000003</v>
       </c>
       <c r="P18" s="6">
         <v>2</v>
@@ -1985,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>105.17</v>
+        <v>143.45500000000001</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6">
@@ -2014,7 +2019,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2037,7 +2042,7 @@
         <v>3</v>
       </c>
       <c r="O19" s="6">
-        <v>244.72</v>
+        <v>310.70999999999998</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2064,7 +2069,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2087,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="6">
-        <v>418.99</v>
+        <v>628.22</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2114,7 +2119,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2122,41 +2127,25 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>14.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="C21" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="E21" s="5">
-        <v>3130.55</v>
-      </c>
-      <c r="F21" s="5">
-        <v>9</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>9</v>
-      </c>
-      <c r="I21" s="5">
-        <v>4</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <v>347.83888888888799</v>
-      </c>
-      <c r="L21" s="5">
-        <v>782.63750000000005</v>
-      </c>
-      <c r="M21" s="5">
-        <v>-100</v>
-      </c>
+        <v>3952.72</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
@@ -2176,7 +2165,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2184,16 +2173,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
       </c>
       <c r="D22" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5">
-        <v>415.43</v>
+        <v>505.62</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -2222,49 +2211,35 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5">
-        <v>17.97</v>
-      </c>
-      <c r="C23" s="5">
-        <v>17.97</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>5277.01</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I23" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J23" s="5">
         <v>0</v>
       </c>
-      <c r="K23" s="5">
-        <v>5277.01</v>
-      </c>
-      <c r="L23" s="5">
-        <v>5277.01</v>
-      </c>
-      <c r="M23" s="5">
-        <v>-100</v>
-      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -2278,43 +2253,41 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
-      <c r="AA23" s="8">
-        <v>40000</v>
-      </c>
+      <c r="AA23" s="8"/>
       <c r="AB23" s="9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AC23" s="9">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>4.67</v>
+        <v>25.96</v>
       </c>
       <c r="C24" s="5">
-        <v>0</v>
+        <v>23.96</v>
       </c>
       <c r="D24" s="5">
-        <v>4.67</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5">
-        <v>824.11</v>
+        <v>6562.88</v>
       </c>
       <c r="F24" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" s="5">
         <v>1</v>
@@ -2323,78 +2296,64 @@
         <v>0</v>
       </c>
       <c r="K24" s="5">
-        <v>206.0275</v>
+        <v>3281.44</v>
       </c>
       <c r="L24" s="5">
-        <v>824.11</v>
+        <v>6562.88</v>
       </c>
       <c r="M24" s="5">
         <v>-100</v>
       </c>
-      <c r="N24" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="O24" s="6">
-        <v>310.95</v>
-      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
-      <c r="V24" s="7">
-        <v>22.52</v>
-      </c>
-      <c r="W24" s="7">
-        <v>3629.71</v>
-      </c>
-      <c r="X24" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>0</v>
-      </c>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
       <c r="AA24" s="8">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="AB24" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC24" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5">
-        <v>2.96</v>
+        <v>5.67</v>
       </c>
       <c r="C25" s="5">
         <v>0</v>
       </c>
       <c r="D25" s="5">
-        <v>2.96</v>
+        <v>5.67</v>
       </c>
       <c r="E25" s="5">
-        <v>570.37</v>
+        <v>1041.27</v>
       </c>
       <c r="F25" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="5">
         <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="5">
         <v>1</v>
@@ -2403,47 +2362,37 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>190.12333333333299</v>
+        <v>260.3175</v>
       </c>
       <c r="L25" s="5">
-        <v>570.37</v>
+        <v>1041.27</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="6">
-        <v>90.31</v>
-      </c>
-      <c r="P25" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <v>45.155000000000001</v>
-      </c>
+        <v>463.09</v>
+      </c>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
       <c r="T25" s="6"/>
-      <c r="U25" s="6">
-        <v>-100</v>
-      </c>
+      <c r="U25" s="6"/>
       <c r="V25" s="7">
-        <v>4</v>
+        <v>22.52</v>
       </c>
       <c r="W25" s="7">
-        <v>1033.75</v>
+        <v>3629.71</v>
       </c>
       <c r="X25" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="7">
         <v>0</v>
@@ -2452,99 +2401,121 @@
         <v>7000</v>
       </c>
       <c r="AB25" s="9">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC25" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1064.21</v>
+      </c>
+      <c r="F26" s="5">
+        <v>3</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>3</v>
+      </c>
+      <c r="I26" s="5">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5">
+        <v>354.736666666666</v>
+      </c>
+      <c r="L26" s="5">
+        <v>1064.21</v>
+      </c>
+      <c r="M26" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="6">
+        <v>0</v>
+      </c>
+      <c r="O26" s="6">
+        <v>158.08000000000001</v>
+      </c>
+      <c r="P26" s="6">
         <v>2</v>
       </c>
-      <c r="D26" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1611.02</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="6">
-        <v>11</v>
-      </c>
-      <c r="O26" s="6">
-        <v>1526.78</v>
-      </c>
-      <c r="P26" s="6">
-        <v>5</v>
-      </c>
       <c r="Q26" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" s="6">
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>305.35599999999999</v>
-      </c>
-      <c r="T26" s="6">
-        <v>763.39</v>
-      </c>
+        <v>79.040000000000006</v>
+      </c>
+      <c r="T26" s="6"/>
       <c r="U26" s="6">
         <v>-100</v>
       </c>
       <c r="V26" s="7">
-        <v>66.569999999999993</v>
+        <v>4</v>
       </c>
       <c r="W26" s="7">
-        <v>14965.45</v>
+        <v>1033.75</v>
       </c>
       <c r="X26" s="7">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="Y26" s="7">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Z26" s="7">
         <v>0</v>
       </c>
       <c r="AA26" s="8">
-        <v>12000</v>
+        <v>7000</v>
       </c>
       <c r="AB26" s="9">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AC26" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B27" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2029.93</v>
+      </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -2554,97 +2525,81 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="6">
-        <v>9</v>
+        <v>11.33</v>
       </c>
       <c r="O27" s="6">
-        <v>460.07</v>
+        <v>1926.14</v>
       </c>
       <c r="P27" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R27" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="6">
-        <v>92.013999999999996</v>
+        <v>321.02333333333303</v>
       </c>
       <c r="T27" s="6">
-        <v>460.07</v>
+        <v>481.53500000000003</v>
       </c>
       <c r="U27" s="6">
-        <v>-100</v>
+        <v>144.634346413033</v>
       </c>
       <c r="V27" s="7">
-        <v>65.91</v>
+        <v>66.569999999999993</v>
       </c>
       <c r="W27" s="7">
-        <v>3947.31</v>
+        <v>14965.45</v>
       </c>
       <c r="X27" s="7">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y27" s="7">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Z27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>12000</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>26</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>7</v>
+      </c>
       <c r="AD27" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="5">
-        <v>4.99</v>
-      </c>
-      <c r="C28" s="5">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5">
-        <v>4.99</v>
-      </c>
-      <c r="E28" s="5">
-        <v>1594.66</v>
-      </c>
-      <c r="F28" s="5">
-        <v>7</v>
-      </c>
-      <c r="G28" s="5">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5">
-        <v>7</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5">
-        <v>227.80857142857101</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="5">
-        <v>-100</v>
-      </c>
+      <c r="M28" s="5"/>
       <c r="N28" s="6">
-        <v>4.58</v>
+        <v>9</v>
       </c>
       <c r="O28" s="6">
-        <v>630.16</v>
+        <v>587.62</v>
       </c>
       <c r="P28" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q28" s="6">
         <v>1</v>
@@ -2653,105 +2608,131 @@
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>210.053333333333</v>
+        <v>97.936666666666596</v>
       </c>
       <c r="T28" s="6">
-        <v>630.16</v>
+        <v>587.62</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
       </c>
       <c r="V28" s="7">
-        <v>55.58</v>
+        <v>65.91</v>
       </c>
       <c r="W28" s="7">
-        <v>8745.86</v>
+        <v>3947.31</v>
       </c>
       <c r="X28" s="7">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="Y28" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Z28" s="7">
         <v>0</v>
       </c>
-      <c r="AA28" s="8">
-        <v>13000</v>
-      </c>
-      <c r="AB28" s="9">
-        <v>31</v>
-      </c>
-      <c r="AC28" s="9">
-        <v>10</v>
-      </c>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="B29" s="5">
+        <v>6.99</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2036.08</v>
+      </c>
+      <c r="F29" s="5">
+        <v>8</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5">
+        <v>7</v>
+      </c>
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
+        <v>254.51</v>
+      </c>
+      <c r="L29" s="5">
+        <v>2036.08</v>
+      </c>
+      <c r="M29" s="5">
+        <v>-100</v>
+      </c>
       <c r="N29" s="6">
-        <v>15.99</v>
+        <v>8.58</v>
       </c>
       <c r="O29" s="6">
-        <v>1000.4</v>
+        <v>977.45</v>
       </c>
       <c r="P29" s="6">
         <v>6</v>
       </c>
       <c r="Q29" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" s="6">
         <v>0</v>
       </c>
       <c r="S29" s="6">
-        <v>166.73333333333301</v>
-      </c>
-      <c r="T29" s="6"/>
+        <v>162.90833333333299</v>
+      </c>
+      <c r="T29" s="6">
+        <v>488.72500000000002</v>
+      </c>
       <c r="U29" s="6">
         <v>-100</v>
       </c>
       <c r="V29" s="7">
-        <v>98.369999999999905</v>
+        <v>55.58</v>
       </c>
       <c r="W29" s="7">
-        <v>6238.21</v>
+        <v>8745.86</v>
       </c>
       <c r="X29" s="7">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="Y29" s="7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Z29" s="7">
         <v>0</v>
       </c>
-      <c r="AA29" s="8"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
+      <c r="AA29" s="8">
+        <v>13000</v>
+      </c>
+      <c r="AB29" s="9">
+        <v>31</v>
+      </c>
+      <c r="AC29" s="9">
+        <v>10</v>
+      </c>
       <c r="AD29" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2766,13 +2747,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>13.02</v>
+        <v>17.52</v>
       </c>
       <c r="O30" s="6">
-        <v>1115.83</v>
+        <v>1212.04</v>
       </c>
       <c r="P30" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -2781,20 +2762,20 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>557.91499999999996</v>
+        <v>202.00666666666601</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
         <v>-100</v>
       </c>
       <c r="V30" s="7">
-        <v>126.03</v>
+        <v>98.369999999999905</v>
       </c>
       <c r="W30" s="7">
-        <v>9571.31</v>
+        <v>6238.21</v>
       </c>
       <c r="X30" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y30" s="7">
         <v>2</v>
@@ -2806,203 +2787,197 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="5">
-        <v>14.44</v>
-      </c>
-      <c r="C31" s="5">
-        <v>7.94</v>
-      </c>
-      <c r="D31" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="E31" s="5">
-        <v>3916.88</v>
-      </c>
-      <c r="F31" s="5">
-        <v>7</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5">
-        <v>7</v>
-      </c>
-      <c r="I31" s="5">
+        <v>50</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6">
+        <v>17.02</v>
+      </c>
+      <c r="O31" s="6">
+        <v>1358.98</v>
+      </c>
+      <c r="P31" s="6">
         <v>3</v>
       </c>
-      <c r="J31" s="5">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5">
-        <v>559.55428571428502</v>
-      </c>
-      <c r="L31" s="5">
-        <v>1305.62666666666</v>
-      </c>
-      <c r="M31" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N31" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="O31" s="6">
-        <v>1211.51</v>
-      </c>
-      <c r="P31" s="6">
-        <v>5</v>
-      </c>
       <c r="Q31" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="6">
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>242.30199999999999</v>
-      </c>
-      <c r="T31" s="6">
-        <v>1211.51</v>
-      </c>
+        <v>452.993333333333</v>
+      </c>
+      <c r="T31" s="6"/>
       <c r="U31" s="6">
         <v>-100</v>
       </c>
       <c r="V31" s="7">
-        <v>22.8</v>
+        <v>126.03</v>
       </c>
       <c r="W31" s="7">
-        <v>6170.17</v>
+        <v>9571.31</v>
       </c>
       <c r="X31" s="7">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Y31" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="7">
         <v>0</v>
       </c>
-      <c r="AA31" s="8">
-        <v>28000</v>
-      </c>
-      <c r="AB31" s="9">
-        <v>42</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>21</v>
-      </c>
+      <c r="AA31" s="8"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>11.85</v>
+        <v>17.939999999999898</v>
       </c>
       <c r="C32" s="5">
-        <v>3.63</v>
+        <v>10.94</v>
       </c>
       <c r="D32" s="5">
-        <v>8.2200000000000006</v>
+        <v>7</v>
       </c>
       <c r="E32" s="5">
-        <v>4097.45</v>
+        <v>4950.0200000000004</v>
       </c>
       <c r="F32" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G32" s="5">
         <v>0</v>
       </c>
       <c r="H32" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5">
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <v>585.35</v>
+        <v>550.00222222222203</v>
       </c>
       <c r="L32" s="5">
-        <v>4097.45</v>
+        <v>1650.0066666666601</v>
       </c>
       <c r="M32" s="5">
         <v>-100</v>
       </c>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
+      <c r="N32" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="O32" s="6">
+        <v>1604.36</v>
+      </c>
+      <c r="P32" s="6">
+        <v>7</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>1</v>
+      </c>
+      <c r="R32" s="6">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6">
+        <v>229.194285714285</v>
+      </c>
+      <c r="T32" s="6">
+        <v>1604.36</v>
+      </c>
+      <c r="U32" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="7">
+        <v>22.8</v>
+      </c>
+      <c r="W32" s="7">
+        <v>6170.17</v>
+      </c>
+      <c r="X32" s="7">
+        <v>30</v>
+      </c>
+      <c r="Y32" s="7">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="7">
+        <v>0</v>
+      </c>
       <c r="AA32" s="8">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="AB32" s="9">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="AC32" s="9">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>15.35</v>
+        <v>15.85</v>
       </c>
       <c r="C33" s="5">
-        <v>8.35</v>
+        <v>4.63</v>
       </c>
       <c r="D33" s="5">
-        <v>7</v>
+        <v>11.22</v>
       </c>
       <c r="E33" s="5">
-        <v>4917.6400000000003</v>
+        <v>5150.6400000000003</v>
       </c>
       <c r="F33" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
       </c>
       <c r="H33" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I33" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="5">
         <v>0</v>
       </c>
       <c r="K33" s="5">
-        <v>614.70500000000004</v>
+        <v>515.06399999999996</v>
       </c>
       <c r="L33" s="5">
-        <v>1639.21333333333</v>
+        <v>5150.6400000000003</v>
       </c>
       <c r="M33" s="5">
         <v>-100</v>
@@ -3021,152 +2996,174 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="8">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AB33" s="9">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="AC33" s="9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>12.99</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="C34" s="5">
-        <v>8.99</v>
+        <v>8.85</v>
       </c>
       <c r="D34" s="5">
+        <v>11</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5839.7</v>
+      </c>
+      <c r="F34" s="5">
+        <v>10</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5">
+        <v>10</v>
+      </c>
+      <c r="I34" s="5">
         <v>4</v>
       </c>
-      <c r="E34" s="5">
-        <v>3179.4</v>
-      </c>
-      <c r="F34" s="5">
-        <v>5</v>
-      </c>
-      <c r="G34" s="5">
-        <v>2</v>
-      </c>
-      <c r="H34" s="5">
-        <v>3</v>
-      </c>
-      <c r="I34" s="5">
-        <v>1</v>
-      </c>
       <c r="J34" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="5">
-        <v>635.88</v>
+        <v>583.97</v>
       </c>
       <c r="L34" s="5">
-        <v>3179.4</v>
+        <v>1459.925</v>
       </c>
       <c r="M34" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N34" s="6">
-        <v>7</v>
-      </c>
-      <c r="O34" s="6">
-        <v>2855.89</v>
-      </c>
-      <c r="P34" s="6">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>3</v>
-      </c>
-      <c r="R34" s="6">
-        <v>0</v>
-      </c>
-      <c r="S34" s="6">
-        <v>285.589</v>
-      </c>
-      <c r="T34" s="6">
-        <v>951.96333333333303</v>
-      </c>
-      <c r="U34" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V34" s="7">
-        <v>110.24</v>
-      </c>
-      <c r="W34" s="7">
-        <v>28910.07</v>
-      </c>
-      <c r="X34" s="7">
-        <v>128</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>45</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>0</v>
-      </c>
+        <v>-4.7896296042604796</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
       <c r="AA34" s="8">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="AB34" s="9">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="AC34" s="9">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>3</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="C35" s="5">
+        <v>13.99</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="E35" s="5">
+        <v>4397.24</v>
+      </c>
+      <c r="F35" s="5">
+        <v>6</v>
+      </c>
+      <c r="G35" s="5">
         <v>2</v>
       </c>
-      <c r="D35" s="5">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1458.13</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
+      <c r="H35" s="5">
+        <v>4</v>
+      </c>
+      <c r="I35" s="5">
+        <v>2</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>732.87333333333299</v>
+      </c>
+      <c r="L35" s="5">
+        <v>2198.62</v>
+      </c>
+      <c r="M35" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="6">
+        <v>8</v>
+      </c>
+      <c r="O35" s="6">
+        <v>4085.11</v>
+      </c>
+      <c r="P35" s="6">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>4</v>
+      </c>
+      <c r="R35" s="6">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6">
+        <v>314.23923076923001</v>
+      </c>
+      <c r="T35" s="6">
+        <v>1021.2775</v>
+      </c>
+      <c r="U35" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V35" s="7">
+        <v>110.24</v>
+      </c>
+      <c r="W35" s="7">
+        <v>28910.07</v>
+      </c>
+      <c r="X35" s="7">
+        <v>128</v>
+      </c>
+      <c r="Y35" s="7">
+        <v>45</v>
+      </c>
+      <c r="Z35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="8">
+        <v>35000</v>
+      </c>
+      <c r="AB35" s="9">
+        <v>57</v>
+      </c>
+      <c r="AC35" s="9">
+        <v>14</v>
+      </c>
       <c r="AD35" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3186,13 +3183,13 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="6">
-        <v>27.81</v>
+        <v>35.81</v>
       </c>
       <c r="O36" s="6">
-        <v>880.27</v>
+        <v>1136.49</v>
       </c>
       <c r="P36" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -3201,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="6">
-        <v>220.0675</v>
+        <v>227.298</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6">
@@ -3226,7 +3223,7 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3243,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="5">
-        <v>1019.98</v>
+        <v>1300.25</v>
       </c>
       <c r="F37" s="5">
         <v>2</v>
@@ -3261,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>509.99</v>
+        <v>650.125</v>
       </c>
       <c r="L37" s="5">
-        <v>1019.98</v>
+        <v>1300.25</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
@@ -3292,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="AD37" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3300,16 +3297,16 @@
         <v>58</v>
       </c>
       <c r="B38" s="5">
-        <v>8.99</v>
+        <v>10.99</v>
       </c>
       <c r="C38" s="5">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
       <c r="D38" s="5">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E38" s="5">
-        <v>2742.85</v>
+        <v>3329.43</v>
       </c>
       <c r="F38" s="5">
         <v>1</v>
@@ -3327,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="5">
-        <v>2742.85</v>
+        <v>3329.43</v>
       </c>
       <c r="L38" s="5">
-        <v>2742.85</v>
+        <v>3329.43</v>
       </c>
       <c r="M38" s="5">
         <v>-100</v>
@@ -3339,10 +3336,10 @@
         <v>1</v>
       </c>
       <c r="O38" s="6">
-        <v>1242.1099999999999</v>
+        <v>1636.35</v>
       </c>
       <c r="P38" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="6">
         <v>1</v>
@@ -3351,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="6">
-        <v>414.03666666666601</v>
+        <v>409.08749999999998</v>
       </c>
       <c r="T38" s="6">
-        <v>1242.1099999999999</v>
+        <v>1636.35</v>
       </c>
       <c r="U38" s="6">
         <v>-100</v>
@@ -3384,7 +3381,7 @@
         <v>16</v>
       </c>
       <c r="AD38" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3404,10 +3401,10 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O39" s="6">
-        <v>767.62</v>
+        <v>945.28</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
@@ -3434,7 +3431,7 @@
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3442,44 +3439,30 @@
         <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="C40" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="D40" s="5">
         <v>2</v>
       </c>
-      <c r="D40" s="5">
-        <v>1</v>
-      </c>
       <c r="E40" s="5">
-        <v>2322.61</v>
-      </c>
-      <c r="F40" s="5">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5">
-        <v>1</v>
-      </c>
-      <c r="I40" s="5">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5">
-        <v>2322.61</v>
-      </c>
+        <v>2919.05</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
       <c r="L40" s="5"/>
-      <c r="M40" s="5">
-        <v>-100</v>
-      </c>
+      <c r="M40" s="5"/>
       <c r="N40" s="6">
         <v>0</v>
       </c>
       <c r="O40" s="6">
-        <v>89.37</v>
+        <v>129.74</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -3502,7 +3485,7 @@
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
@@ -3510,49 +3493,49 @@
         <v>60</v>
       </c>
       <c r="B41">
-        <v>7.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C41">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>2861.78</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>9</v>
+      </c>
+      <c r="I41">
         <v>4</v>
       </c>
-      <c r="E41">
-        <v>2016.05</v>
-      </c>
-      <c r="F41">
-        <v>7</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>7</v>
-      </c>
-      <c r="I41">
-        <v>3</v>
-      </c>
       <c r="J41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>288.00714285714201</v>
+        <v>286.178</v>
       </c>
       <c r="L41">
-        <v>672.01666666666597</v>
+        <v>715.44500000000005</v>
       </c>
       <c r="M41">
-        <v>289.55779866570703</v>
+        <v>476.97237383726201</v>
       </c>
       <c r="N41">
-        <v>8.02</v>
+        <v>10.02</v>
       </c>
       <c r="O41">
-        <v>979.17</v>
+        <v>1254.9100000000001</v>
       </c>
       <c r="P41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q41">
         <v>1</v>
@@ -3561,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="S41">
-        <v>108.796666666666</v>
+        <v>114.082727272727</v>
       </c>
       <c r="T41">
-        <v>979.17</v>
+        <v>1254.9100000000001</v>
       </c>
       <c r="U41">
         <v>-100</v>
@@ -3594,204 +3577,216 @@
         <v>12</v>
       </c>
       <c r="AD41" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B42">
-        <v>2</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>1104.46</v>
+        <v>61</v>
+      </c>
+      <c r="N42">
+        <v>23.16</v>
+      </c>
+      <c r="O42">
+        <v>1238.47</v>
+      </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>247.69399999999999</v>
+      </c>
+      <c r="U42">
+        <v>-100</v>
+      </c>
+      <c r="V42">
+        <v>127.59</v>
+      </c>
+      <c r="W42">
+        <v>8783.7999999999993</v>
+      </c>
+      <c r="X42">
+        <v>27</v>
+      </c>
+      <c r="Y42">
+        <v>4</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
       </c>
       <c r="AD42" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="B43">
+        <v>7.99</v>
+      </c>
+      <c r="C43">
+        <v>3.99</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>1870.58</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>467.64499999999998</v>
+      </c>
+      <c r="L43">
+        <v>1870.58</v>
+      </c>
+      <c r="M43">
+        <v>-100</v>
       </c>
       <c r="N43">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O43">
-        <v>936.73</v>
+        <v>577.48</v>
       </c>
       <c r="P43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>234.1825</v>
+        <v>192.493333333333</v>
+      </c>
+      <c r="T43">
+        <v>577.48</v>
       </c>
       <c r="U43">
         <v>-100</v>
       </c>
       <c r="V43">
-        <v>127.59</v>
+        <v>23.02</v>
       </c>
       <c r="W43">
-        <v>8783.7999999999993</v>
+        <v>4636.55</v>
       </c>
       <c r="X43">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y43">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z43">
         <v>0</v>
       </c>
+      <c r="AA43">
+        <v>11000</v>
+      </c>
+      <c r="AB43">
+        <v>14</v>
+      </c>
+      <c r="AC43">
+        <v>6</v>
+      </c>
       <c r="AD43" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44">
-        <v>3.99</v>
-      </c>
-      <c r="C44">
-        <v>1.99</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44">
-        <v>1416.29</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>2</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>708.14499999999998</v>
-      </c>
-      <c r="L44">
-        <v>1416.29</v>
-      </c>
-      <c r="M44">
-        <v>-100</v>
+        <v>66</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>13.19</v>
       </c>
       <c r="O44">
-        <v>473.88</v>
+        <v>672.34</v>
       </c>
       <c r="P44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <v>0</v>
       </c>
       <c r="S44">
-        <v>236.94</v>
+        <v>224.113333333333</v>
+      </c>
+      <c r="T44">
+        <v>672.34</v>
       </c>
       <c r="U44">
         <v>-100</v>
       </c>
       <c r="V44">
-        <v>23.02</v>
+        <v>56.01</v>
       </c>
       <c r="W44">
-        <v>4636.55</v>
+        <v>4863.79</v>
       </c>
       <c r="X44">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z44">
         <v>0</v>
       </c>
-      <c r="AA44">
-        <v>11000</v>
-      </c>
-      <c r="AB44">
-        <v>14</v>
-      </c>
-      <c r="AC44">
-        <v>6</v>
-      </c>
       <c r="AD44" s="13">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="N45">
-        <v>7.19</v>
-      </c>
-      <c r="O45">
-        <v>531.65</v>
-      </c>
-      <c r="P45">
+        <v>139</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
         <v>2</v>
       </c>
-      <c r="Q45">
-        <v>1</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>265.82499999999999</v>
-      </c>
-      <c r="T45">
-        <v>531.65</v>
-      </c>
-      <c r="U45">
-        <v>-100</v>
-      </c>
-      <c r="V45">
-        <v>56.01</v>
-      </c>
-      <c r="W45">
-        <v>4863.79</v>
-      </c>
-      <c r="X45">
-        <v>10</v>
-      </c>
-      <c r="Y45">
-        <v>4</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
+      <c r="AC45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
@@ -3827,7 +3822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4704,13 +4699,13 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
+        <v>12</v>
+      </c>
+      <c r="E21" s="10">
         <v>10</v>
       </c>
-      <c r="E21" s="10">
-        <v>8</v>
-      </c>
       <c r="F21" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="10">
         <v>1</v>
@@ -4728,13 +4723,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>10.31</v>
+        <v>9.84</v>
       </c>
       <c r="M21" s="10">
         <v>0</v>
       </c>
       <c r="N21" s="10">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="O21" s="10">
         <v>0</v>
@@ -4745,7 +4740,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B22" s="19">
         <v>2026</v>
@@ -4754,16 +4749,16 @@
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E22" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F22" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10">
         <v>0</v>
@@ -4778,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>10.31</v>
+        <v>0.82</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
       </c>
       <c r="N22" s="10">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O22" s="10">
         <v>0</v>
@@ -4795,7 +4790,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="19">
         <v>2026</v>
@@ -4804,16 +4799,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E23" s="10">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F23" s="10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G23" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="10">
         <v>0</v>
@@ -4828,22 +4823,24 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.03</v>
+        <v>10.66</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
       </c>
       <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10"/>
+        <v>53.85</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0</v>
+      </c>
       <c r="P23" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="19">
         <v>2026</v>
@@ -4852,16 +4849,16 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
@@ -4876,24 +4873,22 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.06</v>
+        <v>0.82</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
       </c>
       <c r="N24" s="10">
-        <v>50</v>
-      </c>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10"/>
       <c r="P24" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B25" s="19">
         <v>2026</v>
@@ -4902,13 +4897,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="10">
         <v>0</v>
@@ -4926,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>6.19</v>
+        <v>1.64</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -4943,7 +4938,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" s="19">
         <v>2026</v>
@@ -4952,16 +4947,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" s="10">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F26" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10">
         <v>0</v>
@@ -4976,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>12.37</v>
+        <v>4.92</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -4993,7 +4988,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B27" s="19">
         <v>2026</v>
@@ -5002,48 +4997,48 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E27" s="10">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F27" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="10">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="J27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="10">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="L27" s="10">
-        <v>7.22</v>
+        <v>10.66</v>
       </c>
       <c r="M27" s="10">
-        <v>0</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="N27" s="10">
-        <v>14.29</v>
+        <v>38.46</v>
       </c>
       <c r="O27" s="10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P27" s="10">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B28" s="19">
         <v>2026</v>
@@ -5052,16 +5047,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E28" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -5076,22 +5071,24 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>12.37</v>
+        <v>5.74</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>0</v>
-      </c>
-      <c r="O28" s="10"/>
+        <v>14.29</v>
+      </c>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
       <c r="P28" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B29" s="19">
         <v>2026</v>
@@ -5100,16 +5097,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E29" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F29" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H29" s="10">
         <v>0</v>
@@ -5124,24 +5121,22 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>11.34</v>
+        <v>13.11</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>36.36</v>
-      </c>
-      <c r="O29" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O29" s="10"/>
       <c r="P29" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="19">
         <v>2026</v>
@@ -5150,16 +5145,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E30" s="10">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F30" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="10">
         <v>0</v>
@@ -5174,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>9.2799999999999994</v>
+        <v>13.11</v>
       </c>
       <c r="M30" s="10">
         <v>0</v>
       </c>
       <c r="N30" s="10">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="O30" s="10">
         <v>0</v>
@@ -5191,7 +5186,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="19">
         <v>2026</v>
@@ -5200,16 +5195,16 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
+        <v>10</v>
+      </c>
+      <c r="E31" s="10">
+        <v>8</v>
+      </c>
+      <c r="F31" s="10">
         <v>3</v>
       </c>
-      <c r="E31" s="10">
-        <v>3</v>
-      </c>
-      <c r="F31" s="10">
-        <v>2</v>
-      </c>
       <c r="G31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
@@ -5224,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>3.09</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
       </c>
       <c r="N31" s="10">
-        <v>66.67</v>
+        <v>30</v>
       </c>
       <c r="O31" s="10">
         <v>0</v>
@@ -5241,7 +5236,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="19">
         <v>2026</v>
@@ -5250,46 +5245,48 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="10">
-        <v>0</v>
+        <v>5560</v>
       </c>
       <c r="J32" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="10">
-        <v>0</v>
+        <v>5560</v>
       </c>
       <c r="L32" s="10">
-        <v>4.12</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M32" s="10">
-        <v>0</v>
+        <v>22.98</v>
       </c>
       <c r="N32" s="10">
-        <v>0</v>
-      </c>
-      <c r="O32" s="10"/>
+        <v>60</v>
+      </c>
+      <c r="O32" s="10">
+        <v>33.33</v>
+      </c>
       <c r="P32" s="10">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="19">
         <v>2026</v>
@@ -5298,48 +5295,46 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
       </c>
       <c r="H33" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="10">
-        <v>7853.68</v>
+        <v>0</v>
       </c>
       <c r="J33" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="10">
-        <v>7853.68</v>
+        <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>6.19</v>
+        <v>2.46</v>
       </c>
       <c r="M33" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>66.67</v>
-      </c>
-      <c r="O33" s="10">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O33" s="10"/>
       <c r="P33" s="10">
-        <v>16.670000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="19">
         <v>2026</v>
@@ -5348,42 +5343,92 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E34" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F34" s="10">
+        <v>5</v>
+      </c>
+      <c r="G34" s="10">
         <v>2</v>
       </c>
-      <c r="G34" s="10">
-        <v>0</v>
-      </c>
       <c r="H34" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="10">
-        <v>0</v>
+        <v>16511.68</v>
       </c>
       <c r="J34" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" s="10">
-        <v>0</v>
+        <v>16511.68</v>
       </c>
       <c r="L34" s="10">
-        <v>4.12</v>
+        <v>7.38</v>
       </c>
       <c r="M34" s="10">
-        <v>0</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="N34" s="10">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="O34" s="10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P34" s="10">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>6.56</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>25</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
         <v>0</v>
       </c>
     </row>
@@ -5543,13 +5588,13 @@
         <v>92</v>
       </c>
       <c r="I7" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7" s="5">
-        <v>444089.44</v>
+        <v>449291.44</v>
       </c>
       <c r="K7" s="5">
-        <v>16.91</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5747,7 +5792,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5855,16 +5900,16 @@
         <v>301</v>
       </c>
       <c r="H16" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I16" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J16" s="5">
-        <v>511623.25</v>
+        <v>504461.62</v>
       </c>
       <c r="K16" s="5">
-        <v>32.840000000000003</v>
+        <v>32.369999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5893,13 +5938,13 @@
         <v>94</v>
       </c>
       <c r="I17" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" s="5">
-        <v>242533.65</v>
+        <v>245530.65</v>
       </c>
       <c r="K17" s="5">
-        <v>18.149999999999999</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5957,7 +6002,7 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H19" s="5">
         <v>101</v>
@@ -6001,10 +6046,10 @@
         <v>28</v>
       </c>
       <c r="J20" s="10">
-        <v>221115.51999999999</v>
+        <v>219615.52</v>
       </c>
       <c r="K20" s="10">
-        <v>24.18</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -6018,28 +6063,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>514</v>
+        <v>686</v>
       </c>
       <c r="E21" s="10">
-        <v>1307.6300000000001</v>
+        <v>1785.97</v>
       </c>
       <c r="F21" s="10">
-        <v>33.01</v>
+        <v>43.51</v>
       </c>
       <c r="G21" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H21" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="10">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="K21" s="10">
-        <v>-1</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6246,7 +6291,7 @@
         <v>3</v>
       </c>
       <c r="J27" s="10">
-        <v>22604.559999999899</v>
+        <v>22604.560000000001</v>
       </c>
       <c r="K27" s="10">
         <v>3.62</v>
@@ -6374,7 +6419,7 @@
         <v>6171.75</v>
       </c>
       <c r="F31" s="10">
-        <v>37.019999999999897</v>
+        <v>37.020000000000003</v>
       </c>
       <c r="G31" s="10">
         <v>16</v>
@@ -6421,7 +6466,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>14306.779999999901</v>
+        <v>14306.78</v>
       </c>
       <c r="K32" s="10">
         <v>1.22</v>
@@ -6593,13 +6638,13 @@
         <v>11</v>
       </c>
       <c r="I37" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="10">
-        <v>23381.68</v>
+        <v>31697.68</v>
       </c>
       <c r="K37" s="10">
-        <v>1.97</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -6613,16 +6658,16 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E38" s="10">
-        <v>1186.94</v>
+        <v>1551.92</v>
       </c>
       <c r="F38" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="10">
         <v>1</v>
@@ -6829,7 +6874,7 @@
         <v>22445.41</v>
       </c>
       <c r="F44" s="10">
-        <v>66.789999999999907</v>
+        <v>66.790000000000006</v>
       </c>
       <c r="G44" s="10">
         <v>91</v>
@@ -7004,7 +7049,7 @@
         <v>14924.23</v>
       </c>
       <c r="F49" s="10">
-        <v>57.019999999999897</v>
+        <v>57.02</v>
       </c>
       <c r="G49" s="10">
         <v>58</v>
@@ -7109,7 +7154,7 @@
         <v>27112.02</v>
       </c>
       <c r="F52" s="10">
-        <v>104.94999999999899</v>
+        <v>104.95</v>
       </c>
       <c r="G52" s="10">
         <v>64</v>
@@ -7147,7 +7192,7 @@
         <v>141.16999999999999</v>
       </c>
       <c r="G53" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H53" s="10">
         <v>36</v>
@@ -7208,16 +7253,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>462</v>
+        <v>565</v>
       </c>
       <c r="E55" s="10">
-        <v>5346.43</v>
+        <v>6637.43</v>
       </c>
       <c r="F55" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G55" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H55" s="10">
         <v>3</v>
@@ -7621,7 +7666,7 @@
         <v>518</v>
       </c>
       <c r="E67" s="10">
-        <v>6279.5199999999904</v>
+        <v>6279.52</v>
       </c>
       <c r="F67" s="10">
         <v>16</v>
@@ -7846,7 +7891,7 @@
         <v>2</v>
       </c>
       <c r="J73" s="10">
-        <v>12248.279999999901</v>
+        <v>12248.28</v>
       </c>
       <c r="K73" s="10">
         <v>1.4</v>
@@ -7968,19 +8013,19 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E77" s="10">
-        <v>1140.1199999999999</v>
+        <v>1298.3800000000001</v>
       </c>
       <c r="F77" s="10">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="G77" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="10">
         <v>0</v>
@@ -8723,29 +8768,19 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="E100" s="10">
-        <v>2322.61</v>
+        <v>2919.05</v>
       </c>
       <c r="F100" s="10">
-        <v>3</v>
-      </c>
-      <c r="G100" s="10">
-        <v>1</v>
-      </c>
-      <c r="H100" s="10">
-        <v>0</v>
-      </c>
-      <c r="I100" s="10">
-        <v>0</v>
-      </c>
-      <c r="J100" s="10">
-        <v>0</v>
-      </c>
-      <c r="K100" s="10">
-        <v>-1</v>
-      </c>
+        <v>4.67</v>
+      </c>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
@@ -9294,7 +9329,7 @@
         <v>32413.439999999999</v>
       </c>
       <c r="F117" s="10">
-        <v>188.32999999999899</v>
+        <v>188.33</v>
       </c>
       <c r="G117" s="10">
         <v>34</v>
@@ -9577,7 +9612,7 @@
         <v>50.47</v>
       </c>
       <c r="G125" s="10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H125" s="10">
         <v>19</v>
@@ -9848,10 +9883,10 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E133" s="10">
-        <v>55.35</v>
+        <v>109.62</v>
       </c>
       <c r="F133" s="10">
         <v>1</v>
@@ -10426,7 +10461,7 @@
         <v>3</v>
       </c>
       <c r="J149" s="10">
-        <v>22749.7399999999</v>
+        <v>22749.74</v>
       </c>
       <c r="K149" s="10">
         <v>2.15</v>
@@ -10461,7 +10496,7 @@
         <v>5</v>
       </c>
       <c r="J150" s="10">
-        <v>32597.059999999899</v>
+        <v>32597.06</v>
       </c>
       <c r="K150" s="10">
         <v>3.14</v>
@@ -10519,7 +10554,7 @@
         <v>9261.49</v>
       </c>
       <c r="F152" s="10">
-        <v>32.349999999999902</v>
+        <v>32.35</v>
       </c>
       <c r="G152" s="10">
         <v>12</v>
@@ -10589,7 +10624,7 @@
         <v>8958.39</v>
       </c>
       <c r="F154" s="10">
-        <v>13.969999999999899</v>
+        <v>13.97</v>
       </c>
       <c r="G154" s="10">
         <v>7</v>
@@ -11193,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="J172" s="10">
-        <v>7696.8099999999904</v>
+        <v>7696.81</v>
       </c>
       <c r="K172" s="10">
         <v>0.92</v>
@@ -11666,7 +11701,7 @@
         <v>4</v>
       </c>
       <c r="J186" s="10">
-        <v>24872.559999999899</v>
+        <v>24872.560000000001</v>
       </c>
       <c r="K186" s="10">
         <v>0.09</v>
@@ -11683,19 +11718,19 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>352</v>
+        <v>434</v>
       </c>
       <c r="E187" s="10">
-        <v>3130.55</v>
+        <v>3952.72</v>
       </c>
       <c r="F187" s="10">
-        <v>14.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="G187" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H187" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I187" s="10">
         <v>0</v>
@@ -11768,13 +11803,13 @@
         <v>18</v>
       </c>
       <c r="D190" s="10">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E190" s="10">
-        <v>415.43</v>
+        <v>505.62</v>
       </c>
       <c r="F190" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
@@ -11828,16 +11863,16 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>11592</v>
+        <v>14697</v>
       </c>
       <c r="E192" s="10">
-        <v>5277.01</v>
+        <v>6562.88</v>
       </c>
       <c r="F192" s="10">
-        <v>17.97</v>
+        <v>25.96</v>
       </c>
       <c r="G192" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" s="10">
         <v>1</v>
@@ -12034,7 +12069,7 @@
         <v>3926.43</v>
       </c>
       <c r="F198" s="10">
-        <v>16.009999999999899</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="G198" s="10">
         <v>11</v>
@@ -12326,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="J206" s="10">
-        <v>5742.7999999999902</v>
+        <v>5742.8</v>
       </c>
       <c r="K206" s="10">
         <v>0.16</v>
@@ -12413,13 +12448,13 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E209" s="10">
-        <v>824.11</v>
+        <v>1041.27</v>
       </c>
       <c r="F209" s="10">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="G209" s="10">
         <v>4</v>
@@ -12524,7 +12559,7 @@
         <v>1671.98</v>
       </c>
       <c r="F212" s="10">
-        <v>8.71999999999999</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="G212" s="10">
         <v>7</v>
@@ -12676,7 +12711,7 @@
         <v>1</v>
       </c>
       <c r="J216" s="10">
-        <v>7991.99999999999</v>
+        <v>7992</v>
       </c>
       <c r="K216" s="10">
         <v>145.88</v>
@@ -12886,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="J222" s="10">
-        <v>3995.99999999999</v>
+        <v>3996</v>
       </c>
       <c r="K222" s="10">
         <v>-0.03</v>
@@ -13008,10 +13043,10 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E226" s="10">
-        <v>570.37</v>
+        <v>1064.21</v>
       </c>
       <c r="F226" s="10">
         <v>2.96</v>
@@ -13434,7 +13469,7 @@
         <v>9126.74</v>
       </c>
       <c r="F238" s="10">
-        <v>20.009999999999899</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="G238" s="10">
         <v>30</v>
@@ -13472,10 +13507,10 @@
         <v>31.97</v>
       </c>
       <c r="G239" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H239" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I239" s="10">
         <v>4</v>
@@ -13586,7 +13621,7 @@
         <v>2</v>
       </c>
       <c r="J242" s="10">
-        <v>15351.779999999901</v>
+        <v>15351.78</v>
       </c>
       <c r="K242" s="10">
         <v>0.28000000000000003</v>
@@ -13603,13 +13638,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E243" s="10">
-        <v>1611.02</v>
+        <v>2029.93</v>
       </c>
       <c r="F243" s="10">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G243" s="10"/>
       <c r="H243" s="10"/>
@@ -13634,7 +13669,7 @@
         <v>2070.7399999999998</v>
       </c>
       <c r="F244" s="10">
-        <v>16.939999999999898</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="G244" s="10">
         <v>10</v>
@@ -13704,7 +13739,7 @@
         <v>3037.13</v>
       </c>
       <c r="F246" s="10">
-        <v>34.519999999999897</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="G246" s="10">
         <v>12</v>
@@ -13774,7 +13809,7 @@
         <v>3925.81</v>
       </c>
       <c r="F248" s="10">
-        <v>18.509999999999899</v>
+        <v>18.510000000000002</v>
       </c>
       <c r="G248" s="10">
         <v>18</v>
@@ -14159,7 +14194,7 @@
         <v>12933.74</v>
       </c>
       <c r="F259" s="10">
-        <v>44.879999999999903</v>
+        <v>44.88</v>
       </c>
       <c r="G259" s="10">
         <v>19</v>
@@ -14346,7 +14381,7 @@
         <v>4</v>
       </c>
       <c r="J264" s="10">
-        <v>27768.2399999999</v>
+        <v>27768.240000000002</v>
       </c>
       <c r="K264" s="10">
         <v>0.5</v>
@@ -14369,7 +14404,7 @@
         <v>12460.44</v>
       </c>
       <c r="F265" s="10">
-        <v>66.009999999999906</v>
+        <v>66.010000000000005</v>
       </c>
       <c r="G265" s="10">
         <v>29</v>
@@ -14398,19 +14433,19 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="E266" s="10">
-        <v>1594.66</v>
+        <v>2036.08</v>
       </c>
       <c r="F266" s="10">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="G266" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H266" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I266" s="10">
         <v>0</v>
@@ -14439,7 +14474,7 @@
         <v>4824.59</v>
       </c>
       <c r="F267" s="10">
-        <v>60.559999999999903</v>
+        <v>60.56</v>
       </c>
       <c r="G267" s="10">
         <v>23</v>
@@ -14474,7 +14509,7 @@
         <v>6238.21</v>
       </c>
       <c r="F268" s="10">
-        <v>98.369999999999905</v>
+        <v>98.37</v>
       </c>
       <c r="G268" s="10">
         <v>19</v>
@@ -14509,7 +14544,7 @@
         <v>5890.79</v>
       </c>
       <c r="F269" s="10">
-        <v>68.039999999999907</v>
+        <v>68.040000000000006</v>
       </c>
       <c r="G269" s="10">
         <v>15</v>
@@ -14921,7 +14956,7 @@
         <v>7</v>
       </c>
       <c r="J283" s="10">
-        <v>54199.229999999901</v>
+        <v>54199.23</v>
       </c>
       <c r="K283" s="10">
         <v>10.08</v>
@@ -15049,7 +15084,7 @@
         <v>7178.57</v>
       </c>
       <c r="F287" s="10">
-        <v>37.519999999999897</v>
+        <v>37.520000000000003</v>
       </c>
       <c r="G287" s="10">
         <v>24</v>
@@ -15402,10 +15437,10 @@
         <v>70.47</v>
       </c>
       <c r="G297" s="10">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H297" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I297" s="10">
         <v>8</v>
@@ -15437,19 +15472,19 @@
         <v>104.01</v>
       </c>
       <c r="G298" s="10">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H298" s="10">
         <v>30</v>
       </c>
       <c r="I298" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J298" s="10">
-        <v>61881.13</v>
+        <v>55483.13</v>
       </c>
       <c r="K298" s="10">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
@@ -15609,7 +15644,7 @@
         <v>28271.919999999998</v>
       </c>
       <c r="F303" s="10">
-        <v>103.979999999999</v>
+        <v>103.98</v>
       </c>
       <c r="G303" s="10">
         <v>41</v>
@@ -15673,16 +15708,16 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>334</v>
+        <v>417</v>
       </c>
       <c r="E305" s="10">
-        <v>3916.88</v>
+        <v>4950.0200000000004</v>
       </c>
       <c r="F305" s="10">
-        <v>14.44</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="G305" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H305" s="10">
         <v>3</v>
@@ -15777,7 +15812,7 @@
         <v>196.53</v>
       </c>
       <c r="G308" s="10">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H308" s="10">
         <v>35</v>
@@ -15821,7 +15856,7 @@
         <v>14</v>
       </c>
       <c r="J309" s="10">
-        <v>100687.459999999</v>
+        <v>100687.46</v>
       </c>
       <c r="K309" s="10">
         <v>2.1</v>
@@ -15891,10 +15926,10 @@
         <v>8</v>
       </c>
       <c r="J311" s="10">
-        <v>64137.120000000003</v>
+        <v>63762.12</v>
       </c>
       <c r="K311" s="10">
-        <v>1.1200000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
@@ -15920,7 +15955,7 @@
         <v>66</v>
       </c>
       <c r="H312" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I312" s="10">
         <v>9</v>
@@ -15943,16 +15978,16 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>671</v>
+        <v>896</v>
       </c>
       <c r="E313" s="10">
-        <v>4097.45</v>
+        <v>5150.6400000000003</v>
       </c>
       <c r="F313" s="10">
-        <v>11.85</v>
+        <v>15.85</v>
       </c>
       <c r="G313" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H313" s="10">
         <v>1</v>
@@ -16057,19 +16092,19 @@
         <v>119.16</v>
       </c>
       <c r="G316" s="10">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H316" s="10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I316" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J316" s="10">
-        <v>57233.21</v>
+        <v>64394.84</v>
       </c>
       <c r="K316" s="10">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
@@ -16089,7 +16124,7 @@
         <v>32402.04</v>
       </c>
       <c r="F317" s="10">
-        <v>118.16999999999901</v>
+        <v>118.17</v>
       </c>
       <c r="G317" s="10">
         <v>87</v>
@@ -16194,22 +16229,22 @@
         <v>30410.11</v>
       </c>
       <c r="F320" s="10">
-        <v>163.26999999999899</v>
+        <v>163.27000000000001</v>
       </c>
       <c r="G320" s="10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H320" s="10">
         <v>27</v>
       </c>
       <c r="I320" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J320" s="10">
-        <v>30257</v>
+        <v>22091</v>
       </c>
       <c r="K320" s="10">
-        <v>-0.01</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
@@ -16223,28 +16258,28 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>1143</v>
+        <v>1451</v>
       </c>
       <c r="E321" s="10">
-        <v>4917.6400000000003</v>
+        <v>5839.7</v>
       </c>
       <c r="F321" s="10">
-        <v>15.35</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="G321" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H321" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I321" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J321" s="10">
-        <v>0</v>
+        <v>5560</v>
       </c>
       <c r="K321" s="10">
-        <v>-1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16639,7 +16674,7 @@
         <v>20276.71</v>
       </c>
       <c r="F333" s="10">
-        <v>49.099999999999902</v>
+        <v>49.1</v>
       </c>
       <c r="G333" s="10">
         <v>35</v>
@@ -16686,7 +16721,7 @@
         <v>9</v>
       </c>
       <c r="J334" s="10">
-        <v>61616.659999999902</v>
+        <v>61616.66</v>
       </c>
       <c r="K334" s="10">
         <v>2</v>
@@ -16744,7 +16779,7 @@
         <v>26470.52</v>
       </c>
       <c r="F336" s="10">
-        <v>164.02999999999901</v>
+        <v>164.03</v>
       </c>
       <c r="G336" s="10">
         <v>66</v>
@@ -16843,13 +16878,13 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>274</v>
+        <v>361</v>
       </c>
       <c r="E339" s="10">
-        <v>3179.4</v>
+        <v>4397.24</v>
       </c>
       <c r="F339" s="10">
-        <v>12.99</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="G339" s="10">
         <v>5</v>
@@ -16884,7 +16919,7 @@
         <v>1458.13</v>
       </c>
       <c r="F340" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G340" s="10"/>
       <c r="H340" s="10"/>
@@ -17096,7 +17131,7 @@
         <v>1</v>
       </c>
       <c r="J346" s="10">
-        <v>8166.99999999999</v>
+        <v>8167</v>
       </c>
       <c r="K346" s="10">
         <v>0.13</v>
@@ -17214,7 +17249,7 @@
         <v>5077.71</v>
       </c>
       <c r="F350" s="10">
-        <v>43.269999999999897</v>
+        <v>43.27</v>
       </c>
       <c r="G350" s="10">
         <v>24</v>
@@ -17249,7 +17284,7 @@
         <v>5048.16</v>
       </c>
       <c r="F351" s="10">
-        <v>40.269999999999897</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="G351" s="10">
         <v>23</v>
@@ -17348,10 +17383,10 @@
         <v>18</v>
       </c>
       <c r="D354" s="10">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="E354" s="10">
-        <v>1019.98</v>
+        <v>1300.25</v>
       </c>
       <c r="F354" s="10">
         <v>5</v>
@@ -17424,7 +17459,7 @@
         <v>18545.96</v>
       </c>
       <c r="F356" s="10">
-        <v>74.679999999999893</v>
+        <v>74.680000000000007</v>
       </c>
       <c r="G356" s="10">
         <v>41</v>
@@ -17774,7 +17809,7 @@
         <v>19172.93</v>
       </c>
       <c r="F366" s="10">
-        <v>78.449999999999903</v>
+        <v>78.45</v>
       </c>
       <c r="G366" s="10">
         <v>41</v>
@@ -17853,13 +17888,13 @@
         <v>11</v>
       </c>
       <c r="I368" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J368" s="10">
-        <v>37756.74</v>
+        <v>38485.74</v>
       </c>
       <c r="K368" s="10">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -17879,10 +17914,10 @@
         <v>20205.009999999998</v>
       </c>
       <c r="F369" s="10">
-        <v>81.229999999999905</v>
+        <v>81.23</v>
       </c>
       <c r="G369" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H369" s="10">
         <v>15</v>
@@ -17943,13 +17978,13 @@
         <v>18</v>
       </c>
       <c r="D371" s="10">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="E371" s="10">
-        <v>2742.85</v>
+        <v>3329.43</v>
       </c>
       <c r="F371" s="10">
-        <v>8.99</v>
+        <v>10.99</v>
       </c>
       <c r="G371" s="10">
         <v>1</v>
@@ -18486,7 +18521,7 @@
         <v>6</v>
       </c>
       <c r="J386" s="10">
-        <v>50193.159999999902</v>
+        <v>50193.16</v>
       </c>
       <c r="K386" s="10">
         <v>1.22</v>
@@ -18783,28 +18818,28 @@
         <v>18</v>
       </c>
       <c r="D395" s="10">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="E395" s="10">
-        <v>2016.05</v>
+        <v>2861.78</v>
       </c>
       <c r="F395" s="10">
-        <v>7.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G395" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H395" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I395" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J395" s="10">
-        <v>7853.68</v>
+        <v>16511.68</v>
       </c>
       <c r="K395" s="10">
-        <v>2.9</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
@@ -19024,7 +19059,7 @@
         <v>6472.59</v>
       </c>
       <c r="F402" s="10">
-        <v>17.759999999999899</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="G402" s="10">
         <v>9</v>
@@ -19291,7 +19326,7 @@
         <v>6</v>
       </c>
       <c r="J411" s="10">
-        <v>44540.869999999901</v>
+        <v>44540.87</v>
       </c>
       <c r="K411" s="10">
         <v>2.21</v>
@@ -19524,7 +19559,7 @@
         <v>9969.59</v>
       </c>
       <c r="F418" s="10">
-        <v>39.519999999999897</v>
+        <v>39.520000000000003</v>
       </c>
       <c r="G418" s="10">
         <v>26</v>
@@ -19594,7 +19629,7 @@
         <v>7066.25</v>
       </c>
       <c r="F420" s="10">
-        <v>33.489999999999903</v>
+        <v>33.49</v>
       </c>
       <c r="G420" s="10">
         <v>13</v>
@@ -19798,16 +19833,16 @@
         <v>18</v>
       </c>
       <c r="D426" s="10">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E426" s="10">
-        <v>1416.29</v>
+        <v>1870.58</v>
       </c>
       <c r="F426" s="10">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
       <c r="G426" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H426" s="10">
         <v>1</v>
@@ -20064,7 +20099,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L165"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24581,13 +24616,13 @@
         <v>26</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -24619,10 +24654,10 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G123">
         <v>3</v>
@@ -24683,7 +24718,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B125" s="18">
         <v>2026</v>
@@ -24692,16 +24727,16 @@
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -24730,19 +24765,19 @@
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G126">
         <v>1</v>
       </c>
       <c r="H126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -24768,7 +24803,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -24780,7 +24815,7 @@
         <v>1</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -24806,16 +24841,16 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="E128">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -24835,7 +24870,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B129" s="18">
         <v>2026</v>
@@ -24844,19 +24879,19 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -24873,7 +24908,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B130" s="18">
         <v>2026</v>
@@ -24882,7 +24917,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -24891,10 +24926,10 @@
         <v>1</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -24911,7 +24946,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B131" s="18">
         <v>2026</v>
@@ -24920,19 +24955,19 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -24949,7 +24984,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B132" s="18">
         <v>2026</v>
@@ -24964,13 +24999,13 @@
         <v>1</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132">
         <v>0</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -24987,7 +25022,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B133" s="18">
         <v>2026</v>
@@ -24996,16 +25031,16 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -25025,7 +25060,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B134" s="18">
         <v>2026</v>
@@ -25034,13 +25069,13 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -25063,7 +25098,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B135" s="18">
         <v>2026</v>
@@ -25075,13 +25110,13 @@
         <v>13</v>
       </c>
       <c r="E135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -25101,7 +25136,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B136" s="18">
         <v>2026</v>
@@ -25110,7 +25145,7 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -25119,10 +25154,10 @@
         <v>3</v>
       </c>
       <c r="G136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -25139,7 +25174,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B137" s="18">
         <v>2026</v>
@@ -25148,7 +25183,7 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E137">
         <v>2</v>
@@ -25157,7 +25192,7 @@
         <v>2</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -25186,31 +25221,31 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="F138">
+        <v>3</v>
+      </c>
+      <c r="G138">
         <v>2</v>
       </c>
-      <c r="F138">
-        <v>2</v>
-      </c>
-      <c r="G138">
-        <v>1</v>
-      </c>
       <c r="H138">
         <v>1</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -25224,19 +25259,19 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -25253,7 +25288,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B140" s="18">
         <v>2026</v>
@@ -25262,19 +25297,19 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G140">
         <v>1</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -25291,7 +25326,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B141" s="18">
         <v>2026</v>
@@ -25300,19 +25335,19 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -25329,7 +25364,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B142" s="18">
         <v>2026</v>
@@ -25338,13 +25373,13 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -25367,7 +25402,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B143" s="18">
         <v>2026</v>
@@ -25376,19 +25411,19 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E143">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F143">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -25405,7 +25440,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B144" s="18">
         <v>2026</v>
@@ -25414,13 +25449,13 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -25443,7 +25478,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B145" s="18">
         <v>2026</v>
@@ -25452,7 +25487,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -25490,19 +25525,19 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F146">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G146">
         <v>0</v>
       </c>
       <c r="H146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -25528,19 +25563,19 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147">
         <v>0</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -25557,7 +25592,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B148" s="18">
         <v>2026</v>
@@ -25566,19 +25601,19 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G148">
         <v>0</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -25595,7 +25630,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B149" s="18">
         <v>2026</v>
@@ -25604,19 +25639,19 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E149">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F149">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -25633,7 +25668,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B150" s="18">
         <v>2026</v>
@@ -25642,13 +25677,13 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -25671,7 +25706,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B151" s="18">
         <v>2026</v>
@@ -25680,7 +25715,7 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -25689,10 +25724,10 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -25709,7 +25744,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B152" s="18">
         <v>2026</v>
@@ -25724,7 +25759,7 @@
         <v>3</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -25747,7 +25782,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B153" s="18">
         <v>2026</v>
@@ -25756,16 +25791,16 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -25785,7 +25820,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B154" s="18">
         <v>2026</v>
@@ -25794,19 +25829,19 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E154">
+        <v>3</v>
+      </c>
+      <c r="F154">
         <v>2</v>
       </c>
-      <c r="F154">
-        <v>1</v>
-      </c>
       <c r="G154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -25823,7 +25858,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B155" s="18">
         <v>2026</v>
@@ -25832,7 +25867,7 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -25870,16 +25905,16 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -25899,7 +25934,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B157" s="18">
         <v>2026</v>
@@ -25908,16 +25943,16 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -25937,7 +25972,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B158" s="18">
         <v>2026</v>
@@ -25946,10 +25981,10 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -25958,7 +25993,7 @@
         <v>1</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -25975,7 +26010,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B159" s="18">
         <v>2026</v>
@@ -25984,16 +26019,16 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -26013,7 +26048,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B160" s="18">
         <v>2026</v>
@@ -26022,7 +26057,7 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -26051,7 +26086,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B161" s="18">
         <v>2026</v>
@@ -26060,16 +26095,16 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -26089,7 +26124,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B162" s="18">
         <v>2026</v>
@@ -26098,36 +26133,36 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162">
         <v>1</v>
       </c>
       <c r="J162">
-        <v>7853.68</v>
+        <v>5560</v>
       </c>
       <c r="K162">
         <v>1</v>
       </c>
       <c r="L162">
-        <v>7853.68</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B163" s="18">
         <v>2026</v>
@@ -26136,7 +26171,7 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -26148,7 +26183,7 @@
         <v>1</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -26165,7 +26200,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B164" s="18">
         <v>2026</v>
@@ -26174,13 +26209,13 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -26203,7 +26238,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B165" s="18">
         <v>2026</v>
@@ -26212,7 +26247,7 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -26236,6 +26271,196 @@
         <v>0</v>
       </c>
       <c r="L165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>131</v>
+      </c>
+      <c r="B166" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C166" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" t="s">
+        <v>60</v>
+      </c>
+      <c r="E166">
+        <v>7</v>
+      </c>
+      <c r="F166">
+        <v>7</v>
+      </c>
+      <c r="G166">
+        <v>4</v>
+      </c>
+      <c r="H166">
+        <v>2</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>16511.68</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>16511.68</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>132</v>
+      </c>
+      <c r="B167" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C167" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D167" t="s">
+        <v>137</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>132</v>
+      </c>
+      <c r="B168" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C168" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" t="s">
+        <v>52</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>132</v>
+      </c>
+      <c r="B169" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C169" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" t="s">
+        <v>55</v>
+      </c>
+      <c r="E169">
+        <v>2</v>
+      </c>
+      <c r="F169">
+        <v>2</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>132</v>
+      </c>
+      <c r="B170" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C170" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D170" t="s">
+        <v>65</v>
+      </c>
+      <c r="E170">
+        <v>4</v>
+      </c>
+      <c r="F170">
+        <v>4</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41511329-2019-4BFC-9CDC-4283B86DF55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD31E75-0C3E-4BF4-96D7-FAFCA433C9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="1020" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="143">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>Competitors â€“ USA</t>
+  </si>
+  <si>
+    <t>Pasadena Single Form CPA Decrease - Pasadena 2</t>
+  </si>
+  <si>
+    <t>San Diego Single Form CPA Decrease San Diego 2</t>
   </si>
 </sst>
 </file>
@@ -946,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.44140625" customWidth="1"/>
@@ -1091,64 +1097,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>253.89</v>
+        <v>324.88</v>
       </c>
       <c r="C6" s="5">
-        <v>133.80000000000001</v>
+        <v>181.79</v>
       </c>
       <c r="D6" s="5">
-        <v>120.09</v>
+        <v>143.09</v>
       </c>
       <c r="E6" s="5">
-        <v>63757.31</v>
+        <v>76566.75</v>
       </c>
       <c r="F6" s="5">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5">
+        <v>11</v>
+      </c>
+      <c r="H6" s="5">
+        <v>134</v>
+      </c>
+      <c r="I6" s="5">
+        <v>52</v>
+      </c>
+      <c r="J6" s="5">
         <v>7</v>
       </c>
-      <c r="H6" s="5">
-        <v>115</v>
-      </c>
-      <c r="I6" s="5">
-        <v>39</v>
-      </c>
-      <c r="J6" s="5">
-        <v>4</v>
-      </c>
       <c r="K6" s="5">
-        <v>522.60090163934399</v>
+        <v>528.04655172413698</v>
       </c>
       <c r="L6" s="5">
-        <v>1634.8028205128201</v>
+        <v>1472.4375</v>
       </c>
       <c r="M6" s="5">
-        <v>-62.050343717449799</v>
+        <v>-46.022679557379597</v>
       </c>
       <c r="N6" s="6">
-        <v>324.14</v>
+        <v>391.65</v>
       </c>
       <c r="O6" s="6">
-        <v>35412.97</v>
+        <v>43963.48</v>
       </c>
       <c r="P6" s="6">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="Q6" s="6">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="R6" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S6" s="6">
-        <v>183.48689119170899</v>
+        <v>179.442775510204</v>
       </c>
       <c r="T6" s="6">
-        <v>983.69361111111095</v>
+        <v>862.029019607843</v>
       </c>
       <c r="U6" s="6">
-        <v>-19.439120751521202</v>
+        <v>-16.261951965585901</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1163,7 +1169,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1175,7 +1181,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1183,64 +1189,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>43.51</v>
+        <v>65.010000000000005</v>
       </c>
       <c r="C7" s="5">
-        <v>20.75</v>
+        <v>34.75</v>
       </c>
       <c r="D7" s="5">
-        <v>22.76</v>
+        <v>30.26</v>
       </c>
       <c r="E7" s="5">
-        <v>1785.97</v>
+        <v>2203.6999999999998</v>
       </c>
       <c r="F7" s="5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I7" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7" s="5">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>74.415416666666601</v>
+        <v>71.087096774193498</v>
       </c>
       <c r="L7" s="5">
-        <v>297.66166666666601</v>
+        <v>244.85555555555499</v>
       </c>
       <c r="M7" s="5">
-        <v>18.926969657944898</v>
+        <v>-3.6166447338566798</v>
       </c>
       <c r="N7" s="6">
-        <v>57.54</v>
+        <v>70.979999999999905</v>
       </c>
       <c r="O7" s="6">
-        <v>3345.9</v>
+        <v>4263.82</v>
       </c>
       <c r="P7" s="6">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="Q7" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R7" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" s="6">
-        <v>46.470833333333303</v>
+        <v>47.375777777777699</v>
       </c>
       <c r="T7" s="6">
-        <v>238.99285714285699</v>
+        <v>224.41157894736801</v>
       </c>
       <c r="U7" s="6">
-        <v>333.156998117098</v>
+        <v>255.12756167005099</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1255,7 +1261,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1267,7 +1273,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,16 +1281,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5">
         <v>2</v>
       </c>
       <c r="E8" s="5">
-        <v>1551.92</v>
+        <v>1923.82</v>
       </c>
       <c r="F8" s="5">
         <v>2</v>
@@ -1302,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>775.96</v>
+        <v>961.91</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1312,22 +1318,22 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>508.95</v>
+        <v>622.16</v>
       </c>
       <c r="P8" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="6">
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>254.47499999999999</v>
+        <v>207.386666666666</v>
       </c>
       <c r="T8" s="6">
-        <v>508.95</v>
+        <v>311.08</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1357,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1365,37 +1371,37 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5">
+        <v>11</v>
+      </c>
+      <c r="D9" s="5">
         <v>9</v>
       </c>
-      <c r="D9" s="5">
-        <v>7</v>
-      </c>
       <c r="E9" s="5">
-        <v>6637.43</v>
+        <v>7965.62</v>
       </c>
       <c r="F9" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I9" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>829.67875000000004</v>
+        <v>796.56200000000001</v>
       </c>
       <c r="L9" s="5">
-        <v>2212.4766666666601</v>
+        <v>1991.405</v>
       </c>
       <c r="M9" s="5">
         <v>-100</v>
@@ -1404,10 +1410,10 @@
         <v>6.84</v>
       </c>
       <c r="O9" s="6">
-        <v>1414.13</v>
+        <v>1804.27</v>
       </c>
       <c r="P9" s="6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q9" s="6">
         <v>1</v>
@@ -1416,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>141.41300000000001</v>
+        <v>128.87642857142799</v>
       </c>
       <c r="T9" s="6">
-        <v>1414.13</v>
+        <v>1804.27</v>
       </c>
       <c r="U9" s="6">
-        <v>26.013874254842101</v>
+        <v>-1.23429420208726</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1449,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1493,7 +1499,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1513,10 +1519,10 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>28.8</v>
+        <v>40.79</v>
       </c>
       <c r="O11" s="6">
-        <v>1627.18</v>
+        <v>2037.08</v>
       </c>
       <c r="P11" s="6">
         <v>5</v>
@@ -1528,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>325.43599999999998</v>
+        <v>407.416</v>
       </c>
       <c r="T11" s="6">
-        <v>813.59</v>
+        <v>1018.54</v>
       </c>
       <c r="U11" s="6">
-        <v>363.50127213952902</v>
+        <v>270.23582775345102</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1555,7 +1561,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1572,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="5">
-        <v>1298.3800000000001</v>
+        <v>1438.92</v>
       </c>
       <c r="F12" s="5">
         <v>4</v>
@@ -1590,19 +1596,19 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>324.59500000000003</v>
+        <v>359.73</v>
       </c>
       <c r="L12" s="5">
-        <v>1298.3800000000001</v>
+        <v>1438.92</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
       </c>
       <c r="N12" s="6">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="O12" s="6">
-        <v>251.99</v>
+        <v>434.74</v>
       </c>
       <c r="P12" s="6">
         <v>3</v>
@@ -1614,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>83.996666666666599</v>
+        <v>144.91333333333299</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6">
@@ -1645,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1689,7 +1695,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,10 +1715,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>4.05</v>
+        <v>6.05</v>
       </c>
       <c r="O14" s="6">
-        <v>396.63</v>
+        <v>546.91</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1739,7 +1745,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1762,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>117.44</v>
+        <v>137.29</v>
       </c>
       <c r="P15" s="6">
         <v>1</v>
@@ -1774,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>117.44</v>
+        <v>137.29</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1803,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1811,25 +1817,25 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
       </c>
       <c r="D16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5">
-        <v>109.62</v>
+        <v>141.54</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="5">
         <v>1</v>
@@ -1838,22 +1844,22 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>109.62</v>
+        <v>70.77</v>
       </c>
       <c r="L16" s="5">
-        <v>109.62</v>
+        <v>141.54</v>
       </c>
       <c r="M16" s="5">
         <v>-100</v>
       </c>
       <c r="N16" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="6">
-        <v>2494.98</v>
+        <v>3020.86</v>
       </c>
       <c r="P16" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="6">
         <v>2</v>
@@ -1862,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>166.33199999999999</v>
+        <v>188.80375000000001</v>
       </c>
       <c r="T16" s="6">
-        <v>1247.49</v>
+        <v>1510.43</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1895,7 +1901,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1915,13 +1921,13 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O17" s="6">
-        <v>1732.13</v>
+        <v>2131.1</v>
       </c>
       <c r="P17" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -1930,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>577.37666666666598</v>
+        <v>355.183333333333</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6">
@@ -1955,7 +1961,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1978,7 +1984,7 @@
         <v>0.98</v>
       </c>
       <c r="O18" s="6">
-        <v>286.91000000000003</v>
+        <v>324.27</v>
       </c>
       <c r="P18" s="6">
         <v>2</v>
@@ -1990,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>143.45500000000001</v>
+        <v>162.13499999999999</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6">
@@ -2019,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2042,7 +2048,7 @@
         <v>3</v>
       </c>
       <c r="O19" s="6">
-        <v>310.70999999999998</v>
+        <v>429.91</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2069,7 +2075,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2089,10 +2095,10 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="6">
-        <v>628.22</v>
+        <v>849.59</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2119,7 +2125,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2127,16 +2133,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>19.989999999999998</v>
+        <v>25.99</v>
       </c>
       <c r="C21" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D21" s="5">
-        <v>8.99</v>
+        <v>10.99</v>
       </c>
       <c r="E21" s="5">
-        <v>3952.72</v>
+        <v>4783.37</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2165,7 +2171,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2211,7 +2217,7 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2223,16 +2229,16 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" s="5">
         <v>0</v>
       </c>
       <c r="H23" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I23" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J23" s="5">
         <v>0</v>
@@ -2261,7 +2267,7 @@
         <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2269,16 +2275,16 @@
         <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>25.96</v>
+        <v>32.96</v>
       </c>
       <c r="C24" s="5">
-        <v>23.96</v>
+        <v>30.96</v>
       </c>
       <c r="D24" s="5">
         <v>2</v>
       </c>
       <c r="E24" s="5">
-        <v>6562.88</v>
+        <v>7908.26</v>
       </c>
       <c r="F24" s="5">
         <v>2</v>
@@ -2293,16 +2299,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>3281.44</v>
+        <v>3954.13</v>
       </c>
       <c r="L24" s="5">
-        <v>6562.88</v>
+        <v>7908.26</v>
       </c>
       <c r="M24" s="5">
-        <v>-100</v>
+        <v>-2.7093191169739002</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2327,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2344,7 +2350,7 @@
         <v>5.67</v>
       </c>
       <c r="E25" s="5">
-        <v>1041.27</v>
+        <v>1338.54</v>
       </c>
       <c r="F25" s="5">
         <v>4</v>
@@ -2362,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>260.3175</v>
+        <v>334.63499999999999</v>
       </c>
       <c r="L25" s="5">
-        <v>1041.27</v>
+        <v>1338.54</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O25" s="6">
-        <v>463.09</v>
+        <v>632.55999999999995</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -2407,7 +2413,7 @@
         <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2415,16 +2421,16 @@
         <v>42</v>
       </c>
       <c r="B26" s="5">
-        <v>2.96</v>
+        <v>3.46</v>
       </c>
       <c r="C26" s="5">
         <v>0</v>
       </c>
       <c r="D26" s="5">
-        <v>2.96</v>
+        <v>3.46</v>
       </c>
       <c r="E26" s="5">
-        <v>1064.21</v>
+        <v>1276.8599999999999</v>
       </c>
       <c r="F26" s="5">
         <v>3</v>
@@ -2442,22 +2448,22 @@
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>354.736666666666</v>
+        <v>425.62</v>
       </c>
       <c r="L26" s="5">
-        <v>1064.21</v>
+        <v>1276.8599999999999</v>
       </c>
       <c r="M26" s="5">
         <v>-100</v>
       </c>
       <c r="N26" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="6">
-        <v>158.08000000000001</v>
+        <v>232.26</v>
       </c>
       <c r="P26" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -2466,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>79.040000000000006</v>
+        <v>77.42</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
@@ -2497,7 +2503,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2505,16 +2511,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="C27" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" s="5">
         <v>1.5</v>
       </c>
       <c r="E27" s="5">
-        <v>2029.93</v>
+        <v>2442.3000000000002</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -2528,10 +2534,10 @@
         <v>11.33</v>
       </c>
       <c r="O27" s="6">
-        <v>1926.14</v>
+        <v>2279.4</v>
       </c>
       <c r="P27" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q27" s="6">
         <v>4</v>
@@ -2540,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="S27" s="6">
-        <v>321.02333333333303</v>
+        <v>325.62857142857098</v>
       </c>
       <c r="T27" s="6">
-        <v>481.53500000000003</v>
+        <v>569.85</v>
       </c>
       <c r="U27" s="6">
-        <v>144.634346413033</v>
+        <v>106.721066947442</v>
       </c>
       <c r="V27" s="7">
         <v>66.569999999999993</v>
@@ -2573,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="AD27" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2596,7 +2602,7 @@
         <v>9</v>
       </c>
       <c r="O28" s="6">
-        <v>587.62</v>
+        <v>714.06</v>
       </c>
       <c r="P28" s="6">
         <v>6</v>
@@ -2608,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>97.936666666666596</v>
+        <v>119.009999999999</v>
       </c>
       <c r="T28" s="6">
-        <v>587.62</v>
+        <v>714.06</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
@@ -2635,7 +2641,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2643,16 +2649,16 @@
         <v>45</v>
       </c>
       <c r="B29" s="5">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="C29" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5">
         <v>5.99</v>
       </c>
       <c r="E29" s="5">
-        <v>2036.08</v>
+        <v>2480.56</v>
       </c>
       <c r="F29" s="5">
         <v>8</v>
@@ -2670,37 +2676,37 @@
         <v>0</v>
       </c>
       <c r="K29" s="5">
-        <v>254.51</v>
+        <v>310.07</v>
       </c>
       <c r="L29" s="5">
-        <v>2036.08</v>
+        <v>2480.56</v>
       </c>
       <c r="M29" s="5">
         <v>-100</v>
       </c>
       <c r="N29" s="6">
-        <v>8.58</v>
+        <v>9.58</v>
       </c>
       <c r="O29" s="6">
-        <v>977.45</v>
+        <v>1124.04</v>
       </c>
       <c r="P29" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q29" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="6">
-        <v>162.90833333333299</v>
+        <v>160.57714285714201</v>
       </c>
       <c r="T29" s="6">
-        <v>488.72500000000002</v>
+        <v>281.01</v>
       </c>
       <c r="U29" s="6">
-        <v>-100</v>
+        <v>579.349489342016</v>
       </c>
       <c r="V29" s="7">
         <v>55.58</v>
@@ -2715,7 +2721,7 @@
         <v>13</v>
       </c>
       <c r="Z29" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="8">
         <v>13000</v>
@@ -2727,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2747,13 +2753,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>17.52</v>
+        <v>18.52</v>
       </c>
       <c r="O30" s="6">
-        <v>1212.04</v>
+        <v>1391.3</v>
       </c>
       <c r="P30" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -2762,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>202.00666666666601</v>
+        <v>198.75714285714199</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
@@ -2787,7 +2793,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2807,10 +2813,10 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="6">
-        <v>17.02</v>
+        <v>21.02</v>
       </c>
       <c r="O31" s="6">
-        <v>1358.98</v>
+        <v>1619.31</v>
       </c>
       <c r="P31" s="6">
         <v>3</v>
@@ -2822,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>452.993333333333</v>
+        <v>539.77</v>
       </c>
       <c r="T31" s="6"/>
       <c r="U31" s="6">
@@ -2847,7 +2853,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2855,22 +2861,22 @@
         <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>17.939999999999898</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="C32" s="5">
-        <v>10.94</v>
+        <v>11.94</v>
       </c>
       <c r="D32" s="5">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E32" s="5">
-        <v>4950.0200000000004</v>
+        <v>5984.59</v>
       </c>
       <c r="F32" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="5">
         <v>9</v>
@@ -2882,34 +2888,34 @@
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <v>550.00222222222203</v>
+        <v>598.45899999999995</v>
       </c>
       <c r="L32" s="5">
-        <v>1650.0066666666601</v>
+        <v>1994.86333333333</v>
       </c>
       <c r="M32" s="5">
         <v>-100</v>
       </c>
       <c r="N32" s="6">
-        <v>6.3</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="O32" s="6">
-        <v>1604.36</v>
+        <v>2244.6799999999998</v>
       </c>
       <c r="P32" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q32" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" s="6">
         <v>0</v>
       </c>
       <c r="S32" s="6">
-        <v>229.194285714285</v>
+        <v>224.46799999999999</v>
       </c>
       <c r="T32" s="6">
-        <v>1604.36</v>
+        <v>1122.3399999999999</v>
       </c>
       <c r="U32" s="6">
         <v>-100</v>
@@ -2939,7 +2945,7 @@
         <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2947,40 +2953,40 @@
         <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>15.85</v>
+        <v>20.68</v>
       </c>
       <c r="C33" s="5">
-        <v>4.63</v>
+        <v>5.96</v>
       </c>
       <c r="D33" s="5">
-        <v>11.22</v>
+        <v>14.72</v>
       </c>
       <c r="E33" s="5">
-        <v>5150.6400000000003</v>
+        <v>6077.08</v>
       </c>
       <c r="F33" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
       </c>
       <c r="H33" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I33" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="5">
-        <v>515.06399999999996</v>
+        <v>506.42333333333301</v>
       </c>
       <c r="L33" s="5">
-        <v>5150.6400000000003</v>
+        <v>1519.27</v>
       </c>
       <c r="M33" s="5">
-        <v>-100</v>
+        <v>39.178684499792602</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3005,7 +3011,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3013,40 +3019,40 @@
         <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>19.850000000000001</v>
+        <v>22.85</v>
       </c>
       <c r="C34" s="5">
-        <v>8.85</v>
+        <v>9.85</v>
       </c>
       <c r="D34" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E34" s="5">
-        <v>5839.7</v>
+        <v>6887.76</v>
       </c>
       <c r="F34" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G34" s="5">
         <v>0</v>
       </c>
       <c r="H34" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I34" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="5">
         <v>1</v>
       </c>
       <c r="K34" s="5">
-        <v>583.97</v>
+        <v>573.98</v>
       </c>
       <c r="L34" s="5">
-        <v>1459.925</v>
+        <v>1377.5519999999999</v>
       </c>
       <c r="M34" s="5">
-        <v>-4.7896296042604796</v>
+        <v>-19.277094439992101</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3071,7 +3077,7 @@
         <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3079,25 +3085,25 @@
         <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>18.489999999999998</v>
+        <v>19.82</v>
       </c>
       <c r="C35" s="5">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
       <c r="D35" s="5">
-        <v>4.5</v>
+        <v>3.83</v>
       </c>
       <c r="E35" s="5">
-        <v>4397.24</v>
+        <v>5320.85</v>
       </c>
       <c r="F35" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="5">
         <v>2</v>
@@ -3106,34 +3112,34 @@
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>732.87333333333299</v>
+        <v>665.10625000000005</v>
       </c>
       <c r="L35" s="5">
-        <v>2198.62</v>
+        <v>2660.4250000000002</v>
       </c>
       <c r="M35" s="5">
         <v>-100</v>
       </c>
       <c r="N35" s="6">
-        <v>8</v>
+        <v>12.05</v>
       </c>
       <c r="O35" s="6">
-        <v>4085.11</v>
+        <v>4966.0200000000004</v>
       </c>
       <c r="P35" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35" s="6">
         <v>0</v>
       </c>
       <c r="S35" s="6">
-        <v>314.23923076923001</v>
+        <v>292.11882352941097</v>
       </c>
       <c r="T35" s="6">
-        <v>1021.2775</v>
+        <v>993.20399999999995</v>
       </c>
       <c r="U35" s="6">
         <v>-100</v>
@@ -3163,17 +3169,25 @@
         <v>14</v>
       </c>
       <c r="AD35" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="B36" s="5">
+        <v>3</v>
+      </c>
+      <c r="C36" s="5">
+        <v>3</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <v>304.11</v>
+      </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3182,90 +3196,50 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="6">
-        <v>35.81</v>
-      </c>
-      <c r="O36" s="6">
-        <v>1136.49</v>
-      </c>
-      <c r="P36" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="6">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6">
-        <v>227.298</v>
-      </c>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
       <c r="T36" s="6"/>
-      <c r="U36" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V36" s="7">
-        <v>250.18</v>
-      </c>
-      <c r="W36" s="7">
-        <v>7865.5</v>
-      </c>
-      <c r="X36" s="7">
-        <v>18</v>
-      </c>
-      <c r="Y36" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="7">
-        <v>0</v>
-      </c>
+      <c r="U36" s="6"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="B37" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="5">
         <v>2</v>
       </c>
       <c r="D37" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5">
-        <v>1300.25</v>
-      </c>
-      <c r="F37" s="5">
-        <v>2</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5">
-        <v>2</v>
-      </c>
-      <c r="I37" s="5">
-        <v>1</v>
-      </c>
-      <c r="J37" s="5">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5">
-        <v>650.125</v>
-      </c>
-      <c r="L37" s="5">
-        <v>1300.25</v>
-      </c>
-      <c r="M37" s="5">
-        <v>-100</v>
-      </c>
+        <v>1458.13</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -3279,539 +3253,636 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
-      <c r="AA37" s="8">
-        <v>7500</v>
-      </c>
-      <c r="AB37" s="9">
-        <v>16</v>
-      </c>
-      <c r="AC37" s="9">
-        <v>7</v>
-      </c>
+      <c r="AA37" s="8"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
       <c r="AD37" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="5">
-        <v>10.99</v>
-      </c>
-      <c r="C38" s="5">
-        <v>8.49</v>
-      </c>
-      <c r="D38" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="E38" s="5">
-        <v>3329.43</v>
-      </c>
-      <c r="F38" s="5">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5">
-        <v>1</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <v>3329.43</v>
-      </c>
-      <c r="L38" s="5">
-        <v>3329.43</v>
-      </c>
-      <c r="M38" s="5">
-        <v>-100</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
       <c r="N38" s="6">
-        <v>1</v>
+        <v>39.82</v>
       </c>
       <c r="O38" s="6">
-        <v>1636.35</v>
+        <v>1408.19</v>
       </c>
       <c r="P38" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q38" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="6">
-        <v>409.08749999999998</v>
-      </c>
-      <c r="T38" s="6">
-        <v>1636.35</v>
-      </c>
+        <v>201.17</v>
+      </c>
+      <c r="T38" s="6"/>
       <c r="U38" s="6">
         <v>-100</v>
       </c>
       <c r="V38" s="7">
-        <v>42.5</v>
+        <v>250.18</v>
       </c>
       <c r="W38" s="7">
-        <v>12015.14</v>
+        <v>7865.5</v>
       </c>
       <c r="X38" s="7">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="Y38" s="7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="7">
         <v>0</v>
       </c>
-      <c r="AA38" s="8">
-        <v>17000</v>
-      </c>
-      <c r="AB38" s="9">
-        <v>27</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>16</v>
-      </c>
+      <c r="AA38" s="8"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
       <c r="AD38" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6">
-        <v>8</v>
-      </c>
-      <c r="O39" s="6">
-        <v>945.28</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B39" s="5">
+        <v>5</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1557.88</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <v>2</v>
+      </c>
+      <c r="I39" s="5">
+        <v>1</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>778.94</v>
+      </c>
+      <c r="L39" s="5">
+        <v>1557.88</v>
+      </c>
+      <c r="M39" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
-      <c r="V39" s="7">
-        <v>97.34</v>
-      </c>
-      <c r="W39" s="7">
-        <v>5964.35</v>
-      </c>
-      <c r="X39" s="7">
-        <v>9</v>
-      </c>
-      <c r="Y39" s="7">
-        <v>3</v>
-      </c>
-      <c r="Z39" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="8">
+        <v>7500</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>16</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>7</v>
+      </c>
       <c r="AD39" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B40" s="5">
-        <v>4.67</v>
+        <v>17.98</v>
       </c>
       <c r="C40" s="5">
-        <v>2.67</v>
+        <v>14.48</v>
       </c>
       <c r="D40" s="5">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E40" s="5">
-        <v>2919.05</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
+        <v>3953.27</v>
+      </c>
+      <c r="F40" s="5">
+        <v>2</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5">
+        <v>2</v>
+      </c>
+      <c r="I40" s="5">
+        <v>1</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <v>1976.635</v>
+      </c>
+      <c r="L40" s="5">
+        <v>3953.27</v>
+      </c>
+      <c r="M40" s="5">
+        <v>-100</v>
+      </c>
       <c r="N40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="6">
-        <v>129.74</v>
-      </c>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
+        <v>2123.86</v>
+      </c>
+      <c r="P40" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>4</v>
+      </c>
+      <c r="R40" s="6">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6">
+        <v>265.48250000000002</v>
+      </c>
+      <c r="T40" s="6">
+        <v>530.96500000000003</v>
+      </c>
+      <c r="U40" s="6">
+        <v>-100</v>
+      </c>
       <c r="V40" s="7">
-        <v>3.01</v>
+        <v>42.5</v>
       </c>
       <c r="W40" s="7">
-        <v>1758.25</v>
-      </c>
-      <c r="X40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7"/>
+        <v>12015.14</v>
+      </c>
+      <c r="X40" s="7">
+        <v>56</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>24</v>
+      </c>
+      <c r="Z40" s="7">
+        <v>0</v>
+      </c>
       <c r="AA40" s="8">
         <v>17000</v>
       </c>
-      <c r="AB40" s="9"/>
-      <c r="AC40" s="9"/>
+      <c r="AB40" s="9">
+        <v>27</v>
+      </c>
+      <c r="AC40" s="9">
+        <v>16</v>
+      </c>
       <c r="AD40" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="C41">
-        <v>4.2</v>
-      </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="E41">
-        <v>2861.78</v>
-      </c>
-      <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>9</v>
-      </c>
-      <c r="I41">
-        <v>4</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41">
-        <v>286.178</v>
-      </c>
-      <c r="L41">
-        <v>715.44500000000005</v>
-      </c>
-      <c r="M41">
-        <v>476.97237383726201</v>
+        <v>59</v>
       </c>
       <c r="N41">
-        <v>10.02</v>
+        <v>13</v>
       </c>
       <c r="O41">
-        <v>1254.9100000000001</v>
+        <v>1132.8399999999999</v>
       </c>
       <c r="P41">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <v>0</v>
       </c>
       <c r="S41">
-        <v>114.082727272727</v>
-      </c>
-      <c r="T41">
-        <v>1254.9100000000001</v>
+        <v>1132.8399999999999</v>
       </c>
       <c r="U41">
         <v>-100</v>
       </c>
       <c r="V41">
-        <v>52.03</v>
+        <v>97.34</v>
       </c>
       <c r="W41">
-        <v>10931.15</v>
+        <v>5964.35</v>
       </c>
       <c r="X41">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Z41">
         <v>0</v>
       </c>
-      <c r="AA41">
-        <v>24000</v>
-      </c>
-      <c r="AB41">
-        <v>29</v>
-      </c>
-      <c r="AC41">
-        <v>12</v>
-      </c>
       <c r="AD41" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
+      </c>
+      <c r="B42">
+        <v>5.67</v>
+      </c>
+      <c r="C42">
+        <v>3.67</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>3534.56</v>
       </c>
       <c r="N42">
-        <v>23.16</v>
+        <v>0.98</v>
       </c>
       <c r="O42">
-        <v>1238.47</v>
-      </c>
-      <c r="P42">
-        <v>5</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>247.69399999999999</v>
-      </c>
-      <c r="U42">
-        <v>-100</v>
+        <v>188.6</v>
       </c>
       <c r="V42">
-        <v>127.59</v>
+        <v>3.01</v>
       </c>
       <c r="W42">
-        <v>8783.7999999999993</v>
-      </c>
-      <c r="X42">
-        <v>27</v>
-      </c>
-      <c r="Y42">
-        <v>4</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
+        <v>1758.25</v>
+      </c>
+      <c r="AA42">
+        <v>17000</v>
       </c>
       <c r="AD42" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B43">
-        <v>7.99</v>
+        <v>12.87</v>
       </c>
       <c r="C43">
-        <v>3.99</v>
+        <v>4.87</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>1870.58</v>
+        <v>3495.82</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>467.64499999999998</v>
+        <v>268.90923076923002</v>
       </c>
       <c r="L43">
-        <v>1870.58</v>
+        <v>499.40285714285699</v>
       </c>
       <c r="M43">
-        <v>-100</v>
+        <v>400.38846393693001</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>11.02</v>
       </c>
       <c r="O43">
-        <v>577.48</v>
+        <v>1583.4</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>192.493333333333</v>
+        <v>131.94999999999999</v>
       </c>
       <c r="T43">
-        <v>577.48</v>
+        <v>791.7</v>
       </c>
       <c r="U43">
         <v>-100</v>
       </c>
       <c r="V43">
-        <v>23.02</v>
+        <v>52.03</v>
       </c>
       <c r="W43">
-        <v>4636.55</v>
+        <v>10931.15</v>
       </c>
       <c r="X43">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z43">
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="AB43">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AC43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AD43" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>66</v>
-      </c>
-      <c r="N44">
-        <v>13.19</v>
-      </c>
-      <c r="O44">
-        <v>672.34</v>
-      </c>
-      <c r="P44">
-        <v>3</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>224.113333333333</v>
-      </c>
-      <c r="T44">
-        <v>672.34</v>
-      </c>
-      <c r="U44">
-        <v>-100</v>
-      </c>
-      <c r="V44">
-        <v>56.01</v>
-      </c>
-      <c r="W44">
-        <v>4863.79</v>
-      </c>
-      <c r="X44">
-        <v>10</v>
-      </c>
-      <c r="Y44">
-        <v>4</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1104.46</v>
       </c>
       <c r="AD44" s="13">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="AB45">
-        <v>2</v>
-      </c>
-      <c r="AC45">
-        <v>1</v>
+        <v>142</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>205.16</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46">
+        <v>23.17</v>
+      </c>
+      <c r="O46">
+        <v>1533.08</v>
+      </c>
+      <c r="P46">
+        <v>6</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>255.51333333333301</v>
+      </c>
+      <c r="U46">
+        <v>-100</v>
+      </c>
+      <c r="V46">
+        <v>127.59</v>
+      </c>
+      <c r="W46">
+        <v>8783.7999999999993</v>
+      </c>
+      <c r="X46">
+        <v>27</v>
+      </c>
+      <c r="Y46">
+        <v>4</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47">
+        <v>9.66</v>
+      </c>
+      <c r="C47">
+        <v>4.99</v>
+      </c>
+      <c r="D47">
+        <v>4.67</v>
+      </c>
+      <c r="E47">
+        <v>2273.9699999999998</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>568.49249999999995</v>
+      </c>
+      <c r="L47">
+        <v>2273.9699999999998</v>
+      </c>
+      <c r="M47">
+        <v>-100</v>
+      </c>
+      <c r="N47">
+        <v>5.0299999999999896</v>
+      </c>
+      <c r="O47">
+        <v>969.49</v>
+      </c>
+      <c r="P47">
+        <v>7</v>
+      </c>
+      <c r="Q47">
+        <v>2</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>138.49857142857101</v>
+      </c>
+      <c r="T47">
+        <v>484.745</v>
+      </c>
+      <c r="U47">
+        <v>-100</v>
+      </c>
+      <c r="V47">
+        <v>23.02</v>
+      </c>
+      <c r="W47">
+        <v>4636.55</v>
+      </c>
+      <c r="X47">
+        <v>23</v>
+      </c>
+      <c r="Y47">
+        <v>9</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>11000</v>
+      </c>
+      <c r="AB47">
+        <v>14</v>
+      </c>
+      <c r="AC47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="N48">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="O48">
+        <v>884.52</v>
+      </c>
+      <c r="P48">
+        <v>4</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>221.13</v>
+      </c>
+      <c r="T48">
+        <v>884.52</v>
+      </c>
+      <c r="U48">
+        <v>-100</v>
+      </c>
+      <c r="V48">
+        <v>56.01</v>
+      </c>
+      <c r="W48">
+        <v>4863.79</v>
+      </c>
+      <c r="X48">
+        <v>10</v>
+      </c>
+      <c r="Y48">
+        <v>4</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>139</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>2</v>
-      </c>
-      <c r="AC46">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>2</v>
+      </c>
+      <c r="AC49">
         <v>1</v>
       </c>
     </row>
@@ -4699,16 +4770,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
@@ -4723,13 +4794,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>9.84</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="M21" s="10">
         <v>0</v>
       </c>
       <c r="N21" s="10">
-        <v>33.33</v>
+        <v>46.15</v>
       </c>
       <c r="O21" s="10">
         <v>0</v>
@@ -4773,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.82</v>
+        <v>0.69</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -4799,43 +4870,43 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
+        <v>14</v>
+      </c>
+      <c r="E23" s="10">
         <v>13</v>
       </c>
-      <c r="E23" s="10">
-        <v>12</v>
-      </c>
       <c r="F23" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="10">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="J23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="10">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="L23" s="10">
-        <v>10.66</v>
+        <v>9.66</v>
       </c>
       <c r="M23" s="10">
-        <v>0</v>
+        <v>18.62</v>
       </c>
       <c r="N23" s="10">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="O23" s="10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P23" s="10">
-        <v>0</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -4873,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>0.82</v>
+        <v>0.69</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4906,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
@@ -4921,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -4947,10 +5018,10 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="10">
         <v>3</v>
@@ -4971,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>4.92</v>
+        <v>5.52</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -4997,43 +5068,43 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E27" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" s="10">
         <v>4</v>
       </c>
       <c r="H27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="10">
-        <v>2124</v>
+        <v>10582</v>
       </c>
       <c r="J27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="10">
-        <v>2124</v>
+        <v>10582</v>
       </c>
       <c r="L27" s="10">
-        <v>10.66</v>
+        <v>10.34</v>
       </c>
       <c r="M27" s="10">
-        <v>8.7799999999999994</v>
+        <v>25.6</v>
       </c>
       <c r="N27" s="10">
-        <v>38.46</v>
+        <v>53.33</v>
       </c>
       <c r="O27" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P27" s="10">
-        <v>7.69</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5047,16 +5118,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>8</v>
+      </c>
+      <c r="E28" s="10">
         <v>7</v>
       </c>
-      <c r="E28" s="10">
-        <v>6</v>
-      </c>
       <c r="F28" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -5071,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>5.74</v>
+        <v>5.52</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -5097,10 +5168,10 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="10">
         <v>0</v>
@@ -5121,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>13.11</v>
+        <v>11.72</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -5145,16 +5216,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E30" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F30" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="10">
         <v>0</v>
@@ -5169,13 +5240,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>13.11</v>
+        <v>13.79</v>
       </c>
       <c r="M30" s="10">
         <v>0</v>
       </c>
       <c r="N30" s="10">
-        <v>31.25</v>
+        <v>30</v>
       </c>
       <c r="O30" s="10">
         <v>0</v>
@@ -5195,16 +5266,16 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E31" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F31" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
@@ -5219,13 +5290,13 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>8.1999999999999993</v>
+        <v>10.34</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
       </c>
       <c r="N31" s="10">
-        <v>30</v>
+        <v>26.67</v>
       </c>
       <c r="O31" s="10">
         <v>0</v>
@@ -5245,16 +5316,16 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E32" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F32" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -5269,19 +5340,19 @@
         <v>5560</v>
       </c>
       <c r="L32" s="10">
-        <v>4.0999999999999996</v>
+        <v>5.52</v>
       </c>
       <c r="M32" s="10">
-        <v>22.98</v>
+        <v>13.45</v>
       </c>
       <c r="N32" s="10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O32" s="10">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="P32" s="10">
-        <v>20</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5295,13 +5366,13 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -5319,15 +5390,17 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>0</v>
-      </c>
-      <c r="O33" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="O33" s="10">
+        <v>0</v>
+      </c>
       <c r="P33" s="10">
         <v>0</v>
       </c>
@@ -5343,43 +5416,43 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E34" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F34" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" s="10">
         <v>2</v>
       </c>
       <c r="H34" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="10">
-        <v>16511.68</v>
+        <v>17492.68</v>
       </c>
       <c r="J34" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="10">
-        <v>16511.68</v>
+        <v>17492.68</v>
       </c>
       <c r="L34" s="10">
-        <v>7.38</v>
+        <v>7.59</v>
       </c>
       <c r="M34" s="10">
-        <v>68.239999999999995</v>
+        <v>42.33</v>
       </c>
       <c r="N34" s="10">
-        <v>55.56</v>
+        <v>63.64</v>
       </c>
       <c r="O34" s="10">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="P34" s="10">
-        <v>22.22</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5392,43 +5465,43 @@
       <c r="C35" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="10">
         <v>8</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="10">
         <v>8</v>
       </c>
-      <c r="F35">
-        <v>2</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>6.56</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>25</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
+      <c r="F35" s="10">
+        <v>3</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <v>5.52</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>37.5</v>
+      </c>
+      <c r="O35" s="10">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5440,7 +5513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O433"/>
+  <dimension ref="A1:O435"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5792,7 +5865,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -5862,7 +5935,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -5897,7 +5970,7 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
@@ -6002,10 +6075,10 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H19" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I19" s="5">
         <v>52</v>
@@ -6043,13 +6116,13 @@
         <v>76</v>
       </c>
       <c r="I20" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" s="10">
-        <v>219615.52</v>
+        <v>227784.52</v>
       </c>
       <c r="K20" s="10">
-        <v>24.01</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -6063,19 +6136,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>686</v>
+        <v>836</v>
       </c>
       <c r="E21" s="10">
-        <v>1785.97</v>
+        <v>2203.6999999999998</v>
       </c>
       <c r="F21" s="10">
-        <v>43.51</v>
+        <v>65.010000000000005</v>
       </c>
       <c r="G21" s="10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H21" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
@@ -6084,7 +6157,7 @@
         <v>2124</v>
       </c>
       <c r="K21" s="10">
-        <v>0.19</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6291,7 +6364,7 @@
         <v>3</v>
       </c>
       <c r="J27" s="10">
-        <v>22604.560000000001</v>
+        <v>22604.559999999899</v>
       </c>
       <c r="K27" s="10">
         <v>3.62</v>
@@ -6419,7 +6492,7 @@
         <v>6171.75</v>
       </c>
       <c r="F31" s="10">
-        <v>37.020000000000003</v>
+        <v>37.019999999999897</v>
       </c>
       <c r="G31" s="10">
         <v>16</v>
@@ -6466,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>14306.78</v>
+        <v>14306.779999999901</v>
       </c>
       <c r="K32" s="10">
         <v>1.22</v>
@@ -6658,13 +6731,13 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="E38" s="10">
-        <v>1551.92</v>
+        <v>1923.82</v>
       </c>
       <c r="F38" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="10">
         <v>2</v>
@@ -6874,7 +6947,7 @@
         <v>22445.41</v>
       </c>
       <c r="F44" s="10">
-        <v>66.790000000000006</v>
+        <v>66.789999999999907</v>
       </c>
       <c r="G44" s="10">
         <v>91</v>
@@ -7049,7 +7122,7 @@
         <v>14924.23</v>
       </c>
       <c r="F49" s="10">
-        <v>57.02</v>
+        <v>57.019999999999897</v>
       </c>
       <c r="G49" s="10">
         <v>58</v>
@@ -7154,7 +7227,7 @@
         <v>27112.02</v>
       </c>
       <c r="F52" s="10">
-        <v>104.95</v>
+        <v>104.94999999999899</v>
       </c>
       <c r="G52" s="10">
         <v>64</v>
@@ -7236,7 +7309,7 @@
         <v>6</v>
       </c>
       <c r="J54" s="10">
-        <v>43551.29</v>
+        <v>43541.29</v>
       </c>
       <c r="K54" s="10">
         <v>0.08</v>
@@ -7253,19 +7326,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>565</v>
+        <v>667</v>
       </c>
       <c r="E55" s="10">
-        <v>6637.43</v>
+        <v>7965.62</v>
       </c>
       <c r="F55" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G55" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H55" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55" s="10">
         <v>0</v>
@@ -7666,7 +7739,7 @@
         <v>518</v>
       </c>
       <c r="E67" s="10">
-        <v>6279.52</v>
+        <v>6279.5199999999904</v>
       </c>
       <c r="F67" s="10">
         <v>16</v>
@@ -7891,7 +7964,7 @@
         <v>2</v>
       </c>
       <c r="J73" s="10">
-        <v>12248.28</v>
+        <v>12248.279999999901</v>
       </c>
       <c r="K73" s="10">
         <v>1.4</v>
@@ -8013,10 +8086,10 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E77" s="10">
-        <v>1298.3800000000001</v>
+        <v>1438.92</v>
       </c>
       <c r="F77" s="10">
         <v>4.33</v>
@@ -8768,13 +8841,13 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="E100" s="10">
-        <v>2919.05</v>
+        <v>3534.56</v>
       </c>
       <c r="F100" s="10">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
@@ -9300,7 +9373,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="10">
         <v>0</v>
@@ -9329,7 +9402,7 @@
         <v>32413.439999999999</v>
       </c>
       <c r="F117" s="10">
-        <v>188.33</v>
+        <v>188.32999999999899</v>
       </c>
       <c r="G117" s="10">
         <v>34</v>
@@ -9612,7 +9685,7 @@
         <v>50.47</v>
       </c>
       <c r="G125" s="10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H125" s="10">
         <v>19</v>
@@ -9682,10 +9755,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H127" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -9883,16 +9956,16 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E133" s="10">
-        <v>109.62</v>
+        <v>141.54</v>
       </c>
       <c r="F133" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" s="10">
         <v>1</v>
@@ -10461,7 +10534,7 @@
         <v>3</v>
       </c>
       <c r="J149" s="10">
-        <v>22749.74</v>
+        <v>22749.7399999999</v>
       </c>
       <c r="K149" s="10">
         <v>2.15</v>
@@ -10496,7 +10569,7 @@
         <v>5</v>
       </c>
       <c r="J150" s="10">
-        <v>32597.06</v>
+        <v>32597.059999999899</v>
       </c>
       <c r="K150" s="10">
         <v>3.14</v>
@@ -10554,7 +10627,7 @@
         <v>9261.49</v>
       </c>
       <c r="F152" s="10">
-        <v>32.35</v>
+        <v>32.349999999999902</v>
       </c>
       <c r="G152" s="10">
         <v>12</v>
@@ -10624,7 +10697,7 @@
         <v>8958.39</v>
       </c>
       <c r="F154" s="10">
-        <v>13.97</v>
+        <v>13.969999999999899</v>
       </c>
       <c r="G154" s="10">
         <v>7</v>
@@ -11228,7 +11301,7 @@
         <v>1</v>
       </c>
       <c r="J172" s="10">
-        <v>7696.81</v>
+        <v>7696.8099999999904</v>
       </c>
       <c r="K172" s="10">
         <v>0.92</v>
@@ -11701,7 +11774,7 @@
         <v>4</v>
       </c>
       <c r="J186" s="10">
-        <v>24872.560000000001</v>
+        <v>24872.559999999899</v>
       </c>
       <c r="K186" s="10">
         <v>0.09</v>
@@ -11718,19 +11791,19 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>434</v>
+        <v>524</v>
       </c>
       <c r="E187" s="10">
-        <v>3952.72</v>
+        <v>4783.37</v>
       </c>
       <c r="F187" s="10">
-        <v>19.989999999999998</v>
+        <v>25.99</v>
       </c>
       <c r="G187" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H187" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I187" s="10">
         <v>0</v>
@@ -11863,13 +11936,13 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>14697</v>
+        <v>17667</v>
       </c>
       <c r="E192" s="10">
-        <v>6562.88</v>
+        <v>7908.26</v>
       </c>
       <c r="F192" s="10">
-        <v>25.96</v>
+        <v>32.96</v>
       </c>
       <c r="G192" s="10">
         <v>2</v>
@@ -11878,13 +11951,13 @@
         <v>1</v>
       </c>
       <c r="I192" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" s="10">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-1</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12069,7 +12142,7 @@
         <v>3926.43</v>
       </c>
       <c r="F198" s="10">
-        <v>16.010000000000002</v>
+        <v>16.009999999999899</v>
       </c>
       <c r="G198" s="10">
         <v>11</v>
@@ -12361,7 +12434,7 @@
         <v>1</v>
       </c>
       <c r="J206" s="10">
-        <v>5742.8</v>
+        <v>5742.7999999999902</v>
       </c>
       <c r="K206" s="10">
         <v>0.16</v>
@@ -12448,10 +12521,10 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E209" s="10">
-        <v>1041.27</v>
+        <v>1338.54</v>
       </c>
       <c r="F209" s="10">
         <v>5.67</v>
@@ -12559,7 +12632,7 @@
         <v>1671.98</v>
       </c>
       <c r="F212" s="10">
-        <v>8.7200000000000006</v>
+        <v>8.71999999999999</v>
       </c>
       <c r="G212" s="10">
         <v>7</v>
@@ -12711,7 +12784,7 @@
         <v>1</v>
       </c>
       <c r="J216" s="10">
-        <v>7992</v>
+        <v>7991.99999999999</v>
       </c>
       <c r="K216" s="10">
         <v>145.88</v>
@@ -12921,7 +12994,7 @@
         <v>1</v>
       </c>
       <c r="J222" s="10">
-        <v>3996</v>
+        <v>3995.99999999999</v>
       </c>
       <c r="K222" s="10">
         <v>-0.03</v>
@@ -13043,13 +13116,13 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E226" s="10">
-        <v>1064.21</v>
+        <v>1276.8599999999999</v>
       </c>
       <c r="F226" s="10">
-        <v>2.96</v>
+        <v>3.46</v>
       </c>
       <c r="G226" s="10">
         <v>3</v>
@@ -13469,7 +13542,7 @@
         <v>9126.74</v>
       </c>
       <c r="F238" s="10">
-        <v>20.010000000000002</v>
+        <v>20.009999999999899</v>
       </c>
       <c r="G238" s="10">
         <v>30</v>
@@ -13586,10 +13659,10 @@
         <v>4</v>
       </c>
       <c r="J241" s="10">
-        <v>26681</v>
+        <v>27176</v>
       </c>
       <c r="K241" s="10">
-        <v>1.1499999999999999</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
@@ -13621,7 +13694,7 @@
         <v>2</v>
       </c>
       <c r="J242" s="10">
-        <v>15351.78</v>
+        <v>15351.779999999901</v>
       </c>
       <c r="K242" s="10">
         <v>0.28000000000000003</v>
@@ -13638,13 +13711,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="E243" s="10">
-        <v>2029.93</v>
+        <v>2442.3000000000002</v>
       </c>
       <c r="F243" s="10">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="G243" s="10"/>
       <c r="H243" s="10"/>
@@ -13669,7 +13742,7 @@
         <v>2070.7399999999998</v>
       </c>
       <c r="F244" s="10">
-        <v>16.940000000000001</v>
+        <v>16.939999999999898</v>
       </c>
       <c r="G244" s="10">
         <v>10</v>
@@ -13739,7 +13812,7 @@
         <v>3037.13</v>
       </c>
       <c r="F246" s="10">
-        <v>34.520000000000003</v>
+        <v>34.519999999999897</v>
       </c>
       <c r="G246" s="10">
         <v>12</v>
@@ -13809,7 +13882,7 @@
         <v>3925.81</v>
       </c>
       <c r="F248" s="10">
-        <v>18.510000000000002</v>
+        <v>18.509999999999899</v>
       </c>
       <c r="G248" s="10">
         <v>18</v>
@@ -14194,7 +14267,7 @@
         <v>12933.74</v>
       </c>
       <c r="F259" s="10">
-        <v>44.88</v>
+        <v>44.879999999999903</v>
       </c>
       <c r="G259" s="10">
         <v>19</v>
@@ -14381,7 +14454,7 @@
         <v>4</v>
       </c>
       <c r="J264" s="10">
-        <v>27768.240000000002</v>
+        <v>27768.2399999999</v>
       </c>
       <c r="K264" s="10">
         <v>0.5</v>
@@ -14404,7 +14477,7 @@
         <v>12460.44</v>
       </c>
       <c r="F265" s="10">
-        <v>66.010000000000005</v>
+        <v>66.009999999999906</v>
       </c>
       <c r="G265" s="10">
         <v>29</v>
@@ -14433,13 +14506,13 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="E266" s="10">
-        <v>2036.08</v>
+        <v>2480.56</v>
       </c>
       <c r="F266" s="10">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="G266" s="10">
         <v>8</v>
@@ -14474,7 +14547,7 @@
         <v>4824.59</v>
       </c>
       <c r="F267" s="10">
-        <v>60.56</v>
+        <v>60.559999999999903</v>
       </c>
       <c r="G267" s="10">
         <v>23</v>
@@ -14509,7 +14582,7 @@
         <v>6238.21</v>
       </c>
       <c r="F268" s="10">
-        <v>98.37</v>
+        <v>98.369999999999905</v>
       </c>
       <c r="G268" s="10">
         <v>19</v>
@@ -14544,7 +14617,7 @@
         <v>5890.79</v>
       </c>
       <c r="F269" s="10">
-        <v>68.040000000000006</v>
+        <v>68.039999999999907</v>
       </c>
       <c r="G269" s="10">
         <v>15</v>
@@ -14956,7 +15029,7 @@
         <v>7</v>
       </c>
       <c r="J283" s="10">
-        <v>54199.23</v>
+        <v>54199.229999999901</v>
       </c>
       <c r="K283" s="10">
         <v>10.08</v>
@@ -15084,7 +15157,7 @@
         <v>7178.57</v>
       </c>
       <c r="F287" s="10">
-        <v>37.520000000000003</v>
+        <v>37.519999999999897</v>
       </c>
       <c r="G287" s="10">
         <v>24</v>
@@ -15437,10 +15510,10 @@
         <v>70.47</v>
       </c>
       <c r="G297" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H297" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I297" s="10">
         <v>8</v>
@@ -15644,7 +15717,7 @@
         <v>28271.919999999998</v>
       </c>
       <c r="F303" s="10">
-        <v>103.98</v>
+        <v>103.979999999999</v>
       </c>
       <c r="G303" s="10">
         <v>41</v>
@@ -15656,10 +15729,10 @@
         <v>7</v>
       </c>
       <c r="J303" s="10">
-        <v>52832.77</v>
+        <v>46219.77</v>
       </c>
       <c r="K303" s="10">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
@@ -15682,10 +15755,10 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H304" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I304" s="10">
         <v>5</v>
@@ -15708,16 +15781,16 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>417</v>
+        <v>490</v>
       </c>
       <c r="E305" s="10">
-        <v>4950.0200000000004</v>
+        <v>5984.59</v>
       </c>
       <c r="F305" s="10">
-        <v>17.940000000000001</v>
+        <v>19.439999999999898</v>
       </c>
       <c r="G305" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H305" s="10">
         <v>3</v>
@@ -15812,7 +15885,7 @@
         <v>196.53</v>
       </c>
       <c r="G308" s="10">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H308" s="10">
         <v>35</v>
@@ -15850,16 +15923,16 @@
         <v>109</v>
       </c>
       <c r="H309" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I309" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J309" s="10">
-        <v>100687.46</v>
+        <v>101818.459999999</v>
       </c>
       <c r="K309" s="10">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
@@ -15958,13 +16031,13 @@
         <v>33</v>
       </c>
       <c r="I312" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J312" s="10">
-        <v>60879.96</v>
+        <v>66845.959999999905</v>
       </c>
       <c r="K312" s="10">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
@@ -15978,28 +16051,28 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>896</v>
+        <v>1124</v>
       </c>
       <c r="E313" s="10">
-        <v>5150.6400000000003</v>
+        <v>6077.08</v>
       </c>
       <c r="F313" s="10">
-        <v>15.85</v>
+        <v>20.68</v>
       </c>
       <c r="G313" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H313" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I313" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J313" s="10">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K313" s="10">
-        <v>-1</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16124,7 +16197,7 @@
         <v>32402.04</v>
       </c>
       <c r="F317" s="10">
-        <v>118.17</v>
+        <v>118.16999999999901</v>
       </c>
       <c r="G317" s="10">
         <v>87</v>
@@ -16229,7 +16302,7 @@
         <v>30410.11</v>
       </c>
       <c r="F320" s="10">
-        <v>163.27000000000001</v>
+        <v>163.26999999999899</v>
       </c>
       <c r="G320" s="10">
         <v>86</v>
@@ -16258,19 +16331,19 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>1451</v>
+        <v>1832</v>
       </c>
       <c r="E321" s="10">
-        <v>5839.7</v>
+        <v>6887.76</v>
       </c>
       <c r="F321" s="10">
-        <v>19.850000000000001</v>
+        <v>22.85</v>
       </c>
       <c r="G321" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H321" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I321" s="10">
         <v>1</v>
@@ -16279,7 +16352,7 @@
         <v>5560</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16674,7 +16747,7 @@
         <v>20276.71</v>
       </c>
       <c r="F333" s="10">
-        <v>49.1</v>
+        <v>49.099999999999902</v>
       </c>
       <c r="G333" s="10">
         <v>35</v>
@@ -16721,7 +16794,7 @@
         <v>9</v>
       </c>
       <c r="J334" s="10">
-        <v>61616.66</v>
+        <v>61616.659999999902</v>
       </c>
       <c r="K334" s="10">
         <v>2</v>
@@ -16779,7 +16852,7 @@
         <v>26470.52</v>
       </c>
       <c r="F336" s="10">
-        <v>164.03</v>
+        <v>164.02999999999901</v>
       </c>
       <c r="G336" s="10">
         <v>66</v>
@@ -16852,7 +16925,7 @@
         <v>171.77</v>
       </c>
       <c r="G338" s="10">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H338" s="10">
         <v>14</v>
@@ -16878,16 +16951,16 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="E339" s="10">
-        <v>4397.24</v>
+        <v>5320.85</v>
       </c>
       <c r="F339" s="10">
-        <v>18.489999999999998</v>
+        <v>19.82</v>
       </c>
       <c r="G339" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H339" s="10">
         <v>1</v>
@@ -16904,7 +16977,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B340" s="10">
         <v>2026</v>
@@ -16913,13 +16986,13 @@
         <v>18</v>
       </c>
       <c r="D340" s="10">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E340" s="10">
-        <v>1458.13</v>
+        <v>304.11</v>
       </c>
       <c r="F340" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G340" s="10"/>
       <c r="H340" s="10"/>
@@ -16929,38 +17002,28 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B341" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D341" s="10">
-        <v>2604</v>
+        <v>136</v>
       </c>
       <c r="E341" s="10">
-        <v>3023.13</v>
+        <v>1458.13</v>
       </c>
       <c r="F341" s="10">
-        <v>46.9</v>
-      </c>
-      <c r="G341" s="10">
-        <v>9</v>
-      </c>
-      <c r="H341" s="10">
-        <v>2</v>
-      </c>
-      <c r="I341" s="10">
-        <v>0</v>
-      </c>
-      <c r="J341" s="10">
-        <v>0</v>
-      </c>
-      <c r="K341" s="10">
-        <v>-1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G341" s="10"/>
+      <c r="H341" s="10"/>
+      <c r="I341" s="10"/>
+      <c r="J341" s="10"/>
+      <c r="K341" s="10"/>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
@@ -16970,22 +17033,22 @@
         <v>2025</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D342" s="10">
-        <v>9763</v>
+        <v>2604</v>
       </c>
       <c r="E342" s="10">
-        <v>7865.5</v>
+        <v>3023.13</v>
       </c>
       <c r="F342" s="10">
-        <v>250.18</v>
+        <v>46.9</v>
       </c>
       <c r="G342" s="10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H342" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I342" s="10">
         <v>0</v>
@@ -17005,31 +17068,31 @@
         <v>2025</v>
       </c>
       <c r="C343" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D343" s="10">
+        <v>9763</v>
+      </c>
+      <c r="E343" s="10">
+        <v>7865.5</v>
+      </c>
+      <c r="F343" s="10">
+        <v>250.18</v>
+      </c>
+      <c r="G343" s="10">
         <v>19</v>
       </c>
-      <c r="D343" s="10">
-        <v>7820</v>
-      </c>
-      <c r="E343" s="10">
-        <v>5484.57</v>
-      </c>
-      <c r="F343" s="10">
-        <v>168.25</v>
-      </c>
-      <c r="G343" s="10">
-        <v>17</v>
-      </c>
       <c r="H343" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I343" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J343" s="10">
-        <v>14334.7</v>
+        <v>0</v>
       </c>
       <c r="K343" s="10">
-        <v>1.61</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
@@ -17040,31 +17103,31 @@
         <v>2025</v>
       </c>
       <c r="C344" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D344" s="10">
-        <v>5809</v>
+        <v>7820</v>
       </c>
       <c r="E344" s="10">
-        <v>7919.47</v>
+        <v>5484.57</v>
       </c>
       <c r="F344" s="10">
-        <v>58.83</v>
+        <v>168.25</v>
       </c>
       <c r="G344" s="10">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H344" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I344" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J344" s="10">
-        <v>44163</v>
+        <v>14334.7</v>
       </c>
       <c r="K344" s="10">
-        <v>4.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.3">
@@ -17075,31 +17138,31 @@
         <v>2025</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D345" s="10">
-        <v>3271</v>
+        <v>5809</v>
       </c>
       <c r="E345" s="10">
-        <v>7851.36</v>
+        <v>7919.47</v>
       </c>
       <c r="F345" s="10">
-        <v>33.46</v>
+        <v>58.83</v>
       </c>
       <c r="G345" s="10">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H345" s="10">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I345" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J345" s="10">
-        <v>6792</v>
+        <v>44163</v>
       </c>
       <c r="K345" s="10">
-        <v>-0.13</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
@@ -17110,31 +17173,31 @@
         <v>2025</v>
       </c>
       <c r="C346" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D346" s="10">
-        <v>3463</v>
+        <v>3271</v>
       </c>
       <c r="E346" s="10">
-        <v>7226.69</v>
+        <v>7851.36</v>
       </c>
       <c r="F346" s="10">
-        <v>31.99</v>
+        <v>33.46</v>
       </c>
       <c r="G346" s="10">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H346" s="10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I346" s="10">
         <v>1</v>
       </c>
       <c r="J346" s="10">
-        <v>8167</v>
+        <v>6792</v>
       </c>
       <c r="K346" s="10">
-        <v>0.13</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.3">
@@ -17145,57 +17208,67 @@
         <v>2025</v>
       </c>
       <c r="C347" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D347" s="10">
-        <v>90</v>
+        <v>3463</v>
       </c>
       <c r="E347" s="10">
-        <v>182.43</v>
+        <v>7226.69</v>
       </c>
       <c r="F347" s="10">
-        <v>0</v>
+        <v>31.99</v>
       </c>
       <c r="G347" s="10">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H347" s="10">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I347" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J347" s="10">
-        <v>33153.71</v>
+        <v>8166.99999999999</v>
       </c>
       <c r="K347" s="10">
-        <v>180.73</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B348" s="10">
         <v>2025</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D348" s="10">
-        <v>285</v>
+        <v>90</v>
       </c>
       <c r="E348" s="10">
-        <v>3317.91</v>
+        <v>182.43</v>
       </c>
       <c r="F348" s="10">
-        <v>17.61</v>
-      </c>
-      <c r="G348" s="10"/>
-      <c r="H348" s="10"/>
-      <c r="I348" s="10"/>
-      <c r="J348" s="10"/>
-      <c r="K348" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="G348" s="10">
+        <v>51</v>
+      </c>
+      <c r="H348" s="10">
+        <v>21</v>
+      </c>
+      <c r="I348" s="10">
+        <v>4</v>
+      </c>
+      <c r="J348" s="10">
+        <v>33153.71</v>
+      </c>
+      <c r="K348" s="10">
+        <v>180.73</v>
+      </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
@@ -17205,66 +17278,56 @@
         <v>2025</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D349" s="10">
-        <v>539</v>
+        <v>285</v>
       </c>
       <c r="E349" s="10">
-        <v>5046.47</v>
+        <v>3317.91</v>
       </c>
       <c r="F349" s="10">
-        <v>51.03</v>
-      </c>
-      <c r="G349" s="10">
-        <v>10</v>
-      </c>
-      <c r="H349" s="10">
-        <v>4</v>
-      </c>
-      <c r="I349" s="10">
-        <v>1</v>
-      </c>
-      <c r="J349" s="10">
-        <v>7648.97</v>
-      </c>
-      <c r="K349" s="10">
-        <v>0.52</v>
-      </c>
+        <v>17.61</v>
+      </c>
+      <c r="G349" s="10"/>
+      <c r="H349" s="10"/>
+      <c r="I349" s="10"/>
+      <c r="J349" s="10"/>
+      <c r="K349" s="10"/>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B350" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D350" s="10">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E350" s="10">
-        <v>5077.71</v>
+        <v>5046.47</v>
       </c>
       <c r="F350" s="10">
-        <v>43.27</v>
+        <v>51.03</v>
       </c>
       <c r="G350" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H350" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I350" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J350" s="10">
-        <v>27569.200000000001</v>
+        <v>7648.97</v>
       </c>
       <c r="K350" s="10">
-        <v>4.43</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
@@ -17275,31 +17338,31 @@
         <v>2026</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D351" s="10">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="E351" s="10">
-        <v>5048.16</v>
+        <v>5077.71</v>
       </c>
       <c r="F351" s="10">
-        <v>40.270000000000003</v>
+        <v>43.269999999999897</v>
       </c>
       <c r="G351" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H351" s="10">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I351" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J351" s="10">
-        <v>38914.239999999998</v>
+        <v>27569.200000000001</v>
       </c>
       <c r="K351" s="10">
-        <v>6.71</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.3">
@@ -17310,31 +17373,31 @@
         <v>2026</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D352" s="10">
-        <v>711</v>
+        <v>568</v>
       </c>
       <c r="E352" s="10">
-        <v>7574.66</v>
+        <v>5048.16</v>
       </c>
       <c r="F352" s="10">
-        <v>45.68</v>
+        <v>40.269999999999897</v>
       </c>
       <c r="G352" s="10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H352" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I352" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J352" s="10">
-        <v>39275.800000000003</v>
+        <v>38914.239999999998</v>
       </c>
       <c r="K352" s="10">
-        <v>4.1900000000000004</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.3">
@@ -17345,31 +17408,31 @@
         <v>2026</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D353" s="10">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="E353" s="10">
-        <v>7600.17</v>
+        <v>7574.66</v>
       </c>
       <c r="F353" s="10">
-        <v>51.39</v>
+        <v>45.68</v>
       </c>
       <c r="G353" s="10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H353" s="10">
+        <v>12</v>
+      </c>
+      <c r="I353" s="10">
         <v>6</v>
       </c>
-      <c r="I353" s="10">
-        <v>2</v>
-      </c>
       <c r="J353" s="10">
-        <v>8523</v>
+        <v>39275.800000000003</v>
       </c>
       <c r="K353" s="10">
-        <v>0.12</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.3">
@@ -17380,66 +17443,66 @@
         <v>2026</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D354" s="10">
-        <v>112</v>
+        <v>693</v>
       </c>
       <c r="E354" s="10">
-        <v>1300.25</v>
+        <v>7600.17</v>
       </c>
       <c r="F354" s="10">
-        <v>5</v>
+        <v>51.39</v>
       </c>
       <c r="G354" s="10">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H354" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I354" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J354" s="10">
-        <v>0</v>
+        <v>8523</v>
       </c>
       <c r="K354" s="10">
-        <v>-1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B355" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D355" s="10">
-        <v>1279</v>
+        <v>138</v>
       </c>
       <c r="E355" s="10">
-        <v>18483.38</v>
+        <v>1557.88</v>
       </c>
       <c r="F355" s="10">
-        <v>113.5</v>
+        <v>5</v>
       </c>
       <c r="G355" s="10">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H355" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I355" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J355" s="10">
-        <v>17074</v>
+        <v>0</v>
       </c>
       <c r="K355" s="10">
-        <v>-0.08</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
@@ -17450,31 +17513,31 @@
         <v>2025</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D356" s="10">
-        <v>1343</v>
+        <v>1279</v>
       </c>
       <c r="E356" s="10">
-        <v>18545.96</v>
+        <v>18483.38</v>
       </c>
       <c r="F356" s="10">
-        <v>74.680000000000007</v>
+        <v>113.5</v>
       </c>
       <c r="G356" s="10">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H356" s="10">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I356" s="10">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J356" s="10">
-        <v>86918.12</v>
+        <v>17074</v>
       </c>
       <c r="K356" s="10">
-        <v>3.69</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.3">
@@ -17485,31 +17548,31 @@
         <v>2025</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D357" s="10">
-        <v>986</v>
+        <v>1343</v>
       </c>
       <c r="E357" s="10">
-        <v>10133.459999999999</v>
+        <v>18545.96</v>
       </c>
       <c r="F357" s="10">
-        <v>42.49</v>
+        <v>74.679999999999893</v>
       </c>
       <c r="G357" s="10">
         <v>41</v>
       </c>
       <c r="H357" s="10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I357" s="10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J357" s="10">
-        <v>43710.22</v>
+        <v>86918.12</v>
       </c>
       <c r="K357" s="10">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.3">
@@ -17520,31 +17583,31 @@
         <v>2025</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D358" s="10">
-        <v>1032</v>
+        <v>986</v>
       </c>
       <c r="E358" s="10">
-        <v>9463.0300000000007</v>
+        <v>10133.459999999999</v>
       </c>
       <c r="F358" s="10">
-        <v>34</v>
+        <v>42.49</v>
       </c>
       <c r="G358" s="10">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H358" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I358" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J358" s="10">
-        <v>64285.36</v>
+        <v>43710.22</v>
       </c>
       <c r="K358" s="10">
-        <v>5.79</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.3">
@@ -17555,31 +17618,31 @@
         <v>2025</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D359" s="10">
-        <v>1399</v>
+        <v>1032</v>
       </c>
       <c r="E359" s="10">
-        <v>12015.14</v>
+        <v>9463.0300000000007</v>
       </c>
       <c r="F359" s="10">
-        <v>42.5</v>
+        <v>34</v>
       </c>
       <c r="G359" s="10">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H359" s="10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I359" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J359" s="10">
-        <v>91057.75</v>
+        <v>64285.36</v>
       </c>
       <c r="K359" s="10">
-        <v>6.58</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.3">
@@ -17590,31 +17653,31 @@
         <v>2025</v>
       </c>
       <c r="C360" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D360" s="10">
-        <v>1186</v>
+        <v>1399</v>
       </c>
       <c r="E360" s="10">
-        <v>11775.01</v>
+        <v>12015.14</v>
       </c>
       <c r="F360" s="10">
-        <v>45.32</v>
+        <v>42.5</v>
       </c>
       <c r="G360" s="10">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H360" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I360" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J360" s="10">
-        <v>67230.75</v>
+        <v>91057.75</v>
       </c>
       <c r="K360" s="10">
-        <v>4.71</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.3">
@@ -17625,31 +17688,31 @@
         <v>2025</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D361" s="10">
-        <v>1647</v>
+        <v>1186</v>
       </c>
       <c r="E361" s="10">
-        <v>18879.95</v>
+        <v>11775.01</v>
       </c>
       <c r="F361" s="10">
-        <v>47.7</v>
+        <v>45.32</v>
       </c>
       <c r="G361" s="10">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H361" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I361" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J361" s="10">
-        <v>29024.63</v>
+        <v>67230.75</v>
       </c>
       <c r="K361" s="10">
-        <v>0.54</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.3">
@@ -17660,31 +17723,31 @@
         <v>2025</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D362" s="10">
-        <v>1846</v>
+        <v>1647</v>
       </c>
       <c r="E362" s="10">
-        <v>21280.35</v>
+        <v>18879.95</v>
       </c>
       <c r="F362" s="10">
-        <v>51.08</v>
+        <v>47.7</v>
       </c>
       <c r="G362" s="10">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H362" s="10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I362" s="10">
         <v>6</v>
       </c>
       <c r="J362" s="10">
-        <v>39893.14</v>
+        <v>29024.63</v>
       </c>
       <c r="K362" s="10">
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.3">
@@ -17695,31 +17758,31 @@
         <v>2025</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D363" s="10">
-        <v>1506</v>
+        <v>1846</v>
       </c>
       <c r="E363" s="10">
-        <v>21078.14</v>
+        <v>21280.35</v>
       </c>
       <c r="F363" s="10">
-        <v>41.56</v>
+        <v>51.08</v>
       </c>
       <c r="G363" s="10">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H363" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I363" s="10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J363" s="10">
-        <v>79358.69</v>
+        <v>39893.14</v>
       </c>
       <c r="K363" s="10">
-        <v>2.76</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.3">
@@ -17730,31 +17793,31 @@
         <v>2025</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D364" s="10">
-        <v>1305</v>
+        <v>1506</v>
       </c>
       <c r="E364" s="10">
-        <v>18345.509999999998</v>
+        <v>21078.14</v>
       </c>
       <c r="F364" s="10">
-        <v>55</v>
+        <v>41.56</v>
       </c>
       <c r="G364" s="10">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H364" s="10">
+        <v>24</v>
+      </c>
+      <c r="I364" s="10">
         <v>12</v>
       </c>
-      <c r="I364" s="10">
-        <v>6</v>
-      </c>
       <c r="J364" s="10">
-        <v>43960.28</v>
+        <v>79358.69</v>
       </c>
       <c r="K364" s="10">
-        <v>1.4</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.3">
@@ -17765,31 +17828,31 @@
         <v>2025</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D365" s="10">
-        <v>1379</v>
+        <v>1305</v>
       </c>
       <c r="E365" s="10">
-        <v>18633.439999999999</v>
+        <v>18345.509999999998</v>
       </c>
       <c r="F365" s="10">
-        <v>51.48</v>
+        <v>55</v>
       </c>
       <c r="G365" s="10">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H365" s="10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I365" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J365" s="10">
-        <v>32175.87</v>
+        <v>43960.28</v>
       </c>
       <c r="K365" s="10">
-        <v>0.73</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.3">
@@ -17800,31 +17863,31 @@
         <v>2025</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D366" s="10">
-        <v>1592</v>
+        <v>1379</v>
       </c>
       <c r="E366" s="10">
-        <v>19172.93</v>
+        <v>18633.439999999999</v>
       </c>
       <c r="F366" s="10">
-        <v>78.45</v>
+        <v>51.48</v>
       </c>
       <c r="G366" s="10">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H366" s="10">
         <v>19</v>
       </c>
       <c r="I366" s="10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J366" s="10">
-        <v>54648.83</v>
+        <v>32175.87</v>
       </c>
       <c r="K366" s="10">
-        <v>1.85</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.3">
@@ -17832,34 +17895,34 @@
         <v>58</v>
       </c>
       <c r="B367" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D367" s="10">
-        <v>1861</v>
+        <v>1592</v>
       </c>
       <c r="E367" s="10">
-        <v>20545.41</v>
+        <v>19172.93</v>
       </c>
       <c r="F367" s="10">
-        <v>91.5</v>
+        <v>78.449999999999903</v>
       </c>
       <c r="G367" s="10">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H367" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I367" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J367" s="10">
-        <v>50898.68</v>
+        <v>54648.83</v>
       </c>
       <c r="K367" s="10">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.3">
@@ -17870,31 +17933,31 @@
         <v>2026</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D368" s="10">
-        <v>1516</v>
+        <v>1861</v>
       </c>
       <c r="E368" s="10">
-        <v>18973.55</v>
+        <v>20545.41</v>
       </c>
       <c r="F368" s="10">
-        <v>73.5</v>
+        <v>91.5</v>
       </c>
       <c r="G368" s="10">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H368" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I368" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J368" s="10">
-        <v>38485.74</v>
+        <v>50898.68</v>
       </c>
       <c r="K368" s="10">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -17905,31 +17968,31 @@
         <v>2026</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D369" s="10">
-        <v>1685</v>
+        <v>1516</v>
       </c>
       <c r="E369" s="10">
-        <v>20205.009999999998</v>
+        <v>18973.55</v>
       </c>
       <c r="F369" s="10">
-        <v>81.23</v>
+        <v>73.5</v>
       </c>
       <c r="G369" s="10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H369" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I369" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J369" s="10">
-        <v>51854.48</v>
+        <v>38485.74</v>
       </c>
       <c r="K369" s="10">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
@@ -17940,31 +18003,31 @@
         <v>2026</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D370" s="10">
-        <v>1511</v>
+        <v>1685</v>
       </c>
       <c r="E370" s="10">
-        <v>20210.580000000002</v>
+        <v>20205.009999999998</v>
       </c>
       <c r="F370" s="10">
-        <v>82.38</v>
+        <v>81.229999999999905</v>
       </c>
       <c r="G370" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H370" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I370" s="10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J370" s="10">
-        <v>15847</v>
+        <v>51854.48</v>
       </c>
       <c r="K370" s="10">
-        <v>-0.22</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.3">
@@ -17975,54 +18038,54 @@
         <v>2026</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D371" s="10">
-        <v>266</v>
+        <v>1511</v>
       </c>
       <c r="E371" s="10">
-        <v>3329.43</v>
+        <v>20210.580000000002</v>
       </c>
       <c r="F371" s="10">
-        <v>10.99</v>
+        <v>82.38</v>
       </c>
       <c r="G371" s="10">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H371" s="10">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I371" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J371" s="10">
-        <v>0</v>
+        <v>15847</v>
       </c>
       <c r="K371" s="10">
-        <v>-1</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B372" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D372" s="10">
-        <v>166</v>
+        <v>307</v>
       </c>
       <c r="E372" s="10">
-        <v>34.65</v>
+        <v>3953.27</v>
       </c>
       <c r="F372" s="10">
-        <v>9.99</v>
+        <v>17.98</v>
       </c>
       <c r="G372" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H372" s="10">
         <v>1</v>
@@ -18045,22 +18108,22 @@
         <v>2025</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D373" s="10">
-        <v>8380</v>
+        <v>166</v>
       </c>
       <c r="E373" s="10">
-        <v>3368</v>
+        <v>34.65</v>
       </c>
       <c r="F373" s="10">
-        <v>29</v>
+        <v>9.99</v>
       </c>
       <c r="G373" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H373" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I373" s="10">
         <v>0</v>
@@ -18080,31 +18143,31 @@
         <v>2025</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D374" s="10">
-        <v>17369</v>
+        <v>8380</v>
       </c>
       <c r="E374" s="10">
-        <v>5964.35</v>
+        <v>3368</v>
       </c>
       <c r="F374" s="10">
-        <v>97.34</v>
+        <v>29</v>
       </c>
       <c r="G374" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H374" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I374" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J374" s="10">
-        <v>12747</v>
+        <v>0</v>
       </c>
       <c r="K374" s="10">
-        <v>1.1399999999999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.3">
@@ -18115,31 +18178,31 @@
         <v>2025</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D375" s="10">
-        <v>11231</v>
+        <v>17369</v>
       </c>
       <c r="E375" s="10">
-        <v>5898.88</v>
+        <v>5964.35</v>
       </c>
       <c r="F375" s="10">
-        <v>81.56</v>
+        <v>97.34</v>
       </c>
       <c r="G375" s="10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H375" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I375" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J375" s="10">
-        <v>16757.05</v>
+        <v>12747</v>
       </c>
       <c r="K375" s="10">
-        <v>1.84</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.3">
@@ -18150,31 +18213,31 @@
         <v>2025</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D376" s="10">
-        <v>7135</v>
+        <v>11231</v>
       </c>
       <c r="E376" s="10">
-        <v>5899.41</v>
+        <v>5898.88</v>
       </c>
       <c r="F376" s="10">
-        <v>43.97</v>
+        <v>81.56</v>
       </c>
       <c r="G376" s="10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H376" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I376" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J376" s="10">
-        <v>8908</v>
+        <v>16757.05</v>
       </c>
       <c r="K376" s="10">
-        <v>0.51</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.3">
@@ -18185,31 +18248,31 @@
         <v>2025</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D377" s="10">
-        <v>3123</v>
+        <v>7135</v>
       </c>
       <c r="E377" s="10">
-        <v>5907.54</v>
+        <v>5899.41</v>
       </c>
       <c r="F377" s="10">
-        <v>33.409999999999997</v>
+        <v>43.97</v>
       </c>
       <c r="G377" s="10">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H377" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I377" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J377" s="10">
-        <v>279</v>
+        <v>8908</v>
       </c>
       <c r="K377" s="10">
-        <v>-0.95</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.3">
@@ -18220,66 +18283,66 @@
         <v>2025</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D378" s="10">
-        <v>1847</v>
+        <v>3123</v>
       </c>
       <c r="E378" s="10">
-        <v>4432.75</v>
+        <v>5907.54</v>
       </c>
       <c r="F378" s="10">
-        <v>22.07</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="G378" s="10">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H378" s="10">
         <v>6</v>
       </c>
       <c r="I378" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J378" s="10">
-        <v>21925.09</v>
+        <v>279</v>
       </c>
       <c r="K378" s="10">
-        <v>3.95</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B379" s="10">
         <v>2025</v>
       </c>
       <c r="C379" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D379" s="10">
+        <v>1847</v>
+      </c>
+      <c r="E379" s="10">
+        <v>4432.75</v>
+      </c>
+      <c r="F379" s="10">
+        <v>22.07</v>
+      </c>
+      <c r="G379" s="10">
         <v>14</v>
       </c>
-      <c r="D379" s="10">
-        <v>1120</v>
-      </c>
-      <c r="E379" s="10">
-        <v>13806.08</v>
-      </c>
-      <c r="F379" s="10">
-        <v>117.67</v>
-      </c>
-      <c r="G379" s="10">
-        <v>26</v>
-      </c>
       <c r="H379" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I379" s="10">
         <v>3</v>
       </c>
       <c r="J379" s="10">
-        <v>20651.47</v>
+        <v>21925.09</v>
       </c>
       <c r="K379" s="10">
-        <v>0.5</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
@@ -18290,31 +18353,31 @@
         <v>2025</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D380" s="10">
-        <v>1428</v>
+        <v>1120</v>
       </c>
       <c r="E380" s="10">
-        <v>19992.240000000002</v>
+        <v>13806.08</v>
       </c>
       <c r="F380" s="10">
-        <v>121.03</v>
+        <v>117.67</v>
       </c>
       <c r="G380" s="10">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H380" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I380" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J380" s="10">
-        <v>50381.37</v>
+        <v>20651.47</v>
       </c>
       <c r="K380" s="10">
-        <v>1.52</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
@@ -18325,19 +18388,19 @@
         <v>2025</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D381" s="10">
-        <v>1375</v>
+        <v>1428</v>
       </c>
       <c r="E381" s="10">
-        <v>15772.75</v>
+        <v>19992.240000000002</v>
       </c>
       <c r="F381" s="10">
-        <v>43.66</v>
+        <v>121.03</v>
       </c>
       <c r="G381" s="10">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H381" s="10">
         <v>13</v>
@@ -18346,10 +18409,10 @@
         <v>7</v>
       </c>
       <c r="J381" s="10">
-        <v>43934.68</v>
+        <v>50381.37</v>
       </c>
       <c r="K381" s="10">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
@@ -18360,31 +18423,31 @@
         <v>2025</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D382" s="10">
-        <v>1013</v>
+        <v>1375</v>
       </c>
       <c r="E382" s="10">
-        <v>8945.9699999999993</v>
+        <v>15772.75</v>
       </c>
       <c r="F382" s="10">
-        <v>36.5</v>
+        <v>43.66</v>
       </c>
       <c r="G382" s="10">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H382" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I382" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J382" s="10">
-        <v>21029.41</v>
+        <v>43934.68</v>
       </c>
       <c r="K382" s="10">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
@@ -18395,31 +18458,31 @@
         <v>2025</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D383" s="10">
-        <v>1203</v>
+        <v>1013</v>
       </c>
       <c r="E383" s="10">
-        <v>10931.15</v>
+        <v>8945.9699999999993</v>
       </c>
       <c r="F383" s="10">
-        <v>52.03</v>
+        <v>36.5</v>
       </c>
       <c r="G383" s="10">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H383" s="10">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I383" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J383" s="10">
-        <v>12295.56</v>
+        <v>21029.41</v>
       </c>
       <c r="K383" s="10">
-        <v>0.12</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.3">
@@ -18430,31 +18493,31 @@
         <v>2025</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D384" s="10">
-        <v>1039</v>
+        <v>1203</v>
       </c>
       <c r="E384" s="10">
-        <v>11764.77</v>
+        <v>10931.15</v>
       </c>
       <c r="F384" s="10">
-        <v>27.64</v>
+        <v>52.03</v>
       </c>
       <c r="G384" s="10">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H384" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I384" s="10">
         <v>2</v>
       </c>
       <c r="J384" s="10">
-        <v>12747.9</v>
+        <v>12295.56</v>
       </c>
       <c r="K384" s="10">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.3">
@@ -18465,31 +18528,31 @@
         <v>2025</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D385" s="10">
-        <v>1570</v>
+        <v>1039</v>
       </c>
       <c r="E385" s="10">
-        <v>18806.53</v>
+        <v>11764.77</v>
       </c>
       <c r="F385" s="10">
-        <v>57.81</v>
+        <v>27.64</v>
       </c>
       <c r="G385" s="10">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H385" s="10">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I385" s="10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J385" s="10">
-        <v>65983.360000000001</v>
+        <v>12747.9</v>
       </c>
       <c r="K385" s="10">
-        <v>2.5099999999999998</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.3">
@@ -18500,31 +18563,31 @@
         <v>2025</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D386" s="10">
-        <v>1875</v>
+        <v>1570</v>
       </c>
       <c r="E386" s="10">
-        <v>22624.03</v>
+        <v>18806.53</v>
       </c>
       <c r="F386" s="10">
-        <v>51.14</v>
+        <v>57.81</v>
       </c>
       <c r="G386" s="10">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H386" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I386" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J386" s="10">
-        <v>50193.16</v>
+        <v>65983.360000000001</v>
       </c>
       <c r="K386" s="10">
-        <v>1.22</v>
+        <v>2.5099999999999998</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.3">
@@ -18535,31 +18598,31 @@
         <v>2025</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D387" s="10">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="E387" s="10">
-        <v>23802.080000000002</v>
+        <v>22624.03</v>
       </c>
       <c r="F387" s="10">
-        <v>82.19</v>
+        <v>51.14</v>
       </c>
       <c r="G387" s="10">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H387" s="10">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I387" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J387" s="10">
-        <v>45254.8</v>
+        <v>50193.159999999902</v>
       </c>
       <c r="K387" s="10">
-        <v>0.9</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.3">
@@ -18570,31 +18633,31 @@
         <v>2025</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D388" s="10">
-        <v>1542</v>
+        <v>1869</v>
       </c>
       <c r="E388" s="10">
-        <v>18523.04</v>
+        <v>23802.080000000002</v>
       </c>
       <c r="F388" s="10">
-        <v>91.55</v>
+        <v>82.19</v>
       </c>
       <c r="G388" s="10">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H388" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I388" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J388" s="10">
-        <v>32969.129999999997</v>
+        <v>45254.8</v>
       </c>
       <c r="K388" s="10">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.3">
@@ -18605,31 +18668,31 @@
         <v>2025</v>
       </c>
       <c r="C389" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D389" s="10">
+        <v>1542</v>
+      </c>
+      <c r="E389" s="10">
+        <v>18523.04</v>
+      </c>
+      <c r="F389" s="10">
+        <v>91.55</v>
+      </c>
+      <c r="G389" s="10">
+        <v>47</v>
+      </c>
+      <c r="H389" s="10">
         <v>24</v>
-      </c>
-      <c r="D389" s="10">
-        <v>1232</v>
-      </c>
-      <c r="E389" s="10">
-        <v>16789.099999999999</v>
-      </c>
-      <c r="F389" s="10">
-        <v>62.82</v>
-      </c>
-      <c r="G389" s="10">
-        <v>29</v>
-      </c>
-      <c r="H389" s="10">
-        <v>16</v>
       </c>
       <c r="I389" s="10">
         <v>5</v>
       </c>
       <c r="J389" s="10">
-        <v>50911.08</v>
+        <v>32969.129999999997</v>
       </c>
       <c r="K389" s="10">
-        <v>2.0299999999999998</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
@@ -18640,31 +18703,31 @@
         <v>2025</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D390" s="10">
-        <v>1254</v>
+        <v>1232</v>
       </c>
       <c r="E390" s="10">
-        <v>14120.95</v>
+        <v>16789.099999999999</v>
       </c>
       <c r="F390" s="10">
-        <v>60.65</v>
+        <v>62.82</v>
       </c>
       <c r="G390" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H390" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I390" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J390" s="10">
-        <v>26825.68</v>
+        <v>50911.08</v>
       </c>
       <c r="K390" s="10">
-        <v>0.9</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.3">
@@ -18672,34 +18735,34 @@
         <v>60</v>
       </c>
       <c r="B391" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D391" s="10">
-        <v>1456</v>
+        <v>1254</v>
       </c>
       <c r="E391" s="10">
-        <v>16923.400000000001</v>
+        <v>14120.95</v>
       </c>
       <c r="F391" s="10">
-        <v>77.13</v>
+        <v>60.65</v>
       </c>
       <c r="G391" s="10">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H391" s="10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I391" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J391" s="10">
-        <v>30172.16</v>
+        <v>27841.64</v>
       </c>
       <c r="K391" s="10">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.3">
@@ -18710,31 +18773,31 @@
         <v>2026</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D392" s="10">
-        <v>1682</v>
+        <v>1456</v>
       </c>
       <c r="E392" s="10">
-        <v>21330.36</v>
+        <v>16923.400000000001</v>
       </c>
       <c r="F392" s="10">
-        <v>73.819999999999993</v>
+        <v>77.13</v>
       </c>
       <c r="G392" s="10">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H392" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I392" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J392" s="10">
-        <v>21036.240000000002</v>
+        <v>30172.16</v>
       </c>
       <c r="K392" s="10">
-        <v>-0.01</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.3">
@@ -18745,31 +18808,31 @@
         <v>2026</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D393" s="10">
-        <v>1622</v>
+        <v>1682</v>
       </c>
       <c r="E393" s="10">
-        <v>18924.47</v>
+        <v>21330.36</v>
       </c>
       <c r="F393" s="10">
-        <v>80.14</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="G393" s="10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H393" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I393" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J393" s="10">
-        <v>54059.12</v>
+        <v>21036.240000000002</v>
       </c>
       <c r="K393" s="10">
-        <v>1.86</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.3">
@@ -18780,31 +18843,31 @@
         <v>2026</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D394" s="10">
-        <v>1765</v>
+        <v>1622</v>
       </c>
       <c r="E394" s="10">
-        <v>23623.439999999999</v>
+        <v>18924.47</v>
       </c>
       <c r="F394" s="10">
-        <v>81.02</v>
+        <v>80.14</v>
       </c>
       <c r="G394" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H394" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I394" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J394" s="10">
-        <v>7311</v>
+        <v>54059.12</v>
       </c>
       <c r="K394" s="10">
-        <v>-0.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -18815,36 +18878,36 @@
         <v>2026</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D395" s="10">
-        <v>213</v>
+        <v>1765</v>
       </c>
       <c r="E395" s="10">
-        <v>2861.78</v>
+        <v>23623.439999999999</v>
       </c>
       <c r="F395" s="10">
-        <v>10.199999999999999</v>
+        <v>81.02</v>
       </c>
       <c r="G395" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H395" s="10">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I395" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J395" s="10">
-        <v>16511.68</v>
+        <v>7311</v>
       </c>
       <c r="K395" s="10">
-        <v>4.7699999999999996</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="10" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="B396" s="10">
         <v>2026</v>
@@ -18853,89 +18916,79 @@
         <v>18</v>
       </c>
       <c r="D396" s="10">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="E396" s="10">
-        <v>1104.46</v>
+        <v>3495.82</v>
       </c>
       <c r="F396" s="10">
-        <v>2</v>
-      </c>
-      <c r="G396" s="10"/>
-      <c r="H396" s="10"/>
-      <c r="I396" s="10"/>
-      <c r="J396" s="10"/>
-      <c r="K396" s="10"/>
+        <v>12.87</v>
+      </c>
+      <c r="G396" s="10">
+        <v>13</v>
+      </c>
+      <c r="H396" s="10">
+        <v>7</v>
+      </c>
+      <c r="I396" s="10">
+        <v>3</v>
+      </c>
+      <c r="J396" s="10">
+        <v>17492.68</v>
+      </c>
+      <c r="K396" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="10" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="B397" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D397" s="10">
-        <v>4206</v>
+        <v>94</v>
       </c>
       <c r="E397" s="10">
-        <v>3006.79</v>
+        <v>1104.46</v>
       </c>
       <c r="F397" s="10">
-        <v>39.630000000000003</v>
-      </c>
-      <c r="G397" s="10">
-        <v>8</v>
-      </c>
-      <c r="H397" s="10">
-        <v>4</v>
-      </c>
-      <c r="I397" s="10">
-        <v>0</v>
-      </c>
-      <c r="J397" s="10">
-        <v>0</v>
-      </c>
-      <c r="K397" s="10">
-        <v>-1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G397" s="10"/>
+      <c r="H397" s="10"/>
+      <c r="I397" s="10"/>
+      <c r="J397" s="10"/>
+      <c r="K397" s="10"/>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="10" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="B398" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C398" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D398" s="10">
-        <v>24682</v>
+        <v>22</v>
       </c>
       <c r="E398" s="10">
-        <v>8783.7999999999993</v>
+        <v>205.16</v>
       </c>
       <c r="F398" s="10">
-        <v>127.59</v>
-      </c>
-      <c r="G398" s="10">
-        <v>29</v>
-      </c>
-      <c r="H398" s="10">
-        <v>4</v>
-      </c>
-      <c r="I398" s="10">
-        <v>3</v>
-      </c>
-      <c r="J398" s="10">
-        <v>26702.85</v>
-      </c>
-      <c r="K398" s="10">
-        <v>2.04</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G398" s="10"/>
+      <c r="H398" s="10"/>
+      <c r="I398" s="10"/>
+      <c r="J398" s="10"/>
+      <c r="K398" s="10"/>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="10" t="s">
@@ -18945,31 +18998,31 @@
         <v>2025</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D399" s="10">
-        <v>13233</v>
+        <v>4206</v>
       </c>
       <c r="E399" s="10">
-        <v>6345.41</v>
+        <v>3006.79</v>
       </c>
       <c r="F399" s="10">
-        <v>63.95</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="G399" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H399" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I399" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J399" s="10">
-        <v>7926.23</v>
+        <v>0</v>
       </c>
       <c r="K399" s="10">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.3">
@@ -18980,31 +19033,31 @@
         <v>2025</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D400" s="10">
-        <v>7954</v>
+        <v>24682</v>
       </c>
       <c r="E400" s="10">
-        <v>8876.9699999999993</v>
+        <v>8783.7999999999993</v>
       </c>
       <c r="F400" s="10">
-        <v>32.35</v>
+        <v>127.59</v>
       </c>
       <c r="G400" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H400" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I400" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J400" s="10">
-        <v>17571.16</v>
+        <v>26702.85</v>
       </c>
       <c r="K400" s="10">
-        <v>0.98</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.3">
@@ -19015,31 +19068,31 @@
         <v>2025</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D401" s="10">
-        <v>3356</v>
+        <v>13233</v>
       </c>
       <c r="E401" s="10">
-        <v>8805.02</v>
+        <v>6345.41</v>
       </c>
       <c r="F401" s="10">
-        <v>14.43</v>
+        <v>63.95</v>
       </c>
       <c r="G401" s="10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H401" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I401" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J401" s="10">
-        <v>22959</v>
+        <v>7926.23</v>
       </c>
       <c r="K401" s="10">
-        <v>1.61</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.3">
@@ -19050,28 +19103,28 @@
         <v>2025</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D402" s="10">
-        <v>2567</v>
+        <v>7954</v>
       </c>
       <c r="E402" s="10">
-        <v>6472.59</v>
+        <v>8876.9699999999993</v>
       </c>
       <c r="F402" s="10">
-        <v>17.760000000000002</v>
+        <v>32.35</v>
       </c>
       <c r="G402" s="10">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H402" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I402" s="10">
         <v>2</v>
       </c>
       <c r="J402" s="10">
-        <v>12792</v>
+        <v>17571.16</v>
       </c>
       <c r="K402" s="10">
         <v>0.98</v>
@@ -19079,72 +19132,92 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B403" s="10">
         <v>2025</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D403" s="10">
-        <v>1945</v>
+        <v>3356</v>
       </c>
       <c r="E403" s="10">
-        <v>3569.76</v>
+        <v>8805.02</v>
       </c>
       <c r="F403" s="10">
-        <v>10.01</v>
-      </c>
-      <c r="G403" s="10"/>
-      <c r="H403" s="10"/>
-      <c r="I403" s="10"/>
-      <c r="J403" s="10"/>
-      <c r="K403" s="10"/>
+        <v>14.43</v>
+      </c>
+      <c r="G403" s="10">
+        <v>15</v>
+      </c>
+      <c r="H403" s="10">
+        <v>8</v>
+      </c>
+      <c r="I403" s="10">
+        <v>3</v>
+      </c>
+      <c r="J403" s="10">
+        <v>22959</v>
+      </c>
+      <c r="K403" s="10">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B404" s="10">
         <v>2025</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D404" s="10">
-        <v>154</v>
+        <v>2567</v>
       </c>
       <c r="E404" s="10">
-        <v>36.21</v>
+        <v>6472.59</v>
       </c>
       <c r="F404" s="10">
-        <v>0</v>
-      </c>
-      <c r="G404" s="10"/>
-      <c r="H404" s="10"/>
-      <c r="I404" s="10"/>
-      <c r="J404" s="10"/>
-      <c r="K404" s="10"/>
+        <v>17.759999999999899</v>
+      </c>
+      <c r="G404" s="10">
+        <v>9</v>
+      </c>
+      <c r="H404" s="10">
+        <v>4</v>
+      </c>
+      <c r="I404" s="10">
+        <v>2</v>
+      </c>
+      <c r="J404" s="10">
+        <v>12792</v>
+      </c>
+      <c r="K404" s="10">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B405" s="10">
         <v>2025</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D405" s="10">
-        <v>799</v>
+        <v>1945</v>
       </c>
       <c r="E405" s="10">
-        <v>1830.52</v>
+        <v>3569.76</v>
       </c>
       <c r="F405" s="10">
-        <v>4.43</v>
+        <v>10.01</v>
       </c>
       <c r="G405" s="10"/>
       <c r="H405" s="10"/>
@@ -19160,32 +19233,22 @@
         <v>2025</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D406" s="10">
-        <v>1365</v>
+        <v>154</v>
       </c>
       <c r="E406" s="10">
-        <v>2992.53</v>
+        <v>36.21</v>
       </c>
       <c r="F406" s="10">
-        <v>5.83</v>
-      </c>
-      <c r="G406" s="10">
-        <v>2</v>
-      </c>
-      <c r="H406" s="10">
-        <v>2</v>
-      </c>
-      <c r="I406" s="10">
-        <v>1</v>
-      </c>
-      <c r="J406" s="10">
-        <v>8192</v>
-      </c>
-      <c r="K406" s="10">
-        <v>1.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G406" s="10"/>
+      <c r="H406" s="10"/>
+      <c r="I406" s="10"/>
+      <c r="J406" s="10"/>
+      <c r="K406" s="10"/>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="10" t="s">
@@ -19195,16 +19258,16 @@
         <v>2025</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D407" s="10">
-        <v>566</v>
+        <v>799</v>
       </c>
       <c r="E407" s="10">
-        <v>2266.7199999999998</v>
+        <v>1830.52</v>
       </c>
       <c r="F407" s="10">
-        <v>2.67</v>
+        <v>4.43</v>
       </c>
       <c r="G407" s="10"/>
       <c r="H407" s="10"/>
@@ -19214,47 +19277,57 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B408" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D408" s="10">
-        <v>75</v>
+        <v>1365</v>
       </c>
       <c r="E408" s="10">
-        <v>2453.9299999999998</v>
+        <v>2992.53</v>
       </c>
       <c r="F408" s="10">
-        <v>1</v>
-      </c>
-      <c r="G408" s="10"/>
-      <c r="H408" s="10"/>
-      <c r="I408" s="10"/>
-      <c r="J408" s="10"/>
-      <c r="K408" s="10"/>
+        <v>5.83</v>
+      </c>
+      <c r="G408" s="10">
+        <v>2</v>
+      </c>
+      <c r="H408" s="10">
+        <v>2</v>
+      </c>
+      <c r="I408" s="10">
+        <v>1</v>
+      </c>
+      <c r="J408" s="10">
+        <v>8192</v>
+      </c>
+      <c r="K408" s="10">
+        <v>1.74</v>
+      </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B409" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D409" s="10">
-        <v>130</v>
+        <v>566</v>
       </c>
       <c r="E409" s="10">
-        <v>3862.91</v>
+        <v>2266.7199999999998</v>
       </c>
       <c r="F409" s="10">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="G409" s="10"/>
       <c r="H409" s="10"/>
@@ -19264,73 +19337,53 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B410" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D410" s="10">
-        <v>782</v>
+        <v>75</v>
       </c>
       <c r="E410" s="10">
-        <v>13793.84</v>
+        <v>2453.9299999999998</v>
       </c>
       <c r="F410" s="10">
-        <v>84.41</v>
-      </c>
-      <c r="G410" s="10">
-        <v>12</v>
-      </c>
-      <c r="H410" s="10">
-        <v>5</v>
-      </c>
-      <c r="I410" s="10">
-        <v>3</v>
-      </c>
-      <c r="J410" s="10">
-        <v>21292.16</v>
-      </c>
-      <c r="K410" s="10">
-        <v>0.54</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G410" s="10"/>
+      <c r="H410" s="10"/>
+      <c r="I410" s="10"/>
+      <c r="J410" s="10"/>
+      <c r="K410" s="10"/>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B411" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C411" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D411" s="10">
-        <v>799</v>
+        <v>130</v>
       </c>
       <c r="E411" s="10">
-        <v>13861.32</v>
+        <v>3862.91</v>
       </c>
       <c r="F411" s="10">
-        <v>45.25</v>
-      </c>
-      <c r="G411" s="10">
-        <v>28</v>
-      </c>
-      <c r="H411" s="10">
-        <v>11</v>
-      </c>
-      <c r="I411" s="10">
-        <v>6</v>
-      </c>
-      <c r="J411" s="10">
-        <v>44540.87</v>
-      </c>
-      <c r="K411" s="10">
-        <v>2.21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G411" s="10"/>
+      <c r="H411" s="10"/>
+      <c r="I411" s="10"/>
+      <c r="J411" s="10"/>
+      <c r="K411" s="10"/>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="10" t="s">
@@ -19340,31 +19393,31 @@
         <v>2025</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D412" s="10">
-        <v>715</v>
+        <v>782</v>
       </c>
       <c r="E412" s="10">
-        <v>8808.84</v>
+        <v>13793.84</v>
       </c>
       <c r="F412" s="10">
-        <v>37.08</v>
+        <v>84.41</v>
       </c>
       <c r="G412" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H412" s="10">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I412" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J412" s="10">
-        <v>50422.34</v>
+        <v>21292.16</v>
       </c>
       <c r="K412" s="10">
-        <v>4.72</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
@@ -19375,31 +19428,31 @@
         <v>2025</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D413" s="10">
-        <v>437</v>
+        <v>799</v>
       </c>
       <c r="E413" s="10">
-        <v>4902.3</v>
+        <v>13861.32</v>
       </c>
       <c r="F413" s="10">
-        <v>18.989999999999998</v>
+        <v>45.25</v>
       </c>
       <c r="G413" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H413" s="10">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I413" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J413" s="10">
-        <v>7295.12</v>
+        <v>44540.869999999901</v>
       </c>
       <c r="K413" s="10">
-        <v>0.49</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
@@ -19410,31 +19463,31 @@
         <v>2025</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D414" s="10">
-        <v>482</v>
+        <v>715</v>
       </c>
       <c r="E414" s="10">
-        <v>4636.55</v>
+        <v>8808.84</v>
       </c>
       <c r="F414" s="10">
-        <v>23.02</v>
+        <v>37.08</v>
       </c>
       <c r="G414" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H414" s="10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I414" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J414" s="10">
-        <v>15184</v>
+        <v>50422.34</v>
       </c>
       <c r="K414" s="10">
-        <v>2.27</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
@@ -19445,31 +19498,31 @@
         <v>2025</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D415" s="10">
-        <v>596</v>
+        <v>437</v>
       </c>
       <c r="E415" s="10">
-        <v>7884.31</v>
+        <v>4902.3</v>
       </c>
       <c r="F415" s="10">
-        <v>27.98</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="G415" s="10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H415" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I415" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J415" s="10">
-        <v>20933.39</v>
+        <v>7295.12</v>
       </c>
       <c r="K415" s="10">
-        <v>1.66</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.3">
@@ -19480,31 +19533,31 @@
         <v>2025</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D416" s="10">
-        <v>608</v>
+        <v>482</v>
       </c>
       <c r="E416" s="10">
-        <v>8219.64</v>
+        <v>4636.55</v>
       </c>
       <c r="F416" s="10">
-        <v>19.079999999999998</v>
+        <v>23.02</v>
       </c>
       <c r="G416" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H416" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I416" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J416" s="10">
-        <v>21432.66</v>
+        <v>15184</v>
       </c>
       <c r="K416" s="10">
-        <v>1.61</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.3">
@@ -19515,31 +19568,31 @@
         <v>2025</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D417" s="10">
-        <v>631</v>
+        <v>596</v>
       </c>
       <c r="E417" s="10">
-        <v>8535.4500000000007</v>
+        <v>7884.31</v>
       </c>
       <c r="F417" s="10">
-        <v>26.04</v>
+        <v>27.98</v>
       </c>
       <c r="G417" s="10">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H417" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I417" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J417" s="10">
-        <v>7292</v>
+        <v>20933.39</v>
       </c>
       <c r="K417" s="10">
-        <v>-0.15</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.3">
@@ -19550,31 +19603,31 @@
         <v>2025</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D418" s="10">
-        <v>709</v>
+        <v>608</v>
       </c>
       <c r="E418" s="10">
-        <v>9969.59</v>
+        <v>8219.64</v>
       </c>
       <c r="F418" s="10">
-        <v>39.520000000000003</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="G418" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H418" s="10">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I418" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J418" s="10">
-        <v>40761</v>
+        <v>21432.66</v>
       </c>
       <c r="K418" s="10">
-        <v>3.09</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.3">
@@ -19585,31 +19638,31 @@
         <v>2025</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D419" s="10">
-        <v>558</v>
+        <v>631</v>
       </c>
       <c r="E419" s="10">
-        <v>8231.73</v>
+        <v>8535.4500000000007</v>
       </c>
       <c r="F419" s="10">
-        <v>36.35</v>
+        <v>26.04</v>
       </c>
       <c r="G419" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H419" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I419" s="10">
         <v>1</v>
       </c>
       <c r="J419" s="10">
-        <v>5980</v>
+        <v>7292</v>
       </c>
       <c r="K419" s="10">
-        <v>-0.27</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
@@ -19620,31 +19673,31 @@
         <v>2025</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D420" s="10">
-        <v>487</v>
+        <v>709</v>
       </c>
       <c r="E420" s="10">
-        <v>7066.25</v>
+        <v>9969.59</v>
       </c>
       <c r="F420" s="10">
-        <v>33.49</v>
+        <v>39.519999999999897</v>
       </c>
       <c r="G420" s="10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H420" s="10">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I420" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J420" s="10">
-        <v>7456.01</v>
+        <v>40761</v>
       </c>
       <c r="K420" s="10">
-        <v>0.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
@@ -19655,31 +19708,31 @@
         <v>2025</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D421" s="10">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="E421" s="10">
-        <v>9964.6</v>
+        <v>8231.73</v>
       </c>
       <c r="F421" s="10">
-        <v>31.08</v>
+        <v>36.35</v>
       </c>
       <c r="G421" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H421" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I421" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J421" s="10">
-        <v>33101.519999999997</v>
+        <v>5980</v>
       </c>
       <c r="K421" s="10">
-        <v>2.3199999999999998</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
@@ -19687,34 +19740,34 @@
         <v>65</v>
       </c>
       <c r="B422" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D422" s="10">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="E422" s="10">
-        <v>7220.33</v>
+        <v>7066.25</v>
       </c>
       <c r="F422" s="10">
-        <v>39</v>
+        <v>33.489999999999903</v>
       </c>
       <c r="G422" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H422" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I422" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J422" s="10">
-        <v>16184</v>
+        <v>7456.01</v>
       </c>
       <c r="K422" s="10">
-        <v>1.24</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
@@ -19722,34 +19775,34 @@
         <v>65</v>
       </c>
       <c r="B423" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D423" s="10">
-        <v>450</v>
+        <v>615</v>
       </c>
       <c r="E423" s="10">
-        <v>6693.08</v>
+        <v>9964.6</v>
       </c>
       <c r="F423" s="10">
-        <v>28.01</v>
+        <v>31.08</v>
       </c>
       <c r="G423" s="10">
+        <v>14</v>
+      </c>
+      <c r="H423" s="10">
         <v>9</v>
       </c>
-      <c r="H423" s="10">
-        <v>4</v>
-      </c>
       <c r="I423" s="10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J423" s="10">
-        <v>0</v>
+        <v>33101.519999999997</v>
       </c>
       <c r="K423" s="10">
-        <v>-1</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
@@ -19760,31 +19813,31 @@
         <v>2026</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D424" s="10">
-        <v>675</v>
+        <v>512</v>
       </c>
       <c r="E424" s="10">
-        <v>11556.36</v>
+        <v>7220.33</v>
       </c>
       <c r="F424" s="10">
-        <v>36.159999999999997</v>
+        <v>39</v>
       </c>
       <c r="G424" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H424" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I424" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J424" s="10">
-        <v>7594</v>
+        <v>16184</v>
       </c>
       <c r="K424" s="10">
-        <v>-0.34</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
@@ -19795,31 +19848,31 @@
         <v>2026</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D425" s="10">
-        <v>644</v>
+        <v>450</v>
       </c>
       <c r="E425" s="10">
-        <v>10129.77</v>
+        <v>6693.08</v>
       </c>
       <c r="F425" s="10">
-        <v>37.64</v>
+        <v>28.01</v>
       </c>
       <c r="G425" s="10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H425" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I425" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J425" s="10">
-        <v>16532</v>
+        <v>0</v>
       </c>
       <c r="K425" s="10">
-        <v>0.63</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
@@ -19830,82 +19883,92 @@
         <v>2026</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D426" s="10">
-        <v>122</v>
+        <v>675</v>
       </c>
       <c r="E426" s="10">
-        <v>1870.58</v>
+        <v>11556.36</v>
       </c>
       <c r="F426" s="10">
-        <v>7.99</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="G426" s="10">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H426" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I426" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J426" s="10">
-        <v>0</v>
+        <v>7594</v>
       </c>
       <c r="K426" s="10">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B427" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C427" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D427" s="10">
+        <v>644</v>
+      </c>
+      <c r="E427" s="10">
+        <v>10129.77</v>
+      </c>
+      <c r="F427" s="10">
+        <v>37.64</v>
+      </c>
+      <c r="G427" s="10">
         <v>14</v>
       </c>
-      <c r="D427" s="10">
-        <v>512</v>
-      </c>
-      <c r="E427" s="10">
-        <v>105.12</v>
-      </c>
-      <c r="F427" s="10">
-        <v>1</v>
-      </c>
-      <c r="G427" s="10"/>
-      <c r="H427" s="10"/>
-      <c r="I427" s="10"/>
-      <c r="J427" s="10"/>
-      <c r="K427" s="10"/>
+      <c r="H427" s="10">
+        <v>7</v>
+      </c>
+      <c r="I427" s="10">
+        <v>2</v>
+      </c>
+      <c r="J427" s="10">
+        <v>16532</v>
+      </c>
+      <c r="K427" s="10">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B428" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D428" s="10">
-        <v>1674</v>
+        <v>142</v>
       </c>
       <c r="E428" s="10">
-        <v>1060.3499999999999</v>
+        <v>2273.9699999999998</v>
       </c>
       <c r="F428" s="10">
-        <v>8</v>
+        <v>9.66</v>
       </c>
       <c r="G428" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H428" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I428" s="10">
         <v>0</v>
@@ -19925,32 +19988,22 @@
         <v>2025</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D429" s="10">
-        <v>16401</v>
+        <v>512</v>
       </c>
       <c r="E429" s="10">
-        <v>4863.79</v>
+        <v>105.12</v>
       </c>
       <c r="F429" s="10">
-        <v>56.01</v>
-      </c>
-      <c r="G429" s="10">
-        <v>9</v>
-      </c>
-      <c r="H429" s="10">
-        <v>2</v>
-      </c>
-      <c r="I429" s="10">
-        <v>1</v>
-      </c>
-      <c r="J429" s="10">
-        <v>7203.18</v>
-      </c>
-      <c r="K429" s="10">
-        <v>0.48</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G429" s="10"/>
+      <c r="H429" s="10"/>
+      <c r="I429" s="10"/>
+      <c r="J429" s="10"/>
+      <c r="K429" s="10"/>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="10" t="s">
@@ -19960,22 +20013,22 @@
         <v>2025</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D430" s="10">
-        <v>10089</v>
+        <v>1674</v>
       </c>
       <c r="E430" s="10">
-        <v>4896.22</v>
+        <v>1060.3499999999999</v>
       </c>
       <c r="F430" s="10">
-        <v>17.29</v>
+        <v>8</v>
       </c>
       <c r="G430" s="10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H430" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I430" s="10">
         <v>0</v>
@@ -19995,31 +20048,31 @@
         <v>2025</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D431" s="10">
-        <v>3081</v>
+        <v>16401</v>
       </c>
       <c r="E431" s="10">
-        <v>4895.66</v>
+        <v>4863.79</v>
       </c>
       <c r="F431" s="10">
-        <v>14.84</v>
+        <v>56.01</v>
       </c>
       <c r="G431" s="10">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H431" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I431" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J431" s="10">
-        <v>29604.87</v>
+        <v>7203.18</v>
       </c>
       <c r="K431" s="10">
-        <v>5.05</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
@@ -20030,22 +20083,22 @@
         <v>2025</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D432" s="10">
-        <v>3146</v>
+        <v>10089</v>
       </c>
       <c r="E432" s="10">
-        <v>4895.83</v>
+        <v>4896.22</v>
       </c>
       <c r="F432" s="10">
-        <v>21.38</v>
+        <v>17.29</v>
       </c>
       <c r="G432" s="10">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H432" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I432" s="10">
         <v>0</v>
@@ -20065,30 +20118,100 @@
         <v>2025</v>
       </c>
       <c r="C433" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D433" s="10">
+        <v>3081</v>
+      </c>
+      <c r="E433" s="10">
+        <v>4895.66</v>
+      </c>
+      <c r="F433" s="10">
+        <v>14.84</v>
+      </c>
+      <c r="G433" s="10">
+        <v>20</v>
+      </c>
+      <c r="H433" s="10">
+        <v>6</v>
+      </c>
+      <c r="I433" s="10">
+        <v>3</v>
+      </c>
+      <c r="J433" s="10">
+        <v>29604.87</v>
+      </c>
+      <c r="K433" s="10">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>66</v>
+      </c>
+      <c r="B434">
+        <v>2025</v>
+      </c>
+      <c r="C434" t="s">
+        <v>21</v>
+      </c>
+      <c r="D434">
+        <v>3146</v>
+      </c>
+      <c r="E434">
+        <v>4895.83</v>
+      </c>
+      <c r="F434">
+        <v>21.38</v>
+      </c>
+      <c r="G434">
+        <v>17</v>
+      </c>
+      <c r="H434">
+        <v>3</v>
+      </c>
+      <c r="I434">
+        <v>0</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+      <c r="K434">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>66</v>
+      </c>
+      <c r="B435">
+        <v>2025</v>
+      </c>
+      <c r="C435" t="s">
         <v>22</v>
       </c>
-      <c r="D433" s="10">
+      <c r="D435">
         <v>1865</v>
       </c>
-      <c r="E433" s="10">
+      <c r="E435">
         <v>3655.34</v>
       </c>
-      <c r="F433" s="10">
+      <c r="F435">
         <v>11</v>
       </c>
-      <c r="G433" s="10">
+      <c r="G435">
         <v>6</v>
       </c>
-      <c r="H433" s="10">
+      <c r="H435">
         <v>4</v>
       </c>
-      <c r="I433" s="10">
-        <v>2</v>
-      </c>
-      <c r="J433" s="10">
+      <c r="I435">
+        <v>2</v>
+      </c>
+      <c r="J435">
         <v>16861</v>
       </c>
-      <c r="K433" s="10">
+      <c r="K435">
         <v>3.61</v>
       </c>
     </row>
@@ -20099,7 +20222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24622,7 +24745,7 @@
         <v>2</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -24654,16 +24777,16 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -24716,7 +24839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>118</v>
       </c>
@@ -24853,7 +24976,7 @@
         <v>1</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -24891,19 +25014,19 @@
         <v>1</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -24964,7 +25087,7 @@
         <v>5</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -24984,7 +25107,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B132" s="18">
         <v>2026</v>
@@ -24993,7 +25116,7 @@
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -25005,7 +25128,7 @@
         <v>0</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -25022,7 +25145,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B133" s="18">
         <v>2026</v>
@@ -25043,7 +25166,7 @@
         <v>0</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -25069,7 +25192,7 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -25078,7 +25201,7 @@
         <v>1</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -25098,7 +25221,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B135" s="18">
         <v>2026</v>
@@ -25107,19 +25230,19 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -25145,16 +25268,16 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -25183,16 +25306,16 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="E137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -25212,7 +25335,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B138" s="18">
         <v>2026</v>
@@ -25221,36 +25344,36 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138">
-        <v>2124</v>
+        <v>0</v>
       </c>
       <c r="K138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138">
-        <v>2124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B139" s="18">
         <v>2026</v>
@@ -25259,19 +25382,19 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -25297,7 +25420,7 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -25306,22 +25429,22 @@
         <v>3</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H140">
         <v>1</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -25335,13 +25458,13 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -25373,36 +25496,36 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B143" s="18">
         <v>2026</v>
@@ -25411,19 +25534,19 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143">
         <v>1</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -25440,7 +25563,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B144" s="18">
         <v>2026</v>
@@ -25449,16 +25572,16 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E144">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -25487,7 +25610,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -25496,7 +25619,7 @@
         <v>1</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -25516,7 +25639,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B146" s="18">
         <v>2026</v>
@@ -25525,19 +25648,19 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E146">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F146">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -25554,7 +25677,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B147" s="18">
         <v>2026</v>
@@ -25563,13 +25686,13 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E147">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -25592,7 +25715,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B148" s="18">
         <v>2026</v>
@@ -25601,19 +25724,19 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>0</v>
       </c>
       <c r="H148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -25639,19 +25762,19 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E149">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F149">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G149">
         <v>0</v>
       </c>
       <c r="H149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -25677,19 +25800,19 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150">
         <v>0</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -25715,13 +25838,13 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -25744,7 +25867,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B152" s="18">
         <v>2026</v>
@@ -25753,19 +25876,19 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -25782,7 +25905,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B153" s="18">
         <v>2026</v>
@@ -25791,19 +25914,19 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E153">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F153">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -25820,7 +25943,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B154" s="18">
         <v>2026</v>
@@ -25829,13 +25952,13 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E154">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -25867,19 +25990,19 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -25896,7 +26019,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B156" s="18">
         <v>2026</v>
@@ -25905,16 +26028,16 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -25934,7 +26057,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B157" s="18">
         <v>2026</v>
@@ -25943,16 +26066,16 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E157">
+        <v>10</v>
+      </c>
+      <c r="F157">
+        <v>9</v>
+      </c>
+      <c r="G157">
         <v>3</v>
-      </c>
-      <c r="F157">
-        <v>3</v>
-      </c>
-      <c r="G157">
-        <v>0</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -25972,7 +26095,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B158" s="18">
         <v>2026</v>
@@ -25981,16 +26104,16 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -26010,7 +26133,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B159" s="18">
         <v>2026</v>
@@ -26019,7 +26142,7 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -26028,7 +26151,7 @@
         <v>1</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -26048,7 +26171,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B160" s="18">
         <v>2026</v>
@@ -26057,7 +26180,7 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -26066,7 +26189,7 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -26086,7 +26209,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B161" s="18">
         <v>2026</v>
@@ -26095,19 +26218,19 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E161">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -26124,7 +26247,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B162" s="18">
         <v>2026</v>
@@ -26133,36 +26256,36 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>5560</v>
+        <v>0</v>
       </c>
       <c r="K162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162">
-        <v>5560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B163" s="18">
         <v>2026</v>
@@ -26171,7 +26294,7 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -26180,10 +26303,10 @@
         <v>1</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -26200,7 +26323,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B164" s="18">
         <v>2026</v>
@@ -26209,16 +26332,16 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -26238,7 +26361,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B165" s="18">
         <v>2026</v>
@@ -26247,10 +26370,10 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F165">
         <v>2</v>
@@ -26259,7 +26382,7 @@
         <v>1</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26276,7 +26399,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B166" s="18">
         <v>2026</v>
@@ -26285,36 +26408,36 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E166">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F166">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G166">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J166">
-        <v>16511.68</v>
+        <v>0</v>
       </c>
       <c r="K166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L166">
-        <v>16511.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B167" s="18">
         <v>2026</v>
@@ -26323,7 +26446,7 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -26352,7 +26475,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B168" s="18">
         <v>2026</v>
@@ -26361,7 +26484,7 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -26370,7 +26493,7 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -26390,7 +26513,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B169" s="18">
         <v>2026</v>
@@ -26399,13 +26522,13 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -26428,7 +26551,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B170" s="18">
         <v>2026</v>
@@ -26437,30 +26560,350 @@
         <v>18</v>
       </c>
       <c r="D170" t="s">
+        <v>137</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>129</v>
+      </c>
+      <c r="D171" t="s">
+        <v>53</v>
+      </c>
+      <c r="E171">
+        <v>4</v>
+      </c>
+      <c r="F171">
+        <v>4</v>
+      </c>
+      <c r="G171">
+        <v>2</v>
+      </c>
+      <c r="H171">
+        <v>2</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>5560</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>5560</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>129</v>
+      </c>
+      <c r="D172" t="s">
+        <v>58</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>130</v>
+      </c>
+      <c r="D173" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>130</v>
+      </c>
+      <c r="D174" t="s">
+        <v>29</v>
+      </c>
+      <c r="E174">
+        <v>3</v>
+      </c>
+      <c r="F174">
+        <v>3</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>131</v>
+      </c>
+      <c r="D175" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175">
+        <v>2</v>
+      </c>
+      <c r="F175">
+        <v>2</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>131</v>
+      </c>
+      <c r="D176" t="s">
+        <v>60</v>
+      </c>
+      <c r="E176">
+        <v>9</v>
+      </c>
+      <c r="F176">
+        <v>9</v>
+      </c>
+      <c r="G176">
+        <v>6</v>
+      </c>
+      <c r="H176">
+        <v>2</v>
+      </c>
+      <c r="I176">
+        <v>3</v>
+      </c>
+      <c r="J176">
+        <v>17492.68</v>
+      </c>
+      <c r="K176">
+        <v>3</v>
+      </c>
+      <c r="L176">
+        <v>17492.68</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>132</v>
+      </c>
+      <c r="D177" t="s">
+        <v>137</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>132</v>
+      </c>
+      <c r="D178" t="s">
+        <v>52</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>132</v>
+      </c>
+      <c r="D179" t="s">
+        <v>55</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>132</v>
+      </c>
+      <c r="D180" t="s">
         <v>65</v>
       </c>
-      <c r="E170">
+      <c r="E180">
         <v>4</v>
       </c>
-      <c r="F170">
+      <c r="F180">
         <v>4</v>
       </c>
-      <c r="G170">
-        <v>1</v>
-      </c>
-      <c r="H170">
-        <v>0</v>
-      </c>
-      <c r="I170">
-        <v>0</v>
-      </c>
-      <c r="J170">
-        <v>0</v>
-      </c>
-      <c r="K170">
-        <v>0</v>
-      </c>
-      <c r="L170">
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD31E75-0C3E-4BF4-96D7-FAFCA433C9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DE9E8D-8BF5-4A62-904F-2ED5FBEF88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="139">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -430,12 +430,6 @@
     <t>One row per region-campaign per month. Add new rows each month, never edit old ones.</t>
   </si>
   <si>
-    <t>Pasadena Single Form CPA Decrease Pasadena</t>
-  </si>
-  <si>
-    <t>San Diego Single Form CPA Decrease San Diego</t>
-  </si>
-  <si>
     <t>Competitors – USA</t>
   </si>
   <si>
@@ -446,12 +440,6 @@
   </si>
   <si>
     <t>Competitors â€“ USA</t>
-  </si>
-  <si>
-    <t>Pasadena Single Form CPA Decrease - Pasadena 2</t>
-  </si>
-  <si>
-    <t>San Diego Single Form CPA Decrease San Diego 2</t>
   </si>
 </sst>
 </file>
@@ -1097,64 +1085,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>324.88</v>
+        <v>374.86</v>
       </c>
       <c r="C6" s="5">
-        <v>181.79</v>
+        <v>213.79</v>
       </c>
       <c r="D6" s="5">
-        <v>143.09</v>
+        <v>161.07</v>
       </c>
       <c r="E6" s="5">
-        <v>76566.75</v>
+        <v>88965.95</v>
       </c>
       <c r="F6" s="5">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G6" s="5">
+        <v>18</v>
+      </c>
+      <c r="H6" s="5">
+        <v>148</v>
+      </c>
+      <c r="I6" s="5">
+        <v>61</v>
+      </c>
+      <c r="J6" s="5">
         <v>11</v>
       </c>
-      <c r="H6" s="5">
-        <v>134</v>
-      </c>
-      <c r="I6" s="5">
-        <v>52</v>
-      </c>
-      <c r="J6" s="5">
-        <v>7</v>
-      </c>
       <c r="K6" s="5">
-        <v>528.04655172413698</v>
+        <v>535.93945783132494</v>
       </c>
       <c r="L6" s="5">
-        <v>1472.4375</v>
+        <v>1458.4581967213101</v>
       </c>
       <c r="M6" s="5">
-        <v>-46.022679557379597</v>
+        <v>-20.511386659727599</v>
       </c>
       <c r="N6" s="6">
-        <v>391.65</v>
+        <v>471.31</v>
       </c>
       <c r="O6" s="6">
-        <v>43963.48</v>
+        <v>51527.229999999901</v>
       </c>
       <c r="P6" s="6">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="Q6" s="6">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="R6" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S6" s="6">
-        <v>179.442775510204</v>
+        <v>180.16513986013899</v>
       </c>
       <c r="T6" s="6">
-        <v>862.029019607843</v>
+        <v>769.06313432835805</v>
       </c>
       <c r="U6" s="6">
-        <v>-16.261951965585901</v>
+        <v>23.095963047111201</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1169,7 +1157,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1181,7 +1169,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1189,64 +1177,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>65.010000000000005</v>
+        <v>74.489999999999995</v>
       </c>
       <c r="C7" s="5">
-        <v>34.75</v>
+        <v>37.25</v>
       </c>
       <c r="D7" s="5">
-        <v>30.26</v>
+        <v>37.24</v>
       </c>
       <c r="E7" s="5">
-        <v>2203.6999999999998</v>
+        <v>2728.23</v>
       </c>
       <c r="F7" s="5">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G7" s="5">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5">
+        <v>33</v>
+      </c>
+      <c r="I7" s="5">
+        <v>12</v>
+      </c>
+      <c r="J7" s="5">
         <v>2</v>
       </c>
-      <c r="H7" s="5">
-        <v>29</v>
-      </c>
-      <c r="I7" s="5">
-        <v>9</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
       <c r="K7" s="5">
-        <v>71.087096774193498</v>
+        <v>75.784166666666593</v>
       </c>
       <c r="L7" s="5">
-        <v>244.85555555555499</v>
+        <v>227.35249999999999</v>
       </c>
       <c r="M7" s="5">
-        <v>-3.6166447338566798</v>
+        <v>282.66568434479501</v>
       </c>
       <c r="N7" s="6">
-        <v>70.979999999999905</v>
+        <v>80.28</v>
       </c>
       <c r="O7" s="6">
-        <v>4263.82</v>
+        <v>4859.45</v>
       </c>
       <c r="P7" s="6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R7" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7" s="6">
-        <v>47.375777777777699</v>
+        <v>48.594499999999996</v>
       </c>
       <c r="T7" s="6">
-        <v>224.41157894736801</v>
+        <v>202.47708333333301</v>
       </c>
       <c r="U7" s="6">
-        <v>255.12756167005099</v>
+        <v>505.19194559055001</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1261,7 +1249,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1273,7 +1261,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1281,16 +1269,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5">
         <v>2</v>
       </c>
       <c r="E8" s="5">
-        <v>1923.82</v>
+        <v>2363.48</v>
       </c>
       <c r="F8" s="5">
         <v>2</v>
@@ -1302,15 +1290,17 @@
         <v>2</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>961.91</v>
-      </c>
-      <c r="L8" s="5"/>
+        <v>1181.74</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2363.48</v>
+      </c>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
@@ -1318,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>622.16</v>
+        <v>677.69</v>
       </c>
       <c r="P8" s="6">
         <v>3</v>
@@ -1330,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>207.386666666666</v>
+        <v>225.89666666666599</v>
       </c>
       <c r="T8" s="6">
-        <v>311.08</v>
+        <v>338.84500000000003</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1363,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1371,25 +1361,25 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5">
         <v>11</v>
       </c>
-      <c r="D9" s="5">
-        <v>9</v>
-      </c>
       <c r="E9" s="5">
-        <v>7965.62</v>
+        <v>9421.2199999999993</v>
       </c>
       <c r="F9" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" s="5">
         <v>4</v>
@@ -1398,37 +1388,37 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>796.56200000000001</v>
+        <v>785.10166666666601</v>
       </c>
       <c r="L9" s="5">
-        <v>1991.405</v>
+        <v>2355.3049999999998</v>
       </c>
       <c r="M9" s="5">
         <v>-100</v>
       </c>
       <c r="N9" s="6">
-        <v>6.84</v>
+        <v>8.84</v>
       </c>
       <c r="O9" s="6">
-        <v>1804.27</v>
+        <v>2137.77</v>
       </c>
       <c r="P9" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="6">
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>128.87642857142799</v>
+        <v>118.765</v>
       </c>
       <c r="T9" s="6">
-        <v>1804.27</v>
+        <v>1068.885</v>
       </c>
       <c r="U9" s="6">
-        <v>-1.23429420208726</v>
+        <v>-16.642108365259102</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1455,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1499,7 +1489,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1519,13 +1509,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>40.79</v>
+        <v>46.55</v>
       </c>
       <c r="O11" s="6">
-        <v>2037.08</v>
+        <v>2357.7800000000002</v>
       </c>
       <c r="P11" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="6">
         <v>2</v>
@@ -1534,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>407.416</v>
+        <v>392.96333333333303</v>
       </c>
       <c r="T11" s="6">
-        <v>1018.54</v>
+        <v>1178.8900000000001</v>
       </c>
       <c r="U11" s="6">
-        <v>270.23582775345102</v>
+        <v>219.877172594559</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1561,7 +1551,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1578,7 +1568,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="5">
-        <v>1438.92</v>
+        <v>1611.92</v>
       </c>
       <c r="F12" s="5">
         <v>4</v>
@@ -1596,19 +1586,19 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>359.73</v>
+        <v>402.98</v>
       </c>
       <c r="L12" s="5">
-        <v>1438.92</v>
+        <v>1611.92</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
       </c>
       <c r="N12" s="6">
-        <v>3.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="O12" s="6">
-        <v>434.74</v>
+        <v>558.27</v>
       </c>
       <c r="P12" s="6">
         <v>3</v>
@@ -1620,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>144.91333333333299</v>
+        <v>186.09</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6">
@@ -1651,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1695,7 +1685,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1718,7 +1708,7 @@
         <v>6.05</v>
       </c>
       <c r="O14" s="6">
-        <v>546.91</v>
+        <v>646.04</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1745,7 +1735,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1768,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>137.29</v>
+        <v>149.44999999999999</v>
       </c>
       <c r="P15" s="6">
         <v>1</v>
@@ -1780,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>137.29</v>
+        <v>149.44999999999999</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1809,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1817,25 +1807,25 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
       </c>
       <c r="D16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5">
-        <v>141.54</v>
+        <v>206.59</v>
       </c>
       <c r="F16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="5">
         <v>1</v>
@@ -1844,34 +1834,34 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>70.77</v>
+        <v>68.863333333333301</v>
       </c>
       <c r="L16" s="5">
-        <v>141.54</v>
+        <v>206.59</v>
       </c>
       <c r="M16" s="5">
         <v>-100</v>
       </c>
       <c r="N16" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O16" s="6">
-        <v>3020.86</v>
+        <v>3604.18</v>
       </c>
       <c r="P16" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>188.80375000000001</v>
+        <v>189.69368421052599</v>
       </c>
       <c r="T16" s="6">
-        <v>1510.43</v>
+        <v>901.04499999999996</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1901,7 +1891,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1921,13 +1911,13 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>22</v>
+        <v>34.67</v>
       </c>
       <c r="O17" s="6">
-        <v>2131.1</v>
+        <v>2443.11</v>
       </c>
       <c r="P17" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -1936,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>355.183333333333</v>
+        <v>305.38875000000002</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6">
@@ -1961,7 +1951,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1981,13 +1971,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>0.98</v>
+        <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>324.27</v>
+        <v>469.8</v>
       </c>
       <c r="P18" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -1996,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>162.13499999999999</v>
+        <v>156.6</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6">
@@ -2025,7 +2015,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2048,7 +2038,7 @@
         <v>3</v>
       </c>
       <c r="O19" s="6">
-        <v>429.91</v>
+        <v>615.72</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2075,7 +2065,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2098,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="O20" s="6">
-        <v>849.59</v>
+        <v>1023.67</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2125,7 +2115,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2133,16 +2123,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>25.99</v>
+        <v>28.99</v>
       </c>
       <c r="C21" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" s="5">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="E21" s="5">
-        <v>4783.37</v>
+        <v>4931.37</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2171,7 +2161,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2217,25 +2207,25 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" s="5">
         <v>8</v>
@@ -2267,7 +2257,7 @@
         <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2275,40 +2265,40 @@
         <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>32.96</v>
+        <v>42.95</v>
       </c>
       <c r="C24" s="5">
-        <v>30.96</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="D24" s="5">
         <v>2</v>
       </c>
       <c r="E24" s="5">
-        <v>7908.26</v>
+        <v>9254.59</v>
       </c>
       <c r="F24" s="5">
+        <v>5</v>
+      </c>
+      <c r="G24" s="5">
+        <v>4</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5">
         <v>2</v>
       </c>
-      <c r="G24" s="5">
-        <v>1</v>
-      </c>
-      <c r="H24" s="5">
-        <v>1</v>
-      </c>
-      <c r="I24" s="5">
-        <v>1</v>
-      </c>
       <c r="J24" s="5">
         <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>3954.13</v>
+        <v>1850.9179999999999</v>
       </c>
       <c r="L24" s="5">
-        <v>7908.26</v>
+        <v>4627.2950000000001</v>
       </c>
       <c r="M24" s="5">
-        <v>-2.7093191169739002</v>
+        <v>-16.862875610913001</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2333,7 +2323,7 @@
         <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2341,25 +2331,25 @@
         <v>41</v>
       </c>
       <c r="B25" s="5">
-        <v>5.67</v>
+        <v>7.67</v>
       </c>
       <c r="C25" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5">
         <v>5.67</v>
       </c>
       <c r="E25" s="5">
-        <v>1338.54</v>
+        <v>1612.91</v>
       </c>
       <c r="F25" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="5">
         <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="5">
         <v>1</v>
@@ -2368,19 +2358,19 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>334.63499999999999</v>
+        <v>322.58199999999999</v>
       </c>
       <c r="L25" s="5">
-        <v>1338.54</v>
+        <v>1612.91</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="6">
-        <v>632.55999999999995</v>
+        <v>713.24</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -2413,7 +2403,7 @@
         <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2430,7 +2420,7 @@
         <v>3.46</v>
       </c>
       <c r="E26" s="5">
-        <v>1276.8599999999999</v>
+        <v>1513.89</v>
       </c>
       <c r="F26" s="5">
         <v>3</v>
@@ -2448,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>425.62</v>
+        <v>504.63</v>
       </c>
       <c r="L26" s="5">
-        <v>1276.8599999999999</v>
+        <v>1513.89</v>
       </c>
       <c r="M26" s="5">
         <v>-100</v>
@@ -2460,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="O26" s="6">
-        <v>232.26</v>
+        <v>359.08</v>
       </c>
       <c r="P26" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -2472,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>77.42</v>
+        <v>89.77</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
@@ -2503,7 +2493,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2511,48 +2501,62 @@
         <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C27" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="5">
         <v>1.5</v>
       </c>
       <c r="E27" s="5">
-        <v>2442.3000000000002</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+        <v>2845.02</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
+        <v>2845.02</v>
+      </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="5">
+        <v>-100</v>
+      </c>
       <c r="N27" s="6">
-        <v>11.33</v>
+        <v>13.33</v>
       </c>
       <c r="O27" s="6">
-        <v>2279.4</v>
+        <v>2893.14</v>
       </c>
       <c r="P27" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R27" s="6">
         <v>1</v>
       </c>
       <c r="S27" s="6">
-        <v>325.62857142857098</v>
+        <v>361.64249999999998</v>
       </c>
       <c r="T27" s="6">
-        <v>569.85</v>
+        <v>578.62799999999902</v>
       </c>
       <c r="U27" s="6">
-        <v>106.721066947442</v>
+        <v>62.8680257436556</v>
       </c>
       <c r="V27" s="7">
         <v>66.569999999999993</v>
@@ -2579,7 +2583,7 @@
         <v>7</v>
       </c>
       <c r="AD27" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2599,13 +2603,13 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="6">
-        <v>9</v>
+        <v>11.67</v>
       </c>
       <c r="O28" s="6">
-        <v>714.06</v>
+        <v>840.01</v>
       </c>
       <c r="P28" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q28" s="6">
         <v>1</v>
@@ -2614,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>119.009999999999</v>
+        <v>105.00125</v>
       </c>
       <c r="T28" s="6">
-        <v>714.06</v>
+        <v>840.01</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
@@ -2641,7 +2645,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2649,64 +2653,64 @@
         <v>45</v>
       </c>
       <c r="B29" s="5">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="C29" s="5">
         <v>2</v>
       </c>
       <c r="D29" s="5">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="E29" s="5">
-        <v>2480.56</v>
+        <v>2923.57</v>
       </c>
       <c r="F29" s="5">
+        <v>9</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5">
         <v>8</v>
       </c>
-      <c r="G29" s="5">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5">
-        <v>7</v>
-      </c>
       <c r="I29" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="5">
-        <v>310.07</v>
+        <v>324.84111111111099</v>
       </c>
       <c r="L29" s="5">
-        <v>2480.56</v>
+        <v>1461.7850000000001</v>
       </c>
       <c r="M29" s="5">
-        <v>-100</v>
+        <v>75.094148592303199</v>
       </c>
       <c r="N29" s="6">
-        <v>9.58</v>
+        <v>11.58</v>
       </c>
       <c r="O29" s="6">
-        <v>1124.04</v>
+        <v>1367.6</v>
       </c>
       <c r="P29" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q29" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S29" s="6">
-        <v>160.57714285714201</v>
+        <v>151.95555555555501</v>
       </c>
       <c r="T29" s="6">
-        <v>281.01</v>
+        <v>273.52</v>
       </c>
       <c r="U29" s="6">
-        <v>579.349489342016</v>
+        <v>980.59081602807805</v>
       </c>
       <c r="V29" s="7">
         <v>55.58</v>
@@ -2721,7 +2725,7 @@
         <v>13</v>
       </c>
       <c r="Z29" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA29" s="8">
         <v>13000</v>
@@ -2733,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2756,7 +2760,7 @@
         <v>18.52</v>
       </c>
       <c r="O30" s="6">
-        <v>1391.3</v>
+        <v>1594.87</v>
       </c>
       <c r="P30" s="6">
         <v>7</v>
@@ -2768,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>198.75714285714199</v>
+        <v>227.83857142857099</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
@@ -2793,7 +2797,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2813,24 +2817,26 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="6">
-        <v>21.02</v>
+        <v>26.03</v>
       </c>
       <c r="O31" s="6">
-        <v>1619.31</v>
+        <v>1895.52</v>
       </c>
       <c r="P31" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q31" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="6">
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>539.77</v>
-      </c>
-      <c r="T31" s="6"/>
+        <v>473.88</v>
+      </c>
+      <c r="T31" s="6">
+        <v>1895.52</v>
+      </c>
       <c r="U31" s="6">
         <v>-100</v>
       </c>
@@ -2853,7 +2859,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2861,61 +2867,61 @@
         <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>19.440000000000001</v>
+        <v>23.44</v>
       </c>
       <c r="C32" s="5">
-        <v>11.94</v>
+        <v>13.94</v>
       </c>
       <c r="D32" s="5">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E32" s="5">
-        <v>5984.59</v>
+        <v>7019.08</v>
       </c>
       <c r="F32" s="5">
+        <v>11</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5">
         <v>10</v>
-      </c>
-      <c r="G32" s="5">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5">
-        <v>9</v>
       </c>
       <c r="I32" s="5">
         <v>3</v>
       </c>
       <c r="J32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="5">
-        <v>598.45899999999995</v>
+        <v>638.09818181818105</v>
       </c>
       <c r="L32" s="5">
-        <v>1994.86333333333</v>
+        <v>2339.69333333333</v>
       </c>
       <c r="M32" s="5">
-        <v>-100</v>
+        <v>18.477065370390399</v>
       </c>
       <c r="N32" s="6">
-        <v>9.8000000000000007</v>
+        <v>10.3</v>
       </c>
       <c r="O32" s="6">
-        <v>2244.6799999999998</v>
+        <v>2584.15</v>
       </c>
       <c r="P32" s="6">
         <v>10</v>
       </c>
       <c r="Q32" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32" s="6">
         <v>0</v>
       </c>
       <c r="S32" s="6">
-        <v>224.46799999999999</v>
+        <v>258.41500000000002</v>
       </c>
       <c r="T32" s="6">
-        <v>1122.3399999999999</v>
+        <v>861.38333333333298</v>
       </c>
       <c r="U32" s="6">
         <v>-100</v>
@@ -2945,7 +2951,7 @@
         <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2953,16 +2959,16 @@
         <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>20.68</v>
+        <v>22.69</v>
       </c>
       <c r="C33" s="5">
-        <v>5.96</v>
+        <v>6.97</v>
       </c>
       <c r="D33" s="5">
-        <v>14.72</v>
+        <v>15.72</v>
       </c>
       <c r="E33" s="5">
-        <v>6077.08</v>
+        <v>7014.42</v>
       </c>
       <c r="F33" s="5">
         <v>12</v>
@@ -2980,13 +2986,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="5">
-        <v>506.42333333333301</v>
+        <v>584.53499999999997</v>
       </c>
       <c r="L33" s="5">
-        <v>1519.27</v>
+        <v>1753.605</v>
       </c>
       <c r="M33" s="5">
-        <v>39.178684499792602</v>
+        <v>20.580176265464502</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3011,7 +3017,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3019,40 +3025,40 @@
         <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>22.85</v>
+        <v>25.85</v>
       </c>
       <c r="C34" s="5">
-        <v>9.85</v>
+        <v>10.85</v>
       </c>
       <c r="D34" s="5">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5">
+        <v>7841.68</v>
+      </c>
+      <c r="F34" s="5">
         <v>13</v>
       </c>
-      <c r="E34" s="5">
-        <v>6887.76</v>
-      </c>
-      <c r="F34" s="5">
-        <v>12</v>
-      </c>
       <c r="G34" s="5">
         <v>0</v>
       </c>
       <c r="H34" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="5">
         <v>1</v>
       </c>
       <c r="K34" s="5">
-        <v>573.98</v>
+        <v>603.20615384615303</v>
       </c>
       <c r="L34" s="5">
-        <v>1377.5519999999999</v>
+        <v>1306.9466666666599</v>
       </c>
       <c r="M34" s="5">
-        <v>-19.277094439992101</v>
+        <v>-29.0968261903061</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3077,7 +3083,7 @@
         <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3085,22 +3091,22 @@
         <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>19.82</v>
+        <v>24.32</v>
       </c>
       <c r="C35" s="5">
-        <v>15.99</v>
+        <v>20.49</v>
       </c>
       <c r="D35" s="5">
         <v>3.83</v>
       </c>
       <c r="E35" s="5">
-        <v>5320.85</v>
+        <v>6272.81</v>
       </c>
       <c r="F35" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="5">
         <v>5</v>
@@ -3112,34 +3118,34 @@
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>665.10625000000005</v>
+        <v>696.97888888888895</v>
       </c>
       <c r="L35" s="5">
-        <v>2660.4250000000002</v>
+        <v>3136.4050000000002</v>
       </c>
       <c r="M35" s="5">
         <v>-100</v>
       </c>
       <c r="N35" s="6">
-        <v>12.05</v>
+        <v>16.05</v>
       </c>
       <c r="O35" s="6">
-        <v>4966.0200000000004</v>
+        <v>5726.9</v>
       </c>
       <c r="P35" s="6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" s="6">
         <v>0</v>
       </c>
       <c r="S35" s="6">
-        <v>292.11882352941097</v>
+        <v>248.99565217391299</v>
       </c>
       <c r="T35" s="6">
-        <v>993.20399999999995</v>
+        <v>954.48333333333301</v>
       </c>
       <c r="U35" s="6">
         <v>-100</v>
@@ -3169,25 +3175,17 @@
         <v>14</v>
       </c>
       <c r="AD35" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="5">
-        <v>3</v>
-      </c>
-      <c r="C36" s="5">
-        <v>3</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5">
-        <v>304.11</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3196,50 +3194,90 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
+      <c r="N36" s="6">
+        <v>50.73</v>
+      </c>
+      <c r="O36" s="6">
+        <v>1677.96</v>
+      </c>
+      <c r="P36" s="6">
+        <v>7</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>239.70857142857099</v>
+      </c>
       <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
+      <c r="U36" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V36" s="7">
+        <v>250.18</v>
+      </c>
+      <c r="W36" s="7">
+        <v>7865.5</v>
+      </c>
+      <c r="X36" s="7">
+        <v>18</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7">
+        <v>0</v>
+      </c>
       <c r="AA36" s="8"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" s="5">
+        <v>3</v>
+      </c>
+      <c r="D37" s="5">
+        <v>3</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1787.66</v>
+      </c>
+      <c r="F37" s="5">
         <v>2</v>
       </c>
-      <c r="D37" s="5">
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
         <v>2</v>
       </c>
-      <c r="E37" s="5">
-        <v>1458.13</v>
-      </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="I37" s="5">
+        <v>1</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>893.83</v>
+      </c>
+      <c r="L37" s="5">
+        <v>1787.66</v>
+      </c>
+      <c r="M37" s="5">
+        <v>-100</v>
+      </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -3253,437 +3291,524 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
-      <c r="AA37" s="8"/>
-      <c r="AB37" s="9"/>
-      <c r="AC37" s="9"/>
+      <c r="AA37" s="8">
+        <v>7500</v>
+      </c>
+      <c r="AB37" s="9">
+        <v>16</v>
+      </c>
+      <c r="AC37" s="9">
+        <v>7</v>
+      </c>
       <c r="AD37" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B38" s="5">
+        <v>19.98</v>
+      </c>
+      <c r="C38" s="5">
+        <v>15.48</v>
+      </c>
+      <c r="D38" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4510.46</v>
+      </c>
+      <c r="F38" s="5">
+        <v>3</v>
+      </c>
+      <c r="G38" s="5">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5">
+        <v>3</v>
+      </c>
+      <c r="I38" s="5">
+        <v>2</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>1503.4866666666601</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2255.23</v>
+      </c>
+      <c r="M38" s="5">
+        <v>-100</v>
+      </c>
       <c r="N38" s="6">
-        <v>39.82</v>
+        <v>5.5</v>
       </c>
       <c r="O38" s="6">
-        <v>1408.19</v>
+        <v>2521.15</v>
       </c>
       <c r="P38" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q38" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="6">
-        <v>201.17</v>
-      </c>
-      <c r="T38" s="6"/>
+        <v>210.09583333333299</v>
+      </c>
+      <c r="T38" s="6">
+        <v>504.23</v>
+      </c>
       <c r="U38" s="6">
         <v>-100</v>
       </c>
       <c r="V38" s="7">
-        <v>250.18</v>
+        <v>42.5</v>
       </c>
       <c r="W38" s="7">
-        <v>7865.5</v>
+        <v>12015.14</v>
       </c>
       <c r="X38" s="7">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="Y38" s="7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z38" s="7">
         <v>0</v>
       </c>
-      <c r="AA38" s="8"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
+      <c r="AA38" s="8">
+        <v>17000</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>27</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>16</v>
+      </c>
       <c r="AD38" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="5">
-        <v>5</v>
-      </c>
-      <c r="C39" s="5">
+        <v>59</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6">
+        <v>20</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1343.35</v>
+      </c>
+      <c r="P39" s="6">
         <v>2</v>
       </c>
-      <c r="D39" s="5">
+      <c r="Q39" s="6">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6">
+        <v>671.67499999999995</v>
+      </c>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V39" s="7">
+        <v>97.34</v>
+      </c>
+      <c r="W39" s="7">
+        <v>5964.35</v>
+      </c>
+      <c r="X39" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y39" s="7">
         <v>3</v>
       </c>
-      <c r="E39" s="5">
-        <v>1557.88</v>
-      </c>
-      <c r="F39" s="5">
-        <v>2</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5">
-        <v>2</v>
-      </c>
-      <c r="I39" s="5">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>778.94</v>
-      </c>
-      <c r="L39" s="5">
-        <v>1557.88</v>
-      </c>
-      <c r="M39" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="8">
-        <v>7500</v>
-      </c>
-      <c r="AB39" s="9">
-        <v>16</v>
-      </c>
-      <c r="AC39" s="9">
-        <v>7</v>
-      </c>
+      <c r="Z39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>17.98</v>
+        <v>5.67</v>
       </c>
       <c r="C40" s="5">
-        <v>14.48</v>
+        <v>3.67</v>
       </c>
       <c r="D40" s="5">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5">
-        <v>3953.27</v>
-      </c>
-      <c r="F40" s="5">
-        <v>2</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5">
-        <v>2</v>
-      </c>
-      <c r="I40" s="5">
-        <v>1</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5">
-        <v>1976.635</v>
-      </c>
-      <c r="L40" s="5">
-        <v>3953.27</v>
-      </c>
-      <c r="M40" s="5">
-        <v>-100</v>
-      </c>
+        <v>4141.84</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
       <c r="N40" s="6">
-        <v>2</v>
+        <v>0.98</v>
       </c>
       <c r="O40" s="6">
-        <v>2123.86</v>
-      </c>
-      <c r="P40" s="6">
-        <v>8</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>4</v>
-      </c>
-      <c r="R40" s="6">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6">
-        <v>265.48250000000002</v>
-      </c>
-      <c r="T40" s="6">
-        <v>530.96500000000003</v>
-      </c>
-      <c r="U40" s="6">
-        <v>-100</v>
-      </c>
+        <v>243.69</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
       <c r="V40" s="7">
-        <v>42.5</v>
+        <v>3.01</v>
       </c>
       <c r="W40" s="7">
-        <v>12015.14</v>
-      </c>
-      <c r="X40" s="7">
-        <v>56</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>24</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>0</v>
-      </c>
+        <v>1758.25</v>
+      </c>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
       <c r="AA40" s="8">
         <v>17000</v>
       </c>
-      <c r="AB40" s="9">
-        <v>27</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>16</v>
-      </c>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="B41">
+        <v>13.87</v>
+      </c>
+      <c r="C41">
+        <v>5.87</v>
+      </c>
+      <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>4161.45</v>
+      </c>
+      <c r="F41">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>11</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41">
+        <v>297.246428571428</v>
+      </c>
+      <c r="L41">
+        <v>520.18124999999998</v>
+      </c>
+      <c r="M41">
+        <v>503.89527688666197</v>
       </c>
       <c r="N41">
+        <v>13.02</v>
+      </c>
+      <c r="O41">
+        <v>1947.61</v>
+      </c>
+      <c r="P41">
         <v>13</v>
       </c>
-      <c r="O41">
-        <v>1132.8399999999999</v>
-      </c>
-      <c r="P41">
-        <v>1</v>
-      </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41">
-        <v>1132.8399999999999</v>
+        <v>149.81615384615299</v>
+      </c>
+      <c r="T41">
+        <v>649.20333333333303</v>
       </c>
       <c r="U41">
-        <v>-100</v>
+        <v>167.23933436365499</v>
       </c>
       <c r="V41">
-        <v>97.34</v>
+        <v>52.03</v>
       </c>
       <c r="W41">
-        <v>5964.35</v>
+        <v>10931.15</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="Y41">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA41">
+        <v>24000</v>
+      </c>
+      <c r="AB41">
+        <v>29</v>
+      </c>
+      <c r="AC41">
+        <v>12</v>
       </c>
       <c r="AD41" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42">
-        <v>5.67</v>
-      </c>
-      <c r="C42">
-        <v>3.67</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42">
-        <v>3534.56</v>
+        <v>61</v>
       </c>
       <c r="N42">
-        <v>0.98</v>
+        <v>26.51</v>
       </c>
       <c r="O42">
-        <v>188.6</v>
+        <v>1825.75</v>
+      </c>
+      <c r="P42">
+        <v>6</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>304.291666666666</v>
+      </c>
+      <c r="U42">
+        <v>-100</v>
       </c>
       <c r="V42">
-        <v>3.01</v>
+        <v>127.59</v>
       </c>
       <c r="W42">
-        <v>1758.25</v>
-      </c>
-      <c r="AA42">
-        <v>17000</v>
+        <v>8783.7999999999993</v>
+      </c>
+      <c r="X42">
+        <v>27</v>
+      </c>
+      <c r="Y42">
+        <v>4</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
       </c>
       <c r="AD42" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B43">
-        <v>12.87</v>
+        <v>10.66</v>
       </c>
       <c r="C43">
-        <v>4.87</v>
+        <v>5.99</v>
       </c>
       <c r="D43">
+        <v>4.67</v>
+      </c>
+      <c r="E43">
+        <v>2674.19</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>668.54750000000001</v>
+      </c>
+      <c r="L43">
+        <v>2674.19</v>
+      </c>
+      <c r="M43">
+        <v>-100</v>
+      </c>
+      <c r="N43">
+        <v>6.0299999999999896</v>
+      </c>
+      <c r="O43">
+        <v>1058.1199999999999</v>
+      </c>
+      <c r="P43">
         <v>8</v>
       </c>
-      <c r="E43">
-        <v>3495.82</v>
-      </c>
-      <c r="F43">
-        <v>13</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-      <c r="H43">
-        <v>11</v>
-      </c>
-      <c r="I43">
-        <v>7</v>
-      </c>
-      <c r="J43">
+      <c r="Q43">
         <v>3</v>
       </c>
-      <c r="K43">
-        <v>268.90923076923002</v>
-      </c>
-      <c r="L43">
-        <v>499.40285714285699</v>
-      </c>
-      <c r="M43">
-        <v>400.38846393693001</v>
-      </c>
-      <c r="N43">
-        <v>11.02</v>
-      </c>
-      <c r="O43">
-        <v>1583.4</v>
-      </c>
-      <c r="P43">
-        <v>12</v>
-      </c>
-      <c r="Q43">
-        <v>2</v>
-      </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>131.94999999999999</v>
+        <v>132.26499999999999</v>
       </c>
       <c r="T43">
-        <v>791.7</v>
+        <v>352.70666666666602</v>
       </c>
       <c r="U43">
         <v>-100</v>
       </c>
       <c r="V43">
-        <v>52.03</v>
+        <v>23.02</v>
       </c>
       <c r="W43">
-        <v>10931.15</v>
+        <v>4636.55</v>
       </c>
       <c r="X43">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Y43">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z43">
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>24000</v>
+        <v>11000</v>
       </c>
       <c r="AB43">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AC43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AD43" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>136</v>
-      </c>
-      <c r="B44">
-        <v>2</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>1104.46</v>
+        <v>66</v>
+      </c>
+      <c r="N44">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="O44">
+        <v>1058.29</v>
+      </c>
+      <c r="P44">
+        <v>4</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>264.57249999999999</v>
+      </c>
+      <c r="T44">
+        <v>1058.29</v>
+      </c>
+      <c r="U44">
+        <v>-100</v>
+      </c>
+      <c r="V44">
+        <v>56.01</v>
+      </c>
+      <c r="W44">
+        <v>4863.79</v>
+      </c>
+      <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>4</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
       </c>
       <c r="AD44" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>142</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>205.16</v>
+        <v>137</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
@@ -3862,7 +3987,7 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -4770,16 +4895,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E21" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F21" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
@@ -4794,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>8.9700000000000006</v>
+        <v>11.45</v>
       </c>
       <c r="M21" s="10">
         <v>0</v>
       </c>
       <c r="N21" s="10">
-        <v>46.15</v>
+        <v>42.11</v>
       </c>
       <c r="O21" s="10">
         <v>0</v>
@@ -4844,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.69</v>
+        <v>0.6</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -4870,10 +4995,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" s="10">
         <v>8</v>
@@ -4882,31 +5007,31 @@
         <v>5</v>
       </c>
       <c r="H23" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="10">
-        <v>7694</v>
+        <v>12813</v>
       </c>
       <c r="J23" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="10">
-        <v>7694</v>
+        <v>12813</v>
       </c>
       <c r="L23" s="10">
-        <v>9.66</v>
+        <v>9.64</v>
       </c>
       <c r="M23" s="10">
-        <v>18.62</v>
+        <v>18.12</v>
       </c>
       <c r="N23" s="10">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="O23" s="10">
+        <v>25</v>
+      </c>
+      <c r="P23" s="10">
         <v>12.5</v>
-      </c>
-      <c r="P23" s="10">
-        <v>7.14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -4944,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>0.69</v>
+        <v>0.6</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4992,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -5018,13 +5143,13 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
+        <v>9</v>
+      </c>
+      <c r="E26" s="10">
         <v>8</v>
       </c>
-      <c r="E26" s="10">
-        <v>7</v>
-      </c>
       <c r="F26" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="10">
         <v>0</v>
@@ -5042,13 +5167,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -5068,43 +5193,43 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="10">
         <v>8</v>
       </c>
       <c r="G27" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="10">
-        <v>10582</v>
+        <v>18898</v>
       </c>
       <c r="J27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="10">
-        <v>10582</v>
+        <v>18898</v>
       </c>
       <c r="L27" s="10">
-        <v>10.34</v>
+        <v>9.64</v>
       </c>
       <c r="M27" s="10">
-        <v>25.6</v>
+        <v>26.72</v>
       </c>
       <c r="N27" s="10">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="O27" s="10">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="P27" s="10">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5118,13 +5243,13 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>9</v>
+      </c>
+      <c r="E28" s="10">
         <v>8</v>
       </c>
-      <c r="E28" s="10">
-        <v>7</v>
-      </c>
       <c r="F28" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="10">
         <v>1</v>
@@ -5142,13 +5267,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -5168,16 +5293,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" s="10">
         <v>0</v>
       </c>
       <c r="G29" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" s="10">
         <v>0</v>
@@ -5192,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>11.72</v>
+        <v>11.45</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -5216,43 +5341,43 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
+        <v>22</v>
+      </c>
+      <c r="E30" s="10">
         <v>20</v>
-      </c>
-      <c r="E30" s="10">
-        <v>18</v>
       </c>
       <c r="F30" s="10">
         <v>6</v>
       </c>
       <c r="G30" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="10">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="J30" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="10">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="L30" s="10">
-        <v>13.79</v>
+        <v>13.25</v>
       </c>
       <c r="M30" s="10">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="N30" s="10">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="O30" s="10">
-        <v>0</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P30" s="10">
-        <v>0</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5266,16 +5391,16 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E31" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F31" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
@@ -5290,13 +5415,13 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>10.34</v>
+        <v>9.64</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
       </c>
       <c r="N31" s="10">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="O31" s="10">
         <v>0</v>
@@ -5316,13 +5441,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F32" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" s="10">
         <v>4</v>
@@ -5340,19 +5465,19 @@
         <v>5560</v>
       </c>
       <c r="L32" s="10">
-        <v>5.52</v>
+        <v>6.02</v>
       </c>
       <c r="M32" s="10">
-        <v>13.45</v>
+        <v>7.86</v>
       </c>
       <c r="N32" s="10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O32" s="10">
-        <v>25</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P32" s="10">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5366,10 +5491,10 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="10">
         <v>1</v>
@@ -5390,13 +5515,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
@@ -5416,43 +5541,43 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E34" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F34" s="10">
         <v>7</v>
       </c>
       <c r="G34" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="10">
-        <v>17492.68</v>
+        <v>25130.799999999999</v>
       </c>
       <c r="J34" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="10">
-        <v>17492.68</v>
+        <v>25130.799999999999</v>
       </c>
       <c r="L34" s="10">
-        <v>7.59</v>
+        <v>7.83</v>
       </c>
       <c r="M34" s="10">
-        <v>42.33</v>
+        <v>35.54</v>
       </c>
       <c r="N34" s="10">
-        <v>63.64</v>
+        <v>53.85</v>
       </c>
       <c r="O34" s="10">
-        <v>42.86</v>
+        <v>57.14</v>
       </c>
       <c r="P34" s="10">
-        <v>27.27</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5490,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>5.52</v>
+        <v>4.82</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -5935,7 +6060,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -6075,19 +6200,19 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H19" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J19" s="5">
-        <v>372006.09</v>
+        <v>379800.09</v>
       </c>
       <c r="K19" s="5">
-        <v>36.51</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -6116,13 +6241,13 @@
         <v>76</v>
       </c>
       <c r="I20" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J20" s="10">
-        <v>227784.52</v>
+        <v>240258.52</v>
       </c>
       <c r="K20" s="10">
-        <v>24.94</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -6136,28 +6261,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>836</v>
+        <v>1002</v>
       </c>
       <c r="E21" s="10">
-        <v>2203.6999999999998</v>
+        <v>2728.23</v>
       </c>
       <c r="F21" s="10">
-        <v>65.010000000000005</v>
+        <v>74.489999999999995</v>
       </c>
       <c r="G21" s="10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H21" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I21" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="10">
-        <v>2124</v>
+        <v>10440</v>
       </c>
       <c r="K21" s="10">
-        <v>-0.04</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6460,7 +6585,7 @@
         <v>14.33</v>
       </c>
       <c r="G30" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" s="10">
         <v>7</v>
@@ -6731,19 +6856,19 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E38" s="10">
-        <v>1923.82</v>
+        <v>2363.48</v>
       </c>
       <c r="F38" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="10">
         <v>2</v>
       </c>
       <c r="H38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="10">
         <v>0</v>
@@ -7306,13 +7431,13 @@
         <v>21</v>
       </c>
       <c r="I54" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54" s="10">
-        <v>43541.29</v>
+        <v>52815.29</v>
       </c>
       <c r="K54" s="10">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -7326,16 +7451,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>667</v>
+        <v>758</v>
       </c>
       <c r="E55" s="10">
-        <v>7965.62</v>
+        <v>9421.2199999999993</v>
       </c>
       <c r="F55" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G55" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H55" s="10">
         <v>4</v>
@@ -8086,10 +8211,10 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E77" s="10">
-        <v>1438.92</v>
+        <v>1611.92</v>
       </c>
       <c r="F77" s="10">
         <v>4.33</v>
@@ -8841,10 +8966,10 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="E100" s="10">
-        <v>3534.56</v>
+        <v>4141.84</v>
       </c>
       <c r="F100" s="10">
         <v>5.67</v>
@@ -9755,10 +9880,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H127" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -9956,16 +10081,16 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E133" s="10">
-        <v>141.54</v>
+        <v>206.59</v>
       </c>
       <c r="F133" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H133" s="10">
         <v>1</v>
@@ -11519,7 +11644,7 @@
         <v>65.849999999999994</v>
       </c>
       <c r="G179" s="10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H179" s="10">
         <v>15</v>
@@ -11791,16 +11916,16 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="E187" s="10">
-        <v>4783.37</v>
+        <v>4931.37</v>
       </c>
       <c r="F187" s="10">
-        <v>25.99</v>
+        <v>28.99</v>
       </c>
       <c r="G187" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H187" s="10">
         <v>8</v>
@@ -11936,19 +12061,19 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>17667</v>
+        <v>20803</v>
       </c>
       <c r="E192" s="10">
-        <v>7908.26</v>
+        <v>9254.59</v>
       </c>
       <c r="F192" s="10">
-        <v>32.96</v>
+        <v>42.95</v>
       </c>
       <c r="G192" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H192" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I192" s="10">
         <v>1</v>
@@ -11957,7 +12082,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.03</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12521,16 +12646,16 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E209" s="10">
-        <v>1338.54</v>
+        <v>1612.91</v>
       </c>
       <c r="F209" s="10">
-        <v>5.67</v>
+        <v>7.67</v>
       </c>
       <c r="G209" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H209" s="10">
         <v>1</v>
@@ -13116,10 +13241,10 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E226" s="10">
-        <v>1276.8599999999999</v>
+        <v>1513.89</v>
       </c>
       <c r="F226" s="10">
         <v>3.46</v>
@@ -13711,19 +13836,29 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="E243" s="10">
-        <v>2442.3000000000002</v>
+        <v>2845.02</v>
       </c>
       <c r="F243" s="10">
-        <v>5.5</v>
-      </c>
-      <c r="G243" s="10"/>
-      <c r="H243" s="10"/>
-      <c r="I243" s="10"/>
-      <c r="J243" s="10"/>
-      <c r="K243" s="10"/>
+        <v>6.5</v>
+      </c>
+      <c r="G243" s="10">
+        <v>1</v>
+      </c>
+      <c r="H243" s="10">
+        <v>0</v>
+      </c>
+      <c r="I243" s="10">
+        <v>0</v>
+      </c>
+      <c r="J243" s="10">
+        <v>0</v>
+      </c>
+      <c r="K243" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="10" t="s">
@@ -14483,7 +14618,7 @@
         <v>29</v>
       </c>
       <c r="H265" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I265" s="10">
         <v>2</v>
@@ -14506,28 +14641,28 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="E266" s="10">
-        <v>2480.56</v>
+        <v>2923.57</v>
       </c>
       <c r="F266" s="10">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="G266" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H266" s="10">
         <v>1</v>
       </c>
       <c r="I266" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J266" s="10">
-        <v>0</v>
+        <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>-1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15755,10 +15890,10 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H304" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I304" s="10">
         <v>5</v>
@@ -15781,28 +15916,28 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>490</v>
+        <v>572</v>
       </c>
       <c r="E305" s="10">
-        <v>5984.59</v>
+        <v>7019.08</v>
       </c>
       <c r="F305" s="10">
-        <v>19.439999999999898</v>
+        <v>23.439999999999898</v>
       </c>
       <c r="G305" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H305" s="10">
         <v>3</v>
       </c>
       <c r="I305" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305" s="10">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K305" s="10">
-        <v>-1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16051,13 +16186,13 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>1124</v>
+        <v>1260</v>
       </c>
       <c r="E313" s="10">
-        <v>6077.08</v>
+        <v>7014.42</v>
       </c>
       <c r="F313" s="10">
-        <v>20.68</v>
+        <v>22.69</v>
       </c>
       <c r="G313" s="10">
         <v>12</v>
@@ -16072,7 +16207,7 @@
         <v>8458</v>
       </c>
       <c r="K313" s="10">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16308,16 +16443,16 @@
         <v>86</v>
       </c>
       <c r="H320" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I320" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J320" s="10">
-        <v>22091</v>
+        <v>38519</v>
       </c>
       <c r="K320" s="10">
-        <v>-0.27</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
@@ -16331,19 +16466,19 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>1832</v>
+        <v>1983</v>
       </c>
       <c r="E321" s="10">
-        <v>6887.76</v>
+        <v>7841.68</v>
       </c>
       <c r="F321" s="10">
-        <v>22.85</v>
+        <v>25.85</v>
       </c>
       <c r="G321" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H321" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I321" s="10">
         <v>1</v>
@@ -16352,7 +16487,7 @@
         <v>5560</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.19</v>
+        <v>-0.28999999999999998</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16951,16 +17086,16 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>454</v>
+        <v>528</v>
       </c>
       <c r="E339" s="10">
-        <v>5320.85</v>
+        <v>6272.81</v>
       </c>
       <c r="F339" s="10">
-        <v>19.82</v>
+        <v>24.32</v>
       </c>
       <c r="G339" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H339" s="10">
         <v>1</v>
@@ -16977,53 +17112,73 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="B340" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C340" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D340" s="10">
-        <v>25</v>
+        <v>2604</v>
       </c>
       <c r="E340" s="10">
-        <v>304.11</v>
+        <v>3023.13</v>
       </c>
       <c r="F340" s="10">
-        <v>3</v>
-      </c>
-      <c r="G340" s="10"/>
-      <c r="H340" s="10"/>
-      <c r="I340" s="10"/>
-      <c r="J340" s="10"/>
-      <c r="K340" s="10"/>
+        <v>46.9</v>
+      </c>
+      <c r="G340" s="10">
+        <v>9</v>
+      </c>
+      <c r="H340" s="10">
+        <v>2</v>
+      </c>
+      <c r="I340" s="10">
+        <v>0</v>
+      </c>
+      <c r="J340" s="10">
+        <v>0</v>
+      </c>
+      <c r="K340" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="B341" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C341" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D341" s="10">
-        <v>136</v>
+        <v>9763</v>
       </c>
       <c r="E341" s="10">
-        <v>1458.13</v>
+        <v>7865.5</v>
       </c>
       <c r="F341" s="10">
-        <v>4</v>
-      </c>
-      <c r="G341" s="10"/>
-      <c r="H341" s="10"/>
-      <c r="I341" s="10"/>
-      <c r="J341" s="10"/>
-      <c r="K341" s="10"/>
+        <v>250.18</v>
+      </c>
+      <c r="G341" s="10">
+        <v>19</v>
+      </c>
+      <c r="H341" s="10">
+        <v>0</v>
+      </c>
+      <c r="I341" s="10">
+        <v>0</v>
+      </c>
+      <c r="J341" s="10">
+        <v>0</v>
+      </c>
+      <c r="K341" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
@@ -17033,31 +17188,31 @@
         <v>2025</v>
       </c>
       <c r="C342" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D342" s="10">
+        <v>7820</v>
+      </c>
+      <c r="E342" s="10">
+        <v>5484.57</v>
+      </c>
+      <c r="F342" s="10">
+        <v>168.25</v>
+      </c>
+      <c r="G342" s="10">
         <v>17</v>
       </c>
-      <c r="D342" s="10">
-        <v>2604</v>
-      </c>
-      <c r="E342" s="10">
-        <v>3023.13</v>
-      </c>
-      <c r="F342" s="10">
-        <v>46.9</v>
-      </c>
-      <c r="G342" s="10">
-        <v>9</v>
-      </c>
       <c r="H342" s="10">
+        <v>5</v>
+      </c>
+      <c r="I342" s="10">
         <v>2</v>
       </c>
-      <c r="I342" s="10">
-        <v>0</v>
-      </c>
       <c r="J342" s="10">
-        <v>0</v>
+        <v>14334.7</v>
       </c>
       <c r="K342" s="10">
-        <v>-1</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.3">
@@ -17068,31 +17223,31 @@
         <v>2025</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D343" s="10">
-        <v>9763</v>
+        <v>5809</v>
       </c>
       <c r="E343" s="10">
-        <v>7865.5</v>
+        <v>7919.47</v>
       </c>
       <c r="F343" s="10">
-        <v>250.18</v>
+        <v>58.83</v>
       </c>
       <c r="G343" s="10">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H343" s="10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I343" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J343" s="10">
-        <v>0</v>
+        <v>44163</v>
       </c>
       <c r="K343" s="10">
-        <v>-1</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
@@ -17103,31 +17258,31 @@
         <v>2025</v>
       </c>
       <c r="C344" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D344" s="10">
-        <v>7820</v>
+        <v>3271</v>
       </c>
       <c r="E344" s="10">
-        <v>5484.57</v>
+        <v>7851.36</v>
       </c>
       <c r="F344" s="10">
-        <v>168.25</v>
+        <v>33.46</v>
       </c>
       <c r="G344" s="10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H344" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I344" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J344" s="10">
-        <v>14334.7</v>
+        <v>6792</v>
       </c>
       <c r="K344" s="10">
-        <v>1.61</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.3">
@@ -17138,31 +17293,31 @@
         <v>2025</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D345" s="10">
-        <v>5809</v>
+        <v>3463</v>
       </c>
       <c r="E345" s="10">
-        <v>7919.47</v>
+        <v>7226.69</v>
       </c>
       <c r="F345" s="10">
-        <v>58.83</v>
+        <v>31.99</v>
       </c>
       <c r="G345" s="10">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H345" s="10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I345" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J345" s="10">
-        <v>44163</v>
+        <v>8166.99999999999</v>
       </c>
       <c r="K345" s="10">
-        <v>4.58</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
@@ -17173,101 +17328,91 @@
         <v>2025</v>
       </c>
       <c r="C346" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D346" s="10">
+        <v>90</v>
+      </c>
+      <c r="E346" s="10">
+        <v>182.43</v>
+      </c>
+      <c r="F346" s="10">
+        <v>0</v>
+      </c>
+      <c r="G346" s="10">
+        <v>51</v>
+      </c>
+      <c r="H346" s="10">
         <v>21</v>
       </c>
-      <c r="D346" s="10">
-        <v>3271</v>
-      </c>
-      <c r="E346" s="10">
-        <v>7851.36</v>
-      </c>
-      <c r="F346" s="10">
-        <v>33.46</v>
-      </c>
-      <c r="G346" s="10">
-        <v>24</v>
-      </c>
-      <c r="H346" s="10">
-        <v>8</v>
-      </c>
       <c r="I346" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J346" s="10">
-        <v>6792</v>
+        <v>33153.71</v>
       </c>
       <c r="K346" s="10">
-        <v>-0.13</v>
+        <v>180.73</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B347" s="10">
         <v>2025</v>
       </c>
       <c r="C347" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D347" s="10">
-        <v>3463</v>
+        <v>285</v>
       </c>
       <c r="E347" s="10">
-        <v>7226.69</v>
+        <v>3317.91</v>
       </c>
       <c r="F347" s="10">
-        <v>31.99</v>
-      </c>
-      <c r="G347" s="10">
-        <v>10</v>
-      </c>
-      <c r="H347" s="10">
-        <v>3</v>
-      </c>
-      <c r="I347" s="10">
-        <v>1</v>
-      </c>
-      <c r="J347" s="10">
-        <v>8166.99999999999</v>
-      </c>
-      <c r="K347" s="10">
-        <v>0.13</v>
-      </c>
+        <v>17.61</v>
+      </c>
+      <c r="G347" s="10"/>
+      <c r="H347" s="10"/>
+      <c r="I347" s="10"/>
+      <c r="J347" s="10"/>
+      <c r="K347" s="10"/>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B348" s="10">
         <v>2025</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D348" s="10">
-        <v>90</v>
+        <v>539</v>
       </c>
       <c r="E348" s="10">
-        <v>182.43</v>
+        <v>5046.47</v>
       </c>
       <c r="F348" s="10">
-        <v>0</v>
+        <v>51.03</v>
       </c>
       <c r="G348" s="10">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H348" s="10">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I348" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J348" s="10">
-        <v>33153.71</v>
+        <v>7648.97</v>
       </c>
       <c r="K348" s="10">
-        <v>180.73</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
@@ -17275,59 +17420,69 @@
         <v>57</v>
       </c>
       <c r="B349" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C349" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D349" s="10">
+        <v>546</v>
+      </c>
+      <c r="E349" s="10">
+        <v>5077.71</v>
+      </c>
+      <c r="F349" s="10">
+        <v>43.269999999999897</v>
+      </c>
+      <c r="G349" s="10">
         <v>24</v>
       </c>
-      <c r="D349" s="10">
-        <v>285</v>
-      </c>
-      <c r="E349" s="10">
-        <v>3317.91</v>
-      </c>
-      <c r="F349" s="10">
-        <v>17.61</v>
-      </c>
-      <c r="G349" s="10"/>
-      <c r="H349" s="10"/>
-      <c r="I349" s="10"/>
-      <c r="J349" s="10"/>
-      <c r="K349" s="10"/>
+      <c r="H349" s="10">
+        <v>8</v>
+      </c>
+      <c r="I349" s="10">
+        <v>5</v>
+      </c>
+      <c r="J349" s="10">
+        <v>35885.199999999997</v>
+      </c>
+      <c r="K349" s="10">
+        <v>6.07</v>
+      </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B350" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D350" s="10">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="E350" s="10">
-        <v>5046.47</v>
+        <v>5048.16</v>
       </c>
       <c r="F350" s="10">
-        <v>51.03</v>
+        <v>40.269999999999897</v>
       </c>
       <c r="G350" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H350" s="10">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I350" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J350" s="10">
-        <v>7648.97</v>
+        <v>38914.239999999998</v>
       </c>
       <c r="K350" s="10">
-        <v>0.52</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
@@ -17338,31 +17493,31 @@
         <v>2026</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D351" s="10">
-        <v>546</v>
+        <v>711</v>
       </c>
       <c r="E351" s="10">
-        <v>5077.71</v>
+        <v>7574.66</v>
       </c>
       <c r="F351" s="10">
-        <v>43.269999999999897</v>
+        <v>45.68</v>
       </c>
       <c r="G351" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H351" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I351" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J351" s="10">
-        <v>27569.200000000001</v>
+        <v>39275.800000000003</v>
       </c>
       <c r="K351" s="10">
-        <v>4.43</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.3">
@@ -17373,31 +17528,31 @@
         <v>2026</v>
       </c>
       <c r="C352" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D352" s="10">
+        <v>693</v>
+      </c>
+      <c r="E352" s="10">
+        <v>7600.17</v>
+      </c>
+      <c r="F352" s="10">
+        <v>51.39</v>
+      </c>
+      <c r="G352" s="10">
         <v>15</v>
       </c>
-      <c r="D352" s="10">
-        <v>568</v>
-      </c>
-      <c r="E352" s="10">
-        <v>5048.16</v>
-      </c>
-      <c r="F352" s="10">
-        <v>40.269999999999897</v>
-      </c>
-      <c r="G352" s="10">
-        <v>23</v>
-      </c>
       <c r="H352" s="10">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I352" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J352" s="10">
-        <v>38914.239999999998</v>
+        <v>8523</v>
       </c>
       <c r="K352" s="10">
-        <v>6.71</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.3">
@@ -17408,101 +17563,101 @@
         <v>2026</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>711</v>
+        <v>158</v>
       </c>
       <c r="E353" s="10">
-        <v>7574.66</v>
+        <v>1787.66</v>
       </c>
       <c r="F353" s="10">
-        <v>45.68</v>
+        <v>6</v>
       </c>
       <c r="G353" s="10">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H353" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I353" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J353" s="10">
-        <v>39275.800000000003</v>
+        <v>0</v>
       </c>
       <c r="K353" s="10">
-        <v>4.1900000000000004</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B354" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D354" s="10">
-        <v>693</v>
+        <v>1279</v>
       </c>
       <c r="E354" s="10">
-        <v>7600.17</v>
+        <v>18483.38</v>
       </c>
       <c r="F354" s="10">
-        <v>51.39</v>
+        <v>113.5</v>
       </c>
       <c r="G354" s="10">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H354" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I354" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J354" s="10">
-        <v>8523</v>
+        <v>17074</v>
       </c>
       <c r="K354" s="10">
-        <v>0.12</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B355" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D355" s="10">
-        <v>138</v>
+        <v>1343</v>
       </c>
       <c r="E355" s="10">
-        <v>1557.88</v>
+        <v>18545.96</v>
       </c>
       <c r="F355" s="10">
-        <v>5</v>
+        <v>74.679999999999893</v>
       </c>
       <c r="G355" s="10">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H355" s="10">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I355" s="10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J355" s="10">
-        <v>0</v>
+        <v>86918.12</v>
       </c>
       <c r="K355" s="10">
-        <v>-1</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
@@ -17513,31 +17668,31 @@
         <v>2025</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D356" s="10">
-        <v>1279</v>
+        <v>986</v>
       </c>
       <c r="E356" s="10">
-        <v>18483.38</v>
+        <v>10133.459999999999</v>
       </c>
       <c r="F356" s="10">
-        <v>113.5</v>
+        <v>42.49</v>
       </c>
       <c r="G356" s="10">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H356" s="10">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I356" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J356" s="10">
-        <v>17074</v>
+        <v>43710.22</v>
       </c>
       <c r="K356" s="10">
-        <v>-0.08</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.3">
@@ -17548,31 +17703,31 @@
         <v>2025</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D357" s="10">
-        <v>1343</v>
+        <v>1032</v>
       </c>
       <c r="E357" s="10">
-        <v>18545.96</v>
+        <v>9463.0300000000007</v>
       </c>
       <c r="F357" s="10">
-        <v>74.679999999999893</v>
+        <v>34</v>
       </c>
       <c r="G357" s="10">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H357" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I357" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J357" s="10">
-        <v>86918.12</v>
+        <v>64285.36</v>
       </c>
       <c r="K357" s="10">
-        <v>3.69</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.3">
@@ -17583,31 +17738,31 @@
         <v>2025</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D358" s="10">
-        <v>986</v>
+        <v>1399</v>
       </c>
       <c r="E358" s="10">
-        <v>10133.459999999999</v>
+        <v>12015.14</v>
       </c>
       <c r="F358" s="10">
-        <v>42.49</v>
+        <v>42.5</v>
       </c>
       <c r="G358" s="10">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H358" s="10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I358" s="10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J358" s="10">
-        <v>43710.22</v>
+        <v>91057.75</v>
       </c>
       <c r="K358" s="10">
-        <v>3.31</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.3">
@@ -17618,31 +17773,31 @@
         <v>2025</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D359" s="10">
-        <v>1032</v>
+        <v>1186</v>
       </c>
       <c r="E359" s="10">
-        <v>9463.0300000000007</v>
+        <v>11775.01</v>
       </c>
       <c r="F359" s="10">
-        <v>34</v>
+        <v>45.32</v>
       </c>
       <c r="G359" s="10">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H359" s="10">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I359" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J359" s="10">
-        <v>64285.36</v>
+        <v>67230.75</v>
       </c>
       <c r="K359" s="10">
-        <v>5.79</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.3">
@@ -17653,31 +17808,31 @@
         <v>2025</v>
       </c>
       <c r="C360" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D360" s="10">
-        <v>1399</v>
+        <v>1647</v>
       </c>
       <c r="E360" s="10">
-        <v>12015.14</v>
+        <v>18879.95</v>
       </c>
       <c r="F360" s="10">
-        <v>42.5</v>
+        <v>47.7</v>
       </c>
       <c r="G360" s="10">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H360" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I360" s="10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J360" s="10">
-        <v>91057.75</v>
+        <v>29024.63</v>
       </c>
       <c r="K360" s="10">
-        <v>6.58</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.3">
@@ -17688,31 +17843,31 @@
         <v>2025</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D361" s="10">
-        <v>1186</v>
+        <v>1846</v>
       </c>
       <c r="E361" s="10">
-        <v>11775.01</v>
+        <v>21280.35</v>
       </c>
       <c r="F361" s="10">
-        <v>45.32</v>
+        <v>51.08</v>
       </c>
       <c r="G361" s="10">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H361" s="10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I361" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J361" s="10">
-        <v>67230.75</v>
+        <v>39893.14</v>
       </c>
       <c r="K361" s="10">
-        <v>4.71</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.3">
@@ -17723,31 +17878,31 @@
         <v>2025</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D362" s="10">
-        <v>1647</v>
+        <v>1506</v>
       </c>
       <c r="E362" s="10">
-        <v>18879.95</v>
+        <v>21078.14</v>
       </c>
       <c r="F362" s="10">
-        <v>47.7</v>
+        <v>41.56</v>
       </c>
       <c r="G362" s="10">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H362" s="10">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I362" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J362" s="10">
-        <v>29024.63</v>
+        <v>79358.69</v>
       </c>
       <c r="K362" s="10">
-        <v>0.54</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.3">
@@ -17758,31 +17913,31 @@
         <v>2025</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D363" s="10">
-        <v>1846</v>
+        <v>1305</v>
       </c>
       <c r="E363" s="10">
-        <v>21280.35</v>
+        <v>18345.509999999998</v>
       </c>
       <c r="F363" s="10">
-        <v>51.08</v>
+        <v>55</v>
       </c>
       <c r="G363" s="10">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="H363" s="10">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I363" s="10">
         <v>6</v>
       </c>
       <c r="J363" s="10">
-        <v>39893.14</v>
+        <v>43960.28</v>
       </c>
       <c r="K363" s="10">
-        <v>0.87</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.3">
@@ -17793,31 +17948,31 @@
         <v>2025</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D364" s="10">
-        <v>1506</v>
+        <v>1379</v>
       </c>
       <c r="E364" s="10">
-        <v>21078.14</v>
+        <v>18633.439999999999</v>
       </c>
       <c r="F364" s="10">
-        <v>41.56</v>
+        <v>51.48</v>
       </c>
       <c r="G364" s="10">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H364" s="10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I364" s="10">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J364" s="10">
-        <v>79358.69</v>
+        <v>32175.87</v>
       </c>
       <c r="K364" s="10">
-        <v>2.76</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.3">
@@ -17828,31 +17983,31 @@
         <v>2025</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D365" s="10">
-        <v>1305</v>
+        <v>1592</v>
       </c>
       <c r="E365" s="10">
-        <v>18345.509999999998</v>
+        <v>19172.93</v>
       </c>
       <c r="F365" s="10">
-        <v>55</v>
+        <v>78.449999999999903</v>
       </c>
       <c r="G365" s="10">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H365" s="10">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I365" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J365" s="10">
-        <v>43960.28</v>
+        <v>54648.83</v>
       </c>
       <c r="K365" s="10">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.3">
@@ -17860,34 +18015,34 @@
         <v>58</v>
       </c>
       <c r="B366" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D366" s="10">
-        <v>1379</v>
+        <v>1861</v>
       </c>
       <c r="E366" s="10">
-        <v>18633.439999999999</v>
+        <v>20545.41</v>
       </c>
       <c r="F366" s="10">
-        <v>51.48</v>
+        <v>91.5</v>
       </c>
       <c r="G366" s="10">
         <v>38</v>
       </c>
       <c r="H366" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I366" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J366" s="10">
-        <v>32175.87</v>
+        <v>50898.68</v>
       </c>
       <c r="K366" s="10">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.3">
@@ -17895,34 +18050,34 @@
         <v>58</v>
       </c>
       <c r="B367" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C367" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D367" s="10">
+        <v>1516</v>
+      </c>
+      <c r="E367" s="10">
+        <v>18973.55</v>
+      </c>
+      <c r="F367" s="10">
+        <v>73.5</v>
+      </c>
+      <c r="G367" s="10">
         <v>25</v>
       </c>
-      <c r="D367" s="10">
-        <v>1592</v>
-      </c>
-      <c r="E367" s="10">
-        <v>19172.93</v>
-      </c>
-      <c r="F367" s="10">
-        <v>78.449999999999903</v>
-      </c>
-      <c r="G367" s="10">
-        <v>41</v>
-      </c>
       <c r="H367" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I367" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J367" s="10">
-        <v>54648.83</v>
+        <v>38485.74</v>
       </c>
       <c r="K367" s="10">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.3">
@@ -17933,31 +18088,31 @@
         <v>2026</v>
       </c>
       <c r="C368" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D368" s="10">
+        <v>1685</v>
+      </c>
+      <c r="E368" s="10">
+        <v>20205.009999999998</v>
+      </c>
+      <c r="F368" s="10">
+        <v>81.229999999999905</v>
+      </c>
+      <c r="G368" s="10">
+        <v>25</v>
+      </c>
+      <c r="H368" s="10">
         <v>14</v>
       </c>
-      <c r="D368" s="10">
-        <v>1861</v>
-      </c>
-      <c r="E368" s="10">
-        <v>20545.41</v>
-      </c>
-      <c r="F368" s="10">
-        <v>91.5</v>
-      </c>
-      <c r="G368" s="10">
-        <v>38</v>
-      </c>
-      <c r="H368" s="10">
-        <v>21</v>
-      </c>
       <c r="I368" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J368" s="10">
-        <v>50898.68</v>
+        <v>44060.479999999901</v>
       </c>
       <c r="K368" s="10">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -17968,31 +18123,31 @@
         <v>2026</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D369" s="10">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="E369" s="10">
-        <v>18973.55</v>
+        <v>20210.580000000002</v>
       </c>
       <c r="F369" s="10">
-        <v>73.5</v>
+        <v>82.38</v>
       </c>
       <c r="G369" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H369" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I369" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J369" s="10">
-        <v>38485.74</v>
+        <v>8353</v>
       </c>
       <c r="K369" s="10">
-        <v>1.03</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
@@ -18003,92 +18158,92 @@
         <v>2026</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>1685</v>
+        <v>345</v>
       </c>
       <c r="E370" s="10">
-        <v>20205.009999999998</v>
+        <v>4510.46</v>
       </c>
       <c r="F370" s="10">
-        <v>81.229999999999905</v>
+        <v>19.98</v>
       </c>
       <c r="G370" s="10">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H370" s="10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I370" s="10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J370" s="10">
-        <v>51854.48</v>
+        <v>0</v>
       </c>
       <c r="K370" s="10">
-        <v>1.57</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B371" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D371" s="10">
-        <v>1511</v>
+        <v>166</v>
       </c>
       <c r="E371" s="10">
-        <v>20210.580000000002</v>
+        <v>34.65</v>
       </c>
       <c r="F371" s="10">
-        <v>82.38</v>
+        <v>9.99</v>
       </c>
       <c r="G371" s="10">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H371" s="10">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I371" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J371" s="10">
-        <v>15847</v>
+        <v>0</v>
       </c>
       <c r="K371" s="10">
-        <v>-0.22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B372" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D372" s="10">
-        <v>307</v>
+        <v>8380</v>
       </c>
       <c r="E372" s="10">
-        <v>3953.27</v>
+        <v>3368</v>
       </c>
       <c r="F372" s="10">
-        <v>17.98</v>
+        <v>29</v>
       </c>
       <c r="G372" s="10">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H372" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I372" s="10">
         <v>0</v>
@@ -18108,31 +18263,31 @@
         <v>2025</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D373" s="10">
-        <v>166</v>
+        <v>17369</v>
       </c>
       <c r="E373" s="10">
-        <v>34.65</v>
+        <v>5964.35</v>
       </c>
       <c r="F373" s="10">
-        <v>9.99</v>
+        <v>97.34</v>
       </c>
       <c r="G373" s="10">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H373" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I373" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J373" s="10">
-        <v>0</v>
+        <v>12747</v>
       </c>
       <c r="K373" s="10">
-        <v>-1</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
@@ -18143,31 +18298,31 @@
         <v>2025</v>
       </c>
       <c r="C374" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D374" s="10">
+        <v>11231</v>
+      </c>
+      <c r="E374" s="10">
+        <v>5898.88</v>
+      </c>
+      <c r="F374" s="10">
+        <v>81.56</v>
+      </c>
+      <c r="G374" s="10">
         <v>17</v>
-      </c>
-      <c r="D374" s="10">
-        <v>8380</v>
-      </c>
-      <c r="E374" s="10">
-        <v>3368</v>
-      </c>
-      <c r="F374" s="10">
-        <v>29</v>
-      </c>
-      <c r="G374" s="10">
-        <v>12</v>
       </c>
       <c r="H374" s="10">
         <v>4</v>
       </c>
       <c r="I374" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J374" s="10">
-        <v>0</v>
+        <v>16757.05</v>
       </c>
       <c r="K374" s="10">
-        <v>-1</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.3">
@@ -18178,31 +18333,31 @@
         <v>2025</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D375" s="10">
-        <v>17369</v>
+        <v>7135</v>
       </c>
       <c r="E375" s="10">
-        <v>5964.35</v>
+        <v>5899.41</v>
       </c>
       <c r="F375" s="10">
-        <v>97.34</v>
+        <v>43.97</v>
       </c>
       <c r="G375" s="10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H375" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I375" s="10">
         <v>2</v>
       </c>
       <c r="J375" s="10">
-        <v>12747</v>
+        <v>8908</v>
       </c>
       <c r="K375" s="10">
-        <v>1.1399999999999999</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.3">
@@ -18213,31 +18368,31 @@
         <v>2025</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D376" s="10">
-        <v>11231</v>
+        <v>3123</v>
       </c>
       <c r="E376" s="10">
-        <v>5898.88</v>
+        <v>5907.54</v>
       </c>
       <c r="F376" s="10">
-        <v>81.56</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="G376" s="10">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H376" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I376" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J376" s="10">
-        <v>16757.05</v>
+        <v>279</v>
       </c>
       <c r="K376" s="10">
-        <v>1.84</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.3">
@@ -18248,101 +18403,101 @@
         <v>2025</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D377" s="10">
-        <v>7135</v>
+        <v>1847</v>
       </c>
       <c r="E377" s="10">
-        <v>5899.41</v>
+        <v>4432.75</v>
       </c>
       <c r="F377" s="10">
-        <v>43.97</v>
+        <v>22.07</v>
       </c>
       <c r="G377" s="10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H377" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I377" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J377" s="10">
-        <v>8908</v>
+        <v>21925.09</v>
       </c>
       <c r="K377" s="10">
-        <v>0.51</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B378" s="10">
         <v>2025</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D378" s="10">
-        <v>3123</v>
+        <v>1120</v>
       </c>
       <c r="E378" s="10">
-        <v>5907.54</v>
+        <v>13806.08</v>
       </c>
       <c r="F378" s="10">
-        <v>33.409999999999997</v>
+        <v>117.67</v>
       </c>
       <c r="G378" s="10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H378" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I378" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J378" s="10">
-        <v>279</v>
+        <v>20651.47</v>
       </c>
       <c r="K378" s="10">
-        <v>-0.95</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B379" s="10">
         <v>2025</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D379" s="10">
-        <v>1847</v>
+        <v>1428</v>
       </c>
       <c r="E379" s="10">
-        <v>4432.75</v>
+        <v>19992.240000000002</v>
       </c>
       <c r="F379" s="10">
-        <v>22.07</v>
+        <v>121.03</v>
       </c>
       <c r="G379" s="10">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H379" s="10">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I379" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J379" s="10">
-        <v>21925.09</v>
+        <v>50381.37</v>
       </c>
       <c r="K379" s="10">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
@@ -18353,31 +18508,31 @@
         <v>2025</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D380" s="10">
-        <v>1120</v>
+        <v>1375</v>
       </c>
       <c r="E380" s="10">
-        <v>13806.08</v>
+        <v>15772.75</v>
       </c>
       <c r="F380" s="10">
-        <v>117.67</v>
+        <v>43.66</v>
       </c>
       <c r="G380" s="10">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H380" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I380" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J380" s="10">
-        <v>20651.47</v>
+        <v>43934.68</v>
       </c>
       <c r="K380" s="10">
-        <v>0.5</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
@@ -18388,31 +18543,31 @@
         <v>2025</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D381" s="10">
-        <v>1428</v>
+        <v>1013</v>
       </c>
       <c r="E381" s="10">
-        <v>19992.240000000002</v>
+        <v>8945.9699999999993</v>
       </c>
       <c r="F381" s="10">
-        <v>121.03</v>
+        <v>36.5</v>
       </c>
       <c r="G381" s="10">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H381" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I381" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J381" s="10">
-        <v>50381.37</v>
+        <v>21029.41</v>
       </c>
       <c r="K381" s="10">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
@@ -18423,31 +18578,31 @@
         <v>2025</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D382" s="10">
-        <v>1375</v>
+        <v>1203</v>
       </c>
       <c r="E382" s="10">
-        <v>15772.75</v>
+        <v>10931.15</v>
       </c>
       <c r="F382" s="10">
-        <v>43.66</v>
+        <v>52.03</v>
       </c>
       <c r="G382" s="10">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H382" s="10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I382" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J382" s="10">
-        <v>43934.68</v>
+        <v>12295.56</v>
       </c>
       <c r="K382" s="10">
-        <v>1.79</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
@@ -18458,31 +18613,31 @@
         <v>2025</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D383" s="10">
-        <v>1013</v>
+        <v>1039</v>
       </c>
       <c r="E383" s="10">
-        <v>8945.9699999999993</v>
+        <v>11764.77</v>
       </c>
       <c r="F383" s="10">
-        <v>36.5</v>
+        <v>27.64</v>
       </c>
       <c r="G383" s="10">
         <v>34</v>
       </c>
       <c r="H383" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I383" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J383" s="10">
-        <v>21029.41</v>
+        <v>12747.9</v>
       </c>
       <c r="K383" s="10">
-        <v>1.35</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.3">
@@ -18493,31 +18648,31 @@
         <v>2025</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D384" s="10">
-        <v>1203</v>
+        <v>1570</v>
       </c>
       <c r="E384" s="10">
-        <v>10931.15</v>
+        <v>18806.53</v>
       </c>
       <c r="F384" s="10">
-        <v>52.03</v>
+        <v>57.81</v>
       </c>
       <c r="G384" s="10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H384" s="10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I384" s="10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J384" s="10">
-        <v>12295.56</v>
+        <v>65983.360000000001</v>
       </c>
       <c r="K384" s="10">
-        <v>0.12</v>
+        <v>2.5099999999999998</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.3">
@@ -18528,31 +18683,31 @@
         <v>2025</v>
       </c>
       <c r="C385" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D385" s="10">
+        <v>1875</v>
+      </c>
+      <c r="E385" s="10">
+        <v>22624.03</v>
+      </c>
+      <c r="F385" s="10">
+        <v>51.14</v>
+      </c>
+      <c r="G385" s="10">
+        <v>51</v>
+      </c>
+      <c r="H385" s="10">
         <v>19</v>
       </c>
-      <c r="D385" s="10">
-        <v>1039</v>
-      </c>
-      <c r="E385" s="10">
-        <v>11764.77</v>
-      </c>
-      <c r="F385" s="10">
-        <v>27.64</v>
-      </c>
-      <c r="G385" s="10">
-        <v>34</v>
-      </c>
-      <c r="H385" s="10">
-        <v>13</v>
-      </c>
       <c r="I385" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J385" s="10">
-        <v>12747.9</v>
+        <v>50193.159999999902</v>
       </c>
       <c r="K385" s="10">
-        <v>0.08</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.3">
@@ -18563,31 +18718,31 @@
         <v>2025</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D386" s="10">
-        <v>1570</v>
+        <v>1869</v>
       </c>
       <c r="E386" s="10">
-        <v>18806.53</v>
+        <v>23802.080000000002</v>
       </c>
       <c r="F386" s="10">
-        <v>57.81</v>
+        <v>82.19</v>
       </c>
       <c r="G386" s="10">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H386" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I386" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J386" s="10">
-        <v>65983.360000000001</v>
+        <v>45254.8</v>
       </c>
       <c r="K386" s="10">
-        <v>2.5099999999999998</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.3">
@@ -18598,31 +18753,31 @@
         <v>2025</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D387" s="10">
-        <v>1875</v>
+        <v>1542</v>
       </c>
       <c r="E387" s="10">
-        <v>22624.03</v>
+        <v>18523.04</v>
       </c>
       <c r="F387" s="10">
-        <v>51.14</v>
+        <v>91.55</v>
       </c>
       <c r="G387" s="10">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H387" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I387" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J387" s="10">
-        <v>50193.159999999902</v>
+        <v>32969.129999999997</v>
       </c>
       <c r="K387" s="10">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.3">
@@ -18633,31 +18788,31 @@
         <v>2025</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D388" s="10">
-        <v>1869</v>
+        <v>1232</v>
       </c>
       <c r="E388" s="10">
-        <v>23802.080000000002</v>
+        <v>16789.099999999999</v>
       </c>
       <c r="F388" s="10">
-        <v>82.19</v>
+        <v>62.82</v>
       </c>
       <c r="G388" s="10">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="H388" s="10">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I388" s="10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J388" s="10">
-        <v>45254.8</v>
+        <v>50911.08</v>
       </c>
       <c r="K388" s="10">
-        <v>0.9</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.3">
@@ -18668,31 +18823,31 @@
         <v>2025</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D389" s="10">
-        <v>1542</v>
+        <v>1254</v>
       </c>
       <c r="E389" s="10">
-        <v>18523.04</v>
+        <v>14120.95</v>
       </c>
       <c r="F389" s="10">
-        <v>91.55</v>
+        <v>60.65</v>
       </c>
       <c r="G389" s="10">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H389" s="10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I389" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J389" s="10">
-        <v>32969.129999999997</v>
+        <v>26825.68</v>
       </c>
       <c r="K389" s="10">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
@@ -18700,34 +18855,34 @@
         <v>60</v>
       </c>
       <c r="B390" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D390" s="10">
-        <v>1232</v>
+        <v>1456</v>
       </c>
       <c r="E390" s="10">
-        <v>16789.099999999999</v>
+        <v>16923.400000000001</v>
       </c>
       <c r="F390" s="10">
-        <v>62.82</v>
+        <v>77.13</v>
       </c>
       <c r="G390" s="10">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H390" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I390" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J390" s="10">
-        <v>50911.08</v>
+        <v>30172.16</v>
       </c>
       <c r="K390" s="10">
-        <v>2.0299999999999998</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.3">
@@ -18735,34 +18890,34 @@
         <v>60</v>
       </c>
       <c r="B391" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D391" s="10">
-        <v>1254</v>
+        <v>1682</v>
       </c>
       <c r="E391" s="10">
-        <v>14120.95</v>
+        <v>21330.36</v>
       </c>
       <c r="F391" s="10">
-        <v>60.65</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="G391" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H391" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I391" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J391" s="10">
-        <v>27841.64</v>
+        <v>21036.240000000002</v>
       </c>
       <c r="K391" s="10">
-        <v>0.97</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.3">
@@ -18773,31 +18928,31 @@
         <v>2026</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D392" s="10">
-        <v>1456</v>
+        <v>1622</v>
       </c>
       <c r="E392" s="10">
-        <v>16923.400000000001</v>
+        <v>18924.47</v>
       </c>
       <c r="F392" s="10">
-        <v>77.13</v>
+        <v>80.14</v>
       </c>
       <c r="G392" s="10">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H392" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I392" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J392" s="10">
-        <v>30172.16</v>
+        <v>54059.12</v>
       </c>
       <c r="K392" s="10">
-        <v>0.78</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.3">
@@ -18808,31 +18963,31 @@
         <v>2026</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D393" s="10">
-        <v>1682</v>
+        <v>1765</v>
       </c>
       <c r="E393" s="10">
-        <v>21330.36</v>
+        <v>23623.439999999999</v>
       </c>
       <c r="F393" s="10">
-        <v>73.819999999999993</v>
+        <v>81.02</v>
       </c>
       <c r="G393" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H393" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I393" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J393" s="10">
-        <v>21036.240000000002</v>
+        <v>7311</v>
       </c>
       <c r="K393" s="10">
-        <v>-0.01</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.3">
@@ -18843,152 +18998,172 @@
         <v>2026</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>1622</v>
+        <v>288</v>
       </c>
       <c r="E394" s="10">
-        <v>18924.47</v>
+        <v>4161.45</v>
       </c>
       <c r="F394" s="10">
-        <v>80.14</v>
+        <v>13.87</v>
       </c>
       <c r="G394" s="10">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H394" s="10">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I394" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J394" s="10">
-        <v>54059.12</v>
+        <v>25130.799999999999</v>
       </c>
       <c r="K394" s="10">
-        <v>1.86</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B395" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C395" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D395" s="10">
-        <v>1765</v>
+        <v>4206</v>
       </c>
       <c r="E395" s="10">
-        <v>23623.439999999999</v>
+        <v>3006.79</v>
       </c>
       <c r="F395" s="10">
-        <v>81.02</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="G395" s="10">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H395" s="10">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I395" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J395" s="10">
-        <v>7311</v>
+        <v>0</v>
       </c>
       <c r="K395" s="10">
-        <v>-0.69</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B396" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C396" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D396" s="10">
-        <v>252</v>
+        <v>24682</v>
       </c>
       <c r="E396" s="10">
-        <v>3495.82</v>
+        <v>8783.7999999999993</v>
       </c>
       <c r="F396" s="10">
-        <v>12.87</v>
+        <v>127.59</v>
       </c>
       <c r="G396" s="10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H396" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I396" s="10">
         <v>3</v>
       </c>
       <c r="J396" s="10">
-        <v>17492.68</v>
+        <v>26702.85</v>
       </c>
       <c r="K396" s="10">
-        <v>4</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="10" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="B397" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D397" s="10">
-        <v>94</v>
+        <v>13233</v>
       </c>
       <c r="E397" s="10">
-        <v>1104.46</v>
+        <v>6345.41</v>
       </c>
       <c r="F397" s="10">
-        <v>2</v>
-      </c>
-      <c r="G397" s="10"/>
-      <c r="H397" s="10"/>
-      <c r="I397" s="10"/>
-      <c r="J397" s="10"/>
-      <c r="K397" s="10"/>
+        <v>63.95</v>
+      </c>
+      <c r="G397" s="10">
+        <v>9</v>
+      </c>
+      <c r="H397" s="10">
+        <v>1</v>
+      </c>
+      <c r="I397" s="10">
+        <v>1</v>
+      </c>
+      <c r="J397" s="10">
+        <v>7926.23</v>
+      </c>
+      <c r="K397" s="10">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="10" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="B398" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D398" s="10">
-        <v>22</v>
+        <v>7954</v>
       </c>
       <c r="E398" s="10">
-        <v>205.16</v>
+        <v>8876.9699999999993</v>
       </c>
       <c r="F398" s="10">
-        <v>1</v>
-      </c>
-      <c r="G398" s="10"/>
-      <c r="H398" s="10"/>
-      <c r="I398" s="10"/>
-      <c r="J398" s="10"/>
-      <c r="K398" s="10"/>
+        <v>32.35</v>
+      </c>
+      <c r="G398" s="10">
+        <v>24</v>
+      </c>
+      <c r="H398" s="10">
+        <v>7</v>
+      </c>
+      <c r="I398" s="10">
+        <v>2</v>
+      </c>
+      <c r="J398" s="10">
+        <v>17571.16</v>
+      </c>
+      <c r="K398" s="10">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="10" t="s">
@@ -18998,31 +19173,31 @@
         <v>2025</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D399" s="10">
-        <v>4206</v>
+        <v>3356</v>
       </c>
       <c r="E399" s="10">
-        <v>3006.79</v>
+        <v>8805.02</v>
       </c>
       <c r="F399" s="10">
-        <v>39.630000000000003</v>
+        <v>14.43</v>
       </c>
       <c r="G399" s="10">
+        <v>15</v>
+      </c>
+      <c r="H399" s="10">
         <v>8</v>
       </c>
-      <c r="H399" s="10">
-        <v>4</v>
-      </c>
       <c r="I399" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J399" s="10">
-        <v>0</v>
+        <v>22959</v>
       </c>
       <c r="K399" s="10">
-        <v>-1</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.3">
@@ -19033,176 +19208,146 @@
         <v>2025</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D400" s="10">
-        <v>24682</v>
+        <v>2567</v>
       </c>
       <c r="E400" s="10">
-        <v>8783.7999999999993</v>
+        <v>6472.59</v>
       </c>
       <c r="F400" s="10">
-        <v>127.59</v>
+        <v>17.759999999999899</v>
       </c>
       <c r="G400" s="10">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H400" s="10">
         <v>4</v>
       </c>
       <c r="I400" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J400" s="10">
-        <v>26702.85</v>
+        <v>12792</v>
       </c>
       <c r="K400" s="10">
-        <v>2.04</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B401" s="10">
         <v>2025</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D401" s="10">
-        <v>13233</v>
+        <v>1945</v>
       </c>
       <c r="E401" s="10">
-        <v>6345.41</v>
+        <v>3569.76</v>
       </c>
       <c r="F401" s="10">
-        <v>63.95</v>
-      </c>
-      <c r="G401" s="10">
-        <v>9</v>
-      </c>
-      <c r="H401" s="10">
-        <v>1</v>
-      </c>
-      <c r="I401" s="10">
-        <v>1</v>
-      </c>
-      <c r="J401" s="10">
-        <v>7926.23</v>
-      </c>
-      <c r="K401" s="10">
-        <v>0.25</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="G401" s="10"/>
+      <c r="H401" s="10"/>
+      <c r="I401" s="10"/>
+      <c r="J401" s="10"/>
+      <c r="K401" s="10"/>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B402" s="10">
         <v>2025</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D402" s="10">
-        <v>7954</v>
+        <v>154</v>
       </c>
       <c r="E402" s="10">
-        <v>8876.9699999999993</v>
+        <v>36.21</v>
       </c>
       <c r="F402" s="10">
-        <v>32.35</v>
-      </c>
-      <c r="G402" s="10">
-        <v>24</v>
-      </c>
-      <c r="H402" s="10">
-        <v>7</v>
-      </c>
-      <c r="I402" s="10">
-        <v>2</v>
-      </c>
-      <c r="J402" s="10">
-        <v>17571.16</v>
-      </c>
-      <c r="K402" s="10">
-        <v>0.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G402" s="10"/>
+      <c r="H402" s="10"/>
+      <c r="I402" s="10"/>
+      <c r="J402" s="10"/>
+      <c r="K402" s="10"/>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B403" s="10">
         <v>2025</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D403" s="10">
-        <v>3356</v>
+        <v>799</v>
       </c>
       <c r="E403" s="10">
-        <v>8805.02</v>
+        <v>1830.52</v>
       </c>
       <c r="F403" s="10">
-        <v>14.43</v>
-      </c>
-      <c r="G403" s="10">
-        <v>15</v>
-      </c>
-      <c r="H403" s="10">
-        <v>8</v>
-      </c>
-      <c r="I403" s="10">
-        <v>3</v>
-      </c>
-      <c r="J403" s="10">
-        <v>22959</v>
-      </c>
-      <c r="K403" s="10">
-        <v>1.61</v>
-      </c>
+        <v>4.43</v>
+      </c>
+      <c r="G403" s="10"/>
+      <c r="H403" s="10"/>
+      <c r="I403" s="10"/>
+      <c r="J403" s="10"/>
+      <c r="K403" s="10"/>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B404" s="10">
         <v>2025</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D404" s="10">
-        <v>2567</v>
+        <v>1365</v>
       </c>
       <c r="E404" s="10">
-        <v>6472.59</v>
+        <v>2992.53</v>
       </c>
       <c r="F404" s="10">
-        <v>17.759999999999899</v>
+        <v>5.83</v>
       </c>
       <c r="G404" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H404" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I404" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J404" s="10">
-        <v>12792</v>
+        <v>8192</v>
       </c>
       <c r="K404" s="10">
-        <v>0.98</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B405" s="10">
         <v>2025</v>
@@ -19211,13 +19356,13 @@
         <v>22</v>
       </c>
       <c r="D405" s="10">
-        <v>1945</v>
+        <v>566</v>
       </c>
       <c r="E405" s="10">
-        <v>3569.76</v>
+        <v>2266.7199999999998</v>
       </c>
       <c r="F405" s="10">
-        <v>10.01</v>
+        <v>2.67</v>
       </c>
       <c r="G405" s="10"/>
       <c r="H405" s="10"/>
@@ -19227,22 +19372,22 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B406" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C406" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D406" s="10">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="E406" s="10">
-        <v>36.21</v>
+        <v>2453.9299999999998</v>
       </c>
       <c r="F406" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G406" s="10"/>
       <c r="H406" s="10"/>
@@ -19252,22 +19397,22 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B407" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D407" s="10">
-        <v>799</v>
+        <v>130</v>
       </c>
       <c r="E407" s="10">
-        <v>1830.52</v>
+        <v>3862.91</v>
       </c>
       <c r="F407" s="10">
-        <v>4.43</v>
+        <v>1</v>
       </c>
       <c r="G407" s="10"/>
       <c r="H407" s="10"/>
@@ -19277,113 +19422,143 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B408" s="10">
         <v>2025</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D408" s="10">
-        <v>1365</v>
+        <v>782</v>
       </c>
       <c r="E408" s="10">
-        <v>2992.53</v>
+        <v>13793.84</v>
       </c>
       <c r="F408" s="10">
-        <v>5.83</v>
+        <v>84.41</v>
       </c>
       <c r="G408" s="10">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H408" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I408" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J408" s="10">
-        <v>8192</v>
+        <v>21292.16</v>
       </c>
       <c r="K408" s="10">
-        <v>1.74</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B409" s="10">
         <v>2025</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D409" s="10">
-        <v>566</v>
+        <v>799</v>
       </c>
       <c r="E409" s="10">
-        <v>2266.7199999999998</v>
+        <v>13861.32</v>
       </c>
       <c r="F409" s="10">
-        <v>2.67</v>
-      </c>
-      <c r="G409" s="10"/>
-      <c r="H409" s="10"/>
-      <c r="I409" s="10"/>
-      <c r="J409" s="10"/>
-      <c r="K409" s="10"/>
+        <v>45.25</v>
+      </c>
+      <c r="G409" s="10">
+        <v>28</v>
+      </c>
+      <c r="H409" s="10">
+        <v>11</v>
+      </c>
+      <c r="I409" s="10">
+        <v>6</v>
+      </c>
+      <c r="J409" s="10">
+        <v>44540.869999999901</v>
+      </c>
+      <c r="K409" s="10">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B410" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C410" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D410" s="10">
+        <v>715</v>
+      </c>
+      <c r="E410" s="10">
+        <v>8808.84</v>
+      </c>
+      <c r="F410" s="10">
+        <v>37.08</v>
+      </c>
+      <c r="G410" s="10">
+        <v>24</v>
+      </c>
+      <c r="H410" s="10">
         <v>14</v>
       </c>
-      <c r="D410" s="10">
-        <v>75</v>
-      </c>
-      <c r="E410" s="10">
-        <v>2453.9299999999998</v>
-      </c>
-      <c r="F410" s="10">
-        <v>1</v>
-      </c>
-      <c r="G410" s="10"/>
-      <c r="H410" s="10"/>
-      <c r="I410" s="10"/>
-      <c r="J410" s="10"/>
-      <c r="K410" s="10"/>
+      <c r="I410" s="10">
+        <v>6</v>
+      </c>
+      <c r="J410" s="10">
+        <v>50422.34</v>
+      </c>
+      <c r="K410" s="10">
+        <v>4.72</v>
+      </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B411" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D411" s="10">
-        <v>130</v>
+        <v>437</v>
       </c>
       <c r="E411" s="10">
-        <v>3862.91</v>
+        <v>4902.3</v>
       </c>
       <c r="F411" s="10">
-        <v>1</v>
-      </c>
-      <c r="G411" s="10"/>
-      <c r="H411" s="10"/>
-      <c r="I411" s="10"/>
-      <c r="J411" s="10"/>
-      <c r="K411" s="10"/>
+        <v>18.989999999999998</v>
+      </c>
+      <c r="G411" s="10">
+        <v>22</v>
+      </c>
+      <c r="H411" s="10">
+        <v>5</v>
+      </c>
+      <c r="I411" s="10">
+        <v>1</v>
+      </c>
+      <c r="J411" s="10">
+        <v>7295.12</v>
+      </c>
+      <c r="K411" s="10">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="10" t="s">
@@ -19393,31 +19568,31 @@
         <v>2025</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D412" s="10">
-        <v>782</v>
+        <v>482</v>
       </c>
       <c r="E412" s="10">
-        <v>13793.84</v>
+        <v>4636.55</v>
       </c>
       <c r="F412" s="10">
-        <v>84.41</v>
+        <v>23.02</v>
       </c>
       <c r="G412" s="10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H412" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I412" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J412" s="10">
-        <v>21292.16</v>
+        <v>15184</v>
       </c>
       <c r="K412" s="10">
-        <v>0.54</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
@@ -19428,31 +19603,31 @@
         <v>2025</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D413" s="10">
-        <v>799</v>
+        <v>596</v>
       </c>
       <c r="E413" s="10">
-        <v>13861.32</v>
+        <v>7884.31</v>
       </c>
       <c r="F413" s="10">
-        <v>45.25</v>
+        <v>27.98</v>
       </c>
       <c r="G413" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H413" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I413" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J413" s="10">
-        <v>44540.869999999901</v>
+        <v>20933.39</v>
       </c>
       <c r="K413" s="10">
-        <v>2.21</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
@@ -19463,31 +19638,31 @@
         <v>2025</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D414" s="10">
-        <v>715</v>
+        <v>608</v>
       </c>
       <c r="E414" s="10">
-        <v>8808.84</v>
+        <v>8219.64</v>
       </c>
       <c r="F414" s="10">
-        <v>37.08</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="G414" s="10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H414" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I414" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J414" s="10">
-        <v>50422.34</v>
+        <v>21432.66</v>
       </c>
       <c r="K414" s="10">
-        <v>4.72</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
@@ -19498,31 +19673,31 @@
         <v>2025</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D415" s="10">
-        <v>437</v>
+        <v>631</v>
       </c>
       <c r="E415" s="10">
-        <v>4902.3</v>
+        <v>8535.4500000000007</v>
       </c>
       <c r="F415" s="10">
-        <v>18.989999999999998</v>
+        <v>26.04</v>
       </c>
       <c r="G415" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H415" s="10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I415" s="10">
         <v>1</v>
       </c>
       <c r="J415" s="10">
-        <v>7295.12</v>
+        <v>7292</v>
       </c>
       <c r="K415" s="10">
-        <v>0.49</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.3">
@@ -19533,31 +19708,31 @@
         <v>2025</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D416" s="10">
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="E416" s="10">
-        <v>4636.55</v>
+        <v>9969.59</v>
       </c>
       <c r="F416" s="10">
-        <v>23.02</v>
+        <v>39.519999999999897</v>
       </c>
       <c r="G416" s="10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H416" s="10">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I416" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J416" s="10">
-        <v>15184</v>
+        <v>40761</v>
       </c>
       <c r="K416" s="10">
-        <v>2.27</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.3">
@@ -19568,31 +19743,31 @@
         <v>2025</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D417" s="10">
-        <v>596</v>
+        <v>558</v>
       </c>
       <c r="E417" s="10">
-        <v>7884.31</v>
+        <v>8231.73</v>
       </c>
       <c r="F417" s="10">
-        <v>27.98</v>
+        <v>36.35</v>
       </c>
       <c r="G417" s="10">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H417" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I417" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J417" s="10">
-        <v>20933.39</v>
+        <v>5980</v>
       </c>
       <c r="K417" s="10">
-        <v>1.66</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.3">
@@ -19603,31 +19778,31 @@
         <v>2025</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D418" s="10">
-        <v>608</v>
+        <v>487</v>
       </c>
       <c r="E418" s="10">
-        <v>8219.64</v>
+        <v>7066.25</v>
       </c>
       <c r="F418" s="10">
-        <v>19.079999999999998</v>
+        <v>33.489999999999903</v>
       </c>
       <c r="G418" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H418" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I418" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J418" s="10">
-        <v>21432.66</v>
+        <v>7456.01</v>
       </c>
       <c r="K418" s="10">
-        <v>1.61</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.3">
@@ -19638,31 +19813,31 @@
         <v>2025</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D419" s="10">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="E419" s="10">
-        <v>8535.4500000000007</v>
+        <v>9964.6</v>
       </c>
       <c r="F419" s="10">
-        <v>26.04</v>
+        <v>31.08</v>
       </c>
       <c r="G419" s="10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H419" s="10">
         <v>9</v>
       </c>
       <c r="I419" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J419" s="10">
-        <v>7292</v>
+        <v>33101.519999999997</v>
       </c>
       <c r="K419" s="10">
-        <v>-0.15</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
@@ -19670,34 +19845,34 @@
         <v>65</v>
       </c>
       <c r="B420" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D420" s="10">
-        <v>709</v>
+        <v>512</v>
       </c>
       <c r="E420" s="10">
-        <v>9969.59</v>
+        <v>7220.33</v>
       </c>
       <c r="F420" s="10">
-        <v>39.519999999999897</v>
+        <v>39</v>
       </c>
       <c r="G420" s="10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H420" s="10">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I420" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J420" s="10">
-        <v>40761</v>
+        <v>16184</v>
       </c>
       <c r="K420" s="10">
-        <v>3.09</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
@@ -19705,34 +19880,34 @@
         <v>65</v>
       </c>
       <c r="B421" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D421" s="10">
-        <v>558</v>
+        <v>450</v>
       </c>
       <c r="E421" s="10">
-        <v>8231.73</v>
+        <v>6693.08</v>
       </c>
       <c r="F421" s="10">
-        <v>36.35</v>
+        <v>28.01</v>
       </c>
       <c r="G421" s="10">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H421" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I421" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J421" s="10">
-        <v>5980</v>
+        <v>0</v>
       </c>
       <c r="K421" s="10">
-        <v>-0.27</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
@@ -19740,34 +19915,34 @@
         <v>65</v>
       </c>
       <c r="B422" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D422" s="10">
-        <v>487</v>
+        <v>675</v>
       </c>
       <c r="E422" s="10">
-        <v>7066.25</v>
+        <v>11556.36</v>
       </c>
       <c r="F422" s="10">
-        <v>33.489999999999903</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="G422" s="10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H422" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I422" s="10">
         <v>1</v>
       </c>
       <c r="J422" s="10">
-        <v>7456.01</v>
+        <v>7594</v>
       </c>
       <c r="K422" s="10">
-        <v>0.06</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
@@ -19775,34 +19950,34 @@
         <v>65</v>
       </c>
       <c r="B423" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D423" s="10">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="E423" s="10">
-        <v>9964.6</v>
+        <v>10129.77</v>
       </c>
       <c r="F423" s="10">
-        <v>31.08</v>
+        <v>37.64</v>
       </c>
       <c r="G423" s="10">
         <v>14</v>
       </c>
       <c r="H423" s="10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I423" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J423" s="10">
-        <v>33101.519999999997</v>
+        <v>16532</v>
       </c>
       <c r="K423" s="10">
-        <v>2.3199999999999998</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
@@ -19813,162 +19988,152 @@
         <v>2026</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>512</v>
+        <v>166</v>
       </c>
       <c r="E424" s="10">
-        <v>7220.33</v>
+        <v>2674.19</v>
       </c>
       <c r="F424" s="10">
-        <v>39</v>
+        <v>10.66</v>
       </c>
       <c r="G424" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H424" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I424" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J424" s="10">
-        <v>16184</v>
+        <v>0</v>
       </c>
       <c r="K424" s="10">
-        <v>1.24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B425" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D425" s="10">
-        <v>450</v>
+        <v>512</v>
       </c>
       <c r="E425" s="10">
-        <v>6693.08</v>
+        <v>105.12</v>
       </c>
       <c r="F425" s="10">
-        <v>28.01</v>
-      </c>
-      <c r="G425" s="10">
-        <v>9</v>
-      </c>
-      <c r="H425" s="10">
-        <v>4</v>
-      </c>
-      <c r="I425" s="10">
-        <v>0</v>
-      </c>
-      <c r="J425" s="10">
-        <v>0</v>
-      </c>
-      <c r="K425" s="10">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G425" s="10"/>
+      <c r="H425" s="10"/>
+      <c r="I425" s="10"/>
+      <c r="J425" s="10"/>
+      <c r="K425" s="10"/>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B426" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D426" s="10">
-        <v>675</v>
+        <v>1674</v>
       </c>
       <c r="E426" s="10">
-        <v>11556.36</v>
+        <v>1060.3499999999999</v>
       </c>
       <c r="F426" s="10">
-        <v>36.159999999999997</v>
+        <v>8</v>
       </c>
       <c r="G426" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H426" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I426" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J426" s="10">
-        <v>7594</v>
+        <v>0</v>
       </c>
       <c r="K426" s="10">
-        <v>-0.34</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B427" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D427" s="10">
-        <v>644</v>
+        <v>16401</v>
       </c>
       <c r="E427" s="10">
-        <v>10129.77</v>
+        <v>4863.79</v>
       </c>
       <c r="F427" s="10">
-        <v>37.64</v>
+        <v>56.01</v>
       </c>
       <c r="G427" s="10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H427" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I427" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J427" s="10">
-        <v>16532</v>
+        <v>7203.18</v>
       </c>
       <c r="K427" s="10">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B428" s="10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D428" s="10">
-        <v>142</v>
+        <v>10089</v>
       </c>
       <c r="E428" s="10">
-        <v>2273.9699999999998</v>
+        <v>4896.22</v>
       </c>
       <c r="F428" s="10">
-        <v>9.66</v>
+        <v>17.29</v>
       </c>
       <c r="G428" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H428" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I428" s="10">
         <v>0</v>
@@ -19988,22 +20153,32 @@
         <v>2025</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D429" s="10">
-        <v>512</v>
+        <v>3081</v>
       </c>
       <c r="E429" s="10">
-        <v>105.12</v>
+        <v>4895.66</v>
       </c>
       <c r="F429" s="10">
-        <v>1</v>
-      </c>
-      <c r="G429" s="10"/>
-      <c r="H429" s="10"/>
-      <c r="I429" s="10"/>
-      <c r="J429" s="10"/>
-      <c r="K429" s="10"/>
+        <v>14.84</v>
+      </c>
+      <c r="G429" s="10">
+        <v>20</v>
+      </c>
+      <c r="H429" s="10">
+        <v>6</v>
+      </c>
+      <c r="I429" s="10">
+        <v>3</v>
+      </c>
+      <c r="J429" s="10">
+        <v>29604.87</v>
+      </c>
+      <c r="K429" s="10">
+        <v>5.05</v>
+      </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="10" t="s">
@@ -20013,22 +20188,22 @@
         <v>2025</v>
       </c>
       <c r="C430" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D430" s="10">
+        <v>3146</v>
+      </c>
+      <c r="E430" s="10">
+        <v>4895.83</v>
+      </c>
+      <c r="F430" s="10">
+        <v>21.38</v>
+      </c>
+      <c r="G430" s="10">
         <v>17</v>
       </c>
-      <c r="D430" s="10">
-        <v>1674</v>
-      </c>
-      <c r="E430" s="10">
-        <v>1060.3499999999999</v>
-      </c>
-      <c r="F430" s="10">
-        <v>8</v>
-      </c>
-      <c r="G430" s="10">
+      <c r="H430" s="10">
         <v>3</v>
-      </c>
-      <c r="H430" s="10">
-        <v>0</v>
       </c>
       <c r="I430" s="10">
         <v>0</v>
@@ -20048,31 +20223,31 @@
         <v>2025</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D431" s="10">
-        <v>16401</v>
+        <v>1865</v>
       </c>
       <c r="E431" s="10">
-        <v>4863.79</v>
+        <v>3655.34</v>
       </c>
       <c r="F431" s="10">
-        <v>56.01</v>
+        <v>11</v>
       </c>
       <c r="G431" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H431" s="10">
+        <v>4</v>
+      </c>
+      <c r="I431" s="10">
         <v>2</v>
       </c>
-      <c r="I431" s="10">
-        <v>1</v>
-      </c>
       <c r="J431" s="10">
-        <v>7203.18</v>
+        <v>16861</v>
       </c>
       <c r="K431" s="10">
-        <v>0.48</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
@@ -20222,7 +20397,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -20404,7 +20579,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E8" s="18">
         <v>4</v>
@@ -20556,7 +20731,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="18">
         <v>1</v>
@@ -20670,7 +20845,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E15" s="18">
         <v>8</v>
@@ -20898,7 +21073,7 @@
         <v>17</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E21" s="18">
         <v>1</v>
@@ -21088,7 +21263,7 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -21430,7 +21605,7 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E35">
         <v>11</v>
@@ -21886,7 +22061,7 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -22152,7 +22327,7 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E54">
         <v>10</v>
@@ -22266,7 +22441,7 @@
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -22836,7 +23011,7 @@
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E72">
         <v>2</v>
@@ -23254,7 +23429,7 @@
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E83">
         <v>14</v>
@@ -23596,7 +23771,7 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -23862,7 +24037,7 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>23</v>
@@ -23900,7 +24075,7 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -24014,7 +24189,7 @@
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -24128,7 +24303,7 @@
         <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E106">
         <v>5</v>
@@ -24508,7 +24683,7 @@
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E116">
         <v>5</v>
@@ -24736,7 +24911,7 @@
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E122">
         <v>2</v>
@@ -24745,10 +24920,10 @@
         <v>2</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -24774,19 +24949,19 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E123">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F123">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -24812,19 +24987,19 @@
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="E124">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F124">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -24841,7 +25016,7 @@
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B125" s="18">
         <v>2026</v>
@@ -24850,13 +25025,13 @@
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -24879,7 +25054,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B126" s="18">
         <v>2026</v>
@@ -24888,13 +25063,13 @@
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -24917,7 +25092,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B127" s="18">
         <v>2026</v>
@@ -24926,7 +25101,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -24938,7 +25113,7 @@
         <v>1</v>
       </c>
       <c r="H127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -24955,7 +25130,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B128" s="18">
         <v>2026</v>
@@ -24964,7 +25139,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -24976,7 +25151,7 @@
         <v>1</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -25002,7 +25177,7 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E129">
         <v>2</v>
@@ -25014,19 +25189,19 @@
         <v>1</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>7694</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129">
-        <v>7694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -25040,13 +25215,13 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -25078,16 +25253,16 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E131">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F131">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -25116,36 +25291,36 @@
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B133" s="18">
         <v>2026</v>
@@ -25154,7 +25329,7 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -25163,27 +25338,27 @@
         <v>1</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133">
         <v>1</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>5119</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B134" s="18">
         <v>2026</v>
@@ -25192,19 +25367,19 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E134">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -25221,7 +25396,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B135" s="18">
         <v>2026</v>
@@ -25230,7 +25405,7 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -25239,10 +25414,10 @@
         <v>1</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -25259,7 +25434,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B136" s="18">
         <v>2026</v>
@@ -25271,7 +25446,7 @@
         <v>13</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -25280,7 +25455,7 @@
         <v>0</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -25297,7 +25472,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B137" s="18">
         <v>2026</v>
@@ -25306,16 +25481,16 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -25335,7 +25510,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B138" s="18">
         <v>2026</v>
@@ -25344,19 +25519,19 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G138">
         <v>1</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -25382,16 +25557,16 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -25411,7 +25586,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B140" s="18">
         <v>2026</v>
@@ -25420,7 +25595,7 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -25429,27 +25604,27 @@
         <v>3</v>
       </c>
       <c r="G140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140">
-        <v>2124</v>
+        <v>0</v>
       </c>
       <c r="K140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140">
-        <v>2124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B141" s="18">
         <v>2026</v>
@@ -25458,7 +25633,7 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E141">
         <v>3</v>
@@ -25470,7 +25645,7 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -25487,7 +25662,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B142" s="18">
         <v>2026</v>
@@ -25496,31 +25671,31 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142">
-        <v>8458</v>
+        <v>0</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142">
-        <v>8458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -25534,31 +25709,31 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E143">
+        <v>3</v>
+      </c>
+      <c r="F143">
+        <v>3</v>
+      </c>
+      <c r="G143">
+        <v>3</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
         <v>2</v>
       </c>
-      <c r="F143">
+      <c r="J143">
+        <v>10440</v>
+      </c>
+      <c r="K143">
         <v>2</v>
       </c>
-      <c r="G143">
-        <v>1</v>
-      </c>
-      <c r="H143">
-        <v>1</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
       <c r="L143">
-        <v>0</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -25572,7 +25747,7 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E144">
         <v>3</v>
@@ -25584,7 +25759,7 @@
         <v>1</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -25601,7 +25776,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B145" s="18">
         <v>2026</v>
@@ -25610,7 +25785,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -25619,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -25639,7 +25814,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B146" s="18">
         <v>2026</v>
@@ -25648,36 +25823,36 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="E146">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B147" s="18">
         <v>2026</v>
@@ -25686,19 +25861,19 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E147">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -25715,7 +25890,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B148" s="18">
         <v>2026</v>
@@ -25724,16 +25899,16 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -25753,7 +25928,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B149" s="18">
         <v>2026</v>
@@ -25765,16 +25940,16 @@
         <v>13</v>
       </c>
       <c r="E149">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F149">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -25791,7 +25966,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B150" s="18">
         <v>2026</v>
@@ -25800,7 +25975,7 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -25809,10 +25984,10 @@
         <v>1</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -25829,7 +26004,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B151" s="18">
         <v>2026</v>
@@ -25838,19 +26013,19 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -25867,7 +26042,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B152" s="18">
         <v>2026</v>
@@ -25876,19 +26051,19 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G152">
         <v>0</v>
       </c>
       <c r="H152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -25914,19 +26089,19 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G153">
         <v>0</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -25952,7 +26127,7 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -25964,7 +26139,7 @@
         <v>0</v>
       </c>
       <c r="H154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -25981,7 +26156,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B155" s="18">
         <v>2026</v>
@@ -25990,16 +26165,16 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -26019,7 +26194,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B156" s="18">
         <v>2026</v>
@@ -26028,19 +26203,19 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156">
         <v>0</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -26057,7 +26232,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B157" s="18">
         <v>2026</v>
@@ -26066,19 +26241,19 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E157">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F157">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -26095,7 +26270,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B158" s="18">
         <v>2026</v>
@@ -26104,13 +26279,13 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -26142,19 +26317,19 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -26180,7 +26355,7 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -26189,7 +26364,7 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -26209,7 +26384,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B161" s="18">
         <v>2026</v>
@@ -26218,19 +26393,19 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -26247,7 +26422,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B162" s="18">
         <v>2026</v>
@@ -26256,36 +26431,36 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B163" s="18">
         <v>2026</v>
@@ -26294,19 +26469,19 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G163">
         <v>0</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -26323,7 +26498,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B164" s="18">
         <v>2026</v>
@@ -26332,16 +26507,16 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E164">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F164">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -26361,7 +26536,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B165" s="18">
         <v>2026</v>
@@ -26370,19 +26545,19 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G165">
         <v>1</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26408,19 +26583,19 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -26446,13 +26621,13 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E167">
         <v>1</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -26475,7 +26650,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B168" s="18">
         <v>2026</v>
@@ -26484,7 +26659,7 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -26513,7 +26688,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B169" s="18">
         <v>2026</v>
@@ -26522,16 +26697,16 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E169">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F169">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -26551,7 +26726,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B170" s="18">
         <v>2026</v>
@@ -26560,19 +26735,19 @@
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="E170">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G170">
         <v>1</v>
       </c>
       <c r="H170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -26589,42 +26764,42 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D171" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E171">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F171">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171">
-        <v>5560</v>
+        <v>0</v>
       </c>
       <c r="K171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171">
-        <v>5560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D172" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -26633,10 +26808,10 @@
         <v>1</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -26653,7 +26828,7 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -26665,7 +26840,7 @@
         <v>1</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -26685,16 +26860,16 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D174" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -26717,22 +26892,22 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D175" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G175">
         <v>1</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -26749,54 +26924,54 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D176" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E176">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F176">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G176">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H176">
         <v>2</v>
       </c>
       <c r="I176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J176">
-        <v>17492.68</v>
+        <v>5560</v>
       </c>
       <c r="K176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L176">
-        <v>17492.68</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D177" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -26813,22 +26988,22 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D178" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G178">
         <v>1</v>
       </c>
       <c r="H178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -26845,16 +27020,16 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D179" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -26877,33 +27052,257 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>131</v>
+      </c>
+      <c r="D180" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180">
+        <v>2</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>131</v>
+      </c>
+      <c r="D181" t="s">
+        <v>135</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>131</v>
+      </c>
+      <c r="D182" t="s">
+        <v>40</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>131</v>
+      </c>
+      <c r="D183" t="s">
+        <v>60</v>
+      </c>
+      <c r="E183">
+        <v>9</v>
+      </c>
+      <c r="F183">
+        <v>9</v>
+      </c>
+      <c r="G183">
+        <v>6</v>
+      </c>
+      <c r="H183">
+        <v>3</v>
+      </c>
+      <c r="I183">
+        <v>4</v>
+      </c>
+      <c r="J183">
+        <v>25130.799999999999</v>
+      </c>
+      <c r="K183">
+        <v>4</v>
+      </c>
+      <c r="L183">
+        <v>25130.799999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>132</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D184" t="s">
+        <v>135</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>1</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>132</v>
+      </c>
+      <c r="D185" t="s">
+        <v>52</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>1</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>132</v>
+      </c>
+      <c r="D186" t="s">
+        <v>55</v>
+      </c>
+      <c r="E186">
+        <v>2</v>
+      </c>
+      <c r="F186">
+        <v>2</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>132</v>
+      </c>
+      <c r="D187" t="s">
         <v>65</v>
       </c>
-      <c r="E180">
+      <c r="E187">
         <v>4</v>
       </c>
-      <c r="F180">
+      <c r="F187">
         <v>4</v>
       </c>
-      <c r="G180">
-        <v>1</v>
-      </c>
-      <c r="H180">
-        <v>0</v>
-      </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
-      <c r="J180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="L180">
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DE9E8D-8BF5-4A62-904F-2ED5FBEF88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F01F6B-34C7-4890-AE44-69B8746CEAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="139">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1085,64 +1085,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>374.86</v>
+        <v>526.99</v>
       </c>
       <c r="C6" s="5">
-        <v>213.79</v>
+        <v>289.95</v>
       </c>
       <c r="D6" s="5">
-        <v>161.07</v>
+        <v>237.04</v>
       </c>
       <c r="E6" s="5">
-        <v>88965.95</v>
+        <v>122090.129999999</v>
       </c>
       <c r="F6" s="5">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="G6" s="5">
+        <v>27</v>
+      </c>
+      <c r="H6" s="5">
+        <v>211</v>
+      </c>
+      <c r="I6" s="5">
+        <v>82</v>
+      </c>
+      <c r="J6" s="5">
         <v>18</v>
       </c>
-      <c r="H6" s="5">
-        <v>148</v>
-      </c>
-      <c r="I6" s="5">
-        <v>61</v>
-      </c>
-      <c r="J6" s="5">
-        <v>11</v>
-      </c>
       <c r="K6" s="5">
-        <v>535.93945783132494</v>
+        <v>512.98373949579798</v>
       </c>
       <c r="L6" s="5">
-        <v>1458.4581967213101</v>
+        <v>1488.90402439024</v>
       </c>
       <c r="M6" s="5">
-        <v>-20.511386659727599</v>
+        <v>-5.2331912497758601</v>
       </c>
       <c r="N6" s="6">
-        <v>471.31</v>
+        <v>657.92</v>
       </c>
       <c r="O6" s="6">
-        <v>51527.229999999901</v>
+        <v>72081.019999999902</v>
       </c>
       <c r="P6" s="6">
-        <v>286</v>
+        <v>390</v>
       </c>
       <c r="Q6" s="6">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="R6" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="S6" s="6">
-        <v>180.16513986013899</v>
+        <v>184.823128205128</v>
       </c>
       <c r="T6" s="6">
-        <v>769.06313432835805</v>
+        <v>743.10329896907194</v>
       </c>
       <c r="U6" s="6">
-        <v>23.095963047111201</v>
+        <v>127.179457227436</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1157,7 +1157,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1169,7 +1169,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,64 +1177,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>74.489999999999995</v>
+        <v>110.21</v>
       </c>
       <c r="C7" s="5">
-        <v>37.25</v>
+        <v>50.84</v>
       </c>
       <c r="D7" s="5">
-        <v>37.24</v>
+        <v>59.37</v>
       </c>
       <c r="E7" s="5">
-        <v>2728.23</v>
+        <v>3948.2</v>
       </c>
       <c r="F7" s="5">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I7" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="5">
-        <v>75.784166666666593</v>
+        <v>66.918644067796606</v>
       </c>
       <c r="L7" s="5">
-        <v>227.35249999999999</v>
+        <v>219.34444444444401</v>
       </c>
       <c r="M7" s="5">
-        <v>282.66568434479501</v>
+        <v>164.424294615267</v>
       </c>
       <c r="N7" s="6">
-        <v>80.28</v>
+        <v>115.48</v>
       </c>
       <c r="O7" s="6">
-        <v>4859.45</v>
+        <v>6723.18</v>
       </c>
       <c r="P7" s="6">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="Q7" s="6">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="R7" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S7" s="6">
-        <v>48.594499999999996</v>
+        <v>48.022714285714201</v>
       </c>
       <c r="T7" s="6">
-        <v>202.47708333333301</v>
+        <v>176.92578947368401</v>
       </c>
       <c r="U7" s="6">
-        <v>505.19194559055001</v>
+        <v>978.32900502440805</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1249,7 +1249,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1261,7 +1261,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1269,16 +1269,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="C8" s="5">
         <v>4</v>
       </c>
       <c r="D8" s="5">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="E8" s="5">
-        <v>2363.48</v>
+        <v>3383</v>
       </c>
       <c r="F8" s="5">
         <v>2</v>
@@ -1296,37 +1296,37 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1181.74</v>
+        <v>1691.5</v>
       </c>
       <c r="L8" s="5">
-        <v>2363.48</v>
+        <v>3383</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
       <c r="N8" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="6">
-        <v>677.69</v>
+        <v>909.4</v>
       </c>
       <c r="P8" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="6">
         <v>2</v>
       </c>
       <c r="R8" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="6">
-        <v>225.89666666666599</v>
+        <v>227.35</v>
       </c>
       <c r="T8" s="6">
-        <v>338.84500000000003</v>
+        <v>454.7</v>
       </c>
       <c r="U8" s="6">
-        <v>-100</v>
+        <v>46.580162744666801</v>
       </c>
       <c r="V8" s="7">
         <v>12</v>
@@ -1341,7 +1341,7 @@
         <v>7</v>
       </c>
       <c r="Z8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="8">
         <v>10000</v>
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1361,64 +1361,64 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>23</v>
+        <v>37.67</v>
       </c>
       <c r="C9" s="5">
-        <v>12</v>
+        <v>20.67</v>
       </c>
       <c r="D9" s="5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5">
-        <v>9421.2199999999993</v>
+        <v>12975.05</v>
       </c>
       <c r="F9" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I9" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>785.10166666666601</v>
+        <v>865.00333333333299</v>
       </c>
       <c r="L9" s="5">
-        <v>2355.3049999999998</v>
+        <v>2595.0100000000002</v>
       </c>
       <c r="M9" s="5">
-        <v>-100</v>
+        <v>10.126743249544299</v>
       </c>
       <c r="N9" s="6">
-        <v>8.84</v>
+        <v>11.84</v>
       </c>
       <c r="O9" s="6">
-        <v>2137.77</v>
+        <v>2810.4</v>
       </c>
       <c r="P9" s="6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="6">
         <v>2</v>
       </c>
       <c r="R9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="6">
-        <v>118.765</v>
+        <v>133.828571428571</v>
       </c>
       <c r="T9" s="6">
-        <v>1068.885</v>
+        <v>1405.2</v>
       </c>
       <c r="U9" s="6">
-        <v>-16.642108365259102</v>
+        <v>201.91431824651201</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1433,7 +1433,7 @@
         <v>14</v>
       </c>
       <c r="Z9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="8">
         <v>40000</v>
@@ -1445,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1489,7 +1489,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1509,13 +1509,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>46.55</v>
+        <v>65.289999999999907</v>
       </c>
       <c r="O11" s="6">
-        <v>2357.7800000000002</v>
+        <v>3316.08</v>
       </c>
       <c r="P11" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q11" s="6">
         <v>2</v>
@@ -1524,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>392.96333333333303</v>
+        <v>473.72571428571399</v>
       </c>
       <c r="T11" s="6">
-        <v>1178.8900000000001</v>
+        <v>1658.04</v>
       </c>
       <c r="U11" s="6">
-        <v>219.877172594559</v>
+        <v>127.43721502496901</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1551,7 +1551,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1559,26 +1559,26 @@
         <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>4.33</v>
+        <v>5.33</v>
       </c>
       <c r="C12" s="5">
         <v>1.33</v>
       </c>
       <c r="D12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>1611.92</v>
+        <v>2113.67</v>
       </c>
       <c r="F12" s="5">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
         <v>4</v>
       </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5">
-        <v>3</v>
-      </c>
       <c r="I12" s="5">
         <v>1</v>
       </c>
@@ -1586,33 +1586,35 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>402.98</v>
+        <v>422.73399999999998</v>
       </c>
       <c r="L12" s="5">
-        <v>1611.92</v>
+        <v>2113.67</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
       </c>
       <c r="N12" s="6">
-        <v>4.0199999999999996</v>
+        <v>6.02</v>
       </c>
       <c r="O12" s="6">
-        <v>558.27</v>
+        <v>894.27</v>
       </c>
       <c r="P12" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="6">
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>186.09</v>
-      </c>
-      <c r="T12" s="6"/>
+        <v>223.5675</v>
+      </c>
+      <c r="T12" s="6">
+        <v>894.27</v>
+      </c>
       <c r="U12" s="6">
         <v>-100</v>
       </c>
@@ -1641,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1685,7 +1687,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1705,10 +1707,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>6.05</v>
+        <v>10.08</v>
       </c>
       <c r="O14" s="6">
-        <v>646.04</v>
+        <v>937.93</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1735,7 +1737,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>149.44999999999999</v>
+        <v>246.59</v>
       </c>
       <c r="P15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -1770,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>149.44999999999999</v>
+        <v>123.295</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1799,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1807,61 +1809,61 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5">
-        <v>206.59</v>
+        <v>319.56</v>
       </c>
       <c r="F16" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5">
         <v>3</v>
       </c>
       <c r="I16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="5">
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>68.863333333333301</v>
+        <v>79.89</v>
       </c>
       <c r="L16" s="5">
-        <v>206.59</v>
+        <v>159.78</v>
       </c>
       <c r="M16" s="5">
         <v>-100</v>
       </c>
       <c r="N16" s="6">
-        <v>12</v>
+        <v>21.99</v>
       </c>
       <c r="O16" s="6">
-        <v>3604.18</v>
+        <v>5039.53</v>
       </c>
       <c r="P16" s="6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>189.69368421052599</v>
+        <v>193.828076923076</v>
       </c>
       <c r="T16" s="6">
-        <v>901.04499999999996</v>
+        <v>839.92166666666606</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1891,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1911,24 +1913,26 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>34.67</v>
+        <v>49.67</v>
       </c>
       <c r="O17" s="6">
-        <v>2443.11</v>
+        <v>3486.23</v>
       </c>
       <c r="P17" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="6">
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>305.38875000000002</v>
-      </c>
-      <c r="T17" s="6"/>
+        <v>290.51916666666602</v>
+      </c>
+      <c r="T17" s="6">
+        <v>3486.23</v>
+      </c>
       <c r="U17" s="6">
         <v>-100</v>
       </c>
@@ -1951,7 +1955,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1974,21 +1978,23 @@
         <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>469.8</v>
+        <v>697.34</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="6">
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>156.6</v>
-      </c>
-      <c r="T18" s="6"/>
+        <v>232.446666666666</v>
+      </c>
+      <c r="T18" s="6">
+        <v>697.34</v>
+      </c>
       <c r="U18" s="6">
         <v>-100</v>
       </c>
@@ -2015,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2035,10 +2041,10 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="6">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="O19" s="6">
-        <v>615.72</v>
+        <v>915.43</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2065,7 +2071,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2085,10 +2091,10 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O20" s="6">
-        <v>1023.67</v>
+        <v>1398.67</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2115,7 +2121,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2123,16 +2129,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>28.99</v>
+        <v>36</v>
       </c>
       <c r="C21" s="5">
-        <v>17</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="D21" s="5">
-        <v>11.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="E21" s="5">
-        <v>4931.37</v>
+        <v>5143.7299999999996</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2161,7 +2167,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2207,7 +2213,7 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2219,19 +2225,19 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5">
         <v>8</v>
       </c>
       <c r="J23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -2257,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2265,25 +2271,25 @@
         <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>42.95</v>
+        <v>62.11</v>
       </c>
       <c r="C24" s="5">
-        <v>40.950000000000003</v>
+        <v>58.12</v>
       </c>
       <c r="D24" s="5">
-        <v>2</v>
+        <v>3.99</v>
       </c>
       <c r="E24" s="5">
-        <v>9254.59</v>
+        <v>12830.88</v>
       </c>
       <c r="F24" s="5">
+        <v>8</v>
+      </c>
+      <c r="G24" s="5">
         <v>5</v>
       </c>
-      <c r="G24" s="5">
-        <v>4</v>
-      </c>
       <c r="H24" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="5">
         <v>2</v>
@@ -2292,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>1850.9179999999999</v>
+        <v>1603.86</v>
       </c>
       <c r="L24" s="5">
-        <v>4627.2950000000001</v>
+        <v>6415.44</v>
       </c>
       <c r="M24" s="5">
-        <v>-16.862875610913001</v>
+        <v>-40.035289863205001</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2323,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2331,25 +2337,25 @@
         <v>41</v>
       </c>
       <c r="B25" s="5">
+        <v>9.67</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5">
         <v>7.67</v>
       </c>
-      <c r="C25" s="5">
-        <v>2</v>
-      </c>
-      <c r="D25" s="5">
-        <v>5.67</v>
-      </c>
       <c r="E25" s="5">
-        <v>1612.91</v>
+        <v>2257.33</v>
       </c>
       <c r="F25" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="5">
         <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I25" s="5">
         <v>1</v>
@@ -2358,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>322.58199999999999</v>
+        <v>322.47571428571399</v>
       </c>
       <c r="L25" s="5">
-        <v>1612.91</v>
+        <v>2257.33</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
@@ -2370,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="O25" s="6">
-        <v>713.24</v>
+        <v>1000.54</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -2403,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2411,46 +2417,46 @@
         <v>42</v>
       </c>
       <c r="B26" s="5">
-        <v>3.46</v>
+        <v>5.46</v>
       </c>
       <c r="C26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>3.46</v>
+        <v>4.46</v>
       </c>
       <c r="E26" s="5">
-        <v>1513.89</v>
+        <v>2440.33</v>
       </c>
       <c r="F26" s="5">
+        <v>5</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5">
+        <v>4</v>
+      </c>
+      <c r="I26" s="5">
         <v>3</v>
       </c>
-      <c r="G26" s="5">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5">
-        <v>3</v>
-      </c>
-      <c r="I26" s="5">
-        <v>1</v>
-      </c>
       <c r="J26" s="5">
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>504.63</v>
+        <v>488.06599999999997</v>
       </c>
       <c r="L26" s="5">
-        <v>1513.89</v>
+        <v>813.44333333333304</v>
       </c>
       <c r="M26" s="5">
         <v>-100</v>
       </c>
       <c r="N26" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="6">
-        <v>359.08</v>
+        <v>403.72</v>
       </c>
       <c r="P26" s="6">
         <v>4</v>
@@ -2462,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>89.77</v>
+        <v>100.93</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
@@ -2493,7 +2499,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2501,16 +2507,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="C27" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5">
         <v>1.5</v>
       </c>
       <c r="E27" s="5">
-        <v>2845.02</v>
+        <v>4075.71</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -2522,41 +2528,43 @@
         <v>1</v>
       </c>
       <c r="I27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>2845.02</v>
-      </c>
-      <c r="L27" s="5"/>
+        <v>4075.71</v>
+      </c>
+      <c r="L27" s="5">
+        <v>4075.71</v>
+      </c>
       <c r="M27" s="5">
-        <v>-100</v>
+        <v>99.130948963493395</v>
       </c>
       <c r="N27" s="6">
-        <v>13.33</v>
+        <v>22.33</v>
       </c>
       <c r="O27" s="6">
-        <v>2893.14</v>
+        <v>4177.1400000000003</v>
       </c>
       <c r="P27" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R27" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" s="6">
-        <v>361.64249999999998</v>
+        <v>298.36714285714203</v>
       </c>
       <c r="T27" s="6">
-        <v>578.62799999999902</v>
+        <v>696.19</v>
       </c>
       <c r="U27" s="6">
-        <v>62.8680257436556</v>
+        <v>254.33334769722799</v>
       </c>
       <c r="V27" s="7">
         <v>66.569999999999993</v>
@@ -2571,7 +2579,7 @@
         <v>20</v>
       </c>
       <c r="Z27" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="8">
         <v>12000</v>
@@ -2583,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="AD27" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2603,13 +2611,13 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="6">
-        <v>11.67</v>
+        <v>14.67</v>
       </c>
       <c r="O28" s="6">
-        <v>840.01</v>
+        <v>1212.93</v>
       </c>
       <c r="P28" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q28" s="6">
         <v>1</v>
@@ -2618,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>105.00125</v>
+        <v>134.77000000000001</v>
       </c>
       <c r="T28" s="6">
-        <v>840.01</v>
+        <v>1212.93</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
@@ -2645,7 +2653,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2653,64 +2661,64 @@
         <v>45</v>
       </c>
       <c r="B29" s="5">
-        <v>8.99</v>
+        <v>14.66</v>
       </c>
       <c r="C29" s="5">
-        <v>2</v>
+        <v>4.67</v>
       </c>
       <c r="D29" s="5">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="E29" s="5">
-        <v>2923.57</v>
+        <v>4394.24</v>
       </c>
       <c r="F29" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
       </c>
       <c r="H29" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I29" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="5">
         <v>1</v>
       </c>
       <c r="K29" s="5">
-        <v>324.84111111111099</v>
+        <v>366.18666666666599</v>
       </c>
       <c r="L29" s="5">
-        <v>1461.7850000000001</v>
+        <v>1464.7466666666601</v>
       </c>
       <c r="M29" s="5">
-        <v>75.094148592303199</v>
+        <v>16.493409554325599</v>
       </c>
       <c r="N29" s="6">
         <v>11.58</v>
       </c>
       <c r="O29" s="6">
-        <v>1367.6</v>
+        <v>1912.87</v>
       </c>
       <c r="P29" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q29" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R29" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S29" s="6">
-        <v>151.95555555555501</v>
+        <v>173.897272727272</v>
       </c>
       <c r="T29" s="6">
-        <v>273.52</v>
+        <v>318.81166666666599</v>
       </c>
       <c r="U29" s="6">
-        <v>980.59081602807805</v>
+        <v>1051.1142942280401</v>
       </c>
       <c r="V29" s="7">
         <v>55.58</v>
@@ -2725,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="Z29" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA29" s="8">
         <v>13000</v>
@@ -2737,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2757,13 +2765,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>18.52</v>
+        <v>31.509999999999899</v>
       </c>
       <c r="O30" s="6">
-        <v>1594.87</v>
+        <v>2205.4</v>
       </c>
       <c r="P30" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -2772,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>227.83857142857099</v>
+        <v>275.67500000000001</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
@@ -2797,7 +2805,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2817,13 +2825,13 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="6">
-        <v>26.03</v>
+        <v>35.04</v>
       </c>
       <c r="O31" s="6">
-        <v>1895.52</v>
+        <v>2670.65</v>
       </c>
       <c r="P31" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="6">
         <v>1</v>
@@ -2832,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>473.88</v>
+        <v>534.13</v>
       </c>
       <c r="T31" s="6">
-        <v>1895.52</v>
+        <v>2670.65</v>
       </c>
       <c r="U31" s="6">
         <v>-100</v>
@@ -2859,7 +2867,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2867,25 +2875,25 @@
         <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>23.44</v>
+        <v>30.93</v>
       </c>
       <c r="C32" s="5">
-        <v>13.94</v>
+        <v>18.43</v>
       </c>
       <c r="D32" s="5">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="E32" s="5">
-        <v>7019.08</v>
+        <v>9000.58</v>
       </c>
       <c r="F32" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G32" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I32" s="5">
         <v>3</v>
@@ -2894,22 +2902,22 @@
         <v>1</v>
       </c>
       <c r="K32" s="5">
-        <v>638.09818181818105</v>
+        <v>600.03866666666602</v>
       </c>
       <c r="L32" s="5">
-        <v>2339.69333333333</v>
+        <v>3000.19333333333</v>
       </c>
       <c r="M32" s="5">
-        <v>18.477065370390399</v>
+        <v>-7.6059542829462004</v>
       </c>
       <c r="N32" s="6">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="O32" s="6">
-        <v>2584.15</v>
+        <v>3792.62</v>
       </c>
       <c r="P32" s="6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q32" s="6">
         <v>3</v>
@@ -2918,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="6">
-        <v>258.41500000000002</v>
+        <v>210.701111111111</v>
       </c>
       <c r="T32" s="6">
-        <v>861.38333333333298</v>
+        <v>1264.2066666666601</v>
       </c>
       <c r="U32" s="6">
         <v>-100</v>
@@ -2951,7 +2959,7 @@
         <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2959,40 +2967,40 @@
         <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>22.69</v>
+        <v>31.16</v>
       </c>
       <c r="C33" s="5">
-        <v>6.97</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="D33" s="5">
-        <v>15.72</v>
+        <v>21.71</v>
       </c>
       <c r="E33" s="5">
-        <v>7014.42</v>
+        <v>10018.93</v>
       </c>
       <c r="F33" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
       </c>
       <c r="H33" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I33" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J33" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" s="5">
-        <v>584.53499999999997</v>
+        <v>589.34882352941099</v>
       </c>
       <c r="L33" s="5">
-        <v>1753.605</v>
+        <v>1252.36625</v>
       </c>
       <c r="M33" s="5">
-        <v>20.580176265464502</v>
+        <v>142.11288031755799</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3017,7 +3025,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3025,40 +3033,40 @@
         <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>25.85</v>
+        <v>41.09</v>
       </c>
       <c r="C34" s="5">
-        <v>10.85</v>
+        <v>16.59</v>
       </c>
       <c r="D34" s="5">
-        <v>15</v>
+        <v>24.5</v>
       </c>
       <c r="E34" s="5">
-        <v>7841.68</v>
+        <v>9971.42</v>
       </c>
       <c r="F34" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G34" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I34" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="5">
-        <v>603.20615384615303</v>
+        <v>453.24636363636301</v>
       </c>
       <c r="L34" s="5">
-        <v>1306.9466666666599</v>
+        <v>1424.4885714285699</v>
       </c>
       <c r="M34" s="5">
-        <v>-29.0968261903061</v>
+        <v>-41.242069835590101</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3083,7 +3091,7 @@
         <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3091,64 +3099,64 @@
         <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>24.32</v>
+        <v>31.32</v>
       </c>
       <c r="C35" s="5">
-        <v>20.49</v>
+        <v>23.49</v>
       </c>
       <c r="D35" s="5">
-        <v>3.83</v>
+        <v>7.83</v>
       </c>
       <c r="E35" s="5">
-        <v>6272.81</v>
+        <v>8878.7999999999993</v>
       </c>
       <c r="F35" s="5">
+        <v>14</v>
+      </c>
+      <c r="G35" s="5">
+        <v>5</v>
+      </c>
+      <c r="H35" s="5">
         <v>9</v>
       </c>
-      <c r="G35" s="5">
-        <v>4</v>
-      </c>
-      <c r="H35" s="5">
-        <v>5</v>
-      </c>
       <c r="I35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="5">
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>696.97888888888895</v>
+        <v>634.19999999999902</v>
       </c>
       <c r="L35" s="5">
-        <v>3136.4050000000002</v>
+        <v>2959.6</v>
       </c>
       <c r="M35" s="5">
         <v>-100</v>
       </c>
       <c r="N35" s="6">
-        <v>16.05</v>
+        <v>23.59</v>
       </c>
       <c r="O35" s="6">
-        <v>5726.9</v>
+        <v>8155.36</v>
       </c>
       <c r="P35" s="6">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Q35" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R35" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S35" s="6">
-        <v>248.99565217391299</v>
+        <v>239.86352941176401</v>
       </c>
       <c r="T35" s="6">
-        <v>954.48333333333301</v>
+        <v>741.39636363636305</v>
       </c>
       <c r="U35" s="6">
-        <v>-100</v>
+        <v>185.92447175845001</v>
       </c>
       <c r="V35" s="7">
         <v>110.24</v>
@@ -3163,7 +3171,7 @@
         <v>45</v>
       </c>
       <c r="Z35" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA35" s="8">
         <v>35000</v>
@@ -3175,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="AD35" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3195,13 +3203,13 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="6">
-        <v>50.73</v>
+        <v>69.86</v>
       </c>
       <c r="O36" s="6">
-        <v>1677.96</v>
+        <v>2455.0700000000002</v>
       </c>
       <c r="P36" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -3210,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="6">
-        <v>239.70857142857099</v>
+        <v>306.88375000000002</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6">
@@ -3235,7 +3243,7 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3243,25 +3251,25 @@
         <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>6</v>
+        <v>9.34</v>
       </c>
       <c r="C37" s="5">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="D37" s="5">
-        <v>3</v>
+        <v>5.01</v>
       </c>
       <c r="E37" s="5">
-        <v>1787.66</v>
+        <v>2671.04</v>
       </c>
       <c r="F37" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" s="5">
         <v>0</v>
       </c>
       <c r="H37" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="5">
         <v>1</v>
@@ -3270,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>893.83</v>
+        <v>667.76</v>
       </c>
       <c r="L37" s="5">
-        <v>1787.66</v>
+        <v>2671.04</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
@@ -3301,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="AD37" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3309,64 +3317,64 @@
         <v>58</v>
       </c>
       <c r="B38" s="5">
-        <v>19.98</v>
+        <v>26.49</v>
       </c>
       <c r="C38" s="5">
-        <v>15.48</v>
+        <v>19.489999999999998</v>
       </c>
       <c r="D38" s="5">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E38" s="5">
-        <v>4510.46</v>
+        <v>6301.03</v>
       </c>
       <c r="F38" s="5">
+        <v>5</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1</v>
+      </c>
+      <c r="H38" s="5">
+        <v>4</v>
+      </c>
+      <c r="I38" s="5">
         <v>3</v>
       </c>
-      <c r="G38" s="5">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
-        <v>3</v>
-      </c>
-      <c r="I38" s="5">
-        <v>2</v>
-      </c>
       <c r="J38" s="5">
         <v>0</v>
       </c>
       <c r="K38" s="5">
-        <v>1503.4866666666601</v>
+        <v>1260.2059999999999</v>
       </c>
       <c r="L38" s="5">
-        <v>2255.23</v>
+        <v>2100.3433333333301</v>
       </c>
       <c r="M38" s="5">
         <v>-100</v>
       </c>
       <c r="N38" s="6">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="O38" s="6">
-        <v>2521.15</v>
+        <v>3457.68</v>
       </c>
       <c r="P38" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q38" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="6">
-        <v>210.09583333333299</v>
+        <v>181.983157894736</v>
       </c>
       <c r="T38" s="6">
-        <v>504.23</v>
+        <v>493.95428571428499</v>
       </c>
       <c r="U38" s="6">
-        <v>-100</v>
+        <v>147.33347215473901</v>
       </c>
       <c r="V38" s="7">
         <v>42.5</v>
@@ -3381,7 +3389,7 @@
         <v>24</v>
       </c>
       <c r="Z38" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" s="8">
         <v>17000</v>
@@ -3393,7 +3401,7 @@
         <v>16</v>
       </c>
       <c r="AD38" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3413,24 +3421,26 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="6">
-        <v>20</v>
+        <v>30.34</v>
       </c>
       <c r="O39" s="6">
-        <v>1343.35</v>
+        <v>1949.86</v>
       </c>
       <c r="P39" s="6">
         <v>2</v>
       </c>
       <c r="Q39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="6">
         <v>0</v>
       </c>
       <c r="S39" s="6">
-        <v>671.67499999999995</v>
-      </c>
-      <c r="T39" s="6"/>
+        <v>974.93</v>
+      </c>
+      <c r="T39" s="6">
+        <v>1949.86</v>
+      </c>
       <c r="U39" s="6">
         <v>-100</v>
       </c>
@@ -3453,7 +3463,7 @@
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3461,30 +3471,46 @@
         <v>31</v>
       </c>
       <c r="B40" s="5">
+        <v>9.17</v>
+      </c>
+      <c r="C40" s="5">
         <v>5.67</v>
       </c>
-      <c r="C40" s="5">
-        <v>3.67</v>
-      </c>
       <c r="D40" s="5">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E40" s="5">
-        <v>4141.84</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
+        <v>5837.63</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5">
+        <v>1</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <v>5837.63</v>
+      </c>
+      <c r="L40" s="5">
+        <v>5837.63</v>
+      </c>
+      <c r="M40" s="5">
+        <v>-100</v>
+      </c>
       <c r="N40" s="6">
         <v>0.98</v>
       </c>
       <c r="O40" s="6">
-        <v>243.69</v>
+        <v>331.81</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -3507,7 +3533,7 @@
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
@@ -3515,49 +3541,49 @@
         <v>60</v>
       </c>
       <c r="B41">
-        <v>13.87</v>
+        <v>18.87</v>
       </c>
       <c r="C41">
-        <v>5.87</v>
+        <v>7.87</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E41">
-        <v>4161.45</v>
+        <v>6062.59</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G41">
         <v>3</v>
       </c>
       <c r="H41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>4</v>
       </c>
       <c r="K41">
-        <v>297.246428571428</v>
+        <v>378.91187500000001</v>
       </c>
       <c r="L41">
-        <v>520.18124999999998</v>
+        <v>673.62111111111096</v>
       </c>
       <c r="M41">
-        <v>503.89527688666197</v>
+        <v>314.52250605764198</v>
       </c>
       <c r="N41">
-        <v>13.02</v>
+        <v>17.16</v>
       </c>
       <c r="O41">
-        <v>1947.61</v>
+        <v>2992.72</v>
       </c>
       <c r="P41">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -3566,13 +3592,13 @@
         <v>1</v>
       </c>
       <c r="S41">
-        <v>149.81615384615299</v>
+        <v>157.51157894736801</v>
       </c>
       <c r="T41">
-        <v>649.20333333333303</v>
+        <v>997.57333333333304</v>
       </c>
       <c r="U41">
-        <v>167.23933436365499</v>
+        <v>73.914699671202101</v>
       </c>
       <c r="V41">
         <v>52.03</v>
@@ -3599,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="AD41" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
@@ -3607,22 +3633,25 @@
         <v>61</v>
       </c>
       <c r="N42">
-        <v>26.51</v>
+        <v>36.56</v>
       </c>
       <c r="O42">
-        <v>1825.75</v>
+        <v>2668.87</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>304.291666666666</v>
+        <v>333.60874999999999</v>
+      </c>
+      <c r="T42">
+        <v>2668.87</v>
       </c>
       <c r="U42">
         <v>-100</v>
@@ -3643,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="AD42" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
@@ -3651,16 +3680,16 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>10.66</v>
+        <v>13.66</v>
       </c>
       <c r="C43">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="D43">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="E43">
-        <v>2674.19</v>
+        <v>3750.22</v>
       </c>
       <c r="F43">
         <v>4</v>
@@ -3678,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>668.54750000000001</v>
+        <v>937.55499999999995</v>
       </c>
       <c r="L43">
-        <v>2674.19</v>
+        <v>3750.22</v>
       </c>
       <c r="M43">
         <v>-100</v>
@@ -3690,7 +3719,7 @@
         <v>6.0299999999999896</v>
       </c>
       <c r="O43">
-        <v>1058.1199999999999</v>
+        <v>1415.24</v>
       </c>
       <c r="P43">
         <v>8</v>
@@ -3702,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="S43">
-        <v>132.26499999999999</v>
+        <v>176.905</v>
       </c>
       <c r="T43">
-        <v>352.70666666666602</v>
+        <v>471.74666666666599</v>
       </c>
       <c r="U43">
         <v>-100</v>
@@ -3735,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="AD43" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
@@ -3743,10 +3772,10 @@
         <v>66</v>
       </c>
       <c r="N44">
-        <v>17.690000000000001</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="O44">
-        <v>1058.29</v>
+        <v>1569.62</v>
       </c>
       <c r="P44">
         <v>4</v>
@@ -3758,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>264.57249999999999</v>
+        <v>392.40499999999997</v>
       </c>
       <c r="T44">
-        <v>1058.29</v>
+        <v>1569.62</v>
       </c>
       <c r="U44">
         <v>-100</v>
@@ -3782,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
@@ -3790,10 +3819,10 @@
         <v>137</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -4895,43 +4924,43 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F21" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H21" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" s="10">
-        <v>0</v>
+        <v>14289</v>
       </c>
       <c r="J21" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" s="10">
-        <v>0</v>
+        <v>14289</v>
       </c>
       <c r="L21" s="10">
-        <v>11.45</v>
+        <v>10.08</v>
       </c>
       <c r="M21" s="10">
-        <v>0</v>
+        <v>12.35</v>
       </c>
       <c r="N21" s="10">
-        <v>42.11</v>
+        <v>41.67</v>
       </c>
       <c r="O21" s="10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P21" s="10">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -4945,10 +4974,10 @@
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="10">
         <v>1</v>
@@ -4969,13 +4998,13 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
       </c>
       <c r="N22" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O22" s="10">
         <v>0</v>
@@ -4995,16 +5024,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E23" s="10">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F23" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G23" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="10">
         <v>2</v>
@@ -5019,19 +5048,19 @@
         <v>12813</v>
       </c>
       <c r="L23" s="10">
-        <v>9.64</v>
+        <v>11.76</v>
       </c>
       <c r="M23" s="10">
-        <v>18.12</v>
+        <v>11.07</v>
       </c>
       <c r="N23" s="10">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="O23" s="10">
-        <v>25</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P23" s="10">
-        <v>12.5</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -5045,7 +5074,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
@@ -5054,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
@@ -5069,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -5093,13 +5122,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="10">
         <v>1</v>
@@ -5117,13 +5146,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -5143,10 +5172,10 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E26" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" s="10">
         <v>4</v>
@@ -5155,31 +5184,31 @@
         <v>0</v>
       </c>
       <c r="H26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="10">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="J26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="10">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="L26" s="10">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="M26" s="10">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N26" s="10">
-        <v>44.44</v>
+        <v>30.77</v>
       </c>
       <c r="O26" s="10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P26" s="10">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -5193,43 +5222,43 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E27" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F27" s="10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G27" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="10">
-        <v>18898</v>
+        <v>27014</v>
       </c>
       <c r="J27" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="10">
-        <v>18898</v>
+        <v>27014</v>
       </c>
       <c r="L27" s="10">
-        <v>9.64</v>
+        <v>8.4</v>
       </c>
       <c r="M27" s="10">
-        <v>26.72</v>
+        <v>23.35</v>
       </c>
       <c r="N27" s="10">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O27" s="10">
-        <v>37.5</v>
+        <v>30.77</v>
       </c>
       <c r="P27" s="10">
-        <v>18.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5243,17 +5272,17 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E28" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F28" s="10">
+        <v>5</v>
+      </c>
+      <c r="G28" s="10">
         <v>3</v>
       </c>
-      <c r="G28" s="10">
-        <v>1</v>
-      </c>
       <c r="H28" s="10">
         <v>0</v>
       </c>
@@ -5267,13 +5296,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>5.42</v>
+        <v>5.04</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -5293,13 +5322,13 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E29" s="10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F29" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="10">
         <v>9</v>
@@ -5317,15 +5346,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>11.45</v>
+        <v>13.45</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10"/>
+        <v>3.12</v>
+      </c>
+      <c r="O29" s="10">
+        <v>0</v>
+      </c>
       <c r="P29" s="10">
         <v>0</v>
       </c>
@@ -5341,16 +5372,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E30" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="10">
         <v>1</v>
@@ -5365,19 +5396,19 @@
         <v>8316</v>
       </c>
       <c r="L30" s="10">
-        <v>13.25</v>
+        <v>11.76</v>
       </c>
       <c r="M30" s="10">
-        <v>11.76</v>
+        <v>7.19</v>
       </c>
       <c r="N30" s="10">
-        <v>27.27</v>
+        <v>32.14</v>
       </c>
       <c r="O30" s="10">
-        <v>16.670000000000002</v>
+        <v>11.11</v>
       </c>
       <c r="P30" s="10">
-        <v>4.55</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5391,43 +5422,43 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E31" s="10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F31" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G31" s="10">
         <v>3</v>
       </c>
       <c r="H31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="10">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="J31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="10">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="L31" s="10">
-        <v>9.64</v>
+        <v>12.18</v>
       </c>
       <c r="M31" s="10">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="N31" s="10">
-        <v>31.25</v>
+        <v>27.59</v>
       </c>
       <c r="O31" s="10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P31" s="10">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -5441,43 +5472,43 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F32" s="10">
         <v>6</v>
       </c>
       <c r="G32" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="10">
-        <v>5560</v>
+        <v>5859</v>
       </c>
       <c r="J32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="10">
-        <v>5560</v>
+        <v>5859</v>
       </c>
       <c r="L32" s="10">
-        <v>6.02</v>
+        <v>4.62</v>
       </c>
       <c r="M32" s="10">
-        <v>7.86</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="N32" s="10">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="O32" s="10">
-        <v>16.670000000000002</v>
+        <v>33.33</v>
       </c>
       <c r="P32" s="10">
-        <v>10</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5491,13 +5522,13 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -5515,13 +5546,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>20</v>
+        <v>28.57</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
@@ -5541,13 +5572,13 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E34" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F34" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G34" s="10">
         <v>3</v>
@@ -5565,19 +5596,19 @@
         <v>25130.799999999999</v>
       </c>
       <c r="L34" s="10">
-        <v>7.83</v>
+        <v>6.3</v>
       </c>
       <c r="M34" s="10">
-        <v>35.54</v>
+        <v>21.72</v>
       </c>
       <c r="N34" s="10">
-        <v>53.85</v>
+        <v>60</v>
       </c>
       <c r="O34" s="10">
-        <v>57.14</v>
+        <v>44.44</v>
       </c>
       <c r="P34" s="10">
-        <v>30.77</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5591,43 +5622,43 @@
         <v>18</v>
       </c>
       <c r="D35" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E35" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G35" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="10">
-        <v>0</v>
+        <v>7483.12</v>
       </c>
       <c r="J35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="10">
-        <v>0</v>
+        <v>7483.12</v>
       </c>
       <c r="L35" s="10">
-        <v>4.82</v>
+        <v>4.2</v>
       </c>
       <c r="M35" s="10">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="N35" s="10">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="O35" s="10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P35" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5745,7 +5776,7 @@
         <v>425.17</v>
       </c>
       <c r="G6" s="5">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H6" s="5">
         <v>110</v>
@@ -5850,7 +5881,7 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H9" s="5">
         <v>105</v>
@@ -6060,7 +6091,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -6200,10 +6231,10 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H19" s="5">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I19" s="5">
         <v>53</v>
@@ -6235,16 +6266,16 @@
         <v>293.32</v>
       </c>
       <c r="G20" s="10">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H20" s="10">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I20" s="10">
         <v>30</v>
       </c>
       <c r="J20" s="10">
-        <v>240258.52</v>
+        <v>240308.52</v>
       </c>
       <c r="K20" s="10">
         <v>26.36</v>
@@ -6261,19 +6292,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1002</v>
+        <v>1399</v>
       </c>
       <c r="E21" s="10">
-        <v>2728.23</v>
+        <v>3948.2</v>
       </c>
       <c r="F21" s="10">
-        <v>74.489999999999995</v>
+        <v>110.21</v>
       </c>
       <c r="G21" s="10">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="H21" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I21" s="10">
         <v>2</v>
@@ -6282,7 +6313,7 @@
         <v>10440</v>
       </c>
       <c r="K21" s="10">
-        <v>2.83</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6585,7 +6616,7 @@
         <v>14.33</v>
       </c>
       <c r="G30" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="10">
         <v>7</v>
@@ -6856,13 +6887,13 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="E38" s="10">
-        <v>2363.48</v>
+        <v>3383</v>
       </c>
       <c r="F38" s="10">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="G38" s="10">
         <v>2</v>
@@ -7110,10 +7141,10 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G45" s="10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H45" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I45" s="10">
         <v>7</v>
@@ -7425,10 +7456,10 @@
         <v>162.57</v>
       </c>
       <c r="G54" s="10">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" s="10">
         <v>7</v>
@@ -7451,28 +7482,28 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>758</v>
+        <v>1088</v>
       </c>
       <c r="E55" s="10">
-        <v>9421.2199999999993</v>
+        <v>12975.05</v>
       </c>
       <c r="F55" s="10">
-        <v>23</v>
+        <v>37.67</v>
       </c>
       <c r="G55" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H55" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I55" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="10">
-        <v>0</v>
+        <v>14289</v>
       </c>
       <c r="K55" s="10">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -8211,16 +8242,16 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E77" s="10">
-        <v>1611.92</v>
+        <v>2113.67</v>
       </c>
       <c r="F77" s="10">
-        <v>4.33</v>
+        <v>5.33</v>
       </c>
       <c r="G77" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H77" s="10">
         <v>1</v>
@@ -8946,13 +8977,13 @@
         <v>13</v>
       </c>
       <c r="I99" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="10">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="K99" s="10">
-        <v>-1</v>
+        <v>-0.57999999999999996</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
@@ -8966,19 +8997,29 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>322</v>
+        <v>452</v>
       </c>
       <c r="E100" s="10">
-        <v>4141.84</v>
+        <v>5837.63</v>
       </c>
       <c r="F100" s="10">
-        <v>5.67</v>
-      </c>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
+        <v>9.17</v>
+      </c>
+      <c r="G100" s="10">
+        <v>1</v>
+      </c>
+      <c r="H100" s="10">
+        <v>1</v>
+      </c>
+      <c r="I100" s="10">
+        <v>0</v>
+      </c>
+      <c r="J100" s="10">
+        <v>0</v>
+      </c>
+      <c r="K100" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
@@ -9880,10 +9921,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H127" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -10081,19 +10122,19 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E133" s="10">
-        <v>206.59</v>
+        <v>319.56</v>
       </c>
       <c r="F133" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G133" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H133" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I133" s="10">
         <v>0</v>
@@ -10545,7 +10586,7 @@
         <v>7.83</v>
       </c>
       <c r="G146" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H146" s="10">
         <v>4</v>
@@ -11644,7 +11685,7 @@
         <v>65.849999999999994</v>
       </c>
       <c r="G179" s="10">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H179" s="10">
         <v>15</v>
@@ -11916,28 +11957,28 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="E187" s="10">
-        <v>4931.37</v>
+        <v>5143.7299999999996</v>
       </c>
       <c r="F187" s="10">
-        <v>28.99</v>
+        <v>36</v>
       </c>
       <c r="G187" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H187" s="10">
         <v>8</v>
       </c>
       <c r="I187" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="10">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="K187" s="10">
-        <v>-1</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -12061,16 +12102,16 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>20803</v>
+        <v>28926</v>
       </c>
       <c r="E192" s="10">
-        <v>9254.59</v>
+        <v>12830.88</v>
       </c>
       <c r="F192" s="10">
-        <v>42.95</v>
+        <v>62.11</v>
       </c>
       <c r="G192" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H192" s="10">
         <v>3</v>
@@ -12082,7 +12123,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.17</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12646,16 +12687,16 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="E209" s="10">
-        <v>1612.91</v>
+        <v>2257.33</v>
       </c>
       <c r="F209" s="10">
-        <v>7.67</v>
+        <v>9.67</v>
       </c>
       <c r="G209" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H209" s="10">
         <v>1</v>
@@ -13241,19 +13282,19 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="E226" s="10">
-        <v>1513.89</v>
+        <v>2440.33</v>
       </c>
       <c r="F226" s="10">
-        <v>3.46</v>
+        <v>5.46</v>
       </c>
       <c r="G226" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H226" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I226" s="10">
         <v>0</v>
@@ -13836,28 +13877,28 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>264</v>
+        <v>381</v>
       </c>
       <c r="E243" s="10">
-        <v>2845.02</v>
+        <v>4075.71</v>
       </c>
       <c r="F243" s="10">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G243" s="10">
         <v>1</v>
       </c>
       <c r="H243" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" s="10">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K243" s="10">
-        <v>-1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
@@ -14641,19 +14682,19 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>238</v>
+        <v>376</v>
       </c>
       <c r="E266" s="10">
-        <v>2923.57</v>
+        <v>4394.24</v>
       </c>
       <c r="F266" s="10">
-        <v>8.99</v>
+        <v>14.66</v>
       </c>
       <c r="G266" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H266" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I266" s="10">
         <v>1</v>
@@ -14662,7 +14703,7 @@
         <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>0.75</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15505,7 +15546,7 @@
         <v>22.8</v>
       </c>
       <c r="G293" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H293" s="10">
         <v>12</v>
@@ -15890,19 +15931,19 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H304" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I304" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J304" s="10">
-        <v>31377</v>
+        <v>39633</v>
       </c>
       <c r="K304" s="10">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
@@ -15916,16 +15957,16 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>572</v>
+        <v>749</v>
       </c>
       <c r="E305" s="10">
-        <v>7019.08</v>
+        <v>9000.58</v>
       </c>
       <c r="F305" s="10">
-        <v>23.439999999999898</v>
+        <v>30.93</v>
       </c>
       <c r="G305" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H305" s="10">
         <v>3</v>
@@ -15937,7 +15978,7 @@
         <v>8316</v>
       </c>
       <c r="K305" s="10">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16160,19 +16201,19 @@
         <v>110.71</v>
       </c>
       <c r="G312" s="10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H312" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I312" s="10">
         <v>10</v>
       </c>
       <c r="J312" s="10">
-        <v>66845.959999999905</v>
+        <v>67220.959999999905</v>
       </c>
       <c r="K312" s="10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
@@ -16186,28 +16227,28 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>1260</v>
+        <v>1752</v>
       </c>
       <c r="E313" s="10">
-        <v>7014.42</v>
+        <v>10018.93</v>
       </c>
       <c r="F313" s="10">
-        <v>22.69</v>
+        <v>31.16</v>
       </c>
       <c r="G313" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H313" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I313" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J313" s="10">
-        <v>8458</v>
+        <v>24257.119999999999</v>
       </c>
       <c r="K313" s="10">
-        <v>0.21</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16443,7 +16484,7 @@
         <v>86</v>
       </c>
       <c r="H320" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I320" s="10">
         <v>7</v>
@@ -16466,28 +16507,28 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>1983</v>
+        <v>2630</v>
       </c>
       <c r="E321" s="10">
-        <v>7841.68</v>
+        <v>9971.42</v>
       </c>
       <c r="F321" s="10">
-        <v>25.85</v>
+        <v>41.09</v>
       </c>
       <c r="G321" s="10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H321" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I321" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J321" s="10">
-        <v>5560</v>
+        <v>5859</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.28999999999999998</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16570,7 +16611,7 @@
         <v>237.06</v>
       </c>
       <c r="G324" s="10">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H324" s="10">
         <v>32</v>
@@ -16605,19 +16646,19 @@
         <v>118.06</v>
       </c>
       <c r="G325" s="10">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H325" s="10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I325" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J325" s="10">
-        <v>126854.51</v>
+        <v>132287.63</v>
       </c>
       <c r="K325" s="10">
-        <v>2.4300000000000002</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
@@ -16710,19 +16751,19 @@
         <v>95.25</v>
       </c>
       <c r="G328" s="10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H328" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I328" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J328" s="10">
-        <v>108090.19</v>
+        <v>101762.3</v>
       </c>
       <c r="K328" s="10">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
@@ -17086,19 +17127,19 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>528</v>
+        <v>794</v>
       </c>
       <c r="E339" s="10">
-        <v>6272.81</v>
+        <v>8878.7999999999993</v>
       </c>
       <c r="F339" s="10">
-        <v>24.32</v>
+        <v>31.32</v>
       </c>
       <c r="G339" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H339" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I339" s="10">
         <v>0</v>
@@ -17540,10 +17581,10 @@
         <v>51.39</v>
       </c>
       <c r="G352" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H352" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I352" s="10">
         <v>2</v>
@@ -17566,16 +17607,16 @@
         <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="E353" s="10">
-        <v>1787.66</v>
+        <v>2671.04</v>
       </c>
       <c r="F353" s="10">
-        <v>6</v>
+        <v>9.34</v>
       </c>
       <c r="G353" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H353" s="10">
         <v>1</v>
@@ -17645,19 +17686,19 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G355" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H355" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I355" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J355" s="10">
-        <v>86918.12</v>
+        <v>80023.12</v>
       </c>
       <c r="K355" s="10">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
@@ -18100,19 +18141,19 @@
         <v>81.229999999999905</v>
       </c>
       <c r="G368" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H368" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I368" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J368" s="10">
-        <v>44060.479999999901</v>
+        <v>51854.48</v>
       </c>
       <c r="K368" s="10">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -18161,19 +18202,19 @@
         <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>345</v>
+        <v>507</v>
       </c>
       <c r="E370" s="10">
-        <v>4510.46</v>
+        <v>6301.03</v>
       </c>
       <c r="F370" s="10">
-        <v>19.98</v>
+        <v>26.49</v>
       </c>
       <c r="G370" s="10">
+        <v>5</v>
+      </c>
+      <c r="H370" s="10">
         <v>3</v>
-      </c>
-      <c r="H370" s="10">
-        <v>2</v>
       </c>
       <c r="I370" s="10">
         <v>0</v>
@@ -18695,7 +18736,7 @@
         <v>51.14</v>
       </c>
       <c r="G385" s="10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H385" s="10">
         <v>19</v>
@@ -18835,19 +18876,19 @@
         <v>60.65</v>
       </c>
       <c r="G389" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H389" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I389" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J389" s="10">
-        <v>26825.68</v>
+        <v>27841.64</v>
       </c>
       <c r="K389" s="10">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
@@ -19001,19 +19042,19 @@
         <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>288</v>
+        <v>449</v>
       </c>
       <c r="E394" s="10">
-        <v>4161.45</v>
+        <v>6062.59</v>
       </c>
       <c r="F394" s="10">
-        <v>13.87</v>
+        <v>18.87</v>
       </c>
       <c r="G394" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H394" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I394" s="10">
         <v>4</v>
@@ -19022,7 +19063,7 @@
         <v>25130.799999999999</v>
       </c>
       <c r="K394" s="10">
-        <v>5.04</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -19650,7 +19691,7 @@
         <v>19.079999999999998</v>
       </c>
       <c r="G414" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H414" s="10">
         <v>4</v>
@@ -19991,13 +20032,13 @@
         <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="E424" s="10">
-        <v>2674.19</v>
+        <v>3750.22</v>
       </c>
       <c r="F424" s="10">
-        <v>10.66</v>
+        <v>13.66</v>
       </c>
       <c r="G424" s="10">
         <v>4</v>
@@ -20397,7 +20438,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L187"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24914,13 +24955,13 @@
         <v>13</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -24990,28 +25031,28 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F124">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G124">
+        <v>5</v>
+      </c>
+      <c r="H124">
         <v>4</v>
       </c>
-      <c r="H124">
-        <v>2</v>
-      </c>
       <c r="I124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>14289</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>14289</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -25075,7 +25116,7 @@
         <v>1</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -25142,10 +25183,10 @@
         <v>29</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -25180,16 +25221,16 @@
         <v>13</v>
       </c>
       <c r="E129">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F129">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -25218,13 +25259,13 @@
         <v>33</v>
       </c>
       <c r="E130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -25294,10 +25335,10 @@
         <v>40</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -25370,16 +25411,16 @@
         <v>53</v>
       </c>
       <c r="E134">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F134">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -25408,13 +25449,13 @@
         <v>58</v>
       </c>
       <c r="E135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -25472,7 +25513,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B137" s="18">
         <v>2026</v>
@@ -25481,19 +25522,19 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E137">
         <v>1</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137">
         <v>0</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -25519,7 +25560,7 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -25528,10 +25569,10 @@
         <v>1</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -25548,7 +25589,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B139" s="18">
         <v>2026</v>
@@ -25557,10 +25598,10 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -25569,7 +25610,7 @@
         <v>1</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -25586,7 +25627,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B140" s="18">
         <v>2026</v>
@@ -25595,7 +25636,7 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -25604,7 +25645,7 @@
         <v>3</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -25633,13 +25674,13 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -25671,36 +25712,36 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B143" s="18">
         <v>2026</v>
@@ -25709,36 +25750,36 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J143">
-        <v>10440</v>
+        <v>0</v>
       </c>
       <c r="K143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L143">
-        <v>10440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B144" s="18">
         <v>2026</v>
@@ -25747,19 +25788,19 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -25776,7 +25817,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B145" s="18">
         <v>2026</v>
@@ -25785,7 +25826,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -25823,31 +25864,31 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146">
-        <v>8458</v>
+        <v>10440</v>
       </c>
       <c r="K146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L146">
-        <v>8458</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -25861,16 +25902,16 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F147">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -25899,36 +25940,36 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>1</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B149" s="18">
         <v>2026</v>
@@ -25937,7 +25978,7 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -25946,7 +25987,7 @@
         <v>1</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -25966,7 +26007,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B150" s="18">
         <v>2026</v>
@@ -25975,36 +26016,36 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B151" s="18">
         <v>2026</v>
@@ -26013,19 +26054,19 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E151">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F151">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G151">
         <v>1</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -26042,7 +26083,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B152" s="18">
         <v>2026</v>
@@ -26051,16 +26092,16 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E152">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -26080,7 +26121,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B153" s="18">
         <v>2026</v>
@@ -26092,16 +26133,16 @@
         <v>13</v>
       </c>
       <c r="E153">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -26118,7 +26159,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B154" s="18">
         <v>2026</v>
@@ -26127,7 +26168,7 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -26136,10 +26177,10 @@
         <v>1</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -26156,7 +26197,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B155" s="18">
         <v>2026</v>
@@ -26165,16 +26206,16 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F155">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -26194,7 +26235,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B156" s="18">
         <v>2026</v>
@@ -26203,19 +26244,19 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G156">
         <v>0</v>
       </c>
       <c r="H156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -26241,19 +26282,19 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -26279,7 +26320,7 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="E158">
         <v>1</v>
@@ -26291,7 +26332,7 @@
         <v>0</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -26308,7 +26349,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B159" s="18">
         <v>2026</v>
@@ -26317,16 +26358,16 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E159">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F159">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -26346,7 +26387,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B160" s="18">
         <v>2026</v>
@@ -26355,19 +26396,19 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G160">
         <v>0</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -26384,7 +26425,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B161" s="18">
         <v>2026</v>
@@ -26393,19 +26434,19 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161">
         <v>0</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -26422,7 +26463,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B162" s="18">
         <v>2026</v>
@@ -26434,33 +26475,33 @@
         <v>51</v>
       </c>
       <c r="E162">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="K162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162">
-        <v>8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B163" s="18">
         <v>2026</v>
@@ -26469,10 +26510,10 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F163">
         <v>2</v>
@@ -26498,7 +26539,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B164" s="18">
         <v>2026</v>
@@ -26507,7 +26548,7 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E164">
         <v>1</v>
@@ -26545,19 +26586,19 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26574,7 +26615,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B166" s="18">
         <v>2026</v>
@@ -26583,19 +26624,19 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E166">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F166">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -26612,7 +26653,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B167" s="18">
         <v>2026</v>
@@ -26621,13 +26662,13 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E167">
         <v>1</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -26650,7 +26691,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B168" s="18">
         <v>2026</v>
@@ -26659,36 +26700,36 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="E168">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B169" s="18">
         <v>2026</v>
@@ -26700,7 +26741,7 @@
         <v>52</v>
       </c>
       <c r="E169">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F169">
         <v>4</v>
@@ -26709,7 +26750,7 @@
         <v>1</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -26726,7 +26767,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B170" s="18">
         <v>2026</v>
@@ -26738,16 +26779,16 @@
         <v>55</v>
       </c>
       <c r="E170">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F170">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -26764,13 +26805,13 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D171" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="E171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -26799,19 +26840,19 @@
         <v>128</v>
       </c>
       <c r="D172" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -26828,16 +26869,16 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D173" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E173">
         <v>1</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173">
         <v>0</v>
@@ -26860,16 +26901,16 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D174" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -26892,10 +26933,10 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D175" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -26904,10 +26945,10 @@
         <v>1</v>
       </c>
       <c r="G175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -26924,54 +26965,54 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D176" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H176">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I176">
         <v>1</v>
       </c>
       <c r="J176">
-        <v>5560</v>
+        <v>8316</v>
       </c>
       <c r="K176">
         <v>1</v>
       </c>
       <c r="L176">
-        <v>5560</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D177" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F177">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G177">
         <v>2</v>
       </c>
       <c r="H177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -26988,16 +27029,16 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D178" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -27020,16 +27061,16 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D179" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -27052,19 +27093,19 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D180" t="s">
         <v>13</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -27084,10 +27125,10 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D181" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -27116,10 +27157,10 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -27128,10 +27169,10 @@
         <v>1</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -27148,54 +27189,54 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D183" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E183">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F183">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G183">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I183">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J183">
-        <v>25130.799999999999</v>
+        <v>5859</v>
       </c>
       <c r="K183">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L183">
-        <v>25130.799999999999</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D184" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="E184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -27212,22 +27253,22 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D185" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G185">
         <v>1</v>
       </c>
       <c r="H185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -27244,16 +27285,16 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D186" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -27276,33 +27317,321 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>130</v>
+      </c>
+      <c r="D187" t="s">
+        <v>136</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>131</v>
+      </c>
+      <c r="D188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188">
+        <v>3</v>
+      </c>
+      <c r="F188">
+        <v>3</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>131</v>
+      </c>
+      <c r="D189" t="s">
+        <v>135</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>1</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>131</v>
+      </c>
+      <c r="D190" t="s">
+        <v>40</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>131</v>
+      </c>
+      <c r="D191" t="s">
+        <v>60</v>
+      </c>
+      <c r="E191">
+        <v>10</v>
+      </c>
+      <c r="F191">
+        <v>10</v>
+      </c>
+      <c r="G191">
+        <v>7</v>
+      </c>
+      <c r="H191">
+        <v>3</v>
+      </c>
+      <c r="I191">
+        <v>4</v>
+      </c>
+      <c r="J191">
+        <v>25130.799999999999</v>
+      </c>
+      <c r="K191">
+        <v>4</v>
+      </c>
+      <c r="L191">
+        <v>25130.799999999999</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>132</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D192" t="s">
+        <v>13</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>1</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>132</v>
+      </c>
+      <c r="D193" t="s">
+        <v>135</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193">
+        <v>1</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>132</v>
+      </c>
+      <c r="D194" t="s">
+        <v>52</v>
+      </c>
+      <c r="E194">
+        <v>2</v>
+      </c>
+      <c r="F194">
+        <v>2</v>
+      </c>
+      <c r="G194">
+        <v>2</v>
+      </c>
+      <c r="H194">
+        <v>2</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>7483.12</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194">
+        <v>7483.12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>132</v>
+      </c>
+      <c r="D195" t="s">
+        <v>55</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>132</v>
+      </c>
+      <c r="D196" t="s">
         <v>65</v>
       </c>
-      <c r="E187">
+      <c r="E196">
         <v>4</v>
       </c>
-      <c r="F187">
+      <c r="F196">
         <v>4</v>
       </c>
-      <c r="G187">
-        <v>1</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
-      </c>
-      <c r="I187">
-        <v>0</v>
-      </c>
-      <c r="J187">
-        <v>0</v>
-      </c>
-      <c r="K187">
-        <v>0</v>
-      </c>
-      <c r="L187">
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F01F6B-34C7-4890-AE44-69B8746CEAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4A6875-6427-4953-9045-23A1E0FAFB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="139">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1085,64 +1085,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>526.99</v>
+        <v>596.95999999999901</v>
       </c>
       <c r="C6" s="5">
-        <v>289.95</v>
+        <v>330.94</v>
       </c>
       <c r="D6" s="5">
-        <v>237.04</v>
+        <v>266.02</v>
       </c>
       <c r="E6" s="5">
-        <v>122090.129999999</v>
+        <v>135066.35999999999</v>
       </c>
       <c r="F6" s="5">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="G6" s="5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="I6" s="5">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="J6" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K6" s="5">
-        <v>512.98373949579798</v>
+        <v>502.10542750929301</v>
       </c>
       <c r="L6" s="5">
-        <v>1488.90402439024</v>
+        <v>1298.7149999999999</v>
       </c>
       <c r="M6" s="5">
-        <v>-5.2331912497758601</v>
+        <v>3.8688834140491801</v>
       </c>
       <c r="N6" s="6">
-        <v>657.92</v>
+        <v>699.14</v>
       </c>
       <c r="O6" s="6">
-        <v>72081.019999999902</v>
+        <v>76807.850000000006</v>
       </c>
       <c r="P6" s="6">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="Q6" s="6">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R6" s="6">
         <v>25</v>
       </c>
       <c r="S6" s="6">
-        <v>184.823128205128</v>
+        <v>187.794254278728</v>
       </c>
       <c r="T6" s="6">
-        <v>743.10329896907194</v>
+        <v>783.75357142857104</v>
       </c>
       <c r="U6" s="6">
-        <v>127.179457227436</v>
+        <v>113.19861186063601</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1169,7 +1169,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,49 +1177,49 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>110.21</v>
+        <v>126.96</v>
       </c>
       <c r="C7" s="5">
-        <v>50.84</v>
+        <v>60.09</v>
       </c>
       <c r="D7" s="5">
-        <v>59.37</v>
+        <v>66.87</v>
       </c>
       <c r="E7" s="5">
-        <v>3948.2</v>
+        <v>4517.24</v>
       </c>
       <c r="F7" s="5">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5">
+        <v>63</v>
+      </c>
+      <c r="I7" s="5">
+        <v>22</v>
+      </c>
+      <c r="J7" s="5">
         <v>4</v>
       </c>
-      <c r="H7" s="5">
-        <v>55</v>
-      </c>
-      <c r="I7" s="5">
-        <v>18</v>
-      </c>
-      <c r="J7" s="5">
-        <v>2</v>
-      </c>
       <c r="K7" s="5">
-        <v>66.918644067796606</v>
+        <v>64.531999999999996</v>
       </c>
       <c r="L7" s="5">
-        <v>219.34444444444401</v>
+        <v>205.32909090909001</v>
       </c>
       <c r="M7" s="5">
-        <v>164.424294615267</v>
+        <v>482.56811681469202</v>
       </c>
       <c r="N7" s="6">
-        <v>115.48</v>
+        <v>119.48</v>
       </c>
       <c r="O7" s="6">
-        <v>6723.18</v>
+        <v>7014.78</v>
       </c>
       <c r="P7" s="6">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Q7" s="6">
         <v>38</v>
@@ -1228,13 +1228,13 @@
         <v>11</v>
       </c>
       <c r="S7" s="6">
-        <v>48.022714285714201</v>
+        <v>48.377793103448198</v>
       </c>
       <c r="T7" s="6">
-        <v>176.92578947368401</v>
+        <v>184.59947368421001</v>
       </c>
       <c r="U7" s="6">
-        <v>978.32900502440805</v>
+        <v>933.50354537134399</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1261,7 +1261,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1269,49 +1269,49 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>6.35</v>
+        <v>9.35</v>
       </c>
       <c r="C8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3711.22</v>
+      </c>
+      <c r="F8" s="5">
         <v>4</v>
       </c>
-      <c r="D8" s="5">
-        <v>2.35</v>
-      </c>
-      <c r="E8" s="5">
-        <v>3383</v>
-      </c>
-      <c r="F8" s="5">
-        <v>2</v>
-      </c>
       <c r="G8" s="5">
         <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1691.5</v>
+        <v>927.80499999999995</v>
       </c>
       <c r="L8" s="5">
-        <v>3383</v>
+        <v>1237.0733333333301</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
       <c r="N8" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O8" s="6">
-        <v>909.4</v>
+        <v>998.12</v>
       </c>
       <c r="P8" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="6">
         <v>2</v>
@@ -1320,13 +1320,13 @@
         <v>1</v>
       </c>
       <c r="S8" s="6">
-        <v>227.35</v>
+        <v>199.624</v>
       </c>
       <c r="T8" s="6">
-        <v>454.7</v>
+        <v>499.06</v>
       </c>
       <c r="U8" s="6">
-        <v>46.580162744666801</v>
+        <v>33.551076022922999</v>
       </c>
       <c r="V8" s="7">
         <v>12</v>
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1361,46 +1361,46 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>37.67</v>
+        <v>47.66</v>
       </c>
       <c r="C9" s="5">
-        <v>20.67</v>
+        <v>25.66</v>
       </c>
       <c r="D9" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5">
-        <v>12975.05</v>
+        <v>14925.18</v>
       </c>
       <c r="F9" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I9" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>865.00333333333299</v>
+        <v>746.25900000000001</v>
       </c>
       <c r="L9" s="5">
-        <v>2595.0100000000002</v>
+        <v>2132.16857142857</v>
       </c>
       <c r="M9" s="5">
-        <v>10.126743249544299</v>
+        <v>-4.26246115624736</v>
       </c>
       <c r="N9" s="6">
-        <v>11.84</v>
+        <v>12.84</v>
       </c>
       <c r="O9" s="6">
-        <v>2810.4</v>
+        <v>2939.1</v>
       </c>
       <c r="P9" s="6">
         <v>21</v>
@@ -1412,13 +1412,13 @@
         <v>2</v>
       </c>
       <c r="S9" s="6">
-        <v>133.828571428571</v>
+        <v>139.957142857142</v>
       </c>
       <c r="T9" s="6">
-        <v>1405.2</v>
+        <v>1469.55</v>
       </c>
       <c r="U9" s="6">
-        <v>201.91431824651201</v>
+        <v>188.693817835391</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1445,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1489,7 +1489,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1509,10 +1509,10 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>65.289999999999907</v>
+        <v>67.789999999999907</v>
       </c>
       <c r="O11" s="6">
-        <v>3316.08</v>
+        <v>3575.05</v>
       </c>
       <c r="P11" s="6">
         <v>7</v>
@@ -1524,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>473.72571428571399</v>
+        <v>510.72142857142802</v>
       </c>
       <c r="T11" s="6">
-        <v>1658.04</v>
+        <v>1787.5250000000001</v>
       </c>
       <c r="U11" s="6">
-        <v>127.43721502496901</v>
+        <v>110.96208444637099</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1551,7 +1551,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1559,22 +1559,22 @@
         <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>5.33</v>
+        <v>6.33</v>
       </c>
       <c r="C12" s="5">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="D12" s="5">
         <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>2113.67</v>
+        <v>2253.6999999999998</v>
       </c>
       <c r="F12" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>4</v>
@@ -1586,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>422.73399999999998</v>
+        <v>375.61666666666599</v>
       </c>
       <c r="L12" s="5">
-        <v>2113.67</v>
+        <v>2253.6999999999998</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
@@ -1598,22 +1598,22 @@
         <v>6.02</v>
       </c>
       <c r="O12" s="6">
-        <v>894.27</v>
+        <v>995.21</v>
       </c>
       <c r="P12" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="6">
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>223.5675</v>
+        <v>199.042</v>
       </c>
       <c r="T12" s="6">
-        <v>894.27</v>
+        <v>497.60500000000002</v>
       </c>
       <c r="U12" s="6">
         <v>-100</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1687,7 +1687,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1710,7 +1710,7 @@
         <v>10.08</v>
       </c>
       <c r="O14" s="6">
-        <v>937.93</v>
+        <v>989.39</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1737,7 +1737,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>246.59</v>
+        <v>254.84</v>
       </c>
       <c r="P15" s="6">
         <v>2</v>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>123.295</v>
+        <v>127.42</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1809,16 +1809,16 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5">
         <v>4</v>
       </c>
       <c r="E16" s="5">
-        <v>319.56</v>
+        <v>566.04999999999995</v>
       </c>
       <c r="F16" s="5">
         <v>4</v>
@@ -1833,22 +1833,22 @@
         <v>2</v>
       </c>
       <c r="J16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="5">
-        <v>79.89</v>
+        <v>141.51249999999999</v>
       </c>
       <c r="L16" s="5">
-        <v>159.78</v>
+        <v>283.02499999999998</v>
       </c>
       <c r="M16" s="5">
-        <v>-100</v>
+        <v>1250.94072961752</v>
       </c>
       <c r="N16" s="6">
         <v>21.99</v>
       </c>
       <c r="O16" s="6">
-        <v>5039.53</v>
+        <v>5209.58</v>
       </c>
       <c r="P16" s="6">
         <v>26</v>
@@ -1860,10 +1860,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>193.828076923076</v>
+        <v>200.36846153846099</v>
       </c>
       <c r="T16" s="6">
-        <v>839.92166666666606</v>
+        <v>868.26333333333298</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,10 +1913,10 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>49.67</v>
+        <v>59.68</v>
       </c>
       <c r="O17" s="6">
-        <v>3486.23</v>
+        <v>3787.36</v>
       </c>
       <c r="P17" s="6">
         <v>12</v>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>290.51916666666602</v>
+        <v>315.613333333333</v>
       </c>
       <c r="T17" s="6">
-        <v>3486.23</v>
+        <v>3787.36</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1955,7 +1955,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1978,7 +1978,7 @@
         <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>697.34</v>
+        <v>729.14</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1990,10 +1990,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>232.446666666666</v>
+        <v>243.046666666666</v>
       </c>
       <c r="T18" s="6">
-        <v>697.34</v>
+        <v>729.14</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -2021,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2044,7 +2044,7 @@
         <v>4.45</v>
       </c>
       <c r="O19" s="6">
-        <v>915.43</v>
+        <v>1016.94</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2071,7 +2071,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2094,7 +2094,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="6">
-        <v>1398.67</v>
+        <v>1449.11</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2121,7 +2121,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2129,16 +2129,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C21" s="5">
         <v>19.010000000000002</v>
       </c>
       <c r="D21" s="5">
-        <v>16.989999999999998</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="E21" s="5">
-        <v>5143.7299999999996</v>
+        <v>5339.78</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2167,7 +2167,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2213,7 +2213,7 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2225,16 +2225,16 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I23" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J23" s="5">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2271,16 +2271,16 @@
         <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>62.11</v>
+        <v>65.11</v>
       </c>
       <c r="C24" s="5">
-        <v>58.12</v>
+        <v>61.12</v>
       </c>
       <c r="D24" s="5">
         <v>3.99</v>
       </c>
       <c r="E24" s="5">
-        <v>12830.88</v>
+        <v>14326.02</v>
       </c>
       <c r="F24" s="5">
         <v>8</v>
@@ -2298,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>1603.86</v>
+        <v>1790.7525000000001</v>
       </c>
       <c r="L24" s="5">
-        <v>6415.44</v>
+        <v>7163.01</v>
       </c>
       <c r="M24" s="5">
-        <v>-40.035289863205001</v>
+        <v>-46.293527441675998</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2329,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2346,7 +2346,7 @@
         <v>7.67</v>
       </c>
       <c r="E25" s="5">
-        <v>2257.33</v>
+        <v>2487.0700000000002</v>
       </c>
       <c r="F25" s="5">
         <v>7</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>322.47571428571399</v>
+        <v>355.29571428571398</v>
       </c>
       <c r="L25" s="5">
-        <v>2257.33</v>
+        <v>2487.0700000000002</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="O25" s="6">
-        <v>1000.54</v>
+        <v>1029.5899999999999</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -2409,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2426,7 +2426,7 @@
         <v>4.46</v>
       </c>
       <c r="E26" s="5">
-        <v>2440.33</v>
+        <v>2610.1799999999998</v>
       </c>
       <c r="F26" s="5">
         <v>5</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>488.06599999999997</v>
+        <v>522.03599999999994</v>
       </c>
       <c r="L26" s="5">
-        <v>813.44333333333304</v>
+        <v>870.06</v>
       </c>
       <c r="M26" s="5">
         <v>-100</v>
@@ -2456,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="6">
-        <v>403.72</v>
+        <v>408.05</v>
       </c>
       <c r="P26" s="6">
         <v>4</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>100.93</v>
+        <v>102.0125</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
@@ -2499,7 +2499,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2507,16 +2507,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="C27" s="5">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="D27" s="5">
         <v>1.5</v>
       </c>
       <c r="E27" s="5">
-        <v>4075.71</v>
+        <v>4463.3599999999997</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -2534,22 +2534,22 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>4075.71</v>
+        <v>4463.3599999999997</v>
       </c>
       <c r="L27" s="5">
-        <v>4075.71</v>
+        <v>4463.3599999999997</v>
       </c>
       <c r="M27" s="5">
-        <v>99.130948963493395</v>
+        <v>81.836105534843696</v>
       </c>
       <c r="N27" s="6">
         <v>22.33</v>
       </c>
       <c r="O27" s="6">
-        <v>4177.1400000000003</v>
+        <v>4449.97</v>
       </c>
       <c r="P27" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q27" s="6">
         <v>6</v>
@@ -2558,13 +2558,13 @@
         <v>2</v>
       </c>
       <c r="S27" s="6">
-        <v>298.36714285714203</v>
+        <v>278.12312500000002</v>
       </c>
       <c r="T27" s="6">
-        <v>696.19</v>
+        <v>741.66166666666595</v>
       </c>
       <c r="U27" s="6">
-        <v>254.33334769722799</v>
+        <v>232.60898388078999</v>
       </c>
       <c r="V27" s="7">
         <v>66.569999999999993</v>
@@ -2591,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="AD27" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2611,13 +2611,13 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="6">
-        <v>14.67</v>
+        <v>18.579999999999998</v>
       </c>
       <c r="O28" s="6">
-        <v>1212.93</v>
+        <v>1404.47</v>
       </c>
       <c r="P28" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="6">
         <v>1</v>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>134.77000000000001</v>
+        <v>140.447</v>
       </c>
       <c r="T28" s="6">
-        <v>1212.93</v>
+        <v>1404.47</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
@@ -2653,7 +2653,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2661,16 +2661,16 @@
         <v>45</v>
       </c>
       <c r="B29" s="5">
-        <v>14.66</v>
+        <v>15.66</v>
       </c>
       <c r="C29" s="5">
         <v>4.67</v>
       </c>
       <c r="D29" s="5">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="E29" s="5">
-        <v>4394.24</v>
+        <v>4791.03</v>
       </c>
       <c r="F29" s="5">
         <v>12</v>
@@ -2682,28 +2682,28 @@
         <v>11</v>
       </c>
       <c r="I29" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="5">
         <v>1</v>
       </c>
       <c r="K29" s="5">
-        <v>366.18666666666599</v>
+        <v>399.2525</v>
       </c>
       <c r="L29" s="5">
-        <v>1464.7466666666601</v>
+        <v>1197.7574999999999</v>
       </c>
       <c r="M29" s="5">
-        <v>16.493409554325599</v>
+        <v>6.8455008630711998</v>
       </c>
       <c r="N29" s="6">
-        <v>11.58</v>
+        <v>12.58</v>
       </c>
       <c r="O29" s="6">
-        <v>1912.87</v>
+        <v>2049.96</v>
       </c>
       <c r="P29" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q29" s="6">
         <v>6</v>
@@ -2712,13 +2712,13 @@
         <v>3</v>
       </c>
       <c r="S29" s="6">
-        <v>173.897272727272</v>
+        <v>170.83</v>
       </c>
       <c r="T29" s="6">
-        <v>318.81166666666599</v>
+        <v>341.66</v>
       </c>
       <c r="U29" s="6">
-        <v>1051.1142942280401</v>
+        <v>974.13412944642801</v>
       </c>
       <c r="V29" s="7">
         <v>55.58</v>
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2765,10 +2765,10 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>31.509999999999899</v>
+        <v>34.51</v>
       </c>
       <c r="O30" s="6">
-        <v>2205.4</v>
+        <v>2448.02</v>
       </c>
       <c r="P30" s="6">
         <v>8</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>275.67500000000001</v>
+        <v>306.0025</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
@@ -2805,7 +2805,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2825,13 +2825,13 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="6">
-        <v>35.04</v>
+        <v>37.04</v>
       </c>
       <c r="O31" s="6">
-        <v>2670.65</v>
+        <v>2931.44</v>
       </c>
       <c r="P31" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q31" s="6">
         <v>1</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>534.13</v>
+        <v>488.57333333333298</v>
       </c>
       <c r="T31" s="6">
-        <v>2670.65</v>
+        <v>2931.44</v>
       </c>
       <c r="U31" s="6">
         <v>-100</v>
@@ -2867,7 +2867,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2875,49 +2875,49 @@
         <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>30.93</v>
+        <v>35.93</v>
       </c>
       <c r="C32" s="5">
-        <v>18.43</v>
+        <v>20.43</v>
       </c>
       <c r="D32" s="5">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E32" s="5">
-        <v>9000.58</v>
+        <v>9914.74</v>
       </c>
       <c r="F32" s="5">
+        <v>17</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5">
         <v>15</v>
       </c>
-      <c r="G32" s="5">
-        <v>2</v>
-      </c>
-      <c r="H32" s="5">
-        <v>13</v>
-      </c>
       <c r="I32" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J32" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="5">
-        <v>600.03866666666602</v>
+        <v>583.22</v>
       </c>
       <c r="L32" s="5">
-        <v>3000.19333333333</v>
+        <v>1652.4566666666601</v>
       </c>
       <c r="M32" s="5">
-        <v>-7.6059542829462004</v>
+        <v>-13.250372677447899</v>
       </c>
       <c r="N32" s="6">
         <v>11.3</v>
       </c>
       <c r="O32" s="6">
-        <v>3792.62</v>
+        <v>3938.92</v>
       </c>
       <c r="P32" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q32" s="6">
         <v>3</v>
@@ -2926,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="6">
-        <v>210.701111111111</v>
+        <v>207.31157894736799</v>
       </c>
       <c r="T32" s="6">
-        <v>1264.2066666666601</v>
+        <v>1312.9733333333299</v>
       </c>
       <c r="U32" s="6">
         <v>-100</v>
@@ -2959,7 +2959,7 @@
         <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2967,16 +2967,16 @@
         <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>31.16</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="C33" s="5">
-        <v>9.4499999999999993</v>
+        <v>10.95</v>
       </c>
       <c r="D33" s="5">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="E33" s="5">
-        <v>10018.93</v>
+        <v>10985.68</v>
       </c>
       <c r="F33" s="5">
         <v>17</v>
@@ -2994,13 +2994,13 @@
         <v>3</v>
       </c>
       <c r="K33" s="5">
-        <v>589.34882352941099</v>
+        <v>646.21647058823498</v>
       </c>
       <c r="L33" s="5">
-        <v>1252.36625</v>
+        <v>1373.21</v>
       </c>
       <c r="M33" s="5">
-        <v>142.11288031755799</v>
+        <v>120.806722933855</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3025,7 +3025,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3033,40 +3033,40 @@
         <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>41.09</v>
+        <v>45.34</v>
       </c>
       <c r="C34" s="5">
-        <v>16.59</v>
+        <v>18.59</v>
       </c>
       <c r="D34" s="5">
-        <v>24.5</v>
+        <v>26.75</v>
       </c>
       <c r="E34" s="5">
-        <v>9971.42</v>
+        <v>10954.77</v>
       </c>
       <c r="F34" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G34" s="5">
         <v>1</v>
       </c>
       <c r="H34" s="5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I34" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J34" s="5">
         <v>2</v>
       </c>
       <c r="K34" s="5">
-        <v>453.24636363636301</v>
+        <v>438.19080000000002</v>
       </c>
       <c r="L34" s="5">
-        <v>1424.4885714285699</v>
+        <v>1095.4770000000001</v>
       </c>
       <c r="M34" s="5">
-        <v>-41.242069835590101</v>
+        <v>-46.516448998929199</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3091,7 +3091,7 @@
         <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3099,49 +3099,49 @@
         <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>31.32</v>
+        <v>36.32</v>
       </c>
       <c r="C35" s="5">
-        <v>23.49</v>
+        <v>28.49</v>
       </c>
       <c r="D35" s="5">
         <v>7.83</v>
       </c>
       <c r="E35" s="5">
-        <v>8878.7999999999993</v>
+        <v>10168.52</v>
       </c>
       <c r="F35" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35" s="5">
         <v>9</v>
       </c>
       <c r="I35" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="5">
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>634.19999999999902</v>
+        <v>677.90133333333301</v>
       </c>
       <c r="L35" s="5">
-        <v>2959.6</v>
+        <v>2542.13</v>
       </c>
       <c r="M35" s="5">
         <v>-100</v>
       </c>
       <c r="N35" s="6">
-        <v>23.59</v>
+        <v>25.59</v>
       </c>
       <c r="O35" s="6">
-        <v>8155.36</v>
+        <v>8569.51</v>
       </c>
       <c r="P35" s="6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q35" s="6">
         <v>11</v>
@@ -3150,13 +3150,13 @@
         <v>3</v>
       </c>
       <c r="S35" s="6">
-        <v>239.86352941176401</v>
+        <v>225.513421052631</v>
       </c>
       <c r="T35" s="6">
-        <v>741.39636363636305</v>
+        <v>779.04636363636303</v>
       </c>
       <c r="U35" s="6">
-        <v>185.92447175845001</v>
+        <v>172.10622310960599</v>
       </c>
       <c r="V35" s="7">
         <v>110.24</v>
@@ -3183,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="AD35" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3203,10 +3203,10 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="6">
-        <v>69.86</v>
+        <v>74.66</v>
       </c>
       <c r="O36" s="6">
-        <v>2455.0700000000002</v>
+        <v>2677.98</v>
       </c>
       <c r="P36" s="6">
         <v>8</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="6">
-        <v>306.88375000000002</v>
+        <v>334.7475</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6">
@@ -3243,7 +3243,7 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3251,16 +3251,16 @@
         <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>9.34</v>
+        <v>13.32</v>
       </c>
       <c r="C37" s="5">
-        <v>4.33</v>
+        <v>6.33</v>
       </c>
       <c r="D37" s="5">
-        <v>5.01</v>
+        <v>6.99</v>
       </c>
       <c r="E37" s="5">
-        <v>2671.04</v>
+        <v>2889.48</v>
       </c>
       <c r="F37" s="5">
         <v>4</v>
@@ -3278,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>667.76</v>
+        <v>722.37</v>
       </c>
       <c r="L37" s="5">
-        <v>2671.04</v>
+        <v>2889.48</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
@@ -3309,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="AD37" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3317,16 +3317,16 @@
         <v>58</v>
       </c>
       <c r="B38" s="5">
-        <v>26.49</v>
+        <v>28.74</v>
       </c>
       <c r="C38" s="5">
-        <v>19.489999999999998</v>
+        <v>21.49</v>
       </c>
       <c r="D38" s="5">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="E38" s="5">
-        <v>6301.03</v>
+        <v>6803.57</v>
       </c>
       <c r="F38" s="5">
         <v>5</v>
@@ -3344,22 +3344,22 @@
         <v>0</v>
       </c>
       <c r="K38" s="5">
-        <v>1260.2059999999999</v>
+        <v>1360.7139999999999</v>
       </c>
       <c r="L38" s="5">
-        <v>2100.3433333333301</v>
+        <v>2267.8566666666602</v>
       </c>
       <c r="M38" s="5">
         <v>-100</v>
       </c>
       <c r="N38" s="6">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="O38" s="6">
-        <v>3457.68</v>
+        <v>3711.6</v>
       </c>
       <c r="P38" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="6">
         <v>7</v>
@@ -3368,13 +3368,13 @@
         <v>1</v>
       </c>
       <c r="S38" s="6">
-        <v>181.983157894736</v>
+        <v>185.57999999999899</v>
       </c>
       <c r="T38" s="6">
-        <v>493.95428571428499</v>
+        <v>530.22857142857094</v>
       </c>
       <c r="U38" s="6">
-        <v>147.33347215473901</v>
+        <v>130.41275999568899</v>
       </c>
       <c r="V38" s="7">
         <v>42.5</v>
@@ -3401,7 +3401,7 @@
         <v>16</v>
       </c>
       <c r="AD38" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3424,7 +3424,7 @@
         <v>30.34</v>
       </c>
       <c r="O39" s="6">
-        <v>1949.86</v>
+        <v>2127.2800000000002</v>
       </c>
       <c r="P39" s="6">
         <v>2</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="6">
-        <v>974.93</v>
+        <v>1063.6400000000001</v>
       </c>
       <c r="T39" s="6">
-        <v>1949.86</v>
+        <v>2127.2800000000002</v>
       </c>
       <c r="U39" s="6">
         <v>-100</v>
@@ -3463,7 +3463,7 @@
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3471,25 +3471,25 @@
         <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>9.17</v>
+        <v>10.17</v>
       </c>
       <c r="C40" s="5">
         <v>5.67</v>
       </c>
       <c r="D40" s="5">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E40" s="5">
-        <v>5837.63</v>
+        <v>6334.25</v>
       </c>
       <c r="F40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5">
         <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="5">
         <v>1</v>
@@ -3498,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>5837.63</v>
+        <v>3167.125</v>
       </c>
       <c r="L40" s="5">
-        <v>5837.63</v>
+        <v>6334.25</v>
       </c>
       <c r="M40" s="5">
         <v>-100</v>
@@ -3510,7 +3510,7 @@
         <v>0.98</v>
       </c>
       <c r="O40" s="6">
-        <v>331.81</v>
+        <v>350.58</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -3533,7 +3533,7 @@
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
@@ -3541,49 +3541,49 @@
         <v>60</v>
       </c>
       <c r="B41">
-        <v>18.87</v>
+        <v>19.87</v>
       </c>
       <c r="C41">
         <v>7.87</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41">
-        <v>6062.59</v>
+        <v>6744.19</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41">
         <v>3</v>
       </c>
       <c r="H41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J41">
         <v>4</v>
       </c>
       <c r="K41">
-        <v>378.91187500000001</v>
+        <v>396.71705882352899</v>
       </c>
       <c r="L41">
-        <v>673.62111111111096</v>
+        <v>674.41899999999998</v>
       </c>
       <c r="M41">
-        <v>314.52250605764198</v>
+        <v>272.62888501065299</v>
       </c>
       <c r="N41">
         <v>17.16</v>
       </c>
       <c r="O41">
-        <v>2992.72</v>
+        <v>3208.69</v>
       </c>
       <c r="P41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -3592,13 +3592,13 @@
         <v>1</v>
       </c>
       <c r="S41">
-        <v>157.51157894736801</v>
+        <v>160.43450000000001</v>
       </c>
       <c r="T41">
-        <v>997.57333333333304</v>
+        <v>1069.5633333333301</v>
       </c>
       <c r="U41">
-        <v>73.914699671202101</v>
+        <v>62.2088765197011</v>
       </c>
       <c r="V41">
         <v>52.03</v>
@@ -3625,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="AD41" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
@@ -3633,10 +3633,10 @@
         <v>61</v>
       </c>
       <c r="N42">
-        <v>36.56</v>
+        <v>39.56</v>
       </c>
       <c r="O42">
-        <v>2668.87</v>
+        <v>2999.83</v>
       </c>
       <c r="P42">
         <v>8</v>
@@ -3648,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <v>333.60874999999999</v>
+        <v>374.97874999999999</v>
       </c>
       <c r="T42">
-        <v>2668.87</v>
+        <v>2999.83</v>
       </c>
       <c r="U42">
         <v>-100</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="AD42" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
@@ -3680,37 +3680,37 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>13.66</v>
+        <v>16.66</v>
       </c>
       <c r="C43">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="D43">
-        <v>5.67</v>
+        <v>6.67</v>
       </c>
       <c r="E43">
-        <v>3750.22</v>
+        <v>4115.1400000000003</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>4</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>937.55499999999995</v>
+        <v>823.02800000000002</v>
       </c>
       <c r="L43">
-        <v>3750.22</v>
+        <v>2057.5700000000002</v>
       </c>
       <c r="M43">
         <v>-100</v>
@@ -3719,7 +3719,7 @@
         <v>6.0299999999999896</v>
       </c>
       <c r="O43">
-        <v>1415.24</v>
+        <v>1468.67</v>
       </c>
       <c r="P43">
         <v>8</v>
@@ -3731,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="S43">
-        <v>176.905</v>
+        <v>183.58375000000001</v>
       </c>
       <c r="T43">
-        <v>471.74666666666599</v>
+        <v>489.55666666666599</v>
       </c>
       <c r="U43">
         <v>-100</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="AD43" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
@@ -3775,7 +3775,7 @@
         <v>19.690000000000001</v>
       </c>
       <c r="O44">
-        <v>1569.62</v>
+        <v>1740.8</v>
       </c>
       <c r="P44">
         <v>4</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>392.40499999999997</v>
+        <v>435.2</v>
       </c>
       <c r="T44">
-        <v>1569.62</v>
+        <v>1740.8</v>
       </c>
       <c r="U44">
         <v>-100</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
@@ -4924,43 +4924,43 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E21" s="10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F21" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G21" s="10">
         <v>6</v>
       </c>
       <c r="H21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="10">
-        <v>14289</v>
+        <v>23255</v>
       </c>
       <c r="J21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="10">
-        <v>14289</v>
+        <v>23255</v>
       </c>
       <c r="L21" s="10">
-        <v>10.08</v>
+        <v>12.27</v>
       </c>
       <c r="M21" s="10">
-        <v>12.35</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="N21" s="10">
-        <v>41.67</v>
+        <v>48.48</v>
       </c>
       <c r="O21" s="10">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="P21" s="10">
-        <v>8.33</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -4980,7 +4980,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="10">
         <v>0</v>
@@ -4998,17 +4998,15 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
       </c>
       <c r="N22" s="10">
-        <v>50</v>
-      </c>
-      <c r="O22" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O22" s="10"/>
       <c r="P22" s="10">
         <v>0</v>
       </c>
@@ -5024,43 +5022,43 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23" s="10">
         <v>12</v>
       </c>
       <c r="G23" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="10">
-        <v>12813</v>
+        <v>20460</v>
       </c>
       <c r="J23" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="10">
-        <v>12813</v>
+        <v>20460</v>
       </c>
       <c r="L23" s="10">
-        <v>11.76</v>
+        <v>10.78</v>
       </c>
       <c r="M23" s="10">
-        <v>11.07</v>
+        <v>14.58</v>
       </c>
       <c r="N23" s="10">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="O23" s="10">
-        <v>16.670000000000002</v>
+        <v>25</v>
       </c>
       <c r="P23" s="10">
-        <v>7.14</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -5074,7 +5072,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
@@ -5083,13 +5081,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="10">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="J24" s="10">
         <v>0</v>
@@ -5098,17 +5096,17 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>0.84</v>
+        <v>1.49</v>
       </c>
       <c r="M24" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -5131,7 +5129,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
@@ -5146,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -5178,34 +5176,34 @@
         <v>11</v>
       </c>
       <c r="F26" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="10">
         <v>1</v>
       </c>
       <c r="I26" s="10">
-        <v>6480</v>
+        <v>7263</v>
       </c>
       <c r="J26" s="10">
         <v>1</v>
       </c>
       <c r="K26" s="10">
-        <v>6480</v>
+        <v>7263</v>
       </c>
       <c r="L26" s="10">
-        <v>5.46</v>
+        <v>4.83</v>
       </c>
       <c r="M26" s="10">
-        <v>5.6</v>
+        <v>5.18</v>
       </c>
       <c r="N26" s="10">
-        <v>30.77</v>
+        <v>46.15</v>
       </c>
       <c r="O26" s="10">
-        <v>25</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P26" s="10">
         <v>7.69</v>
@@ -5222,13 +5220,13 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E27" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F27" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="10">
         <v>6</v>
@@ -5246,19 +5244,19 @@
         <v>27014</v>
       </c>
       <c r="L27" s="10">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="M27" s="10">
-        <v>23.35</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="N27" s="10">
-        <v>65</v>
+        <v>63.64</v>
       </c>
       <c r="O27" s="10">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="P27" s="10">
-        <v>20</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5296,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>5.04</v>
+        <v>4.46</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -5322,16 +5320,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E29" s="10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F29" s="10">
         <v>1</v>
       </c>
       <c r="G29" s="10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H29" s="10">
         <v>0</v>
@@ -5346,13 +5344,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>13.45</v>
+        <v>14.13</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="O29" s="10">
         <v>0</v>
@@ -5372,13 +5370,13 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E30" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F30" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G30" s="10">
         <v>4</v>
@@ -5396,19 +5394,19 @@
         <v>8316</v>
       </c>
       <c r="L30" s="10">
-        <v>11.76</v>
+        <v>10.78</v>
       </c>
       <c r="M30" s="10">
-        <v>7.19</v>
+        <v>5.93</v>
       </c>
       <c r="N30" s="10">
-        <v>32.14</v>
+        <v>37.93</v>
       </c>
       <c r="O30" s="10">
-        <v>11.11</v>
+        <v>9.09</v>
       </c>
       <c r="P30" s="10">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5422,16 +5420,16 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
+        <v>35</v>
+      </c>
+      <c r="E31" s="10">
         <v>29</v>
       </c>
-      <c r="E31" s="10">
-        <v>24</v>
-      </c>
       <c r="F31" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G31" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" s="10">
         <v>1</v>
@@ -5446,19 +5444,19 @@
         <v>8316</v>
       </c>
       <c r="L31" s="10">
-        <v>12.18</v>
+        <v>13.01</v>
       </c>
       <c r="M31" s="10">
-        <v>7.19</v>
+        <v>5.93</v>
       </c>
       <c r="N31" s="10">
-        <v>27.59</v>
+        <v>34.29</v>
       </c>
       <c r="O31" s="10">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="P31" s="10">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -5472,13 +5470,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F32" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="10">
         <v>5</v>
@@ -5496,19 +5494,19 @@
         <v>5859</v>
       </c>
       <c r="L32" s="10">
-        <v>4.62</v>
+        <v>4.83</v>
       </c>
       <c r="M32" s="10">
-        <v>5.0599999999999996</v>
+        <v>4.18</v>
       </c>
       <c r="N32" s="10">
-        <v>54.55</v>
+        <v>53.85</v>
       </c>
       <c r="O32" s="10">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="P32" s="10">
-        <v>18.18</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5522,10 +5520,10 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F33" s="10">
         <v>2</v>
@@ -5546,13 +5544,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
@@ -5596,10 +5594,10 @@
         <v>25130.799999999999</v>
       </c>
       <c r="L34" s="10">
-        <v>6.3</v>
+        <v>5.58</v>
       </c>
       <c r="M34" s="10">
-        <v>21.72</v>
+        <v>17.91</v>
       </c>
       <c r="N34" s="10">
         <v>60</v>
@@ -5622,22 +5620,22 @@
         <v>18</v>
       </c>
       <c r="D35" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" s="10">
         <v>10</v>
       </c>
       <c r="F35" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" s="10">
         <v>2</v>
       </c>
       <c r="H35" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="10">
-        <v>7483.12</v>
+        <v>14393.12</v>
       </c>
       <c r="J35" s="10">
         <v>1</v>
@@ -5646,19 +5644,19 @@
         <v>7483.12</v>
       </c>
       <c r="L35" s="10">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="M35" s="10">
-        <v>6.47</v>
+        <v>10.26</v>
       </c>
       <c r="N35" s="10">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="O35" s="10">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="P35" s="10">
-        <v>10</v>
+        <v>18.18</v>
       </c>
     </row>
   </sheetData>
@@ -5776,7 +5774,7 @@
         <v>425.17</v>
       </c>
       <c r="G6" s="5">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H6" s="5">
         <v>110</v>
@@ -5852,13 +5850,13 @@
         <v>96</v>
       </c>
       <c r="I8" s="5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J8" s="5">
-        <v>394170.38</v>
+        <v>394899.38</v>
       </c>
       <c r="K8" s="5">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5881,7 +5879,7 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H9" s="5">
         <v>105</v>
@@ -6021,7 +6019,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -6091,7 +6089,7 @@
         <v>437.62</v>
       </c>
       <c r="G15" s="5">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H15" s="5">
         <v>111</v>
@@ -6126,7 +6124,7 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
@@ -6231,7 +6229,7 @@
         <v>419</v>
       </c>
       <c r="G19" s="5">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H19" s="5">
         <v>102</v>
@@ -6266,10 +6264,10 @@
         <v>293.32</v>
       </c>
       <c r="G20" s="10">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" s="10">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I20" s="10">
         <v>30</v>
@@ -6292,28 +6290,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1399</v>
+        <v>1557</v>
       </c>
       <c r="E21" s="10">
-        <v>3948.2</v>
+        <v>4517.24</v>
       </c>
       <c r="F21" s="10">
-        <v>110.21</v>
+        <v>126.96</v>
       </c>
       <c r="G21" s="10">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H21" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>10440</v>
+        <v>19406</v>
       </c>
       <c r="K21" s="10">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6887,19 +6885,19 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="E38" s="10">
-        <v>3383</v>
+        <v>3711.22</v>
       </c>
       <c r="F38" s="10">
-        <v>6.35</v>
+        <v>9.35</v>
       </c>
       <c r="G38" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="10">
         <v>0</v>
@@ -7001,7 +6999,7 @@
         <v>64.36</v>
       </c>
       <c r="G41" s="10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H41" s="10">
         <v>17</v>
@@ -7141,10 +7139,10 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G45" s="10">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H45" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I45" s="10">
         <v>7</v>
@@ -7482,19 +7480,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>1088</v>
+        <v>1234</v>
       </c>
       <c r="E55" s="10">
-        <v>12975.05</v>
+        <v>14925.18</v>
       </c>
       <c r="F55" s="10">
-        <v>37.67</v>
+        <v>47.66</v>
       </c>
       <c r="G55" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H55" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
@@ -7503,7 +7501,7 @@
         <v>14289</v>
       </c>
       <c r="K55" s="10">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -8242,16 +8240,16 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E77" s="10">
-        <v>2113.67</v>
+        <v>2253.6999999999998</v>
       </c>
       <c r="F77" s="10">
-        <v>5.33</v>
+        <v>6.33</v>
       </c>
       <c r="G77" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H77" s="10">
         <v>1</v>
@@ -8997,16 +8995,16 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="E100" s="10">
-        <v>5837.63</v>
+        <v>6334.25</v>
       </c>
       <c r="F100" s="10">
-        <v>9.17</v>
+        <v>10.17</v>
       </c>
       <c r="G100" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="10">
         <v>1</v>
@@ -9676,7 +9674,7 @@
         <v>61.03</v>
       </c>
       <c r="G120" s="10">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H120" s="10">
         <v>31</v>
@@ -9851,7 +9849,7 @@
         <v>50.47</v>
       </c>
       <c r="G125" s="10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H125" s="10">
         <v>19</v>
@@ -9921,10 +9919,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H127" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -10122,13 +10120,13 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E133" s="10">
-        <v>319.56</v>
+        <v>566.04999999999995</v>
       </c>
       <c r="F133" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G133" s="10">
         <v>4</v>
@@ -10137,13 +10135,13 @@
         <v>2</v>
       </c>
       <c r="I133" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" s="10">
-        <v>0</v>
+        <v>7647</v>
       </c>
       <c r="K133" s="10">
-        <v>-1</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -10271,7 +10269,7 @@
         <v>59.03</v>
       </c>
       <c r="G137" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H137" s="10">
         <v>21</v>
@@ -10446,7 +10444,7 @@
         <v>8.01</v>
       </c>
       <c r="G142" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H142" s="10">
         <v>2</v>
@@ -11957,28 +11955,28 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="E187" s="10">
-        <v>5143.7299999999996</v>
+        <v>5339.78</v>
       </c>
       <c r="F187" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G187" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H187" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I187" s="10">
         <v>1</v>
       </c>
       <c r="J187" s="10">
-        <v>6480</v>
+        <v>7263</v>
       </c>
       <c r="K187" s="10">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -12102,13 +12100,13 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>28926</v>
+        <v>30707</v>
       </c>
       <c r="E192" s="10">
-        <v>12830.88</v>
+        <v>14326.02</v>
       </c>
       <c r="F192" s="10">
-        <v>62.11</v>
+        <v>65.11</v>
       </c>
       <c r="G192" s="10">
         <v>8</v>
@@ -12123,7 +12121,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12149,7 +12147,7 @@
         <v>4</v>
       </c>
       <c r="H193" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I193" s="10">
         <v>0</v>
@@ -12687,10 +12685,10 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="E209" s="10">
-        <v>2257.33</v>
+        <v>2487.0700000000002</v>
       </c>
       <c r="F209" s="10">
         <v>9.67</v>
@@ -13282,10 +13280,10 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E226" s="10">
-        <v>2440.33</v>
+        <v>2610.1799999999998</v>
       </c>
       <c r="F226" s="10">
         <v>5.46</v>
@@ -13877,13 +13875,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="E243" s="10">
-        <v>4075.71</v>
+        <v>4463.3599999999997</v>
       </c>
       <c r="F243" s="10">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="G243" s="10">
         <v>1</v>
@@ -13898,7 +13896,7 @@
         <v>8116</v>
       </c>
       <c r="K243" s="10">
-        <v>0.99</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
@@ -14624,7 +14622,7 @@
         <v>29</v>
       </c>
       <c r="H264" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I264" s="10">
         <v>4</v>
@@ -14682,19 +14680,19 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E266" s="10">
-        <v>4394.24</v>
+        <v>4791.03</v>
       </c>
       <c r="F266" s="10">
-        <v>14.66</v>
+        <v>15.66</v>
       </c>
       <c r="G266" s="10">
         <v>12</v>
       </c>
       <c r="H266" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I266" s="10">
         <v>1</v>
@@ -14703,7 +14701,7 @@
         <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>0.16</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15546,7 +15544,7 @@
         <v>22.8</v>
       </c>
       <c r="G293" s="10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H293" s="10">
         <v>12</v>
@@ -15686,10 +15684,10 @@
         <v>70.47</v>
       </c>
       <c r="G297" s="10">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H297" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I297" s="10">
         <v>8</v>
@@ -15931,10 +15929,10 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H304" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I304" s="10">
         <v>6</v>
@@ -15957,19 +15955,19 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>749</v>
+        <v>819</v>
       </c>
       <c r="E305" s="10">
-        <v>9000.58</v>
+        <v>9914.74</v>
       </c>
       <c r="F305" s="10">
-        <v>30.93</v>
+        <v>35.93</v>
       </c>
       <c r="G305" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H305" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I305" s="10">
         <v>1</v>
@@ -15978,7 +15976,7 @@
         <v>8316</v>
       </c>
       <c r="K305" s="10">
-        <v>-0.08</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16061,7 +16059,7 @@
         <v>196.53</v>
       </c>
       <c r="G308" s="10">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H308" s="10">
         <v>35</v>
@@ -16201,10 +16199,10 @@
         <v>110.71</v>
       </c>
       <c r="G312" s="10">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H312" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I312" s="10">
         <v>10</v>
@@ -16227,13 +16225,13 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>1752</v>
+        <v>1850</v>
       </c>
       <c r="E313" s="10">
-        <v>10018.93</v>
+        <v>10985.68</v>
       </c>
       <c r="F313" s="10">
-        <v>31.16</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="G313" s="10">
         <v>17</v>
@@ -16248,7 +16246,7 @@
         <v>24257.119999999999</v>
       </c>
       <c r="K313" s="10">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16507,19 +16505,19 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>2630</v>
+        <v>2786</v>
       </c>
       <c r="E321" s="10">
-        <v>9971.42</v>
+        <v>10954.77</v>
       </c>
       <c r="F321" s="10">
-        <v>41.09</v>
+        <v>45.34</v>
       </c>
       <c r="G321" s="10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H321" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I321" s="10">
         <v>2</v>
@@ -16528,7 +16526,7 @@
         <v>5859</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16751,19 +16749,19 @@
         <v>95.25</v>
       </c>
       <c r="G328" s="10">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H328" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I328" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J328" s="10">
-        <v>101762.3</v>
+        <v>108090.19</v>
       </c>
       <c r="K328" s="10">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
@@ -16786,19 +16784,19 @@
         <v>84.09</v>
       </c>
       <c r="G329" s="10">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H329" s="10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I329" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J329" s="10">
-        <v>173857.81</v>
+        <v>179349.81</v>
       </c>
       <c r="K329" s="10">
-        <v>4.99</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.3">
@@ -17101,7 +17099,7 @@
         <v>171.77</v>
       </c>
       <c r="G338" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H338" s="10">
         <v>14</v>
@@ -17127,19 +17125,19 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>794</v>
+        <v>907</v>
       </c>
       <c r="E339" s="10">
-        <v>8878.7999999999993</v>
+        <v>10168.52</v>
       </c>
       <c r="F339" s="10">
-        <v>31.32</v>
+        <v>36.32</v>
       </c>
       <c r="G339" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H339" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I339" s="10">
         <v>0</v>
@@ -17479,7 +17477,7 @@
         <v>24</v>
       </c>
       <c r="H349" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I349" s="10">
         <v>5</v>
@@ -17581,10 +17579,10 @@
         <v>51.39</v>
       </c>
       <c r="G352" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H352" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I352" s="10">
         <v>2</v>
@@ -17607,13 +17605,13 @@
         <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="E353" s="10">
-        <v>2671.04</v>
+        <v>2889.48</v>
       </c>
       <c r="F353" s="10">
-        <v>9.34</v>
+        <v>13.32</v>
       </c>
       <c r="G353" s="10">
         <v>4</v>
@@ -17686,7 +17684,7 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G355" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H355" s="10">
         <v>23</v>
@@ -18202,13 +18200,13 @@
         <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>507</v>
+        <v>547</v>
       </c>
       <c r="E370" s="10">
-        <v>6301.03</v>
+        <v>6803.57</v>
       </c>
       <c r="F370" s="10">
-        <v>26.49</v>
+        <v>28.74</v>
       </c>
       <c r="G370" s="10">
         <v>5</v>
@@ -18736,7 +18734,7 @@
         <v>51.14</v>
       </c>
       <c r="G385" s="10">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H385" s="10">
         <v>19</v>
@@ -18876,19 +18874,19 @@
         <v>60.65</v>
       </c>
       <c r="G389" s="10">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H389" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I389" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J389" s="10">
-        <v>27841.64</v>
+        <v>26825.68</v>
       </c>
       <c r="K389" s="10">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
@@ -19042,19 +19040,19 @@
         <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="E394" s="10">
-        <v>6062.59</v>
+        <v>6744.19</v>
       </c>
       <c r="F394" s="10">
-        <v>18.87</v>
+        <v>19.87</v>
       </c>
       <c r="G394" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H394" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I394" s="10">
         <v>4</v>
@@ -19063,7 +19061,7 @@
         <v>25130.799999999999</v>
       </c>
       <c r="K394" s="10">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -20032,19 +20030,19 @@
         <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="E424" s="10">
-        <v>3750.22</v>
+        <v>4115.1400000000003</v>
       </c>
       <c r="F424" s="10">
-        <v>13.66</v>
+        <v>16.66</v>
       </c>
       <c r="G424" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H424" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I424" s="10">
         <v>0</v>
@@ -20241,7 +20239,7 @@
         <v>21.38</v>
       </c>
       <c r="G430" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H430" s="10">
         <v>3</v>
@@ -20438,7 +20436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24955,28 +24953,28 @@
         <v>13</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122">
         <v>1</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>8966</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>8966</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -24993,13 +24991,13 @@
         <v>26</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -25031,13 +25029,13 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F124">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G124">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H124">
         <v>4</v>
@@ -25069,13 +25067,13 @@
         <v>135</v>
       </c>
       <c r="E125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -25183,13 +25181,13 @@
         <v>29</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -25209,7 +25207,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B129" s="18">
         <v>2026</v>
@@ -25218,19 +25216,19 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="E129">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F129">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -25256,19 +25254,19 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E130">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F130">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G130">
         <v>2</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -25294,31 +25292,31 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131">
         <v>1</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>7647</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -25332,13 +25330,13 @@
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -25347,16 +25345,16 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132">
-        <v>7694</v>
+        <v>0</v>
       </c>
       <c r="K132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132">
-        <v>7694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -25370,13 +25368,13 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -25388,13 +25386,13 @@
         <v>1</v>
       </c>
       <c r="J133">
-        <v>5119</v>
+        <v>7694</v>
       </c>
       <c r="K133">
         <v>1</v>
       </c>
       <c r="L133">
-        <v>5119</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -25408,31 +25406,31 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E134">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F134">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G134">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134">
-        <v>0</v>
+        <v>5119</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -25446,19 +25444,19 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E135">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -25475,7 +25473,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B136" s="18">
         <v>2026</v>
@@ -25484,19 +25482,19 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -25522,19 +25520,19 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137">
         <v>0</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -25551,7 +25549,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B138" s="18">
         <v>2026</v>
@@ -25560,25 +25558,25 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E138">
         <v>1</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138">
         <v>0</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -25598,7 +25596,7 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -25607,10 +25605,10 @@
         <v>1</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -25636,19 +25634,19 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140">
         <v>1</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -25665,7 +25663,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B141" s="18">
         <v>2026</v>
@@ -25674,19 +25672,19 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G141">
         <v>1</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -25712,31 +25710,31 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142">
-        <v>6480</v>
+        <v>0</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142">
-        <v>6480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -25750,31 +25748,31 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E143">
         <v>4</v>
       </c>
       <c r="F143">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>7263</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143">
-        <v>0</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -25788,16 +25786,16 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -25826,16 +25824,16 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -25855,7 +25853,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B146" s="18">
         <v>2026</v>
@@ -25864,31 +25862,31 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J146">
-        <v>10440</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L146">
-        <v>10440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -25902,31 +25900,31 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H147">
         <v>1</v>
       </c>
       <c r="I147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J147">
-        <v>0</v>
+        <v>10440</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -25940,31 +25938,31 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H148">
         <v>1</v>
       </c>
       <c r="I148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148">
-        <v>8116</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148">
-        <v>8116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -25978,7 +25976,7 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -25987,22 +25985,22 @@
         <v>1</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -26016,31 +26014,31 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150">
-        <v>8458</v>
+        <v>0</v>
       </c>
       <c r="K150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150">
-        <v>8458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -26054,31 +26052,31 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -26092,19 +26090,19 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F152">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -26121,7 +26119,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B153" s="18">
         <v>2026</v>
@@ -26130,19 +26128,19 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -26168,7 +26166,7 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -26206,16 +26204,16 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E155">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F155">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -26244,19 +26242,19 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -26273,7 +26271,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B157" s="18">
         <v>2026</v>
@@ -26282,19 +26280,19 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E157">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F157">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -26320,19 +26318,19 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -26358,19 +26356,19 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="E159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G159">
         <v>0</v>
       </c>
       <c r="H159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -26396,19 +26394,19 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G160">
         <v>0</v>
       </c>
       <c r="H160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -26434,13 +26432,13 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -26472,19 +26470,19 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G162">
         <v>0</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -26510,13 +26508,13 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E163">
         <v>2</v>
       </c>
       <c r="F163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -26548,7 +26546,7 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E164">
         <v>1</v>
@@ -26577,7 +26575,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B165" s="18">
         <v>2026</v>
@@ -26586,16 +26584,16 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E165">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F165">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H165">
         <v>2</v>
@@ -26615,7 +26613,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B166" s="18">
         <v>2026</v>
@@ -26624,13 +26622,13 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="E166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -26662,19 +26660,19 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -26700,31 +26698,31 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="E168">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F168">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G168">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168">
-        <v>8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -26738,19 +26736,19 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E169">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F169">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -26776,51 +26774,57 @@
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E170">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L170">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>127</v>
       </c>
+      <c r="B171" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D171" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="E171">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -26837,22 +26841,28 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+      <c r="B172" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C172" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E172">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F172">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -26869,19 +26879,25 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+      <c r="B173" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C173" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="E173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -26903,20 +26919,26 @@
       <c r="A174" t="s">
         <v>128</v>
       </c>
+      <c r="B174" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C174" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D174" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -26935,14 +26957,20 @@
       <c r="A175" t="s">
         <v>128</v>
       </c>
+      <c r="B175" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D175" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E175">
         <v>1</v>
       </c>
       <c r="F175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -26967,52 +26995,64 @@
       <c r="A176" t="s">
         <v>128</v>
       </c>
+      <c r="B176" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C176" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D176" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F176">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G176">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H176">
         <v>0</v>
       </c>
       <c r="I176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="K176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L176">
-        <v>8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>128</v>
       </c>
+      <c r="B177" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D177" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E177">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F177">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -27031,8 +27071,14 @@
       <c r="A178" t="s">
         <v>128</v>
       </c>
+      <c r="B178" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C178" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D178" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -27063,52 +27109,64 @@
       <c r="A179" t="s">
         <v>128</v>
       </c>
+      <c r="B179" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D179" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H179">
         <v>0</v>
       </c>
       <c r="I179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="B180" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C180" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E180">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F180">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I180">
         <v>0</v>
@@ -27125,10 +27183,16 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="B181" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C181" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -27137,7 +27201,7 @@
         <v>1</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -27157,10 +27221,16 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="B182" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C182" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -27169,10 +27239,10 @@
         <v>1</v>
       </c>
       <c r="G182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -27191,52 +27261,64 @@
       <c r="A183" t="s">
         <v>129</v>
       </c>
+      <c r="B183" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C183" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D183" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E183">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J183">
-        <v>5859</v>
+        <v>0</v>
       </c>
       <c r="K183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L183">
-        <v>5859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>129</v>
       </c>
+      <c r="B184" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C184" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D184" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -27253,22 +27335,28 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="B185" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C185" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G185">
         <v>1</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -27285,54 +27373,66 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="B186" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C186" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E186">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F186">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>5859</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="B187" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C187" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -27349,7 +27449,13 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+      <c r="B188" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C188" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D188" t="s">
         <v>13</v>
@@ -27361,7 +27467,7 @@
         <v>3</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -27381,16 +27487,22 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+      <c r="B189" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C189" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -27413,10 +27525,16 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+      <c r="B190" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C190" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -27425,7 +27543,7 @@
         <v>1</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -27447,40 +27565,52 @@
       <c r="A191" t="s">
         <v>131</v>
       </c>
+      <c r="B191" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C191" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D191" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E191">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F191">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G191">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H191">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J191">
-        <v>25130.799999999999</v>
+        <v>0</v>
       </c>
       <c r="K191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L191">
-        <v>25130.799999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="B192" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C192" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -27509,10 +27639,16 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="B193" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C193" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -27521,7 +27657,7 @@
         <v>1</v>
       </c>
       <c r="G193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -27541,60 +27677,72 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="B194" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C194" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E194">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F194">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G194">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H194">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I194">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J194">
-        <v>7483.12</v>
+        <v>25130.799999999999</v>
       </c>
       <c r="K194">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L194">
-        <v>7483.12</v>
+        <v>25130.799999999999</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>132</v>
       </c>
+      <c r="B195" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C195" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D195" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195">
         <v>0</v>
       </c>
       <c r="I195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>6910</v>
       </c>
       <c r="K195">
         <v>0</v>
@@ -27607,31 +27755,151 @@
       <c r="A196" t="s">
         <v>132</v>
       </c>
+      <c r="B196" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C196" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="D196" t="s">
+        <v>135</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>132</v>
+      </c>
+      <c r="B197" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C197" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D197" t="s">
+        <v>52</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="F197">
+        <v>2</v>
+      </c>
+      <c r="G197">
+        <v>2</v>
+      </c>
+      <c r="H197">
+        <v>2</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>7483.12</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>7483.12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>132</v>
+      </c>
+      <c r="B198" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C198" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D198" t="s">
+        <v>55</v>
+      </c>
+      <c r="E198">
+        <v>2</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>132</v>
+      </c>
+      <c r="B199" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C199" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" t="s">
         <v>65</v>
       </c>
-      <c r="E196">
-        <v>4</v>
-      </c>
-      <c r="F196">
-        <v>4</v>
-      </c>
-      <c r="G196">
-        <v>1</v>
-      </c>
-      <c r="H196">
-        <v>0</v>
-      </c>
-      <c r="I196">
-        <v>0</v>
-      </c>
-      <c r="J196">
-        <v>0</v>
-      </c>
-      <c r="K196">
-        <v>0</v>
-      </c>
-      <c r="L196">
+      <c r="E199">
+        <v>5</v>
+      </c>
+      <c r="F199">
+        <v>5</v>
+      </c>
+      <c r="G199">
+        <v>2</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4A6875-6427-4953-9045-23A1E0FAFB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C814BC05-AAE7-4952-8BE5-ED5374D038EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="139">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1085,64 +1085,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>596.95999999999901</v>
+        <v>656.93999999999903</v>
       </c>
       <c r="C6" s="5">
-        <v>330.94</v>
+        <v>361.94</v>
       </c>
       <c r="D6" s="5">
-        <v>266.02</v>
+        <v>295</v>
       </c>
       <c r="E6" s="5">
-        <v>135066.35999999999</v>
+        <v>148033.99</v>
       </c>
       <c r="F6" s="5">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="G6" s="5">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H6" s="5">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="I6" s="5">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J6" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K6" s="5">
-        <v>502.10542750929301</v>
+        <v>503.51697278911502</v>
       </c>
       <c r="L6" s="5">
-        <v>1298.7149999999999</v>
+        <v>1254.52533898305</v>
       </c>
       <c r="M6" s="5">
-        <v>3.8688834140491801</v>
+        <v>6.1804522056049302</v>
       </c>
       <c r="N6" s="6">
-        <v>699.14</v>
+        <v>779.7</v>
       </c>
       <c r="O6" s="6">
-        <v>76807.850000000006</v>
+        <v>85256.959999999905</v>
       </c>
       <c r="P6" s="6">
-        <v>409</v>
+        <v>454</v>
       </c>
       <c r="Q6" s="6">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="R6" s="6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S6" s="6">
-        <v>187.794254278728</v>
+        <v>187.790660792951</v>
       </c>
       <c r="T6" s="6">
-        <v>783.75357142857104</v>
+        <v>754.48637168141499</v>
       </c>
       <c r="U6" s="6">
-        <v>113.19861186063601</v>
+        <v>123.526161383187</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1157,7 +1157,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1169,7 +1169,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,64 +1177,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>126.96</v>
+        <v>140.96</v>
       </c>
       <c r="C7" s="5">
-        <v>60.09</v>
+        <v>66.09</v>
       </c>
       <c r="D7" s="5">
-        <v>66.87</v>
+        <v>74.87</v>
       </c>
       <c r="E7" s="5">
-        <v>4517.24</v>
+        <v>5123.1000000000004</v>
       </c>
       <c r="F7" s="5">
+        <v>78</v>
+      </c>
+      <c r="G7" s="5">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5">
         <v>70</v>
       </c>
-      <c r="G7" s="5">
-        <v>7</v>
-      </c>
-      <c r="H7" s="5">
-        <v>63</v>
-      </c>
       <c r="I7" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J7" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7" s="5">
-        <v>64.531999999999996</v>
+        <v>65.680769230769201</v>
       </c>
       <c r="L7" s="5">
-        <v>205.32909090909001</v>
+        <v>197.04230769230699</v>
       </c>
       <c r="M7" s="5">
-        <v>482.56811681469202</v>
+        <v>616.48025609494198</v>
       </c>
       <c r="N7" s="6">
-        <v>119.48</v>
+        <v>140.69999999999999</v>
       </c>
       <c r="O7" s="6">
-        <v>7014.78</v>
+        <v>7909.06</v>
       </c>
       <c r="P7" s="6">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="Q7" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R7" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S7" s="6">
-        <v>48.377793103448198</v>
+        <v>51.026193548387099</v>
       </c>
       <c r="T7" s="6">
-        <v>184.59947368421001</v>
+        <v>202.79641025641001</v>
       </c>
       <c r="U7" s="6">
-        <v>933.50354537134399</v>
+        <v>1027.1293933792299</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1249,7 +1249,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1261,7 +1261,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1278,7 +1278,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E8" s="5">
-        <v>3711.22</v>
+        <v>4043.73</v>
       </c>
       <c r="F8" s="5">
         <v>4</v>
@@ -1296,23 +1296,23 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>927.80499999999995</v>
+        <v>1010.9325</v>
       </c>
       <c r="L8" s="5">
-        <v>1237.0733333333301</v>
+        <v>1347.91</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
       <c r="N8" s="6">
+        <v>7</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1130.74</v>
+      </c>
+      <c r="P8" s="6">
         <v>6</v>
       </c>
-      <c r="O8" s="6">
-        <v>998.12</v>
-      </c>
-      <c r="P8" s="6">
-        <v>5</v>
-      </c>
       <c r="Q8" s="6">
         <v>2</v>
       </c>
@@ -1320,13 +1320,13 @@
         <v>1</v>
       </c>
       <c r="S8" s="6">
-        <v>199.624</v>
+        <v>188.456666666666</v>
       </c>
       <c r="T8" s="6">
-        <v>499.06</v>
+        <v>565.37</v>
       </c>
       <c r="U8" s="6">
-        <v>33.551076022922999</v>
+        <v>17.8874011709146</v>
       </c>
       <c r="V8" s="7">
         <v>12</v>
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1361,64 +1361,64 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>47.66</v>
+        <v>53.66</v>
       </c>
       <c r="C9" s="5">
-        <v>25.66</v>
+        <v>30.66</v>
       </c>
       <c r="D9" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5">
-        <v>14925.18</v>
+        <v>16436.72</v>
       </c>
       <c r="F9" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>746.25900000000001</v>
+        <v>782.700952380952</v>
       </c>
       <c r="L9" s="5">
-        <v>2132.16857142857</v>
+        <v>2054.59</v>
       </c>
       <c r="M9" s="5">
-        <v>-4.26246115624736</v>
+        <v>-13.066597228644101</v>
       </c>
       <c r="N9" s="6">
-        <v>12.84</v>
+        <v>14.84</v>
       </c>
       <c r="O9" s="6">
-        <v>2939.1</v>
+        <v>3364.98</v>
       </c>
       <c r="P9" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="6">
         <v>2</v>
       </c>
       <c r="R9" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" s="6">
-        <v>139.957142857142</v>
+        <v>140.20750000000001</v>
       </c>
       <c r="T9" s="6">
-        <v>1469.55</v>
+        <v>1682.49</v>
       </c>
       <c r="U9" s="6">
-        <v>188.693817835391</v>
+        <v>231.027227502095</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1445,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1489,7 +1489,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1509,13 +1509,13 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>67.789999999999907</v>
+        <v>70.789999999999907</v>
       </c>
       <c r="O11" s="6">
-        <v>3575.05</v>
+        <v>3911.34</v>
       </c>
       <c r="P11" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q11" s="6">
         <v>2</v>
@@ -1524,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>510.72142857142802</v>
+        <v>488.91750000000002</v>
       </c>
       <c r="T11" s="6">
-        <v>1787.5250000000001</v>
+        <v>1955.67</v>
       </c>
       <c r="U11" s="6">
-        <v>110.96208444637099</v>
+        <v>92.823942689717498</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1551,7 +1551,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1568,7 +1568,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>2253.6999999999998</v>
+        <v>2411.5500000000002</v>
       </c>
       <c r="F12" s="5">
         <v>6</v>
@@ -1586,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>375.61666666666599</v>
+        <v>401.92500000000001</v>
       </c>
       <c r="L12" s="5">
-        <v>2253.6999999999998</v>
+        <v>2411.5500000000002</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
@@ -1598,7 +1598,7 @@
         <v>6.02</v>
       </c>
       <c r="O12" s="6">
-        <v>995.21</v>
+        <v>1140.02</v>
       </c>
       <c r="P12" s="6">
         <v>5</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>199.042</v>
+        <v>228.00399999999999</v>
       </c>
       <c r="T12" s="6">
-        <v>497.60500000000002</v>
+        <v>570.01</v>
       </c>
       <c r="U12" s="6">
         <v>-100</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1687,7 +1687,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1707,10 +1707,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>10.08</v>
+        <v>11.08</v>
       </c>
       <c r="O14" s="6">
-        <v>989.39</v>
+        <v>1152.4000000000001</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1737,7 +1737,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>254.84</v>
+        <v>261.54000000000002</v>
       </c>
       <c r="P15" s="6">
         <v>2</v>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>127.42</v>
+        <v>130.77000000000001</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1809,25 +1809,25 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="5">
-        <v>566.04999999999995</v>
+        <v>1221.7</v>
       </c>
       <c r="F16" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
       </c>
       <c r="H16" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I16" s="5">
         <v>2</v>
@@ -1836,34 +1836,34 @@
         <v>1</v>
       </c>
       <c r="K16" s="5">
-        <v>141.51249999999999</v>
+        <v>152.71250000000001</v>
       </c>
       <c r="L16" s="5">
-        <v>283.02499999999998</v>
+        <v>610.85</v>
       </c>
       <c r="M16" s="5">
-        <v>1250.94072961752</v>
+        <v>525.93107964312003</v>
       </c>
       <c r="N16" s="6">
-        <v>21.99</v>
+        <v>24.99</v>
       </c>
       <c r="O16" s="6">
-        <v>5209.58</v>
+        <v>5840.76</v>
       </c>
       <c r="P16" s="6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q16" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>200.36846153846099</v>
+        <v>194.69200000000001</v>
       </c>
       <c r="T16" s="6">
-        <v>868.26333333333298</v>
+        <v>648.97333333333302</v>
       </c>
       <c r="U16" s="6">
         <v>-100</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,25 +1913,25 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>59.68</v>
+        <v>60.68</v>
       </c>
       <c r="O17" s="6">
-        <v>3787.36</v>
+        <v>4083.01</v>
       </c>
       <c r="P17" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="6">
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>315.613333333333</v>
+        <v>291.64357142857102</v>
       </c>
       <c r="T17" s="6">
-        <v>3787.36</v>
+        <v>2041.5050000000001</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1955,7 +1955,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1978,7 +1978,7 @@
         <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>729.14</v>
+        <v>822.48</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1990,10 +1990,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>243.046666666666</v>
+        <v>274.16000000000003</v>
       </c>
       <c r="T18" s="6">
-        <v>729.14</v>
+        <v>822.48</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -2021,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2041,10 +2041,10 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="6">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="O19" s="6">
-        <v>1016.94</v>
+        <v>1097.23</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2071,7 +2071,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2094,7 +2094,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="6">
-        <v>1449.11</v>
+        <v>1586.62</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2121,7 +2121,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2138,7 +2138,7 @@
         <v>18.989999999999998</v>
       </c>
       <c r="E21" s="5">
-        <v>5339.78</v>
+        <v>5412.08</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2167,7 +2167,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2213,7 +2213,7 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2234,7 +2234,7 @@
         <v>22</v>
       </c>
       <c r="I23" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="5">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2271,40 +2271,40 @@
         <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>65.11</v>
+        <v>70.11</v>
       </c>
       <c r="C24" s="5">
-        <v>61.12</v>
+        <v>64.12</v>
       </c>
       <c r="D24" s="5">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="E24" s="5">
-        <v>14326.02</v>
+        <v>15756.97</v>
       </c>
       <c r="F24" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G24" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24" s="5">
         <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>1790.7525000000001</v>
+        <v>1432.45181818181</v>
       </c>
       <c r="L24" s="5">
-        <v>7163.01</v>
+        <v>3939.2424999999998</v>
       </c>
       <c r="M24" s="5">
-        <v>-46.293527441675998</v>
+        <v>-51.170815201145899</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2329,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2346,7 +2346,7 @@
         <v>7.67</v>
       </c>
       <c r="E25" s="5">
-        <v>2487.0700000000002</v>
+        <v>2730.54</v>
       </c>
       <c r="F25" s="5">
         <v>7</v>
@@ -2364,19 +2364,19 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>355.29571428571398</v>
+        <v>390.07714285714201</v>
       </c>
       <c r="L25" s="5">
-        <v>2487.0700000000002</v>
+        <v>2730.54</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>5</v>
+        <v>7.02</v>
       </c>
       <c r="O25" s="6">
-        <v>1029.5899999999999</v>
+        <v>1164.8900000000001</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -2409,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2417,16 +2417,16 @@
         <v>42</v>
       </c>
       <c r="B26" s="5">
-        <v>5.46</v>
+        <v>6.46</v>
       </c>
       <c r="C26" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="5">
         <v>4.46</v>
       </c>
       <c r="E26" s="5">
-        <v>2610.1799999999998</v>
+        <v>2812.04</v>
       </c>
       <c r="F26" s="5">
         <v>5</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>522.03599999999994</v>
+        <v>562.40800000000002</v>
       </c>
       <c r="L26" s="5">
-        <v>870.06</v>
+        <v>937.34666666666601</v>
       </c>
       <c r="M26" s="5">
         <v>-100</v>
@@ -2456,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="6">
-        <v>408.05</v>
+        <v>428.06</v>
       </c>
       <c r="P26" s="6">
         <v>4</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <v>102.0125</v>
+        <v>107.015</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
@@ -2499,7 +2499,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2507,16 +2507,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>9.75</v>
+        <v>11.75</v>
       </c>
       <c r="C27" s="5">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="D27" s="5">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E27" s="5">
-        <v>4463.3599999999997</v>
+        <v>4851.8</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -2534,22 +2534,22 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>4463.3599999999997</v>
+        <v>4851.8</v>
       </c>
       <c r="L27" s="5">
-        <v>4463.3599999999997</v>
+        <v>4851.8</v>
       </c>
       <c r="M27" s="5">
-        <v>81.836105534843696</v>
+        <v>67.278123583000095</v>
       </c>
       <c r="N27" s="6">
-        <v>22.33</v>
+        <v>24.31</v>
       </c>
       <c r="O27" s="6">
-        <v>4449.97</v>
+        <v>4956</v>
       </c>
       <c r="P27" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="6">
         <v>6</v>
@@ -2558,13 +2558,13 @@
         <v>2</v>
       </c>
       <c r="S27" s="6">
-        <v>278.12312500000002</v>
+        <v>275.33333333333297</v>
       </c>
       <c r="T27" s="6">
-        <v>741.66166666666595</v>
+        <v>826</v>
       </c>
       <c r="U27" s="6">
-        <v>232.60898388078999</v>
+        <v>198.64810330911999</v>
       </c>
       <c r="V27" s="7">
         <v>66.569999999999993</v>
@@ -2591,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="AD27" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2614,22 +2614,22 @@
         <v>18.579999999999998</v>
       </c>
       <c r="O28" s="6">
-        <v>1404.47</v>
+        <v>1530.43</v>
       </c>
       <c r="P28" s="6">
         <v>10</v>
       </c>
       <c r="Q28" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>140.447</v>
+        <v>153.04300000000001</v>
       </c>
       <c r="T28" s="6">
-        <v>1404.47</v>
+        <v>765.21500000000003</v>
       </c>
       <c r="U28" s="6">
         <v>-100</v>
@@ -2653,7 +2653,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2661,16 +2661,16 @@
         <v>45</v>
       </c>
       <c r="B29" s="5">
-        <v>15.66</v>
+        <v>17.66</v>
       </c>
       <c r="C29" s="5">
-        <v>4.67</v>
+        <v>6.67</v>
       </c>
       <c r="D29" s="5">
         <v>10.99</v>
       </c>
       <c r="E29" s="5">
-        <v>4791.03</v>
+        <v>5213.82</v>
       </c>
       <c r="F29" s="5">
         <v>12</v>
@@ -2688,37 +2688,37 @@
         <v>1</v>
       </c>
       <c r="K29" s="5">
-        <v>399.2525</v>
+        <v>434.48500000000001</v>
       </c>
       <c r="L29" s="5">
-        <v>1197.7574999999999</v>
+        <v>1303.4549999999999</v>
       </c>
       <c r="M29" s="5">
-        <v>6.8455008630711998</v>
+        <v>-1.8186281843254899</v>
       </c>
       <c r="N29" s="6">
-        <v>12.58</v>
+        <v>14.54</v>
       </c>
       <c r="O29" s="6">
-        <v>2049.96</v>
+        <v>2271.2399999999998</v>
       </c>
       <c r="P29" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="6">
         <v>6</v>
       </c>
       <c r="R29" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S29" s="6">
-        <v>170.83</v>
+        <v>174.71076923076899</v>
       </c>
       <c r="T29" s="6">
-        <v>341.66</v>
+        <v>378.539999999999</v>
       </c>
       <c r="U29" s="6">
-        <v>974.13412944642801</v>
+        <v>1200.4490938870399</v>
       </c>
       <c r="V29" s="7">
         <v>55.58</v>
@@ -2733,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="Z29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA29" s="8">
         <v>13000</v>
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2765,13 +2765,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>34.51</v>
+        <v>37.51</v>
       </c>
       <c r="O30" s="6">
-        <v>2448.02</v>
+        <v>2652.42</v>
       </c>
       <c r="P30" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>306.0025</v>
+        <v>241.12909090909</v>
       </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6">
@@ -2805,7 +2805,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2825,25 +2825,25 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="6">
-        <v>37.04</v>
+        <v>42.05</v>
       </c>
       <c r="O31" s="6">
-        <v>2931.44</v>
+        <v>3260.41</v>
       </c>
       <c r="P31" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" s="6">
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <v>488.57333333333298</v>
+        <v>407.55124999999998</v>
       </c>
       <c r="T31" s="6">
-        <v>2931.44</v>
+        <v>1630.2049999999999</v>
       </c>
       <c r="U31" s="6">
         <v>-100</v>
@@ -2867,7 +2867,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2875,46 +2875,46 @@
         <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>35.93</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="C32" s="5">
-        <v>20.43</v>
+        <v>21.43</v>
       </c>
       <c r="D32" s="5">
-        <v>15.5</v>
+        <v>18.48</v>
       </c>
       <c r="E32" s="5">
-        <v>9914.74</v>
+        <v>11084.85</v>
       </c>
       <c r="F32" s="5">
+        <v>19</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5">
         <v>17</v>
       </c>
-      <c r="G32" s="5">
-        <v>2</v>
-      </c>
-      <c r="H32" s="5">
-        <v>15</v>
-      </c>
       <c r="I32" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="5">
-        <v>583.22</v>
+        <v>583.41315789473595</v>
       </c>
       <c r="L32" s="5">
-        <v>1652.4566666666601</v>
+        <v>1583.55</v>
       </c>
       <c r="M32" s="5">
-        <v>-13.250372677447899</v>
+        <v>45.092085143235998</v>
       </c>
       <c r="N32" s="6">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="O32" s="6">
-        <v>3938.92</v>
+        <v>4446.25</v>
       </c>
       <c r="P32" s="6">
         <v>19</v>
@@ -2926,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="6">
-        <v>207.31157894736799</v>
+        <v>234.013157894736</v>
       </c>
       <c r="T32" s="6">
-        <v>1312.9733333333299</v>
+        <v>1482.0833333333301</v>
       </c>
       <c r="U32" s="6">
         <v>-100</v>
@@ -2959,7 +2959,7 @@
         <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2967,25 +2967,25 @@
         <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>33.659999999999997</v>
+        <v>34.81</v>
       </c>
       <c r="C33" s="5">
-        <v>10.95</v>
+        <v>11.1</v>
       </c>
       <c r="D33" s="5">
-        <v>22.71</v>
+        <v>23.71</v>
       </c>
       <c r="E33" s="5">
-        <v>10985.68</v>
+        <v>11872.43</v>
       </c>
       <c r="F33" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
       </c>
       <c r="H33" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="5">
         <v>8</v>
@@ -2994,13 +2994,13 @@
         <v>3</v>
       </c>
       <c r="K33" s="5">
-        <v>646.21647058823498</v>
+        <v>659.57944444444399</v>
       </c>
       <c r="L33" s="5">
-        <v>1373.21</v>
+        <v>1484.05375</v>
       </c>
       <c r="M33" s="5">
-        <v>120.806722933855</v>
+        <v>104.31470221344701</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3025,7 +3025,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3033,22 +3033,22 @@
         <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>45.34</v>
+        <v>50.34</v>
       </c>
       <c r="C34" s="5">
-        <v>18.59</v>
+        <v>22.59</v>
       </c>
       <c r="D34" s="5">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
       <c r="E34" s="5">
-        <v>10954.77</v>
+        <v>11968.76</v>
       </c>
       <c r="F34" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G34" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="5">
         <v>24</v>
@@ -3060,13 +3060,13 @@
         <v>2</v>
       </c>
       <c r="K34" s="5">
-        <v>438.19080000000002</v>
+        <v>460.33692307692297</v>
       </c>
       <c r="L34" s="5">
-        <v>1095.4770000000001</v>
+        <v>1196.876</v>
       </c>
       <c r="M34" s="5">
-        <v>-46.516448998929199</v>
+        <v>-51.0475604824559</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3091,7 +3091,7 @@
         <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3099,64 +3099,64 @@
         <v>55</v>
       </c>
       <c r="B35" s="5">
-        <v>36.32</v>
+        <v>39.32</v>
       </c>
       <c r="C35" s="5">
-        <v>28.49</v>
+        <v>29.49</v>
       </c>
       <c r="D35" s="5">
-        <v>7.83</v>
+        <v>9.83</v>
       </c>
       <c r="E35" s="5">
-        <v>10168.52</v>
+        <v>11448.69</v>
       </c>
       <c r="F35" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G35" s="5">
         <v>6</v>
       </c>
       <c r="H35" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" s="5">
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>677.90133333333301</v>
+        <v>715.54312500000003</v>
       </c>
       <c r="L35" s="5">
-        <v>2542.13</v>
+        <v>1908.115</v>
       </c>
       <c r="M35" s="5">
         <v>-100</v>
       </c>
       <c r="N35" s="6">
-        <v>25.59</v>
+        <v>28.37</v>
       </c>
       <c r="O35" s="6">
-        <v>8569.51</v>
+        <v>9495.82</v>
       </c>
       <c r="P35" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q35" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R35" s="6">
         <v>3</v>
       </c>
       <c r="S35" s="6">
-        <v>225.513421052631</v>
+        <v>231.60536585365799</v>
       </c>
       <c r="T35" s="6">
-        <v>779.04636363636303</v>
+        <v>730.44769230769202</v>
       </c>
       <c r="U35" s="6">
-        <v>172.10622310960599</v>
+        <v>145.56246853878801</v>
       </c>
       <c r="V35" s="7">
         <v>110.24</v>
@@ -3183,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="AD35" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3203,10 +3203,10 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="6">
-        <v>74.66</v>
+        <v>81.2</v>
       </c>
       <c r="O36" s="6">
-        <v>2677.98</v>
+        <v>3033.65</v>
       </c>
       <c r="P36" s="6">
         <v>8</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="6">
-        <v>334.7475</v>
+        <v>379.20625000000001</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6">
@@ -3243,7 +3243,7 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3251,16 +3251,16 @@
         <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>13.32</v>
+        <v>14.32</v>
       </c>
       <c r="C37" s="5">
-        <v>6.33</v>
+        <v>7.33</v>
       </c>
       <c r="D37" s="5">
         <v>6.99</v>
       </c>
       <c r="E37" s="5">
-        <v>2889.48</v>
+        <v>3120.24</v>
       </c>
       <c r="F37" s="5">
         <v>4</v>
@@ -3278,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>722.37</v>
+        <v>780.06</v>
       </c>
       <c r="L37" s="5">
-        <v>2889.48</v>
+        <v>3120.24</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
@@ -3309,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="AD37" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3317,22 +3317,22 @@
         <v>58</v>
       </c>
       <c r="B38" s="5">
-        <v>28.74</v>
+        <v>31.74</v>
       </c>
       <c r="C38" s="5">
-        <v>21.49</v>
+        <v>22.49</v>
       </c>
       <c r="D38" s="5">
-        <v>7.25</v>
+        <v>9.25</v>
       </c>
       <c r="E38" s="5">
-        <v>6803.57</v>
+        <v>7308.75</v>
       </c>
       <c r="F38" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="5">
         <v>4</v>
@@ -3344,37 +3344,37 @@
         <v>0</v>
       </c>
       <c r="K38" s="5">
-        <v>1360.7139999999999</v>
+        <v>1218.125</v>
       </c>
       <c r="L38" s="5">
-        <v>2267.8566666666602</v>
+        <v>2436.25</v>
       </c>
       <c r="M38" s="5">
         <v>-100</v>
       </c>
       <c r="N38" s="6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="O38" s="6">
-        <v>3711.6</v>
+        <v>4093.35</v>
       </c>
       <c r="P38" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q38" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R38" s="6">
         <v>1</v>
       </c>
       <c r="S38" s="6">
-        <v>185.57999999999899</v>
+        <v>163.73400000000001</v>
       </c>
       <c r="T38" s="6">
-        <v>530.22857142857094</v>
+        <v>341.11250000000001</v>
       </c>
       <c r="U38" s="6">
-        <v>130.41275999568899</v>
+        <v>108.924230764532</v>
       </c>
       <c r="V38" s="7">
         <v>42.5</v>
@@ -3401,7 +3401,7 @@
         <v>16</v>
       </c>
       <c r="AD38" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3421,13 +3421,13 @@
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="6">
-        <v>30.34</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="O39" s="6">
-        <v>2127.2800000000002</v>
+        <v>2326.6999999999998</v>
       </c>
       <c r="P39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="6">
         <v>1</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="6">
-        <v>1063.6400000000001</v>
+        <v>581.67499999999995</v>
       </c>
       <c r="T39" s="6">
-        <v>2127.2800000000002</v>
+        <v>2326.6999999999998</v>
       </c>
       <c r="U39" s="6">
         <v>-100</v>
@@ -3463,7 +3463,7 @@
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3471,37 +3471,37 @@
         <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>10.17</v>
+        <v>13.17</v>
       </c>
       <c r="C40" s="5">
-        <v>5.67</v>
+        <v>6.67</v>
       </c>
       <c r="D40" s="5">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E40" s="5">
-        <v>6334.25</v>
+        <v>6870.74</v>
       </c>
       <c r="F40" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="5">
         <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="5">
         <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>3167.125</v>
+        <v>1717.6849999999999</v>
       </c>
       <c r="L40" s="5">
-        <v>6334.25</v>
+        <v>3435.37</v>
       </c>
       <c r="M40" s="5">
         <v>-100</v>
@@ -3510,7 +3510,7 @@
         <v>0.98</v>
       </c>
       <c r="O40" s="6">
-        <v>350.58</v>
+        <v>456.91</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -3533,7 +3533,7 @@
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
@@ -3541,49 +3541,49 @@
         <v>60</v>
       </c>
       <c r="B41">
-        <v>19.87</v>
+        <v>22.72</v>
       </c>
       <c r="C41">
-        <v>7.87</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>6744.19</v>
+        <v>7663.34</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41">
         <v>14</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41">
-        <v>396.71705882352899</v>
+        <v>425.74111111111102</v>
       </c>
       <c r="L41">
-        <v>674.41899999999998</v>
+        <v>638.611666666666</v>
       </c>
       <c r="M41">
-        <v>272.62888501065299</v>
+        <v>215.134132114717</v>
       </c>
       <c r="N41">
-        <v>17.16</v>
+        <v>18.16</v>
       </c>
       <c r="O41">
-        <v>3208.69</v>
+        <v>3631.19</v>
       </c>
       <c r="P41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -3592,13 +3592,13 @@
         <v>1</v>
       </c>
       <c r="S41">
-        <v>160.43450000000001</v>
+        <v>172.91380952380899</v>
       </c>
       <c r="T41">
-        <v>1069.5633333333301</v>
+        <v>1210.3966666666599</v>
       </c>
       <c r="U41">
-        <v>62.2088765197011</v>
+        <v>43.335380412481797</v>
       </c>
       <c r="V41">
         <v>52.03</v>
@@ -3625,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="AD41" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
@@ -3633,13 +3633,13 @@
         <v>61</v>
       </c>
       <c r="N42">
-        <v>39.56</v>
+        <v>46.56</v>
       </c>
       <c r="O42">
-        <v>2999.83</v>
+        <v>3336.66</v>
       </c>
       <c r="P42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3648,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <v>374.97874999999999</v>
+        <v>303.33272727272703</v>
       </c>
       <c r="T42">
-        <v>2999.83</v>
+        <v>3336.66</v>
       </c>
       <c r="U42">
         <v>-100</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="AD42" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
@@ -3680,16 +3680,16 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>16.66</v>
+        <v>18.66</v>
       </c>
       <c r="C43">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="D43">
-        <v>6.67</v>
+        <v>7.67</v>
       </c>
       <c r="E43">
-        <v>4115.1400000000003</v>
+        <v>4516.95</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -3707,34 +3707,34 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>823.02800000000002</v>
+        <v>903.39</v>
       </c>
       <c r="L43">
-        <v>2057.5700000000002</v>
+        <v>2258.4749999999999</v>
       </c>
       <c r="M43">
         <v>-100</v>
       </c>
       <c r="N43">
-        <v>6.0299999999999896</v>
+        <v>7.03</v>
       </c>
       <c r="O43">
-        <v>1468.67</v>
+        <v>1615.87</v>
       </c>
       <c r="P43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>183.58375000000001</v>
+        <v>179.54111111111101</v>
       </c>
       <c r="T43">
-        <v>489.55666666666599</v>
+        <v>403.96749999999997</v>
       </c>
       <c r="U43">
         <v>-100</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="AD43" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
@@ -3772,13 +3772,13 @@
         <v>66</v>
       </c>
       <c r="N44">
-        <v>19.690000000000001</v>
+        <v>24.69</v>
       </c>
       <c r="O44">
-        <v>1740.8</v>
+        <v>1923.06</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>435.2</v>
+        <v>384.611999999999</v>
       </c>
       <c r="T44">
-        <v>1740.8</v>
+        <v>1923.06</v>
       </c>
       <c r="U44">
         <v>-100</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
@@ -3839,6 +3839,9 @@
       <c r="AC45">
         <v>1</v>
       </c>
+      <c r="AD45" s="13">
+        <v>46154</v>
+      </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -3880,6 +3883,9 @@
       <c r="Z46">
         <v>0</v>
       </c>
+      <c r="AD46" s="13">
+        <v>46154</v>
+      </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -3969,6 +3975,9 @@
       <c r="AC47">
         <v>6</v>
       </c>
+      <c r="AD47" s="13">
+        <v>46154</v>
+      </c>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -4013,8 +4022,11 @@
       <c r="Z48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD48" s="13">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>137</v>
       </c>
@@ -4038,6 +4050,9 @@
       </c>
       <c r="AC49">
         <v>1</v>
+      </c>
+      <c r="AD49" s="13">
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
@@ -4924,16 +4939,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
+        <v>35</v>
+      </c>
+      <c r="E21" s="10">
         <v>33</v>
       </c>
-      <c r="E21" s="10">
-        <v>31</v>
-      </c>
       <c r="F21" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G21" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
@@ -4948,19 +4963,19 @@
         <v>23255</v>
       </c>
       <c r="L21" s="10">
-        <v>12.27</v>
+        <v>11.9</v>
       </c>
       <c r="M21" s="10">
-        <v>16.579999999999998</v>
+        <v>14.79</v>
       </c>
       <c r="N21" s="10">
-        <v>48.48</v>
+        <v>54.29</v>
       </c>
       <c r="O21" s="10">
-        <v>18.75</v>
+        <v>15.79</v>
       </c>
       <c r="P21" s="10">
-        <v>9.09</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -4998,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -5022,13 +5037,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E23" s="10">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F23" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" s="10">
         <v>8</v>
@@ -5046,19 +5061,19 @@
         <v>20460</v>
       </c>
       <c r="L23" s="10">
-        <v>10.78</v>
+        <v>12.93</v>
       </c>
       <c r="M23" s="10">
-        <v>14.58</v>
+        <v>13.02</v>
       </c>
       <c r="N23" s="10">
-        <v>41.38</v>
+        <v>39.47</v>
       </c>
       <c r="O23" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P23" s="10">
-        <v>10.34</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -5081,13 +5096,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="10">
-        <v>285</v>
+        <v>5975</v>
       </c>
       <c r="J24" s="10">
         <v>0</v>
@@ -5096,17 +5111,17 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="M24" s="10">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -5120,10 +5135,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="10">
         <v>2</v>
@@ -5144,13 +5159,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -5179,7 +5194,7 @@
         <v>6</v>
       </c>
       <c r="G26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="10">
         <v>1</v>
@@ -5194,10 +5209,10 @@
         <v>7263</v>
       </c>
       <c r="L26" s="10">
-        <v>4.83</v>
+        <v>4.42</v>
       </c>
       <c r="M26" s="10">
-        <v>5.18</v>
+        <v>4.62</v>
       </c>
       <c r="N26" s="10">
         <v>46.15</v>
@@ -5220,43 +5235,43 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E27" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F27" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G27" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="10">
-        <v>27014</v>
+        <v>18698</v>
       </c>
       <c r="J27" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="10">
-        <v>27014</v>
+        <v>18698</v>
       </c>
       <c r="L27" s="10">
-        <v>8.18</v>
+        <v>8.16</v>
       </c>
       <c r="M27" s="10">
-        <v>19.260000000000002</v>
+        <v>11.9</v>
       </c>
       <c r="N27" s="10">
-        <v>63.64</v>
+        <v>70.83</v>
       </c>
       <c r="O27" s="10">
-        <v>28.57</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="P27" s="10">
-        <v>18.18</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5279,7 +5294,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -5294,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>4.46</v>
+        <v>4.08</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -5320,16 +5335,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E29" s="10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F29" s="10">
         <v>1</v>
       </c>
       <c r="G29" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" s="10">
         <v>0</v>
@@ -5344,13 +5359,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>14.13</v>
+        <v>13.61</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O29" s="10">
         <v>0</v>
@@ -5370,43 +5385,43 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E30" s="10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F30" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="10">
         <v>4</v>
       </c>
       <c r="H30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="10">
-        <v>8316</v>
+        <v>15860</v>
       </c>
       <c r="J30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="10">
-        <v>8316</v>
+        <v>15860</v>
       </c>
       <c r="L30" s="10">
-        <v>10.78</v>
+        <v>11.56</v>
       </c>
       <c r="M30" s="10">
-        <v>5.93</v>
+        <v>10.09</v>
       </c>
       <c r="N30" s="10">
-        <v>37.93</v>
+        <v>35.29</v>
       </c>
       <c r="O30" s="10">
-        <v>9.09</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P30" s="10">
-        <v>3.45</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5420,43 +5435,43 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E31" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F31" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G31" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H31" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="10">
-        <v>8316</v>
+        <v>21270.240000000002</v>
       </c>
       <c r="J31" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="10">
-        <v>8316</v>
+        <v>21270.240000000002</v>
       </c>
       <c r="L31" s="10">
-        <v>13.01</v>
+        <v>12.59</v>
       </c>
       <c r="M31" s="10">
-        <v>5.93</v>
+        <v>13.53</v>
       </c>
       <c r="N31" s="10">
-        <v>34.29</v>
+        <v>40.54</v>
       </c>
       <c r="O31" s="10">
-        <v>8.33</v>
+        <v>20</v>
       </c>
       <c r="P31" s="10">
-        <v>2.86</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -5476,10 +5491,10 @@
         <v>13</v>
       </c>
       <c r="F32" s="10">
+        <v>8</v>
+      </c>
+      <c r="G32" s="10">
         <v>7</v>
-      </c>
-      <c r="G32" s="10">
-        <v>5</v>
       </c>
       <c r="H32" s="10">
         <v>2</v>
@@ -5494,16 +5509,16 @@
         <v>5859</v>
       </c>
       <c r="L32" s="10">
-        <v>4.83</v>
+        <v>4.42</v>
       </c>
       <c r="M32" s="10">
-        <v>4.18</v>
+        <v>3.73</v>
       </c>
       <c r="N32" s="10">
-        <v>53.85</v>
+        <v>61.54</v>
       </c>
       <c r="O32" s="10">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="P32" s="10">
         <v>15.38</v>
@@ -5520,13 +5535,13 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E33" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F33" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -5544,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>2.97</v>
+        <v>3.74</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>25</v>
+        <v>27.27</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
@@ -5570,43 +5585,43 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E34" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F34" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" s="10">
+        <v>4</v>
+      </c>
+      <c r="H34" s="10">
         <v>3</v>
       </c>
-      <c r="H34" s="10">
-        <v>4</v>
-      </c>
       <c r="I34" s="10">
-        <v>25130.799999999999</v>
+        <v>24149.8</v>
       </c>
       <c r="J34" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="10">
-        <v>25130.799999999999</v>
+        <v>24149.8</v>
       </c>
       <c r="L34" s="10">
-        <v>5.58</v>
+        <v>5.44</v>
       </c>
       <c r="M34" s="10">
-        <v>17.91</v>
+        <v>15.36</v>
       </c>
       <c r="N34" s="10">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="O34" s="10">
-        <v>44.44</v>
+        <v>30</v>
       </c>
       <c r="P34" s="10">
-        <v>26.67</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5629,7 +5644,7 @@
         <v>6</v>
       </c>
       <c r="G35" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="10">
         <v>2</v>
@@ -5644,10 +5659,10 @@
         <v>7483.12</v>
       </c>
       <c r="L35" s="10">
-        <v>4.09</v>
+        <v>3.74</v>
       </c>
       <c r="M35" s="10">
-        <v>10.26</v>
+        <v>9.16</v>
       </c>
       <c r="N35" s="10">
         <v>54.55</v>
@@ -5667,7 +5682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O435"/>
+  <dimension ref="A1:O431"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5739,7 +5754,7 @@
         <v>667.25</v>
       </c>
       <c r="G5" s="5">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H5" s="5">
         <v>70</v>
@@ -5879,7 +5894,7 @@
         <v>357.99</v>
       </c>
       <c r="G9" s="5">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H9" s="5">
         <v>105</v>
@@ -6019,7 +6034,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -6124,7 +6139,7 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H16" s="5">
         <v>140</v>
@@ -6238,10 +6253,10 @@
         <v>53</v>
       </c>
       <c r="J19" s="5">
-        <v>379800.09</v>
+        <v>382052.09</v>
       </c>
       <c r="K19" s="5">
-        <v>37.299999999999997</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -6290,28 +6305,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1557</v>
+        <v>1731</v>
       </c>
       <c r="E21" s="10">
-        <v>4517.24</v>
+        <v>5123.1000000000004</v>
       </c>
       <c r="F21" s="10">
-        <v>126.96</v>
+        <v>140.96</v>
       </c>
       <c r="G21" s="10">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H21" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I21" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>19406</v>
+        <v>24106</v>
       </c>
       <c r="K21" s="10">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6885,10 +6900,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="E38" s="10">
-        <v>3711.22</v>
+        <v>4043.73</v>
       </c>
       <c r="F38" s="10">
         <v>9.35</v>
@@ -7139,10 +7154,10 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G45" s="10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H45" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I45" s="10">
         <v>7</v>
@@ -7480,19 +7495,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>1234</v>
+        <v>1339</v>
       </c>
       <c r="E55" s="10">
-        <v>14925.18</v>
+        <v>16436.72</v>
       </c>
       <c r="F55" s="10">
-        <v>47.66</v>
+        <v>53.66</v>
       </c>
       <c r="G55" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H55" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
@@ -7501,7 +7516,7 @@
         <v>14289</v>
       </c>
       <c r="K55" s="10">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -8240,10 +8255,10 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E77" s="10">
-        <v>2253.6999999999998</v>
+        <v>2411.5500000000002</v>
       </c>
       <c r="F77" s="10">
         <v>6.33</v>
@@ -8995,19 +9010,19 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="E100" s="10">
-        <v>6334.25</v>
+        <v>6870.74</v>
       </c>
       <c r="F100" s="10">
-        <v>10.17</v>
+        <v>13.17</v>
       </c>
       <c r="G100" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H100" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="10">
         <v>0</v>
@@ -9674,7 +9689,7 @@
         <v>61.03</v>
       </c>
       <c r="G120" s="10">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H120" s="10">
         <v>31</v>
@@ -9849,7 +9864,7 @@
         <v>50.47</v>
       </c>
       <c r="G125" s="10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H125" s="10">
         <v>19</v>
@@ -9919,10 +9934,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H127" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -10120,19 +10135,19 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="E133" s="10">
-        <v>566.04999999999995</v>
+        <v>1221.7</v>
       </c>
       <c r="F133" s="10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G133" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H133" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I133" s="10">
         <v>1</v>
@@ -10141,7 +10156,7 @@
         <v>7647</v>
       </c>
       <c r="K133" s="10">
-        <v>12.51</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -10269,7 +10284,7 @@
         <v>59.03</v>
       </c>
       <c r="G137" s="10">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H137" s="10">
         <v>21</v>
@@ -10444,7 +10459,7 @@
         <v>8.01</v>
       </c>
       <c r="G142" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H142" s="10">
         <v>2</v>
@@ -10584,7 +10599,7 @@
         <v>7.83</v>
       </c>
       <c r="G146" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H146" s="10">
         <v>4</v>
@@ -11955,10 +11970,10 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="E187" s="10">
-        <v>5339.78</v>
+        <v>5412.08</v>
       </c>
       <c r="F187" s="10">
         <v>38</v>
@@ -11967,7 +11982,7 @@
         <v>23</v>
       </c>
       <c r="H187" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I187" s="10">
         <v>1</v>
@@ -11976,7 +11991,7 @@
         <v>7263</v>
       </c>
       <c r="K187" s="10">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -12100,19 +12115,19 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>30707</v>
+        <v>31423</v>
       </c>
       <c r="E192" s="10">
-        <v>14326.02</v>
+        <v>15756.97</v>
       </c>
       <c r="F192" s="10">
-        <v>65.11</v>
+        <v>70.11</v>
       </c>
       <c r="G192" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H192" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I192" s="10">
         <v>1</v>
@@ -12121,7 +12136,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12685,10 +12700,10 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="E209" s="10">
-        <v>2487.0700000000002</v>
+        <v>2730.54</v>
       </c>
       <c r="F209" s="10">
         <v>9.67</v>
@@ -13280,13 +13295,13 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E226" s="10">
-        <v>2610.1799999999998</v>
+        <v>2812.04</v>
       </c>
       <c r="F226" s="10">
-        <v>5.46</v>
+        <v>6.46</v>
       </c>
       <c r="G226" s="10">
         <v>5</v>
@@ -13875,13 +13890,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="E243" s="10">
-        <v>4463.3599999999997</v>
+        <v>4851.8</v>
       </c>
       <c r="F243" s="10">
-        <v>9.75</v>
+        <v>11.75</v>
       </c>
       <c r="G243" s="10">
         <v>1</v>
@@ -13896,7 +13911,7 @@
         <v>8116</v>
       </c>
       <c r="K243" s="10">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
@@ -14680,13 +14695,13 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="E266" s="10">
-        <v>4791.03</v>
+        <v>5213.82</v>
       </c>
       <c r="F266" s="10">
-        <v>15.66</v>
+        <v>17.66</v>
       </c>
       <c r="G266" s="10">
         <v>12</v>
@@ -14701,7 +14716,7 @@
         <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15544,7 +15559,7 @@
         <v>22.8</v>
       </c>
       <c r="G293" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H293" s="10">
         <v>12</v>
@@ -15684,10 +15699,10 @@
         <v>70.47</v>
       </c>
       <c r="G297" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H297" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I297" s="10">
         <v>8</v>
@@ -15955,28 +15970,28 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>819</v>
+        <v>910</v>
       </c>
       <c r="E305" s="10">
-        <v>9914.74</v>
+        <v>11084.85</v>
       </c>
       <c r="F305" s="10">
-        <v>35.93</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="G305" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H305" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I305" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J305" s="10">
-        <v>8316</v>
+        <v>15798.24</v>
       </c>
       <c r="K305" s="10">
-        <v>-0.16</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16059,7 +16074,7 @@
         <v>196.53</v>
       </c>
       <c r="G308" s="10">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H308" s="10">
         <v>35</v>
@@ -16225,16 +16240,16 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>1850</v>
+        <v>1957</v>
       </c>
       <c r="E313" s="10">
-        <v>10985.68</v>
+        <v>11872.43</v>
       </c>
       <c r="F313" s="10">
-        <v>33.659999999999997</v>
+        <v>34.81</v>
       </c>
       <c r="G313" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H313" s="10">
         <v>8</v>
@@ -16246,7 +16261,7 @@
         <v>24257.119999999999</v>
       </c>
       <c r="K313" s="10">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16505,16 +16520,16 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>2786</v>
+        <v>2992</v>
       </c>
       <c r="E321" s="10">
-        <v>10954.77</v>
+        <v>11968.76</v>
       </c>
       <c r="F321" s="10">
-        <v>45.34</v>
+        <v>50.34</v>
       </c>
       <c r="G321" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H321" s="10">
         <v>11</v>
@@ -16526,7 +16541,7 @@
         <v>5859</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.47</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16609,7 +16624,7 @@
         <v>237.06</v>
       </c>
       <c r="G324" s="10">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H324" s="10">
         <v>32</v>
@@ -16749,19 +16764,19 @@
         <v>95.25</v>
       </c>
       <c r="G328" s="10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H328" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I328" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J328" s="10">
-        <v>108090.19</v>
+        <v>101762.3</v>
       </c>
       <c r="K328" s="10">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
@@ -16784,19 +16799,19 @@
         <v>84.09</v>
       </c>
       <c r="G329" s="10">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H329" s="10">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I329" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J329" s="10">
-        <v>179349.81</v>
+        <v>173857.81</v>
       </c>
       <c r="K329" s="10">
-        <v>5.18</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.3">
@@ -17108,10 +17123,10 @@
         <v>3</v>
       </c>
       <c r="J338" s="10">
-        <v>21331</v>
+        <v>20831</v>
       </c>
       <c r="K338" s="10">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
@@ -17125,19 +17140,19 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>907</v>
+        <v>1003</v>
       </c>
       <c r="E339" s="10">
-        <v>10168.52</v>
+        <v>11448.69</v>
       </c>
       <c r="F339" s="10">
-        <v>36.32</v>
+        <v>39.32</v>
       </c>
       <c r="G339" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H339" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I339" s="10">
         <v>0</v>
@@ -17605,13 +17620,13 @@
         <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="E353" s="10">
-        <v>2889.48</v>
+        <v>3120.24</v>
       </c>
       <c r="F353" s="10">
-        <v>13.32</v>
+        <v>14.32</v>
       </c>
       <c r="G353" s="10">
         <v>4</v>
@@ -17684,7 +17699,7 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G355" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H355" s="10">
         <v>23</v>
@@ -17929,7 +17944,7 @@
         <v>41.56</v>
       </c>
       <c r="G362" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H362" s="10">
         <v>24</v>
@@ -18200,16 +18215,16 @@
         <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="E370" s="10">
-        <v>6803.57</v>
+        <v>7308.75</v>
       </c>
       <c r="F370" s="10">
-        <v>28.74</v>
+        <v>31.74</v>
       </c>
       <c r="G370" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H370" s="10">
         <v>3</v>
@@ -18734,7 +18749,7 @@
         <v>51.14</v>
       </c>
       <c r="G385" s="10">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H385" s="10">
         <v>19</v>
@@ -19040,28 +19055,28 @@
         <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>493</v>
+        <v>554</v>
       </c>
       <c r="E394" s="10">
-        <v>6744.19</v>
+        <v>7663.34</v>
       </c>
       <c r="F394" s="10">
-        <v>19.87</v>
+        <v>22.72</v>
       </c>
       <c r="G394" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H394" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I394" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J394" s="10">
-        <v>25130.799999999999</v>
+        <v>24149.8</v>
       </c>
       <c r="K394" s="10">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -19689,7 +19704,7 @@
         <v>19.079999999999998</v>
       </c>
       <c r="G414" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H414" s="10">
         <v>4</v>
@@ -20030,13 +20045,13 @@
         <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E424" s="10">
-        <v>4115.1400000000003</v>
+        <v>4516.95</v>
       </c>
       <c r="F424" s="10">
-        <v>16.66</v>
+        <v>18.66</v>
       </c>
       <c r="G424" s="10">
         <v>5</v>
@@ -20239,7 +20254,7 @@
         <v>21.38</v>
       </c>
       <c r="G430" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H430" s="10">
         <v>3</v>
@@ -20286,146 +20301,6 @@
         <v>16861</v>
       </c>
       <c r="K431" s="10">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A432" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B432" s="10">
-        <v>2025</v>
-      </c>
-      <c r="C432" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D432" s="10">
-        <v>10089</v>
-      </c>
-      <c r="E432" s="10">
-        <v>4896.22</v>
-      </c>
-      <c r="F432" s="10">
-        <v>17.29</v>
-      </c>
-      <c r="G432" s="10">
-        <v>9</v>
-      </c>
-      <c r="H432" s="10">
-        <v>5</v>
-      </c>
-      <c r="I432" s="10">
-        <v>0</v>
-      </c>
-      <c r="J432" s="10">
-        <v>0</v>
-      </c>
-      <c r="K432" s="10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A433" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B433" s="10">
-        <v>2025</v>
-      </c>
-      <c r="C433" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D433" s="10">
-        <v>3081</v>
-      </c>
-      <c r="E433" s="10">
-        <v>4895.66</v>
-      </c>
-      <c r="F433" s="10">
-        <v>14.84</v>
-      </c>
-      <c r="G433" s="10">
-        <v>20</v>
-      </c>
-      <c r="H433" s="10">
-        <v>6</v>
-      </c>
-      <c r="I433" s="10">
-        <v>3</v>
-      </c>
-      <c r="J433" s="10">
-        <v>29604.87</v>
-      </c>
-      <c r="K433" s="10">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A434" t="s">
-        <v>66</v>
-      </c>
-      <c r="B434">
-        <v>2025</v>
-      </c>
-      <c r="C434" t="s">
-        <v>21</v>
-      </c>
-      <c r="D434">
-        <v>3146</v>
-      </c>
-      <c r="E434">
-        <v>4895.83</v>
-      </c>
-      <c r="F434">
-        <v>21.38</v>
-      </c>
-      <c r="G434">
-        <v>17</v>
-      </c>
-      <c r="H434">
-        <v>3</v>
-      </c>
-      <c r="I434">
-        <v>0</v>
-      </c>
-      <c r="J434">
-        <v>0</v>
-      </c>
-      <c r="K434">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A435" t="s">
-        <v>66</v>
-      </c>
-      <c r="B435">
-        <v>2025</v>
-      </c>
-      <c r="C435" t="s">
-        <v>22</v>
-      </c>
-      <c r="D435">
-        <v>1865</v>
-      </c>
-      <c r="E435">
-        <v>3655.34</v>
-      </c>
-      <c r="F435">
-        <v>11</v>
-      </c>
-      <c r="G435">
-        <v>6</v>
-      </c>
-      <c r="H435">
-        <v>4</v>
-      </c>
-      <c r="I435">
-        <v>2</v>
-      </c>
-      <c r="J435">
-        <v>16861</v>
-      </c>
-      <c r="K435">
         <v>3.61</v>
       </c>
     </row>
@@ -20436,7 +20311,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24959,7 +24834,7 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -25029,16 +24904,16 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F124">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G124">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H124">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I124">
         <v>2</v>
@@ -25140,7 +25015,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -25149,7 +25024,7 @@
         <v>1</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -25169,7 +25044,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B128" s="18">
         <v>2026</v>
@@ -25178,7 +25053,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -25187,7 +25062,7 @@
         <v>1</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -25216,7 +25091,7 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -25245,7 +25120,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B130" s="18">
         <v>2026</v>
@@ -25254,19 +25129,19 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="E130">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F130">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -25292,31 +25167,31 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E131">
+        <v>7</v>
+      </c>
+      <c r="F131">
+        <v>7</v>
+      </c>
+      <c r="G131">
         <v>3</v>
       </c>
-      <c r="F131">
-        <v>3</v>
-      </c>
-      <c r="G131">
-        <v>2</v>
-      </c>
       <c r="H131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131">
-        <v>7647</v>
+        <v>0</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131">
-        <v>7647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -25330,31 +25205,31 @@
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H132">
         <v>1</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>7647</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -25368,13 +25243,13 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -25383,16 +25258,16 @@
         <v>1</v>
       </c>
       <c r="I133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133">
-        <v>7694</v>
+        <v>0</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133">
-        <v>7694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -25406,16 +25281,16 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E134">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -25424,13 +25299,13 @@
         <v>1</v>
       </c>
       <c r="J134">
-        <v>5119</v>
+        <v>7694</v>
       </c>
       <c r="K134">
         <v>1</v>
       </c>
       <c r="L134">
-        <v>5119</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -25444,31 +25319,31 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E135">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F135">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135">
-        <v>0</v>
+        <v>5119</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135">
-        <v>0</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -25482,19 +25357,19 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E136">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F136">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G136">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -25511,7 +25386,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B137" s="18">
         <v>2026</v>
@@ -25520,19 +25395,19 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E137">
+        <v>4</v>
+      </c>
+      <c r="F137">
         <v>3</v>
       </c>
-      <c r="F137">
-        <v>1</v>
-      </c>
       <c r="G137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -25558,25 +25433,25 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138">
         <v>0</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I138">
         <v>1</v>
       </c>
       <c r="J138">
-        <v>285</v>
+        <v>5690</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -25587,7 +25462,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B139" s="18">
         <v>2026</v>
@@ -25596,25 +25471,25 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E139">
         <v>1</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139">
         <v>0</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -25634,7 +25509,7 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -25643,10 +25518,10 @@
         <v>1</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -25672,13 +25547,13 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -25701,7 +25576,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B142" s="18">
         <v>2026</v>
@@ -25710,13 +25585,13 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E142">
         <v>2</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -25748,31 +25623,31 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143">
-        <v>7263</v>
+        <v>0</v>
       </c>
       <c r="K143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143">
-        <v>7263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -25786,31 +25661,31 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E144">
         <v>4</v>
       </c>
       <c r="F144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H144">
         <v>0</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>7263</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -25824,13 +25699,13 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F145">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -25862,19 +25737,19 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -25891,7 +25766,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B147" s="18">
         <v>2026</v>
@@ -25900,31 +25775,31 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J147">
-        <v>10440</v>
+        <v>0</v>
       </c>
       <c r="K147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L147">
-        <v>10440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -25938,31 +25813,31 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H148">
         <v>1</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -25976,31 +25851,31 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E149">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149">
-        <v>8116</v>
+        <v>0</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149">
-        <v>8116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -26014,7 +25889,7 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -26023,22 +25898,22 @@
         <v>1</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150">
-        <v>0</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -26052,31 +25927,31 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151">
-        <v>8458</v>
+        <v>0</v>
       </c>
       <c r="K151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151">
-        <v>8458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -26090,31 +25965,31 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -26128,19 +26003,19 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F153">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -26157,7 +26032,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B154" s="18">
         <v>2026</v>
@@ -26166,19 +26041,19 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E154">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -26204,7 +26079,7 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -26242,16 +26117,16 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E156">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F156">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -26280,19 +26155,19 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E157">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -26309,7 +26184,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B158" s="18">
         <v>2026</v>
@@ -26318,19 +26193,19 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E158">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F158">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -26356,19 +26231,19 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -26394,7 +26269,7 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -26406,7 +26281,7 @@
         <v>0</v>
       </c>
       <c r="H160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -26432,13 +26307,13 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="E161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -26470,7 +26345,7 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E162">
         <v>3</v>
@@ -26482,7 +26357,7 @@
         <v>0</v>
       </c>
       <c r="H162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -26508,19 +26383,19 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G163">
         <v>0</v>
       </c>
       <c r="H163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -26546,19 +26421,19 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164">
         <v>0</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -26584,19 +26459,19 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G165">
         <v>0</v>
       </c>
       <c r="H165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26622,19 +26497,19 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G166">
         <v>0</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -26651,7 +26526,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B167" s="18">
         <v>2026</v>
@@ -26660,19 +26535,19 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E167">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G167">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -26698,31 +26573,31 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F168">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>7544</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168">
-        <v>0</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -26736,16 +26611,16 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -26774,31 +26649,31 @@
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E170">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F170">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="K170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170">
-        <v>8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -26812,31 +26687,31 @@
         <v>18</v>
       </c>
       <c r="D171" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E171">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F171">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H171">
         <v>1</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -26850,19 +26725,19 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -26888,16 +26763,16 @@
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="E173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -26917,7 +26792,7 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B174" s="18">
         <v>2026</v>
@@ -26926,19 +26801,19 @@
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E174">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F174">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G174">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -26964,31 +26839,31 @@
         <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E175">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>5472</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>5472</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -27002,13 +26877,13 @@
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="E176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -27040,13 +26915,13 @@
         <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -27078,7 +26953,7 @@
         <v>18</v>
       </c>
       <c r="D178" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -27087,7 +26962,7 @@
         <v>1</v>
       </c>
       <c r="G178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -27116,31 +26991,31 @@
         <v>18</v>
       </c>
       <c r="D179" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F179">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179">
         <v>1</v>
       </c>
       <c r="J179">
-        <v>8316</v>
+        <v>7482.24</v>
       </c>
       <c r="K179">
         <v>1</v>
       </c>
       <c r="L179">
-        <v>8316</v>
+        <v>7482.24</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -27154,31 +27029,31 @@
         <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E180">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F180">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -27192,19 +27067,19 @@
         <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E181">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G181">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -27230,7 +27105,7 @@
         <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -27239,7 +27114,7 @@
         <v>1</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -27259,7 +27134,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B183" s="18">
         <v>2026</v>
@@ -27268,7 +27143,7 @@
         <v>18</v>
       </c>
       <c r="D183" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -27306,7 +27181,7 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -27344,19 +27219,19 @@
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -27382,31 +27257,31 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E186">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F186">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G186">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H186">
         <v>2</v>
       </c>
       <c r="I186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J186">
-        <v>5859</v>
+        <v>0</v>
       </c>
       <c r="K186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L186">
-        <v>5859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -27420,36 +27295,36 @@
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E187">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F187">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>5859</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L187">
-        <v>0</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B188" s="18">
         <v>2026</v>
@@ -27458,19 +27333,19 @@
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188">
         <v>0</v>
@@ -27496,7 +27371,7 @@
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E189">
         <v>4</v>
@@ -27505,7 +27380,7 @@
         <v>4</v>
       </c>
       <c r="G189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -27534,13 +27409,13 @@
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -27563,7 +27438,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B191" s="18">
         <v>2026</v>
@@ -27572,7 +27447,7 @@
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -27581,7 +27456,7 @@
         <v>3</v>
       </c>
       <c r="G191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -27610,13 +27485,13 @@
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -27648,7 +27523,7 @@
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -27657,10 +27532,10 @@
         <v>1</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -27686,36 +27561,36 @@
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E194">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F194">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H194">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I194">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J194">
-        <v>25130.799999999999</v>
+        <v>0</v>
       </c>
       <c r="K194">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L194">
-        <v>25130.799999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B195" s="18">
         <v>2026</v>
@@ -27724,31 +27599,31 @@
         <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E195">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G195">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J195">
-        <v>6910</v>
+        <v>24149.8</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>24149.8</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -27762,13 +27637,13 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -27777,10 +27652,10 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>6910</v>
       </c>
       <c r="K196">
         <v>0</v>
@@ -27800,31 +27675,31 @@
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="E197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H197">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197">
-        <v>7483.12</v>
+        <v>0</v>
       </c>
       <c r="K197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L197">
-        <v>7483.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -27838,7 +27713,7 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E198">
         <v>2</v>
@@ -27847,22 +27722,22 @@
         <v>2</v>
       </c>
       <c r="G198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>7483.12</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>7483.12</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -27876,30 +27751,68 @@
         <v>18</v>
       </c>
       <c r="D199" t="s">
+        <v>55</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199">
+        <v>2</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>132</v>
+      </c>
+      <c r="B200" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C200" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" t="s">
         <v>65</v>
       </c>
-      <c r="E199">
+      <c r="E200">
         <v>5</v>
       </c>
-      <c r="F199">
+      <c r="F200">
         <v>5</v>
       </c>
-      <c r="G199">
-        <v>2</v>
-      </c>
-      <c r="H199">
-        <v>0</v>
-      </c>
-      <c r="I199">
-        <v>0</v>
-      </c>
-      <c r="J199">
-        <v>0</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="L199">
+      <c r="G200">
+        <v>2</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C814BC05-AAE7-4952-8BE5-ED5374D038EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDB2113-CE19-4086-824F-02A6B62BDA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="138">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -437,9 +437,6 @@
   </si>
   <si>
     <t>gbp</t>
-  </si>
-  <si>
-    <t>Competitors â€“ USA</t>
   </si>
 </sst>
 </file>
@@ -1085,64 +1082,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>656.93999999999903</v>
+        <v>712.91</v>
       </c>
       <c r="C6" s="5">
-        <v>361.94</v>
+        <v>387.92</v>
       </c>
       <c r="D6" s="5">
-        <v>295</v>
+        <v>324.99</v>
       </c>
       <c r="E6" s="5">
-        <v>148033.99</v>
+        <v>160563.48000000001</v>
       </c>
       <c r="F6" s="5">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="G6" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="5">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="I6" s="5">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="J6" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K6" s="5">
-        <v>503.51697278911502</v>
+        <v>495.566296296296</v>
       </c>
       <c r="L6" s="5">
-        <v>1254.52533898305</v>
+        <v>1171.9962043795599</v>
       </c>
       <c r="M6" s="5">
-        <v>6.1804522056049302</v>
+        <v>2.6106060979744301</v>
       </c>
       <c r="N6" s="6">
-        <v>779.7</v>
+        <v>874.78</v>
       </c>
       <c r="O6" s="6">
-        <v>85256.959999999905</v>
+        <v>94301.84</v>
       </c>
       <c r="P6" s="6">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="Q6" s="6">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="R6" s="6">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="S6" s="6">
-        <v>187.790660792951</v>
+        <v>188.60368</v>
       </c>
       <c r="T6" s="6">
-        <v>754.48637168141499</v>
+        <v>766.68162601626</v>
       </c>
       <c r="U6" s="6">
-        <v>123.526161383187</v>
+        <v>162.83066162865899</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1157,7 +1154,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1169,7 +1166,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,64 +1174,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>140.96</v>
+        <v>153.94</v>
       </c>
       <c r="C7" s="5">
-        <v>66.09</v>
+        <v>71.08</v>
       </c>
       <c r="D7" s="5">
-        <v>74.87</v>
+        <v>82.86</v>
       </c>
       <c r="E7" s="5">
-        <v>5123.1000000000004</v>
+        <v>5645.96</v>
       </c>
       <c r="F7" s="5">
+        <v>87</v>
+      </c>
+      <c r="G7" s="5">
+        <v>9</v>
+      </c>
+      <c r="H7" s="5">
         <v>78</v>
       </c>
-      <c r="G7" s="5">
-        <v>8</v>
-      </c>
-      <c r="H7" s="5">
-        <v>70</v>
-      </c>
       <c r="I7" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="5">
-        <v>65.680769230769201</v>
+        <v>64.896091954022907</v>
       </c>
       <c r="L7" s="5">
-        <v>197.04230769230699</v>
+        <v>188.19866666666601</v>
       </c>
       <c r="M7" s="5">
-        <v>616.48025609494198</v>
+        <v>684.24218379159595</v>
       </c>
       <c r="N7" s="6">
-        <v>140.69999999999999</v>
+        <v>163.84</v>
       </c>
       <c r="O7" s="6">
-        <v>7909.06</v>
+        <v>8815.01</v>
       </c>
       <c r="P7" s="6">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="Q7" s="6">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R7" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S7" s="6">
-        <v>51.026193548387099</v>
+        <v>50.371485714285697</v>
       </c>
       <c r="T7" s="6">
-        <v>202.79641025641001</v>
+        <v>205.000232558139</v>
       </c>
       <c r="U7" s="6">
-        <v>1027.1293933792299</v>
+        <v>997.41611183651503</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1249,7 +1246,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1261,7 +1258,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1269,25 +1266,25 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>9.35</v>
+        <v>13.35</v>
       </c>
       <c r="C8" s="5">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4442.26</v>
+      </c>
+      <c r="F8" s="5">
+        <v>6</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
         <v>5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="E8" s="5">
-        <v>4043.73</v>
-      </c>
-      <c r="F8" s="5">
-        <v>4</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>4</v>
       </c>
       <c r="I8" s="5">
         <v>3</v>
@@ -1296,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1010.9325</v>
+        <v>740.37666666666598</v>
       </c>
       <c r="L8" s="5">
-        <v>1347.91</v>
+        <v>1480.7533333333299</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
@@ -1308,7 +1305,7 @@
         <v>7</v>
       </c>
       <c r="O8" s="6">
-        <v>1130.74</v>
+        <v>1232.8599999999999</v>
       </c>
       <c r="P8" s="6">
         <v>6</v>
@@ -1320,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="S8" s="6">
-        <v>188.456666666666</v>
+        <v>205.47666666666601</v>
       </c>
       <c r="T8" s="6">
-        <v>565.37</v>
+        <v>616.42999999999995</v>
       </c>
       <c r="U8" s="6">
-        <v>17.8874011709146</v>
+        <v>8.1225767727073706</v>
       </c>
       <c r="V8" s="7">
         <v>12</v>
@@ -1353,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1361,49 +1358,49 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>53.66</v>
+        <v>59.66</v>
       </c>
       <c r="C9" s="5">
-        <v>30.66</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="D9" s="5">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5">
+        <v>17674.21</v>
+      </c>
+      <c r="F9" s="5">
         <v>23</v>
       </c>
-      <c r="E9" s="5">
-        <v>16436.72</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
         <v>21</v>
       </c>
-      <c r="G9" s="5">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5">
-        <v>19</v>
-      </c>
       <c r="I9" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>782.700952380952</v>
+        <v>768.44391304347801</v>
       </c>
       <c r="L9" s="5">
-        <v>2054.59</v>
+        <v>1963.80111111111</v>
       </c>
       <c r="M9" s="5">
-        <v>-13.066597228644101</v>
+        <v>-19.153387902486099</v>
       </c>
       <c r="N9" s="6">
-        <v>14.84</v>
+        <v>15.84</v>
       </c>
       <c r="O9" s="6">
-        <v>3364.98</v>
+        <v>3832.66</v>
       </c>
       <c r="P9" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="6">
         <v>2</v>
@@ -1412,13 +1409,13 @@
         <v>3</v>
       </c>
       <c r="S9" s="6">
-        <v>140.20750000000001</v>
+        <v>153.3064</v>
       </c>
       <c r="T9" s="6">
-        <v>1682.49</v>
+        <v>1916.33</v>
       </c>
       <c r="U9" s="6">
-        <v>231.027227502095</v>
+        <v>190.63365912968999</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1445,7 +1442,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1489,7 +1486,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1509,10 +1506,10 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>70.789999999999907</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="O11" s="6">
-        <v>3911.34</v>
+        <v>4246.4799999999996</v>
       </c>
       <c r="P11" s="6">
         <v>8</v>
@@ -1524,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>488.91750000000002</v>
+        <v>530.80999999999995</v>
       </c>
       <c r="T11" s="6">
-        <v>1955.67</v>
+        <v>2123.2399999999998</v>
       </c>
       <c r="U11" s="6">
-        <v>92.823942689717498</v>
+        <v>77.605923023304001</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1551,7 +1548,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1568,7 +1565,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>2411.5500000000002</v>
+        <v>2553.41</v>
       </c>
       <c r="F12" s="5">
         <v>6</v>
@@ -1580,25 +1577,25 @@
         <v>4</v>
       </c>
       <c r="I12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="5">
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>401.92500000000001</v>
+        <v>425.56833333333299</v>
       </c>
       <c r="L12" s="5">
-        <v>2411.5500000000002</v>
+        <v>1276.7049999999999</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
       </c>
       <c r="N12" s="6">
-        <v>6.02</v>
+        <v>7</v>
       </c>
       <c r="O12" s="6">
-        <v>1140.02</v>
+        <v>1297.5999999999999</v>
       </c>
       <c r="P12" s="6">
         <v>5</v>
@@ -1610,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>228.00399999999999</v>
+        <v>259.52</v>
       </c>
       <c r="T12" s="6">
-        <v>570.01</v>
+        <v>648.79999999999995</v>
       </c>
       <c r="U12" s="6">
         <v>-100</v>
@@ -1643,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1687,7 +1684,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1707,10 +1704,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>11.08</v>
+        <v>12.08</v>
       </c>
       <c r="O14" s="6">
-        <v>1152.4000000000001</v>
+        <v>1238.29</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1737,7 +1734,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1760,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>261.54000000000002</v>
+        <v>301.73</v>
       </c>
       <c r="P15" s="6">
         <v>2</v>
@@ -1772,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>130.77000000000001</v>
+        <v>150.86500000000001</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1801,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1809,64 +1806,64 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="5">
         <v>8</v>
       </c>
       <c r="E16" s="5">
-        <v>1221.7</v>
+        <v>2492.39</v>
       </c>
       <c r="F16" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
       </c>
       <c r="H16" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I16" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="5">
         <v>1</v>
       </c>
       <c r="K16" s="5">
-        <v>152.71250000000001</v>
+        <v>249.239</v>
       </c>
       <c r="L16" s="5">
-        <v>610.85</v>
+        <v>623.09749999999997</v>
       </c>
       <c r="M16" s="5">
-        <v>525.93107964312003</v>
+        <v>206.81394163834699</v>
       </c>
       <c r="N16" s="6">
-        <v>24.99</v>
+        <v>28.99</v>
       </c>
       <c r="O16" s="6">
-        <v>5840.76</v>
+        <v>6532.72</v>
       </c>
       <c r="P16" s="6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q16" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="6">
-        <v>194.69200000000001</v>
+        <v>197.96121212121199</v>
       </c>
       <c r="T16" s="6">
-        <v>648.97333333333302</v>
+        <v>653.27200000000005</v>
       </c>
       <c r="U16" s="6">
-        <v>-100</v>
+        <v>5.0922127383386897</v>
       </c>
       <c r="V16" s="7">
         <v>73.650000000000006</v>
@@ -1881,7 +1878,7 @@
         <v>25</v>
       </c>
       <c r="Z16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="8">
         <v>24000</v>
@@ -1893,7 +1890,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,10 +1910,10 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>60.68</v>
+        <v>67.69</v>
       </c>
       <c r="O17" s="6">
-        <v>4083.01</v>
+        <v>4399.08</v>
       </c>
       <c r="P17" s="6">
         <v>14</v>
@@ -1928,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>291.64357142857102</v>
+        <v>314.219999999999</v>
       </c>
       <c r="T17" s="6">
-        <v>2041.5050000000001</v>
+        <v>2199.54</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1955,7 +1952,7 @@
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1978,7 +1975,7 @@
         <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>822.48</v>
+        <v>859.97</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1987,16 +1984,16 @@
         <v>1</v>
       </c>
       <c r="R18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="6">
-        <v>274.16000000000003</v>
+        <v>286.65666666666601</v>
       </c>
       <c r="T18" s="6">
-        <v>822.48</v>
+        <v>859.97</v>
       </c>
       <c r="U18" s="6">
-        <v>-100</v>
+        <v>1004.92226473016</v>
       </c>
       <c r="V18" s="7">
         <v>5.98</v>
@@ -2011,7 +2008,7 @@
         <v>2</v>
       </c>
       <c r="Z18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="9">
@@ -2021,7 +2018,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2041,17 +2038,27 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O19" s="6">
-        <v>1097.23</v>
-      </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
+        <v>1220.5</v>
+      </c>
+      <c r="P19" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6">
+        <v>1220.5</v>
+      </c>
       <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
+      <c r="U19" s="6">
+        <v>-100</v>
+      </c>
       <c r="V19" s="7">
         <v>24</v>
       </c>
@@ -2071,7 +2078,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2091,17 +2098,27 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>5</v>
+        <v>6.02</v>
       </c>
       <c r="O20" s="6">
-        <v>1586.62</v>
-      </c>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
+        <v>1858.63</v>
+      </c>
+      <c r="P20" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
+        <v>929.31500000000005</v>
+      </c>
       <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
+      <c r="U20" s="6">
+        <v>-100</v>
+      </c>
       <c r="V20" s="7">
         <v>16.02</v>
       </c>
@@ -2121,7 +2138,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2129,22 +2146,32 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C21" s="5">
-        <v>19.010000000000002</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="D21" s="5">
-        <v>18.989999999999998</v>
+        <v>20.99</v>
       </c>
       <c r="E21" s="5">
-        <v>5412.08</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+        <v>5519.75</v>
+      </c>
+      <c r="F21" s="5">
+        <v>25</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>24</v>
+      </c>
+      <c r="I21" s="5">
+        <v>13</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1</v>
+      </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -2164,10 +2191,14 @@
       <c r="AA21" s="8">
         <v>22000</v>
       </c>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
+      <c r="AB21" s="9">
+        <v>60</v>
+      </c>
+      <c r="AC21" s="9">
+        <v>28</v>
+      </c>
       <c r="AD21" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2213,35 +2244,49 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="B23" s="5">
+        <v>70.11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>64.12</v>
+      </c>
+      <c r="D23" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="E23" s="5">
+        <v>16668.36</v>
+      </c>
       <c r="F23" s="5">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G23" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H23" s="5">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I23" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J23" s="5">
         <v>1</v>
       </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="K23" s="5">
+        <v>1666.836</v>
+      </c>
+      <c r="L23" s="5">
+        <v>3333.672</v>
+      </c>
+      <c r="M23" s="5">
+        <v>-53.840689785917696</v>
+      </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -2255,146 +2300,172 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
-      <c r="AA23" s="8"/>
+      <c r="AA23" s="8">
+        <v>40000</v>
+      </c>
       <c r="AB23" s="9">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AC23" s="9">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AD23" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="5">
-        <v>70.11</v>
+        <v>10.67</v>
       </c>
       <c r="C24" s="5">
-        <v>64.12</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5">
-        <v>5.99</v>
+        <v>8.67</v>
       </c>
       <c r="E24" s="5">
-        <v>15756.97</v>
+        <v>3022.33</v>
       </c>
       <c r="F24" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G24" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I24" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5">
-        <v>1432.45181818181</v>
+        <v>377.79124999999999</v>
       </c>
       <c r="L24" s="5">
-        <v>3939.2424999999998</v>
+        <v>3022.33</v>
       </c>
       <c r="M24" s="5">
-        <v>-51.170815201145899</v>
-      </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+        <v>-100</v>
+      </c>
+      <c r="N24" s="6">
+        <v>8.02</v>
+      </c>
+      <c r="O24" s="6">
+        <v>1386.28</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
+      <c r="V24" s="7">
+        <v>22.52</v>
+      </c>
+      <c r="W24" s="7">
+        <v>3629.71</v>
+      </c>
+      <c r="X24" s="7">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="7">
+        <v>0</v>
+      </c>
       <c r="AA24" s="8">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="AB24" s="9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AC24" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD24" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5">
-        <v>9.67</v>
+        <v>7.46</v>
       </c>
       <c r="C25" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="5">
-        <v>7.67</v>
+        <v>4.46</v>
       </c>
       <c r="E25" s="5">
-        <v>2730.54</v>
+        <v>2943.88</v>
       </c>
       <c r="F25" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="5">
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>390.07714285714201</v>
+        <v>588.77599999999995</v>
       </c>
       <c r="L25" s="5">
-        <v>2730.54</v>
+        <v>981.29333333333295</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>7.02</v>
+        <v>2</v>
       </c>
       <c r="O25" s="6">
-        <v>1164.8900000000001</v>
-      </c>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
+        <v>501.24</v>
+      </c>
+      <c r="P25" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
+        <v>125.31</v>
+      </c>
       <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
+      <c r="U25" s="6">
+        <v>-100</v>
+      </c>
       <c r="V25" s="7">
-        <v>22.52</v>
+        <v>4</v>
       </c>
       <c r="W25" s="7">
-        <v>3629.71</v>
+        <v>1033.75</v>
       </c>
       <c r="X25" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z25" s="7">
         <v>0</v>
@@ -2403,354 +2474,324 @@
         <v>7000</v>
       </c>
       <c r="AB25" s="9">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AC25" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD25" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="5">
-        <v>6.46</v>
+        <v>11.75</v>
       </c>
       <c r="C26" s="5">
-        <v>2</v>
+        <v>9.25</v>
       </c>
       <c r="D26" s="5">
-        <v>4.46</v>
+        <v>2.5</v>
       </c>
       <c r="E26" s="5">
-        <v>2812.04</v>
+        <v>5279.13</v>
       </c>
       <c r="F26" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="5">
-        <v>562.40800000000002</v>
+        <v>5279.13</v>
       </c>
       <c r="L26" s="5">
-        <v>937.34666666666601</v>
+        <v>5279.13</v>
       </c>
       <c r="M26" s="5">
-        <v>-100</v>
+        <v>53.737452951527999</v>
       </c>
       <c r="N26" s="6">
-        <v>2</v>
+        <v>30.65</v>
       </c>
       <c r="O26" s="6">
-        <v>428.06</v>
+        <v>5656.08</v>
       </c>
       <c r="P26" s="6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R26" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="6">
-        <v>107.015</v>
-      </c>
-      <c r="T26" s="6"/>
+        <v>257.09454545454503</v>
+      </c>
+      <c r="T26" s="6">
+        <v>707.01</v>
+      </c>
       <c r="U26" s="6">
-        <v>-100</v>
+        <v>161.68300306926301</v>
       </c>
       <c r="V26" s="7">
-        <v>4</v>
+        <v>66.569999999999993</v>
       </c>
       <c r="W26" s="7">
-        <v>1033.75</v>
+        <v>14965.45</v>
       </c>
       <c r="X26" s="7">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="Y26" s="7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Z26" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" s="8">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="AB26" s="9">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AC26" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD26" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="5">
-        <v>11.75</v>
-      </c>
-      <c r="C27" s="5">
-        <v>9.25</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="E27" s="5">
-        <v>4851.8</v>
-      </c>
-      <c r="F27" s="5">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5">
-        <v>1</v>
-      </c>
-      <c r="I27" s="5">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5">
-        <v>1</v>
-      </c>
-      <c r="K27" s="5">
-        <v>4851.8</v>
-      </c>
-      <c r="L27" s="5">
-        <v>4851.8</v>
-      </c>
-      <c r="M27" s="5">
-        <v>67.278123583000095</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
       <c r="N27" s="6">
-        <v>24.31</v>
+        <v>20.04</v>
       </c>
       <c r="O27" s="6">
-        <v>4956</v>
+        <v>1667.25</v>
       </c>
       <c r="P27" s="6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q27" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R27" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" s="6">
-        <v>275.33333333333297</v>
+        <v>151.56818181818099</v>
       </c>
       <c r="T27" s="6">
-        <v>826</v>
+        <v>833.625</v>
       </c>
       <c r="U27" s="6">
-        <v>198.64810330911999</v>
+        <v>-100</v>
       </c>
       <c r="V27" s="7">
-        <v>66.569999999999993</v>
+        <v>65.91</v>
       </c>
       <c r="W27" s="7">
-        <v>14965.45</v>
+        <v>3947.31</v>
       </c>
       <c r="X27" s="7">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="Y27" s="7">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="7">
-        <v>2</v>
-      </c>
-      <c r="AA27" s="8">
-        <v>12000</v>
-      </c>
-      <c r="AB27" s="9">
-        <v>26</v>
-      </c>
-      <c r="AC27" s="9">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="8"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
       <c r="AD27" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="B28" s="5">
+        <v>17.66</v>
+      </c>
+      <c r="C28" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10.99</v>
+      </c>
+      <c r="E28" s="5">
+        <v>5603.39</v>
+      </c>
+      <c r="F28" s="5">
+        <v>12</v>
+      </c>
+      <c r="G28" s="5">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5">
+        <v>11</v>
+      </c>
+      <c r="I28" s="5">
+        <v>4</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5">
+        <v>466.94916666666597</v>
+      </c>
+      <c r="L28" s="5">
+        <v>1400.8475000000001</v>
+      </c>
+      <c r="M28" s="5">
+        <v>-8.6445883652574604</v>
+      </c>
       <c r="N28" s="6">
-        <v>18.579999999999998</v>
+        <v>16.54</v>
       </c>
       <c r="O28" s="6">
-        <v>1530.43</v>
+        <v>2577.71</v>
       </c>
       <c r="P28" s="6">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>6</v>
+      </c>
+      <c r="R28" s="6">
+        <v>4</v>
+      </c>
+      <c r="S28" s="6">
+        <v>184.12214285714199</v>
+      </c>
+      <c r="T28" s="6">
+        <v>429.618333333333</v>
+      </c>
+      <c r="U28" s="6">
+        <v>1045.83564481652</v>
+      </c>
+      <c r="V28" s="7">
+        <v>55.58</v>
+      </c>
+      <c r="W28" s="7">
+        <v>8745.86</v>
+      </c>
+      <c r="X28" s="7">
+        <v>39</v>
+      </c>
+      <c r="Y28" s="7">
+        <v>13</v>
+      </c>
+      <c r="Z28" s="7">
+        <v>4</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>13000</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>31</v>
+      </c>
+      <c r="AC28" s="9">
         <v>10</v>
       </c>
-      <c r="Q28" s="6">
-        <v>2</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6">
-        <v>153.04300000000001</v>
-      </c>
-      <c r="T28" s="6">
-        <v>765.21500000000003</v>
-      </c>
-      <c r="U28" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V28" s="7">
-        <v>65.91</v>
-      </c>
-      <c r="W28" s="7">
-        <v>3947.31</v>
-      </c>
-      <c r="X28" s="7">
-        <v>19</v>
-      </c>
-      <c r="Y28" s="7">
-        <v>2</v>
-      </c>
-      <c r="Z28" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="5">
-        <v>17.66</v>
-      </c>
-      <c r="C29" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="D29" s="5">
-        <v>10.99</v>
-      </c>
-      <c r="E29" s="5">
-        <v>5213.82</v>
-      </c>
-      <c r="F29" s="5">
+        <v>46</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6">
+        <v>41.51</v>
+      </c>
+      <c r="O29" s="6">
+        <v>2876.08</v>
+      </c>
+      <c r="P29" s="6">
         <v>12</v>
       </c>
-      <c r="G29" s="5">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5">
-        <v>11</v>
-      </c>
-      <c r="I29" s="5">
-        <v>4</v>
-      </c>
-      <c r="J29" s="5">
-        <v>1</v>
-      </c>
-      <c r="K29" s="5">
-        <v>434.48500000000001</v>
-      </c>
-      <c r="L29" s="5">
-        <v>1303.4549999999999</v>
-      </c>
-      <c r="M29" s="5">
-        <v>-1.8186281843254899</v>
-      </c>
-      <c r="N29" s="6">
-        <v>14.54</v>
-      </c>
-      <c r="O29" s="6">
-        <v>2271.2399999999998</v>
-      </c>
-      <c r="P29" s="6">
-        <v>13</v>
-      </c>
       <c r="Q29" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R29" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S29" s="6">
-        <v>174.71076923076899</v>
-      </c>
-      <c r="T29" s="6">
-        <v>378.539999999999</v>
-      </c>
+        <v>239.67333333333301</v>
+      </c>
+      <c r="T29" s="6"/>
       <c r="U29" s="6">
-        <v>1200.4490938870399</v>
+        <v>-100</v>
       </c>
       <c r="V29" s="7">
-        <v>55.58</v>
+        <v>98.369999999999905</v>
       </c>
       <c r="W29" s="7">
-        <v>8745.86</v>
+        <v>6238.21</v>
       </c>
       <c r="X29" s="7">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="Y29" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Z29" s="7">
-        <v>4</v>
-      </c>
-      <c r="AA29" s="8">
-        <v>13000</v>
-      </c>
-      <c r="AB29" s="9">
-        <v>31</v>
-      </c>
-      <c r="AC29" s="9">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
       <c r="AD29" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2765,242 +2806,248 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>37.51</v>
+        <v>46.28</v>
       </c>
       <c r="O30" s="6">
-        <v>2652.42</v>
+        <v>3506.76</v>
       </c>
       <c r="P30" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="6">
-        <v>241.12909090909</v>
-      </c>
-      <c r="T30" s="6"/>
+        <v>438.34500000000003</v>
+      </c>
+      <c r="T30" s="6">
+        <v>1753.38</v>
+      </c>
       <c r="U30" s="6">
-        <v>-100</v>
+        <v>88.008303961491507</v>
       </c>
       <c r="V30" s="7">
-        <v>98.369999999999905</v>
+        <v>126.03</v>
       </c>
       <c r="W30" s="7">
-        <v>6238.21</v>
+        <v>9571.31</v>
       </c>
       <c r="X30" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y30" s="7">
         <v>2</v>
       </c>
       <c r="Z30" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" s="8"/>
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="B31" s="5">
+        <v>43.91</v>
+      </c>
+      <c r="C31" s="5">
+        <v>23.43</v>
+      </c>
+      <c r="D31" s="5">
+        <v>20.48</v>
+      </c>
+      <c r="E31" s="5">
+        <v>11848.18</v>
+      </c>
+      <c r="F31" s="5">
+        <v>23</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5">
+        <v>21</v>
+      </c>
+      <c r="I31" s="5">
+        <v>8</v>
+      </c>
+      <c r="J31" s="5">
+        <v>3</v>
+      </c>
+      <c r="K31" s="5">
+        <v>515.13826086956499</v>
+      </c>
+      <c r="L31" s="5">
+        <v>1481.0225</v>
+      </c>
+      <c r="M31" s="5">
+        <v>35.744392809697302</v>
+      </c>
       <c r="N31" s="6">
-        <v>42.05</v>
+        <v>13.8</v>
       </c>
       <c r="O31" s="6">
-        <v>3260.41</v>
+        <v>4952.03</v>
       </c>
       <c r="P31" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R31" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="6">
-        <v>407.55124999999998</v>
+        <v>247.60149999999999</v>
       </c>
       <c r="T31" s="6">
-        <v>1630.2049999999999</v>
+        <v>1238.0074999999999</v>
       </c>
       <c r="U31" s="6">
-        <v>-100</v>
+        <v>31.461239128195899</v>
       </c>
       <c r="V31" s="7">
-        <v>126.03</v>
+        <v>22.8</v>
       </c>
       <c r="W31" s="7">
-        <v>9571.31</v>
+        <v>6170.17</v>
       </c>
       <c r="X31" s="7">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Y31" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z31" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="8"/>
-      <c r="AB31" s="9"/>
-      <c r="AC31" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="AA31" s="8">
+        <v>28000</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>42</v>
+      </c>
+      <c r="AC31" s="9">
+        <v>21</v>
+      </c>
       <c r="AD31" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" s="5">
-        <v>39.909999999999997</v>
+        <v>36.81</v>
       </c>
       <c r="C32" s="5">
-        <v>21.43</v>
+        <v>11.1</v>
       </c>
       <c r="D32" s="5">
-        <v>18.48</v>
+        <v>25.71</v>
       </c>
       <c r="E32" s="5">
-        <v>11084.85</v>
+        <v>12945.3</v>
       </c>
       <c r="F32" s="5">
         <v>19</v>
       </c>
       <c r="G32" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I32" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J32" s="5">
         <v>3</v>
       </c>
       <c r="K32" s="5">
-        <v>583.41315789473595</v>
+        <v>681.33157894736803</v>
       </c>
       <c r="L32" s="5">
-        <v>1583.55</v>
+        <v>1294.53</v>
       </c>
       <c r="M32" s="5">
-        <v>45.092085143235998</v>
-      </c>
-      <c r="N32" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="O32" s="6">
-        <v>4446.25</v>
-      </c>
-      <c r="P32" s="6">
-        <v>19</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>3</v>
-      </c>
-      <c r="R32" s="6">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6">
-        <v>234.013157894736</v>
-      </c>
-      <c r="T32" s="6">
-        <v>1482.0833333333301</v>
-      </c>
-      <c r="U32" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V32" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="W32" s="7">
-        <v>6170.17</v>
-      </c>
-      <c r="X32" s="7">
-        <v>30</v>
-      </c>
-      <c r="Y32" s="7">
-        <v>10</v>
-      </c>
-      <c r="Z32" s="7">
-        <v>0</v>
-      </c>
+        <v>87.381675202583097</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="7"/>
       <c r="AA32" s="8">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="AB32" s="9">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="AC32" s="9">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AD32" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" s="5">
-        <v>34.81</v>
+        <v>54.34</v>
       </c>
       <c r="C33" s="5">
-        <v>11.1</v>
+        <v>22.59</v>
       </c>
       <c r="D33" s="5">
-        <v>23.71</v>
+        <v>31.75</v>
       </c>
       <c r="E33" s="5">
-        <v>11872.43</v>
+        <v>12729.71</v>
       </c>
       <c r="F33" s="5">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G33" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I33" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J33" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" s="5">
-        <v>659.57944444444399</v>
+        <v>438.95551724137903</v>
       </c>
       <c r="L33" s="5">
-        <v>1484.05375</v>
+        <v>1060.8091666666601</v>
       </c>
       <c r="M33" s="5">
-        <v>104.31470221344701</v>
+        <v>-53.973814014616202</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3016,802 +3063,765 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="8">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="AB33" s="9">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="AC33" s="9">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AD33" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B34" s="5">
-        <v>50.34</v>
+        <v>46.32</v>
       </c>
       <c r="C34" s="5">
-        <v>22.59</v>
+        <v>35.49</v>
       </c>
       <c r="D34" s="5">
-        <v>27.75</v>
+        <v>10.83</v>
       </c>
       <c r="E34" s="5">
-        <v>11968.76</v>
+        <v>12447.74</v>
       </c>
       <c r="F34" s="5">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G34" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H34" s="5">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I34" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J34" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5">
-        <v>460.33692307692297</v>
+        <v>732.22</v>
       </c>
       <c r="L34" s="5">
-        <v>1196.876</v>
+        <v>1778.2485714285699</v>
       </c>
       <c r="M34" s="5">
-        <v>-51.0475604824559</v>
-      </c>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
+        <v>-100</v>
+      </c>
+      <c r="N34" s="6">
+        <v>33.369999999999997</v>
+      </c>
+      <c r="O34" s="6">
+        <v>10389.030000000001</v>
+      </c>
+      <c r="P34" s="6">
+        <v>48</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>14</v>
+      </c>
+      <c r="R34" s="6">
+        <v>3</v>
+      </c>
+      <c r="S34" s="6">
+        <v>216.43812500000001</v>
+      </c>
+      <c r="T34" s="6">
+        <v>742.07357142857097</v>
+      </c>
+      <c r="U34" s="6">
+        <v>124.44992458391199</v>
+      </c>
+      <c r="V34" s="7">
+        <v>110.24</v>
+      </c>
+      <c r="W34" s="7">
+        <v>28910.07</v>
+      </c>
+      <c r="X34" s="7">
+        <v>128</v>
+      </c>
+      <c r="Y34" s="7">
+        <v>45</v>
+      </c>
+      <c r="Z34" s="7">
+        <v>3</v>
+      </c>
       <c r="AA34" s="8">
-        <v>25000</v>
+        <v>35000</v>
       </c>
       <c r="AB34" s="9">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="AC34" s="9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AD34" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="5">
-        <v>39.32</v>
-      </c>
-      <c r="C35" s="5">
-        <v>29.49</v>
-      </c>
-      <c r="D35" s="5">
-        <v>9.83</v>
-      </c>
-      <c r="E35" s="5">
-        <v>11448.69</v>
-      </c>
-      <c r="F35" s="5">
-        <v>16</v>
-      </c>
-      <c r="G35" s="5">
-        <v>6</v>
-      </c>
-      <c r="H35" s="5">
-        <v>10</v>
-      </c>
-      <c r="I35" s="5">
-        <v>6</v>
-      </c>
-      <c r="J35" s="5">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5">
-        <v>715.54312500000003</v>
-      </c>
-      <c r="L35" s="5">
-        <v>1908.115</v>
-      </c>
-      <c r="M35" s="5">
+        <v>56</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6">
+        <v>91.9</v>
+      </c>
+      <c r="O35" s="6">
+        <v>3306.32</v>
+      </c>
+      <c r="P35" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0</v>
+      </c>
+      <c r="R35" s="6">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6">
+        <v>413.29</v>
+      </c>
+      <c r="T35" s="6"/>
+      <c r="U35" s="6">
         <v>-100</v>
       </c>
-      <c r="N35" s="6">
-        <v>28.37</v>
-      </c>
-      <c r="O35" s="6">
-        <v>9495.82</v>
-      </c>
-      <c r="P35" s="6">
-        <v>41</v>
-      </c>
-      <c r="Q35" s="6">
-        <v>13</v>
-      </c>
-      <c r="R35" s="6">
-        <v>3</v>
-      </c>
-      <c r="S35" s="6">
-        <v>231.60536585365799</v>
-      </c>
-      <c r="T35" s="6">
-        <v>730.44769230769202</v>
-      </c>
-      <c r="U35" s="6">
-        <v>145.56246853878801</v>
-      </c>
       <c r="V35" s="7">
-        <v>110.24</v>
+        <v>250.18</v>
       </c>
       <c r="W35" s="7">
-        <v>28910.07</v>
+        <v>7865.5</v>
       </c>
       <c r="X35" s="7">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="Y35" s="7">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="7">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="8">
-        <v>35000</v>
-      </c>
-      <c r="AB35" s="9">
-        <v>57</v>
-      </c>
-      <c r="AC35" s="9">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
       <c r="AD35" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6">
-        <v>81.2</v>
-      </c>
-      <c r="O36" s="6">
-        <v>3033.65</v>
-      </c>
-      <c r="P36" s="6">
-        <v>8</v>
-      </c>
-      <c r="Q36" s="6">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6">
-        <v>379.20625000000001</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B36" s="5">
+        <v>15.31</v>
+      </c>
+      <c r="C36" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="D36" s="5">
+        <v>6.99</v>
+      </c>
+      <c r="E36" s="5">
+        <v>3376.33</v>
+      </c>
+      <c r="F36" s="5">
+        <v>4</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5">
+        <v>4</v>
+      </c>
+      <c r="I36" s="5">
+        <v>1</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>844.08249999999998</v>
+      </c>
+      <c r="L36" s="5">
+        <v>3376.33</v>
+      </c>
+      <c r="M36" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
       <c r="T36" s="6"/>
-      <c r="U36" s="6">
-        <v>-100</v>
-      </c>
-      <c r="V36" s="7">
-        <v>250.18</v>
-      </c>
-      <c r="W36" s="7">
-        <v>7865.5</v>
-      </c>
-      <c r="X36" s="7">
-        <v>18</v>
-      </c>
-      <c r="Y36" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
+      <c r="AA36" s="8">
+        <v>7500</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>16</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>7</v>
+      </c>
       <c r="AD36" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="5">
-        <v>14.32</v>
+        <v>31.74</v>
       </c>
       <c r="C37" s="5">
-        <v>7.33</v>
+        <v>22.49</v>
       </c>
       <c r="D37" s="5">
-        <v>6.99</v>
+        <v>9.25</v>
       </c>
       <c r="E37" s="5">
-        <v>3120.24</v>
+        <v>7850.61</v>
       </c>
       <c r="F37" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G37" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" s="5">
         <v>4</v>
       </c>
       <c r="I37" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J37" s="5">
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>780.06</v>
+        <v>1308.4349999999999</v>
       </c>
       <c r="L37" s="5">
-        <v>3120.24</v>
+        <v>1962.6524999999999</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
       </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
+      <c r="N37" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="O37" s="6">
+        <v>4589.93</v>
+      </c>
+      <c r="P37" s="6">
+        <v>26</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>12</v>
+      </c>
+      <c r="R37" s="6">
+        <v>4</v>
+      </c>
+      <c r="S37" s="6">
+        <v>176.53576923076901</v>
+      </c>
+      <c r="T37" s="6">
+        <v>382.49416666666599</v>
+      </c>
+      <c r="U37" s="6">
+        <v>403.10484037882901</v>
+      </c>
+      <c r="V37" s="7">
+        <v>42.5</v>
+      </c>
+      <c r="W37" s="7">
+        <v>12015.14</v>
+      </c>
+      <c r="X37" s="7">
+        <v>56</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>24</v>
+      </c>
+      <c r="Z37" s="7">
+        <v>4</v>
+      </c>
       <c r="AA37" s="8">
-        <v>7500</v>
+        <v>17000</v>
       </c>
       <c r="AB37" s="9">
+        <v>27</v>
+      </c>
+      <c r="AC37" s="9">
         <v>16</v>
       </c>
-      <c r="AC37" s="9">
-        <v>7</v>
-      </c>
       <c r="AD37" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="5">
-        <v>31.74</v>
-      </c>
-      <c r="C38" s="5">
-        <v>22.49</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.25</v>
-      </c>
-      <c r="E38" s="5">
-        <v>7308.75</v>
-      </c>
-      <c r="F38" s="5">
-        <v>6</v>
-      </c>
-      <c r="G38" s="5">
-        <v>2</v>
-      </c>
-      <c r="H38" s="5">
+        <v>59</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6">
+        <v>38.340000000000003</v>
+      </c>
+      <c r="O38" s="6">
+        <v>2486.69</v>
+      </c>
+      <c r="P38" s="6">
         <v>4</v>
       </c>
-      <c r="I38" s="5">
+      <c r="Q38" s="6">
+        <v>1</v>
+      </c>
+      <c r="R38" s="6">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6">
+        <v>621.67250000000001</v>
+      </c>
+      <c r="T38" s="6">
+        <v>2486.69</v>
+      </c>
+      <c r="U38" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V38" s="7">
+        <v>97.34</v>
+      </c>
+      <c r="W38" s="7">
+        <v>5964.35</v>
+      </c>
+      <c r="X38" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y38" s="7">
         <v>3</v>
       </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <v>1218.125</v>
-      </c>
-      <c r="L38" s="5">
-        <v>2436.25</v>
-      </c>
-      <c r="M38" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N38" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="O38" s="6">
-        <v>4093.35</v>
-      </c>
-      <c r="P38" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q38" s="6">
-        <v>12</v>
-      </c>
-      <c r="R38" s="6">
-        <v>1</v>
-      </c>
-      <c r="S38" s="6">
-        <v>163.73400000000001</v>
-      </c>
-      <c r="T38" s="6">
-        <v>341.11250000000001</v>
-      </c>
-      <c r="U38" s="6">
-        <v>108.924230764532</v>
-      </c>
-      <c r="V38" s="7">
-        <v>42.5</v>
-      </c>
-      <c r="W38" s="7">
-        <v>12015.14</v>
-      </c>
-      <c r="X38" s="7">
-        <v>56</v>
-      </c>
-      <c r="Y38" s="7">
-        <v>24</v>
-      </c>
       <c r="Z38" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="8">
-        <v>17000</v>
-      </c>
-      <c r="AB38" s="9">
-        <v>27</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA38" s="8"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
       <c r="AD38" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="B39" s="5">
+        <v>13.17</v>
+      </c>
+      <c r="C39" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="D39" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="E39" s="5">
+        <v>7507.61</v>
+      </c>
+      <c r="F39" s="5">
+        <v>4</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <v>4</v>
+      </c>
+      <c r="I39" s="5">
+        <v>2</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>1876.9024999999999</v>
+      </c>
+      <c r="L39" s="5">
+        <v>3753.8049999999998</v>
+      </c>
+      <c r="M39" s="5">
+        <v>-100</v>
+      </c>
       <c r="N39" s="6">
-        <v>36.340000000000003</v>
+        <v>0.98</v>
       </c>
       <c r="O39" s="6">
-        <v>2326.6999999999998</v>
-      </c>
-      <c r="P39" s="6">
-        <v>4</v>
-      </c>
-      <c r="Q39" s="6">
-        <v>1</v>
-      </c>
-      <c r="R39" s="6">
-        <v>0</v>
-      </c>
-      <c r="S39" s="6">
-        <v>581.67499999999995</v>
-      </c>
-      <c r="T39" s="6">
-        <v>2326.6999999999998</v>
-      </c>
-      <c r="U39" s="6">
-        <v>-100</v>
-      </c>
+        <v>519.54</v>
+      </c>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
       <c r="V39" s="7">
-        <v>97.34</v>
+        <v>3.01</v>
       </c>
       <c r="W39" s="7">
-        <v>5964.35</v>
-      </c>
-      <c r="X39" s="7">
-        <v>9</v>
-      </c>
-      <c r="Y39" s="7">
-        <v>3</v>
-      </c>
-      <c r="Z39" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="8"/>
+        <v>1758.25</v>
+      </c>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="8">
+        <v>17000</v>
+      </c>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="B40" s="5">
-        <v>13.17</v>
+        <v>27.72</v>
       </c>
       <c r="C40" s="5">
-        <v>6.67</v>
+        <v>11.72</v>
       </c>
       <c r="D40" s="5">
-        <v>6.5</v>
+        <v>16</v>
       </c>
       <c r="E40" s="5">
-        <v>6870.74</v>
+        <v>8597.1299999999992</v>
       </c>
       <c r="F40" s="5">
+        <v>21</v>
+      </c>
+      <c r="G40" s="5">
         <v>4</v>
       </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
       <c r="H40" s="5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I40" s="5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J40" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K40" s="5">
-        <v>1717.6849999999999</v>
+        <v>409.38714285714201</v>
       </c>
       <c r="L40" s="5">
-        <v>3435.37</v>
+        <v>614.08071428571395</v>
       </c>
       <c r="M40" s="5">
-        <v>-100</v>
+        <v>180.90537190899701</v>
       </c>
       <c r="N40" s="6">
-        <v>0.98</v>
+        <v>19.16</v>
       </c>
       <c r="O40" s="6">
-        <v>456.91</v>
-      </c>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
+        <v>4060.99</v>
+      </c>
+      <c r="P40" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>3</v>
+      </c>
+      <c r="R40" s="6">
+        <v>1</v>
+      </c>
+      <c r="S40" s="6">
+        <v>193.380476190476</v>
+      </c>
+      <c r="T40" s="6">
+        <v>1353.66333333333</v>
+      </c>
+      <c r="U40" s="6">
+        <v>28.165299594433801</v>
+      </c>
       <c r="V40" s="7">
-        <v>3.01</v>
+        <v>52.03</v>
       </c>
       <c r="W40" s="7">
-        <v>1758.25</v>
-      </c>
-      <c r="X40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7"/>
+        <v>10931.15</v>
+      </c>
+      <c r="X40" s="7">
+        <v>47</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>13</v>
+      </c>
+      <c r="Z40" s="7">
+        <v>1</v>
+      </c>
       <c r="AA40" s="8">
-        <v>17000</v>
-      </c>
-      <c r="AB40" s="9"/>
-      <c r="AC40" s="9"/>
+        <v>24000</v>
+      </c>
+      <c r="AB40" s="9">
+        <v>29</v>
+      </c>
+      <c r="AC40" s="9">
+        <v>12</v>
+      </c>
       <c r="AD40" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41">
-        <v>22.72</v>
-      </c>
-      <c r="C41">
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="D41">
-        <v>13</v>
-      </c>
-      <c r="E41">
-        <v>7663.34</v>
-      </c>
-      <c r="F41">
-        <v>18</v>
-      </c>
-      <c r="G41">
+        <v>61</v>
+      </c>
+      <c r="N41">
+        <v>50.72</v>
+      </c>
+      <c r="O41">
+        <v>3627.23</v>
+      </c>
+      <c r="P41">
+        <v>11</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>329.74818181818102</v>
+      </c>
+      <c r="T41">
+        <v>3627.23</v>
+      </c>
+      <c r="U41">
+        <v>56.593323279747899</v>
+      </c>
+      <c r="V41">
+        <v>127.59</v>
+      </c>
+      <c r="W41">
+        <v>8783.7999999999993</v>
+      </c>
+      <c r="X41">
+        <v>27</v>
+      </c>
+      <c r="Y41">
         <v>4</v>
       </c>
-      <c r="H41">
-        <v>14</v>
-      </c>
-      <c r="I41">
-        <v>12</v>
-      </c>
-      <c r="J41">
-        <v>3</v>
-      </c>
-      <c r="K41">
-        <v>425.74111111111102</v>
-      </c>
-      <c r="L41">
-        <v>638.611666666666</v>
-      </c>
-      <c r="M41">
-        <v>215.134132114717</v>
-      </c>
-      <c r="N41">
-        <v>18.16</v>
-      </c>
-      <c r="O41">
-        <v>3631.19</v>
-      </c>
-      <c r="P41">
-        <v>21</v>
-      </c>
-      <c r="Q41">
-        <v>3</v>
-      </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41">
-        <v>172.91380952380899</v>
-      </c>
-      <c r="T41">
-        <v>1210.3966666666599</v>
-      </c>
-      <c r="U41">
-        <v>43.335380412481797</v>
-      </c>
-      <c r="V41">
-        <v>52.03</v>
-      </c>
-      <c r="W41">
-        <v>10931.15</v>
-      </c>
-      <c r="X41">
-        <v>47</v>
-      </c>
-      <c r="Y41">
-        <v>13</v>
-      </c>
       <c r="Z41">
         <v>1</v>
       </c>
-      <c r="AA41">
-        <v>24000</v>
-      </c>
-      <c r="AB41">
-        <v>29</v>
-      </c>
-      <c r="AC41">
-        <v>12</v>
-      </c>
       <c r="AD41" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="B42">
+        <v>20.66</v>
+      </c>
+      <c r="C42">
+        <v>11.99</v>
+      </c>
+      <c r="D42">
+        <v>8.67</v>
+      </c>
+      <c r="E42">
+        <v>4917.6400000000003</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>5</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>819.606666666666</v>
+      </c>
+      <c r="L42">
+        <v>1639.21333333333</v>
+      </c>
+      <c r="M42">
+        <v>-100</v>
       </c>
       <c r="N42">
-        <v>46.56</v>
+        <v>9.07</v>
       </c>
       <c r="O42">
-        <v>3336.66</v>
+        <v>1920.3</v>
       </c>
       <c r="P42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>303.33272727272703</v>
+        <v>160.02500000000001</v>
       </c>
       <c r="T42">
-        <v>3336.66</v>
+        <v>384.06</v>
       </c>
       <c r="U42">
         <v>-100</v>
       </c>
       <c r="V42">
-        <v>127.59</v>
+        <v>23.02</v>
       </c>
       <c r="W42">
-        <v>8783.7999999999993</v>
+        <v>4636.55</v>
       </c>
       <c r="X42">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y42">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z42">
         <v>0</v>
       </c>
+      <c r="AA42">
+        <v>11000</v>
+      </c>
+      <c r="AB42">
+        <v>14</v>
+      </c>
+      <c r="AC42">
+        <v>6</v>
+      </c>
       <c r="AD42" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43">
-        <v>18.66</v>
-      </c>
-      <c r="C43">
-        <v>10.99</v>
-      </c>
-      <c r="D43">
-        <v>7.67</v>
-      </c>
-      <c r="E43">
-        <v>4516.95</v>
-      </c>
-      <c r="F43">
+        <v>66</v>
+      </c>
+      <c r="N43">
+        <v>25.69</v>
+      </c>
+      <c r="O43">
+        <v>2108.98</v>
+      </c>
+      <c r="P43">
         <v>5</v>
       </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>4</v>
-      </c>
-      <c r="I43">
-        <v>2</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>903.39</v>
-      </c>
-      <c r="L43">
-        <v>2258.4749999999999</v>
-      </c>
-      <c r="M43">
-        <v>-100</v>
-      </c>
-      <c r="N43">
-        <v>7.03</v>
-      </c>
-      <c r="O43">
-        <v>1615.87</v>
-      </c>
-      <c r="P43">
-        <v>9</v>
-      </c>
       <c r="Q43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R43">
         <v>0</v>
       </c>
       <c r="S43">
-        <v>179.54111111111101</v>
+        <v>421.79599999999999</v>
       </c>
       <c r="T43">
-        <v>403.96749999999997</v>
+        <v>2108.98</v>
       </c>
       <c r="U43">
         <v>-100</v>
       </c>
       <c r="V43">
-        <v>23.02</v>
+        <v>56.01</v>
       </c>
       <c r="W43">
-        <v>4636.55</v>
+        <v>4863.79</v>
       </c>
       <c r="X43">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z43">
         <v>0</v>
       </c>
-      <c r="AA43">
-        <v>11000</v>
-      </c>
-      <c r="AB43">
-        <v>14</v>
-      </c>
-      <c r="AC43">
-        <v>6</v>
-      </c>
       <c r="AD43" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>66</v>
-      </c>
-      <c r="N44">
-        <v>24.69</v>
-      </c>
-      <c r="O44">
-        <v>1923.06</v>
-      </c>
-      <c r="P44">
-        <v>5</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>384.611999999999</v>
-      </c>
-      <c r="T44">
-        <v>1923.06</v>
-      </c>
-      <c r="U44">
-        <v>-100</v>
-      </c>
-      <c r="V44">
-        <v>56.01</v>
-      </c>
-      <c r="W44">
-        <v>4863.79</v>
-      </c>
-      <c r="X44">
-        <v>10</v>
-      </c>
-      <c r="Y44">
-        <v>4</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>2</v>
+      </c>
+      <c r="AC44">
+        <v>1</v>
       </c>
       <c r="AD44" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
@@ -3840,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="AD45" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
@@ -3884,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.3">
@@ -3976,7 +3986,7 @@
         <v>6</v>
       </c>
       <c r="AD47" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.3">
@@ -4023,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.3">
@@ -4052,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="AD49" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
   </sheetData>
@@ -4939,16 +4949,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E21" s="10">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F21" s="10">
         <v>19</v>
       </c>
       <c r="G21" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
@@ -4963,19 +4973,19 @@
         <v>23255</v>
       </c>
       <c r="L21" s="10">
-        <v>11.9</v>
+        <v>12.04</v>
       </c>
       <c r="M21" s="10">
-        <v>14.79</v>
+        <v>14.11</v>
       </c>
       <c r="N21" s="10">
-        <v>54.29</v>
+        <v>48.72</v>
       </c>
       <c r="O21" s="10">
         <v>15.79</v>
       </c>
       <c r="P21" s="10">
-        <v>8.57</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -5013,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -5043,10 +5053,10 @@
         <v>35</v>
       </c>
       <c r="F23" s="10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G23" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H23" s="10">
         <v>3</v>
@@ -5061,16 +5071,16 @@
         <v>20460</v>
       </c>
       <c r="L23" s="10">
-        <v>12.93</v>
+        <v>11.73</v>
       </c>
       <c r="M23" s="10">
-        <v>13.02</v>
+        <v>12.42</v>
       </c>
       <c r="N23" s="10">
-        <v>39.47</v>
+        <v>50</v>
       </c>
       <c r="O23" s="10">
-        <v>20</v>
+        <v>15.79</v>
       </c>
       <c r="P23" s="10">
         <v>7.89</v>
@@ -5111,10 +5121,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="M24" s="10">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
@@ -5159,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -5185,10 +5195,10 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" s="10">
         <v>6</v>
@@ -5209,19 +5219,19 @@
         <v>7263</v>
       </c>
       <c r="L26" s="10">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="M26" s="10">
-        <v>4.62</v>
+        <v>4.41</v>
       </c>
       <c r="N26" s="10">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="O26" s="10">
         <v>16.670000000000002</v>
       </c>
       <c r="P26" s="10">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -5235,16 +5245,16 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E27" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F27" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G27" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="10">
         <v>3</v>
@@ -5259,19 +5269,19 @@
         <v>18698</v>
       </c>
       <c r="L27" s="10">
-        <v>8.16</v>
+        <v>8.33</v>
       </c>
       <c r="M27" s="10">
-        <v>11.9</v>
+        <v>11.35</v>
       </c>
       <c r="N27" s="10">
-        <v>70.83</v>
+        <v>70.37</v>
       </c>
       <c r="O27" s="10">
-        <v>17.649999999999999</v>
+        <v>15.79</v>
       </c>
       <c r="P27" s="10">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5285,13 +5295,13 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>13</v>
+      </c>
+      <c r="E28" s="10">
         <v>12</v>
       </c>
-      <c r="E28" s="10">
-        <v>11</v>
-      </c>
       <c r="F28" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="10">
         <v>4</v>
@@ -5309,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -5335,22 +5345,22 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E29" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F29" s="10">
         <v>1</v>
       </c>
       <c r="G29" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H29" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="10">
-        <v>0</v>
+        <v>7572</v>
       </c>
       <c r="J29" s="10">
         <v>0</v>
@@ -5359,19 +5369,19 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>13.61</v>
+        <v>13.27</v>
       </c>
       <c r="M29" s="10">
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N29" s="10">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O29" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29" s="10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
@@ -5385,13 +5395,13 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E30" s="10">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F30" s="10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10">
         <v>4</v>
@@ -5409,19 +5419,19 @@
         <v>15860</v>
       </c>
       <c r="L30" s="10">
-        <v>11.56</v>
+        <v>11.42</v>
       </c>
       <c r="M30" s="10">
-        <v>10.09</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="N30" s="10">
-        <v>35.29</v>
+        <v>43.24</v>
       </c>
       <c r="O30" s="10">
-        <v>16.670000000000002</v>
+        <v>12.5</v>
       </c>
       <c r="P30" s="10">
-        <v>5.88</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5435,13 +5445,13 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E31" s="10">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F31" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" s="10">
         <v>7</v>
@@ -5459,19 +5469,19 @@
         <v>21270.240000000002</v>
       </c>
       <c r="L31" s="10">
-        <v>12.59</v>
+        <v>13.27</v>
       </c>
       <c r="M31" s="10">
-        <v>13.53</v>
+        <v>12.91</v>
       </c>
       <c r="N31" s="10">
-        <v>40.54</v>
+        <v>37.21</v>
       </c>
       <c r="O31" s="10">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="P31" s="10">
-        <v>8.11</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -5485,13 +5495,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E32" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F32" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G32" s="10">
         <v>7</v>
@@ -5509,19 +5519,19 @@
         <v>5859</v>
       </c>
       <c r="L32" s="10">
-        <v>4.42</v>
+        <v>4.63</v>
       </c>
       <c r="M32" s="10">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="N32" s="10">
-        <v>61.54</v>
+        <v>66.67</v>
       </c>
       <c r="O32" s="10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P32" s="10">
-        <v>15.38</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5541,7 +5551,7 @@
         <v>11</v>
       </c>
       <c r="F33" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -5559,13 +5569,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>27.27</v>
+        <v>36.36</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
@@ -5585,16 +5595,16 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E34" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F34" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G34" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="10">
         <v>3</v>
@@ -5609,19 +5619,19 @@
         <v>24149.8</v>
       </c>
       <c r="L34" s="10">
-        <v>5.44</v>
+        <v>6.17</v>
       </c>
       <c r="M34" s="10">
-        <v>15.36</v>
+        <v>14.66</v>
       </c>
       <c r="N34" s="10">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="O34" s="10">
-        <v>30</v>
+        <v>23.08</v>
       </c>
       <c r="P34" s="10">
-        <v>18.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5635,13 +5645,13 @@
         <v>18</v>
       </c>
       <c r="D35" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E35" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" s="10">
         <v>3</v>
@@ -5659,19 +5669,19 @@
         <v>7483.12</v>
       </c>
       <c r="L35" s="10">
-        <v>3.74</v>
+        <v>4.32</v>
       </c>
       <c r="M35" s="10">
-        <v>9.16</v>
+        <v>8.74</v>
       </c>
       <c r="N35" s="10">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="O35" s="10">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="P35" s="10">
-        <v>18.18</v>
+        <v>14.29</v>
       </c>
     </row>
   </sheetData>
@@ -5754,7 +5764,7 @@
         <v>667.25</v>
       </c>
       <c r="G5" s="5">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H5" s="5">
         <v>70</v>
@@ -5859,19 +5869,19 @@
         <v>354.93</v>
       </c>
       <c r="G8" s="5">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H8" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J8" s="5">
-        <v>394899.38</v>
+        <v>402143.38</v>
       </c>
       <c r="K8" s="5">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5929,7 +5939,7 @@
         <v>322.38</v>
       </c>
       <c r="G10" s="5">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H10" s="5">
         <v>109</v>
@@ -6034,7 +6044,7 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H13" s="5">
         <v>115</v>
@@ -6139,19 +6149,19 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H16" s="5">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I16" s="5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" s="5">
-        <v>504461.62</v>
+        <v>511623.25</v>
       </c>
       <c r="K16" s="5">
-        <v>32.369999999999997</v>
+        <v>32.840000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6183,10 +6193,10 @@
         <v>37</v>
       </c>
       <c r="J17" s="5">
-        <v>245530.65</v>
+        <v>249351.65</v>
       </c>
       <c r="K17" s="5">
-        <v>18.38</v>
+        <v>18.690000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6247,16 +6257,16 @@
         <v>250</v>
       </c>
       <c r="H19" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J19" s="5">
-        <v>382052.09</v>
+        <v>389846.09</v>
       </c>
       <c r="K19" s="5">
-        <v>37.53</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -6279,10 +6289,10 @@
         <v>293.32</v>
       </c>
       <c r="G20" s="10">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H20" s="10">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" s="10">
         <v>30</v>
@@ -6305,19 +6315,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1731</v>
+        <v>1885</v>
       </c>
       <c r="E21" s="10">
-        <v>5123.1000000000004</v>
+        <v>5645.96</v>
       </c>
       <c r="F21" s="10">
-        <v>140.96</v>
+        <v>153.94</v>
       </c>
       <c r="G21" s="10">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H21" s="10">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I21" s="10">
         <v>4</v>
@@ -6326,7 +6336,7 @@
         <v>24106</v>
       </c>
       <c r="K21" s="10">
-        <v>3.71</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6900,16 +6910,16 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="E38" s="10">
-        <v>4043.73</v>
+        <v>4442.26</v>
       </c>
       <c r="F38" s="10">
-        <v>9.35</v>
+        <v>13.35</v>
       </c>
       <c r="G38" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="10">
         <v>4</v>
@@ -7434,7 +7444,7 @@
         <v>141.16999999999999</v>
       </c>
       <c r="G53" s="10">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H53" s="10">
         <v>36</v>
@@ -7495,19 +7505,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>1339</v>
+        <v>1439</v>
       </c>
       <c r="E55" s="10">
-        <v>16436.72</v>
+        <v>17674.21</v>
       </c>
       <c r="F55" s="10">
-        <v>53.66</v>
+        <v>59.66</v>
       </c>
       <c r="G55" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H55" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
@@ -7516,7 +7526,7 @@
         <v>14289</v>
       </c>
       <c r="K55" s="10">
-        <v>-0.13</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -8255,10 +8265,10 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E77" s="10">
-        <v>2411.5500000000002</v>
+        <v>2553.41</v>
       </c>
       <c r="F77" s="10">
         <v>6.33</v>
@@ -8267,7 +8277,7 @@
         <v>6</v>
       </c>
       <c r="H77" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="10">
         <v>0</v>
@@ -9010,10 +9020,10 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>529</v>
+        <v>565</v>
       </c>
       <c r="E100" s="10">
-        <v>6870.74</v>
+        <v>7507.61</v>
       </c>
       <c r="F100" s="10">
         <v>13.17</v>
@@ -9934,10 +9944,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H127" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -10135,19 +10145,19 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="E133" s="10">
-        <v>1221.7</v>
+        <v>2492.39</v>
       </c>
       <c r="F133" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G133" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H133" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I133" s="10">
         <v>1</v>
@@ -10156,7 +10166,7 @@
         <v>7647</v>
       </c>
       <c r="K133" s="10">
-        <v>5.26</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -10599,7 +10609,7 @@
         <v>7.83</v>
       </c>
       <c r="G146" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H146" s="10">
         <v>4</v>
@@ -11970,16 +11980,16 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="E187" s="10">
-        <v>5412.08</v>
+        <v>5519.75</v>
       </c>
       <c r="F187" s="10">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G187" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H187" s="10">
         <v>12</v>
@@ -11991,7 +12001,7 @@
         <v>7263</v>
       </c>
       <c r="K187" s="10">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -12115,19 +12125,19 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>31423</v>
+        <v>31731</v>
       </c>
       <c r="E192" s="10">
-        <v>15756.97</v>
+        <v>16668.36</v>
       </c>
       <c r="F192" s="10">
         <v>70.11</v>
       </c>
       <c r="G192" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H192" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I192" s="10">
         <v>1</v>
@@ -12136,7 +12146,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12700,16 +12710,16 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="E209" s="10">
-        <v>2730.54</v>
+        <v>3022.33</v>
       </c>
       <c r="F209" s="10">
-        <v>9.67</v>
+        <v>10.67</v>
       </c>
       <c r="G209" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H209" s="10">
         <v>1</v>
@@ -13295,13 +13305,13 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E226" s="10">
-        <v>2812.04</v>
+        <v>2943.88</v>
       </c>
       <c r="F226" s="10">
-        <v>6.46</v>
+        <v>7.46</v>
       </c>
       <c r="G226" s="10">
         <v>5</v>
@@ -13759,10 +13769,10 @@
         <v>31.97</v>
       </c>
       <c r="G239" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H239" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I239" s="10">
         <v>4</v>
@@ -13890,10 +13900,10 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="E243" s="10">
-        <v>4851.8</v>
+        <v>5279.13</v>
       </c>
       <c r="F243" s="10">
         <v>11.75</v>
@@ -13911,7 +13921,7 @@
         <v>8116</v>
       </c>
       <c r="K243" s="10">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
@@ -14602,7 +14612,7 @@
         <v>42</v>
       </c>
       <c r="H263" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I263" s="10">
         <v>3</v>
@@ -14678,10 +14688,10 @@
         <v>2</v>
       </c>
       <c r="J265" s="10">
-        <v>11620</v>
+        <v>12059</v>
       </c>
       <c r="K265" s="10">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
@@ -14695,10 +14705,10 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="E266" s="10">
-        <v>5213.82</v>
+        <v>5603.39</v>
       </c>
       <c r="F266" s="10">
         <v>17.66</v>
@@ -14716,7 +14726,7 @@
         <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15734,19 +15744,19 @@
         <v>104.01</v>
       </c>
       <c r="G298" s="10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H298" s="10">
         <v>30</v>
       </c>
       <c r="I298" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J298" s="10">
-        <v>55483.13</v>
+        <v>61881.13</v>
       </c>
       <c r="K298" s="10">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
@@ -15944,10 +15954,10 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H304" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I304" s="10">
         <v>6</v>
@@ -15970,19 +15980,19 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>910</v>
+        <v>954</v>
       </c>
       <c r="E305" s="10">
-        <v>11084.85</v>
+        <v>11848.18</v>
       </c>
       <c r="F305" s="10">
-        <v>39.909999999999997</v>
+        <v>43.91</v>
       </c>
       <c r="G305" s="10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H305" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I305" s="10">
         <v>2</v>
@@ -15991,7 +16001,7 @@
         <v>15798.24</v>
       </c>
       <c r="K305" s="10">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16214,10 +16224,10 @@
         <v>110.71</v>
       </c>
       <c r="G312" s="10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H312" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I312" s="10">
         <v>10</v>
@@ -16240,19 +16250,19 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>1957</v>
+        <v>2085</v>
       </c>
       <c r="E313" s="10">
-        <v>11872.43</v>
+        <v>12945.3</v>
       </c>
       <c r="F313" s="10">
-        <v>34.81</v>
+        <v>36.81</v>
       </c>
       <c r="G313" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H313" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I313" s="10">
         <v>3</v>
@@ -16261,7 +16271,7 @@
         <v>24257.119999999999</v>
       </c>
       <c r="K313" s="10">
-        <v>1.04</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16354,19 +16364,19 @@
         <v>119.16</v>
       </c>
       <c r="G316" s="10">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H316" s="10">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I316" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J316" s="10">
-        <v>64394.84</v>
+        <v>57233.21</v>
       </c>
       <c r="K316" s="10">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
@@ -16462,16 +16472,16 @@
         <v>53</v>
       </c>
       <c r="H319" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I319" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J319" s="10">
-        <v>23880</v>
+        <v>39861</v>
       </c>
       <c r="K319" s="10">
-        <v>-0.21</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
@@ -16520,19 +16530,19 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>2992</v>
+        <v>3189</v>
       </c>
       <c r="E321" s="10">
-        <v>11968.76</v>
+        <v>12729.71</v>
       </c>
       <c r="F321" s="10">
-        <v>50.34</v>
+        <v>54.34</v>
       </c>
       <c r="G321" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H321" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I321" s="10">
         <v>2</v>
@@ -16541,7 +16551,7 @@
         <v>5859</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -16659,19 +16669,19 @@
         <v>118.06</v>
       </c>
       <c r="G325" s="10">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H325" s="10">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I325" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J325" s="10">
-        <v>132287.63</v>
+        <v>126854.51</v>
       </c>
       <c r="K325" s="10">
-        <v>2.57</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
@@ -16764,19 +16774,19 @@
         <v>95.25</v>
       </c>
       <c r="G328" s="10">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H328" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I328" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J328" s="10">
-        <v>101762.3</v>
+        <v>108090.19</v>
       </c>
       <c r="K328" s="10">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
@@ -17114,7 +17124,7 @@
         <v>171.77</v>
       </c>
       <c r="G338" s="10">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H338" s="10">
         <v>14</v>
@@ -17140,19 +17150,19 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>1003</v>
+        <v>1057</v>
       </c>
       <c r="E339" s="10">
-        <v>11448.69</v>
+        <v>12447.74</v>
       </c>
       <c r="F339" s="10">
-        <v>39.32</v>
+        <v>46.32</v>
       </c>
       <c r="G339" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H339" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I339" s="10">
         <v>0</v>
@@ -17594,10 +17604,10 @@
         <v>51.39</v>
       </c>
       <c r="G352" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H352" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I352" s="10">
         <v>2</v>
@@ -17620,13 +17630,13 @@
         <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="E353" s="10">
-        <v>3120.24</v>
+        <v>3376.33</v>
       </c>
       <c r="F353" s="10">
-        <v>14.32</v>
+        <v>15.31</v>
       </c>
       <c r="G353" s="10">
         <v>4</v>
@@ -17699,19 +17709,19 @@
         <v>74.679999999999893</v>
       </c>
       <c r="G355" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H355" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I355" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J355" s="10">
-        <v>80023.12</v>
+        <v>86918.12</v>
       </c>
       <c r="K355" s="10">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
@@ -18157,16 +18167,16 @@
         <v>26</v>
       </c>
       <c r="H368" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I368" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J368" s="10">
-        <v>51854.48</v>
+        <v>44060.479999999901</v>
       </c>
       <c r="K368" s="10">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -18215,10 +18225,10 @@
         <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="E370" s="10">
-        <v>7308.75</v>
+        <v>7850.61</v>
       </c>
       <c r="F370" s="10">
         <v>31.74</v>
@@ -18227,7 +18237,7 @@
         <v>6</v>
       </c>
       <c r="H370" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I370" s="10">
         <v>0</v>
@@ -19055,19 +19065,19 @@
         <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>554</v>
+        <v>609</v>
       </c>
       <c r="E394" s="10">
-        <v>7663.34</v>
+        <v>8597.1299999999992</v>
       </c>
       <c r="F394" s="10">
-        <v>22.72</v>
+        <v>27.72</v>
       </c>
       <c r="G394" s="10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H394" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I394" s="10">
         <v>3</v>
@@ -19076,7 +19086,7 @@
         <v>24149.8</v>
       </c>
       <c r="K394" s="10">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -19704,7 +19714,7 @@
         <v>19.079999999999998</v>
       </c>
       <c r="G414" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H414" s="10">
         <v>4</v>
@@ -20045,19 +20055,19 @@
         <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="E424" s="10">
-        <v>4516.95</v>
+        <v>4917.6400000000003</v>
       </c>
       <c r="F424" s="10">
-        <v>18.66</v>
+        <v>20.66</v>
       </c>
       <c r="G424" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H424" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I424" s="10">
         <v>0</v>
@@ -20311,7 +20321,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24837,7 +24847,7 @@
         <v>3</v>
       </c>
       <c r="H122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -24866,10 +24876,10 @@
         <v>26</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F123">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G123">
         <v>3</v>
@@ -24904,16 +24914,16 @@
         <v>27</v>
       </c>
       <c r="E124">
+        <v>21</v>
+      </c>
+      <c r="F124">
         <v>19</v>
-      </c>
-      <c r="F124">
-        <v>17</v>
       </c>
       <c r="G124">
         <v>9</v>
       </c>
       <c r="H124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I124">
         <v>2</v>
@@ -24951,7 +24961,7 @@
         <v>2</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -25208,16 +25218,16 @@
         <v>33</v>
       </c>
       <c r="E132">
+        <v>8</v>
+      </c>
+      <c r="F132">
         <v>7</v>
       </c>
-      <c r="F132">
-        <v>6</v>
-      </c>
       <c r="G132">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -25284,13 +25294,13 @@
         <v>40</v>
       </c>
       <c r="E134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -25369,7 +25379,7 @@
         <v>4</v>
       </c>
       <c r="H136">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -25404,7 +25414,7 @@
         <v>3</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -25702,10 +25712,10 @@
         <v>41</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -25816,16 +25826,16 @@
         <v>13</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F148">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -25968,13 +25978,13 @@
         <v>52</v>
       </c>
       <c r="E152">
+        <v>5</v>
+      </c>
+      <c r="F152">
+        <v>5</v>
+      </c>
+      <c r="G152">
         <v>4</v>
-      </c>
-      <c r="F152">
-        <v>4</v>
-      </c>
-      <c r="G152">
-        <v>3</v>
       </c>
       <c r="H152">
         <v>2</v>
@@ -26082,13 +26092,13 @@
         <v>13</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -26234,22 +26244,22 @@
         <v>13</v>
       </c>
       <c r="E159">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F159">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G159">
         <v>1</v>
       </c>
       <c r="H159">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159">
-        <v>0</v>
+        <v>7572</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -26345,19 +26355,19 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162">
         <v>0</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -26383,7 +26393,7 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -26421,19 +26431,19 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G164">
         <v>0</v>
       </c>
       <c r="H164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -26459,19 +26469,19 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165">
         <v>0</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26497,19 +26507,19 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E166">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F166">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G166">
         <v>0</v>
       </c>
       <c r="H166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -26535,19 +26545,19 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G167">
         <v>0</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -26564,7 +26574,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B168" s="18">
         <v>2026</v>
@@ -26573,31 +26583,31 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E168">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F168">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G168">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168">
-        <v>7544</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168">
-        <v>7544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -26611,31 +26621,31 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F169">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>7544</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169">
-        <v>0</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -26649,16 +26659,16 @@
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -26687,31 +26697,31 @@
         <v>18</v>
       </c>
       <c r="D171" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E171">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F171">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="K171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171">
-        <v>8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -26725,31 +26735,31 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E172">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H172">
         <v>1</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -26763,19 +26773,19 @@
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E173">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -26801,16 +26811,16 @@
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -26830,7 +26840,7 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B175" s="18">
         <v>2026</v>
@@ -26839,31 +26849,31 @@
         <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E175">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F175">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G175">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H175">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175">
-        <v>5472</v>
+        <v>0</v>
       </c>
       <c r="K175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175">
-        <v>5472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -26877,31 +26887,31 @@
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>5472</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L176">
-        <v>0</v>
+        <v>5472</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -26915,13 +26925,13 @@
         <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -26953,13 +26963,13 @@
         <v>18</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -26991,7 +27001,7 @@
         <v>18</v>
       </c>
       <c r="D179" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -27000,22 +27010,22 @@
         <v>1</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179">
-        <v>7482.24</v>
+        <v>0</v>
       </c>
       <c r="K179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L179">
-        <v>7482.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -27029,31 +27039,31 @@
         <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E180">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F180">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180">
         <v>1</v>
       </c>
       <c r="J180">
-        <v>8316</v>
+        <v>7482.24</v>
       </c>
       <c r="K180">
         <v>1</v>
       </c>
       <c r="L180">
-        <v>8316</v>
+        <v>7482.24</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -27067,31 +27077,31 @@
         <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E181">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F181">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G181">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>8316</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181">
-        <v>0</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -27105,19 +27115,19 @@
         <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E182">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G182">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -27143,7 +27153,7 @@
         <v>18</v>
       </c>
       <c r="D183" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -27152,7 +27162,7 @@
         <v>1</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -27172,7 +27182,7 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B184" s="18">
         <v>2026</v>
@@ -27181,7 +27191,7 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -27219,7 +27229,7 @@
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -27257,19 +27267,19 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -27295,31 +27305,31 @@
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E187">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F187">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G187">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J187">
-        <v>5859</v>
+        <v>0</v>
       </c>
       <c r="K187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L187">
-        <v>5859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -27333,36 +27343,36 @@
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E188">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F188">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G188">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>5859</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L188">
-        <v>0</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B189" s="18">
         <v>2026</v>
@@ -27371,19 +27381,19 @@
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E189">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F189">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I189">
         <v>0</v>
@@ -27409,7 +27419,7 @@
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E190">
         <v>4</v>
@@ -27418,7 +27428,7 @@
         <v>4</v>
       </c>
       <c r="G190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -27447,13 +27457,13 @@
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="E191">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F191">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G191">
         <v>2</v>
@@ -27476,7 +27486,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B192" s="18">
         <v>2026</v>
@@ -27485,7 +27495,7 @@
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="E192">
         <v>3</v>
@@ -27494,7 +27504,7 @@
         <v>3</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -27523,19 +27533,19 @@
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
       <c r="H193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -27561,7 +27571,7 @@
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -27570,10 +27580,10 @@
         <v>1</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194">
         <v>0</v>
@@ -27599,36 +27609,36 @@
         <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E195">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F195">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G195">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I195">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J195">
-        <v>24149.8</v>
+        <v>0</v>
       </c>
       <c r="K195">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L195">
-        <v>24149.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B196" s="18">
         <v>2026</v>
@@ -27637,13 +27647,13 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -27652,10 +27662,10 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196">
-        <v>6910</v>
+        <v>0</v>
       </c>
       <c r="K196">
         <v>0</v>
@@ -27666,7 +27676,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B197" s="18">
         <v>2026</v>
@@ -27675,31 +27685,31 @@
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E197">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>24149.8</v>
       </c>
       <c r="K197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L197">
-        <v>0</v>
+        <v>24149.8</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -27713,31 +27723,31 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I198">
         <v>1</v>
       </c>
       <c r="J198">
-        <v>7483.12</v>
+        <v>6910</v>
       </c>
       <c r="K198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198">
-        <v>7483.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -27751,7 +27761,7 @@
         <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="E199">
         <v>2</v>
@@ -27760,7 +27770,7 @@
         <v>2</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -27789,30 +27799,144 @@
         <v>18</v>
       </c>
       <c r="D200" t="s">
+        <v>52</v>
+      </c>
+      <c r="E200">
+        <v>2</v>
+      </c>
+      <c r="F200">
+        <v>2</v>
+      </c>
+      <c r="G200">
+        <v>2</v>
+      </c>
+      <c r="H200">
+        <v>2</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>7483.12</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>7483.12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>132</v>
+      </c>
+      <c r="B201" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C201" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" t="s">
+        <v>53</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>132</v>
+      </c>
+      <c r="B202" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C202" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>55</v>
+      </c>
+      <c r="E202">
+        <v>2</v>
+      </c>
+      <c r="F202">
+        <v>2</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>132</v>
+      </c>
+      <c r="B203" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C203" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D203" t="s">
         <v>65</v>
       </c>
-      <c r="E200">
-        <v>5</v>
-      </c>
-      <c r="F200">
-        <v>5</v>
-      </c>
-      <c r="G200">
-        <v>2</v>
-      </c>
-      <c r="H200">
-        <v>1</v>
-      </c>
-      <c r="I200">
-        <v>0</v>
-      </c>
-      <c r="J200">
-        <v>0</v>
-      </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="L200">
+      <c r="E203">
+        <v>6</v>
+      </c>
+      <c r="F203">
+        <v>6</v>
+      </c>
+      <c r="G203">
+        <v>3</v>
+      </c>
+      <c r="H203">
+        <v>1</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
         <v>0</v>
       </c>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDB2113-CE19-4086-824F-02A6B62BDA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9982F5-8245-4CCF-868C-A066B069D642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="139">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -437,6 +437,9 @@
   </si>
   <si>
     <t>gbp</t>
+  </si>
+  <si>
+    <t>Competitors â€“ USA</t>
   </si>
 </sst>
 </file>
@@ -1082,64 +1085,64 @@
         <v>99</v>
       </c>
       <c r="B6" s="5">
-        <v>712.91</v>
+        <v>765.91</v>
       </c>
       <c r="C6" s="5">
-        <v>387.92</v>
+        <v>412.92</v>
       </c>
       <c r="D6" s="5">
-        <v>324.99</v>
+        <v>352.99</v>
       </c>
       <c r="E6" s="5">
-        <v>160563.48000000001</v>
+        <v>173684.89</v>
       </c>
       <c r="F6" s="5">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="G6" s="5">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H6" s="5">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="I6" s="5">
+        <v>152</v>
+      </c>
+      <c r="J6" s="5">
+        <v>34</v>
+      </c>
+      <c r="K6" s="5">
+        <v>494.82874643874601</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1142.6637499999999</v>
+      </c>
+      <c r="M6" s="5">
+        <v>24.1942232280539</v>
+      </c>
+      <c r="N6" s="6">
+        <v>961.44999999999902</v>
+      </c>
+      <c r="O6" s="6">
+        <v>102656.44</v>
+      </c>
+      <c r="P6" s="6">
+        <v>547</v>
+      </c>
+      <c r="Q6" s="6">
         <v>137</v>
       </c>
-      <c r="J6" s="5">
-        <v>25</v>
-      </c>
-      <c r="K6" s="5">
-        <v>495.566296296296</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1171.9962043795599</v>
-      </c>
-      <c r="M6" s="5">
-        <v>2.6106060979744301</v>
-      </c>
-      <c r="N6" s="6">
-        <v>874.78</v>
-      </c>
-      <c r="O6" s="6">
-        <v>94301.84</v>
-      </c>
-      <c r="P6" s="6">
-        <v>500</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>123</v>
-      </c>
       <c r="R6" s="6">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="S6" s="6">
-        <v>188.60368</v>
+        <v>187.67173674588599</v>
       </c>
       <c r="T6" s="6">
-        <v>766.68162601626</v>
+        <v>749.31708029197</v>
       </c>
       <c r="U6" s="6">
-        <v>162.83066162865899</v>
+        <v>168.32427658703099</v>
       </c>
       <c r="V6" s="7">
         <v>2201.0699999999902</v>
@@ -1154,7 +1157,7 @@
         <v>313</v>
       </c>
       <c r="Z6" s="7">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AA6" s="8">
         <v>392500</v>
@@ -1166,7 +1169,7 @@
         <v>314</v>
       </c>
       <c r="AD6" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1174,64 +1177,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>153.94</v>
+        <v>167.94</v>
       </c>
       <c r="C7" s="5">
-        <v>71.08</v>
+        <v>76.08</v>
       </c>
       <c r="D7" s="5">
-        <v>82.86</v>
+        <v>91.86</v>
       </c>
       <c r="E7" s="5">
-        <v>5645.96</v>
+        <v>6138.3</v>
       </c>
       <c r="F7" s="5">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G7" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H7" s="5">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I7" s="5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" s="5">
-        <v>64.896091954022907</v>
+        <v>64.613684210526301</v>
       </c>
       <c r="L7" s="5">
-        <v>188.19866666666601</v>
+        <v>180.53823529411699</v>
       </c>
       <c r="M7" s="5">
-        <v>684.24218379159595</v>
+        <v>813.84324650147403</v>
       </c>
       <c r="N7" s="6">
-        <v>163.84</v>
+        <v>184.32</v>
       </c>
       <c r="O7" s="6">
-        <v>8815.01</v>
+        <v>9770.25</v>
       </c>
       <c r="P7" s="6">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="Q7" s="6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R7" s="6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S7" s="6">
-        <v>50.371485714285697</v>
+        <v>50.362113402061802</v>
       </c>
       <c r="T7" s="6">
-        <v>205.000232558139</v>
+        <v>217.11666666666599</v>
       </c>
       <c r="U7" s="6">
-        <v>997.41611183651503</v>
+        <v>1093.3506307412799</v>
       </c>
       <c r="V7" s="7">
         <v>349.01</v>
@@ -1246,7 +1249,7 @@
         <v>93</v>
       </c>
       <c r="Z7" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA7" s="8">
         <v>15000</v>
@@ -1258,7 +1261,7 @@
         <v>71</v>
       </c>
       <c r="AD7" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,7 +1278,7 @@
         <v>6.35</v>
       </c>
       <c r="E8" s="5">
-        <v>4442.26</v>
+        <v>4840.0600000000004</v>
       </c>
       <c r="F8" s="5">
         <v>6</v>
@@ -1293,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>740.37666666666598</v>
+        <v>806.67666666666605</v>
       </c>
       <c r="L8" s="5">
-        <v>1480.7533333333299</v>
+        <v>1613.3533333333301</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
@@ -1305,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="O8" s="6">
-        <v>1232.8599999999999</v>
+        <v>1404.23</v>
       </c>
       <c r="P8" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="6">
         <v>2</v>
@@ -1317,13 +1320,13 @@
         <v>1</v>
       </c>
       <c r="S8" s="6">
-        <v>205.47666666666601</v>
+        <v>175.52875</v>
       </c>
       <c r="T8" s="6">
-        <v>616.42999999999995</v>
+        <v>702.11500000000001</v>
       </c>
       <c r="U8" s="6">
-        <v>8.1225767727073706</v>
+        <v>-5.0725308532078097</v>
       </c>
       <c r="V8" s="7">
         <v>12</v>
@@ -1350,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="AD8" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1358,25 +1361,25 @@
         <v>27</v>
       </c>
       <c r="B9" s="5">
-        <v>59.66</v>
+        <v>62.66</v>
       </c>
       <c r="C9" s="5">
-        <v>33.659999999999997</v>
+        <v>35.659999999999997</v>
       </c>
       <c r="D9" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="5">
-        <v>17674.21</v>
+        <v>19034.95</v>
       </c>
       <c r="F9" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="5">
         <v>9</v>
@@ -1385,37 +1388,37 @@
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>768.44391304347801</v>
+        <v>793.12291666666601</v>
       </c>
       <c r="L9" s="5">
-        <v>1963.80111111111</v>
+        <v>2114.99444444444</v>
       </c>
       <c r="M9" s="5">
-        <v>-19.153387902486099</v>
+        <v>-24.9328209425294</v>
       </c>
       <c r="N9" s="6">
-        <v>15.84</v>
+        <v>16.84</v>
       </c>
       <c r="O9" s="6">
-        <v>3832.66</v>
+        <v>4158.2</v>
       </c>
       <c r="P9" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" s="6">
         <v>3</v>
       </c>
       <c r="S9" s="6">
-        <v>153.3064</v>
+        <v>148.50714285714199</v>
       </c>
       <c r="T9" s="6">
-        <v>1916.33</v>
+        <v>1386.06666666666</v>
       </c>
       <c r="U9" s="6">
-        <v>190.63365912968999</v>
+        <v>167.88033283632299</v>
       </c>
       <c r="V9" s="7">
         <v>41.38</v>
@@ -1442,7 +1445,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1486,7 +1489,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1506,10 +1509,10 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6">
-        <v>77.790000000000006</v>
+        <v>82.79</v>
       </c>
       <c r="O11" s="6">
-        <v>4246.4799999999996</v>
+        <v>4531.01</v>
       </c>
       <c r="P11" s="6">
         <v>8</v>
@@ -1521,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="6">
-        <v>530.80999999999995</v>
+        <v>566.37625000000003</v>
       </c>
       <c r="T11" s="6">
-        <v>2123.2399999999998</v>
+        <v>2265.5050000000001</v>
       </c>
       <c r="U11" s="6">
-        <v>77.605923023304001</v>
+        <v>66.452954197849905</v>
       </c>
       <c r="V11" s="7">
         <v>168.78</v>
@@ -1548,7 +1551,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="9"/>
       <c r="AD11" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1556,22 +1559,22 @@
         <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>6.33</v>
+        <v>7.33</v>
       </c>
       <c r="C12" s="5">
-        <v>2.33</v>
+        <v>3.33</v>
       </c>
       <c r="D12" s="5">
         <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>2553.41</v>
+        <v>2699.25</v>
       </c>
       <c r="F12" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="5">
         <v>4</v>
@@ -1583,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>425.56833333333299</v>
+        <v>385.60714285714198</v>
       </c>
       <c r="L12" s="5">
-        <v>1276.7049999999999</v>
+        <v>1349.625</v>
       </c>
       <c r="M12" s="5">
         <v>-100</v>
@@ -1595,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="O12" s="6">
-        <v>1297.5999999999999</v>
+        <v>1435.09</v>
       </c>
       <c r="P12" s="6">
         <v>5</v>
@@ -1607,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="6">
-        <v>259.52</v>
+        <v>287.01799999999997</v>
       </c>
       <c r="T12" s="6">
-        <v>648.79999999999995</v>
+        <v>717.54499999999996</v>
       </c>
       <c r="U12" s="6">
         <v>-100</v>
@@ -1640,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1684,7 +1687,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
       <c r="AD13" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1704,10 +1707,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>12.08</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="O14" s="6">
-        <v>1238.29</v>
+        <v>1322.76</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1734,7 +1737,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1757,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>301.73</v>
+        <v>315.20999999999998</v>
       </c>
       <c r="P15" s="6">
         <v>2</v>
@@ -1769,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <v>150.86500000000001</v>
+        <v>157.60499999999999</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
@@ -1798,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1806,64 +1809,64 @@
         <v>33</v>
       </c>
       <c r="B16" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5">
         <v>5</v>
       </c>
       <c r="D16" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="5">
-        <v>2492.39</v>
+        <v>4332.3500000000004</v>
       </c>
       <c r="F16" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
       </c>
       <c r="H16" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="5">
         <v>1</v>
       </c>
       <c r="K16" s="5">
-        <v>249.239</v>
+        <v>361.02916666666601</v>
       </c>
       <c r="L16" s="5">
-        <v>623.09749999999997</v>
+        <v>866.47</v>
       </c>
       <c r="M16" s="5">
-        <v>206.81394163834699</v>
+        <v>76.509284799242806</v>
       </c>
       <c r="N16" s="6">
-        <v>28.99</v>
+        <v>31</v>
       </c>
       <c r="O16" s="6">
-        <v>6532.72</v>
+        <v>7196.22</v>
       </c>
       <c r="P16" s="6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R16" s="6">
         <v>1</v>
       </c>
       <c r="S16" s="6">
-        <v>197.96121212121199</v>
+        <v>199.89500000000001</v>
       </c>
       <c r="T16" s="6">
-        <v>653.27200000000005</v>
+        <v>599.68499999999995</v>
       </c>
       <c r="U16" s="6">
-        <v>5.0922127383386897</v>
+        <v>-4.5974136421621301</v>
       </c>
       <c r="V16" s="7">
         <v>73.650000000000006</v>
@@ -1890,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,28 +1913,28 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>67.69</v>
+        <v>72.69</v>
       </c>
       <c r="O17" s="6">
-        <v>4399.08</v>
+        <v>4722.0600000000004</v>
       </c>
       <c r="P17" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q17" s="6">
         <v>2</v>
       </c>
       <c r="R17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="6">
-        <v>314.219999999999</v>
+        <v>314.80399999999997</v>
       </c>
       <c r="T17" s="6">
-        <v>2199.54</v>
+        <v>2361.0300000000002</v>
       </c>
       <c r="U17" s="6">
-        <v>-100</v>
+        <v>-96.8234202869086</v>
       </c>
       <c r="V17" s="7">
         <v>191.54</v>
@@ -1946,13 +1949,13 @@
         <v>7</v>
       </c>
       <c r="Z17" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="8"/>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1975,7 +1978,7 @@
         <v>2.98</v>
       </c>
       <c r="O18" s="6">
-        <v>859.97</v>
+        <v>895.35</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1987,13 +1990,13 @@
         <v>1</v>
       </c>
       <c r="S18" s="6">
-        <v>286.65666666666601</v>
+        <v>298.45</v>
       </c>
       <c r="T18" s="6">
-        <v>859.97</v>
+        <v>895.35</v>
       </c>
       <c r="U18" s="6">
-        <v>1004.92226473016</v>
+        <v>961.26095940135099</v>
       </c>
       <c r="V18" s="7">
         <v>5.98</v>
@@ -2018,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2041,7 +2044,7 @@
         <v>8</v>
       </c>
       <c r="O19" s="6">
-        <v>1220.5</v>
+        <v>1291.24</v>
       </c>
       <c r="P19" s="6">
         <v>1</v>
@@ -2053,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <v>1220.5</v>
+        <v>1291.24</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6">
@@ -2078,7 +2081,7 @@
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2101,7 +2104,7 @@
         <v>6.02</v>
       </c>
       <c r="O20" s="6">
-        <v>1858.63</v>
+        <v>2055.21</v>
       </c>
       <c r="P20" s="6">
         <v>2</v>
@@ -2113,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>929.31500000000005</v>
+        <v>1027.605</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6">
@@ -2138,7 +2141,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2146,32 +2149,22 @@
         <v>38</v>
       </c>
       <c r="B21" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5">
-        <v>20.010000000000002</v>
+        <v>21.01</v>
       </c>
       <c r="D21" s="5">
         <v>20.99</v>
       </c>
       <c r="E21" s="5">
-        <v>5519.75</v>
-      </c>
-      <c r="F21" s="5">
-        <v>25</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5">
-        <v>24</v>
-      </c>
-      <c r="I21" s="5">
-        <v>13</v>
-      </c>
-      <c r="J21" s="5">
-        <v>1</v>
-      </c>
+        <v>5552.92</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -2191,14 +2184,10 @@
       <c r="AA21" s="8">
         <v>22000</v>
       </c>
-      <c r="AB21" s="9">
-        <v>60</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>28</v>
-      </c>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2244,49 +2233,35 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5">
-        <v>70.11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>64.12</v>
-      </c>
-      <c r="D23" s="5">
-        <v>5.99</v>
-      </c>
-      <c r="E23" s="5">
-        <v>16668.36</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G23" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I23" s="5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J23" s="5">
         <v>1</v>
       </c>
-      <c r="K23" s="5">
-        <v>1666.836</v>
-      </c>
-      <c r="L23" s="5">
-        <v>3333.672</v>
-      </c>
-      <c r="M23" s="5">
-        <v>-53.840689785917696</v>
-      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -2300,172 +2275,146 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
-      <c r="AA23" s="8">
-        <v>40000</v>
-      </c>
+      <c r="AA23" s="8"/>
       <c r="AB23" s="9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AC23" s="9">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AD23" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5">
-        <v>10.67</v>
+        <v>71.11</v>
       </c>
       <c r="C24" s="5">
-        <v>2</v>
+        <v>64.12</v>
       </c>
       <c r="D24" s="5">
-        <v>8.67</v>
+        <v>6.99</v>
       </c>
       <c r="E24" s="5">
-        <v>3022.33</v>
+        <v>17220.240000000002</v>
       </c>
       <c r="F24" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G24" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H24" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I24" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="5">
-        <v>377.79124999999999</v>
+        <v>1565.47636363636</v>
       </c>
       <c r="L24" s="5">
-        <v>3022.33</v>
+        <v>2870.04</v>
       </c>
       <c r="M24" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N24" s="6">
-        <v>8.02</v>
-      </c>
-      <c r="O24" s="6">
-        <v>1386.28</v>
-      </c>
+        <v>-55.320018768611803</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
-      <c r="V24" s="7">
-        <v>22.52</v>
-      </c>
-      <c r="W24" s="7">
-        <v>3629.71</v>
-      </c>
-      <c r="X24" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="7">
-        <v>0</v>
-      </c>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
       <c r="AA24" s="8">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="AB24" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC24" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD24" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5">
-        <v>7.46</v>
+        <v>11.67</v>
       </c>
       <c r="C25" s="5">
         <v>3</v>
       </c>
       <c r="D25" s="5">
-        <v>4.46</v>
+        <v>8.67</v>
       </c>
       <c r="E25" s="5">
-        <v>2943.88</v>
+        <v>3306.81</v>
       </c>
       <c r="F25" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I25" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" s="5">
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>588.77599999999995</v>
+        <v>413.35124999999999</v>
       </c>
       <c r="L25" s="5">
-        <v>981.29333333333295</v>
+        <v>3306.81</v>
       </c>
       <c r="M25" s="5">
         <v>-100</v>
       </c>
       <c r="N25" s="6">
-        <v>2</v>
+        <v>10.02</v>
       </c>
       <c r="O25" s="6">
-        <v>501.24</v>
-      </c>
-      <c r="P25" s="6">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <v>125.31</v>
-      </c>
+        <v>1440.12</v>
+      </c>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
       <c r="T25" s="6"/>
-      <c r="U25" s="6">
-        <v>-100</v>
-      </c>
+      <c r="U25" s="6"/>
       <c r="V25" s="7">
-        <v>4</v>
+        <v>22.52</v>
       </c>
       <c r="W25" s="7">
-        <v>1033.75</v>
+        <v>3629.71</v>
       </c>
       <c r="X25" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="7">
         <v>0</v>
@@ -2474,324 +2423,354 @@
         <v>7000</v>
       </c>
       <c r="AB25" s="9">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AC25" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD25" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5">
-        <v>11.75</v>
+        <v>7.46</v>
       </c>
       <c r="C26" s="5">
-        <v>9.25</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5">
-        <v>2.5</v>
+        <v>4.46</v>
       </c>
       <c r="E26" s="5">
-        <v>5279.13</v>
+        <v>3158.48</v>
       </c>
       <c r="F26" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>5279.13</v>
+        <v>631.69600000000003</v>
       </c>
       <c r="L26" s="5">
-        <v>5279.13</v>
+        <v>1052.82666666666</v>
       </c>
       <c r="M26" s="5">
-        <v>53.737452951527999</v>
+        <v>-100</v>
       </c>
       <c r="N26" s="6">
-        <v>30.65</v>
+        <v>2</v>
       </c>
       <c r="O26" s="6">
-        <v>5656.08</v>
+        <v>506.16</v>
       </c>
       <c r="P26" s="6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6">
+        <v>126.54</v>
+      </c>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6">
+        <v>-100</v>
+      </c>
+      <c r="V26" s="7">
+        <v>4</v>
+      </c>
+      <c r="W26" s="7">
+        <v>1033.75</v>
+      </c>
+      <c r="X26" s="7">
         <v>8</v>
       </c>
-      <c r="R26" s="6">
+      <c r="Y26" s="7">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="8">
+        <v>7000</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC26" s="9">
         <v>2</v>
       </c>
-      <c r="S26" s="6">
-        <v>257.09454545454503</v>
-      </c>
-      <c r="T26" s="6">
-        <v>707.01</v>
-      </c>
-      <c r="U26" s="6">
-        <v>161.68300306926301</v>
-      </c>
-      <c r="V26" s="7">
-        <v>66.569999999999993</v>
-      </c>
-      <c r="W26" s="7">
-        <v>14965.45</v>
-      </c>
-      <c r="X26" s="7">
-        <v>50</v>
-      </c>
-      <c r="Y26" s="7">
-        <v>20</v>
-      </c>
-      <c r="Z26" s="7">
-        <v>2</v>
-      </c>
-      <c r="AA26" s="8">
-        <v>12000</v>
-      </c>
-      <c r="AB26" s="9">
-        <v>26</v>
-      </c>
-      <c r="AC26" s="9">
-        <v>7</v>
-      </c>
       <c r="AD26" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B27" s="5">
+        <v>12.75</v>
+      </c>
+      <c r="C27" s="5">
+        <v>10.25</v>
+      </c>
+      <c r="D27" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>5693.2</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5">
+        <v>5693.2</v>
+      </c>
+      <c r="L27" s="5">
+        <v>5693.2</v>
+      </c>
+      <c r="M27" s="5">
+        <v>42.556031757184002</v>
+      </c>
       <c r="N27" s="6">
-        <v>20.04</v>
+        <v>33.65</v>
       </c>
       <c r="O27" s="6">
-        <v>1667.25</v>
+        <v>6185.74</v>
       </c>
       <c r="P27" s="6">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q27" s="6">
+        <v>9</v>
+      </c>
+      <c r="R27" s="6">
         <v>2</v>
       </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
       <c r="S27" s="6">
-        <v>151.56818181818099</v>
+        <v>268.94521739130403</v>
       </c>
       <c r="T27" s="6">
-        <v>833.625</v>
+        <v>687.30444444444402</v>
       </c>
       <c r="U27" s="6">
-        <v>-100</v>
+        <v>139.27614157724</v>
       </c>
       <c r="V27" s="7">
-        <v>65.91</v>
+        <v>66.569999999999993</v>
       </c>
       <c r="W27" s="7">
-        <v>3947.31</v>
+        <v>14965.45</v>
       </c>
       <c r="X27" s="7">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y27" s="7">
+        <v>20</v>
+      </c>
+      <c r="Z27" s="7">
         <v>2</v>
       </c>
-      <c r="Z27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
+      <c r="AA27" s="8">
+        <v>12000</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>26</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>7</v>
+      </c>
       <c r="AD27" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="5">
-        <v>17.66</v>
-      </c>
-      <c r="C28" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="D28" s="5">
-        <v>10.99</v>
-      </c>
-      <c r="E28" s="5">
-        <v>5603.39</v>
-      </c>
-      <c r="F28" s="5">
+        <v>44</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6">
+        <v>25.04</v>
+      </c>
+      <c r="O28" s="6">
+        <v>1790.82</v>
+      </c>
+      <c r="P28" s="6">
         <v>12</v>
       </c>
-      <c r="G28" s="5">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5">
-        <v>11</v>
-      </c>
-      <c r="I28" s="5">
-        <v>4</v>
-      </c>
-      <c r="J28" s="5">
-        <v>1</v>
-      </c>
-      <c r="K28" s="5">
-        <v>466.94916666666597</v>
-      </c>
-      <c r="L28" s="5">
-        <v>1400.8475000000001</v>
-      </c>
-      <c r="M28" s="5">
-        <v>-8.6445883652574604</v>
-      </c>
-      <c r="N28" s="6">
-        <v>16.54</v>
-      </c>
-      <c r="O28" s="6">
-        <v>2577.71</v>
-      </c>
-      <c r="P28" s="6">
-        <v>14</v>
-      </c>
       <c r="Q28" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R28" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S28" s="6">
-        <v>184.12214285714199</v>
+        <v>149.23499999999899</v>
       </c>
       <c r="T28" s="6">
-        <v>429.618333333333</v>
+        <v>895.41</v>
       </c>
       <c r="U28" s="6">
-        <v>1045.83564481652</v>
+        <v>-100</v>
       </c>
       <c r="V28" s="7">
-        <v>55.58</v>
+        <v>65.91</v>
       </c>
       <c r="W28" s="7">
-        <v>8745.86</v>
+        <v>3947.31</v>
       </c>
       <c r="X28" s="7">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="Y28" s="7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Z28" s="7">
-        <v>4</v>
-      </c>
-      <c r="AA28" s="8">
-        <v>13000</v>
-      </c>
-      <c r="AB28" s="9">
-        <v>31</v>
-      </c>
-      <c r="AC28" s="9">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
       <c r="AD28" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="B29" s="5">
+        <v>21.66</v>
+      </c>
+      <c r="C29" s="5">
+        <v>8.67</v>
+      </c>
+      <c r="D29" s="5">
+        <v>12.99</v>
+      </c>
+      <c r="E29" s="5">
+        <v>6103.87</v>
+      </c>
+      <c r="F29" s="5">
+        <v>13</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5">
+        <v>12</v>
+      </c>
+      <c r="I29" s="5">
+        <v>4</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <v>469.52846153846099</v>
+      </c>
+      <c r="L29" s="5">
+        <v>1525.9675</v>
+      </c>
+      <c r="M29" s="5">
+        <v>-16.135173258932401</v>
+      </c>
       <c r="N29" s="6">
-        <v>41.51</v>
+        <v>18.54</v>
       </c>
       <c r="O29" s="6">
-        <v>2876.08</v>
+        <v>2859.78</v>
       </c>
       <c r="P29" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q29" s="6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R29" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="6">
-        <v>239.67333333333301</v>
-      </c>
-      <c r="T29" s="6"/>
+        <v>204.27</v>
+      </c>
+      <c r="T29" s="6">
+        <v>476.63</v>
+      </c>
       <c r="U29" s="6">
-        <v>-100</v>
+        <v>932.81790906992796</v>
       </c>
       <c r="V29" s="7">
-        <v>98.369999999999905</v>
+        <v>55.58</v>
       </c>
       <c r="W29" s="7">
-        <v>6238.21</v>
+        <v>8745.86</v>
       </c>
       <c r="X29" s="7">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="Y29" s="7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Z29" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="8"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
+        <v>4</v>
+      </c>
+      <c r="AA29" s="8">
+        <v>13000</v>
+      </c>
+      <c r="AB29" s="9">
+        <v>31</v>
+      </c>
+      <c r="AC29" s="9">
+        <v>10</v>
+      </c>
       <c r="AD29" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2806,248 +2785,242 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="6">
-        <v>46.28</v>
+        <v>42.52</v>
       </c>
       <c r="O30" s="6">
-        <v>3506.76</v>
+        <v>3098.57</v>
       </c>
       <c r="P30" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q30" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="6">
-        <v>438.34500000000003</v>
-      </c>
-      <c r="T30" s="6">
-        <v>1753.38</v>
-      </c>
+        <v>258.21416666666602</v>
+      </c>
+      <c r="T30" s="6"/>
       <c r="U30" s="6">
-        <v>88.008303961491507</v>
+        <v>-100</v>
       </c>
       <c r="V30" s="7">
-        <v>126.03</v>
+        <v>98.369999999999905</v>
       </c>
       <c r="W30" s="7">
-        <v>9571.31</v>
+        <v>6238.21</v>
       </c>
       <c r="X30" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y30" s="7">
         <v>2</v>
       </c>
       <c r="Z30" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="8"/>
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="5">
-        <v>43.91</v>
-      </c>
-      <c r="C31" s="5">
-        <v>23.43</v>
-      </c>
-      <c r="D31" s="5">
-        <v>20.48</v>
-      </c>
-      <c r="E31" s="5">
-        <v>11848.18</v>
-      </c>
-      <c r="F31" s="5">
-        <v>23</v>
-      </c>
-      <c r="G31" s="5">
+        <v>50</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6">
+        <v>51.12</v>
+      </c>
+      <c r="O31" s="6">
+        <v>3734.44</v>
+      </c>
+      <c r="P31" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q31" s="6">
         <v>2</v>
       </c>
-      <c r="H31" s="5">
-        <v>21</v>
-      </c>
-      <c r="I31" s="5">
-        <v>8</v>
-      </c>
-      <c r="J31" s="5">
-        <v>3</v>
-      </c>
-      <c r="K31" s="5">
-        <v>515.13826086956499</v>
-      </c>
-      <c r="L31" s="5">
-        <v>1481.0225</v>
-      </c>
-      <c r="M31" s="5">
-        <v>35.744392809697302</v>
-      </c>
-      <c r="N31" s="6">
-        <v>13.8</v>
-      </c>
-      <c r="O31" s="6">
-        <v>4952.03</v>
-      </c>
-      <c r="P31" s="6">
-        <v>20</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>4</v>
-      </c>
       <c r="R31" s="6">
         <v>1</v>
       </c>
       <c r="S31" s="6">
-        <v>247.60149999999999</v>
+        <v>466.80500000000001</v>
       </c>
       <c r="T31" s="6">
-        <v>1238.0074999999999</v>
+        <v>1867.22</v>
       </c>
       <c r="U31" s="6">
-        <v>31.461239128195899</v>
+        <v>76.545881042405199</v>
       </c>
       <c r="V31" s="7">
-        <v>22.8</v>
+        <v>126.03</v>
       </c>
       <c r="W31" s="7">
-        <v>6170.17</v>
+        <v>9571.31</v>
       </c>
       <c r="X31" s="7">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Y31" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="7">
         <v>1</v>
       </c>
-      <c r="AA31" s="8">
-        <v>28000</v>
-      </c>
-      <c r="AB31" s="9">
-        <v>42</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>21</v>
-      </c>
+      <c r="AA31" s="8"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
       <c r="AD31" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="5">
-        <v>36.81</v>
+        <v>44.91</v>
       </c>
       <c r="C32" s="5">
-        <v>11.1</v>
+        <v>23.43</v>
       </c>
       <c r="D32" s="5">
-        <v>25.71</v>
+        <v>21.48</v>
       </c>
       <c r="E32" s="5">
-        <v>12945.3</v>
+        <v>12613.99</v>
       </c>
       <c r="F32" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G32" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I32" s="5">
+        <v>11</v>
+      </c>
+      <c r="J32" s="5">
+        <v>4</v>
+      </c>
+      <c r="K32" s="5">
+        <v>525.58291666666605</v>
+      </c>
+      <c r="L32" s="5">
+        <v>1146.72636363636</v>
+      </c>
+      <c r="M32" s="5">
+        <v>36.469427992253003</v>
+      </c>
+      <c r="N32" s="6">
+        <v>17.3</v>
+      </c>
+      <c r="O32" s="6">
+        <v>5440.38</v>
+      </c>
+      <c r="P32" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>6</v>
+      </c>
+      <c r="R32" s="6">
+        <v>1</v>
+      </c>
+      <c r="S32" s="6">
+        <v>226.6825</v>
+      </c>
+      <c r="T32" s="6">
+        <v>906.73</v>
+      </c>
+      <c r="U32" s="6">
+        <v>19.660758991099801</v>
+      </c>
+      <c r="V32" s="7">
+        <v>22.8</v>
+      </c>
+      <c r="W32" s="7">
+        <v>6170.17</v>
+      </c>
+      <c r="X32" s="7">
+        <v>30</v>
+      </c>
+      <c r="Y32" s="7">
         <v>10</v>
       </c>
-      <c r="J32" s="5">
-        <v>3</v>
-      </c>
-      <c r="K32" s="5">
-        <v>681.33157894736803</v>
-      </c>
-      <c r="L32" s="5">
-        <v>1294.53</v>
-      </c>
-      <c r="M32" s="5">
-        <v>87.381675202583097</v>
-      </c>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
+      <c r="Z32" s="7">
+        <v>1</v>
+      </c>
       <c r="AA32" s="8">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="AB32" s="9">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="AC32" s="9">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="AD32" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" s="5">
-        <v>54.34</v>
+        <v>41.31</v>
       </c>
       <c r="C33" s="5">
-        <v>22.59</v>
+        <v>12.6</v>
       </c>
       <c r="D33" s="5">
-        <v>31.75</v>
+        <v>28.71</v>
       </c>
       <c r="E33" s="5">
-        <v>12729.71</v>
+        <v>13693.78</v>
       </c>
       <c r="F33" s="5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G33" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I33" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J33" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="5">
-        <v>438.95551724137903</v>
+        <v>622.44454545454505</v>
       </c>
       <c r="L33" s="5">
-        <v>1060.8091666666601</v>
+        <v>1369.3779999999999</v>
       </c>
       <c r="M33" s="5">
-        <v>-53.973814014616202</v>
+        <v>77.139694080085903</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3063,765 +3036,802 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="8">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AB33" s="9">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="AC33" s="9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AD33" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>46.32</v>
+        <v>57.34</v>
       </c>
       <c r="C34" s="5">
-        <v>35.49</v>
+        <v>23.59</v>
       </c>
       <c r="D34" s="5">
-        <v>10.83</v>
+        <v>33.75</v>
       </c>
       <c r="E34" s="5">
-        <v>12447.74</v>
+        <v>13999.34</v>
       </c>
       <c r="F34" s="5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G34" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H34" s="5">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I34" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J34" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" s="5">
-        <v>732.22</v>
+        <v>466.64466666666601</v>
       </c>
       <c r="L34" s="5">
-        <v>1778.2485714285699</v>
+        <v>999.95285714285706</v>
       </c>
       <c r="M34" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N34" s="6">
-        <v>33.369999999999997</v>
-      </c>
-      <c r="O34" s="6">
-        <v>10389.030000000001</v>
-      </c>
-      <c r="P34" s="6">
-        <v>48</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>14</v>
-      </c>
-      <c r="R34" s="6">
-        <v>3</v>
-      </c>
-      <c r="S34" s="6">
-        <v>216.43812500000001</v>
-      </c>
-      <c r="T34" s="6">
-        <v>742.07357142857097</v>
-      </c>
-      <c r="U34" s="6">
-        <v>124.44992458391199</v>
-      </c>
-      <c r="V34" s="7">
-        <v>110.24</v>
-      </c>
-      <c r="W34" s="7">
-        <v>28910.07</v>
-      </c>
-      <c r="X34" s="7">
-        <v>128</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>45</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>3</v>
-      </c>
+        <v>54.071549087314096</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
       <c r="AA34" s="8">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="AB34" s="9">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="AC34" s="9">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AD34" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="5">
+        <v>49.82</v>
+      </c>
+      <c r="C35" s="5">
+        <v>38.99</v>
+      </c>
+      <c r="D35" s="5">
+        <v>10.83</v>
+      </c>
+      <c r="E35" s="5">
+        <v>13456.23</v>
+      </c>
+      <c r="F35" s="5">
+        <v>19</v>
+      </c>
+      <c r="G35" s="5">
+        <v>7</v>
+      </c>
+      <c r="H35" s="5">
+        <v>12</v>
+      </c>
+      <c r="I35" s="5">
+        <v>9</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>708.22263157894702</v>
+      </c>
+      <c r="L35" s="5">
+        <v>1495.1366666666599</v>
+      </c>
+      <c r="M35" s="5">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="6">
+        <v>40.369999999999997</v>
+      </c>
+      <c r="O35" s="6">
+        <v>11550.53</v>
+      </c>
+      <c r="P35" s="6">
         <v>56</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="6">
-        <v>91.9</v>
-      </c>
-      <c r="O35" s="6">
-        <v>3306.32</v>
-      </c>
-      <c r="P35" s="6">
-        <v>8</v>
-      </c>
       <c r="Q35" s="6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R35" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S35" s="6">
-        <v>413.29</v>
-      </c>
-      <c r="T35" s="6"/>
+        <v>206.25946428571399</v>
+      </c>
+      <c r="T35" s="6">
+        <v>641.69611111111101</v>
+      </c>
       <c r="U35" s="6">
-        <v>-100</v>
+        <v>101.87965400721799</v>
       </c>
       <c r="V35" s="7">
-        <v>250.18</v>
+        <v>110.24</v>
       </c>
       <c r="W35" s="7">
-        <v>7865.5</v>
+        <v>28910.07</v>
       </c>
       <c r="X35" s="7">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="Y35" s="7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z35" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="AA35" s="8">
+        <v>35000</v>
+      </c>
+      <c r="AB35" s="9">
+        <v>57</v>
+      </c>
+      <c r="AC35" s="9">
+        <v>14</v>
+      </c>
       <c r="AD35" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="5">
-        <v>15.31</v>
-      </c>
-      <c r="C36" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="D36" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="E36" s="5">
-        <v>3376.33</v>
-      </c>
-      <c r="F36" s="5">
-        <v>4</v>
-      </c>
-      <c r="G36" s="5">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
-        <v>4</v>
-      </c>
-      <c r="I36" s="5">
-        <v>1</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <v>844.08249999999998</v>
-      </c>
-      <c r="L36" s="5">
-        <v>3376.33</v>
-      </c>
-      <c r="M36" s="5">
+        <v>56</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6">
+        <v>95.9</v>
+      </c>
+      <c r="O36" s="6">
+        <v>3533.3</v>
+      </c>
+      <c r="P36" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>441.66250000000002</v>
+      </c>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6">
         <v>-100</v>
       </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="8">
-        <v>7500</v>
-      </c>
-      <c r="AB36" s="9">
-        <v>16</v>
-      </c>
-      <c r="AC36" s="9">
-        <v>7</v>
-      </c>
+      <c r="V36" s="7">
+        <v>250.18</v>
+      </c>
+      <c r="W36" s="7">
+        <v>7865.5</v>
+      </c>
+      <c r="X36" s="7">
+        <v>18</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
       <c r="AD36" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="5">
-        <v>31.74</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="C37" s="5">
-        <v>22.49</v>
+        <v>8.32</v>
       </c>
       <c r="D37" s="5">
-        <v>9.25</v>
+        <v>8.99</v>
       </c>
       <c r="E37" s="5">
-        <v>7850.61</v>
+        <v>3631.97</v>
       </c>
       <c r="F37" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J37" s="5">
         <v>0</v>
       </c>
       <c r="K37" s="5">
-        <v>1308.4349999999999</v>
+        <v>726.39400000000001</v>
       </c>
       <c r="L37" s="5">
-        <v>1962.6524999999999</v>
+        <v>3631.97</v>
       </c>
       <c r="M37" s="5">
         <v>-100</v>
       </c>
-      <c r="N37" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="O37" s="6">
-        <v>4589.93</v>
-      </c>
-      <c r="P37" s="6">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>12</v>
-      </c>
-      <c r="R37" s="6">
-        <v>4</v>
-      </c>
-      <c r="S37" s="6">
-        <v>176.53576923076901</v>
-      </c>
-      <c r="T37" s="6">
-        <v>382.49416666666599</v>
-      </c>
-      <c r="U37" s="6">
-        <v>403.10484037882901</v>
-      </c>
-      <c r="V37" s="7">
-        <v>42.5</v>
-      </c>
-      <c r="W37" s="7">
-        <v>12015.14</v>
-      </c>
-      <c r="X37" s="7">
-        <v>56</v>
-      </c>
-      <c r="Y37" s="7">
-        <v>24</v>
-      </c>
-      <c r="Z37" s="7">
-        <v>4</v>
-      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
       <c r="AA37" s="8">
-        <v>17000</v>
+        <v>7500</v>
       </c>
       <c r="AB37" s="9">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AC37" s="9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD37" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="B38" s="5">
+        <v>33.739999999999903</v>
+      </c>
+      <c r="C38" s="5">
+        <v>24.49</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.25</v>
+      </c>
+      <c r="E38" s="5">
+        <v>8400.9599999999991</v>
+      </c>
+      <c r="F38" s="5">
+        <v>8</v>
+      </c>
+      <c r="G38" s="5">
+        <v>4</v>
+      </c>
+      <c r="H38" s="5">
+        <v>4</v>
+      </c>
+      <c r="I38" s="5">
+        <v>4</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>1050.1199999999999</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2100.2399999999998</v>
+      </c>
+      <c r="M38" s="5">
+        <v>-100</v>
+      </c>
       <c r="N38" s="6">
-        <v>38.340000000000003</v>
+        <v>16.5</v>
       </c>
       <c r="O38" s="6">
-        <v>2486.69</v>
+        <v>4883.51</v>
       </c>
       <c r="P38" s="6">
+        <v>27</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>14</v>
+      </c>
+      <c r="R38" s="6">
         <v>4</v>
       </c>
-      <c r="Q38" s="6">
-        <v>1</v>
-      </c>
-      <c r="R38" s="6">
-        <v>0</v>
-      </c>
       <c r="S38" s="6">
-        <v>621.67250000000001</v>
+        <v>180.87074074073999</v>
       </c>
       <c r="T38" s="6">
-        <v>2486.69</v>
+        <v>348.82214285714201</v>
       </c>
       <c r="U38" s="6">
-        <v>-100</v>
+        <v>372.85988971047402</v>
       </c>
       <c r="V38" s="7">
-        <v>97.34</v>
+        <v>42.5</v>
       </c>
       <c r="W38" s="7">
-        <v>5964.35</v>
+        <v>12015.14</v>
       </c>
       <c r="X38" s="7">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="Y38" s="7">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Z38" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="8"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
+        <v>4</v>
+      </c>
+      <c r="AA38" s="8">
+        <v>17000</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>27</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>16</v>
+      </c>
       <c r="AD38" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="5">
-        <v>13.17</v>
-      </c>
-      <c r="C39" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="D39" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="E39" s="5">
-        <v>7507.61</v>
-      </c>
-      <c r="F39" s="5">
+        <v>59</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6">
+        <v>44.34</v>
+      </c>
+      <c r="O39" s="6">
+        <v>2747.07</v>
+      </c>
+      <c r="P39" s="6">
         <v>4</v>
       </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5">
-        <v>4</v>
-      </c>
-      <c r="I39" s="5">
-        <v>2</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5">
-        <v>1876.9024999999999</v>
-      </c>
-      <c r="L39" s="5">
-        <v>3753.8049999999998</v>
-      </c>
-      <c r="M39" s="5">
+      <c r="Q39" s="6">
+        <v>1</v>
+      </c>
+      <c r="R39" s="6">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6">
+        <v>686.76750000000004</v>
+      </c>
+      <c r="T39" s="6">
+        <v>2747.07</v>
+      </c>
+      <c r="U39" s="6">
         <v>-100</v>
       </c>
-      <c r="N39" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="O39" s="6">
-        <v>519.54</v>
-      </c>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
       <c r="V39" s="7">
-        <v>3.01</v>
+        <v>97.34</v>
       </c>
       <c r="W39" s="7">
-        <v>1758.25</v>
-      </c>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="8">
-        <v>17000</v>
-      </c>
+        <v>5964.35</v>
+      </c>
+      <c r="X39" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y39" s="7">
+        <v>3</v>
+      </c>
+      <c r="Z39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8"/>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B40" s="5">
-        <v>27.72</v>
+        <v>14.17</v>
       </c>
       <c r="C40" s="5">
-        <v>11.72</v>
+        <v>6.67</v>
       </c>
       <c r="D40" s="5">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="E40" s="5">
-        <v>8597.1299999999992</v>
+        <v>8131.41</v>
       </c>
       <c r="F40" s="5">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G40" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I40" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" s="5">
-        <v>409.38714285714201</v>
+        <v>1626.2819999999999</v>
       </c>
       <c r="L40" s="5">
-        <v>614.08071428571395</v>
+        <v>2710.47</v>
       </c>
       <c r="M40" s="5">
-        <v>180.90537190899701</v>
+        <v>-0.18951202804925399</v>
       </c>
       <c r="N40" s="6">
-        <v>19.16</v>
+        <v>0.98</v>
       </c>
       <c r="O40" s="6">
-        <v>4060.99</v>
-      </c>
-      <c r="P40" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>3</v>
-      </c>
-      <c r="R40" s="6">
-        <v>1</v>
-      </c>
-      <c r="S40" s="6">
-        <v>193.380476190476</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1353.66333333333</v>
-      </c>
-      <c r="U40" s="6">
-        <v>28.165299594433801</v>
-      </c>
+        <v>613.39</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
       <c r="V40" s="7">
-        <v>52.03</v>
+        <v>3.01</v>
       </c>
       <c r="W40" s="7">
-        <v>10931.15</v>
-      </c>
-      <c r="X40" s="7">
-        <v>47</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>13</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>1</v>
-      </c>
+        <v>1758.25</v>
+      </c>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
       <c r="AA40" s="8">
-        <v>24000</v>
-      </c>
-      <c r="AB40" s="9">
-        <v>29</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>12</v>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
       <c r="AD40" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="B41">
+        <v>31.72</v>
+      </c>
+      <c r="C41">
+        <v>12.72</v>
+      </c>
+      <c r="D41">
+        <v>19</v>
+      </c>
+      <c r="E41">
+        <v>9447.9699999999993</v>
+      </c>
+      <c r="F41">
+        <v>23</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>19</v>
+      </c>
+      <c r="I41">
+        <v>15</v>
+      </c>
+      <c r="J41">
+        <v>3</v>
+      </c>
+      <c r="K41">
+        <v>410.78130434782599</v>
+      </c>
+      <c r="L41">
+        <v>629.86466666666604</v>
+      </c>
+      <c r="M41">
+        <v>155.60834761329599</v>
       </c>
       <c r="N41">
-        <v>50.72</v>
+        <v>20.02</v>
       </c>
       <c r="O41">
-        <v>3627.23</v>
+        <v>4516.53</v>
       </c>
       <c r="P41">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41">
         <v>1</v>
       </c>
       <c r="S41">
-        <v>329.74818181818102</v>
+        <v>205.296818181818</v>
       </c>
       <c r="T41">
-        <v>3627.23</v>
+        <v>1505.51</v>
       </c>
       <c r="U41">
-        <v>56.593323279747899</v>
+        <v>15.2384684702636</v>
       </c>
       <c r="V41">
-        <v>127.59</v>
+        <v>52.03</v>
       </c>
       <c r="W41">
-        <v>8783.7999999999993</v>
+        <v>10931.15</v>
       </c>
       <c r="X41">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="Y41">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Z41">
         <v>1</v>
       </c>
+      <c r="AA41">
+        <v>24000</v>
+      </c>
+      <c r="AB41">
+        <v>29</v>
+      </c>
+      <c r="AC41">
+        <v>12</v>
+      </c>
       <c r="AD41" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42">
-        <v>20.66</v>
-      </c>
-      <c r="C42">
-        <v>11.99</v>
-      </c>
-      <c r="D42">
-        <v>8.67</v>
-      </c>
-      <c r="E42">
-        <v>4917.6400000000003</v>
-      </c>
-      <c r="F42">
-        <v>6</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>5</v>
-      </c>
-      <c r="I42">
-        <v>3</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>819.606666666666</v>
-      </c>
-      <c r="L42">
-        <v>1639.21333333333</v>
-      </c>
-      <c r="M42">
-        <v>-100</v>
+        <v>61</v>
       </c>
       <c r="N42">
-        <v>9.07</v>
+        <v>58.69</v>
       </c>
       <c r="O42">
-        <v>1920.3</v>
+        <v>3951.9</v>
       </c>
       <c r="P42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42">
-        <v>160.02500000000001</v>
+        <v>303.99230769230701</v>
       </c>
       <c r="T42">
-        <v>384.06</v>
+        <v>3951.9</v>
       </c>
       <c r="U42">
-        <v>-100</v>
+        <v>43.728333206811897</v>
       </c>
       <c r="V42">
-        <v>23.02</v>
+        <v>127.59</v>
       </c>
       <c r="W42">
-        <v>4636.55</v>
+        <v>8783.7999999999993</v>
       </c>
       <c r="X42">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>11000</v>
-      </c>
-      <c r="AB42">
-        <v>14</v>
-      </c>
-      <c r="AC42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="B43">
+        <v>21.66</v>
+      </c>
+      <c r="C43">
+        <v>12.99</v>
+      </c>
+      <c r="D43">
+        <v>8.67</v>
+      </c>
+      <c r="E43">
+        <v>5336.16</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>889.36</v>
+      </c>
+      <c r="L43">
+        <v>1778.72</v>
+      </c>
+      <c r="M43">
+        <v>11.203562112080601</v>
       </c>
       <c r="N43">
-        <v>25.69</v>
+        <v>10.07</v>
       </c>
       <c r="O43">
-        <v>2108.98</v>
+        <v>2115.2399999999998</v>
       </c>
       <c r="P43">
+        <v>13</v>
+      </c>
+      <c r="Q43">
         <v>5</v>
       </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
       <c r="R43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43">
-        <v>421.79599999999999</v>
+        <v>162.71076923076899</v>
       </c>
       <c r="T43">
-        <v>2108.98</v>
+        <v>423.04799999999898</v>
       </c>
       <c r="U43">
-        <v>-100</v>
+        <v>258.91908246818298</v>
       </c>
       <c r="V43">
-        <v>56.01</v>
+        <v>23.02</v>
       </c>
       <c r="W43">
-        <v>4863.79</v>
+        <v>4636.55</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Y43">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA43">
+        <v>11000</v>
+      </c>
+      <c r="AB43">
+        <v>14</v>
+      </c>
+      <c r="AC43">
+        <v>6</v>
       </c>
       <c r="AD43" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>137</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>2</v>
-      </c>
-      <c r="AC44">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="N44">
+        <v>26.69</v>
+      </c>
+      <c r="O44">
+        <v>2258.2600000000002</v>
+      </c>
+      <c r="P44">
+        <v>5</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>451.65199999999999</v>
+      </c>
+      <c r="T44">
+        <v>2258.2600000000002</v>
+      </c>
+      <c r="U44">
+        <v>-100</v>
+      </c>
+      <c r="V44">
+        <v>56.01</v>
+      </c>
+      <c r="W44">
+        <v>4863.79</v>
+      </c>
+      <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>4</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
       </c>
       <c r="AD44" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.3">
@@ -3841,7 +3851,7 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45">
         <v>2</v>
@@ -3850,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="AD45" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
@@ -3894,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.3">
@@ -3986,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="AD47" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.3">
@@ -4033,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.3">
@@ -4062,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="AD49" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
   </sheetData>
@@ -4949,16 +4959,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="10">
         <v>19</v>
       </c>
       <c r="G21" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
@@ -4973,19 +4983,19 @@
         <v>23255</v>
       </c>
       <c r="L21" s="10">
-        <v>12.04</v>
+        <v>11.4</v>
       </c>
       <c r="M21" s="10">
-        <v>14.11</v>
+        <v>10.78</v>
       </c>
       <c r="N21" s="10">
-        <v>48.72</v>
+        <v>47.5</v>
       </c>
       <c r="O21" s="10">
         <v>15.79</v>
       </c>
       <c r="P21" s="10">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -4999,10 +5009,10 @@
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
@@ -5023,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -5047,43 +5057,43 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
+        <v>41</v>
+      </c>
+      <c r="E23" s="10">
         <v>38</v>
       </c>
-      <c r="E23" s="10">
-        <v>35</v>
-      </c>
       <c r="F23" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G23" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="10">
-        <v>20460</v>
+        <v>28254</v>
       </c>
       <c r="J23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="10">
-        <v>20460</v>
+        <v>28254</v>
       </c>
       <c r="L23" s="10">
-        <v>11.73</v>
+        <v>11.68</v>
       </c>
       <c r="M23" s="10">
-        <v>12.42</v>
+        <v>13.1</v>
       </c>
       <c r="N23" s="10">
-        <v>50</v>
+        <v>51.22</v>
       </c>
       <c r="O23" s="10">
-        <v>15.79</v>
+        <v>19.05</v>
       </c>
       <c r="P23" s="10">
-        <v>7.89</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -5097,22 +5107,22 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
+        <v>6</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10">
+        <v>5</v>
+      </c>
+      <c r="H24" s="10">
         <v>4</v>
       </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10">
-        <v>4</v>
-      </c>
-      <c r="H24" s="10">
-        <v>2</v>
-      </c>
       <c r="I24" s="10">
-        <v>5975</v>
+        <v>9997.44</v>
       </c>
       <c r="J24" s="10">
         <v>0</v>
@@ -5121,17 +5131,17 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="M24" s="10">
-        <v>3.63</v>
+        <v>4.63</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10">
-        <v>50</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -5169,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1.23</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -5219,10 +5229,10 @@
         <v>7263</v>
       </c>
       <c r="L26" s="10">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="M26" s="10">
-        <v>4.41</v>
+        <v>3.37</v>
       </c>
       <c r="N26" s="10">
         <v>42.86</v>
@@ -5245,13 +5255,13 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" s="10">
         <v>8</v>
@@ -5269,19 +5279,19 @@
         <v>18698</v>
       </c>
       <c r="L27" s="10">
-        <v>8.33</v>
+        <v>7.98</v>
       </c>
       <c r="M27" s="10">
-        <v>11.35</v>
+        <v>8.67</v>
       </c>
       <c r="N27" s="10">
-        <v>70.37</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="O27" s="10">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="P27" s="10">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -5295,16 +5305,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>14</v>
+      </c>
+      <c r="E28" s="10">
         <v>13</v>
-      </c>
-      <c r="E28" s="10">
-        <v>12</v>
       </c>
       <c r="F28" s="10">
         <v>6</v>
       </c>
       <c r="G28" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -5319,13 +5329,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -5345,16 +5355,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
+        <v>48</v>
+      </c>
+      <c r="E29" s="10">
         <v>43</v>
       </c>
-      <c r="E29" s="10">
-        <v>38</v>
-      </c>
       <c r="F29" s="10">
         <v>1</v>
       </c>
       <c r="G29" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -5369,19 +5379,19 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>13.27</v>
+        <v>13.68</v>
       </c>
       <c r="M29" s="10">
-        <v>4.5999999999999996</v>
+        <v>3.51</v>
       </c>
       <c r="N29" s="10">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="O29" s="10">
         <v>100</v>
       </c>
       <c r="P29" s="10">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
@@ -5395,43 +5405,43 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" s="10">
+        <v>5</v>
+      </c>
+      <c r="H30" s="10">
         <v>4</v>
       </c>
-      <c r="H30" s="10">
-        <v>2</v>
-      </c>
       <c r="I30" s="10">
-        <v>15860</v>
+        <v>25235</v>
       </c>
       <c r="J30" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30" s="10">
-        <v>15860</v>
+        <v>25235</v>
       </c>
       <c r="L30" s="10">
-        <v>11.42</v>
+        <v>10.83</v>
       </c>
       <c r="M30" s="10">
-        <v>9.6300000000000008</v>
+        <v>11.7</v>
       </c>
       <c r="N30" s="10">
-        <v>43.24</v>
+        <v>44.74</v>
       </c>
       <c r="O30" s="10">
-        <v>12.5</v>
+        <v>23.53</v>
       </c>
       <c r="P30" s="10">
-        <v>5.41</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -5445,16 +5455,16 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E31" s="10">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F31" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G31" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H31" s="10">
         <v>3</v>
@@ -5469,19 +5479,19 @@
         <v>21270.240000000002</v>
       </c>
       <c r="L31" s="10">
-        <v>13.27</v>
+        <v>13.39</v>
       </c>
       <c r="M31" s="10">
-        <v>12.91</v>
+        <v>9.86</v>
       </c>
       <c r="N31" s="10">
-        <v>37.21</v>
+        <v>42.55</v>
       </c>
       <c r="O31" s="10">
-        <v>18.75</v>
+        <v>15</v>
       </c>
       <c r="P31" s="10">
-        <v>6.98</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -5504,34 +5514,34 @@
         <v>10</v>
       </c>
       <c r="G32" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="10">
-        <v>5859</v>
+        <v>21569</v>
       </c>
       <c r="J32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32" s="10">
-        <v>5859</v>
+        <v>21569</v>
       </c>
       <c r="L32" s="10">
-        <v>4.63</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="M32" s="10">
-        <v>3.56</v>
+        <v>10</v>
       </c>
       <c r="N32" s="10">
         <v>66.67</v>
       </c>
       <c r="O32" s="10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P32" s="10">
-        <v>13.33</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5545,43 +5555,43 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="10">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="J33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="10">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="L33" s="10">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="M33" s="10">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N33" s="10">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="O33" s="10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P33" s="10">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -5595,16 +5605,16 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E34" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F34" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G34" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="10">
         <v>3</v>
@@ -5619,19 +5629,19 @@
         <v>24149.8</v>
       </c>
       <c r="L34" s="10">
-        <v>6.17</v>
+        <v>7.12</v>
       </c>
       <c r="M34" s="10">
-        <v>14.66</v>
+        <v>11.2</v>
       </c>
       <c r="N34" s="10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O34" s="10">
-        <v>23.08</v>
+        <v>20</v>
       </c>
       <c r="P34" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5645,43 +5655,43 @@
         <v>18</v>
       </c>
       <c r="D35" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F35" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G35" s="10">
         <v>3</v>
       </c>
       <c r="H35" s="10">
+        <v>3</v>
+      </c>
+      <c r="I35" s="10">
+        <v>20327.12</v>
+      </c>
+      <c r="J35" s="10">
         <v>2</v>
       </c>
-      <c r="I35" s="10">
-        <v>14393.12</v>
-      </c>
-      <c r="J35" s="10">
-        <v>1</v>
-      </c>
       <c r="K35" s="10">
-        <v>7483.12</v>
+        <v>13417.12</v>
       </c>
       <c r="L35" s="10">
-        <v>4.32</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="M35" s="10">
-        <v>8.74</v>
+        <v>9.42</v>
       </c>
       <c r="N35" s="10">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="O35" s="10">
-        <v>28.57</v>
+        <v>30</v>
       </c>
       <c r="P35" s="10">
-        <v>14.29</v>
+        <v>18.75</v>
       </c>
     </row>
   </sheetData>
@@ -6044,10 +6054,10 @@
         <v>378.9</v>
       </c>
       <c r="G13" s="5">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H13" s="5">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I13" s="5">
         <v>63</v>
@@ -6149,19 +6159,19 @@
         <v>481.96</v>
       </c>
       <c r="G16" s="5">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H16" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I16" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J16" s="5">
-        <v>511623.25</v>
+        <v>504461.62</v>
       </c>
       <c r="K16" s="5">
-        <v>32.840000000000003</v>
+        <v>32.369999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6190,13 +6200,13 @@
         <v>94</v>
       </c>
       <c r="I17" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J17" s="5">
-        <v>249351.65</v>
+        <v>251475.65</v>
       </c>
       <c r="K17" s="5">
-        <v>18.690000000000001</v>
+        <v>18.850000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6257,16 +6267,16 @@
         <v>250</v>
       </c>
       <c r="H19" s="5">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I19" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J19" s="5">
-        <v>389846.09</v>
+        <v>382052.09</v>
       </c>
       <c r="K19" s="5">
-        <v>38.31</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -6289,19 +6299,19 @@
         <v>293.32</v>
       </c>
       <c r="G20" s="10">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" s="10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I20" s="10">
         <v>30</v>
       </c>
       <c r="J20" s="10">
-        <v>240308.52</v>
+        <v>240866.52</v>
       </c>
       <c r="K20" s="10">
-        <v>26.36</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -6315,28 +6325,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1885</v>
+        <v>2056</v>
       </c>
       <c r="E21" s="10">
-        <v>5645.96</v>
+        <v>6138.3</v>
       </c>
       <c r="F21" s="10">
-        <v>153.94</v>
+        <v>167.94</v>
       </c>
       <c r="G21" s="10">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H21" s="10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I21" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="10">
-        <v>24106</v>
+        <v>27978.44</v>
       </c>
       <c r="K21" s="10">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -6910,10 +6920,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="E38" s="10">
-        <v>4442.26</v>
+        <v>4840.0600000000004</v>
       </c>
       <c r="F38" s="10">
         <v>13.35</v>
@@ -6957,7 +6967,7 @@
         <v>26</v>
       </c>
       <c r="H39" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="10">
         <v>4</v>
@@ -7444,7 +7454,7 @@
         <v>141.16999999999999</v>
       </c>
       <c r="G53" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H53" s="10">
         <v>36</v>
@@ -7505,19 +7515,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>1439</v>
+        <v>1568</v>
       </c>
       <c r="E55" s="10">
-        <v>17674.21</v>
+        <v>19034.95</v>
       </c>
       <c r="F55" s="10">
-        <v>59.66</v>
+        <v>62.66</v>
       </c>
       <c r="G55" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
@@ -7526,7 +7536,7 @@
         <v>14289</v>
       </c>
       <c r="K55" s="10">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -8265,16 +8275,16 @@
         <v>18</v>
       </c>
       <c r="D77" s="10">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E77" s="10">
-        <v>2553.41</v>
+        <v>2699.25</v>
       </c>
       <c r="F77" s="10">
-        <v>6.33</v>
+        <v>7.33</v>
       </c>
       <c r="G77" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -9020,28 +9030,28 @@
         <v>18</v>
       </c>
       <c r="D100" s="10">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="E100" s="10">
-        <v>7507.61</v>
+        <v>8131.41</v>
       </c>
       <c r="F100" s="10">
-        <v>13.17</v>
+        <v>14.17</v>
       </c>
       <c r="G100" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H100" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I100" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="10">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K100" s="10">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
@@ -9944,10 +9954,10 @@
         <v>104.45</v>
       </c>
       <c r="G127" s="10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H127" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I127" s="10">
         <v>13</v>
@@ -10145,19 +10155,19 @@
         <v>18</v>
       </c>
       <c r="D133" s="10">
-        <v>243</v>
+        <v>350</v>
       </c>
       <c r="E133" s="10">
-        <v>2492.39</v>
+        <v>4332.3500000000004</v>
       </c>
       <c r="F133" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G133" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H133" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I133" s="10">
         <v>1</v>
@@ -10166,7 +10176,7 @@
         <v>7647</v>
       </c>
       <c r="K133" s="10">
-        <v>2.0699999999999998</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -11980,13 +11990,13 @@
         <v>18</v>
       </c>
       <c r="D187" s="10">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="E187" s="10">
-        <v>5519.75</v>
+        <v>5552.92</v>
       </c>
       <c r="F187" s="10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G187" s="10">
         <v>25</v>
@@ -12001,7 +12011,7 @@
         <v>7263</v>
       </c>
       <c r="K187" s="10">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
@@ -12125,19 +12135,19 @@
         <v>18</v>
       </c>
       <c r="D192" s="10">
-        <v>31731</v>
+        <v>31878</v>
       </c>
       <c r="E192" s="10">
-        <v>16668.36</v>
+        <v>17220.240000000002</v>
       </c>
       <c r="F192" s="10">
-        <v>70.11</v>
+        <v>71.11</v>
       </c>
       <c r="G192" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H192" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I192" s="10">
         <v>1</v>
@@ -12146,7 +12156,7 @@
         <v>7694</v>
       </c>
       <c r="K192" s="10">
-        <v>-0.54</v>
+        <v>-0.55000000000000004</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
@@ -12710,13 +12720,13 @@
         <v>18</v>
       </c>
       <c r="D209" s="10">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E209" s="10">
-        <v>3022.33</v>
+        <v>3306.81</v>
       </c>
       <c r="F209" s="10">
-        <v>10.67</v>
+        <v>11.67</v>
       </c>
       <c r="G209" s="10">
         <v>8</v>
@@ -13305,10 +13315,10 @@
         <v>18</v>
       </c>
       <c r="D226" s="10">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E226" s="10">
-        <v>2943.88</v>
+        <v>3158.48</v>
       </c>
       <c r="F226" s="10">
         <v>7.46</v>
@@ -13769,10 +13779,10 @@
         <v>31.97</v>
       </c>
       <c r="G239" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H239" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I239" s="10">
         <v>4</v>
@@ -13900,13 +13910,13 @@
         <v>18</v>
       </c>
       <c r="D243" s="10">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="E243" s="10">
-        <v>5279.13</v>
+        <v>5693.2</v>
       </c>
       <c r="F243" s="10">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="G243" s="10">
         <v>1</v>
@@ -13921,7 +13931,7 @@
         <v>8116</v>
       </c>
       <c r="K243" s="10">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
@@ -14650,13 +14660,13 @@
         <v>15</v>
       </c>
       <c r="I264" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J264" s="10">
-        <v>27768.2399999999</v>
+        <v>35884.239999999998</v>
       </c>
       <c r="K264" s="10">
-        <v>0.5</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
@@ -14705,16 +14715,16 @@
         <v>18</v>
       </c>
       <c r="D266" s="10">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="E266" s="10">
-        <v>5603.39</v>
+        <v>6103.87</v>
       </c>
       <c r="F266" s="10">
-        <v>17.66</v>
+        <v>21.66</v>
       </c>
       <c r="G266" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H266" s="10">
         <v>3</v>
@@ -14726,7 +14736,7 @@
         <v>5119</v>
       </c>
       <c r="K266" s="10">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
@@ -15744,19 +15754,19 @@
         <v>104.01</v>
       </c>
       <c r="G298" s="10">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H298" s="10">
         <v>30</v>
       </c>
       <c r="I298" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J298" s="10">
-        <v>61881.13</v>
+        <v>55483.13</v>
       </c>
       <c r="K298" s="10">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
@@ -15954,10 +15964,10 @@
         <v>110.06</v>
       </c>
       <c r="G304" s="10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H304" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I304" s="10">
         <v>6</v>
@@ -15980,28 +15990,28 @@
         <v>18</v>
       </c>
       <c r="D305" s="10">
-        <v>954</v>
+        <v>1004</v>
       </c>
       <c r="E305" s="10">
-        <v>11848.18</v>
+        <v>12613.99</v>
       </c>
       <c r="F305" s="10">
-        <v>43.91</v>
+        <v>44.91</v>
       </c>
       <c r="G305" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H305" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I305" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J305" s="10">
-        <v>15798.24</v>
+        <v>16929.2399999999</v>
       </c>
       <c r="K305" s="10">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
@@ -16224,10 +16234,10 @@
         <v>110.71</v>
       </c>
       <c r="G312" s="10">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H312" s="10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I312" s="10">
         <v>10</v>
@@ -16250,16 +16260,16 @@
         <v>18</v>
       </c>
       <c r="D313" s="10">
-        <v>2085</v>
+        <v>2234</v>
       </c>
       <c r="E313" s="10">
-        <v>12945.3</v>
+        <v>13693.78</v>
       </c>
       <c r="F313" s="10">
-        <v>36.81</v>
+        <v>41.31</v>
       </c>
       <c r="G313" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H313" s="10">
         <v>10</v>
@@ -16271,7 +16281,7 @@
         <v>24257.119999999999</v>
       </c>
       <c r="K313" s="10">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -16364,19 +16374,19 @@
         <v>119.16</v>
       </c>
       <c r="G316" s="10">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H316" s="10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I316" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J316" s="10">
-        <v>57233.21</v>
+        <v>64394.84</v>
       </c>
       <c r="K316" s="10">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
@@ -16530,28 +16540,28 @@
         <v>18</v>
       </c>
       <c r="D321" s="10">
-        <v>3189</v>
+        <v>3491</v>
       </c>
       <c r="E321" s="10">
-        <v>12729.71</v>
+        <v>13999.34</v>
       </c>
       <c r="F321" s="10">
-        <v>54.34</v>
+        <v>57.34</v>
       </c>
       <c r="G321" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H321" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I321" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J321" s="10">
-        <v>5859</v>
+        <v>21569</v>
       </c>
       <c r="K321" s="10">
-        <v>-0.54</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
@@ -17124,7 +17134,7 @@
         <v>171.77</v>
       </c>
       <c r="G338" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H338" s="10">
         <v>14</v>
@@ -17150,19 +17160,19 @@
         <v>18</v>
       </c>
       <c r="D339" s="10">
-        <v>1057</v>
+        <v>1130</v>
       </c>
       <c r="E339" s="10">
-        <v>12447.74</v>
+        <v>13456.23</v>
       </c>
       <c r="F339" s="10">
-        <v>46.32</v>
+        <v>49.82</v>
       </c>
       <c r="G339" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H339" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I339" s="10">
         <v>0</v>
@@ -17407,7 +17417,7 @@
         <v>51</v>
       </c>
       <c r="H346" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I346" s="10">
         <v>4</v>
@@ -17505,13 +17515,13 @@
         <v>9</v>
       </c>
       <c r="I349" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J349" s="10">
-        <v>35885.199999999997</v>
+        <v>27569.200000000001</v>
       </c>
       <c r="K349" s="10">
-        <v>6.07</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
@@ -17604,10 +17614,10 @@
         <v>51.39</v>
       </c>
       <c r="G352" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H352" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I352" s="10">
         <v>2</v>
@@ -17630,16 +17640,16 @@
         <v>18</v>
       </c>
       <c r="D353" s="10">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E353" s="10">
-        <v>3376.33</v>
+        <v>3631.97</v>
       </c>
       <c r="F353" s="10">
-        <v>15.31</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="G353" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H353" s="10">
         <v>1</v>
@@ -18167,16 +18177,16 @@
         <v>26</v>
       </c>
       <c r="H368" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I368" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J368" s="10">
-        <v>44060.479999999901</v>
+        <v>51854.48</v>
       </c>
       <c r="K368" s="10">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
@@ -18225,16 +18235,16 @@
         <v>18</v>
       </c>
       <c r="D370" s="10">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="E370" s="10">
-        <v>7850.61</v>
+        <v>8400.9599999999991</v>
       </c>
       <c r="F370" s="10">
-        <v>31.74</v>
+        <v>33.739999999999903</v>
       </c>
       <c r="G370" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H370" s="10">
         <v>4</v>
@@ -19065,19 +19075,19 @@
         <v>18</v>
       </c>
       <c r="D394" s="10">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="E394" s="10">
-        <v>8597.1299999999992</v>
+        <v>9447.9699999999993</v>
       </c>
       <c r="F394" s="10">
-        <v>27.72</v>
+        <v>31.72</v>
       </c>
       <c r="G394" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H394" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I394" s="10">
         <v>3</v>
@@ -19086,7 +19096,7 @@
         <v>24149.8</v>
       </c>
       <c r="K394" s="10">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
@@ -20032,7 +20042,7 @@
         <v>14</v>
       </c>
       <c r="H423" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I423" s="10">
         <v>2</v>
@@ -20055,13 +20065,13 @@
         <v>18</v>
       </c>
       <c r="D424" s="10">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="E424" s="10">
-        <v>4917.6400000000003</v>
+        <v>5336.16</v>
       </c>
       <c r="F424" s="10">
-        <v>20.66</v>
+        <v>21.66</v>
       </c>
       <c r="G424" s="10">
         <v>6</v>
@@ -20070,13 +20080,13 @@
         <v>3</v>
       </c>
       <c r="I424" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J424" s="10">
-        <v>0</v>
+        <v>5934</v>
       </c>
       <c r="K424" s="10">
-        <v>-1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
@@ -20321,7 +20331,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L207"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -24914,16 +24924,16 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F124">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G124">
         <v>9</v>
       </c>
       <c r="H124">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I124">
         <v>2</v>
@@ -25104,10 +25114,10 @@
         <v>29</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25192,16 +25202,16 @@
         <v>2</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>7794.0000000000009</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>7794.0000000000009</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -25218,13 +25228,13 @@
         <v>33</v>
       </c>
       <c r="E132">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132">
         <v>2</v>
@@ -25303,7 +25313,7 @@
         <v>4</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134">
         <v>1</v>
@@ -25370,13 +25380,13 @@
         <v>53</v>
       </c>
       <c r="E136">
+        <v>11</v>
+      </c>
+      <c r="F136">
         <v>10</v>
       </c>
-      <c r="F136">
-        <v>9</v>
-      </c>
       <c r="G136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H136">
         <v>4</v>
@@ -25446,7 +25456,7 @@
         <v>13</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -25458,10 +25468,10 @@
         <v>3</v>
       </c>
       <c r="I138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J138">
-        <v>5690</v>
+        <v>9712.44</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -25510,7 +25520,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B140" s="18">
         <v>2026</v>
@@ -25519,19 +25529,19 @@
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>1</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140">
         <v>0</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -25557,7 +25567,7 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -25566,10 +25576,10 @@
         <v>1</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -25595,13 +25605,13 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -25624,7 +25634,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B143" s="18">
         <v>2026</v>
@@ -25633,13 +25643,13 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -25671,31 +25681,31 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E144">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144">
-        <v>7263</v>
+        <v>0</v>
       </c>
       <c r="K144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144">
-        <v>7263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -25709,31 +25719,31 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F145">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145">
-        <v>0</v>
+        <v>7263</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145">
-        <v>0</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -25747,19 +25757,19 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F146">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G146">
         <v>1</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -25785,19 +25795,19 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -25814,7 +25824,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B148" s="18">
         <v>2026</v>
@@ -25823,31 +25833,31 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E148">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F148">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G148">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148">
-        <v>2124</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148">
-        <v>2124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -25861,31 +25871,31 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E149">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G149">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H149">
         <v>2</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -25899,31 +25909,31 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150">
-        <v>8116</v>
+        <v>0</v>
       </c>
       <c r="K150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150">
-        <v>8116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -25937,7 +25947,7 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -25946,22 +25956,22 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>8116</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151">
-        <v>0</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -25975,31 +25985,31 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E152">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F152">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152">
-        <v>8458</v>
+        <v>0</v>
       </c>
       <c r="K152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152">
-        <v>8458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -26013,31 +26023,31 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E153">
+        <v>6</v>
+      </c>
+      <c r="F153">
+        <v>6</v>
+      </c>
+      <c r="G153">
+        <v>4</v>
+      </c>
+      <c r="H153">
         <v>2</v>
       </c>
-      <c r="F153">
-        <v>2</v>
-      </c>
-      <c r="G153">
-        <v>1</v>
-      </c>
-      <c r="H153">
-        <v>1</v>
-      </c>
       <c r="I153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153">
-        <v>0</v>
+        <v>8458</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153">
-        <v>0</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -26051,19 +26061,19 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E154">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G154">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -26080,7 +26090,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B155" s="18">
         <v>2026</v>
@@ -26089,19 +26099,19 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -26127,19 +26137,19 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -26165,19 +26175,19 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E157">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F157">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -26203,19 +26213,19 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -26232,7 +26242,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B159" s="18">
         <v>2026</v>
@@ -26241,25 +26251,25 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E159">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F159">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159">
-        <v>7572</v>
+        <v>0</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -26279,25 +26289,25 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160">
+        <v>30</v>
+      </c>
+      <c r="F160">
         <v>27</v>
       </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160">
-        <v>0</v>
+        <v>7572</v>
       </c>
       <c r="K160">
         <v>0</v>
@@ -26317,7 +26327,7 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -26329,7 +26339,7 @@
         <v>0</v>
       </c>
       <c r="H161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -26355,7 +26365,7 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -26367,7 +26377,7 @@
         <v>0</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -26393,19 +26403,19 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F163">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G163">
         <v>0</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -26431,7 +26441,7 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E164">
         <v>3</v>
@@ -26469,19 +26479,19 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E165">
+        <v>3</v>
+      </c>
+      <c r="F165">
+        <v>3</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
         <v>2</v>
-      </c>
-      <c r="F165">
-        <v>0</v>
-      </c>
-      <c r="G165">
-        <v>0</v>
-      </c>
-      <c r="H165">
-        <v>1</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26507,19 +26517,19 @@
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>0</v>
    